--- a/business_architecture/ontology/build/output/step3c-definition-authoring-workbook.xlsx
+++ b/business_architecture/ontology/build/output/step3c-definition-authoring-workbook.xlsx
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Review &amp; authoring'!$A$1:$AD$504</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Controlled vocabularies'!$A$3:$C$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Reference register'!$A$7:$I$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Reference register'!$A$7:$I$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'External mappings'!$A$8:$K$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1752,18 +1752,85 @@
           <t>no meaningful APQC candidate</t>
         </is>
       </c>
-      <c r="U11" s="5" t="n"/>
-      <c r="V11" s="5" t="n"/>
-      <c r="W11" s="5" t="n"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Assign available crude and feedstock cargoes, grades, and volumes to specific refineries and receipt windows so each site's approved production plan can be met at the best delivered economics across the region.</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Covers the recurring allocation of secured or available crude and feedstock supply across competing refinery destinations, including grade-to-site matching, volume splits, timing of receipt windows, and reallocation when supply or plan assumptions change. Excludes crude purchase, negotiation, and trade execution, owned by Supply And Trading; excludes vessel, pipeline, and terminal movement execution, owned by Midstream; excludes the refinery's internal decision on which tanks and units process an allocated grade, owned by Refining.</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Grade-to-refinery assignment | volume split across sites | receipt-window timing | reallocation on supply disruption or plan change | allocation of term and spot volumes against planned refinery slates</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>Crude purchasing and trade execution (Supply And Trading) | physical movement, berth and pipeline scheduling (Midstream) | unit-level crude processing decisions (Refining) | refinery slate economics selection (Refinery Planning)</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Crude Allocation | Feedstock Allocation | Crude &amp; Feedstock Allocation</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>Allocate Term Crude Volumes | Allocate Spot Crude Volumes | Reallocate Crude on Supply Disruption</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Label retains the existing “Decision” suffix, but the concept is authored as the recurring allocation process, not the decision record or its output. A later naming pass should consider “Allocate Crude &amp; Feedstock” for verb consistency with sibling labels; not changed in this batch. The boundary against Supply And Trading follows the locked SCM/Commercial rule: this concept places already-secured supply and does not choose counterparty, price, or contract.</t>
+        </is>
+      </c>
+      <c r="U11" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V11" s="5" t="inlineStr">
+        <is>
+          <t>Decide which refinery receives which crude and feedstock volumes, and when, so the regional plan is met at best delivered economics.</t>
+        </is>
+      </c>
+      <c r="W11" s="5" t="inlineStr">
+        <is>
+          <t>SRC-CMU-REFPLAN-001 | SRC-SNF-REFPS-001 | SRC-EIA-GLOSS-001</t>
+        </is>
+      </c>
       <c r="X11" s="5" t="n"/>
-      <c r="Y11" s="5" t="n"/>
-      <c r="Z11" s="5" t="n"/>
-      <c r="AA11" s="5" t="n"/>
-      <c r="AB11" s="5" t="n"/>
-      <c r="AC11" s="5" t="n"/>
+      <c r="Y11" s="5" t="inlineStr">
+        <is>
+          <t>approved refinery production plan | secured and available crude supply position | crude and feedstock quality assays | delivered-cost and freight economics | refinery receipt and storage constraints</t>
+        </is>
+      </c>
+      <c r="Z11" s="5" t="inlineStr">
+        <is>
+          <t>approved crude and feedstock allocation to refineries and receipt windows</t>
+        </is>
+      </c>
+      <c r="AA11" s="5" t="inlineStr">
+        <is>
+          <t>informed-by: Refinery Planning | constrained-by: Inventory | precedes: Refinery Scheduling</t>
+        </is>
+      </c>
+      <c r="AB11" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC11" s="5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -1831,18 +1898,85 @@
           <t>no meaningful APQC candidate</t>
         </is>
       </c>
-      <c r="U12" s="5" t="n"/>
-      <c r="V12" s="5" t="n"/>
-      <c r="W12" s="5" t="n"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Assign available finished-product supply to markets, channels, terminals, and customer commitments for a planning period, so limited or constrained volumes are placed where they best serve contractual obligations and regional margin.</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Covers plan-level placement of finished product across markets, channels, and supply points, including the commercial priority rules applied when available supply cannot meet all demand, and reallocation when supply, demand, or logistics change. Excludes order-level allocation and release against an individual customer order, owned by Order Management; excludes rack and terminal loading allocation enforcement, owned by Terminal Loading; excludes physical movement and delivery execution, owned by Midstream and Distribution.</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Market and channel volume placement | supply-point-to-demand-point assignment | commercial priority rules under constrained supply | exchange and third-party placement within the plan | reallocation on plan change</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Order-level allocation and release (Allocate &amp; Release Order, Order Management) | rack and terminal allocation enforcement (Manage Allocation, Terminal Loading) | sales-target setting (Determine &amp; Allocate Sales Targets, Marketing) | pricing and offer construction (Commercial &amp; Marketing pricing processes) | physical delivery (Midstream, Distribution)</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>Product Allocation | Finished Product Allocation | Supply Allocation</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>Define Product Allocation Priority Rules | Allocate Constrained Product Supply | Allocate Exchange &amp; Third-Party Volumes</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Three allocation concepts coexist at different grains and are deliberately bounded here: plan-level placement (this node), order-level allocation and release (Order Management), and loading-time allocation enforcement (Terminal Loading). The “Decision” suffix is retained pending the same naming pass noted on CM-1-1-2-10.</t>
+        </is>
+      </c>
+      <c r="U12" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V12" s="5" t="inlineStr">
+        <is>
+          <t>Decide where available finished product is placed across markets, channels, and supply points to protect commitments and regional margin.</t>
+        </is>
+      </c>
+      <c r="W12" s="5" t="inlineStr">
+        <is>
+          <t>SRC-ASCM-CSCP-001 | SRC-SNF-REFPS-001 | SRC-EIA-GLOSS-001</t>
+        </is>
+      </c>
       <c r="X12" s="5" t="n"/>
-      <c r="Y12" s="5" t="n"/>
-      <c r="Z12" s="5" t="n"/>
-      <c r="AA12" s="5" t="n"/>
-      <c r="AB12" s="5" t="n"/>
-      <c r="AC12" s="5" t="n"/>
+      <c r="Y12" s="5" t="inlineStr">
+        <is>
+          <t>demand forecast | available and planned production | inventory position | contractual and regulatory supply obligations | logistics and terminal capacity | netback and margin economics</t>
+        </is>
+      </c>
+      <c r="Z12" s="5" t="inlineStr">
+        <is>
+          <t>approved finished-product allocation plan by market, channel, and supply point</t>
+        </is>
+      </c>
+      <c r="AA12" s="5" t="inlineStr">
+        <is>
+          <t>informed-by: Demand Forecasting | constrained-by: Inventory | enables: Order Management | enables: Terminal Loading</t>
+        </is>
+      </c>
+      <c r="AB12" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC12" s="5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -1910,18 +2044,85 @@
           <t>strong APQC candidate but no validator agreed</t>
         </is>
       </c>
-      <c r="U13" s="5" t="n"/>
-      <c r="V13" s="5" t="n"/>
-      <c r="W13" s="5" t="n"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Create, maintain, and retire the reference and parameter data that the regional supply-planning model depends on — such as planning network, sourcing, capacity, lead-time, yield, and product-grouping data — so planning results remain accurate and reproducible.</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Covers stewardship of supply-planning-specific reference and parameter data over its lifecycle, including requesting and validating changes, applying effective dates, and confirming that planning results remain consistent after a change. Excludes enterprise master-data policy, standards, and governance, which sit with the Data Governance workstream; excludes customer, price, product, tax, and location master data, owned by Manage Master Data under Order Management; excludes production-scheduling master data, owned by Maintain Production Scheduling Master Data under Refinery Scheduling.</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Planning network and location data | sourcing and supply-path data | planning capacity and rate parameters | lead times and transit assumptions | planning yields and product groupings | change request, validation, and effective dating of planning parameters</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Enterprise master-data policy and governance standards (Data Governance) | customer, price, product, tax, and location master data (Manage Master Data, Order Management) | production-scheduling master data (Maintain Production Scheduling Master Data, Refinery Scheduling) | demand-forecast master data preparation (Prepare Master Data To Create Demand Forecast, Demand Forecasting) | planning application administration and platform support (Process Excellence &amp; IT)</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>Supply Planning Reference Data Maintenance | Planning Parameter Maintenance</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>Maintain Planning Network Data | Maintain Planning Capacity &amp; Rate Parameters | Maintain Planning Yield Data</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Defined narrowly per Hamid's decision (2026-09-18, Option 1): scope is the supply-planning-specific reference and parameter data consumed by the regional planning model, not master data generally. The taxonomy currently carries four parallel master-data nodes — this one, Maintain Production Scheduling Master Data (CM-1-1-7-2-1), Manage Master Data (CM-1-3-7-1), and Prepare Master Data To Create Demand Forecast (CM-1-1-1-1-1). Their consolidation, and whether a single governed master-data capability should own them, is parked for the EPM Data Governance workstream and is deliberately not resolved here. APQC candidate “Maintain master data” was triaged STRONG but accepted by no validator; used as comparative evidence only, not adopted.</t>
+        </is>
+      </c>
+      <c r="U13" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V13" s="5" t="inlineStr">
+        <is>
+          <t>Keep the reference and parameter data behind regional supply planning accurate, current, and reproducible.</t>
+        </is>
+      </c>
+      <c r="W13" s="5" t="inlineStr">
+        <is>
+          <t>SRC-ASCM-CSCP-001</t>
+        </is>
+      </c>
       <c r="X13" s="5" t="n"/>
-      <c r="Y13" s="5" t="n"/>
-      <c r="Z13" s="5" t="n"/>
-      <c r="AA13" s="5" t="n"/>
-      <c r="AB13" s="5" t="n"/>
-      <c r="AC13" s="5" t="n"/>
+      <c r="Y13" s="5" t="inlineStr">
+        <is>
+          <t>planning parameter change requests | network, capacity, and sourcing changes | refinery and logistics capability updates | product and grade structure changes | enterprise data-governance standards</t>
+        </is>
+      </c>
+      <c r="Z13" s="5" t="inlineStr">
+        <is>
+          <t>validated and effective-dated supply-planning reference and parameter data</t>
+        </is>
+      </c>
+      <c r="AA13" s="5" t="inlineStr">
+        <is>
+          <t>enables: Regional Optimization | governed-by: Data Governance | informed-by: Refinery Planning</t>
+        </is>
+      </c>
+      <c r="AB13" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC13" s="5" t="inlineStr">
+        <is>
+          <t>periodic</t>
+        </is>
+      </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -1989,18 +2190,85 @@
           <t>strong APQC candidate but no validator agreed</t>
         </is>
       </c>
-      <c r="U14" s="5" t="n"/>
-      <c r="V14" s="5" t="n"/>
-      <c r="W14" s="5" t="n"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Set and optimize the planned finished-product inventory levels and positions for the regional plan period, balancing supply availability, demand coverage, and working-capital cost within established inventory policy and storage constraints.</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Covers the planning decision on how much finished product should be held, in which grades, and at which supply points and terminals across the regional plan horizon, including target and minimum operating positions, seasonal and pre-build positions, and the inventory consequences of allocation and production choices. Excludes the setting of inventory policy itself, and excludes inventory measurement, reconciliation, replenishment, consignment, commingled, and re-brand inventory management, all owned by the Inventory cluster under Distribution Planning &amp; Scheduling. Excludes physical storage operation, owned by Midstream.</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Planned finished-product inventory targets by grade and location | minimum operating and safety positions within policy | seasonal and pre-build inventory positioning | inventory implications of allocation and production plan choices | working-capital and storage-cost trade-offs in the plan</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Finished-product inventory policy setting (Develop Finished Product Inventory Policy, Inventory) | inventory measurement and reconciliation (Inventory) | replenishment execution (Manage Inventory Replenishment, Inventory) | consignment, commingled, lot/batch, and re-brand inventory management (Inventory) | physical tank and terminal storage operation (Midstream)</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Finished Goods Inventory Planning | Finished Product Inventory Planning</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>Set Regional Inventory Targets | Plan Seasonal Inventory Build | Plan Inventory for Constrained Supply</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Boundary resolved per Hamid's decision (2026-09-18, Option 1): this node owns the planned inventory level and position inside the regional plan, while the Inventory cluster under Distribution Planning &amp; Scheduling (CM-1-1-3-7) retains policy, measurement, reconciliation, and replenishment. This preserves both approved scope notes — Regional Optimization explicitly names “inventory positioning” — and the locked SCM rule, by separating the plan-period target decision from ongoing inventory management. No tree change required. “Finished goods” retained from the existing label although “finished product” is the more common downstream term; alt labels carry both.</t>
+        </is>
+      </c>
+      <c r="U14" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V14" s="5" t="inlineStr">
+        <is>
+          <t>Decide how much finished product should be held, in which grades, and where, across the regional plan horizon.</t>
+        </is>
+      </c>
+      <c r="W14" s="5" t="inlineStr">
+        <is>
+          <t>SRC-ASCM-CSCP-001 | SRC-SNF-REFPS-001</t>
+        </is>
+      </c>
       <c r="X14" s="5" t="n"/>
-      <c r="Y14" s="5" t="n"/>
-      <c r="Z14" s="5" t="n"/>
-      <c r="AA14" s="5" t="n"/>
-      <c r="AB14" s="5" t="n"/>
-      <c r="AC14" s="5" t="n"/>
+      <c r="Y14" s="5" t="inlineStr">
+        <is>
+          <t>demand forecast | planned production and supply availability | approved inventory policy | storage and terminal capacity | product specifications and seasonal grade changes | working-capital and storage-cost assumptions</t>
+        </is>
+      </c>
+      <c r="Z14" s="5" t="inlineStr">
+        <is>
+          <t>approved planned finished-product inventory targets and positions for the plan period</t>
+        </is>
+      </c>
+      <c r="AA14" s="5" t="inlineStr">
+        <is>
+          <t>constrained-by: Inventory | informed-by: Demand Forecasting | informed-by: Refinery Planning | enables: Product Allocation Decision</t>
+        </is>
+      </c>
+      <c r="AB14" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC14" s="5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -4240,10 +4508,27 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U43" s="5" t="n"/>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>PARKED TREE CHANGE — no definition authored (2026-09-18). See business_architecture/ontology/step3c-parked-tree-changes.md, entry PTC-001, for the full proposal and the steps required to close it. This node carries no local meaning of its own: its three L5 children (Develop Strategic Business Plan, Plan Budgets, Manage Site Specific Business Risk) are not refinery production-planning activities, and Plan Budgets contradicts the locked rule that Finance owns financial governance. Authoring a definition here would silently endorse budgeting and strategic planning under Refinery Planning. Handled the same way as the parked IT Services reparenting question on CM-1, rather than churning the tree during a definition pass. The three L5 children are left untouched and remain pending.</t>
+        </is>
+      </c>
+      <c r="U43" s="5" t="inlineStr">
+        <is>
+          <t>mixed/needs-review</t>
+        </is>
+      </c>
       <c r="V43" s="5" t="n"/>
       <c r="W43" s="5" t="n"/>
-      <c r="X43" s="5" t="n"/>
+      <c r="X43" s="5" t="inlineStr">
+        <is>
+          <t>Question: Should "Commercial Development" remain a child of Refinery Planning, and if so, what is its scope?
+Context: Parent CM-1-1-4 Refinery Planning is approved as the commercially optimal refinery production plan (crude slate, throughput, yield, and specification targets). This node's three L5 children are Develop Strategic Business Plan (CM-1-1-4-6-1), Plan Budgets (CM-1-1-4-6-2), and Manage Site Specific Business Risk (CM-1-1-4-6-3). None is a refinery production-planning activity. Plan Budgets conflicts with the locked Finance boundary. The label itself came from a WEAK / REVIEW LINK APQC match ("Manage employee development") and carries no local meaning. Two of the three children have no existing owner in the tree: there is no Strategy node among the L1 domains, and the only risk nodes are Credit Risk and Market Risk under Supply And Trading, with EHS owning EHS risk only.
+Options: A) Retire the node from Refinery Planning, reparent Plan Budgets to Finance, and create two new nodes outside Planning &amp; Scheduling for the strategic-plan and site-risk children. B) Redefine narrowly as site commercial business development and reparent all three children elsewhere. C) Retire the node and reparent each child individually with no replacement parent.
+Evidence: Approved CM-1-1-4 definition and scope note; locked Finance and EHS boundary rules; Step 3b review_notes recording the weak APQC match; SRC-SNF-REFPS-001 on separation of strategic, planning, and scheduling horizons.
+Recommendation: Option A, parked as a tree-change proposal for the consolidated repo-JSON pass rather than a definition authored now. Accepted by Hamid 2026-09-18; tracked as PTC-001 in step3c-parked-tree-changes.md.</t>
+        </is>
+      </c>
       <c r="Y43" s="5" t="n"/>
       <c r="Z43" s="5" t="n"/>
       <c r="AA43" s="5" t="n"/>
@@ -4556,18 +4841,85 @@
           <t>no meaningful APQC candidate</t>
         </is>
       </c>
-      <c r="U47" s="5" t="n"/>
-      <c r="V47" s="5" t="n"/>
-      <c r="W47" s="5" t="n"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Run the recurring economic-optimization cycle that produces the refinery production plan — assembling the case basis, building and running optimization cases, analyzing scenarios, and selecting the economically preferred production case for approval.</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>Covers the optimization cycle inside Refinery Planning: gathering the demand, crude availability, price, constraint, inventory, and current-plan basis for a case; building and running the optimization model; comparing alternatives through scenario analysis; and recommending the economically preferred case. Accountability for the approved production plan and its commercial targets remains with Refinery Planning. Excludes detailed unit-operation scheduling, tank and transfer line-ups, blend execution, and process control, owned by Refining; excludes optimization-model and application administration, owned by Process Excellence &amp; IT.</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Assemble case basis from demand, crude availability, price, constraints, inventory, and current plan | build and run optimization cases | scenario and sensitivity analysis | compare production alternatives on margin | recommend the economically preferred production case</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>Approval and ownership of the production plan and its commercial targets (Refinery Planning) | detailed unit scheduling, tank line-ups, and blend execution (Refining, Refinery Scheduling) | process control and operational departures from plan (Refining) | optimization application administration and model platform support (Process Excellence &amp; IT) | real-time and closed-loop unit optimization (Refining)</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>Refinery Economic Optimization | Refinery Plan Optimization | Refinery LP Optimization</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>Build Optimization Case | Validate Case Basis | Recommend Preferred Production Case</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Parent-versus-child distinctness resolved per Hamid's decision (2026-09-18, Option 1): Refinery Planning (CM-1-1-4) owns the approved plan and its commercial targets; this node owns the recurring optimization run cycle that produces the candidate plan. Without that split the two primary purposes were near-identical. The eight existing L5 children — six “Capture …” nodes, Evaluate Crude &amp; Feedstock, and Perform Scenario Analysis — are coherent under this reading as case-basis assembly and case analysis. “Capture Monthly Operating Plan” (CM-1-1-4-7-7) appears to name a document rather than a process and is flagged for review in the L5 batch, not resolved here. Avoided naming a specific optimization application; “LP” appears only as an alternate label because it is established industry shorthand.</t>
+        </is>
+      </c>
+      <c r="U47" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V47" s="5" t="inlineStr">
+        <is>
+          <t>Produce and recommend the economically preferred refinery production case for the planning period.</t>
+        </is>
+      </c>
+      <c r="W47" s="5" t="inlineStr">
+        <is>
+          <t>SRC-CMU-REFPLAN-001 | SRC-SNF-REFPS-001 | SRC-EIA-GLOSS-001</t>
+        </is>
+      </c>
       <c r="X47" s="5" t="n"/>
-      <c r="Y47" s="5" t="n"/>
-      <c r="Z47" s="5" t="n"/>
-      <c r="AA47" s="5" t="n"/>
-      <c r="AB47" s="5" t="n"/>
-      <c r="AC47" s="5" t="n"/>
+      <c r="Y47" s="5" t="inlineStr">
+        <is>
+          <t>product demand requirements | crude and feedstock availability and assays | crude, feedstock, and product prices | refinery capacity and operating constraints | inventory position | current approved operating plan</t>
+        </is>
+      </c>
+      <c r="Z47" s="5" t="inlineStr">
+        <is>
+          <t>recommended economically preferred refinery production case with supporting scenario analysis</t>
+        </is>
+      </c>
+      <c r="AA47" s="5" t="inlineStr">
+        <is>
+          <t>enables: Refinery Planning | informed-by: Demand Forecasting | informed-by: Crude Allocation Decision | constrained-by: Inventory | precedes: Refinery Scheduling</t>
+        </is>
+      </c>
+      <c r="AB47" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC47" s="5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AD47" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -41166,7 +41518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -41544,8 +41896,196 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>SRC-EIA-GLOSS-001</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>U.S. Energy Information Administration</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Glossary and petroleum table definitions</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Accessed 2026-09-18</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>https://www.eia.gov/tools/glossary/</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>Government statistical authority</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>Standard US downstream terminology; evidence only, not text to copy</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>Refinery, crude slate, capacity, and product-category terminology</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>SRC-ASCM-CSCP-001</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Association for Supply Chain Management</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>CSCP Exam Content Manual</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>Current edition, accessed 2026-09-18</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>https://www.ascm.org/globalassets/ascm_website_assets/docs/ecm/ecm-cscp.pdf</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>Professional standards body</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>Supply-chain planning terminology; evidence only</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>Allocation, master-data, inventory-planning, and S&amp;OP terminology</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>SRC-CMU-REFPLAN-001</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Carnegie Mellon University (Su, Grossmann et al.)</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Modeling for Integrated Refinery Planning with Crude-oil Scheduling</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Accessed 2026-09-18</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>https://egon.cheme.cmu.edu/Papers/Su_IntegratedRefineryPlanning.pdf</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>Peer-reviewed academic</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>Planning-versus-scheduling decision separation; evidence only</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>Crude allocation, slate selection, and refinery optimization cycle</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>SRC-SNF-REFPS-001</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Institute for Research in Economics and Business Administration (SNF)</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Refinery planning and scheduling</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>Report R29/08, accessed 2026-09-18</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>https://snf.no/media/2uvkatl3/r29_08.pdf</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>Academic research institute</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>Planning hierarchy and horizon separation; evidence only</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>Strategic, planning, and scheduling horizon boundaries in refining</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A7:I13"/>
+  <autoFilter ref="A7:I17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/business_architecture/ontology/build/output/step3c-definition-authoring-workbook.xlsx
+++ b/business_architecture/ontology/build/output/step3c-definition-authoring-workbook.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here — Decisions &amp; Phases" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review &amp; authoring" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Column guide" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Controlled vocabularies" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference register" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="External mappings" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Start Here — Decisions &amp; Phases" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Review &amp; authoring" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Column guide" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Controlled vocabularies" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Reference register" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="External mappings" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Review &amp; authoring'!$A$1:$AD$504</definedName>
@@ -40991,6 +40991,11 @@
           <t>skos:definition (required on every concept; @en)</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Phase 1 — required</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
@@ -41000,12 +41005,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>Coverage list + boundary sentences: what it includes, what it explicitly excludes, and which sibling owns the excluded part.</t>
+          <t>Coverage plus at least one meaningful boundary. Name exclusions and owners only when ambiguity is material and the owner is already in the taxonomy. Do not manufacture boilerplate exclusions.</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
           <t>skos:scopeNote (@en)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Phase 1 — required</t>
         </is>
       </c>
     </row>
@@ -41025,6 +41035,11 @@
           <t>folded into skos:scopeNote</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Phase 1 — supporting</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -41034,12 +41049,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Activities/cases that do NOT belong here + who owns them instead — feeds the scope note's exclusion list.</t>
+          <t>Activities or cases that do not belong here. Name the owning sibling or domain only when it is already established. Otherwise ask in open_questions and leave pending.</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
           <t>folded into skos:scopeNote</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Phase 1 — supporting</t>
         </is>
       </c>
     </row>
@@ -41059,6 +41079,11 @@
           <t>skos:altLabel (@en)</t>
         </is>
       </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Phase 1 — supporting</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -41068,12 +41093,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Future narrower concepts spotted while defining, separated by |. Become new nodes in a later modeling pass.</t>
+          <t>Future narrower concepts spotted while defining, separated by |. Become new nodes in a later modeling pass. Tree moves of existing nodes go in step3c-parked-tree-changes.md, not here.</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
           <t>future skos:narrower concepts; consolidated repo-JSON proposal</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Phase 1 — supporting</t>
         </is>
       </c>
     </row>
@@ -41085,12 +41115,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Wording decisions (e.g. 'production horizons' not 'run schedules') so they don't get reopened.</t>
+          <t>Wording and modeling decisions (e.g. 'production horizons' not 'run schedules') so they don't get reopened. Structured questions for Hamid go in open_questions.</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
           <t>editorial note in the decision log / JSON record</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Phase 1 — supporting</t>
         </is>
       </c>
     </row>
@@ -41102,12 +41137,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>pending → approved. Only approved rows merge into the taxonomy.</t>
+          <t>pending → approved when the row passes all checks. blocked / retired only after Hamid parks or a PTC retires the node. Only approved rows merge.</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
           <t>workflow control; merged via step3-skos-taxonomy.py --authored</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Workflow — pending | approved | blocked | retired</t>
         </is>
       </c>
     </row>
@@ -41132,6 +41172,11 @@
       <c r="A11" s="8" t="inlineStr">
         <is>
           <t>Semantic-intake fields added in the Step 3c intake evolution</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Added in #31. Required on new approvals. The 15 #29 approved rows are grandfathered until a later backfill; the validator flags them as NOTE, not BLOCKING. RDF is not emitted from these fields yet.</t>
         </is>
       </c>
     </row>

--- a/business_architecture/ontology/build/output/step3c-definition-authoring-workbook.xlsx
+++ b/business_architecture/ontology/build/output/step3c-definition-authoring-workbook.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Start Here — Decisions &amp; Phases" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Review &amp; authoring" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Column guide" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Controlled vocabularies" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Reference register" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="External mappings" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here — Decisions &amp; Phases" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review &amp; authoring" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Column guide" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Controlled vocabularies" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference register" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="External mappings" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Review &amp; authoring'!$A$1:$AD$504</definedName>
@@ -4987,18 +4987,80 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U48" s="5" t="n"/>
-      <c r="V48" s="5" t="n"/>
-      <c r="W48" s="5" t="n"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Assemble the demand requirements that the refinery production case must satisfy — by product, volume, quality grade, location, and delivery period — drawing on the approved demand forecast, firm contractual commitments, and internal transfer requirements for the planning period.</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>Covers converting demand signals into the demand basis of an optimization case: selecting the applicable forecast version, adding firm contractual and internal transfer obligations, reconciling units and product grades to planning definitions, and confirming the basis with the demand owner. Excludes producing or owning the forecast itself, which belongs to Demand Forecasting (CM-1-1-1-1) and Refined Product Demand Management (CM-1-2-6-2). Excludes capturing or committing customer orders, owned by Order Management (CM-1-3-7).</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Select the applicable approved demand forecast version | add firm contractual and term commitments | add internal and inter-refinery transfer requirements | reconcile product grades, units, and periods to planning definitions | confirm the agreed demand basis for the case</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>Producing or owning the demand forecast, owned by Demand Forecasting (CM-1-1-1-1) | forecasting refined product demand, owned by Forecast Refined Product Demand (CM-1-2-6-2-3) | capturing and committing customer orders, owned by Order Management (CM-1-3-7) | negotiating the underlying customer commitment, owned by Commercial &amp; Marketing sales | placing supply against demand, owned by Product Allocation Decision (CM-1-1-2-11)</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>Capture Demand Basis | Establish Product Demand Requirements | Demand Basis Capture</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Batch 02 (2026-09-18). Read as a case-basis assembly step inside the CM-1-1-4-7 Refinery Optimization run cycle: this node establishes one input of the optimization case, it does not own the underlying business decision or the source data. Sibling “Capture …” nodes were defined together so their boundaries partition the case basis without overlap. “Requirements” is read as the obligations the plan must meet, not as product specification requirements. Verb kept as the taxonomy label “Capture”; “Receive Demand Forecast” (CM-1-2-1-1-2) is the existing precedent for a consume-not-produce node.</t>
+        </is>
+      </c>
+      <c r="U48" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V48" s="5" t="inlineStr">
+        <is>
+          <t>Establish the agreed demand basis the refinery production case must satisfy.</t>
+        </is>
+      </c>
+      <c r="W48" s="5" t="inlineStr">
+        <is>
+          <t>SRC-EIA-LFMM-001 | SRC-BJCE-REFPS-001 | SRC-ASCM-CSCP-001</t>
+        </is>
+      </c>
       <c r="X48" s="5" t="n"/>
-      <c r="Y48" s="5" t="n"/>
-      <c r="Z48" s="5" t="n"/>
-      <c r="AA48" s="5" t="n"/>
-      <c r="AB48" s="5" t="n"/>
-      <c r="AC48" s="5" t="n"/>
+      <c r="Y48" s="5" t="inlineStr">
+        <is>
+          <t>approved demand forecast | firm contracts and term commitments | internal and inter-refinery transfer requirements | product grade and specification definitions</t>
+        </is>
+      </c>
+      <c r="Z48" s="5" t="inlineStr">
+        <is>
+          <t>agreed product demand basis for the refinery optimization case</t>
+        </is>
+      </c>
+      <c r="AA48" s="5" t="inlineStr">
+        <is>
+          <t>enables: Refinery Optimization | informed-by: Demand Forecasting | informed-by: Refined Product Demand Management | precedes: Perform Scenario Analysis</t>
+        </is>
+      </c>
+      <c r="AB48" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC48" s="5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AD48" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -5066,18 +5128,80 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U49" s="5" t="n"/>
-      <c r="V49" s="5" t="n"/>
-      <c r="W49" s="5" t="n"/>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>Assess candidate crude oils and feedstocks for processing suitability and economic value in the planning period, using assay and quality data, expected yields against the refinery configuration, and delivered-cost economics, to produce the evaluated set available to the optimization case.</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>Covers technical and economic screening of candidate crudes and feedstocks for planning: confirming assay and quality data is current and complete, estimating yields and processing fit against unit configuration and specification limits, valuing each candidate on a delivered-cost and netback basis, and flagging handling or compatibility issues. Excludes laboratory assay testing and certification, and excludes purchase, negotiation, and trade execution, owned by Supply And Trading (CM-1-2). Approval of the final crude slate remains with Refinery Planning (CM-1-1-4).</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Confirm assay and quality data currency and completeness | estimate yields and processing fit against refinery configuration | screen against specification and handling limits | value candidates on delivered cost and netback | rank and publish the evaluated crude and feedstock set</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>Purchasing, negotiating, and executing crude and feedstock trades, owned by Supply And Trading (CM-1-2) | laboratory assay testing and certification, owned by Refining laboratory services | approving the final crude slate, owned by Refinery Planning (CM-1-1-4) | placing secured crude across refineries, owned by Crude Allocation Decision (CM-1-1-2-10) | crude and feedstock master data stewardship, owned by Manage feedstock Data Quality (CM-1-2-5-1-1)</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>Evaluate Crude &amp; Feedstock Slate Candidates | Crude Assay Evaluation | Crude Screening</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Batch 02 (2026-09-18). Read as a case-basis assembly step inside the CM-1-1-4-7 Refinery Optimization run cycle: this node establishes one input of the optimization case, it does not own the underlying business decision or the source data. Sibling “Capture …” nodes were defined together so their boundaries partition the case basis without overlap. Boundary against “Plan Optimal Feedstock Slate And Run Rate” (CM-1-2-5-2-3) under Supply And Trading is unresolved: on its label that node duplicates the approved Refinery Planning accountability for slate and throughput targets. Raised as PTC-002 in step3c-parked-tree-changes.md and deliberately not reconciled here, since resolving it is a tree change. This node is bounded as evaluation only, so it does not depend on that outcome.</t>
+        </is>
+      </c>
+      <c r="U49" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V49" s="5" t="inlineStr">
+        <is>
+          <t>Produce the technically and economically evaluated crude and feedstock set for the planning period.</t>
+        </is>
+      </c>
+      <c r="W49" s="5" t="inlineStr">
+        <is>
+          <t>SRC-EIA-LFMM-001 | SRC-BJCE-REFPS-001 | SRC-CMU-REFPLAN-001</t>
+        </is>
+      </c>
       <c r="X49" s="5" t="n"/>
-      <c r="Y49" s="5" t="n"/>
-      <c r="Z49" s="5" t="n"/>
-      <c r="AA49" s="5" t="n"/>
-      <c r="AB49" s="5" t="n"/>
-      <c r="AC49" s="5" t="n"/>
+      <c r="Y49" s="5" t="inlineStr">
+        <is>
+          <t>crude and feedstock assays and quality data | refinery configuration and unit capability | product specification limits | delivered cost, freight, and differential data | candidate supply offers</t>
+        </is>
+      </c>
+      <c r="Z49" s="5" t="inlineStr">
+        <is>
+          <t>evaluated and ranked crude and feedstock set with yield and value estimates</t>
+        </is>
+      </c>
+      <c r="AA49" s="5" t="inlineStr">
+        <is>
+          <t>enables: Refinery Optimization | uses-input: Capture Crude Availability | uses-input: Capture Product/Crude/Feedstock Price | constrained-by: Capture Refinery Level Constraints</t>
+        </is>
+      </c>
+      <c r="AB49" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC49" s="5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AD49" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -5145,18 +5269,80 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U50" s="5" t="n"/>
-      <c r="V50" s="5" t="n"/>
-      <c r="W50" s="5" t="n"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Establish which crude and feedstock volumes can realistically be secured and delivered inside the planning period — by grade, source, and arrival window — covering already-contracted supply, term liftings, and credible spot opportunities.</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>Covers the supply-side volume basis of an optimization case: confirming contracted and term volumes, identifying credible additional spot availability, and stating arrival windows and any logistics or quality qualifications. Establishes what is available, not what is bought or where it is sent. Excludes securing supply and executing trades, owned by Supply And Trading (CM-1-2); excludes arrival and delivery scheduling, owned by Plan Feedstock Arrival (CM-1-2-5-3-3); excludes placing secured supply across refineries, owned by Crude Allocation Decision (CM-1-1-2-10).</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Confirm contracted and term supply volumes and lifting windows | identify credible incremental spot availability | state arrival windows and delivery qualifications | flag logistics, quality, or compatibility limits on availability | publish the available supply basis for the case</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>Securing, negotiating, and executing supply, owned by Supply And Trading (CM-1-2) | scheduling arrivals and deliveries, owned by Plan Feedstock Arrival (CM-1-2-5-3-3) and Schedule Feedstock Delivery (CM-1-2-5-3-2) | placing secured crude across refineries, owned by Crude Allocation Decision (CM-1-1-2-10) | judging processing suitability or value, owned by Evaluate Crude &amp; Feedstock (CM-1-1-4-7-2) | managing feedstock inventory, owned by Manage Feedstock Inventory (CM-1-2-5-4-2)</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>Capture Crude &amp; Feedstock Availability | Establish Supply Availability | Crude Availability Basis</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Batch 02 (2026-09-18). Read as a case-basis assembly step inside the CM-1-1-4-7 Refinery Optimization run cycle: this node establishes one input of the optimization case, it does not own the underlying business decision or the source data. Sibling “Capture …” nodes were defined together so their boundaries partition the case basis without overlap. Availability is the volume-and-timing basis; suitability and value sit in Evaluate Crude &amp; Feedstock (CM-1-1-4-7-2), and the placement decision sits in the approved Crude Allocation Decision (CM-1-1-2-10). The taxonomy label says “Crude”; feedstock is included because the sibling optimization basis and the parent scope both treat them together.</t>
+        </is>
+      </c>
+      <c r="U50" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V50" s="5" t="inlineStr">
+        <is>
+          <t>Establish the crude and feedstock volumes and arrival windows available to the planning period.</t>
+        </is>
+      </c>
+      <c r="W50" s="5" t="inlineStr">
+        <is>
+          <t>SRC-EIA-LFMM-001 | SRC-BJCE-REFPS-001 | SRC-EIA-GLOSS-001</t>
+        </is>
+      </c>
       <c r="X50" s="5" t="n"/>
-      <c r="Y50" s="5" t="n"/>
-      <c r="Z50" s="5" t="n"/>
-      <c r="AA50" s="5" t="n"/>
-      <c r="AB50" s="5" t="n"/>
-      <c r="AC50" s="5" t="n"/>
+      <c r="Y50" s="5" t="inlineStr">
+        <is>
+          <t>term and spot supply contracts | lifting and nomination schedules | supplier availability advice | marine and pipeline logistics availability | port and tankage receipt limits</t>
+        </is>
+      </c>
+      <c r="Z50" s="5" t="inlineStr">
+        <is>
+          <t>available crude and feedstock supply basis by grade, source, and arrival window</t>
+        </is>
+      </c>
+      <c r="AA50" s="5" t="inlineStr">
+        <is>
+          <t>enables: Refinery Optimization | enables: Evaluate Crude &amp; Feedstock | informed-by: Supply And Trading | constrained-by: Capture Refinery Level Constraints</t>
+        </is>
+      </c>
+      <c r="AB50" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC50" s="5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AD50" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -5224,18 +5410,80 @@
           <t>no meaningful APQC candidate</t>
         </is>
       </c>
-      <c r="U51" s="5" t="n"/>
-      <c r="V51" s="5" t="n"/>
-      <c r="W51" s="5" t="n"/>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Establish the price and economic assumption set used to value crude, feedstock, and finished-product streams in the optimization case — market reference prices, quality and location differentials, freight, and internal transfer values — for the planning period.</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>Covers assembling and confirming the planning price basis: selecting reference quotations and forward curves, applying grade and location differentials and freight, setting internal transfer and intermediate stream values, and recording the assumption set so a case can be reproduced and later backcast. These are planning assumptions, not transactable prices. Excludes setting customer sales prices, owned by Sales Pricing Management (CM-1-3-6-3); excludes pricing strategy, owned by Pricing Strategy Management (CM-1-3-3-2); excludes price master data, owned by Maintain Price &amp; Discount Master Data (CM-1-3-7-1-2).</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Select reference price quotations and forward curves | apply quality, grade, and location differentials | apply freight and delivery cost assumptions | set internal transfer and intermediate stream values | record and version the price assumption set for the case</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>Setting and implementing customer sales prices, owned by Sales Pricing Management (CM-1-3-6-3) | pricing strategy and approach, owned by Pricing Strategy Management (CM-1-3-3-2) | price and discount master data stewardship, owned by Maintain Price &amp; Discount Master Data (CM-1-3-7-1-2) | price risk management and hedging, owned by Supply And Trading (CM-1-2-2) | transaction and invoice pricing, owned by Finance</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>Capture Planning Price Basis | Establish Price Assumptions | Price Assumption Capture</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Batch 02 (2026-09-18). Read as a case-basis assembly step inside the CM-1-1-4-7 Refinery Optimization run cycle: this node establishes one input of the optimization case, it does not own the underlying business decision or the source data. Sibling “Capture …” nodes were defined together so their boundaries partition the case basis without overlap. The distinction that matters is assumption versus transaction: this node sets the prices a case is evaluated against, while the Marketing and Sales pricing nodes set prices a customer actually pays. The recorded assumption set is also the contemporaneous basis the locked backcasting rule requires, since Regional and Distribution Backcasting compare actuals to the approved plan and its original assumptions, never a later reforecast.</t>
+        </is>
+      </c>
+      <c r="U51" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V51" s="5" t="inlineStr">
+        <is>
+          <t>Establish the reproducible price and economic assumption set used to value the optimization case.</t>
+        </is>
+      </c>
+      <c r="W51" s="5" t="inlineStr">
+        <is>
+          <t>SRC-EIA-LFMM-001 | SRC-BJCE-REFPS-001 | SRC-EIA-GLOSS-001</t>
+        </is>
+      </c>
       <c r="X51" s="5" t="n"/>
-      <c r="Y51" s="5" t="n"/>
-      <c r="Z51" s="5" t="n"/>
-      <c r="AA51" s="5" t="n"/>
-      <c r="AB51" s="5" t="n"/>
-      <c r="AC51" s="5" t="n"/>
+      <c r="Y51" s="5" t="inlineStr">
+        <is>
+          <t>published market quotations and forward curves | quality and location differentials | freight and logistics cost rates | internal transfer pricing policy | operating cost assumptions</t>
+        </is>
+      </c>
+      <c r="Z51" s="5" t="inlineStr">
+        <is>
+          <t>versioned price and economic assumption set for the planning period</t>
+        </is>
+      </c>
+      <c r="AA51" s="5" t="inlineStr">
+        <is>
+          <t>enables: Refinery Optimization | enables: Evaluate Crude &amp; Feedstock | informed-by: Supply And Trading | produces: contemporaneous assumption basis for Regional Backcasting</t>
+        </is>
+      </c>
+      <c r="AB51" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC51" s="5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AD51" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -5303,18 +5551,80 @@
           <t>no meaningful APQC candidate</t>
         </is>
       </c>
-      <c r="U52" s="5" t="n"/>
-      <c r="V52" s="5" t="n"/>
-      <c r="W52" s="5" t="n"/>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>Compile the limits a refinery production case must respect — unit capacities and rates, blending and product-specification limits, tankage and movement limits, and planned maintenance or turnaround outages — as the feasible operating envelope for the planning period.</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>Covers gathering, validating, and stating constraints in planning terms: confirming available unit capacity and rate limits including outage-adjusted availability, recording specification and blending limits, recording tankage and movement limits, and reconciling conflicting or stale limits with the constraint owner. Compiles limits set elsewhere; it does not set them. Excludes deciding maintenance and turnaround scope and timing, and excludes operating-limit ownership and process control, both owned by Refining. Excludes regulatory and permit limit ownership, owned by EHS &amp; Gov Reporting.</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Confirm unit capacity, rate, and outage-adjusted availability | record product specification and blending limits | record tankage, movement, and logistics limits | record contractual and regulatory volume limits as planning constraints | reconcile stale or conflicting limits with the constraint owner | publish the case operating envelope</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>Setting and owning unit operating limits and process control, owned by Refining | deciding maintenance and turnaround scope and timing, owned by Refining maintenance planning | owning regulatory, permit, and emissions limits, owned by EHS &amp; Gov Reporting | setting product specifications as an offer decision, owned by Offer Design &amp; Development (CM-1-3-3) | detailed unit scheduling within the envelope, owned by Refining</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>Capture Refinery Constraints | Establish Operating Envelope | Constraint Basis Capture</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Batch 02 (2026-09-18). Read as a case-basis assembly step inside the CM-1-1-4-7 Refinery Optimization run cycle: this node establishes one input of the optimization case, it does not own the underlying business decision or the source data. Sibling “Capture …” nodes were defined together so their boundaries partition the case basis without overlap. “Refinery level” is read as site-wide rather than unit-detail granularity, consistent with the locked boundary that Refinery Planning sets commercial production-plan targets while Refining owns detailed scheduling and execution. Compiling a constraint does not transfer ownership of it.</t>
+        </is>
+      </c>
+      <c r="U52" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V52" s="5" t="inlineStr">
+        <is>
+          <t>Establish the validated feasible operating envelope the production case must respect.</t>
+        </is>
+      </c>
+      <c r="W52" s="5" t="inlineStr">
+        <is>
+          <t>SRC-EIA-LFMM-001 | SRC-BJCE-REFPS-001 | SRC-CMU-REFPLAN-001</t>
+        </is>
+      </c>
       <c r="X52" s="5" t="n"/>
-      <c r="Y52" s="5" t="n"/>
-      <c r="Z52" s="5" t="n"/>
-      <c r="AA52" s="5" t="n"/>
-      <c r="AB52" s="5" t="n"/>
-      <c r="AC52" s="5" t="n"/>
+      <c r="Y52" s="5" t="inlineStr">
+        <is>
+          <t>unit capacity and rate limits | planned maintenance and turnaround schedule | product specification and blending limits | tankage, jetty, and pipeline capacity | regulatory, permit, and contractual limits</t>
+        </is>
+      </c>
+      <c r="Z52" s="5" t="inlineStr">
+        <is>
+          <t>validated refinery operating envelope and constraint set for the case</t>
+        </is>
+      </c>
+      <c r="AA52" s="5" t="inlineStr">
+        <is>
+          <t>enables: Refinery Optimization | constrained-by: Refining | informed-by: EHS &amp; Gov Reporting | constrains: Perform Scenario Analysis</t>
+        </is>
+      </c>
+      <c r="AB52" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC52" s="5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AD52" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -5377,18 +5687,80 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U53" s="5" t="n"/>
-      <c r="V53" s="5" t="n"/>
-      <c r="W53" s="5" t="n"/>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>Establish the inventory position the optimization case starts from and the closing position it must deliver — crude, intermediate, and finished-product volumes by location and grade — including any volume that is unavailable to the plan.</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>Covers stating inventory as a planning boundary condition: taking the opening position from the system of record, adjusting for in-transit and committed volume, separating working stock from unavailable volume such as tank bottoms, minimum operating stock, and consignment or commingled volume, and carrying in the required closing target. Excludes measuring and reconciling inventory, owned by Measure Inventory (CM-1-1-3-7-4) and Perform Inventory Reconciliation (CM-1-1-3-7-5). Excludes inventory policy, owned by the Inventory cluster (CM-1-1-3-7). Excludes setting the plan-period finished-goods target, owned by Plan Finished Goods Inventory (CM-1-1-2-13).</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Take the opening inventory position from the system of record | adjust for in-transit and already-committed volume | separate working stock from unavailable volume | carry in the required closing inventory target | state inventory assumptions and qualifications for the case</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>Measuring, counting, and reconciling inventory, owned by Measure Inventory (CM-1-1-3-7-4) and Perform Inventory Reconciliation (CM-1-1-3-7-5) | setting inventory policy, owned by the Inventory cluster (CM-1-1-3-7) | setting the plan-period finished-goods target and position, owned by Plan Finished Goods Inventory (CM-1-1-2-13) | day-to-day stock and replenishment management, owned by Manage Inventory Replenishment (CM-1-1-3-7-9) | inventory valuation and accounting, owned by Finance</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>Capture Inventory Position | Establish Opening Inventory | Inventory Basis Capture</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Batch 02 (2026-09-18). Read as a case-basis assembly step inside the CM-1-1-4-7 Refinery Optimization run cycle: this node establishes one input of the optimization case, it does not own the underlying business decision or the source data. Sibling “Capture …” nodes were defined together so their boundaries partition the case basis without overlap. Three inventory nodes are now distinct and must stay that way: this node states the position as a case boundary condition, Plan Finished Goods Inventory (CM-1-1-2-13, approved) sets the plan-period target, and the Inventory cluster (CM-1-1-3-7) owns policy, measurement, reconciliation, and replenishment. The bare taxonomy label “Capture Inventory” is the weakest of the eight and “Capture Inventory Position” is recorded as the preferred alternate label.</t>
+        </is>
+      </c>
+      <c r="U53" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V53" s="5" t="inlineStr">
+        <is>
+          <t>Establish the opening and required closing inventory position bounding the optimization case.</t>
+        </is>
+      </c>
+      <c r="W53" s="5" t="inlineStr">
+        <is>
+          <t>SRC-EIA-LFMM-001 | SRC-BJCE-REFPS-001 | SRC-ASCM-CSCP-001</t>
+        </is>
+      </c>
       <c r="X53" s="5" t="n"/>
-      <c r="Y53" s="5" t="n"/>
-      <c r="Z53" s="5" t="n"/>
-      <c r="AA53" s="5" t="n"/>
-      <c r="AB53" s="5" t="n"/>
-      <c r="AC53" s="5" t="n"/>
+      <c r="Y53" s="5" t="inlineStr">
+        <is>
+          <t>inventory system of record position | in-transit and committed volumes | minimum operating and unavailable stock levels | plan-period finished-goods inventory target | tankage and segregation constraints</t>
+        </is>
+      </c>
+      <c r="Z53" s="5" t="inlineStr">
+        <is>
+          <t>opening and required closing inventory basis for the optimization case</t>
+        </is>
+      </c>
+      <c r="AA53" s="5" t="inlineStr">
+        <is>
+          <t>enables: Refinery Optimization | uses-input: Plan Finished Goods Inventory | informed-by: Measure Inventory | constrained-by: Inventory</t>
+        </is>
+      </c>
+      <c r="AB53" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC53" s="5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AD53" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -5456,10 +5828,22 @@
           <t>no meaningful APQC candidate</t>
         </is>
       </c>
-      <c r="U54" s="5" t="n"/>
+      <c r="U54" s="5" t="inlineStr">
+        <is>
+          <t>mixed/needs-review</t>
+        </is>
+      </c>
       <c r="V54" s="5" t="n"/>
       <c r="W54" s="5" t="n"/>
-      <c r="X54" s="5" t="n"/>
+      <c r="X54" s="5" t="inlineStr">
+        <is>
+          <t>Question: Is “Capture Monthly Operating Plan” a process, or does it name the monthly operating plan document itself?
+Context: The seven sibling L5 nodes under Refinery Optimization (CM-1-1-4-7) partition the case basis and its analysis. The monthly operating plan is the output of the optimization cycle, not an input to it, so on a plain reading this node inverts the direction of the sibling set. Its Step 3b APQC candidate was “Plan facility”, scored NONE / NO CANDIDATE, so there is no external signal either way.
+Options: (1) Define it as issuing and registering the approved monthly operating plan as the plan of record handed to Refining for scheduling — a real process, and it closes the optimization cycle; no tree change needed, rename to “Issue Monthly Operating Plan” as preferred label. (2) Define it as loading the current approved operating plan as the starting baseline for the next case — also a real process and a genuine input, but it overlaps the parent scope phrase “current approved operating plan” already covered in the case basis. (3) Classify as not-process, a document rather than an activity, and retire the node; the plan artifact is then represented as the primary_output of CM-1-1-4-7 and CM-1-1-4. (4) Split: keep an issue step here and represent the plan artifact as an output, not a node.
+Evidence: SRC-BJCE-REFPS-001 describes monthly rolling plans as the product of tactical refinery planning, which assigns production targets to process units, and separates planning from scheduling; SRC-SNF-REFPS-001 and SRC-CMU-REFPLAN-001 place the plan as the handover from planning to scheduling. All three support the plan being an output of this cycle, none supports it being captured as an input.
+Recommendation: Option 1. It is the only reading that makes the node a process, leaves the tree unchanged, and gives the optimization cycle an explicit handover step to Refining, which the locked Refining boundary implies but no current node carries. Option 3 is the honest alternative if you would rather not re-point a label. Not defining the row until you decide, because Options 1 and 3 differ on whether the node survives.</t>
+        </is>
+      </c>
       <c r="Y54" s="5" t="n"/>
       <c r="Z54" s="5" t="n"/>
       <c r="AA54" s="5" t="n"/>
@@ -5535,18 +5919,80 @@
           <t>strong APQC candidate but no validator agreed</t>
         </is>
       </c>
-      <c r="U55" s="5" t="n"/>
-      <c r="V55" s="5" t="n"/>
-      <c r="W55" s="5" t="n"/>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Compare alternative production cases by varying crude slate, run rates, product mix, price, or constraint assumptions, and quantify the margin and feasibility consequences of each, so the preferred case and its sensitivities are understood before the plan is approved.</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>Covers case-based analysis inside the optimization cycle: defining the scenarios worth testing, running them against the case basis, reading marginal values and binding constraints, quantifying margin and feasibility differences, and documenting the comparison that supports the recommended case. Excludes selecting and approving the production plan, owned by Refinery Planning (CM-1-1-4). Excludes trading and market risk scenarios, owned by Manage And Run Risk Scenarios (CM-1-2-2-3-11). Excludes comparing actual performance to the approved plan, owned by Regional Backcasting (CM-1-1-5) and Distribution Backcasting (CM-1-1-6).</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Define the scenarios and sensitivities worth testing | run alternative cases against the case basis | read marginal values and identify binding constraints | quantify margin, yield, and feasibility differences | document the case comparison supporting the recommendation</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>Selecting and approving the production plan, owned by Refinery Planning (CM-1-1-4) | trading and market risk scenarios, owned by Manage And Run Risk Scenarios (CM-1-2-2-3-11) | comparing actuals to the approved plan, owned by Regional Backcasting (CM-1-1-5) and Distribution Backcasting (CM-1-1-6) | investment and strategic configuration studies | optimization model and application administration, owned by Process Excellence &amp; IT</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>Perform Case &amp; Sensitivity Analysis | Run Optimization Scenarios | Case Comparison</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Batch 02 (2026-09-18). Read as a case-basis assembly step inside the CM-1-1-4-7 Refinery Optimization run cycle: this node is the analysis step rather than a case-basis input. Sibling “Capture …” nodes were defined together so their boundaries partition the case basis without overlap. Scenario analysis here is forward-looking case comparison within a planning period. It is distinct from backcasting, which is retrospective, and from trading risk scenarios, which test market exposure rather than production alternatives. The APQC candidate “Perform competitive analysis” scored STRONG but is about comparing bidder proposals and was rejected as a false lexical match.</t>
+        </is>
+      </c>
+      <c r="U55" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V55" s="5" t="inlineStr">
+        <is>
+          <t>Quantify and compare production alternatives and their sensitivities to support case selection.</t>
+        </is>
+      </c>
+      <c r="W55" s="5" t="inlineStr">
+        <is>
+          <t>SRC-EIA-LFMM-001 | SRC-BJCE-REFPS-001 | SRC-CMU-REFPLAN-001 | SRC-SNF-REFPS-001</t>
+        </is>
+      </c>
       <c r="X55" s="5" t="n"/>
-      <c r="Y55" s="5" t="n"/>
-      <c r="Z55" s="5" t="n"/>
-      <c r="AA55" s="5" t="n"/>
-      <c r="AB55" s="5" t="n"/>
-      <c r="AC55" s="5" t="n"/>
+      <c r="Y55" s="5" t="inlineStr">
+        <is>
+          <t>assembled case basis of demand, availability, price, constraints, and inventory | base optimization case and solution | candidate scenario definitions | marginal values and binding constraint output</t>
+        </is>
+      </c>
+      <c r="Z55" s="5" t="inlineStr">
+        <is>
+          <t>documented case comparison with margin, feasibility, and sensitivity results</t>
+        </is>
+      </c>
+      <c r="AA55" s="5" t="inlineStr">
+        <is>
+          <t>enables: Refinery Optimization | uses-input: Capture Product Demand Requirements | uses-input: Capture Refinery Level Constraints | precedes: Refinery Planning</t>
+        </is>
+      </c>
+      <c r="AB55" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC55" s="5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AD55" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -25316,6 +25762,16 @@
       <c r="N307" t="inlineStr">
         <is>
           <t>Developing a program to promote the objectives, values, products and services of the company to its employees by treating them as potential customers, in order to extend company client base, increase employee engagement or to foster brand advocacy.</t>
+        </is>
+      </c>
+      <c r="O307" t="inlineStr">
+        <is>
+          <t>Covers setting the strategy for communicating brand, offer, and marketing messages to the organization's own employees as an internal audience: audience and channel choice, message and tone direction, and the intended engagement or advocacy outcome. Strategy only. Excludes executing internal communications, owned by Implement Internal Communications (CM-1-3-5-3-9), and excludes campaign-level planning, owned by Marketing Communications Planning (CM-1-3-5-3). Excludes external, media, public, investor, and government communications, which the locked Legal &amp; Corp Comm boundary places outside this branch. Excludes employee relations, terms of employment, and HR policy communication.</t>
+        </is>
+      </c>
+      <c r="T307" t="inlineStr">
+        <is>
+          <t>Batch 02 (2026-09-18), bundled fix. Row was approved in the #29 pre-intake pass with an empty scope_note and has been the single BLOCKING finding of step3c-workbook-validate.py since #30. Only the missing scope_note was added; the approved definition, status, and all other fields are unchanged. Boundaries asserted here are drawn from existing taxonomy siblings and the locked Legal &amp; Corp Comm decision, not from new research. Phase 1 fields remain empty, consistent with this row staying on the PRE_INTAKE_APPROVED allowlist for the later backfill pass.</t>
         </is>
       </c>
       <c r="U307" s="5" t="n"/>
@@ -41563,7 +42019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -42124,6 +42580,100 @@
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>SRC-EIA-LFMM-001</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>U.S. Energy Information Administration (DiVita)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Liquid Fuels Market Module refinery LP modeling white paper</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Accessed 2026-09-18</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>https://www.eia.gov/outlooks/documentation/workshops/pdf/VDiVita%20LFMM%20White%20Paper.pdf</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Government statistical authority</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Refinery LP input categories and model structure; evidence only, not text to copy</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Refinery optimization case basis: assays, availability, prices, specifications, capacities</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>SRC-BJCE-REFPS-001</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Brazilian Journal of Chemical Engineering (Moro)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Refinery production planning and scheduling: the refining coordination case</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Accessed 2026-09-18</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>https://www.scielo.br/j/bjce/a/GMRKZJGQ5HPqWRPfwKxnWTq/</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Peer-reviewed academic</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Planning-versus-scheduling separation and monthly rolling plan evidence; evidence only</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Case-basis inputs, monthly operating plan as planning output, sensitivity analysis</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
         <is>
           <t>active</t>
         </is>

--- a/business_architecture/ontology/build/output/step3c-definition-authoring-workbook.xlsx
+++ b/business_architecture/ontology/build/output/step3c-definition-authoring-workbook.xlsx
@@ -4510,25 +4510,17 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>PARKED TREE CHANGE — no definition authored (2026-09-18). See business_architecture/ontology/step3c-parked-tree-changes.md, entry PTC-001, for the full proposal and the steps required to close it. This node carries no local meaning of its own: its three L5 children (Develop Strategic Business Plan, Plan Budgets, Manage Site Specific Business Risk) are not refinery production-planning activities, and Plan Budgets contradicts the locked rule that Finance owns financial governance. Authoring a definition here would silently endorse budgeting and strategic planning under Refinery Planning. Handled the same way as the parked IT Services reparenting question on CM-1, rather than churning the tree during a definition pass. The three L5 children are left untouched and remain pending.</t>
+          <t>Retired per PTC-001 (step3c-parked-tree-changes.md), decided by Hamid 2026-09-18. The node carries no local meaning: its Step 3b provenance is a WEAK match against the APQC element “Manage employee development”, and under Option A all three of its children leave. Nothing remains to define, so it is retired rather than defined or left pending. The node itself is still present in downstream_process_map.json — removing it is a Step 3d tree change, not a workbook change. Retired here means “will not be defined”, not “gone from the tree”.</t>
         </is>
       </c>
       <c r="U43" s="5" t="inlineStr">
         <is>
-          <t>mixed/needs-review</t>
+          <t>not-process</t>
         </is>
       </c>
       <c r="V43" s="5" t="n"/>
       <c r="W43" s="5" t="n"/>
-      <c r="X43" s="5" t="inlineStr">
-        <is>
-          <t>Question: Should "Commercial Development" remain a child of Refinery Planning, and if so, what is its scope?
-Context: Parent CM-1-1-4 Refinery Planning is approved as the commercially optimal refinery production plan (crude slate, throughput, yield, and specification targets). This node's three L5 children are Develop Strategic Business Plan (CM-1-1-4-6-1), Plan Budgets (CM-1-1-4-6-2), and Manage Site Specific Business Risk (CM-1-1-4-6-3). None is a refinery production-planning activity. Plan Budgets conflicts with the locked Finance boundary. The label itself came from a WEAK / REVIEW LINK APQC match ("Manage employee development") and carries no local meaning. Two of the three children have no existing owner in the tree: there is no Strategy node among the L1 domains, and the only risk nodes are Credit Risk and Market Risk under Supply And Trading, with EHS owning EHS risk only.
-Options: A) Retire the node from Refinery Planning, reparent Plan Budgets to Finance, and create two new nodes outside Planning &amp; Scheduling for the strategic-plan and site-risk children. B) Redefine narrowly as site commercial business development and reparent all three children elsewhere. C) Retire the node and reparent each child individually with no replacement parent.
-Evidence: Approved CM-1-1-4 definition and scope note; locked Finance and EHS boundary rules; Step 3b review_notes recording the weak APQC match; SRC-SNF-REFPS-001 on separation of strategic, planning, and scheduling horizons.
-Recommendation: Option A, parked as a tree-change proposal for the consolidated repo-JSON pass rather than a definition authored now. Accepted by Hamid 2026-09-18; tracked as PTC-001 in step3c-parked-tree-changes.md.</t>
-        </is>
-      </c>
+      <c r="X43" s="5" t="n"/>
       <c r="Y43" s="5" t="n"/>
       <c r="Z43" s="5" t="n"/>
       <c r="AA43" s="5" t="n"/>
@@ -4536,7 +4528,7 @@
       <c r="AC43" s="5" t="n"/>
       <c r="AD43" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>retired</t>
         </is>
       </c>
     </row>
@@ -4602,6 +4594,11 @@
       <c r="M44" t="inlineStr">
         <is>
           <t>weak APQC candidate; manual review needed</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Parked by PTC-001 (step3c-parked-tree-changes.md), 2026-09-18. Hamid accepted Option A: this node leaves Refinery Planning. It cannot be moved yet — verified against downstream_process_map.json, the destination domain has no decomposition at all, so there is no parent to move it to. Set to blocked rather than left pending so it is not read as queued for definition. Revived by the Step 3d tree pass, not by a definition batch. Destination undecided: Finance or a future strategy domain. Hamid ruled out creating a Strategy L1, since the ten L1 definitions are approved baseline and changing the L1 set is a charter-level decision.</t>
         </is>
       </c>
       <c r="U44" s="5" t="n"/>
@@ -4615,7 +4612,7 @@
       <c r="AC44" s="5" t="n"/>
       <c r="AD44" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>blocked</t>
         </is>
       </c>
     </row>
@@ -4681,6 +4678,11 @@
       <c r="M45" t="inlineStr">
         <is>
           <t>weak APQC candidate; manual review needed</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Parked by PTC-001 (step3c-parked-tree-changes.md), 2026-09-18. Hamid accepted Option A: this node leaves Refinery Planning. It cannot be moved yet — verified against downstream_process_map.json, the destination domain has no decomposition at all, so there is no parent to move it to. Set to blocked rather than left pending so it is not read as queued for definition. Revived by the Step 3d tree pass, not by a definition batch. Destination is Finance, per the locked boundary that Finance owns financial governance. Decided 2026-09-18: no split — one node under Finance. The refinery's operational input to budgeting is already carried by the Refinery Optimization case basis (CM-1-1-4-7-1 to -6) and the Refinery Planning outputs, so a second node would duplicate batch 02.</t>
         </is>
       </c>
       <c r="U45" s="5" t="n"/>
@@ -4694,7 +4696,7 @@
       <c r="AC45" s="5" t="n"/>
       <c r="AD45" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>blocked</t>
         </is>
       </c>
     </row>
@@ -4760,6 +4762,11 @@
       <c r="M46" t="inlineStr">
         <is>
           <t>strong APQC candidate but no validator agreed</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Parked by PTC-001 (step3c-parked-tree-changes.md), 2026-09-18. Hamid accepted Option A: this node leaves Refinery Planning. It cannot be moved yet — verified against downstream_process_map.json, the destination domain has no decomposition at all, so there is no parent to move it to. Set to blocked rather than left pending so it is not read as queued for definition. Revived by the Step 3d tree pass, not by a definition batch. Destination undecided. Refining is the sensible owner as asset owner, but Refining is also undecomposed. Note the taxonomy has no enterprise risk capability anywhere: the only risk nodes are credit, market, and inventory risk, all inside Supply And Trading (CM-1-2-2, CM-1-2-5-4-1), and EHS owns EHS risk only. Whether an enterprise risk capability should exist is part of PTC-001 sub-decision 2.</t>
         </is>
       </c>
       <c r="U46" s="5" t="n"/>
@@ -4773,7 +4780,7 @@
       <c r="AC46" s="5" t="n"/>
       <c r="AD46" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>blocked</t>
         </is>
       </c>
     </row>
@@ -5155,7 +5162,7 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>Batch 02 (2026-09-18). Read as a case-basis assembly step inside the CM-1-1-4-7 Refinery Optimization run cycle: this node establishes one input of the optimization case, it does not own the underlying business decision or the source data. Sibling “Capture …” nodes were defined together so their boundaries partition the case basis without overlap. Boundary against “Plan Optimal Feedstock Slate And Run Rate” (CM-1-2-5-2-3) under Supply And Trading is unresolved: on its label that node duplicates the approved Refinery Planning accountability for slate and throughput targets. Raised as PTC-002 in step3c-parked-tree-changes.md and deliberately not reconciled here, since resolving it is a tree change. This node is bounded as evaluation only, so it does not depend on that outcome.</t>
+          <t>Batch 02 (2026-09-18). Read as a case-basis assembly step inside the CM-1-1-4-7 Refinery Optimization run cycle: this node establishes one input of the optimization case, it does not own the underlying business decision or the source data. Sibling “Capture …” nodes were defined together so their boundaries partition the case basis without overlap. Boundary against “Plan Optimal Feedstock Slate And Run Rate” (CM-1-2-5-2-3) under Supply And Trading is unresolved: on its label that node duplicates the approved Refinery Planning accountability for slate and throughput targets. Raised as PTC-002 in step3c-parked-tree-changes.md and deliberately not reconciled here, since resolving it is a tree change. This node is bounded as evaluation only, so it does not depend on that outcome. PTC-002 resolved 2026-09-18 (Option 1): Refinery Planning decides the binding slate and run rate; CM-1-2-5-2-3 in Supply And Trading advises only. No tree change. This definition was written to hold either way and is unchanged by the resolution.</t>
         </is>
       </c>
       <c r="U49" s="5" t="inlineStr">
@@ -5828,30 +5835,80 @@
           <t>no meaningful APQC candidate</t>
         </is>
       </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>Issue the agreed refinery production plan for the coming month as the plan of record — confirming the selected case, registering it with its assumptions and version, and handing it to Refining as the basis for detailed scheduling.</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>Covers closing the optimization cycle: confirming which case was selected, registering the plan with its price, constraint, and inventory assumptions and a version identifier, publishing it to Refining and the affected commercial functions, and recording it as the baseline that later backcasting compares against. Excludes selecting and approving the plan, which is the Refinery Planning (CM-1-1-4) decision this step records. Excludes detailed scheduling, line-ups, and blend execution against the plan, owned by Refining. Excludes reforecasting or revising the plan mid-period.</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Confirm the selected production case and its approval | register the plan with its assumption set and version identifier | publish the plan of record to Refining and affected commercial functions | record the plan as the backcasting baseline | log in-period changes as versioned restatements</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>Selecting and approving the production plan, owned by Refinery Planning (CM-1-1-4) | running and comparing the cases, owned by Perform Scenario Analysis (CM-1-1-4-7-8) | detailed scheduling and execution against the plan, owned by Refining | comparing actuals to the plan, owned by Regional Backcasting (CM-1-1-5) and Distribution Backcasting (CM-1-1-6) | mid-period reforecasting</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>Issue Monthly Operating Plan | Register Monthly Operating Plan | Publish Plan of Record | MOP Issue</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Resolved 2026-09-18, Hamid accepted Option 1 of the question raised in batch 02. The taxonomy label says “Capture”, but the monthly operating plan is the output of this cycle, not an input to it — SRC-BJCE-REFPS-001 describes monthly rolling plans as the product of tactical refinery planning, and SRC-SNF-REFPS-001 and SRC-CMU-REFPLAN-001 both place the plan as the planning-to-scheduling handover. Read as issuing and registering the plan, the node is a real process, needs no tree change, and gives the cycle the explicit handover to Refining that the locked Refining boundary implies but no other node carried. “Issue Monthly Operating Plan” is recorded as the preferred alternate label; if the label is ever corrected in the tree, that is a cosmetic Step 3d item, not a re-definition. The registered assumption set is also what the locked backcasting rule requires, since backcasting compares actuals to the approved plan and its contemporaneous assumptions, never a later reforecast.</t>
+        </is>
+      </c>
       <c r="U54" s="5" t="inlineStr">
         <is>
-          <t>mixed/needs-review</t>
-        </is>
-      </c>
-      <c r="V54" s="5" t="n"/>
-      <c r="W54" s="5" t="n"/>
-      <c r="X54" s="5" t="inlineStr">
-        <is>
-          <t>Question: Is “Capture Monthly Operating Plan” a process, or does it name the monthly operating plan document itself?
-Context: The seven sibling L5 nodes under Refinery Optimization (CM-1-1-4-7) partition the case basis and its analysis. The monthly operating plan is the output of the optimization cycle, not an input to it, so on a plain reading this node inverts the direction of the sibling set. Its Step 3b APQC candidate was “Plan facility”, scored NONE / NO CANDIDATE, so there is no external signal either way.
-Options: (1) Define it as issuing and registering the approved monthly operating plan as the plan of record handed to Refining for scheduling — a real process, and it closes the optimization cycle; no tree change needed, rename to “Issue Monthly Operating Plan” as preferred label. (2) Define it as loading the current approved operating plan as the starting baseline for the next case — also a real process and a genuine input, but it overlaps the parent scope phrase “current approved operating plan” already covered in the case basis. (3) Classify as not-process, a document rather than an activity, and retire the node; the plan artifact is then represented as the primary_output of CM-1-1-4-7 and CM-1-1-4. (4) Split: keep an issue step here and represent the plan artifact as an output, not a node.
-Evidence: SRC-BJCE-REFPS-001 describes monthly rolling plans as the product of tactical refinery planning, which assigns production targets to process units, and separates planning from scheduling; SRC-SNF-REFPS-001 and SRC-CMU-REFPLAN-001 place the plan as the handover from planning to scheduling. All three support the plan being an output of this cycle, none supports it being captured as an input.
-Recommendation: Option 1. It is the only reading that makes the node a process, leaves the tree unchanged, and gives the optimization cycle an explicit handover step to Refining, which the locked Refining boundary implies but no current node carries. Option 3 is the honest alternative if you would rather not re-point a label. Not defining the row until you decide, because Options 1 and 3 differ on whether the node survives.</t>
-        </is>
-      </c>
-      <c r="Y54" s="5" t="n"/>
-      <c r="Z54" s="5" t="n"/>
-      <c r="AA54" s="5" t="n"/>
-      <c r="AB54" s="5" t="n"/>
-      <c r="AC54" s="5" t="n"/>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V54" s="5" t="inlineStr">
+        <is>
+          <t>Issue and register the approved monthly production plan as the plan of record.</t>
+        </is>
+      </c>
+      <c r="W54" s="5" t="inlineStr">
+        <is>
+          <t>SRC-BJCE-REFPS-001 | SRC-SNF-REFPS-001 | SRC-CMU-REFPLAN-001 | SRC-EIA-LFMM-001</t>
+        </is>
+      </c>
+      <c r="X54" s="5" t="n"/>
+      <c r="Y54" s="5" t="inlineStr">
+        <is>
+          <t>selected and approved production case | case assumption set and scenario results | plan versioning and numbering convention | distribution list for the plan of record</t>
+        </is>
+      </c>
+      <c r="Z54" s="5" t="inlineStr">
+        <is>
+          <t>issued and versioned monthly operating plan of record with its assumption set</t>
+        </is>
+      </c>
+      <c r="AA54" s="5" t="inlineStr">
+        <is>
+          <t>produces: Monthly Operating Plan | informed-by: Perform Scenario Analysis | governed-by: Refinery Planning | precedes: Refining | enables: Regional Backcasting</t>
+        </is>
+      </c>
+      <c r="AB54" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC54" s="5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AD54" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -17616,6 +17673,11 @@
       <c r="M203" t="inlineStr">
         <is>
           <t>no meaningful APQC candidate</t>
+        </is>
+      </c>
+      <c r="T203" t="inlineStr">
+        <is>
+          <t>Boundary decided by Hamid 2026-09-18, PTC-002 closed with no tree change. Refinery Planning (CM-1-1-4) decides the binding crude slate and run rate; this node advises. Whoever defines this row must scope it as the trading-side recommendation of an economically attractive feedstock slate and run rate feeding the refinery plan, and must not claim the slate or throughput decision. Row left pending: it sits in the Supply And Trading cluster and gets its definition in that batch, not this one.</t>
         </is>
       </c>
       <c r="U203" s="5" t="n"/>

--- a/business_architecture/ontology/build/output/step3c-definition-authoring-workbook.xlsx
+++ b/business_architecture/ontology/build/output/step3c-definition-authoring-workbook.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here — Decisions &amp; Phases" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review &amp; authoring" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Column guide" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Controlled vocabularies" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference register" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="External mappings" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Start Here — Decisions &amp; Phases" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Review &amp; authoring" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Column guide" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Controlled vocabularies" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Reference register" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="External mappings" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Review &amp; authoring'!$A$1:$AD$504</definedName>
@@ -1189,18 +1189,80 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U4" s="5" t="n"/>
-      <c r="V4" s="5" t="n"/>
-      <c r="W4" s="5" t="n"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Develop, agree, and publish the recurring product demand forecast that downstream commercial planning runs on — expected demand by product, market, location, and period — by combining a statistical baseline with customer input and market intelligence, and monitor forecast performance so the published forecast remains a reliable planning basis.</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Covers the recurring demand-forecast production cycle: preparing forecasting master data and history, developing the statistical baseline, adjusting it with customer input and market intelligence, publishing the approved forecast with its component-level breakdown, and monitoring forecast performance. Its output is the single approved demand forecast consumed by Regional Optimization, Refinery Optimization, and Supply And Trading. Excludes deciding how demand is met — supply, production, inventory, and allocation choices are owned by Regional Optimization (CM-1-1-2); excludes capturing or committing customer orders, owned by Order Management (CM-1-3-7); excludes Supply And Trading's operational refined-product demand forecasting (Forecast Refined Product Demand, CM-1-2-6-2-3), bounded per the batch 03 decision; excludes designing and agreeing the cross-functional forecasting process with sales, owned by Develop &amp; Agree Demand Forecasting Process (CM-1-3-5-1-2).</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Prepare and validate forecasting inputs | develop the statistical baseline forecast | incorporate customer input and market intelligence | publish the approved forecast and component-level forecast plan | monitor forecast accuracy, bias, and adjustment effect</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Supply, production, inventory, and allocation decisions (Regional Optimization, CM-1-1-2) | customer order capture and commitment (Order Management, CM-1-3-7) | trading-side receipt and use of the published forecast (Receive Demand Forecast, CM-1-2-1-1-2) | Supply And Trading operational refined-product demand forecasting (Forecast Refined Product Demand, CM-1-2-6-2-3) | sales forecasting process design (Develop &amp; Agree Demand Forecasting Process, CM-1-3-5-1-2)</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Product Demand Forecasting</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Batch 03 (2026-09-19). Q1 decision (Hamid, 2026-09-19, Option A): the L4 carries the same label as its L3 parent (CM-1-1-1) and is its only child; authored in place as the operational forecast-production cycle, with the L3 remaining the domain umbrella — no tree change, consistent with the restraint precedent on PTC-001; a later naming pass may disambiguate the duplicate prefLabels. Q2 decision (Hamid, 2026-09-19, Option A): binding constraint on the future definition of CM-1-2-6-2-3 — it must be scoped as Supply And Trading's operational demand forecasting within Refined Product Supply Chain Management and must not claim ownership of the approved commercial planning forecast; same decide-versus-advise pattern as PTC-002. Evidence basis: the planning-cycle forecast (monthly, product/market level; IEA OMR and EIA STEO practice) is distinct from operational network demand forecasting (short-notice, terminal/station level; Mota et al. 2017). APQC 10240 'Evaluate and revise demand forecasting approach' is REVIEW LINK only; approach-governance content sits closest to CM-1-3-5-1-2, not here.</t>
+        </is>
+      </c>
+      <c r="U4" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V4" s="5" t="inlineStr">
+        <is>
+          <t>Produce and maintain the single approved product demand forecast that downstream commercial planning runs on.</t>
+        </is>
+      </c>
+      <c r="W4" s="5" t="inlineStr">
+        <is>
+          <t>SRC-IEA-OMR-001 | SRC-EIA-STEO-001 | SRC-ORP-DPSC-001 | SRC-ASCM-CSCP-001</t>
+        </is>
+      </c>
       <c r="X4" s="5" t="n"/>
-      <c r="Y4" s="5" t="n"/>
-      <c r="Z4" s="5" t="n"/>
-      <c r="AA4" s="5" t="n"/>
-      <c r="AB4" s="5" t="n"/>
-      <c r="AC4" s="5" t="n"/>
+      <c r="Y4" s="5" t="inlineStr">
+        <is>
+          <t>cleansed demand history | customer plans and commitments | market intelligence | product and market master data</t>
+        </is>
+      </c>
+      <c r="Z4" s="5" t="inlineStr">
+        <is>
+          <t>approved and published demand forecast with component-level forecast plan</t>
+        </is>
+      </c>
+      <c r="AA4" s="5" t="inlineStr">
+        <is>
+          <t>precedes: Regional Optimization | enables: Capture Product Demand Requirements | enables: Receive Demand Forecast</t>
+        </is>
+      </c>
+      <c r="AB4" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC4" s="5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -1268,18 +1330,80 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U5" s="5" t="n"/>
-      <c r="V5" s="5" t="n"/>
-      <c r="W5" s="5" t="n"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Prepare and validate the reference data and demand history that each forecast cycle depends on — product and market hierarchies, customer and location groupings, units of measure, and the historical demand series cleansed of outliers and one-off distortions — so the statistical baseline is built from accurate, planning-consistent inputs.</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Covers per-cycle readiness of forecasting inputs: maintaining forecast-specific reference data, aligning product and market hierarchies to planning definitions, and cleansing demand history for outliers, supply disruptions, and other events that would distort the baseline. Excludes supply-planning reference and parameter data, owned by Maintain Supply Planning Master Data (CM-1-1-2-12); excludes production-scheduling master data, owned by Maintain Production Scheduling Master Data (CM-1-1-7-2-1); excludes customer, price, product, tax, and location master data, owned by Manage Master Data under Order Management (CM-1-3-7-1); excludes enterprise master-data policy and governance, which sit with the Data Governance workstream.</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Maintain forecast-specific reference data | align product and market hierarchies to planning definitions | cleanse and adjust demand history for distorting events | validate data readiness for the forecast cycle</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Supply-planning master data (Maintain Supply Planning Master Data, CM-1-1-2-12) | production-scheduling master data (Maintain Production Scheduling Master Data, CM-1-1-7-2-1) | customer, price, product, tax, and location master data (Manage Master Data, CM-1-3-7-1) | enterprise master-data policy and governance (Data Governance workstream) | statistical model development (Develop Statistical Baseline, CM-1-1-1-1-2)</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Forecast Data Preparation</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Batch 03 (2026-09-19). Fourth of the four parallel master-data nodes; consolidation under a governed master-data capability is parked for the EPM Data Governance workstream per the decision recorded on CM-1-1-2-12 (2026-09-18) and deliberately not resolved here — the boundary to CM-1-1-2-12 was already established from its approved out_of_scope. APQC 10252 'Maintain master data' is a WEAK distribution-master-data candidate; comparative evidence only.</t>
+        </is>
+      </c>
+      <c r="U5" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V5" s="5" t="inlineStr">
+        <is>
+          <t>Ensure each forecast cycle starts from validated reference data and cleansed demand history.</t>
+        </is>
+      </c>
+      <c r="W5" s="5" t="inlineStr">
+        <is>
+          <t>SRC-EIA-GLOSS-001 | SRC-ASCM-CSCP-001</t>
+        </is>
+      </c>
       <c r="X5" s="5" t="n"/>
-      <c r="Y5" s="5" t="n"/>
-      <c r="Z5" s="5" t="n"/>
-      <c r="AA5" s="5" t="n"/>
-      <c r="AB5" s="5" t="n"/>
-      <c r="AC5" s="5" t="n"/>
+      <c r="Y5" s="5" t="inlineStr">
+        <is>
+          <t>raw sales and lifting history | product and market hierarchy definitions | customer and location groupings | recorded demand-distorting events</t>
+        </is>
+      </c>
+      <c r="Z5" s="5" t="inlineStr">
+        <is>
+          <t>validated forecasting dataset and reference data for the cycle</t>
+        </is>
+      </c>
+      <c r="AA5" s="5" t="inlineStr">
+        <is>
+          <t>precedes: Develop Statistical Baseline | enables: Demand Forecasting</t>
+        </is>
+      </c>
+      <c r="AB5" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC5" s="5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -1347,18 +1471,80 @@
           <t>CIRCULAR VALIDATOR (human gate): validator is APQC itself ('Develop baseline demand forecasts', apqc.org benchmarking measures page) validating APQC's own description. Triangulation requires an INDEPENDENT source. No adoption without external agreement.</t>
         </is>
       </c>
-      <c r="U6" s="5" t="n"/>
-      <c r="V6" s="5" t="n"/>
-      <c r="W6" s="5" t="n"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Generate the objective statistical baseline forecast of product demand from cleansed history and demonstrated demand drivers, selecting and tuning forecasting methods by product and market segment before any judgmental input is applied.</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Covers producing the unbiased statistical starting point of the forecast cycle: choosing and parameterizing forecasting methods, generating the baseline at the agreed hierarchy levels, and documenting model fit and known limitations. The baseline is deliberately judgment-free — commercial knowledge enters in the adjustment step. Excludes adjusting the forecast with customer input and market intelligence, owned by Adjust Forecast Incorporating Customer Input and Market Intelligence (CM-1-1-1-1-3); excludes publication and disaggregation, owned by Publish Forecast and Generate Component Level Forecast Plan (CM-1-1-1-1-4); excludes measuring forecast performance, owned by Monitor Demand Forecasting Performance and Reporting (CM-1-1-1-1-5).</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Select and tune statistical forecasting methods by segment | generate the baseline forecast at agreed hierarchy levels | apply demonstrated demand drivers | document model fit and limitations</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Judgmental adjustment of the forecast (CM-1-1-1-1-3) | forecast publication and disaggregation (CM-1-1-1-1-4) | forecast performance measurement (CM-1-1-1-1-5) | trading revenue and asset forecasting (Forecasting &amp; Optimization, CM-1-2-1-1)</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Statistical Baseline Forecast | Baseline Forecasting</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Batch 03 (2026-09-19). APQC 20043 'Develop baseline forecasts' scored STRONG but was REJECTED at the Step 3b human gate as circular validation (APQC validating APQC); authored independently per that rejection. Driver-based statistical modeling of fuels demand (economic activity, prices, weather) follows the practice documented in EIA STEO product-consumption modules; monthly product-level demand assessment follows IEA OMR practice. 'Baseline' is used in the demand-planning sense — the pre-judgment statistical forecast — not the plan-baseline sense used in backcasting.</t>
+        </is>
+      </c>
+      <c r="U6" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V6" s="5" t="inlineStr">
+        <is>
+          <t>Produce the objective, judgment-free statistical starting point for the demand forecast.</t>
+        </is>
+      </c>
+      <c r="W6" s="5" t="inlineStr">
+        <is>
+          <t>SRC-EIA-STEO-001 | SRC-IEA-OMR-001 | SRC-ASCM-CSCP-001</t>
+        </is>
+      </c>
       <c r="X6" s="5" t="n"/>
-      <c r="Y6" s="5" t="n"/>
-      <c r="Z6" s="5" t="n"/>
-      <c r="AA6" s="5" t="n"/>
-      <c r="AB6" s="5" t="n"/>
-      <c r="AC6" s="5" t="n"/>
+      <c r="Y6" s="5" t="inlineStr">
+        <is>
+          <t>validated forecasting dataset | demand driver variables | historical model performance</t>
+        </is>
+      </c>
+      <c r="Z6" s="5" t="inlineStr">
+        <is>
+          <t>statistical baseline forecast by product and market segment</t>
+        </is>
+      </c>
+      <c r="AA6" s="5" t="inlineStr">
+        <is>
+          <t>follows: Prepare Master Data To Create Demand Forecast | precedes: Adjust Forecast Incorporating Customer Input and Market Intelligence</t>
+        </is>
+      </c>
+      <c r="AB6" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC6" s="5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -1426,18 +1612,80 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U7" s="5" t="n"/>
-      <c r="V7" s="5" t="n"/>
-      <c r="W7" s="5" t="n"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Review and adjust the statistical baseline with demand knowledge the models cannot see — customer plans and commitments, sales and marketing input, and market and competitive intelligence — recording each adjustment and its rationale so the agreed forecast reflects the best available view of demand.</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Covers the judgmental overlay and agreement step of the forecast cycle: gathering structured input from customer-facing and market-facing teams, challenging and applying adjustments to the baseline, and recording who changed what and why so performance monitoring can attribute accuracy effects. Excludes producing the statistical baseline itself (CM-1-1-1-1-2); excludes gathering market and customer intelligence as an ongoing capability — this step consumes intelligence, it does not own its production; excludes negotiating or committing the underlying customer volumes, owned by Order Management (CM-1-3-7) and sales.</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Collect structured customer and market input | review and challenge the statistical baseline | apply and document adjustments with rationale | agree the adjusted forecast for publication</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Statistical baseline generation (CM-1-1-1-1-2) | ownership of market and customer intelligence production | customer negotiation and order commitment (Order Management, CM-1-3-7) | publication of the agreed forecast (CM-1-1-1-1-4)</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Consensus Forecast Adjustment | Judgmental Forecast Adjustment</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Batch 03 (2026-09-19). Written as the consensus/enrichment step of standard demand-planning practice; the IEA OMR's monthly demand revisions on new market information are the reference pattern for judgment applied over a statistical basis. Adjustments are recorded with rationale specifically so CM-1-1-1-1-5 can measure whether they added accuracy — the adjustment record is part of the process, not an implementation detail. APQC 10106 'Perform customer and market intelligence analysis' is REVIEW LINK; it describes the intelligence capability this step consumes, not this step itself.</t>
+        </is>
+      </c>
+      <c r="U7" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V7" s="5" t="inlineStr">
+        <is>
+          <t>Turn the statistical baseline into the agreed forecast by applying documented customer and market knowledge.</t>
+        </is>
+      </c>
+      <c r="W7" s="5" t="inlineStr">
+        <is>
+          <t>SRC-IEA-OMR-001 | SRC-ASCM-CSCP-001</t>
+        </is>
+      </c>
       <c r="X7" s="5" t="n"/>
-      <c r="Y7" s="5" t="n"/>
-      <c r="Z7" s="5" t="n"/>
-      <c r="AA7" s="5" t="n"/>
-      <c r="AB7" s="5" t="n"/>
-      <c r="AC7" s="5" t="n"/>
+      <c r="Y7" s="5" t="inlineStr">
+        <is>
+          <t>statistical baseline forecast | customer plans and commitments | sales and marketing input | market and competitive intelligence</t>
+        </is>
+      </c>
+      <c r="Z7" s="5" t="inlineStr">
+        <is>
+          <t>agreed adjusted forecast with documented adjustment rationale</t>
+        </is>
+      </c>
+      <c r="AA7" s="5" t="inlineStr">
+        <is>
+          <t>follows: Develop Statistical Baseline | precedes: Publish Forecast and Generate Component Level Forecast Plan</t>
+        </is>
+      </c>
+      <c r="AB7" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC7" s="5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -1505,18 +1753,80 @@
           <t>CIRCULAR VALIDATOR (human gate): validator is APQC itself and the cited URL (turnover-rate-manufacturing-personnel) is unrelated to line-level planning; the 'definition' merely restates APQC's own description (agreement 1.0 is self-match). No independent source, no adoption.</t>
         </is>
       </c>
-      <c r="U8" s="5" t="n"/>
-      <c r="V8" s="5" t="n"/>
-      <c r="W8" s="5" t="n"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Approve and publish the agreed demand forecast as the versioned planning basis, and translate it into the component-level forecast plan — the detailed breakdown by product grade or component, location, and period — that downstream planning processes consume.</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Covers the release step of the forecast cycle: final approval, version identification, disaggregation of the agreed forecast to the component level used by planning, and distribution to its consumers. The published version is the fixed reference that both planning and forecast-performance measurement run against. Excludes acting on the forecast — supply, production, inventory, and allocation decisions are owned by Regional Optimization (CM-1-1-2) and Refinery Planning (CM-1-1-4); excludes the consumers' own receipt and case-assembly steps, owned by Receive Demand Forecast (CM-1-2-1-1-2) and Capture Product Demand Requirements (CM-1-1-4-7-1).</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Approve and version the forecast for release | disaggregate to the component-level forecast plan | distribute the published forecast to consuming processes | maintain the published version as the fixed reference for the period</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Supply and allocation decisions (Regional Optimization, CM-1-1-2) | refinery case-basis assembly (Capture Product Demand Requirements, CM-1-1-4-7-1) | trading-side receipt (Receive Demand Forecast, CM-1-2-1-1-2) | forecast adjustment (CM-1-1-1-1-3)</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>Forecast Publication | Publish Demand Forecast</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Batch 03 (2026-09-19). 'Component level' is read as the detailed disaggregated planning level — product grade or blend component, location, and period — required by the consuming planning processes; the definition states the function without fixing a single technical reading. APQC 10306 'Generate line level plan' scored STRONG but was REJECTED at the Step 3b human gate as circular validation with an unrelated citation; authored independently. The published, versioned forecast is the contemporaneous baseline that CM-1-1-1-1-5 measures against — consistent with the locked backcasting discipline.</t>
+        </is>
+      </c>
+      <c r="U8" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V8" s="5" t="inlineStr">
+        <is>
+          <t>Release one versioned, detailed demand forecast that all downstream planning consumes.</t>
+        </is>
+      </c>
+      <c r="W8" s="5" t="inlineStr">
+        <is>
+          <t>SRC-EIA-STEO-001 | SRC-ORP-DPSC-001 | SRC-ASCM-CSCP-001</t>
+        </is>
+      </c>
       <c r="X8" s="5" t="n"/>
-      <c r="Y8" s="5" t="n"/>
-      <c r="Z8" s="5" t="n"/>
-      <c r="AA8" s="5" t="n"/>
-      <c r="AB8" s="5" t="n"/>
-      <c r="AC8" s="5" t="n"/>
+      <c r="Y8" s="5" t="inlineStr">
+        <is>
+          <t>agreed adjusted forecast | product component and grade structures | planning calendar</t>
+        </is>
+      </c>
+      <c r="Z8" s="5" t="inlineStr">
+        <is>
+          <t>published versioned demand forecast and component-level forecast plan</t>
+        </is>
+      </c>
+      <c r="AA8" s="5" t="inlineStr">
+        <is>
+          <t>follows: Adjust Forecast Incorporating Customer Input and Market Intelligence | precedes: Regional Optimization | enables: Capture Product Demand Requirements | enables: Receive Demand Forecast</t>
+        </is>
+      </c>
+      <c r="AB8" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC8" s="5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -1584,18 +1894,80 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U9" s="5" t="n"/>
-      <c r="V9" s="5" t="n"/>
-      <c r="W9" s="5" t="n"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Measure and report how well published demand forecasts predicted actual demand — tracking accuracy, bias, and the effect of adjustments at agreed levels and lags — and feed the findings back into forecasting methods and adjustment behavior.</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Covers recurring forecast-performance measurement and reporting: comparing actual demand with the forecast as published for that period, analyzing error and bias by segment and lag, evaluating whether judgmental adjustments improved accuracy, reporting results, and recommending method and process improvements. Actuals are compared with the contemporaneously published forecast version, not a later revision. Excludes explaining supply-plan versus actual outcomes, owned by Regional Backcasting (CM-1-1-5) and Distribution Backcasting (CM-1-1-6); excludes agreeing the cross-functional forecasting process design with sales, owned by Develop &amp; Agree Demand Forecasting Process (CM-1-3-5-1-2).</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Compare actual demand with the published forecast version | analyze forecast error and bias by segment and lag | evaluate the accuracy effect of judgmental adjustments | report performance and recommend improvements</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Plan-versus-actual supply and distribution variance analysis (Regional Backcasting, CM-1-1-5; Distribution Backcasting, CM-1-1-6) | forecasting process design and agreement (Develop &amp; Agree Demand Forecasting Process, CM-1-3-5-1-2) | making the forecast adjustments themselves (CM-1-1-1-1-3)</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Forecast Accuracy Monitoring | Forecast Performance Measurement</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Batch 03 (2026-09-19). Measures the forecast against actual demand using the as-published version as the fixed comparison basis — the same contemporaneous-baseline discipline locked for Regional and Distribution Backcasting, applied to the demand side. EIA's published STEO forecast-accuracy evaluations are the reference practice for measuring product-demand forecasts against realized data. Specific accuracy metrics and thresholds are deliberately not named; they belong to the KPI workstream, not the process definition. APQC 16574 'Monitor and report performance' is a WEAK marketing-channel candidate; comparative evidence only.</t>
+        </is>
+      </c>
+      <c r="U9" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V9" s="5" t="inlineStr">
+        <is>
+          <t>Establish whether published forecasts are getting more or less reliable, and why, so the forecasting cycle improves.</t>
+        </is>
+      </c>
+      <c r="W9" s="5" t="inlineStr">
+        <is>
+          <t>SRC-EIA-STEO-001 | SRC-ASCM-CSCP-001</t>
+        </is>
+      </c>
       <c r="X9" s="5" t="n"/>
-      <c r="Y9" s="5" t="n"/>
-      <c r="Z9" s="5" t="n"/>
-      <c r="AA9" s="5" t="n"/>
-      <c r="AB9" s="5" t="n"/>
-      <c r="AC9" s="5" t="n"/>
+      <c r="Y9" s="5" t="inlineStr">
+        <is>
+          <t>published forecast versions | actual demand history | adjustment records with rationale</t>
+        </is>
+      </c>
+      <c r="Z9" s="5" t="inlineStr">
+        <is>
+          <t>forecast performance report with improvement recommendations</t>
+        </is>
+      </c>
+      <c r="AA9" s="5" t="inlineStr">
+        <is>
+          <t>follows: Publish Forecast and Generate Component Level Forecast Plan | uses-input: Adjust Forecast Incorporating Customer Input and Market Intelligence | enables: Demand Forecasting</t>
+        </is>
+      </c>
+      <c r="AB9" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC9" s="5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -42081,7 +42453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -42130,6 +42502,7 @@
         </is>
       </c>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
@@ -42736,6 +43109,194 @@
         </is>
       </c>
       <c r="I19" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>SRC-EIA-STEO-001</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>U.S. Energy Information Administration</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Short-Term Energy Outlook and model documentation (petroleum product consumption modules)</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Accessed 2026-09-19</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>https://www.eia.gov/outlooks/steo/</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Government statistical authority</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Petroleum-product demand forecasting practice and driver-based modeling; evidence only, not text to copy</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Statistical modeling of product demand by fuel, region, and driver variables (economic activity, prices, weather); published forecast-accuracy evaluation</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>SRC-IEA-OMR-001</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>International Energy Agency</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Oil Market Report (monthly series)</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Accessed 2026-09-19</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/oil-market-report</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Intergovernmental energy authority</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Product-level oil demand assessment and forecast practice; evidence only, not text to copy</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Monthly demand-by-product-and-region assessment cycle and revision practice</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>SRC-ORP-DPSC-001</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Operations Research Perspectives (Pudasaini)</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Integrated planning of downstream petroleum supply chain: a multi-objective stochastic approach</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Vol. 8, 2021; accessed 2026-09-19</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>https://www.sciencedirect.com/science/article/pii/S2214716021000129</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Peer-reviewed academic</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Downstream planning structure and demand as planning input; evidence only</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Demand as the driving input of downstream supply and distribution network planning</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>SRC-LNL-T2S-001</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Springer Lecture Notes in Logistics (Mota, Relvas, Goncalves)</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Downstream Oil Products Distribution Planning: A Portuguese Case Study</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2017; accessed 2026-09-19</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1007/978-3-319-42421-7_3</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Peer-reviewed academic</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Secondary-distribution planning and short-term network demand; evidence only</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Operational terminal/station-level demand versus the planning-cycle forecast (batch 03 Q2 boundary evidence)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
         <is>
           <t>active</t>
         </is>

--- a/business_architecture/ontology/build/output/step3c-definition-authoring-workbook.xlsx
+++ b/business_architecture/ontology/build/output/step3c-definition-authoring-workbook.xlsx
@@ -3404,18 +3404,80 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U24" s="5" t="n"/>
-      <c r="V24" s="5" t="n"/>
-      <c r="W24" s="5" t="n"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>The capability to govern, measure, reconcile, control, position, replenish, and account for petroleum feedstocks, intermediates, and refined products across the downstream network, including their quantity, quality, location, ownership, entitlement, identity, and availability.</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Covers development and maintenance of inventory policies by material class; physical inventory measurement and the volumetric inputs to valuation; book-to-physical reconciliation; replenishment management; and stewardship of inventory held under consignment, commingling, third-party-storage, lot/batch, and re-brand arrangements, including controls over ownership, entitlement, product identity, custody, quality, location, and availability. Excludes setting plan-period finished-product inventory targets inside the regional plan, owned by Plan Finished Goods Inventory (CM-1-1-2-13); excludes physical tank, terminal, and pipeline operation, owned by Midstream; excludes inventory valuation, accounting, and financial reporting, owned by Finance; excludes day-to-day crude and refinery-feedstock position management, owned by Manage Feedstock Inventory (CM-1-2-5-4-2) per the batch 04 decision.</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Inventory policy by material class | physical inventory measurement and volumetric inputs to valuation | book-to-physical reconciliation | replenishment management | consignment, commingled, re-brand, lot/batch, and third-party storage stewardship</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>Plan-period inventory targets in the regional plan (Plan Finished Goods Inventory, CM-1-1-2-13) | physical storage and movement operation (Midstream) | inventory valuation, accounting, and financial reporting (Finance) | day-to-day feedstock position management (Manage Feedstock Inventory, CM-1-2-5-4-2) | trading inventory risk management (Supply And Trading)</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>Inventory Management | Stock Management</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Batch 04 (2026-09-19). Q1 decision (Hamid, Option A): capability, not process — the children are distinct recurring processes that jointly enable inventory stewardship, not stages of one cycle. The bare-noun label can denote the asset/state, a count, or the function; this node denotes the capability. Preferred normalized label 'Inventory Management' queued for the consolidated naming pass; current label retained for batch traceability, together with the L4-versus-L5 'Manage Inventory' label collision. Placement rule: Supply Chain Management answers what should be held, moved, made, or replenished, where and when; this capability answers what inventory exists, under what identity, ownership, and entitlement, in what quantity and location, and whether it is controlled and reconciled; Midstream answers how bulk material is physically received, stored, transferred, and transported. Feedstock boundary constraint (Q3 decision, Hamid, Option A): Manage Feedstock Inventory (CM-1-2-5-4-2) owns the day-to-day monitoring, control, and operational management of crude and refinery-feedstock inventory positions within Crude/Feed Supply Management; this cluster owns cross-material inventory policy, measurement, reconciliation, and specialized inventory-arrangement controls, and does not own day-to-day feedstock position management. A reciprocal note is recorded on CM-1-2-5-4-2. Hydrocarbon loss-control ownership beyond reconciliation reporting has no home in the current tree; playbook step 7 carries that question — deliberately not resolved here.</t>
+        </is>
+      </c>
+      <c r="U24" s="5" t="inlineStr">
+        <is>
+          <t>capability</t>
+        </is>
+      </c>
+      <c r="V24" s="5" t="inlineStr">
+        <is>
+          <t>Ensure the network's stock positions are governed by policy, measured accurately, reconciled, and managed across ownership and storage arrangements.</t>
+        </is>
+      </c>
+      <c r="W24" s="5" t="inlineStr">
+        <is>
+          <t>SRC-EI-HM32-001 | SRC-API-MPMS-001 | SRC-ASCM-CSCP-001</t>
+        </is>
+      </c>
       <c r="X24" s="5" t="n"/>
-      <c r="Y24" s="5" t="n"/>
-      <c r="Z24" s="5" t="n"/>
-      <c r="AA24" s="5" t="n"/>
-      <c r="AB24" s="5" t="n"/>
-      <c r="AC24" s="5" t="n"/>
+      <c r="Y24" s="5" t="inlineStr">
+        <is>
+          <t>approved regional and distribution plans | measured tank and meter data | movement and transaction records | storage and consignment agreements</t>
+        </is>
+      </c>
+      <c r="Z24" s="5" t="inlineStr">
+        <is>
+          <t>governed, reconciled inventory positions and policies for the distribution network</t>
+        </is>
+      </c>
+      <c r="AA24" s="5" t="inlineStr">
+        <is>
+          <t>enables: Regional Optimization | enables: Capture Inventory | informed-by: Plan Finished Goods Inventory</t>
+        </is>
+      </c>
+      <c r="AB24" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC24" s="5" t="inlineStr">
+        <is>
+          <t>continuous</t>
+        </is>
+      </c>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -3483,18 +3545,80 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U25" s="5" t="n"/>
-      <c r="V25" s="5" t="n"/>
-      <c r="W25" s="5" t="n"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Establish and maintain the policy governing crude and feedstock inventories — target and minimum operating levels, safety and strategic stock requirements, tankage and segregation rules, and review triggers — so feedstock supply to refineries is protected at an efficient working-capital cost.</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Covers the recurring development, approval, and review of crude and feedstock inventory policy across refinery and terminal storage, including minimum operating and safety stock levels, quality-segregation requirements by grade, and the conditions that trigger policy review. Excludes day-to-day management of feedstock positions against the policy, which sits with Supply And Trading (Manage Feedstock Inventory, CM-1-2-5-4-2) per the batch 04 decision; excludes plan-period inventory choices, owned by Regional Optimization (CM-1-1-2); excludes physical tank operation, owned by Midstream and Refining.</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Set target, minimum operating, and safety stock levels for crude and feedstock | define segregation and tankage policy by grade | define policy review triggers and cadence | approve policy exceptions</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>Day-to-day feedstock position management (Manage Feedstock Inventory, CM-1-2-5-4-2) | plan-period inventory positioning (Regional Optimization, CM-1-1-2) | crude purchasing (Supply And Trading) | physical storage operation (Midstream, Refining)</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>Crude &amp; Feedstock Inventory Policy</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Batch 04 (2026-09-19). One of three sibling policy nodes split by material class; the split follows the physical flow (feedstock → intermediates → finished product), and each policy binds the processes managing that class. APQC 10346 is a WEAK delivery-service-policy candidate; comparative evidence only.</t>
+        </is>
+      </c>
+      <c r="U25" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V25" s="5" t="inlineStr">
+        <is>
+          <t>Set the binding policy for how much crude and feedstock is held, where, and under what rules.</t>
+        </is>
+      </c>
+      <c r="W25" s="5" t="inlineStr">
+        <is>
+          <t>SRC-EI-HM31-001 | SRC-ASCM-CSCP-001</t>
+        </is>
+      </c>
       <c r="X25" s="5" t="n"/>
-      <c r="Y25" s="5" t="n"/>
-      <c r="Z25" s="5" t="n"/>
-      <c r="AA25" s="5" t="n"/>
-      <c r="AB25" s="5" t="n"/>
-      <c r="AC25" s="5" t="n"/>
+      <c r="Y25" s="5" t="inlineStr">
+        <is>
+          <t>refinery feedstock requirements | supply lead times and variability | tankage and segregation constraints | working-capital guidance</t>
+        </is>
+      </c>
+      <c r="Z25" s="5" t="inlineStr">
+        <is>
+          <t>approved crude and feedstock inventory policy</t>
+        </is>
+      </c>
+      <c r="AA25" s="5" t="inlineStr">
+        <is>
+          <t>informed-by: Refinery Planning | enables: Manage Inventory</t>
+        </is>
+      </c>
+      <c r="AB25" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC25" s="5" t="inlineStr">
+        <is>
+          <t>periodic</t>
+        </is>
+      </c>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -3562,18 +3686,80 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U26" s="5" t="n"/>
-      <c r="V26" s="5" t="n"/>
-      <c r="W26" s="5" t="n"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Establish and maintain the policy governing intermediate and blendstock inventories held between process units and blending — target working levels, segregation and quality-protection rules, and review triggers — so conversion and blending operations are decoupled without trapping excess working capital.</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Covers policy for unfinished streams held between refinery processing stages and blending, including working-level ranges that buffer unit outages and campaign changes, segregation rules that protect intermediate quality, and policy review cadence tied to unit campaigns and turnarounds. Excludes intermediate tank and transfer operation, owned by Refining; excludes the production decisions that generate intermediates, owned by Refinery Planning (CM-1-1-4) and Refining; excludes finished-product policy, owned by Develop Finished Product Inventory Policy (CM-1-1-3-7-3).</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Set working-level ranges for intermediates and blendstocks | define segregation and quality-protection rules | define review triggers tied to campaigns and turnarounds | approve policy exceptions</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>Intermediate tank and transfer operation (Refining) | production planning of intermediates (Refinery Planning, CM-1-1-4) | finished-product policy (CM-1-1-3-7-3) | crude and feedstock policy (CM-1-1-3-7-1)</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>Intermediates &amp; Blendstock Inventory Policy</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Batch 04 (2026-09-19). 'Intermediates' read as unfinished refinery streams and blend components held between processing and blending. Middle node of the three material-class policy siblings. Operational accountability for intermediates (Refining versus planning domains) is a follow-up noted in the batch 04 PR; it does not affect this node's placement or definition.</t>
+        </is>
+      </c>
+      <c r="U26" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V26" s="5" t="inlineStr">
+        <is>
+          <t>Set the binding policy for intermediate and blendstock holdings between processing and blending.</t>
+        </is>
+      </c>
+      <c r="W26" s="5" t="inlineStr">
+        <is>
+          <t>SRC-EI-HM31-001 | SRC-ASCM-CSCP-001</t>
+        </is>
+      </c>
       <c r="X26" s="5" t="n"/>
-      <c r="Y26" s="5" t="n"/>
-      <c r="Z26" s="5" t="n"/>
-      <c r="AA26" s="5" t="n"/>
-      <c r="AB26" s="5" t="n"/>
-      <c r="AC26" s="5" t="n"/>
+      <c r="Y26" s="5" t="inlineStr">
+        <is>
+          <t>unit campaign and turnaround plans | blending requirements | intermediate tankage constraints | quality-segregation requirements</t>
+        </is>
+      </c>
+      <c r="Z26" s="5" t="inlineStr">
+        <is>
+          <t>approved intermediates inventory policy</t>
+        </is>
+      </c>
+      <c r="AA26" s="5" t="inlineStr">
+        <is>
+          <t>informed-by: Refinery Planning | enables: Manage Inventory</t>
+        </is>
+      </c>
+      <c r="AB26" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC26" s="5" t="inlineStr">
+        <is>
+          <t>periodic</t>
+        </is>
+      </c>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -3641,18 +3827,80 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U27" s="5" t="n"/>
-      <c r="V27" s="5" t="n"/>
-      <c r="W27" s="5" t="n"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Establish and maintain the policy governing finished-product inventories across refineries and the distribution network — target and minimum operating levels, safety stock by product and location, brand and quality segregation rules, and review triggers — so customer supply reliability is protected at an efficient working-capital cost.</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Covers policy for saleable products at refinery rack, terminal, and depot level, including service-level-driven safety stocks, seasonal and regulatory grade-transition stock rules, and segregation of branded versus unbranded stock. Sets the policy that Plan Finished Goods Inventory (CM-1-1-2-13) plans within — the plan-period target decision itself is owned there per its approved boundary. Excludes replenishment management, owned by Manage Inventory Replenishment (CM-1-1-3-7-9); excludes physical terminal operation, owned by Midstream.</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Set target, minimum operating, and safety stock levels by product and location | define brand and grade segregation policy | set seasonal and grade-transition stock rules | define review triggers and cadence</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>Plan-period inventory targets (Plan Finished Goods Inventory, CM-1-1-2-13) | replenishment management (CM-1-1-3-7-9) | physical storage operation (Midstream) | sales and offer decisions (Marketing)</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>Finished Goods Inventory Policy | Product Inventory Policy</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Batch 04 (2026-09-19). Boundary to CM-1-1-2-13 was fixed in batch 01 (Hamid, 2026-09-18): policy here, plan-period target decision there. 'Finished product' preferred in text; the batch-01 sibling retains 'finished goods' in its label, with both carried as alt labels there.</t>
+        </is>
+      </c>
+      <c r="U27" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V27" s="5" t="inlineStr">
+        <is>
+          <t>Set the binding policy for finished-product holdings across the network.</t>
+        </is>
+      </c>
+      <c r="W27" s="5" t="inlineStr">
+        <is>
+          <t>SRC-EI-HM32-001 | SRC-ASCM-CSCP-001</t>
+        </is>
+      </c>
       <c r="X27" s="5" t="n"/>
-      <c r="Y27" s="5" t="n"/>
-      <c r="Z27" s="5" t="n"/>
-      <c r="AA27" s="5" t="n"/>
-      <c r="AB27" s="5" t="n"/>
-      <c r="AC27" s="5" t="n"/>
+      <c r="Y27" s="5" t="inlineStr">
+        <is>
+          <t>demand forecast and service-level requirements | seasonal and regulatory grade calendars | terminal tankage constraints | working-capital guidance</t>
+        </is>
+      </c>
+      <c r="Z27" s="5" t="inlineStr">
+        <is>
+          <t>approved finished-product inventory policy</t>
+        </is>
+      </c>
+      <c r="AA27" s="5" t="inlineStr">
+        <is>
+          <t>enables: Plan Finished Goods Inventory | enables: Manage Inventory Replenishment | informed-by: Demand Forecasting</t>
+        </is>
+      </c>
+      <c r="AB27" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC27" s="5" t="inlineStr">
+        <is>
+          <t>periodic</t>
+        </is>
+      </c>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -3720,18 +3968,80 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U28" s="5" t="n"/>
-      <c r="V28" s="5" t="n"/>
-      <c r="W28" s="5" t="n"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Establish the measured physical quantity of crude, intermediate, and product inventory across the network — from tank gauging, metering, and vessel and pipeline measurements converted to standard conditions — so book stock, reconciliation, and planning rest on accurate physical positions.</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Covers the recurring determination of physical inventory quantities: setting the measurement basis and standards applied (per API MPMS practice), collecting gauge, meter, temperature, and density data, converting observed to standard volumes, and establishing the official measured position by tank, terminal, and location. Asset operators — Midstream and Refining — operate the tanks and instruments and take the physical readings; this process owns the standards applied and the official measured position, consistent with the owner-versus-executor pattern in the locked rules. Excludes reconciling measured against book stock, owned by Perform Inventory Reconciliation (CM-1-1-3-7-5); excludes custody-transfer measurement disputes, which follow the relevant commercial agreements.</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Define the measurement basis and applicable standards | collect gauging, metering, temperature, and density data | convert observed to standard volumes | establish the official measured position by location</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>Book-versus-physical reconciliation (CM-1-1-3-7-5) | operating tanks, meters, and instruments (Midstream, Refining) | inventory valuation (Finance)</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>Physical Inventory Measurement | Stock Measurement</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Batch 04 (2026-09-19). Measurement practice follows API MPMS (Chapter 3 tank gauging and related chapters) as the reference standard set. Ownership-versus-execution split follows the locked EHS pattern: asset owners execute readings on assets they operate; this process owns the measurement basis and the official measured position. APQC 16436 'Measure and benchmark' is a WEAK organizational-performance candidate; comparative evidence only.</t>
+        </is>
+      </c>
+      <c r="U28" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V28" s="5" t="inlineStr">
+        <is>
+          <t>Produce the accurate, standards-based physical inventory position the network runs on.</t>
+        </is>
+      </c>
+      <c r="W28" s="5" t="inlineStr">
+        <is>
+          <t>SRC-API-MPMS-001 | SRC-EI-HM32-001</t>
+        </is>
+      </c>
       <c r="X28" s="5" t="n"/>
-      <c r="Y28" s="5" t="n"/>
-      <c r="Z28" s="5" t="n"/>
-      <c r="AA28" s="5" t="n"/>
-      <c r="AB28" s="5" t="n"/>
-      <c r="AC28" s="5" t="n"/>
+      <c r="Y28" s="5" t="inlineStr">
+        <is>
+          <t>tank gauge and meter readings | temperature and density observations | vessel and pipeline measurement tickets | measurement standards and procedures</t>
+        </is>
+      </c>
+      <c r="Z28" s="5" t="inlineStr">
+        <is>
+          <t>official measured inventory position by tank, terminal, and location</t>
+        </is>
+      </c>
+      <c r="AA28" s="5" t="inlineStr">
+        <is>
+          <t>precedes: Perform Inventory Reconciliation | enables: Manage Inventory</t>
+        </is>
+      </c>
+      <c r="AB28" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC28" s="5" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -3799,18 +4109,80 @@
           <t>FALSE MATCH: LSC 'Perform Inventory Reconciliation' is inventory reconciliation; APQC 'Perform benefit reconciliation' (10507) is employee-benefits reconciliation (name similarity 0.667 is misleading). Web validator confirms the HR sense.</t>
         </is>
       </c>
-      <c r="U29" s="5" t="n"/>
-      <c r="V29" s="5" t="n"/>
-      <c r="W29" s="5" t="n"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Reconcile book inventory against measured physical inventory by location and material, quantify and classify gains and losses, investigate variances beyond tolerance, and post agreed corrections so stock records remain accurate and losses are made visible.</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Covers the recurring book-to-physical comparison across tanks, terminals, and in-transit stock: computing over/short by material and location, separating apparent loss (measurement and accounting effects) from physical loss, investigating out-of-tolerance variances, and agreeing corrections to book stock, following hydrocarbon-management good practice (EI HM 32). Excludes taking the physical measurements, owned by Measure Inventory (CM-1-1-3-7-4); excludes financial write-off approval and valuation entries, owned by Finance under the locked Finance rule. A standing loss-control capability that would own systemic loss-reduction programs has no home in the current tree — an open cross-model question carried in the playbook (step 7), deliberately not resolved here.</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Compare book with measured stock by material and location | quantify and classify gains and losses (apparent versus physical) | investigate out-of-tolerance variances | agree and post book corrections</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>Physical measurement (CM-1-1-3-7-4) | financial write-offs and valuation entries (Finance) | systemic loss-control programs (no established owner; playbook step 7 open question) | custody-transfer dispute settlement (commercial agreements)</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>Stock Reconciliation | Book-to-Physical Reconciliation</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Batch 04 (2026-09-19). APQC 10507 'Perform benefit reconciliation' was REJECTED at the Step 3b human gate as a false lexical match (HR benefits); authored independently, honoring that rejection. Apparent-versus-physical loss classification follows EI HM 32. Loss-control ownership beyond reconciliation reporting is deliberately left open per playbook step 7 — naming an owner here would silently resolve a cross-model question.</t>
+        </is>
+      </c>
+      <c r="U29" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V29" s="5" t="inlineStr">
+        <is>
+          <t>Keep book stock true to physical stock and make gains and losses visible and explained.</t>
+        </is>
+      </c>
+      <c r="W29" s="5" t="inlineStr">
+        <is>
+          <t>SRC-EI-HM32-001 | SRC-API-MPMS-001</t>
+        </is>
+      </c>
       <c r="X29" s="5" t="n"/>
-      <c r="Y29" s="5" t="n"/>
-      <c r="Z29" s="5" t="n"/>
-      <c r="AA29" s="5" t="n"/>
-      <c r="AB29" s="5" t="n"/>
-      <c r="AC29" s="5" t="n"/>
+      <c r="Y29" s="5" t="inlineStr">
+        <is>
+          <t>official measured positions | book stock and movement transactions | measurement tolerances | prior variance history</t>
+        </is>
+      </c>
+      <c r="Z29" s="5" t="inlineStr">
+        <is>
+          <t>reconciled stock records with classified, investigated gain/loss</t>
+        </is>
+      </c>
+      <c r="AA29" s="5" t="inlineStr">
+        <is>
+          <t>follows: Measure Inventory | enables: Distribution Backcasting | enables: Manage Inventory</t>
+        </is>
+      </c>
+      <c r="AB29" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC29" s="5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -3873,18 +4245,80 @@
           <t>strong APQC candidate but no validator agreed</t>
         </is>
       </c>
-      <c r="U30" s="5" t="n"/>
-      <c r="V30" s="5" t="n"/>
-      <c r="W30" s="5" t="n"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Manage product held under consignment arrangements — stock positioned at a customer's or partner's site, or held for a third party at company sites, that remains the consignor's property until drawn — tracking positions, draws, and settlement triggers so ownership and stock records stay correct on both sides.</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Covers administering consignment stock over its lifecycle: recording consignment positions by agreement, tracking draws and returns, triggering settlement per the agreement, and keeping consignment stock distinct from owned stock in positions and reconciliation. Excludes negotiating the consignment agreement, owned by the commercial owner of the customer or supplier relationship; excludes invoicing and settlement postings, owned by Finance; excludes physical storage operation, owned by the site operator (Midstream or third party).</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Record and track consignment positions by agreement | track draws, returns, and settlement triggers | keep consignment stock segregated from owned stock in records | support consignment reconciliation</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>Consignment agreement negotiation (commercial relationship owner) | billing and settlement postings (Finance) | physical site storage operation (site operator)</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>Consignment Stock Management</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Batch 04 (2026-09-19). Consignment is defined by ownership: stock remains the consignor's property until a defined drawdown, sale, or title-transfer event — the ownership boundary, not the storage location, distinguishes this node from Manage Third Party Storage (CM-1-1-3-7-11), which covers company-owned stock in third-party facilities. The two are orthogonal arrangements that can apply simultaneously (consignment stock at a third-party terminal); they remain peer processes because the control activities differ, and a future data model should not force them into exclusive subclasses.</t>
+        </is>
+      </c>
+      <c r="U30" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V30" s="5" t="inlineStr">
+        <is>
+          <t>Keep consignment stock, its ownership, and its settlement triggers correctly tracked.</t>
+        </is>
+      </c>
+      <c r="W30" s="5" t="inlineStr">
+        <is>
+          <t>SRC-ASCM-CSCP-001 | SRC-EI-HM32-001</t>
+        </is>
+      </c>
       <c r="X30" s="5" t="n"/>
-      <c r="Y30" s="5" t="n"/>
-      <c r="Z30" s="5" t="n"/>
-      <c r="AA30" s="5" t="n"/>
-      <c r="AB30" s="5" t="n"/>
-      <c r="AC30" s="5" t="n"/>
+      <c r="Y30" s="5" t="inlineStr">
+        <is>
+          <t>consignment agreements | draw and return transactions | site stock reports</t>
+        </is>
+      </c>
+      <c r="Z30" s="5" t="inlineStr">
+        <is>
+          <t>accurate consignment stock positions and settlement triggers</t>
+        </is>
+      </c>
+      <c r="AA30" s="5" t="inlineStr">
+        <is>
+          <t>enables: Perform Inventory Reconciliation | informed-by: Develop Finished Product Inventory Policy</t>
+        </is>
+      </c>
+      <c r="AB30" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC30" s="5" t="inlineStr">
+        <is>
+          <t>continuous</t>
+        </is>
+      </c>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -3947,18 +4381,80 @@
           <t>strong APQC candidate but no validator agreed</t>
         </is>
       </c>
-      <c r="U31" s="5" t="n"/>
-      <c r="V31" s="5" t="n"/>
-      <c r="W31" s="5" t="n"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Manage company stock held commingled with other owners' fungible product in shared tanks, pipelines, and terminals — tracking each party's ownership share, quality basis, and allocated gains and losses under the operative agreements — so the company's entitlement in shared stock is always known and defensible.</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Covers stewardship of ownership entitlements in fungible, jointly stored product: recording ownership shares by facility and product, applying the allocation rules of terminalling, exchange, and pipeline agreements to receipts, deliveries, and losses, and reconciling entitlement statements from facility operators. Excludes operating the shared facility, owned by Midstream or the third-party operator; excludes negotiating exchange and terminalling agreements, owned by Supply And Trading; excludes the physical measurement itself, owned by Measure Inventory (CM-1-1-3-7-4).</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Track ownership shares in commingled stock by facility | apply agreement allocation rules to receipts, deliveries, and losses | reconcile operator entitlement statements | keep entitlement records audit-ready</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>Shared facility operation (Midstream or third-party operator) | exchange and terminalling agreement negotiation (Supply And Trading) | physical measurement (CM-1-1-3-7-4)</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>Commingled Stock Management | Fungible Inventory Management</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Batch 04 (2026-09-19). 'Commingled' read in the downstream fungible-product sense: multiple owners' product physically mixed in shared tankage or pipeline systems, with each party's position represented as a measured or contractual entitlement rather than physically segregated stock. Commingled and lot/batch are arrangements, not permanent asset classifications — one facility can support both for different tanks, products, or periods. APQC 12942 'Manage bulk inventory' STRONG with no validator; comparative evidence only.</t>
+        </is>
+      </c>
+      <c r="U31" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V31" s="5" t="inlineStr">
+        <is>
+          <t>Keep the company's ownership entitlement in shared, fungible stock known and defensible.</t>
+        </is>
+      </c>
+      <c r="W31" s="5" t="inlineStr">
+        <is>
+          <t>SRC-EI-HM32-001 | SRC-EIA-GLOSS-001</t>
+        </is>
+      </c>
       <c r="X31" s="5" t="n"/>
-      <c r="Y31" s="5" t="n"/>
-      <c r="Z31" s="5" t="n"/>
-      <c r="AA31" s="5" t="n"/>
-      <c r="AB31" s="5" t="n"/>
-      <c r="AC31" s="5" t="n"/>
+      <c r="Y31" s="5" t="inlineStr">
+        <is>
+          <t>terminalling, exchange, and pipeline agreements | operator entitlement statements | receipt and delivery transactions</t>
+        </is>
+      </c>
+      <c r="Z31" s="5" t="inlineStr">
+        <is>
+          <t>verified ownership entitlements in commingled stock</t>
+        </is>
+      </c>
+      <c r="AA31" s="5" t="inlineStr">
+        <is>
+          <t>enables: Perform Inventory Reconciliation | uses-input: Measure Inventory</t>
+        </is>
+      </c>
+      <c r="AB31" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC31" s="5" t="inlineStr">
+        <is>
+          <t>continuous</t>
+        </is>
+      </c>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -4021,18 +4517,80 @@
           <t>strong APQC candidate but no validator agreed</t>
         </is>
       </c>
-      <c r="U32" s="5" t="n"/>
-      <c r="V32" s="5" t="n"/>
-      <c r="W32" s="5" t="n"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Manage the re-designation of existing inventory between brand, grade, or specification categories — such as converting unbranded stock to branded through additive treatment, or regrading product that qualifies against a different specification — so stock records, quality status, and documentation reflect what the product now is.</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Covers the decision and record-keeping process of re-designating stock: verifying the product qualifies for the target designation, authorizing the re-brand, updating inventory and quality records, and tracking re-brand volumes and reasons, subject to specification, contractual, tax, and inventory-accounting rules. The physical work — additive injection, blending, laboratory testing — is executed by the operating asset (Midstream terminals or Refining). Excludes brand strategy and consumer brand management, owned by Marketing; excludes off-spec and contaminated-product incident handling, which is an event-driven quality matter, not routine re-branding.</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Verify stock qualifies for the target designation | authorize and record re-brands | update inventory, quality, and documentation records | track re-brand volumes and reasons</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>Physical additive injection, blending, and testing (Midstream, Refining) | brand strategy and brand management (Marketing) | off-spec and contaminated-product incident handling (event-driven quality process, not routine re-branding)</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>Inventory Reclassification | Product Re-designation</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Batch 04 (2026-09-19). 'Re-brand' read in the fuels-inventory sense — controlled re-designation of existing stock between branded/unbranded, grade, commercial identity, or market designation categories — not consumer brand management. The node governs the redesignation decision and records; approved physical blending or additive work is execution by the operating asset. APQC 12410 'Develop and manage brands' scored STRONG lexically but is marketing brand management; treated as a false match, comparative evidence only.</t>
+        </is>
+      </c>
+      <c r="U32" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V32" s="5" t="inlineStr">
+        <is>
+          <t>Ensure re-designated stock is qualified, authorized, and correctly reflected in records.</t>
+        </is>
+      </c>
+      <c r="W32" s="5" t="inlineStr">
+        <is>
+          <t>SRC-EI-HM32-001 | SRC-EIA-GLOSS-001</t>
+        </is>
+      </c>
       <c r="X32" s="5" t="n"/>
-      <c r="Y32" s="5" t="n"/>
-      <c r="Z32" s="5" t="n"/>
-      <c r="AA32" s="5" t="n"/>
-      <c r="AB32" s="5" t="n"/>
-      <c r="AC32" s="5" t="n"/>
+      <c r="Y32" s="5" t="inlineStr">
+        <is>
+          <t>stock quality certificates and test results | brand and grade specifications | re-brand authorizations</t>
+        </is>
+      </c>
+      <c r="Z32" s="5" t="inlineStr">
+        <is>
+          <t>authorized, recorded inventory re-designations</t>
+        </is>
+      </c>
+      <c r="AA32" s="5" t="inlineStr">
+        <is>
+          <t>enables: Manage Inventory | uses-input: Measure Inventory</t>
+        </is>
+      </c>
+      <c r="AB32" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC32" s="5" t="inlineStr">
+        <is>
+          <t>event-driven</t>
+        </is>
+      </c>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -4095,18 +4653,80 @@
           <t>strong APQC candidate but no validator agreed</t>
         </is>
       </c>
-      <c r="U33" s="5" t="n"/>
-      <c r="V33" s="5" t="n"/>
-      <c r="W33" s="5" t="n"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Plan and trigger the replenishment of finished-product stock points across the distribution network — determining when and how much to resupply each terminal and depot within inventory policy and the approved plan — so locations stay between minimum and maximum operating levels without emergency movements.</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Covers the recurring replenishment decision for network stock points: monitoring projected positions against policy levels, determining replenishment quantities and timing, issuing requirements to the scheduling processes, and managing replenishment exceptions and shortfall risk. Works within the approved regional and distribution plans and the policies set by the policy siblings. Excludes plan-period inventory positioning, owned by Plan Finished Goods Inventory (CM-1-1-2-13); excludes scheduling the physical movements, owned by Physical Distribution Scheduling (CM-1-1-3-6) and Secondary Distribution Management (CM-1-1-3-8); excludes transport and terminal execution, owned by Midstream; excludes feedstock resupply, which sits with Supply And Trading per the batch 04 boundary.</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Monitor projected stock against policy levels by location | determine replenishment quantities and timing | issue replenishment requirements to scheduling | manage replenishment exceptions and shortfall risk</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>Plan-period inventory targets (CM-1-1-2-13) | movement scheduling (CM-1-1-3-6, CM-1-1-3-8) | transport and terminal execution (Midstream) | feedstock replenishment (Supply And Trading, per the batch 04 boundary)</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>Stock Replenishment Planning | Replenishment Management</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Batch 04 (2026-09-19). Batch 01 already carved 'replenishment execution' out of Plan Finished Goods Inventory to this node; authored to receive that boundary. Scope is finished-product network replenishment; crude and feedstock resupply sits with Supply And Trading per the Q3 decision. Decision right confirmed in batch 04: this node owns the replenishment decision (when and how much); Manage Inventory (CM-1-1-3-7-12) detects and escalates exceptions but does not own the decision; movement scheduling and physical execution remain excluded.</t>
+        </is>
+      </c>
+      <c r="U33" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V33" s="5" t="inlineStr">
+        <is>
+          <t>Decide when and how much each network stock point is resupplied within policy and plan.</t>
+        </is>
+      </c>
+      <c r="W33" s="5" t="inlineStr">
+        <is>
+          <t>SRC-LNL-T2S-001 | SRC-ASCM-CSCP-001</t>
+        </is>
+      </c>
       <c r="X33" s="5" t="n"/>
-      <c r="Y33" s="5" t="n"/>
-      <c r="Z33" s="5" t="n"/>
-      <c r="AA33" s="5" t="n"/>
-      <c r="AB33" s="5" t="n"/>
-      <c r="AC33" s="5" t="n"/>
+      <c r="Y33" s="5" t="inlineStr">
+        <is>
+          <t>projected stock positions | inventory policy levels | approved distribution plan | demand offtake at stock points</t>
+        </is>
+      </c>
+      <c r="Z33" s="5" t="inlineStr">
+        <is>
+          <t>replenishment requirements by location and timing</t>
+        </is>
+      </c>
+      <c r="AA33" s="5" t="inlineStr">
+        <is>
+          <t>governed-by: Develop Finished Product Inventory Policy | precedes: Physical Distribution Scheduling | informed-by: Plan Finished Goods Inventory</t>
+        </is>
+      </c>
+      <c r="AB33" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC33" s="5" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -4169,18 +4789,80 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U34" s="5" t="n"/>
-      <c r="V34" s="5" t="n"/>
-      <c r="W34" s="5" t="n"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Manage inventory that must be tracked by lot or batch identity — such as specialty products, additives, and quality-certified stock — preserving batch identity, certificates, and traceability from receipt through storage to issue.</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Covers lot- and batch-level stock control where identity must survive storage and movement: assigning and preserving batch identity in stock records, holding certificates of analysis and quality status against each lot, applying lot-selection rules at issue, and supporting recall and claims traceability. Distinct from fungible bulk stock managed as commingled entitlements (CM-1-1-3-7-7), where batch identity is deliberately not preserved. Excludes laboratory testing and certificate generation, owned by the operating asset's quality function; excludes batch production and blending execution, owned by Refining.</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Assign and preserve lot/batch identity in stock records | hold quality certificates and status by lot | apply lot-selection rules at issue | maintain lot traceability for recall and claims</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>Laboratory testing and certification (operating asset quality function) | batch production and blending execution (Refining) | fungible bulk entitlement tracking (CM-1-1-3-7-7)</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>Batch-Tracked Inventory Management | Lot Traceability Management</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Batch 04 (2026-09-19). The lot/batch-versus-fungible split is the organizing boundary with CM-1-1-3-7-7: identity-preserved stock here, entitlement-tracked fungible stock there — modeled as arrangements or control requirements, not permanent asset classifications. Relevant to specialty and additive lines where certificates and recall traceability are required.</t>
+        </is>
+      </c>
+      <c r="U34" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V34" s="5" t="inlineStr">
+        <is>
+          <t>Preserve batch identity, quality status, and traceability for stock that must not be treated as fungible.</t>
+        </is>
+      </c>
+      <c r="W34" s="5" t="inlineStr">
+        <is>
+          <t>SRC-ASCM-CSCP-001 | SRC-EI-HM32-001</t>
+        </is>
+      </c>
       <c r="X34" s="5" t="n"/>
-      <c r="Y34" s="5" t="n"/>
-      <c r="Z34" s="5" t="n"/>
-      <c r="AA34" s="5" t="n"/>
-      <c r="AB34" s="5" t="n"/>
-      <c r="AC34" s="5" t="n"/>
+      <c r="Y34" s="5" t="inlineStr">
+        <is>
+          <t>batch and lot identifiers from production and receipt | certificates of analysis | lot-selection rules</t>
+        </is>
+      </c>
+      <c r="Z34" s="5" t="inlineStr">
+        <is>
+          <t>traceable lot/batch stock records with quality status</t>
+        </is>
+      </c>
+      <c r="AA34" s="5" t="inlineStr">
+        <is>
+          <t>enables: Perform Inventory Reconciliation | informed-by: Develop Finished Product Inventory Policy</t>
+        </is>
+      </c>
+      <c r="AB34" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC34" s="5" t="inlineStr">
+        <is>
+          <t>continuous</t>
+        </is>
+      </c>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -4243,18 +4925,80 @@
           <t>strong APQC candidate but no validator agreed</t>
         </is>
       </c>
-      <c r="U35" s="5" t="n"/>
-      <c r="V35" s="5" t="n"/>
-      <c r="W35" s="5" t="n"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Manage company inventory held in third-party storage facilities — leased tankage, throughput agreements, and commercial storage — administering capacity entitlements, monitoring stock positions and operator statements, and managing performance against the storage agreements.</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Covers the inventory-side administration of third-party storage: tracking company stock by facility and agreement, reconciling operator stock statements, monitoring utilization of leased capacity and throughput commitments, and flagging agreement performance issues. Excludes negotiating storage and terminalling agreements, owned by the commercial owner (Supply And Trading); excludes the operator's physical facility operation; excludes commingled entitlement mechanics, owned by Manage Commingled Inventory (CM-1-1-3-7-7) where stock in a third-party facility is fungible and shared.</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Track company stock by third-party facility and agreement | reconcile operator stock statements | monitor leased capacity and throughput utilization | flag storage-agreement performance issues</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>Storage agreement negotiation (Supply And Trading) | physical facility operation (third-party operator) | commingled entitlement tracking (CM-1-1-3-7-7)</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>Third-Party Terminal Storage Management | Leased Storage Management</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Batch 04 (2026-09-19). APQC 12944 'Manage third party bulk storage' scored 0.889 STRONG with no validator source; used as supporting comparative evidence, with the local definition bounded to inventory administration rather than facility operation. Governing distinction is the facility/custody boundary: company-owned stock in someone else's facility. Orthogonal to consignment (ownership boundary, CM-1-1-3-7-6) — both can apply simultaneously — and to commingled (entitlement in shared fungible stock, CM-1-1-3-7-7).</t>
+        </is>
+      </c>
+      <c r="U35" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V35" s="5" t="inlineStr">
+        <is>
+          <t>Keep company stock in third-party facilities visible, reconciled, and within agreement entitlements.</t>
+        </is>
+      </c>
+      <c r="W35" s="5" t="inlineStr">
+        <is>
+          <t>SRC-EI-HM32-001 | SRC-ASCM-CSCP-001</t>
+        </is>
+      </c>
       <c r="X35" s="5" t="n"/>
-      <c r="Y35" s="5" t="n"/>
-      <c r="Z35" s="5" t="n"/>
-      <c r="AA35" s="5" t="n"/>
-      <c r="AB35" s="5" t="n"/>
-      <c r="AC35" s="5" t="n"/>
+      <c r="Y35" s="5" t="inlineStr">
+        <is>
+          <t>storage and throughput agreements | operator stock statements | company movement records</t>
+        </is>
+      </c>
+      <c r="Z35" s="5" t="inlineStr">
+        <is>
+          <t>reconciled third-party storage positions and utilization status</t>
+        </is>
+      </c>
+      <c r="AA35" s="5" t="inlineStr">
+        <is>
+          <t>enables: Perform Inventory Reconciliation | uses-input: Measure Inventory</t>
+        </is>
+      </c>
+      <c r="AB35" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC35" s="5" t="inlineStr">
+        <is>
+          <t>continuous</t>
+        </is>
+      </c>
       <c r="AD35" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -4317,18 +5061,80 @@
           <t>strong APQC candidate but no validator agreed</t>
         </is>
       </c>
-      <c r="U36" s="5" t="n"/>
-      <c r="V36" s="5" t="n"/>
-      <c r="W36" s="5" t="n"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Monitor and control actual and projected inventory positions for finished products and intermediates: identify operating-limit, availability, ownership, quality, location, and balance exceptions, coordinate timely response, and provide reliable current-position information to planning and operational stakeholders.</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Covers the recurring review of physical and book inventory positions, movements, and commitments; minimum, maximum, safety-stock, and operating-limit exceptions; short-term availability and imbalance risks; escalation and coordination of corrective actions; and maintenance of the operational inventory-position view that planning and execution consume — a recurring operational control rhythm that complements planning cycles. Excludes inventory-policy design (CM-1-1-3-7-1/-2/-3), formal measurement methodology (CM-1-1-3-7-4), reconciliation and adjustment governance (CM-1-1-3-7-5), and replenishment planning (CM-1-1-3-7-9); excludes the specialized consignment, commingled, re-brand, lot/batch, and third-party-storage arrangements (CM-1-1-3-7-6/-7/-8/-10/-11), except where those arrangements create an operational position exception requiring response; excludes day-to-day crude and feedstock position management, owned by Manage Feedstock Inventory (CM-1-2-5-4-2).</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Review physical and book positions, movements, and commitments by location | detect operating-limit, availability, and balance exceptions | escalate and coordinate corrective actions | maintain the operational position view for planning and execution</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>Inventory policy design (CM-1-1-3-7-1/-2/-3) | measurement methodology (CM-1-1-3-7-4) | reconciliation governance (CM-1-1-3-7-5) | replenishment planning and decisions (CM-1-1-3-7-9) | specialized arrangement controls (CM-1-1-3-7-6/-7/-8/-10/-11) | feedstock position management (CM-1-2-5-4-2)</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>Monitor and Control Inventory Positions | Inventory Position Management</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Batch 04 (2026-09-19). Q2 decision (Hamid, Option A, tightened): approved in place as a distinct operational process — position stewardship and exception response, which no sibling owns — with material scope limited to finished products and intermediates so it cannot silently reclaim feedstock (Q3). Preferred normalized label 'Monitor and Control Inventory Positions' recorded for the consolidated naming pass; current label retained for traceability, and the collision with the L4 label is queued with it. Decision right: this process identifies and escalates replenishment needs; Manage Inventory Replenishment (CM-1-1-3-7-9) owns the replenishment decision. Daily stock control as distinct from periodic reconciliation follows EI HM 32 practice. APQC 12942 'Manage bulk inventory' STRONG with no validator; comparative evidence only.</t>
+        </is>
+      </c>
+      <c r="U36" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V36" s="5" t="inlineStr">
+        <is>
+          <t>Keep day-to-day finished-product and intermediates positions inside operating limits and make the current position visible.</t>
+        </is>
+      </c>
+      <c r="W36" s="5" t="inlineStr">
+        <is>
+          <t>SRC-EI-HM32-001 | SRC-LNL-T2S-001</t>
+        </is>
+      </c>
       <c r="X36" s="5" t="n"/>
-      <c r="Y36" s="5" t="n"/>
-      <c r="Z36" s="5" t="n"/>
-      <c r="AA36" s="5" t="n"/>
-      <c r="AB36" s="5" t="n"/>
-      <c r="AC36" s="5" t="n"/>
+      <c r="Y36" s="5" t="inlineStr">
+        <is>
+          <t>official measured positions | movement schedules | policy operating limits | demand offtake</t>
+        </is>
+      </c>
+      <c r="Z36" s="5" t="inlineStr">
+        <is>
+          <t>current position picture and excursion responses</t>
+        </is>
+      </c>
+      <c r="AA36" s="5" t="inlineStr">
+        <is>
+          <t>uses-input: Measure Inventory | triggers: Manage Inventory Replenishment | governed-by: Develop Finished Product Inventory Policy</t>
+        </is>
+      </c>
+      <c r="AB36" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC36" s="5" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
       <c r="AD36" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -18588,6 +19394,11 @@
       <c r="M210" t="inlineStr">
         <is>
           <t>strong APQC candidate but no validator agreed</t>
+        </is>
+      </c>
+      <c r="T210" t="inlineStr">
+        <is>
+          <t>Batch 04 (2026-09-19), binding constraint recorded per Hamid's Q3 decision, reciprocal to CM-1-1-3-7: the future definition of this node must be limited to crude-oil and refinery-feedstock inventory positions, availability, operating constraints, and supply/refinery coordination. It must not claim enterprise ownership of inventory policy, measurement standards, formal reconciliation, generic replenishment, or the management of finished-product and intermediate inventory positions — those sit in the Inventory cluster (CM-1-1-3-7). Row remains pending; it belongs to the Supply And Trading batch.</t>
         </is>
       </c>
       <c r="U210" s="5" t="n"/>
@@ -42453,7 +43264,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -43297,6 +44108,147 @@
         </is>
       </c>
       <c r="I23" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>SRC-API-MPMS-001</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>American Petroleum Institute</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Manual of Petroleum Measurement Standards (incl. Chapter 3, Tank Gauging)</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Current editions; accessed 2026-09-19</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>https://www.api.org/-/media/files/publications/2025-catalog/03_measurement_2025.pdf</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Industry standards body</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Measurement practice evidence; evidence only, not text to copy</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Tank gauging, metering, standard-volume conversion; inventory-control versus custody-transfer measurement</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>SRC-EI-HM31-001</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Energy Institute</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>HM 31 - Guide to hydrocarbon management in petroleum refinery operations</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Current edition; accessed 2026-09-19</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>https://www.energyinst.org/industry/publications/topics/hydrocarbon-management/hm-31.-guide-to-hydrocarbon-management-in-petroleum-refinery-operations</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Industry standards body</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Refinery-side stock control practice; evidence only</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Crude, feedstock, and intermediates inventory practice in refinery operations</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>SRC-EI-HM32-001</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Energy Institute</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>HM 32 - Guide to hydrocarbon management at petroleum product marketing and distribution terminals</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Current edition; accessed 2026-09-19</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>https://www.energyinst.org/technical/publications/topics/hydrocarbon-management/hm-32.-guide-to-hydrocarbon-management-at-petroleum-product-marketing-and-distribution-terminals</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Industry standards body</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Terminal stock control practice; evidence only</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Terminal stock control, apparent-versus-physical loss classification, reconciliation and loss monitoring</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
         <is>
           <t>active</t>
         </is>

--- a/business_architecture/ontology/build/output/step3c-definition-authoring-workbook.xlsx
+++ b/business_architecture/ontology/build/output/step3c-definition-authoring-workbook.xlsx
@@ -2708,18 +2708,80 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U15" s="5" t="n"/>
-      <c r="V15" s="5" t="n"/>
-      <c r="W15" s="5" t="n"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Develop and maintain the short-term product supply schedule for the primary distribution network — deciding which products move between refineries, terminals, and supply points, in what quantities and sequence over the coming days and weeks — so the approved regional plan is translated into an executable movement program.</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Covers short-term network scheduling within the approved regional plan: consolidating demand, stock, and supply projections into a rolling network schedule, sequencing bulk product movements, coordinating the trades needed to balance the schedule, and adjusting to disruptions. Excludes plan-period supply and disposition decisions, owned by Regional Optimization (CM-1-1-2); excludes mode-level nomination, load, and movement administration, owned by Physical Distribution Scheduling (CM-1-1-3-6); excludes secondary deliveries, owned by Secondary Distribution Management (CM-1-1-3-8); excludes trade negotiation and execution, owned by Supply And Trading.</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Consolidate short-term demand, stock, and supply projections | develop and maintain the rolling network product schedule | sequence and adjust bulk movements within plan and policy | initiate schedule-balancing trade requests</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Plan-period supply and disposition optimization (Regional Optimization, CM-1-1-2) | nomination, load, and movement administration (CM-1-1-3-6) | secondary delivery scheduling (CM-1-1-3-8) | trade negotiation and execution (Supply And Trading)</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Short-Term Product Supply Scheduling | Network Product Scheduling</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Batch 05 (2026-09-19). Sits between the approved monthly regional plan (CM-1-1-2) and movement administration (CM-1-1-3-6): this L4 decides the short-term schedule; its sibling administers the movements it creates. APQC 16820 'Design for product servicing' is an unrelated lexical match; no meaningful candidate.</t>
+        </is>
+      </c>
+      <c r="U15" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V15" s="5" t="inlineStr">
+        <is>
+          <t>Decide the short-term product movement schedule the primary network runs on.</t>
+        </is>
+      </c>
+      <c r="W15" s="5" t="inlineStr">
+        <is>
+          <t>SRC-ORP-DPSC-001 | SRC-LNL-T2S-001</t>
+        </is>
+      </c>
       <c r="X15" s="5" t="n"/>
-      <c r="Y15" s="5" t="n"/>
-      <c r="Z15" s="5" t="n"/>
-      <c r="AA15" s="5" t="n"/>
-      <c r="AB15" s="5" t="n"/>
-      <c r="AC15" s="5" t="n"/>
+      <c r="Y15" s="5" t="inlineStr">
+        <is>
+          <t>approved regional plan | stock positions and projections | short-term demand and lifting forecasts | transport and terminal availability</t>
+        </is>
+      </c>
+      <c r="Z15" s="5" t="inlineStr">
+        <is>
+          <t>rolling short-term network product schedule</t>
+        </is>
+      </c>
+      <c r="AA15" s="5" t="inlineStr">
+        <is>
+          <t>informed-by: Regional Optimization | precedes: Physical Distribution Scheduling | uses-input: Manage Inventory</t>
+        </is>
+      </c>
+      <c r="AB15" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC15" s="5" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -2787,18 +2849,80 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U16" s="5" t="n"/>
-      <c r="V16" s="5" t="n"/>
-      <c r="W16" s="5" t="n"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Produce the rolling days-to-weeks network supply plan that bridges the approved regional plan and daily execution — projecting stock, demand, production, and movements by location and product, and setting the movement quantities and timings the schedule will execute.</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Covers building and refreshing the short-term network plan: netting projected supply, demand, and stock by location and product; identifying surpluses, shortfalls, and timing constraints; setting planned movements and their windows; reconciling to the regional plan and flagging material deviations back to planning. Excludes plan-period optimization, owned by Regional Optimization (CM-1-1-2); excludes issuing nominations and movement administration (CM-1-1-3-6); consumes replenishment requirements from Manage Inventory Replenishment (CM-1-1-3-7-9) rather than re-deciding them, per the batch 04 decision-right rule.</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Project supply, demand, and stock by location and product | net surpluses and shortfalls and set planned movements | reconcile the short-term plan to the regional plan | flag material deviations to planning</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>Plan-period optimization (Regional Optimization, CM-1-1-2) | nomination and movement administration (CM-1-1-3-6) | stock-point replenishment decisions (Manage Inventory Replenishment, CM-1-1-3-7-9), whose requirements this plan consumes</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Short-Term Supply Plan | Rolling Network Plan</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Batch 05 (2026-09-19). Bridges the monthly regional plan and daily movement administration; the replenishment decision right stays with CM-1-1-3-7-9 per batch 04 — this plan consumes those requirements. APQC 16501 is an unrelated channel-improvement candidate; comparative evidence only.</t>
+        </is>
+      </c>
+      <c r="U16" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V16" s="5" t="inlineStr">
+        <is>
+          <t>Set the executable days-to-weeks network movement plan within the approved regional plan.</t>
+        </is>
+      </c>
+      <c r="W16" s="5" t="inlineStr">
+        <is>
+          <t>SRC-ORP-DPSC-001 | SRC-LNL-T2S-001</t>
+        </is>
+      </c>
       <c r="X16" s="5" t="n"/>
-      <c r="Y16" s="5" t="n"/>
-      <c r="Z16" s="5" t="n"/>
-      <c r="AA16" s="5" t="n"/>
-      <c r="AB16" s="5" t="n"/>
-      <c r="AC16" s="5" t="n"/>
+      <c r="Y16" s="5" t="inlineStr">
+        <is>
+          <t>approved regional plan | replenishment requirements | stock projections | production and receipt forecasts</t>
+        </is>
+      </c>
+      <c r="Z16" s="5" t="inlineStr">
+        <is>
+          <t>rolling short-term network plan with planned movements</t>
+        </is>
+      </c>
+      <c r="AA16" s="5" t="inlineStr">
+        <is>
+          <t>informed-by: Regional Optimization | uses-input: Manage Inventory Replenishment | precedes: Plan &amp; Execute Nominations</t>
+        </is>
+      </c>
+      <c r="AB16" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC16" s="5" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -2866,18 +2990,80 @@
           <t>no meaningful APQC candidate</t>
         </is>
       </c>
-      <c r="U17" s="5" t="n"/>
-      <c r="V17" s="5" t="n"/>
-      <c r="W17" s="5" t="n"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Identify schedule imbalances that cannot be resolved with the company's own supply — surpluses to place or shortfalls to cover — and coordinate with Supply And Trading to request, evaluate, and incorporate the purchases, sales, or exchanges that balance the short-term schedule.</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Covers the scheduling-side interface to trading: quantifying the imbalance and its product, quantity, timing, location, and quality requirements; requesting trading action; evaluating proposed trades for schedulability; and incorporating agreed volumes into the schedule. Excludes trade negotiation and execution, owned by Supply And Trading; excludes plan-period supply sourcing, owned by Regional Optimization (CM-1-1-2); excludes exchange agreement management, owned by Supply And Trading. Trading decides the deal; scheduling decides the schedule.</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Quantify schedule surpluses and shortfalls needing trade action | request and specify trading requirements | evaluate proposed trades for schedulability | incorporate agreed trade volumes into the schedule</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>Trade negotiation and execution (Supply And Trading) | plan-period supply sourcing (Regional Optimization, CM-1-1-2) | exchange agreement management (Supply And Trading)</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>Schedule-Balancing Trade Coordination</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Batch 05 (2026-09-19). Read as the scheduling-side interface to trading, mirroring Coordinate Feedstock Trading (CM-1-2-5-2-1) on the feedstock side and the established decide-versus-advise pattern: this node specifies what the schedule needs and consumes the result; Supply And Trading owns the trade. Whether this coordination is consistently owned by Commercial &amp; Marketing across operating regions is a follow-up noted in the batch 05 PR. No APQC candidate.</t>
+        </is>
+      </c>
+      <c r="U17" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V17" s="5" t="inlineStr">
+        <is>
+          <t>Get schedule imbalances covered through trading without owning the trade.</t>
+        </is>
+      </c>
+      <c r="W17" s="5" t="inlineStr">
+        <is>
+          <t>SRC-ORP-DPSC-001 | SRC-EIA-GLOSS-001</t>
+        </is>
+      </c>
       <c r="X17" s="5" t="n"/>
-      <c r="Y17" s="5" t="n"/>
-      <c r="Z17" s="5" t="n"/>
-      <c r="AA17" s="5" t="n"/>
-      <c r="AB17" s="5" t="n"/>
-      <c r="AC17" s="5" t="n"/>
+      <c r="Y17" s="5" t="inlineStr">
+        <is>
+          <t>short-term network plan imbalances | product quality and location requirements | trading availability and proposals</t>
+        </is>
+      </c>
+      <c r="Z17" s="5" t="inlineStr">
+        <is>
+          <t>trade requests and schedulable trade volumes incorporated into the schedule</t>
+        </is>
+      </c>
+      <c r="AA17" s="5" t="inlineStr">
+        <is>
+          <t>enables: Develop Short-Term Network Plan</t>
+        </is>
+      </c>
+      <c r="AB17" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC17" s="5" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -2948,7 +3134,18 @@
       <c r="U18" s="5" t="n"/>
       <c r="V18" s="5" t="n"/>
       <c r="W18" s="5" t="n"/>
-      <c r="X18" s="5" t="n"/>
+      <c r="X18" s="5" t="inlineStr">
+        <is>
+          <t>Question: What recurring activity does 'Process Business Renewal Request' denote, and which decision right does it hold — deciding network schedulability, approving or renewing a commercial arrangement, or providing scheduling input to a commercial renewal decision made elsewhere?
+Context: L5 under Product Scheduling (CM-1-1-3-5), whose siblings are short-term network scheduling processes; no repo or external anchor exists for the label; APQC 10324 'Process customer request' is a WEAK review-link.
+Options:
+A) Scheduling-side evaluation of renewals of recurring supply, exchange, terminalling, or throughput arrangements for network feasibility (Product Scheduling / Supply And Trading interface).
+B) Customer contract, pricing, or account renewal — would belong to Marketing / Order Management and imply a placement change.
+C) Internal renewal of a business-service request or authorization — would belong to an enabling function and imply a placement change.
+Evidence: Label is organization-specific; parent and siblings support only reading A; no high-quality external source can settle it; the APQC candidate is unrelated.
+Recommendation: Confirm the intended meaning and decision right with the business owner before authoring. Reading A is the only one that passes the parent test but is not evidenced enough to approve. Row stays pending (decision: Hamid, batch 05, 2026-09-19).</t>
+        </is>
+      </c>
       <c r="Y18" s="5" t="n"/>
       <c r="Z18" s="5" t="n"/>
       <c r="AA18" s="5" t="n"/>
@@ -3019,18 +3216,80 @@
           <t>no meaningful APQC candidate</t>
         </is>
       </c>
-      <c r="U19" s="5" t="n"/>
-      <c r="V19" s="5" t="n"/>
-      <c r="W19" s="5" t="n"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Schedule and administer the primary distribution movements that execute the product schedule — nominating volumes to pipelines, vessels, rail, and terminals, administering load and discharge events, and tracking movements to closure — so scheduled product arrives where the plan requires, fully documented.</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Covers mode-level movement scheduling and administration from planned movement to closed load: nominations and confirmations with carriers and terminal operators, load authorization and documentation, in-transit tracking, and discharge confirmation with per-load reconciliation. Midstream, carriers, and terminal operators perform the physical loading, transport, and discharge; this process owns the schedule, the shipper-side administration, and the movement record, per the locked Midstream rule and the owner-versus-executor pattern. Excludes deciding what moves where and when, owned by Product Scheduling (CM-1-1-3-5); excludes secondary deliveries (CM-1-1-3-8).</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Nominate and confirm movements with carriers and terminals | authorize and administer load and discharge events | track movements to closure | maintain the movement record</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>Short-term schedule decisions (Product Scheduling, CM-1-1-3-5) | physical loading, transport, and discharge operation (Midstream, carriers, terminal operators) | secondary delivery scheduling (CM-1-1-3-8)</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>Primary Distribution Scheduling | Movement Scheduling &amp; Administration</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Batch 05 (2026-09-19). 'Physical' in the label refers to the movements being scheduled, not to this process performing them — the locked Midstream rule holds. Nomination-cycle and batching practice per the DOE refined-product pipeline backgrounder. APQC: no meaningful candidate.</t>
+        </is>
+      </c>
+      <c r="U19" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V19" s="5" t="inlineStr">
+        <is>
+          <t>Turn the product schedule into nominated, tracked, closed movements.</t>
+        </is>
+      </c>
+      <c r="W19" s="5" t="inlineStr">
+        <is>
+          <t>SRC-DOE-RPPL-001 | SRC-EI-HM32-001 | SRC-LNL-T2S-001</t>
+        </is>
+      </c>
       <c r="X19" s="5" t="n"/>
-      <c r="Y19" s="5" t="n"/>
-      <c r="Z19" s="5" t="n"/>
-      <c r="AA19" s="5" t="n"/>
-      <c r="AB19" s="5" t="n"/>
-      <c r="AC19" s="5" t="n"/>
+      <c r="Y19" s="5" t="inlineStr">
+        <is>
+          <t>short-term network schedule | carrier and terminal capacities and cycles | movement documentation</t>
+        </is>
+      </c>
+      <c r="Z19" s="5" t="inlineStr">
+        <is>
+          <t>nominated, administered, and closed primary distribution movements</t>
+        </is>
+      </c>
+      <c r="AA19" s="5" t="inlineStr">
+        <is>
+          <t>follows: Product Scheduling | enables: Distribution Backcasting</t>
+        </is>
+      </c>
+      <c r="AB19" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC19" s="5" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -3098,18 +3357,80 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U20" s="5" t="n"/>
-      <c r="V20" s="5" t="n"/>
-      <c r="W20" s="5" t="n"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Prepare, submit, and manage volume nominations to pipelines, vessels, rail, and terminal operators — matching the short-term schedule to each carrier's cycles, batch specifications, and deadlines, and managing confirmations, revisions, and allocations through the cycle.</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Covers the shipper-side nomination process: translating planned movements into nominations per carrier tariff and cycle rules, including segregated versus fungible batch specifications and cycle deadlines; submitting, confirming, and revising nominations; managing carrier allocation and prorationing effects; and keeping the schedule aligned with confirmed nominations. Excludes the carrier's own pipeline scheduling and batching operation; excludes movement quantity decisions, owned by Product Scheduling (CM-1-1-3-5); excludes physical transport, owned by Midstream and carriers.</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Prepare nominations per carrier cycles and specifications | submit, confirm, and revise nominations | manage carrier allocations and prorationing effects | align the schedule with confirmed nominations</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>Carrier pipeline scheduling and batching operation (carriers, Midstream) | movement quantity decisions (CM-1-1-3-5) | physical transport (Midstream, carriers)</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>Nominations Management</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Batch 05 (2026-09-19). Nomination practice per the DOE backgrounder: shippers nominate to common carriers roughly monthly, movements schedule in multi-day cycles, batches are segregated or fungible per tariff specification; revision and allocation management is intra-cycle. Evidence is contextual — nomination frequency, tariffs, and cycle structures vary by carrier and are not asserted as this organization's model. 'Execute' is read as executing the nomination process, not the physical movement. APQC 20851 is an unrelated IT candidate.</t>
+        </is>
+      </c>
+      <c r="U20" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V20" s="5" t="inlineStr">
+        <is>
+          <t>Secure and maintain the carrier capacity the schedule needs, cycle by cycle.</t>
+        </is>
+      </c>
+      <c r="W20" s="5" t="inlineStr">
+        <is>
+          <t>SRC-DOE-RPPL-001</t>
+        </is>
+      </c>
       <c r="X20" s="5" t="n"/>
-      <c r="Y20" s="5" t="n"/>
-      <c r="Z20" s="5" t="n"/>
-      <c r="AA20" s="5" t="n"/>
-      <c r="AB20" s="5" t="n"/>
-      <c r="AC20" s="5" t="n"/>
+      <c r="Y20" s="5" t="inlineStr">
+        <is>
+          <t>planned movements | carrier tariffs, cycles, and deadlines | batch specifications | confirmed capacity</t>
+        </is>
+      </c>
+      <c r="Z20" s="5" t="inlineStr">
+        <is>
+          <t>confirmed nominations aligned to the schedule</t>
+        </is>
+      </c>
+      <c r="AA20" s="5" t="inlineStr">
+        <is>
+          <t>follows: Develop Short-Term Network Plan | precedes: Loading Shipment</t>
+        </is>
+      </c>
+      <c r="AB20" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC20" s="5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -3177,18 +3498,80 @@
           <t>no meaningful APQC candidate</t>
         </is>
       </c>
-      <c r="U21" s="5" t="n"/>
-      <c r="V21" s="5" t="n"/>
-      <c r="W21" s="5" t="n"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Administer the loading of scheduled shipments at refineries and terminals — authorizing the lifting, confirming loaded quantities and quality documentation, and capturing the load into movement and inventory records — so each shipment leaves accounted for and per schedule.</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Covers shipper-side load administration: releasing and authorizing scheduled loads, confirming loaded volumes and documentation (measurement tickets, bills of lading, quality certificates) per despatch practice (EI HM 32), recording the load against movement and stock records, and flagging load exceptions. The physical loading operation is owned by the terminal operator (Midstream or third party) per the locked Midstream rule. Excludes nomination management (CM-1-1-3-6-1) and in-transit tracking (CM-1-1-3-6-3).</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Authorize and release scheduled loads | confirm loaded quantities and quality documentation | record loads into movement and inventory records | flag load exceptions</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>Physical loading operation (terminal operator: Midstream or third party) | nomination management (CM-1-1-3-6-1) | in-transit tracking (CM-1-1-3-6-3)</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>Load Administration | Shipment Loading Administration</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Batch 05 (2026-09-19). Owner-versus-executor per the locked Midstream rule, following the batch 04 Measure Inventory precedent; despatch measurement and documentation practice per EI HM 32. Preferred normalized label 'Administer Shipment Loading' queued for the naming pass (Hamid, batch 05) — the current label reads as an activity in progress rather than a stable process name. APQC: no meaningful candidate.</t>
+        </is>
+      </c>
+      <c r="U21" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V21" s="5" t="inlineStr">
+        <is>
+          <t>Get each scheduled load authorized, documented, and recorded.</t>
+        </is>
+      </c>
+      <c r="W21" s="5" t="inlineStr">
+        <is>
+          <t>SRC-EI-HM32-001 | SRC-DOE-RPPL-001</t>
+        </is>
+      </c>
       <c r="X21" s="5" t="n"/>
-      <c r="Y21" s="5" t="n"/>
-      <c r="Z21" s="5" t="n"/>
-      <c r="AA21" s="5" t="n"/>
-      <c r="AB21" s="5" t="n"/>
-      <c r="AC21" s="5" t="n"/>
+      <c r="Y21" s="5" t="inlineStr">
+        <is>
+          <t>confirmed schedule and nominations | measurement tickets and quality certificates | terminal load confirmations</t>
+        </is>
+      </c>
+      <c r="Z21" s="5" t="inlineStr">
+        <is>
+          <t>documented, recorded loads</t>
+        </is>
+      </c>
+      <c r="AA21" s="5" t="inlineStr">
+        <is>
+          <t>follows: Plan &amp; Execute Nominations | precedes: Track Movements and Inventory Management</t>
+        </is>
+      </c>
+      <c r="AB21" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC21" s="5" t="inlineStr">
+        <is>
+          <t>event-driven</t>
+        </is>
+      </c>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -3256,18 +3639,80 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U22" s="5" t="n"/>
-      <c r="V22" s="5" t="n"/>
-      <c r="W22" s="5" t="n"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Track scheduled movements from load to discharge — monitoring progress against the schedule, maintaining in-transit inventory visibility by movement, and updating scheduling and inventory records as movements progress — so the network always knows what is en route, where, and when it will arrive.</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Covers in-transit tracking and its inventory effects: movement status against schedule, arrival estimates and delays, in-transit stock by product and movement, and feeding position updates to inventory and scheduling processes. The label's 'Inventory Management' is bounded to movement-linked in-transit inventory only; stock-point position stewardship is owned by Manage Inventory (CM-1-1-3-7-12) per batch 04. Excludes carrier transport operation, owned by Midstream and carriers.</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Monitor movement status and arrival estimates against schedule | maintain in-transit inventory visibility by movement | update scheduling and inventory records as movements progress | flag movement delays and exceptions</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>Stock-point position stewardship (Manage Inventory, CM-1-1-3-7-12) | carrier transport operation (Midstream, carriers) | discharge administration (CM-1-1-3-6-4)</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>Movement Tracking | In-Transit Inventory Tracking</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Batch 05 (2026-09-19). The label's 'Inventory Management' is bounded to in-transit, movement-linked inventory; stock-point positions belong to CM-1-1-3-7-12 per batch 04. APQC 10353 'Track inventory deployment' is contextual evidence only (review-link).</t>
+        </is>
+      </c>
+      <c r="U22" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V22" s="5" t="inlineStr">
+        <is>
+          <t>Keep en-route product visible and the schedule honest about arrivals.</t>
+        </is>
+      </c>
+      <c r="W22" s="5" t="inlineStr">
+        <is>
+          <t>SRC-LNL-T2S-001 | SRC-EI-HM32-001</t>
+        </is>
+      </c>
       <c r="X22" s="5" t="n"/>
-      <c r="Y22" s="5" t="n"/>
-      <c r="Z22" s="5" t="n"/>
-      <c r="AA22" s="5" t="n"/>
-      <c r="AB22" s="5" t="n"/>
-      <c r="AC22" s="5" t="n"/>
+      <c r="Y22" s="5" t="inlineStr">
+        <is>
+          <t>load records | carrier status and arrival estimates | movement schedule</t>
+        </is>
+      </c>
+      <c r="Z22" s="5" t="inlineStr">
+        <is>
+          <t>current in-transit positions and movement status</t>
+        </is>
+      </c>
+      <c r="AA22" s="5" t="inlineStr">
+        <is>
+          <t>follows: Loading Shipment | enables: Manage Inventory | precedes: Discharge &amp; Reconcile Load</t>
+        </is>
+      </c>
+      <c r="AB22" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC22" s="5" t="inlineStr">
+        <is>
+          <t>continuous</t>
+        </is>
+      </c>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -3330,18 +3775,80 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U23" s="5" t="n"/>
-      <c r="V23" s="5" t="n"/>
-      <c r="W23" s="5" t="n"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Administer the discharge of arriving shipments — confirming received quantities and quality documentation, reconciling discharged against loaded volumes to surface in-transit gains and losses per movement, and closing the movement in scheduling and inventory records.</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Covers receipt-side load administration per EI HM 32 receipt practice: confirming outturn quantities and documentation, comparing loaded against discharged volumes per movement, resolving or escalating discrepancies, and closing the movement. The physical discharge operation is owned by the terminal operator (Midstream or third party). Per-movement outturn reconciliation feeds, but does not replace, periodic book-to-physical reconciliation, owned by Perform Inventory Reconciliation (CM-1-1-3-7-5); claims against carriers follow the relevant commercial agreements.</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Confirm outturn quantities and documentation | reconcile discharged against loaded volumes per movement | resolve or escalate per-load discrepancies | close movements in scheduling and inventory records</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>Physical discharge operation (terminal operator: Midstream or third party) | periodic book-to-physical reconciliation (CM-1-1-3-7-5) | carrier claims settlement (commercial agreements)</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>Discharge Administration | Outturn Reconciliation</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Batch 05 (2026-09-19). Boundary to CM-1-1-3-7-5: per-movement outturn reconciliation here; periodic book-to-physical reconciliation there. Receipt measurement and loss-surfacing practice per EI HM 32. APQC 12940 'Reconcile inventories' is a WEAK review-link.</t>
+        </is>
+      </c>
+      <c r="U23" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V23" s="5" t="inlineStr">
+        <is>
+          <t>Close each movement with received quantities confirmed and losses surfaced.</t>
+        </is>
+      </c>
+      <c r="W23" s="5" t="inlineStr">
+        <is>
+          <t>SRC-EI-HM32-001 | SRC-API-MPMS-001</t>
+        </is>
+      </c>
       <c r="X23" s="5" t="n"/>
-      <c r="Y23" s="5" t="n"/>
-      <c r="Z23" s="5" t="n"/>
-      <c r="AA23" s="5" t="n"/>
-      <c r="AB23" s="5" t="n"/>
-      <c r="AC23" s="5" t="n"/>
+      <c r="Y23" s="5" t="inlineStr">
+        <is>
+          <t>outturn measurement tickets | load records | movement documentation</t>
+        </is>
+      </c>
+      <c r="Z23" s="5" t="inlineStr">
+        <is>
+          <t>closed, reconciled movements with per-load gain and loss</t>
+        </is>
+      </c>
+      <c r="AA23" s="5" t="inlineStr">
+        <is>
+          <t>follows: Track Movements and Inventory Management | enables: Perform Inventory Reconciliation</t>
+        </is>
+      </c>
+      <c r="AB23" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC23" s="5" t="inlineStr">
+        <is>
+          <t>event-driven</t>
+        </is>
+      </c>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -5202,18 +5709,80 @@
           <t>no meaningful APQC candidate</t>
         </is>
       </c>
-      <c r="U37" s="5" t="n"/>
-      <c r="V37" s="5" t="n"/>
-      <c r="W37" s="5" t="n"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Manage the delivery of products from terminals and depots to retail sites, commercial customers, and other end-delivery points — generating delivery orders for managed sites, scheduling vehicles and routes, and monitoring delivery performance — so site and customer demand is met reliably at efficient delivery cost.</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Covers the secondary distribution leg: order generation for managed sites, daily vehicle and route scheduling within fleet, site, and product constraints, maintenance of the scheduling basis, and delivery-performance monitoring. Excludes primary bulk movements, owned by Physical Distribution Scheduling (CM-1-1-3-6); excludes customer-initiated order capture and fulfillment, owned by Order Management (CM-1-3-7); excludes physical haulage execution, performed by the designated distribution operator, carrier, or logistics provider — outside the scope of this scheduling process; excludes plan-variance analysis, owned by Distribution Backcasting (CM-1-1-6) under its locked rule.</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Generate delivery orders for managed sites | schedule vehicles, routes, and delivery windows | maintain the scheduling basis | monitor delivery performance</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>Primary distribution movements (CM-1-1-3-6) | customer-initiated order capture (Order Management, CM-1-3-7) | physical haulage execution (designated distribution operator, carrier, or logistics provider) | plan-variance backcasting (Distribution Backcasting, CM-1-1-6)</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>Secondary Distribution | Terminal-to-Site Delivery Management</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Batch 05 (2026-09-19). 'Secondary distribution' per downstream practice: terminal and depot to station and customer deliveries, short-notice demand at many points — Mota et al. 2017 (the Galp case) is the direct evidence. Executor wording per Hamid's batch 05 edit: physical haulage execution is performed by the designated distribution operator, carrier, or logistics provider — the taxonomy stays operating-model neutral and does not hard-code Midstream as the secondary-delivery executor. The locked Distribution Backcasting rule is honored: CM-1-1-6 explains variance against the approved plan; this L4's monitoring child watches execution against the issued schedule. Accountable ownership of delivery-performance improvement when fleet execution is outsourced is a follow-up noted in the batch 05 PR.</t>
+        </is>
+      </c>
+      <c r="U37" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V37" s="5" t="inlineStr">
+        <is>
+          <t>Run the terminal-to-site delivery operation to demand, within cost and constraints.</t>
+        </is>
+      </c>
+      <c r="W37" s="5" t="inlineStr">
+        <is>
+          <t>SRC-LNL-T2S-001 | SRC-EI-HM32-001</t>
+        </is>
+      </c>
       <c r="X37" s="5" t="n"/>
-      <c r="Y37" s="5" t="n"/>
-      <c r="Z37" s="5" t="n"/>
-      <c r="AA37" s="5" t="n"/>
-      <c r="AB37" s="5" t="n"/>
-      <c r="AC37" s="5" t="n"/>
+      <c r="Y37" s="5" t="inlineStr">
+        <is>
+          <t>site demand and stock signals | fleet and route constraints | terminal availability</t>
+        </is>
+      </c>
+      <c r="Z37" s="5" t="inlineStr">
+        <is>
+          <t>scheduled, monitored secondary deliveries</t>
+        </is>
+      </c>
+      <c r="AA37" s="5" t="inlineStr">
+        <is>
+          <t>informed-by: Develop Finished Product Inventory Policy | enables: Distribution Backcasting</t>
+        </is>
+      </c>
+      <c r="AB37" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC37" s="5" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
       <c r="AD37" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -5281,18 +5850,80 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U38" s="5" t="n"/>
-      <c r="V38" s="5" t="n"/>
-      <c r="W38" s="5" t="n"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Create the delivery orders that feed secondary distribution scheduling — deriving replenishment needs for managed retail sites and customer tanks from stock readings, consumption forecasts, and agreed service levels, and converting them into deliverable orders with quantities and windows.</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Covers forecast-driven order generation for managed sites: monitoring site tank levels and consumption, computing run-out risk, and generating and sizing orders within site and vehicle constraints. Excludes customer-initiated orders, owned by Order Management (CM-1-3-7); excludes network terminal replenishment, owned by Manage Inventory Replenishment (CM-1-1-3-7-9); excludes scheduling the deliveries, owned by Schedule Secondary Distribution (CM-1-1-3-8-2).</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Monitor site tank levels and consumption | compute run-out risk and replenishment need | generate and size delivery orders within constraints | set required delivery windows</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>Customer-initiated order capture (Order Management, CM-1-3-7) | terminal and depot replenishment (CM-1-1-3-7-9) | delivery scheduling (CM-1-1-3-8-2)</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>Automatic Order Generation | Managed Replenishment Orders</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Batch 05 (2026-09-19). Three order/replenishment boundaries hold together: customer-initiated orders (CM-1-3-7), network stock-point replenishment (CM-1-1-3-7-9, batch 04), and managed-site delivery orders (here). APQC 10136 'Generate sales forecast' is an unrelated candidate.</t>
+        </is>
+      </c>
+      <c r="U38" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V38" s="5" t="inlineStr">
+        <is>
+          <t>Turn site stock and consumption signals into deliverable orders before run-outs.</t>
+        </is>
+      </c>
+      <c r="W38" s="5" t="inlineStr">
+        <is>
+          <t>SRC-LNL-T2S-001</t>
+        </is>
+      </c>
       <c r="X38" s="5" t="n"/>
-      <c r="Y38" s="5" t="n"/>
-      <c r="Z38" s="5" t="n"/>
-      <c r="AA38" s="5" t="n"/>
-      <c r="AB38" s="5" t="n"/>
-      <c r="AC38" s="5" t="n"/>
+      <c r="Y38" s="5" t="inlineStr">
+        <is>
+          <t>site tank levels and consumption forecasts | service-level agreements | vehicle and site constraints</t>
+        </is>
+      </c>
+      <c r="Z38" s="5" t="inlineStr">
+        <is>
+          <t>delivery orders with quantities and windows</t>
+        </is>
+      </c>
+      <c r="AA38" s="5" t="inlineStr">
+        <is>
+          <t>precedes: Schedule Secondary Distribution | informed-by: Demand Forecasting</t>
+        </is>
+      </c>
+      <c r="AB38" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC38" s="5" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
       <c r="AD38" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -5360,18 +5991,80 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U39" s="5" t="n"/>
-      <c r="V39" s="5" t="n"/>
-      <c r="W39" s="5" t="n"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Build and maintain the daily secondary delivery schedule — assigning orders to vehicles, compartments, routes, and time windows within fleet, driver, site-access, and product-segregation constraints — to meet required delivery windows at efficient fleet utilization and cost.</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Covers the daily routing and loading schedule: assigning orders to vehicles and compartments, sequencing routes, respecting driver, access, and product-compatibility constraints, and rescheduling on disruption. Excludes creating the orders, owned by Generate Orders (CM-1-1-3-8-1); excludes physical haulage execution, performed by the designated distribution operator, carrier, or logistics provider — outside the scope of this scheduling process; excludes primary movements (CM-1-1-3-6).</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Assign orders to vehicles and compartments | sequence routes and delivery windows | respect fleet, driver, access, and segregation constraints | reschedule on disruption</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>Order generation (CM-1-1-3-8-1) | physical haulage execution (designated distribution operator, carrier, or logistics provider) | primary distribution scheduling (CM-1-1-3-6)</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>Secondary Delivery Scheduling | Route and Load Scheduling</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Batch 05 (2026-09-19). Mota et al. 2017 documents exactly this process at Galp (tank-to-station scheduling under normal and disrupted operations). Executor wording per Hamid's batch 05 edit: operating-model neutral. APQC 10303 'Schedule production' is a lexical near-match to a different domain; comparative evidence only.</t>
+        </is>
+      </c>
+      <c r="U39" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V39" s="5" t="inlineStr">
+        <is>
+          <t>Get every order onto the right vehicle, route, and window at least cost.</t>
+        </is>
+      </c>
+      <c r="W39" s="5" t="inlineStr">
+        <is>
+          <t>SRC-LNL-T2S-001</t>
+        </is>
+      </c>
       <c r="X39" s="5" t="n"/>
-      <c r="Y39" s="5" t="n"/>
-      <c r="Z39" s="5" t="n"/>
-      <c r="AA39" s="5" t="n"/>
-      <c r="AB39" s="5" t="n"/>
-      <c r="AC39" s="5" t="n"/>
+      <c r="Y39" s="5" t="inlineStr">
+        <is>
+          <t>delivery orders | fleet, driver, and compartment constraints | site access windows</t>
+        </is>
+      </c>
+      <c r="Z39" s="5" t="inlineStr">
+        <is>
+          <t>daily delivery schedule with vehicle and route assignments</t>
+        </is>
+      </c>
+      <c r="AA39" s="5" t="inlineStr">
+        <is>
+          <t>follows: Generate Orders | precedes: Monitor Secondary Distribution Performance</t>
+        </is>
+      </c>
+      <c r="AB39" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC39" s="5" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
       <c r="AD39" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -5439,18 +6132,80 @@
           <t>no meaningful APQC candidate</t>
         </is>
       </c>
-      <c r="U40" s="5" t="n"/>
-      <c r="V40" s="5" t="n"/>
-      <c r="W40" s="5" t="n"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Maintain the reference data, constraints, and operating parameters used for secondary-distribution scheduling — including sites, tanks, vehicles, compartments, drivers, routes, access windows, product-compatibility rules, and scheduling parameters — so generated orders and delivery schedules reflect the current operating network.</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Covers stewardship and controlled maintenance of the secondary-distribution scheduling basis: onboarding, changing, validating, and retiring sites, tanks, vehicles, compartments, drivers, routes, constraints, and scheduling parameters; validating the impact of material changes; and confirming that generated schedules remain operationally feasible. Excludes selection, implementation, configuration, enhancement, integration, technical support, infrastructure operation, and cybersecurity of the scheduling application or platform, which belong to Process Excellence &amp; IT. Excludes enterprise master-data policy, canonical-data-model design, and platform integration architecture, governed through the applicable enterprise data-governance and Process Excellence &amp; IT capabilities. Excludes commercial customer and site onboarding, and the scheduling decisions made in Schedule Secondary Distribution (CM-1-1-3-8-2).</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Onboard, change, validate, and retire sites, tanks, vehicles, compartments, and drivers in the scheduling basis | maintain constraints, compatibility rules, and scheduling parameters | validate the impact of material changes | confirm schedules remain operationally feasible after changes</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>Scheduling application implementation, support, and platform operation (Process Excellence &amp; IT) | enterprise master-data policy and canonical-data-model design (enterprise data governance) | delivery scheduling decisions (CM-1-1-3-8-2) | commercial customer and site onboarding (Marketing)</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>Maintain Secondary Distribution Scheduling Basis</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Batch 05 (2026-09-19). Q2 decision (Hamid, Option A): a recurring process — maintenance of the secondary-distribution scheduling basis — not system implementation, consistent with the master-data precedent (CM-1-1-2-12, CM-1-1-1-1-1, CM-1-1-7-2-1). 'Tanks' added at Hamid's direction as essential to managed-site ordering and run-out prevention; definition opens with 'Maintain' to avoid the one-time-implementation reading. Preferred normalized label 'Maintain Secondary Distribution Scheduling Basis' queued for the naming pass; current label retained for traceability. The parked master-data consolidation question (CM-1-1-2-12, 2026-09-18) applies to this node as well. APQC 10198 is an unrelated sales-order candidate.</t>
+        </is>
+      </c>
+      <c r="U40" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V40" s="5" t="inlineStr">
+        <is>
+          <t>Keep the scheduling basis true to the real fleet, sites, tanks, and constraints.</t>
+        </is>
+      </c>
+      <c r="W40" s="5" t="inlineStr">
+        <is>
+          <t>SRC-ASCM-CSCP-001 | SRC-LNL-T2S-001</t>
+        </is>
+      </c>
       <c r="X40" s="5" t="n"/>
-      <c r="Y40" s="5" t="n"/>
-      <c r="Z40" s="5" t="n"/>
-      <c r="AA40" s="5" t="n"/>
-      <c r="AB40" s="5" t="n"/>
-      <c r="AC40" s="5" t="n"/>
+      <c r="Y40" s="5" t="inlineStr">
+        <is>
+          <t>site, tank, and vehicle onboarding and change requests | constraint and parameter definitions | schedule feedback after changes</t>
+        </is>
+      </c>
+      <c r="Z40" s="5" t="inlineStr">
+        <is>
+          <t>validated scheduling basis and parameters</t>
+        </is>
+      </c>
+      <c r="AA40" s="5" t="inlineStr">
+        <is>
+          <t>enables: Schedule Secondary Distribution | enables: Generate Orders</t>
+        </is>
+      </c>
+      <c r="AB40" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC40" s="5" t="inlineStr">
+        <is>
+          <t>periodic</t>
+        </is>
+      </c>
       <c r="AD40" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -5518,18 +6273,80 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U41" s="5" t="n"/>
-      <c r="V41" s="5" t="n"/>
-      <c r="W41" s="5" t="n"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Measure and report secondary distribution execution against the issued delivery schedule — delivery reliability, fleet utilization, and cost efficiency at agreed levels — investigating recurring shortfalls and feeding improvements back into order generation, scheduling, and the scheduling basis.</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Covers operational execution monitoring: schedule adherence and delivery completion, run-out and retained-delivery incidents, utilization and cost signals, recurring-issue analysis, and improvement recommendations. Actuals are compared with the schedule as issued, keeping the contemporaneous-baseline discipline. Excludes plan-versus-actual distribution variance analysis, owned by Distribution Backcasting (CM-1-1-6) under its locked rule; excludes defining enterprise KPIs, which belongs to the KPI workstream; excludes haulier contract management.</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Track schedule adherence and delivery completion | monitor run-out and retained-delivery incidents | analyze utilization and delivery cost signals | recommend improvements to orders, scheduling, and the basis</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>Plan-versus-actual backcasting (Distribution Backcasting, CM-1-1-6) | enterprise KPI definition (KPI workstream) | haulier contract management (commercial owner)</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>Secondary Distribution Performance Monitoring | Delivery Performance Monitoring</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Batch 05 (2026-09-19). Bounded against the locked Distribution Backcasting rule: CM-1-1-6 explains variance against the approved distribution plan; this node monitors execution against the issued delivery schedule. Horizon set to 'continuous' per Hamid's batch 05 edit — continuous operational monitoring with periodic reporting and review; the controlled vocabulary takes a single value, so the reporting cadence is recorded here. Specific metrics deliberately not named (KPI workstream). APQC 16574 is a marketing-channel candidate; comparative evidence only.</t>
+        </is>
+      </c>
+      <c r="U41" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V41" s="5" t="inlineStr">
+        <is>
+          <t>Establish whether secondary delivery execution is reliable and efficient, and why not when it is not.</t>
+        </is>
+      </c>
+      <c r="W41" s="5" t="inlineStr">
+        <is>
+          <t>SRC-LNL-T2S-001 | SRC-ASCM-CSCP-001</t>
+        </is>
+      </c>
       <c r="X41" s="5" t="n"/>
-      <c r="Y41" s="5" t="n"/>
-      <c r="Z41" s="5" t="n"/>
-      <c r="AA41" s="5" t="n"/>
-      <c r="AB41" s="5" t="n"/>
-      <c r="AC41" s="5" t="n"/>
+      <c r="Y41" s="5" t="inlineStr">
+        <is>
+          <t>issued delivery schedules | delivery completion records | fleet utilization and cost data</t>
+        </is>
+      </c>
+      <c r="Z41" s="5" t="inlineStr">
+        <is>
+          <t>delivery performance report with improvement recommendations</t>
+        </is>
+      </c>
+      <c r="AA41" s="5" t="inlineStr">
+        <is>
+          <t>follows: Schedule Secondary Distribution | enables: Distribution Backcasting</t>
+        </is>
+      </c>
+      <c r="AB41" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC41" s="5" t="inlineStr">
+        <is>
+          <t>continuous</t>
+        </is>
+      </c>
       <c r="AD41" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -43264,7 +44081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -44249,6 +45066,53 @@
         </is>
       </c>
       <c r="I26" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>SRC-DOE-RPPL-001</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>U.S. Department of Energy</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>How it Works: Refined Petroleum Product Pipelines (backgrounder)</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2023; accessed 2026-09-19</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov/sites/default/files/2023-08/Pipeline%20Backgrounder_FINAL_508.pdf</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Government authority</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Nomination, cycle, batching, and FERC common-carrier practice; contextual evidence only, not text to copy and not asserted as this organization's commercial model</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Shipper nominations, multi-day scheduling cycles, segregated versus fungible batches</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
         <is>
           <t>active</t>
         </is>

--- a/business_architecture/ontology/build/output/step3c-definition-authoring-workbook.xlsx
+++ b/business_architecture/ontology/build/output/step3c-definition-authoring-workbook.xlsx
@@ -8290,18 +8290,80 @@
           <t>no meaningful APQC candidate</t>
         </is>
       </c>
-      <c r="U58" s="5" t="n"/>
-      <c r="V58" s="5" t="n"/>
-      <c r="W58" s="5" t="n"/>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>Translate the current production schedule into each day's refinery execution basis — updating the day's scheduling instructions and commitments, confirming the schedule-level resources the day depends on, and closing the daily production accounting balance — so the refinery works each day from a current, feasible, accounted-for scheduling basis.</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>Covers the daily schedule-to-execution cycle: issuing and updating the day's schedule-level instructions and commitments, assigning the schedule-level resources the day's plan assumes, and closing the daily production balance with actualized yields. Under the approved planning-scheduling-operations hierarchy, Refining owns unit-operation scheduling, tank and transfer line-ups, blend and process execution, and safe operational departures from the schedule; this process owns the daily schedule basis and its accounting. Excludes building the dated schedule itself, owned by Production Scheduling (CM-1-1-7-2); excludes the monthly plan (Refinery Planning, CM-1-1-4).</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Issue and update daily schedule-level instructions and commitments | assign schedule-level resources for the day | close the daily production accounting balance | confirm daily feasibility of the issued basis</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>Unit-operation scheduling, line-ups, and execution (Refining) | dated schedule construction (CM-1-1-7-2) | monthly plan targets (CM-1-1-4)</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>Daily Refinery Scheduling</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Batch 06 (2026-09-19). Q1 decision (Hamid, 2026-09-19): the refinery planning-scheduling-operations hierarchy is approved. CM-1-1-7 owns the refinery production-scheduling layer: translating approved refinery plans into dated, feasible campaign, production, movement, and resource schedules; managing schedule exceptions and cross-functional interfaces; and maintaining schedule-level performance visibility. Refining owns detailed unit-operation scheduling and all operational execution, including process-control decisions, line-ups, transfers, blend execution, utility operation, and immediate safety/reliability departures from the schedule. This L4 is the daily rhythm of that scheduling layer. APQC: no meaningful candidate.</t>
+        </is>
+      </c>
+      <c r="U58" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V58" s="5" t="inlineStr">
+        <is>
+          <t>Give the refinery a current, feasible, accounted-for daily scheduling basis.</t>
+        </is>
+      </c>
+      <c r="W58" s="5" t="inlineStr">
+        <is>
+          <t>SRC-BJCE-REFPS-001 | SRC-SNF-REFPS-001</t>
+        </is>
+      </c>
       <c r="X58" s="5" t="n"/>
-      <c r="Y58" s="5" t="n"/>
-      <c r="Z58" s="5" t="n"/>
-      <c r="AA58" s="5" t="n"/>
-      <c r="AB58" s="5" t="n"/>
-      <c r="AC58" s="5" t="n"/>
+      <c r="Y58" s="5" t="inlineStr">
+        <is>
+          <t>current production schedule | execution feedback and measured actuals | resource availability</t>
+        </is>
+      </c>
+      <c r="Z58" s="5" t="inlineStr">
+        <is>
+          <t>issued daily scheduling basis with closed production balance</t>
+        </is>
+      </c>
+      <c r="AA58" s="5" t="inlineStr">
+        <is>
+          <t>follows: Production Scheduling | enables: Regional Backcasting</t>
+        </is>
+      </c>
+      <c r="AB58" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC58" s="5" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
       <c r="AD58" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -8369,18 +8431,80 @@
           <t>no meaningful APQC candidate</t>
         </is>
       </c>
-      <c r="U59" s="5" t="n"/>
-      <c r="V59" s="5" t="n"/>
-      <c r="W59" s="5" t="n"/>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>Maintain and issue the approved daily production-schedule instructions — dated campaign commitments, production and movement requirements, product priorities, planning assumptions, and approved schedule changes — so the refinery's operating teams receive a current, traceable scheduling basis.</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>Covers consolidation, versioning, communication, and controlled revision of the approved scheduling instruction set. It may communicate schedule-level requirements and constraints to refinery operations, but does not prescribe unit feed rates, operating modes, operating procedures, tank or transfer line-ups, blend execution, process-control settings, or other detailed execution methods — those remain within Refining. Excludes changing the monthly plan, owned by Refinery Planning (CM-1-1-4); material schedule deviations flow through Manage Production Schedule Exceptions (CM-1-1-7-2-4).</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Consolidate approved schedule decisions into the instruction set | version and communicate instruction updates | control revisions on approved schedule changes | confirm instructions reflect the current approved schedule</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>Unit feed rates, operating modes, and process-control settings (Refining) | operating procedures, line-ups, and blend execution (Refining) | monthly plan changes (CM-1-1-4) | schedule exception decisions (CM-1-1-7-2-4)</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>Issue Production-Schedule Instructions</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Batch 06 (2026-09-19). Rewritten at Hamid's direction before approval: the original draft named feed rates, operating modes, unit targets, and blend targets, which collide with the locked Refining boundary — instructions here are schedule-level commitments and requirements, never unit-level operating parameters. 'Execution instructions' in the label is read as the scheduling instruction set that provides the approved basis for refinery execution. APQC: no meaningful candidate.</t>
+        </is>
+      </c>
+      <c r="U59" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V59" s="5" t="inlineStr">
+        <is>
+          <t>Keep the refinery's schedule-level instruction set current, traceable, and aligned with the approved schedule.</t>
+        </is>
+      </c>
+      <c r="W59" s="5" t="inlineStr">
+        <is>
+          <t>SRC-BJCE-REFPS-001</t>
+        </is>
+      </c>
       <c r="X59" s="5" t="n"/>
-      <c r="Y59" s="5" t="n"/>
-      <c r="Z59" s="5" t="n"/>
-      <c r="AA59" s="5" t="n"/>
-      <c r="AB59" s="5" t="n"/>
-      <c r="AC59" s="5" t="n"/>
+      <c r="Y59" s="5" t="inlineStr">
+        <is>
+          <t>current schedule and approved changes | schedule exception outcomes</t>
+        </is>
+      </c>
+      <c r="Z59" s="5" t="inlineStr">
+        <is>
+          <t>issued, versioned schedule-level instruction set</t>
+        </is>
+      </c>
+      <c r="AA59" s="5" t="inlineStr">
+        <is>
+          <t>enables: Daily Execution Planning | informed-by: Manage Production Schedule Exceptions</t>
+        </is>
+      </c>
+      <c r="AB59" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC59" s="5" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
       <c r="AD59" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -8448,18 +8572,80 @@
           <t>strong APQC candidate but no validator agreed</t>
         </is>
       </c>
-      <c r="U60" s="5" t="n"/>
-      <c r="V60" s="5" t="n"/>
-      <c r="W60" s="5" t="n"/>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>Assign and confirm the schedule-level shared resources each day's plan depends on — tankage assumptions, movement and rack windows, berth and loading slots, and other capacity the schedule reserves — so the daily scheduling basis is physically feasible before it is issued.</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>Covers schedule-level resource assignment: checking availability, reserving and assigning capacity against the day's plan, resolving conflicts among competing schedule needs, and confirming feasibility. Resource assignment represents capacity reservations and schedule assumptions; it does not direct tank line-ups, valve states, transfers, or other operating configurations. Excludes physical line-ups, transfers, and operation of the resources, owned by Refining and Midstream per the locked rules; excludes maintenance resource and crew planning, owned by Refining's engineering and maintenance functions — outage windows enter the schedule through Manage The Interface to Planning, Operations, Engineering &amp; Maintenance (CM-1-1-7-2-6).</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Check and reserve schedule-level capacity | assign resources to the day's plan | resolve competing schedule resource conflicts | confirm physical feasibility of the daily basis</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>Physical line-ups, valve states, and resource operation (Refining, Midstream) | maintenance and crew planning (Refining) | outage window intake (CM-1-1-7-2-6)</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>Schedule-Level Resource Assignment</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Batch 06 (2026-09-19). 'Resources' read as schedule-level shared capacity — tankage, windows, slots — not personnel rostering or maintenance crews; the capacity-reservation sentence was added at Hamid's direction to protect the boundary where capacity allocation could be confused with refinery operations. APQC 20882 is an IT-services candidate; false lexical match, comparative evidence only.</t>
+        </is>
+      </c>
+      <c r="U60" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V60" s="5" t="inlineStr">
+        <is>
+          <t>Make sure the day's plan has the capacity it assumes.</t>
+        </is>
+      </c>
+      <c r="W60" s="5" t="inlineStr">
+        <is>
+          <t>SRC-SNF-REFPS-001</t>
+        </is>
+      </c>
       <c r="X60" s="5" t="n"/>
-      <c r="Y60" s="5" t="n"/>
-      <c r="Z60" s="5" t="n"/>
-      <c r="AA60" s="5" t="n"/>
-      <c r="AB60" s="5" t="n"/>
-      <c r="AC60" s="5" t="n"/>
+      <c r="Y60" s="5" t="inlineStr">
+        <is>
+          <t>daily plan | resource availability and outage windows | competing schedule demands</t>
+        </is>
+      </c>
+      <c r="Z60" s="5" t="inlineStr">
+        <is>
+          <t>confirmed resource assignments for the daily basis</t>
+        </is>
+      </c>
+      <c r="AA60" s="5" t="inlineStr">
+        <is>
+          <t>enables: Daily Execution Planning | informed-by: Manage The Interface to Planning, Operations, Engineering &amp; Maintenance</t>
+        </is>
+      </c>
+      <c r="AB60" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC60" s="5" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
       <c r="AD60" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -8527,18 +8713,80 @@
           <t>strong APQC candidate but no validator agreed</t>
         </is>
       </c>
-      <c r="U61" s="5" t="n"/>
-      <c r="V61" s="5" t="n"/>
-      <c r="W61" s="5" t="n"/>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>Close the refinery's daily production balance — reconciling measured feed receipts, unit charges and yields, blending, shipments, fuel and loss, and inventory changes into an accounted material balance — and actualize production against the schedule so planning, scheduling, and backcasting run on verified actuals.</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>Covers daily production and yield accounting per refinery hydrocarbon-management practice (EI HM 31): assembling measured quantities, balancing the site by unit and material, attributing imbalance and apparent loss for investigation, and publishing the day's actuals. Excludes owning the physical measurement basis, which sits with Measure Inventory (CM-1-1-3-7-4) with readings taken by asset operators; excludes periodic network book-to-physical stock reconciliation, owned by Perform Inventory Reconciliation (CM-1-1-3-7-5), which this balance feeds; excludes financial and cost accounting, owned by Finance under the locked rule.</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Assemble measured receipts, charges, yields, shipments, and inventory changes | balance the site by unit and material daily | attribute imbalance and apparent loss for investigation | publish actualized production against schedule</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>Measurement basis and standards (CM-1-1-3-7-4) | network book-to-physical reconciliation (CM-1-1-3-7-5) | financial and cost accounting (Finance)</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>Production and Yield Accounting | Refinery Material Balance</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Batch 06 (2026-09-19). Production accounting is the refinery's daily material balance and yield actualization — distinct from network stock reconciliation (batch 04) and from financial inventory accounting. APQC 10774 'Perform inventory accounting' scored STRONG but is financial asset accounting; treated as a false match, comparative evidence only.</t>
+        </is>
+      </c>
+      <c r="U61" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V61" s="5" t="inlineStr">
+        <is>
+          <t>Deliver a verified daily account of what the refinery actually received, made, shipped, and lost.</t>
+        </is>
+      </c>
+      <c r="W61" s="5" t="inlineStr">
+        <is>
+          <t>SRC-EI-HM31-001 | SRC-API-MPMS-001</t>
+        </is>
+      </c>
       <c r="X61" s="5" t="n"/>
-      <c r="Y61" s="5" t="n"/>
-      <c r="Z61" s="5" t="n"/>
-      <c r="AA61" s="5" t="n"/>
-      <c r="AB61" s="5" t="n"/>
-      <c r="AC61" s="5" t="n"/>
+      <c r="Y61" s="5" t="inlineStr">
+        <is>
+          <t>measured quantities and movement tickets | unit charge and yield data | shipment and inventory records</t>
+        </is>
+      </c>
+      <c r="Z61" s="5" t="inlineStr">
+        <is>
+          <t>closed daily production balance with actualized yields</t>
+        </is>
+      </c>
+      <c r="AA61" s="5" t="inlineStr">
+        <is>
+          <t>uses-input: Measure Inventory | enables: Perform Inventory Reconciliation | enables: Regional Backcasting</t>
+        </is>
+      </c>
+      <c r="AB61" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC61" s="5" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
       <c r="AD61" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -8606,18 +8854,80 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U62" s="5" t="n"/>
-      <c r="V62" s="5" t="n"/>
-      <c r="W62" s="5" t="n"/>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>Develop and maintain the refinery production schedule that implements the approved monthly plan — sequencing campaigns, schedule-level unit commitments, blends, and movements over the scheduling horizon, managing schedule exceptions, and coordinating the interfaces the schedule depends on — so the plan becomes a current schedule that provides the approved basis for refinery execution.</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>Covers the refinery scheduling layer between planning and operations: maintaining scheduling master data, reviewing the production wheel and run lengths, creating the dated sequencing plan, managing exceptions, measuring scheduling performance, and managing interfaces to planning, operations, and engineering and maintenance. Under the approved planning-scheduling-operations hierarchy, Refining owns detailed unit-operation scheduling and all operational execution; this L4 owns the production schedule that provides the approved basis for that execution. Excludes the monthly plan itself, owned by Refinery Planning (CM-1-1-4); excludes the daily scheduling basis, owned by Daily Execution Planning (CM-1-1-7-1).</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Maintain the scheduling basis and master data | maintain the production wheel and run lengths | create and refresh the dated sequencing plan | manage schedule exceptions and interfaces | measure scheduling performance</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>Monthly production plan (CM-1-1-4) | unit-operation scheduling and execution (Refining) | daily instruction issuance (CM-1-1-7-1)</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>Refinery Production Scheduling</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Batch 06 (2026-09-19). Q1 decision (Hamid, 2026-09-19): the refinery planning-scheduling-operations hierarchy is approved. CM-1-1-7 owns the refinery production-scheduling layer: translating approved refinery plans into dated, feasible campaign, production, movement, and resource schedules; managing schedule exceptions and cross-functional interfaces; and maintaining schedule-level performance visibility. Refining owns detailed unit-operation scheduling and all operational execution, including process-control decisions, line-ups, transfers, blend execution, utility operation, and immediate safety/reliability departures from the schedule. Supported by the planning/scheduling/operations separation documented in SNF R29/08 and Moro (BJCE); the locked rule's 'detailed unit-operation scheduling' is the operations layer, not this one. APQC 10303 is a WEAK generic candidate; comparative evidence only.</t>
+        </is>
+      </c>
+      <c r="U62" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V62" s="5" t="inlineStr">
+        <is>
+          <t>Turn the approved monthly plan into a current schedule that provides the approved basis for refinery execution.</t>
+        </is>
+      </c>
+      <c r="W62" s="5" t="inlineStr">
+        <is>
+          <t>SRC-BJCE-REFPS-001 | SRC-SNF-REFPS-001 | SRC-CMU-REFPLAN-001</t>
+        </is>
+      </c>
       <c r="X62" s="5" t="n"/>
-      <c r="Y62" s="5" t="n"/>
-      <c r="Z62" s="5" t="n"/>
-      <c r="AA62" s="5" t="n"/>
-      <c r="AB62" s="5" t="n"/>
-      <c r="AC62" s="5" t="n"/>
+      <c r="Y62" s="5" t="inlineStr">
+        <is>
+          <t>approved monthly plan | production wheel and constraints | outage and turnaround windows | execution feedback</t>
+        </is>
+      </c>
+      <c r="Z62" s="5" t="inlineStr">
+        <is>
+          <t>current production schedule providing the approved basis for execution</t>
+        </is>
+      </c>
+      <c r="AA62" s="5" t="inlineStr">
+        <is>
+          <t>follows: Refinery Planning | precedes: Daily Execution Planning</t>
+        </is>
+      </c>
+      <c r="AB62" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC62" s="5" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AD62" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -8685,18 +8995,80 @@
           <t>strong APQC candidate but no validator agreed</t>
         </is>
       </c>
-      <c r="U63" s="5" t="n"/>
-      <c r="V63" s="5" t="n"/>
-      <c r="W63" s="5" t="n"/>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>Create, maintain, and retire the reference and parameter data the production scheduling model depends on — unit capacities and constraints, product and recipe definitions, transition and changeover rules, tankage parameters, and scheduling calendars — so scheduling results remain accurate and reproducible.</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>Covers stewardship of production-scheduling-specific reference and parameter data over its lifecycle: requesting and validating changes, applying effective dates, and confirming scheduling results remain consistent after a change. Excludes supply-planning master data, owned by Maintain Supply Planning Master Data (CM-1-1-2-12); excludes demand-forecast data preparation (CM-1-1-1-1-1); excludes customer, price, product, tax, and location master data (Manage Master Data, CM-1-3-7-1); excludes enterprise master-data policy and governance, which sit with the Data Governance workstream.</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Maintain unit capacity, constraint, and recipe data | maintain transition and changeover rules | apply and validate effective-dated changes | confirm scheduling consistency after changes</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>Supply-planning master data (CM-1-1-2-12) | demand-forecast data preparation (CM-1-1-1-1-1) | commercial master data (CM-1-3-7-1) | enterprise master-data policy (Data Governance workstream)</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>Scheduling Master Data Maintenance</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Batch 06 (2026-09-19). One of the four parallel master-data nodes named in CM-1-1-2-12's approved note (2026-09-18); the parked consolidation question applies here as well and is deliberately not resolved. Whether refinery scheduling runs on a dedicated scheduling system whose master-data ownership needs linking to a later system-integration workstream is a follow-up noted in the batch 06 PR. APQC 10252 scored STRONG but is distribution master data; comparative evidence only.</t>
+        </is>
+      </c>
+      <c r="U63" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V63" s="5" t="inlineStr">
+        <is>
+          <t>Keep the scheduling model's reference data true to the real refinery.</t>
+        </is>
+      </c>
+      <c r="W63" s="5" t="inlineStr">
+        <is>
+          <t>SRC-ASCM-CSCP-001</t>
+        </is>
+      </c>
       <c r="X63" s="5" t="n"/>
-      <c r="Y63" s="5" t="n"/>
-      <c r="Z63" s="5" t="n"/>
-      <c r="AA63" s="5" t="n"/>
-      <c r="AB63" s="5" t="n"/>
-      <c r="AC63" s="5" t="n"/>
+      <c r="Y63" s="5" t="inlineStr">
+        <is>
+          <t>change requests from scheduling and operations | unit test-run and constraint updates | effective-dating rules</t>
+        </is>
+      </c>
+      <c r="Z63" s="5" t="inlineStr">
+        <is>
+          <t>validated scheduling reference and parameter data</t>
+        </is>
+      </c>
+      <c r="AA63" s="5" t="inlineStr">
+        <is>
+          <t>enables: Create Production Scheduling and Sequencing Plan | enables: Review Production Wheel and Run Length</t>
+        </is>
+      </c>
+      <c r="AB63" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC63" s="5" t="inlineStr">
+        <is>
+          <t>periodic</t>
+        </is>
+      </c>
       <c r="AD63" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -8759,18 +9131,80 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U64" s="5" t="n"/>
-      <c r="V64" s="5" t="n"/>
-      <c r="W64" s="5" t="n"/>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>Review and maintain the production wheel — the recurring sequence of product campaigns — and each campaign's run length, balancing transition losses and changeover costs against inventory, demand coverage, and unit constraints, so the schedule is built on an economically sound campaign structure.</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>Covers the periodic review of campaign sequence and duration: the transition structure (which product can follow which at what cost), wheel cycle time, run lengths per product against demand and storage, and wheel exceptions for demand shifts and outages. Excludes building the dated schedule itself, owned by Create Production Scheduling and Sequencing Plan (CM-1-1-7-2-3); excludes plan-period product mix decisions, owned by Refinery Planning (CM-1-1-4); excludes executing transitions, owned by Refining.</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Maintain the campaign transition structure and costs | set wheel cycle time and run lengths | review the wheel against demand, inventory, and constraints | approve wheel exceptions</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>Dated schedule construction (CM-1-1-7-2-3) | plan-period product mix (CM-1-1-4) | transition execution (Refining)</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>Product Wheel Review | Campaign Sequence and Run-Length Review</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Batch 06 (2026-09-19). 'Production wheel' is the standard campaign-scheduling structure where sequence-dependent changeovers matter — directly relevant to specialty and blended product lines. Whether the wheel structure applies across all units or only campaign-oriented lines is a follow-up noted in the batch 06 PR. APQC 12916 is a WEAK review-link; comparative evidence only.</t>
+        </is>
+      </c>
+      <c r="U64" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V64" s="5" t="inlineStr">
+        <is>
+          <t>Keep the campaign structure the schedule runs on economically sound.</t>
+        </is>
+      </c>
+      <c r="W64" s="5" t="inlineStr">
+        <is>
+          <t>SRC-ASCM-CSCP-001 | SRC-BJCE-REFPS-001</t>
+        </is>
+      </c>
       <c r="X64" s="5" t="n"/>
-      <c r="Y64" s="5" t="n"/>
-      <c r="Z64" s="5" t="n"/>
-      <c r="AA64" s="5" t="n"/>
-      <c r="AB64" s="5" t="n"/>
-      <c r="AC64" s="5" t="n"/>
+      <c r="Y64" s="5" t="inlineStr">
+        <is>
+          <t>demand and inventory coverage by product | transition cost and constraint data | unit campaign performance</t>
+        </is>
+      </c>
+      <c r="Z64" s="5" t="inlineStr">
+        <is>
+          <t>maintained production wheel with approved run lengths</t>
+        </is>
+      </c>
+      <c r="AA64" s="5" t="inlineStr">
+        <is>
+          <t>enables: Create Production Scheduling and Sequencing Plan | informed-by: Demand Forecasting</t>
+        </is>
+      </c>
+      <c r="AB64" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC64" s="5" t="inlineStr">
+        <is>
+          <t>periodic</t>
+        </is>
+      </c>
       <c r="AD64" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -8838,18 +9272,80 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U65" s="5" t="n"/>
-      <c r="V65" s="5" t="n"/>
-      <c r="W65" s="5" t="n"/>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>Build the dated production schedule and sequencing plan for the scheduling horizon — assigning campaigns, schedule-level unit commitments, blends, and movements to dates and sequences within the approved plan, the production wheel, and current constraints — producing the schedule that provides the approved basis for refinery execution.</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>Covers constructing and refreshing the dated schedule: sequencing within wheel and transition rules, scheduling blends and movements at schedule level, validating feasibility against constraints and outage windows, and publishing the schedule. Excludes unit-operation scheduling and tank and transfer line-ups, owned by Refining per the locked rule; excludes daily instruction updates (CM-1-1-7-1-1); excludes the plan targets themselves (CM-1-1-4).</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Sequence campaigns, schedule-level unit commitments, blends, and movements to dates | validate feasibility against constraints and outage windows | publish and refresh the dated schedule | reconcile the schedule to the approved plan</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>Unit-operation scheduling and line-ups (Refining) | daily instruction issuance (CM-1-1-7-1-1) | monthly plan targets (CM-1-1-4)</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>Build Production Schedule | Sequencing Plan Development</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Batch 06 (2026-09-19). 'Schedule-level unit commitments' used at Hamid's direction in place of 'unit operations' to preserve the boundary: the schedule commits what a unit should produce and when, never how it is operated. The scheduling-layer output per SNF/BJCE practice; the operations layer is Refining's per the locked rule. APQC 10223 'Create materials plan' is a WEAK generic candidate; comparative evidence only.</t>
+        </is>
+      </c>
+      <c r="U65" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V65" s="5" t="inlineStr">
+        <is>
+          <t>Produce the dated, feasible schedule that implements the plan.</t>
+        </is>
+      </c>
+      <c r="W65" s="5" t="inlineStr">
+        <is>
+          <t>SRC-BJCE-REFPS-001 | SRC-SNF-REFPS-001</t>
+        </is>
+      </c>
       <c r="X65" s="5" t="n"/>
-      <c r="Y65" s="5" t="n"/>
-      <c r="Z65" s="5" t="n"/>
-      <c r="AA65" s="5" t="n"/>
-      <c r="AB65" s="5" t="n"/>
-      <c r="AC65" s="5" t="n"/>
+      <c r="Y65" s="5" t="inlineStr">
+        <is>
+          <t>approved monthly plan | production wheel and run lengths | scheduling master data | outage windows</t>
+        </is>
+      </c>
+      <c r="Z65" s="5" t="inlineStr">
+        <is>
+          <t>published dated production schedule and sequencing plan</t>
+        </is>
+      </c>
+      <c r="AA65" s="5" t="inlineStr">
+        <is>
+          <t>uses-input: Maintain Production Scheduling Master Data | follows: Review Production Wheel and Run Length | precedes: Daily Execution Planning</t>
+        </is>
+      </c>
+      <c r="AB65" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC65" s="5" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AD65" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -8917,18 +9413,80 @@
           <t>strong APQC candidate but no validator agreed</t>
         </is>
       </c>
-      <c r="U66" s="5" t="n"/>
-      <c r="V66" s="5" t="n"/>
-      <c r="W66" s="5" t="n"/>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>Detect, assess, and resolve deviations from the production schedule — unit upsets, feed or quality surprises, outage changes, and demand shifts — deciding schedule responses, triggering rescheduling, and escalating deviations that break the approved plan to planning.</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>Covers the schedule exception rhythm: monitoring execution feedback against the schedule, assessing deviation impact, deciding and coordinating the schedule response, triggering rescheduling through Create Production Scheduling and Sequencing Plan (CM-1-1-7-2-3), escalating plan-level breaks to Refinery Planning (CM-1-1-4), and recording exception causes for performance measurement. The operational decision to depart from the schedule for safety, reliability, or immediate process conditions belongs to Refining under the locked rule; this process manages the schedule consequence of such departures.</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Monitor execution against schedule and detect deviations | assess deviation impact | decide and coordinate schedule responses | escalate plan-breaking deviations to planning | record exception causes</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>Operational departures for safety and reliability (Refining) | rescheduling construction (CM-1-1-7-2-3) | plan revision (CM-1-1-4)</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>Schedule Exception Management</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Batch 06 (2026-09-19). Refining decides safe operational departures (locked); this node owns the schedule response, not the operational decision. APQC 10224 STRONG with no validator; comparative evidence only.</t>
+        </is>
+      </c>
+      <c r="U66" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V66" s="5" t="inlineStr">
+        <is>
+          <t>Keep the schedule valid when reality diverges from it.</t>
+        </is>
+      </c>
+      <c r="W66" s="5" t="inlineStr">
+        <is>
+          <t>SRC-BJCE-REFPS-001</t>
+        </is>
+      </c>
       <c r="X66" s="5" t="n"/>
-      <c r="Y66" s="5" t="n"/>
-      <c r="Z66" s="5" t="n"/>
-      <c r="AA66" s="5" t="n"/>
-      <c r="AB66" s="5" t="n"/>
-      <c r="AC66" s="5" t="n"/>
+      <c r="Y66" s="5" t="inlineStr">
+        <is>
+          <t>execution feedback and deviation reports | schedule and plan constraints | impact assessments</t>
+        </is>
+      </c>
+      <c r="Z66" s="5" t="inlineStr">
+        <is>
+          <t>decided schedule responses and escalations with recorded causes</t>
+        </is>
+      </c>
+      <c r="AA66" s="5" t="inlineStr">
+        <is>
+          <t>triggers: Create Production Scheduling and Sequencing Plan | informed-by: Daily Execution Planning | enables: Measure Production Scheduling Performance</t>
+        </is>
+      </c>
+      <c r="AB66" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC66" s="5" t="inlineStr">
+        <is>
+          <t>event-driven</t>
+        </is>
+      </c>
       <c r="AD66" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -8996,18 +9554,80 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U67" s="5" t="n"/>
-      <c r="V67" s="5" t="n"/>
-      <c r="W67" s="5" t="n"/>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>Measure and report how well execution followed the issued production schedule and how stable the schedule itself was — adherence, rescheduling frequency, and exception causes at agreed levels — feeding improvements back into scheduling practice and master data.</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>Covers schedule-performance measurement against the schedule as issued, keeping the contemporaneous-baseline discipline: adherence and stability analysis, exception-cause patterns, and improvement recommendations to scheduling practice, the wheel, and master data. Excludes plan-versus-actual variance explanation, owned by Regional Backcasting (CM-1-1-5) under its locked rule; excludes asset and yield performance ownership, which belongs to Refining with actuals supplied by production accounting; excludes enterprise KPI definition (KPI workstream).</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Measure adherence to the issued schedule | measure schedule stability and rescheduling frequency | analyze exception-cause patterns | recommend improvements to practice, wheel, and master data</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>Plan-versus-actual backcasting (Regional Backcasting, CM-1-1-5) | asset and yield performance ownership (Refining) | enterprise KPI definition (KPI workstream)</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>Schedule Adherence Measurement | Scheduling Performance Measurement</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Batch 06 (2026-09-19). Horizon set to 'continuous' per the batch 05 precedent (Hamid's -8-4 edit) — continuous operational monitoring with periodic reporting and review; the controlled vocabulary takes a single value, so the cadence is recorded here. Specific metrics deliberately not named (KPI workstream). APQC 10314 is a WEAK generic candidate; comparative evidence only.</t>
+        </is>
+      </c>
+      <c r="U67" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V67" s="5" t="inlineStr">
+        <is>
+          <t>Establish whether the schedule is being followed and whether it is worth following.</t>
+        </is>
+      </c>
+      <c r="W67" s="5" t="inlineStr">
+        <is>
+          <t>SRC-BJCE-REFPS-001 | SRC-ASCM-CSCP-001</t>
+        </is>
+      </c>
       <c r="X67" s="5" t="n"/>
-      <c r="Y67" s="5" t="n"/>
-      <c r="Z67" s="5" t="n"/>
-      <c r="AA67" s="5" t="n"/>
-      <c r="AB67" s="5" t="n"/>
-      <c r="AC67" s="5" t="n"/>
+      <c r="Y67" s="5" t="inlineStr">
+        <is>
+          <t>issued schedules and revisions | actualized production from production accounting | recorded exception causes</t>
+        </is>
+      </c>
+      <c r="Z67" s="5" t="inlineStr">
+        <is>
+          <t>scheduling performance report with improvement recommendations</t>
+        </is>
+      </c>
+      <c r="AA67" s="5" t="inlineStr">
+        <is>
+          <t>uses-input: Perform Production Accounting | follows: Manage Production Schedule Exceptions | enables: Production Scheduling</t>
+        </is>
+      </c>
+      <c r="AB67" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC67" s="5" t="inlineStr">
+        <is>
+          <t>continuous</t>
+        </is>
+      </c>
       <c r="AD67" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -9075,18 +9695,80 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U68" s="5" t="n"/>
-      <c r="V68" s="5" t="n"/>
-      <c r="W68" s="5" t="n"/>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>Run the structured coordination between production scheduling and its counterparties — feasibility and deviation feedback to Refinery Planning, executability alignment with refinery operations, and outage, turnaround, and maintenance windows from engineering and maintenance — so the schedule and its neighbors stay mutually consistent.</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>Covers recurring interface management: scheduled coordination and handoffs, intake of maintenance and turnaround windows into the schedule, executability confirmation with operations, feasibility feedback to planning, and documentation of interface agreements. Excludes the counterparties' own work: plan targets (Refinery Planning, CM-1-1-4), maintenance planning and turnaround execution (Refining, per the locked rule), and operational execution (Refining). The concept is the recurring coordination process, not an organizational liaison role.</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Run scheduled coordination and handoffs | intake outage, turnaround, and maintenance windows | confirm schedule executability with operations | feed feasibility and deviations back to planning</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>Plan targets (CM-1-1-4) | maintenance planning and turnaround execution (Refining) | operational execution (Refining)</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>Scheduling Interface Management</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Batch 06 (2026-09-19). Modeled as the recurring coordination process per the process-concept rule, not a role or an organizational unit. APQC 10734 'Manage treasury operations' is an unrelated false match.</t>
+        </is>
+      </c>
+      <c r="U68" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V68" s="5" t="inlineStr">
+        <is>
+          <t>Keep the schedule and its neighboring functions mutually consistent.</t>
+        </is>
+      </c>
+      <c r="W68" s="5" t="inlineStr">
+        <is>
+          <t>SRC-SNF-REFPS-001 | SRC-ASCM-CSCP-001</t>
+        </is>
+      </c>
       <c r="X68" s="5" t="n"/>
-      <c r="Y68" s="5" t="n"/>
-      <c r="Z68" s="5" t="n"/>
-      <c r="AA68" s="5" t="n"/>
-      <c r="AB68" s="5" t="n"/>
-      <c r="AC68" s="5" t="n"/>
+      <c r="Y68" s="5" t="inlineStr">
+        <is>
+          <t>maintenance and turnaround plans | operations executability feedback | plan updates and constraints</t>
+        </is>
+      </c>
+      <c r="Z68" s="5" t="inlineStr">
+        <is>
+          <t>consistent interface agreements and window intake into the schedule</t>
+        </is>
+      </c>
+      <c r="AA68" s="5" t="inlineStr">
+        <is>
+          <t>enables: Create Production Scheduling and Sequencing Plan | informed-by: Refinery Planning</t>
+        </is>
+      </c>
+      <c r="AB68" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC68" s="5" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AD68" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -9154,18 +9836,80 @@
           <t>no meaningful APQC candidate</t>
         </is>
       </c>
-      <c r="U69" s="5" t="n"/>
-      <c r="V69" s="5" t="n"/>
-      <c r="W69" s="5" t="n"/>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>Optimize energy, utility, and emissions-allowance economics within refinery planning and scheduling by setting sourcing strategies, economic targets, and allowance-position recommendations that inform the production schedule.</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>Covers planning- and scheduling-level energy economics: evaluating internal generation versus purchased-energy options; incorporating energy, utility, and carbon costs into refinery planning and production scheduling; establishing economic operating targets and constraints for schedule development; maintaining an emissions-allowance and credit position; and preparing recommendations for allowance banking, purchase, or sale. Refining operates and controls utility systems, including boilers, cogeneration, steam, fuel-gas, power-distribution, and energy-recovery equipment. EHS &amp; Government Reporting owns regulatory emissions monitoring, calculation, submission, and reporting under its locked rule. The relevant commercial or trading function owns energy contracting and allowance-trade negotiation and execution.</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Evaluate internal generation versus purchased-energy options | incorporate energy, utility, and carbon costs into planning and scheduling | establish economic operating targets and constraints for schedule development | maintain the emissions-allowance and credit position and prepare banking, purchase, and sale recommendations</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>Utility system operation and control (Refining) | regulatory emissions monitoring and reporting (EHS &amp; Government Reporting) | energy contracting and allowance-trade execution (commercial and trading owner) | financial accounting treatment of allowances and credits (Finance)</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>Refinery Energy Economics | Energy &amp; Utilities Optimization</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Batch 06 (2026-09-19). Q2 decision (Hamid, Option A, narrowed): defined explicitly as the economic and scheduling layer of energy and utilities — the bare label could suggest ownership of utility systems, which belong to Refining. EHS reports (locked rule); the trading function executes; Finance records the accounting treatment of allowances and credits. Whether energy contracting is centralized or delegated to site commercial teams is a follow-up noted in the batch 06 PR. APQC: no meaningful candidate.</t>
+        </is>
+      </c>
+      <c r="U69" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V69" s="5" t="inlineStr">
+        <is>
+          <t>Minimize energy cost and carbon exposure from the planning side, within reliable operations.</t>
+        </is>
+      </c>
+      <c r="W69" s="5" t="inlineStr">
+        <is>
+          <t>SRC-EI-HM31-001 | SRC-EPA-EMTR-001</t>
+        </is>
+      </c>
       <c r="X69" s="5" t="n"/>
-      <c r="Y69" s="5" t="n"/>
-      <c r="Z69" s="5" t="n"/>
-      <c r="AA69" s="5" t="n"/>
-      <c r="AB69" s="5" t="n"/>
-      <c r="AC69" s="5" t="n"/>
+      <c r="Y69" s="5" t="inlineStr">
+        <is>
+          <t>energy prices and contract terms | utility system capabilities and constraints | production schedule and emissions position</t>
+        </is>
+      </c>
+      <c r="Z69" s="5" t="inlineStr">
+        <is>
+          <t>energy sourcing strategy, economic targets, and allowance-position recommendations</t>
+        </is>
+      </c>
+      <c r="AA69" s="5" t="inlineStr">
+        <is>
+          <t>informed-by: Production Scheduling | enables: Daily Execution Planning</t>
+        </is>
+      </c>
+      <c r="AB69" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC69" s="5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AD69" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -9233,18 +9977,80 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U70" s="5" t="n"/>
-      <c r="V70" s="5" t="n"/>
-      <c r="W70" s="5" t="n"/>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>Decide the economically optimal mix of self-generated and externally purchased energy — fuel gas, fuel oil, steam, and power, including cogeneration versus grid supply — for the planning period, within reliability, contractual, and emissions constraints.</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>Covers the recurring sourcing optimization: comparing marginal costs of internal generation against purchases, setting the sourcing plan by utility, respecting contract terms and reliability minimums, and reflecting emissions-allowance cost in the choice. Excludes negotiating energy supply contracts, owned by the commercial owner of energy supply; excludes operating generation and distribution assets, owned by Refining; excludes the sitewide balance targets, owned by Optimize Plant Energy Balance (CM-1-1-7-3-2).</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Compare marginal costs of internal generation versus purchase | set the sourcing plan by utility and period | respect contractual and reliability constraints | reflect allowance cost in sourcing choices</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>Energy contract negotiation (commercial owner of energy supply) | generation and distribution operation (Refining) | sitewide balance targets (CM-1-1-7-3-2)</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>Energy Make-versus-Buy Optimization</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Batch 06 (2026-09-19). APQC 10113 is an unrelated strategy candidate; comparative evidence only.</t>
+        </is>
+      </c>
+      <c r="U70" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V70" s="5" t="inlineStr">
+        <is>
+          <t>Choose the cheapest reliable energy mix the refinery can run on.</t>
+        </is>
+      </c>
+      <c r="W70" s="5" t="inlineStr">
+        <is>
+          <t>SRC-EI-HM31-001</t>
+        </is>
+      </c>
       <c r="X70" s="5" t="n"/>
-      <c r="Y70" s="5" t="n"/>
-      <c r="Z70" s="5" t="n"/>
-      <c r="AA70" s="5" t="n"/>
-      <c r="AB70" s="5" t="n"/>
-      <c r="AC70" s="5" t="n"/>
+      <c r="Y70" s="5" t="inlineStr">
+        <is>
+          <t>internal generation costs | purchased energy prices and terms | reliability requirements | allowance prices</t>
+        </is>
+      </c>
+      <c r="Z70" s="5" t="inlineStr">
+        <is>
+          <t>period energy sourcing plan</t>
+        </is>
+      </c>
+      <c r="AA70" s="5" t="inlineStr">
+        <is>
+          <t>enables: Optimize Plant Energy Balance | informed-by: Manage and Support Emission Trading</t>
+        </is>
+      </c>
+      <c r="AB70" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC70" s="5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AD70" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -9307,18 +10113,80 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U71" s="5" t="n"/>
-      <c r="V71" s="5" t="n"/>
-      <c r="W71" s="5" t="n"/>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>Establish and maintain planning and scheduling targets for the refinery's sitewide energy balance — such as expected steam, fuel-gas, power, and energy-recovery requirements — so production schedules reflect energy cost, availability, emissions exposure, and operating constraints.</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>Covers integrating energy-balance assumptions and economic targets into the production schedule; assessing deviations that materially affect scheduled energy cost or emissions exposure; and recommending schedule-level adjustments. Refining owns real-time utility balancing, equipment dispatch, process control, flaring response, and execution of energy-balance moves. Excludes sourcing mix decisions, owned by Optimize Internal vs. External Energy Sources (CM-1-1-7-3-1); excludes energy-efficiency capital projects, owned by Refining and engineering.</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Integrate energy-balance assumptions and economic targets into the schedule | assess deviations affecting scheduled energy cost or emissions exposure | recommend schedule-level adjustments | maintain energy-balance planning assumptions</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>Real-time utility balancing, dispatch, process control, and flaring response (Refining) | sourcing mix decisions (CM-1-1-7-3-1) | energy-efficiency capital projects (Refining, engineering)</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>Energy Balance Target Setting | Site Energy Balance Planning</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Batch 06 (2026-09-19). Rewritten at Hamid's direction before approval: the original draft's 'set the targets the refinery runs to' and 'minimizing purchased energy, flaring, and losses' read as operational control — this node sets planning and scheduling targets and recommendations only; real-time balancing and dispatch are Refining's. APQC 12979 'Optimize plant units' is a WEAK review-link; comparative evidence only.</t>
+        </is>
+      </c>
+      <c r="U71" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V71" s="5" t="inlineStr">
+        <is>
+          <t>Give the schedule sound energy-balance assumptions and targets, and flag deviations that change its economics.</t>
+        </is>
+      </c>
+      <c r="W71" s="5" t="inlineStr">
+        <is>
+          <t>SRC-EI-HM31-001</t>
+        </is>
+      </c>
       <c r="X71" s="5" t="n"/>
-      <c r="Y71" s="5" t="n"/>
-      <c r="Z71" s="5" t="n"/>
-      <c r="AA71" s="5" t="n"/>
-      <c r="AB71" s="5" t="n"/>
-      <c r="AC71" s="5" t="n"/>
+      <c r="Y71" s="5" t="inlineStr">
+        <is>
+          <t>site energy balance data | sourcing plan | production schedule | operating constraints</t>
+        </is>
+      </c>
+      <c r="Z71" s="5" t="inlineStr">
+        <is>
+          <t>energy-balance planning targets and schedule-level recommendations</t>
+        </is>
+      </c>
+      <c r="AA71" s="5" t="inlineStr">
+        <is>
+          <t>follows: Optimize Internal vs. External Energy Sources | enables: Daily Execution Planning</t>
+        </is>
+      </c>
+      <c r="AB71" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC71" s="5" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
       <c r="AD71" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -9381,18 +10249,80 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U72" s="5" t="n"/>
-      <c r="V72" s="5" t="n"/>
-      <c r="W72" s="5" t="n"/>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>Manage the refinery's emissions-allowance and credit position from the planning side — tracking emissions against allowances by program and period, forecasting surplus or shortfall from the production and energy plans, and supporting allowance purchase, sale, and banking decisions — so compliance obligations are met at the best economic outcome.</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>Covers allowance position management per emissions-trading program mechanics: maintaining the position by program, forecasting surplus and shortfall from schedule and energy plans, preparing the economic case for trades and banking, incorporating allowance prices into scheduling and energy decisions, and supporting compliance true-up. Excludes regulatory emissions monitoring and reporting, owned by EHS &amp; Government Reporting under its locked rule; excludes trade negotiation and execution, owned by the trading function (Supply And Trading where modeled); excludes the financial accounting treatment of allowances and credits, owned by Finance. 'Support' in the label reflects this advisory position: the node prepares and supports the decisions without executing trades or filing reports.</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Maintain the allowance and credit position by program | forecast surplus and shortfall from plans | prepare the economic case for trades and banking | support compliance true-up and reflect allowance cost in decisions</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>Regulatory emissions monitoring and reporting (EHS &amp; Government Reporting) | trade negotiation and execution (trading function) | financial accounting of allowances and credits (Finance) | emissions-reduction capital projects (Refining, engineering)</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>Emissions Allowance Position Management</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Batch 06 (2026-09-19). The decide-versus-advise pattern applies twice: EHS owns the regulator-facing report (locked rule); trading owns execution; Finance records the accounting treatment. 'Emissions allowances and credits' used throughout because programs use different, not always interchangeable, instruments. Preferred normalized label 'Manage and Support Emissions Trading' (plural) queued for the naming pass per Hamid. Program mechanics (cap, allowances, trading, banking, true-up) per EPA emissions-trading practice as reference evidence; applicability is jurisdiction- and program-specific. APQC 19562 'Manage support utilities' is a WEAK lexical match; comparative evidence only.</t>
+        </is>
+      </c>
+      <c r="U72" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V72" s="5" t="inlineStr">
+        <is>
+          <t>Keep the allowance position known, forecast, and economically managed without owning the trade or the report.</t>
+        </is>
+      </c>
+      <c r="W72" s="5" t="inlineStr">
+        <is>
+          <t>SRC-EPA-EMTR-001 | SRC-EI-HM31-001</t>
+        </is>
+      </c>
       <c r="X72" s="5" t="n"/>
-      <c r="Y72" s="5" t="n"/>
-      <c r="Z72" s="5" t="n"/>
-      <c r="AA72" s="5" t="n"/>
-      <c r="AB72" s="5" t="n"/>
-      <c r="AC72" s="5" t="n"/>
+      <c r="Y72" s="5" t="inlineStr">
+        <is>
+          <t>emissions forecasts from production and energy plans | allowance holdings and prices | program rules and compliance deadlines</t>
+        </is>
+      </c>
+      <c r="Z72" s="5" t="inlineStr">
+        <is>
+          <t>managed allowance position with trade and banking recommendations</t>
+        </is>
+      </c>
+      <c r="AA72" s="5" t="inlineStr">
+        <is>
+          <t>informed-by: Production Scheduling | enables: Optimize Internal vs. External Energy Sources</t>
+        </is>
+      </c>
+      <c r="AB72" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC72" s="5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AD72" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -44081,7 +45011,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -45113,6 +46043,53 @@
         </is>
       </c>
       <c r="I27" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>SRC-EPA-EMTR-001</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>U.S. Environmental Protection Agency</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Emissions Trading (program resources: how emissions trading programs work; allowance markets)</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Accessed 2026-09-19</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>https://www.epa.gov/emissions-trading</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Regulatory</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Emissions-trading and allowance-market mechanics; evidence only, not text to copy. Applicability is jurisdiction- and program-specific; use only where an applicable emissions-trading regime exists. Does not determine internal ownership assignments.</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Cap, allowance, trading, banking, and compliance true-up mechanics</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
         <is>
           <t>active</t>
         </is>

--- a/business_architecture/ontology/build/output/step3c-definition-authoring-workbook.xlsx
+++ b/business_architecture/ontology/build/output/step3c-definition-authoring-workbook.xlsx
@@ -10390,18 +10390,80 @@
           <t>no meaningful APQC candidate</t>
         </is>
       </c>
-      <c r="U73" s="5" t="n"/>
-      <c r="V73" s="5" t="n"/>
-      <c r="W73" s="5" t="n"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>The front-office capability to assemble and maintain a forward commercial view of supply, demand, generation, renewables, market conditions, and revenue, and to identify how the asset portfolio can be used commercially within approved plans and constraints.</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>Covers receiving and consolidating production, demand, and power-generation forecasts from their owning processes; producing the renewables forward view; identifying and valuing commercial use of asset flexibility; and projecting trading revenue, margin, and exposure. This capability consumes forecasts rather than owning their production: the approved demand forecast is owned by Demand Forecasting (CM-1-1-1-1) per the batch 03 decision, and production plans and schedules by Refinery Planning (CM-1-1-4) and Refinery Scheduling (CM-1-1-7). Excludes trade execution and capture, owned by Trade Capture (CM-1-2-1-3); excludes setting the regional or refinery plans, owned under the locked Regional Optimization and Refinery Planning rules; excludes risk measurement and limits, owned by Market Risk Management (CM-1-2-2-3).</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Receive and consolidate production, demand, and generation forecasts | develop the renewables forward view | identify and value commercial use of asset flexibility | project trading revenue, margin, and exposure</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>Forecast production ownership (CM-1-1-1-1, CM-1-1-4, CM-1-1-7) | trade execution and capture (CM-1-2-1-3) | regional and refinery plan setting (locked rules) | risk measurement and limits (CM-1-2-2-3)</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>Pre-Trade Forecasting &amp; Optimization</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Batch 07 (2026-09-19). Q1 decision (Hamid, Option A): capability — it comprises distinct forecast-intake, renewable-position forecasting, asset-optimization, and revenue-projection processes that collectively enable a current front-office forward view and commercially optimized asset position; it is not a single sequential process. Same test as the batch 04 Inventory L4. Front-office framing per the approved Trading Management (CM-1-2-1) definition; 'market conditions' made explicit at Hamid's direction so the forward-curve context is not read as physical volumes only. Q2 boundary recorded on CM-1-2-1-1-4. APQC 19569 'Perform real-time optimization' is process-control software; no meaningful candidate.</t>
+        </is>
+      </c>
+      <c r="U73" s="5" t="inlineStr">
+        <is>
+          <t>capability</t>
+        </is>
+      </c>
+      <c r="V73" s="5" t="inlineStr">
+        <is>
+          <t>Keep trading running on a current forward commercial view and an identified, valued set of asset opportunities.</t>
+        </is>
+      </c>
+      <c r="W73" s="5" t="inlineStr">
+        <is>
+          <t>SRC-CFTC-GLOSS-001 | SRC-EIA-STEO-001</t>
+        </is>
+      </c>
       <c r="X73" s="5" t="n"/>
-      <c r="Y73" s="5" t="n"/>
-      <c r="Z73" s="5" t="n"/>
-      <c r="AA73" s="5" t="n"/>
-      <c r="AB73" s="5" t="n"/>
-      <c r="AC73" s="5" t="n"/>
+      <c r="Y73" s="5" t="inlineStr">
+        <is>
+          <t>published demand forecast | production plans and schedules | generation forecasts | market prices and forward curves</t>
+        </is>
+      </c>
+      <c r="Z73" s="5" t="inlineStr">
+        <is>
+          <t>current trading forward view and asset-optimization recommendations</t>
+        </is>
+      </c>
+      <c r="AA73" s="5" t="inlineStr">
+        <is>
+          <t>informed-by: Demand Forecasting | informed-by: Refinery Planning | enables: Trading Strategy Management</t>
+        </is>
+      </c>
+      <c r="AB73" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC73" s="5" t="inlineStr">
+        <is>
+          <t>continuous</t>
+        </is>
+      </c>
       <c r="AD73" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -10464,18 +10526,80 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U74" s="5" t="n"/>
-      <c r="V74" s="5" t="n"/>
-      <c r="W74" s="5" t="n"/>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>Receive and incorporate the refinery production plans and schedules into the trading forward view — validating completeness, translating volumes into tradable supply by product, location, and period, and refreshing the view as plans and schedules change.</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>Covers the intake side only: receiving the approved production plan and current schedule from Refinery Planning (CM-1-1-4) and Refinery Scheduling (CM-1-1-7), reconciling product, location, and period granularity to what the trading books use, and flagging material changes to traders. It consumes these plans and does not produce or alter them — their owners hold that right. Excludes the demand-side intake, owned by Receive Demand Forecast (CM-1-2-1-1-2).</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Receive the approved plan and current schedule | validate completeness and version | translate volumes to tradable supply granularity | flag material changes to trading</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>Producing or altering the plan or schedule (CM-1-1-4, CM-1-1-7) | demand forecast intake (CM-1-2-1-1-2) | trading decisions on the supply (Trade Capture, strategy processes)</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>Production Forecast Intake</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Batch 07 (2026-09-19). A consume-not-produce node, per the precedent batch 02 recorded on its sibling CM-1-2-1-1-2. APQC 12901 'Forecast equity crude production' is a WEAK review-link; comparative evidence only.</t>
+        </is>
+      </c>
+      <c r="U74" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V74" s="5" t="inlineStr">
+        <is>
+          <t>Keep the trading view current with what the refinery is currently planned and scheduled to produce.</t>
+        </is>
+      </c>
+      <c r="W74" s="5" t="inlineStr">
+        <is>
+          <t>SRC-EIA-GLOSS-001</t>
+        </is>
+      </c>
       <c r="X74" s="5" t="n"/>
-      <c r="Y74" s="5" t="n"/>
-      <c r="Z74" s="5" t="n"/>
-      <c r="AA74" s="5" t="n"/>
-      <c r="AB74" s="5" t="n"/>
-      <c r="AC74" s="5" t="n"/>
+      <c r="Y74" s="5" t="inlineStr">
+        <is>
+          <t>approved production plan | current production schedule | product and location mappings</t>
+        </is>
+      </c>
+      <c r="Z74" s="5" t="inlineStr">
+        <is>
+          <t>production supply view refreshed in the trading forward view</t>
+        </is>
+      </c>
+      <c r="AA74" s="5" t="inlineStr">
+        <is>
+          <t>informed-by: Refinery Planning | informed-by: Production Scheduling | enables: Perform Asset Optimization</t>
+        </is>
+      </c>
+      <c r="AB74" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC74" s="5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AD74" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -10543,18 +10667,80 @@
           <t>strong APQC candidate but no validator agreed</t>
         </is>
       </c>
-      <c r="U75" s="5" t="n"/>
-      <c r="V75" s="5" t="n"/>
-      <c r="W75" s="5" t="n"/>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>Receive the published demand forecast and incorporate it into the trading forward view — validating the version, translating product, market, and period detail into the granularity trading uses, and refreshing trading assumptions when a new version publishes.</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>Covers the intake of the approved commercial planning forecast, which is owned by Demand Forecasting (CM-1-1-1-1) and released by Publish Forecast and Generate Component Level Forecast Plan (CM-1-1-1-1-4) per the batch 03 decision — this node consumes the published version and must not claim its production. Excludes Supply And Trading's own operational refined-product demand forecasting (Forecast Refined Product Demand, CM-1-2-6-2-3), which serves the supply-chain-management context under the batch 03 constraint. Excludes adjusting or overriding the forecast — trading views that differ from the published forecast are trading positions, not forecast revisions.</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Receive and validate the published forecast version | translate to trading granularity | refresh trading assumptions on new versions | flag material forecast changes to trading</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>Forecast production and ownership (CM-1-1-1-1) | operational refined-product demand forecasting (CM-1-2-6-2-3) | forecast adjustment or override (trading positions are not forecast revisions)</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>Demand Forecast Intake</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Batch 07 (2026-09-19). Batch 02 already cited this node as 'the existing precedent for a consume-not-produce node'; authored to honor that reading and the batch 03 Q2 decision (Demand Forecasting owns the approved forecast). APQC 20634 scored STRONG but is IT-service demand; false lexical match, comparative evidence only.</t>
+        </is>
+      </c>
+      <c r="U75" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V75" s="5" t="inlineStr">
+        <is>
+          <t>Keep trading assumptions aligned to the current published demand forecast.</t>
+        </is>
+      </c>
+      <c r="W75" s="5" t="inlineStr">
+        <is>
+          <t>SRC-EIA-STEO-001</t>
+        </is>
+      </c>
       <c r="X75" s="5" t="n"/>
-      <c r="Y75" s="5" t="n"/>
-      <c r="Z75" s="5" t="n"/>
-      <c r="AA75" s="5" t="n"/>
-      <c r="AB75" s="5" t="n"/>
-      <c r="AC75" s="5" t="n"/>
+      <c r="Y75" s="5" t="inlineStr">
+        <is>
+          <t>published versioned demand forecast | trading granularity mappings</t>
+        </is>
+      </c>
+      <c r="Z75" s="5" t="inlineStr">
+        <is>
+          <t>demand assumptions refreshed in the trading forward view</t>
+        </is>
+      </c>
+      <c r="AA75" s="5" t="inlineStr">
+        <is>
+          <t>informed-by: Demand Forecasting | uses-input: Publish Forecast and Generate Component Level Forecast Plan | enables: Perform Asset Optimization</t>
+        </is>
+      </c>
+      <c r="AB75" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC75" s="5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AD75" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -10622,18 +10808,80 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U76" s="5" t="n"/>
-      <c r="V76" s="5" t="n"/>
-      <c r="W76" s="5" t="n"/>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>Develop and maintain a forward view of renewable-fuel volumes, renewable-energy output or procurement, compliance obligations, and associated program-specific environmental attributes or credits — such as Renewable Identification Numbers where applicable — so commercial, trading, and compliance stakeholders can anticipate expected shortfalls, surpluses, and deadlines.</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>Covers forecasting renewable-fuel production, blending, acquisition, and obligation exposure; expected generation, acquisition, retirement, or need for program-specific environmental attributes and credits; and the resulting forward long and short positions by program and compliance period. Excludes regulatory monitoring, filing, attestation, and submission, owned by EHS &amp; Government Reporting under its locked rule; excludes execution of credit purchases, sales, transfers, or retirements, owned by the trading processes; excludes accounting actualization of issued, acquired, sold, retired, or expired instruments, owned by Perform RINs/REC Actualization (CM-1-2-3-1-7). Program applicability is jurisdiction-specific.</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Forecast renewable-fuel volumes and obligation exposure | forecast generation, acquisition, retirement, and need for program-specific attributes and credits | maintain forward long and short positions by program and compliance period | flag expected shortfalls, surpluses, and deadlines</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>Regulatory monitoring, filing, attestation, and submission (EHS &amp; Government Reporting) | credit purchase, sale, transfer, and retirement execution (trading processes) | credit actualization (CM-1-2-3-1-7)</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>Renewables Position Forecasting</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Batch 07 (2026-09-19). Reworded at Hamid's direction to treat environmental instruments as program-specific: RINs (RFS-type fuel programs) and RECs (renewable power programs) arise under different program architectures with different eligibility, lifecycle, compliance, and market rules and are not interchangeable. Which instruments are genuinely in scope (RINs, RECs, low-carbon fuel credits, allowances, guarantees of origin) is a follow-up noted in the batch 07 PR. EPA RFS practice is US-specific reference evidence for RVO and RIN mechanics only. APQC 10129 is an unrelated sales-forecast candidate.</t>
+        </is>
+      </c>
+      <c r="U76" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V76" s="5" t="inlineStr">
+        <is>
+          <t>Know the renewables obligation and instrument position before the deadline does.</t>
+        </is>
+      </c>
+      <c r="W76" s="5" t="inlineStr">
+        <is>
+          <t>SRC-EPA-RFS-001</t>
+        </is>
+      </c>
       <c r="X76" s="5" t="n"/>
-      <c r="Y76" s="5" t="n"/>
-      <c r="Z76" s="5" t="n"/>
-      <c r="AA76" s="5" t="n"/>
-      <c r="AB76" s="5" t="n"/>
-      <c r="AC76" s="5" t="n"/>
+      <c r="Y76" s="5" t="inlineStr">
+        <is>
+          <t>production and blending plans | program obligations and rules | instrument holdings and prices</t>
+        </is>
+      </c>
+      <c r="Z76" s="5" t="inlineStr">
+        <is>
+          <t>forward renewables position by program and compliance period</t>
+        </is>
+      </c>
+      <c r="AA76" s="5" t="inlineStr">
+        <is>
+          <t>uses-input: Receive Production Forecast | enables: Perform Asset Optimization | precedes: Perform RINs/REC Actualization</t>
+        </is>
+      </c>
+      <c r="AB76" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC76" s="5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AD76" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -10701,18 +10949,80 @@
           <t>strong APQC candidate but no validator agreed</t>
         </is>
       </c>
-      <c r="U77" s="5" t="n"/>
-      <c r="V77" s="5" t="n"/>
-      <c r="W77" s="5" t="n"/>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>Assess and optimize the commercial use of approved asset flexibility — including storage, transportation and terminal capacity, supply commitments, exchanges, and generation availability — against market conditions, identifying and valuing opportunities and providing recommendations to approved trading strategies within established plans and constraints.</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>Covers evaluating storage economics and time spreads; capacity utilization, release, and throughput opportunities; exchange and location-arbitrage opportunities; and the commercial value of generation availability. It identifies and quantifies trading opportunities within approved regional, refinery, and scheduling plans. Excludes changing physical plans, owned under the locked Regional Optimization and Refinery Planning rules; excludes operating or dispatching assets, owned by Refining, Midstream, and the relevant system operators; excludes defining or approving trading strategies, owned by Trading Strategy Management (CM-1-2-1-4); excludes negotiating, executing, capturing, or settling trades, owned by Trade Capture (CM-1-2-1-3) and the Settlements cluster; excludes risk-limit setting and risk measurement, owned by Market Risk Management (CM-1-2-2-3).</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Evaluate storage, capacity, exchange, and generation-availability economics against the market | identify and quantify opportunities within approved plans | value opportunities and their sensitivities | provide recommendations to approved trading strategies</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>Physical plan changes (Regional Optimization, Refinery Planning — locked) | asset operation and dispatch (Refining, Midstream, system operators) | trading strategy definition and approval (CM-1-2-1-4) | trade negotiation, execution, capture, and settlement (CM-1-2-1-3, Settlements) | risk-limit setting and risk measurement (CM-1-2-2-3)</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>Asset-Backed Trading Optimization</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Batch 07 (2026-09-19). Q2 decision (Hamid, Option A, narrowed): approved plans define the base; this process identifies, values, and recommends commercial use of the flexibility those plans leave open — it does not initiate strategies (Trading Strategy Management owns the strategy lifecycle) and does not own dispatch ('generation availability', not dispatch, at Hamid's direction). Whether the desk may submit pre-authorized strategy-linked trade orders, rather than only recommend, is a follow-up to be modeled through the future Trade Capture relationship, noted in the batch 07 PR. APQC 19253 'Perform asset maintenance' scored STRONG but is maintenance; false lexical match, comparative evidence only.</t>
+        </is>
+      </c>
+      <c r="U77" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V77" s="5" t="inlineStr">
+        <is>
+          <t>Identify and value the market opportunities the asset portfolio's approved flexibility offers.</t>
+        </is>
+      </c>
+      <c r="W77" s="5" t="inlineStr">
+        <is>
+          <t>SRC-CFTC-GLOSS-001 | SRC-EIA-GLOSS-001</t>
+        </is>
+      </c>
       <c r="X77" s="5" t="n"/>
-      <c r="Y77" s="5" t="n"/>
-      <c r="Z77" s="5" t="n"/>
-      <c r="AA77" s="5" t="n"/>
-      <c r="AB77" s="5" t="n"/>
-      <c r="AC77" s="5" t="n"/>
+      <c r="Y77" s="5" t="inlineStr">
+        <is>
+          <t>forward view of supply, demand, and generation | market prices and forward curves | asset capacities and constraints | approved plans</t>
+        </is>
+      </c>
+      <c r="Z77" s="5" t="inlineStr">
+        <is>
+          <t>valued asset-optimization opportunities and recommendations to approved strategies</t>
+        </is>
+      </c>
+      <c r="AA77" s="5" t="inlineStr">
+        <is>
+          <t>uses-input: Receive Production Forecast | uses-input: Receive Demand Forecast | enables: Trading Strategy Management</t>
+        </is>
+      </c>
+      <c r="AB77" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC77" s="5" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
       <c r="AD77" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -10780,18 +11090,80 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U78" s="5" t="n"/>
-      <c r="V78" s="5" t="n"/>
-      <c r="W78" s="5" t="n"/>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>Project the trading organization's expected economics — projected trading revenue, gross margin, and economic exposure from current positions, planned flows, the forward view, and market prices — so management and strategy decisions rest on a current forward-looking outlook.</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>Covers the front-office economic projection: projected revenue, gross margin, and exposure by book, strategy, and period, refreshed on market and position changes, with sensitivity to price scenarios. Excludes financial forecasting, budgeting, and reporting ownership, which sit with Finance under the locked rule; excludes official, controlled position and realized/unrealized P&amp;L reporting, owned by Perform Position &amp; PNL Analysis (CM-1-2-2-3-9) and the Accounting cluster (CM-1-2-4-2) — this is a forward-looking planning projection, not the governed result.</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Project revenue, gross margin, and exposure by book, strategy, and period | refresh projections on market and position changes | run price-scenario sensitivities | supply the economic outlook to management and strategy</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>Financial forecasting and budgeting (Finance) | official, controlled position and realized/unrealized P&amp;L reporting (CM-1-2-2-3-9, CM-1-2-4-2) | trading decisions themselves (strategy and capture processes)</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>Trading Revenue Projection | Forward Trading Economics Outlook</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Batch 07 (2026-09-19). Reframed at Hamid's direction as revenue, gross margin, and economic exposure — in a trading environment expected value, exposure, and scenario sensitivity matter alongside accounting-defined revenue; Finance's ownership of official financial forecasting and governed P&amp;L is unchanged. Whether optionality valuation and mark-to-market scenario impact are in scope, or only expected physical-trading margin, is a follow-up noted in the batch 07 PR. APQC 10129 is an unrelated sales-forecast candidate.</t>
+        </is>
+      </c>
+      <c r="U78" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V78" s="5" t="inlineStr">
+        <is>
+          <t>Provide management and strategy owners with a current forward-looking view of projected trading revenue, gross margin, and economic exposure.</t>
+        </is>
+      </c>
+      <c r="W78" s="5" t="inlineStr">
+        <is>
+          <t>SRC-CFTC-GLOSS-001</t>
+        </is>
+      </c>
       <c r="X78" s="5" t="n"/>
-      <c r="Y78" s="5" t="n"/>
-      <c r="Z78" s="5" t="n"/>
-      <c r="AA78" s="5" t="n"/>
-      <c r="AB78" s="5" t="n"/>
-      <c r="AC78" s="5" t="n"/>
+      <c r="Y78" s="5" t="inlineStr">
+        <is>
+          <t>current positions and planned flows | forward view and market prices | price scenarios</t>
+        </is>
+      </c>
+      <c r="Z78" s="5" t="inlineStr">
+        <is>
+          <t>projected trading revenue, gross margin, and exposure outlook</t>
+        </is>
+      </c>
+      <c r="AA78" s="5" t="inlineStr">
+        <is>
+          <t>uses-input: Perform Asset Optimization | enables: Trading Strategy Management</t>
+        </is>
+      </c>
+      <c r="AB78" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC78" s="5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AD78" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -10859,18 +11231,80 @@
           <t>no meaningful APQC candidate</t>
         </is>
       </c>
-      <c r="U79" s="5" t="n"/>
-      <c r="V79" s="5" t="n"/>
-      <c r="W79" s="5" t="n"/>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>Receive and incorporate power generation forecasts — from company cogeneration and any contracted or merchant generation — into the trading forward view, validating them and translating expected generation into tradable positions by period.</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>Covers the intake side only: generation forecasts are produced by the asset operators (Refining for cogeneration) or external suppliers; this node consumes them into the forward view, reconciles period granularity, and flags material changes. Excludes producing generation forecasts (asset operators and suppliers); excludes physical generation dispatch and grid/system operations, owned by the asset operators and the relevant system authorities; excludes power trade execution and settlement, owned by Trade Capture (CM-1-2-1-3) and the Settlements cluster.</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Receive and validate generation forecasts | translate expected generation to tradable positions by period | refresh the forward view on forecast changes | flag material generation changes to trading</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>Generation forecast production (asset operators, suppliers) | physical generation dispatch and grid/system operations (asset operators, system authorities) | power trade execution and settlement (CM-1-2-1-3, Settlements)</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>Generation Forecast Intake</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Batch 07 (2026-09-19). Third of the three consume-not-produce intake siblings; dispatch and grid-operations exclusion worded per Hamid's batch 07 edit for precision. APQC: no meaningful candidate.</t>
+        </is>
+      </c>
+      <c r="U79" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V79" s="5" t="inlineStr">
+        <is>
+          <t>Keep the trading view current with expected power generation.</t>
+        </is>
+      </c>
+      <c r="W79" s="5" t="inlineStr">
+        <is>
+          <t>SRC-EIA-GLOSS-001</t>
+        </is>
+      </c>
       <c r="X79" s="5" t="n"/>
-      <c r="Y79" s="5" t="n"/>
-      <c r="Z79" s="5" t="n"/>
-      <c r="AA79" s="5" t="n"/>
-      <c r="AB79" s="5" t="n"/>
-      <c r="AC79" s="5" t="n"/>
+      <c r="Y79" s="5" t="inlineStr">
+        <is>
+          <t>cogeneration and contracted generation forecasts | period granularity mappings</t>
+        </is>
+      </c>
+      <c r="Z79" s="5" t="inlineStr">
+        <is>
+          <t>generation positions refreshed in the trading forward view</t>
+        </is>
+      </c>
+      <c r="AA79" s="5" t="inlineStr">
+        <is>
+          <t>informed-by: Energy &amp; Utility Management | enables: Perform Asset Optimization</t>
+        </is>
+      </c>
+      <c r="AB79" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC79" s="5" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
       <c r="AD79" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -12824,18 +13258,80 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U104" s="5" t="n"/>
-      <c r="V104" s="5" t="n"/>
-      <c r="W104" s="5" t="n"/>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>Develop, approve, and steward the trading strategies the front office runs — defining each strategy's objective, markets, instruments, and horizon, aligning it with approved authorities and risk limits, reviewing performance, and adjusting or retiring strategies as conditions change.</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>Covers the strategy lifecycle: proposing and documenting strategies, securing approval within the delegation of authority, aligning with risk limits, monitoring strategy performance and adherence, and adjusting or retiring strategies. Excludes setting the delegation of authority and the risk limits themselves, owned by Market Risk Management (Establish &amp; Maintain Delegation Of Authority, CM-1-2-2-3-2; Manage Risk Limits, CM-1-2-2-3-6); excludes portfolio-level risk appetite, limit-setting, independent valuation governance, and risk-control challenge, which belong to Market Risk Management (CM-1-2-2-3); excludes trade execution and capture, owned by Trade Capture (CM-1-2-1-3); excludes trading compliance monitoring, owned by Regulatory &amp; Compliance (CM-1-2-4-3).</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Propose and document trading strategies | secure approval within the delegation of authority | align strategies with risk limits | review strategy performance and adjust or retire</t>
+        </is>
+      </c>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>Delegation of authority and risk limit setting (CM-1-2-2-3-2, CM-1-2-2-3-6) | portfolio risk appetite, independent valuation governance, and risk-control challenge (CM-1-2-2-3) | trade execution and capture (CM-1-2-1-3) | compliance monitoring (CM-1-2-4-3)</t>
+        </is>
+      </c>
+      <c r="R104" t="inlineStr">
+        <is>
+          <t>Trading Strategy Development &amp; Stewardship</t>
+        </is>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Batch 07 (2026-09-19). A leaf L4 with no children in the map; the front-office/middle-office split is preserved — strategy stewardship here; authority, limits, risk appetite, independent valuation governance, and risk-control challenge at Market Risk Management (exclusion made explicit at Hamid's direction so strategy approval and risk-appetite approval cannot blur); compliance at Regulatory &amp; Compliance. APQC 20674 is an IT-strategy candidate; false lexical match, comparative evidence only.</t>
+        </is>
+      </c>
+      <c r="U104" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V104" s="5" t="inlineStr">
+        <is>
+          <t>Ensure every strategy the front office runs is defined, authorized, within limits, and worth running.</t>
+        </is>
+      </c>
+      <c r="W104" s="5" t="inlineStr">
+        <is>
+          <t>SRC-CFTC-GLOSS-001</t>
+        </is>
+      </c>
       <c r="X104" s="5" t="n"/>
-      <c r="Y104" s="5" t="n"/>
-      <c r="Z104" s="5" t="n"/>
-      <c r="AA104" s="5" t="n"/>
-      <c r="AB104" s="5" t="n"/>
-      <c r="AC104" s="5" t="n"/>
+      <c r="Y104" s="5" t="inlineStr">
+        <is>
+          <t>forward view and revenue projections | delegation of authority and risk limits | strategy performance results</t>
+        </is>
+      </c>
+      <c r="Z104" s="5" t="inlineStr">
+        <is>
+          <t>approved, monitored trading strategies</t>
+        </is>
+      </c>
+      <c r="AA104" s="5" t="inlineStr">
+        <is>
+          <t>uses-input: Forecast Revenue | uses-input: Perform Asset Optimization | governed-by: Market Risk Management</t>
+        </is>
+      </c>
+      <c r="AB104" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC104" s="5" t="inlineStr">
+        <is>
+          <t>periodic</t>
+        </is>
+      </c>
       <c r="AD104" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -45011,7 +45507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -46090,6 +46586,100 @@
         </is>
       </c>
       <c r="I28" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>SRC-EPA-RFS-001</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>U.S. Environmental Protection Agency</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Renewable Fuel Standard program (overview; Renewable Identification Numbers under the RFS)</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Accessed 2026-09-19</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>https://www.epa.gov/renewable-fuel-standard/overview-renewable-fuel-standard-program</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Regulatory</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>RFS, RVO, and RIN mechanics; evidence only, not text to copy. Applicable to US RFS/RIN mechanics; jurisdiction- and program-specific. Does not generalize to REC programs or all environmental-credit schemes.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Renewable volumes, obligations, and credit mechanics for renewables forecasting and actualization</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>SRC-CFTC-GLOSS-001</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>U.S. Commodity Futures Trading Commission</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>CFTC Glossary (futures, options, and derivatives terms)</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Accessed 2026-09-19</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>https://www.cftc.gov/LearnAndProtect/AdvisoriesAndArticles/CFTCGlossary/index.htm</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Regulatory</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Derivatives and commodity-trading terminology; evidence only, not text to copy. Does not define the enterprise's process ownership, control model, or operating model.</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Trading, margin, position, swap, and swap-data-reporting terminology for Supply And Trading batches</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
         <is>
           <t>active</t>
         </is>

--- a/business_architecture/ontology/build/output/step3c-definition-authoring-workbook.xlsx
+++ b/business_architecture/ontology/build/output/step3c-definition-authoring-workbook.xlsx
@@ -12315,18 +12315,80 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U92" s="5" t="n"/>
-      <c r="V92" s="5" t="n"/>
-      <c r="W92" s="5" t="n"/>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>Perform the controlled pre-trade analysis, authorization, and post-execution recording of trades in the trading system — capturing complete commercial, operational, and regulatory terms by deal type and submitting required creation-data reports — so authorized transactions are available to confirmation, risk, actualization, settlement, and accounting processes.</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>Covers the per-transaction lifecycle: analyzing prospective deals, obtaining approval within the delegation of authority, capturing executed physical, exchange, storage, environmental, financial, structured, transportation, and transmission deals after execution, and reporting creation data to swap data repositories where an applicable regime requires it. Trading strategies and approved asset-optimization opportunities inform prospective transactions; the authorized trader or delegated execution role executes a transaction only after required pre-trade controls and approvals have been satisfied — capture is the controlled record-creation activity, not the act of purchasing or selling. Excludes trade confirmation and matching with counterparties, owned by Confirmations Management (CM-1-2-2-2); excludes risk measurement and limits (Market Risk Management, CM-1-2-2-3); excludes actualization (CM-1-2-3-1) and settlement (CM-1-2-4-1); excludes counterparty and contract lifecycle administration (Contract Management, CM-1-2-1-2).</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Analyze prospective deals before execution | obtain trade approval within the delegation of authority | capture executed deals by type with full commercial, operational, and regulatory terms | report creation data where an applicable regime requires it</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>Trade execution as an act of purchasing or selling (authorized trader or delegated execution role) | strategy definition (CM-1-2-1-4, CM-1-2-1-1-4) | confirmation and matching (CM-1-2-2-2) | risk measurement and limits (CM-1-2-2-3) | actualization and settlement (CM-1-2-3-1, CM-1-2-4-1) | counterparty and contract administration (CM-1-2-1-2)</t>
+        </is>
+      </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>Deal Capture | Trade Entry &amp; Reporting</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Batch 08 (2026-09-19). Q1 decision (Hamid, Option A): process — the children form a per-transaction lifecycle (analyze, authorize, capture by deal type, report) with the eight capture nodes as instrument-specific variants of one controlled deal-entry activity; the Demand Forecasting process precedent applies, not the batch 04 capability test. Reworded at Hamid's direction to distinguish trade execution from trade capture: this process controls what happens before, at, and immediately after execution and records the trade; it does not execute it. Whether the enterprise's system of record supports a single deal record or a governed golden-deal model across systems is a follow-up noted in the batch 08 PR. APQC 14095 'Document trade' is a WEAK international-trade candidate; comparative evidence only.</t>
+        </is>
+      </c>
+      <c r="U92" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V92" s="5" t="inlineStr">
+        <is>
+          <t>Get every executed trade authorized, completely recorded, and reported where required, once and correctly.</t>
+        </is>
+      </c>
+      <c r="W92" s="5" t="inlineStr">
+        <is>
+          <t>SRC-CFTC-GLOSS-001</t>
+        </is>
+      </c>
       <c r="X92" s="5" t="n"/>
-      <c r="Y92" s="5" t="n"/>
-      <c r="Z92" s="5" t="n"/>
-      <c r="AA92" s="5" t="n"/>
-      <c r="AB92" s="5" t="n"/>
-      <c r="AC92" s="5" t="n"/>
+      <c r="Y92" s="5" t="inlineStr">
+        <is>
+          <t>approved strategies and recommendations | executed transaction terms | delegation of authority | applicable reporting rules</t>
+        </is>
+      </c>
+      <c r="Z92" s="5" t="inlineStr">
+        <is>
+          <t>authorized, complete, reported deal records available to downstream processes</t>
+        </is>
+      </c>
+      <c r="AA92" s="5" t="inlineStr">
+        <is>
+          <t>follows: Trading Strategy Management | precedes: Confirmations Management | enables: Market Risk Management</t>
+        </is>
+      </c>
+      <c r="AB92" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC92" s="5" t="inlineStr">
+        <is>
+          <t>event-driven</t>
+        </is>
+      </c>
       <c r="AD92" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -12394,18 +12456,80 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U93" s="5" t="n"/>
-      <c r="V93" s="5" t="n"/>
-      <c r="W93" s="5" t="n"/>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>Evaluate a prospective trade before execution — its economics, strategy fit, credit and limit headroom, operational feasibility where applicable, and regulatory treatment — so the trader and approver see the deal's value and consequences before committing the company.</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>Covers per-deal analysis ahead of execution: deal economics and sensitivities, fit with the approved strategy, pre-checks against credit exposure and market-risk limit headroom, operational feasibility for physical, capacity, transportation, storage, and structured trades where applicable, and identification of regulatory treatment including reportability. Pre-trade analysis may evaluate available credit exposure and risk-limit headroom, but it does not set limits or independently authorize an override, exception, or breach — those sit with Credit Risk Management (CM-1-2-2-1) and Market Risk Management (CM-1-2-2-3). Distinct from Perform Asset Optimization (CM-1-2-1-1-4), which identifies and values portfolio opportunities — this node analyzes the specific prospective transaction, including ones arising from those recommendations. Excludes the approval decision itself (CM-1-2-1-3-2).</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Analyze deal economics and sensitivities | check strategy fit | pre-check credit exposure and limit headroom | assess operational feasibility where applicable | identify regulatory treatment and reportability</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>Portfolio opportunity identification (CM-1-2-1-1-4) | credit and risk limit setting, overrides, and exceptions (CM-1-2-2-1, CM-1-2-2-3) | the approval decision (CM-1-2-1-3-2)</t>
+        </is>
+      </c>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>Pre-Deal Analysis</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Batch 08 (2026-09-19). Pre-check versus formal clearance distinction added at Hamid's direction: analysis informs, it never clears an exception. Operational feasibility applies to physical, capacity, transportation, storage, and structured trades — not asserted for every financial derivative. Closes the batch 07 follow-up loop: asset-optimization recommendations enter execution through this analysis and the approval sibling. APQC 20102 is an unrelated claims candidate.</t>
+        </is>
+      </c>
+      <c r="U93" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V93" s="5" t="inlineStr">
+        <is>
+          <t>Ensure the economics, authority, credit exposure, risk-limit headroom, operational feasibility, and reporting implications of a specific prospective trade are understood before execution.</t>
+        </is>
+      </c>
+      <c r="W93" s="5" t="inlineStr">
+        <is>
+          <t>SRC-CFTC-GLOSS-001</t>
+        </is>
+      </c>
       <c r="X93" s="5" t="n"/>
-      <c r="Y93" s="5" t="n"/>
-      <c r="Z93" s="5" t="n"/>
-      <c r="AA93" s="5" t="n"/>
-      <c r="AB93" s="5" t="n"/>
-      <c r="AC93" s="5" t="n"/>
+      <c r="Y93" s="5" t="inlineStr">
+        <is>
+          <t>prospective deal terms | asset-optimization recommendations | credit and limit headroom | market prices</t>
+        </is>
+      </c>
+      <c r="Z93" s="5" t="inlineStr">
+        <is>
+          <t>pre-trade analysis supporting the approval decision</t>
+        </is>
+      </c>
+      <c r="AA93" s="5" t="inlineStr">
+        <is>
+          <t>uses-input: Perform Asset Optimization | precedes: Obtain Trade Approval</t>
+        </is>
+      </c>
+      <c r="AB93" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC93" s="5" t="inlineStr">
+        <is>
+          <t>event-driven</t>
+        </is>
+      </c>
       <c r="AD93" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -12473,18 +12597,80 @@
           <t>strong APQC candidate but no validator agreed</t>
         </is>
       </c>
-      <c r="U94" s="5" t="n"/>
-      <c r="V94" s="5" t="n"/>
-      <c r="W94" s="5" t="n"/>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>Secure the approvals a trade requires before execution — verifying the trader's authority under the delegation of authority, escalating deals beyond that authority, and documenting each approval — so every executed trade is traceably authorized.</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>Covers the pre-execution authorization step: checking the deal against the trader's delegated authority, routing above-authority and non-standard deals (including structured deals) for escalated approval, and recording who approved what. Includes escalation and documented approval, rejection, or conditional approval of trades that exceed delegated authority, approach or breach a limit, are non-standard, or require a documented risk or compliance exception; it does not itself set, waive, or permanently amend risk limits, credit limits, or delegation-of-authority policy. The delegation of authority is set and maintained by Market Risk Management (Establish &amp; Maintain Delegation Of Authority, CM-1-2-2-3-2); this process applies it. Excludes strategy approval, owned by Trading Strategy Management (CM-1-2-1-4); excludes post-trade compliance monitoring (Regulatory &amp; Compliance, CM-1-2-4-3).</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Verify trader authority against the delegation of authority | route above-authority, near-limit, and non-standard deals for escalated approval | approve, reject, or conditionally approve under the documented escalation procedure | document approvals traceably and block unapproved execution</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>Setting, waiving, or amending limits and delegation-of-authority policy (CM-1-2-2-3-2, CM-1-2-2-3-6) | strategy approval (CM-1-2-1-4) | compliance monitoring (CM-1-2-4-3)</t>
+        </is>
+      </c>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>Trade Authorization</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Batch 08 (2026-09-19). Escalation wording added at Hamid's direction: exceptions may be approved under the formal escalation procedure, but this process never owns authority-policy design — applying versus setting the delegation of authority is the front-office/middle-office split. Structured deals route here for escalated approval per CM-1-2-1-3-8. APQC 20074 STRONG with no validator; generic approval candidate, comparative evidence only.</t>
+        </is>
+      </c>
+      <c r="U94" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V94" s="5" t="inlineStr">
+        <is>
+          <t>No trade executes without traceable authority.</t>
+        </is>
+      </c>
+      <c r="W94" s="5" t="inlineStr">
+        <is>
+          <t>SRC-CFTC-GLOSS-001</t>
+        </is>
+      </c>
       <c r="X94" s="5" t="n"/>
-      <c r="Y94" s="5" t="n"/>
-      <c r="Z94" s="5" t="n"/>
-      <c r="AA94" s="5" t="n"/>
-      <c r="AB94" s="5" t="n"/>
-      <c r="AC94" s="5" t="n"/>
+      <c r="Y94" s="5" t="inlineStr">
+        <is>
+          <t>pre-trade analysis | delegation of authority | deal terms</t>
+        </is>
+      </c>
+      <c r="Z94" s="5" t="inlineStr">
+        <is>
+          <t>documented trade approvals, rejections, and conditions</t>
+        </is>
+      </c>
+      <c r="AA94" s="5" t="inlineStr">
+        <is>
+          <t>follows: Manage Pre-Trade Analysis | governed-by: Market Risk Management | precedes: Capture Physical Trades</t>
+        </is>
+      </c>
+      <c r="AB94" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC94" s="5" t="inlineStr">
+        <is>
+          <t>event-driven</t>
+        </is>
+      </c>
       <c r="AD94" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -12547,18 +12733,80 @@
           <t>no meaningful APQC candidate</t>
         </is>
       </c>
-      <c r="U95" s="5" t="n"/>
-      <c r="V95" s="5" t="n"/>
-      <c r="W95" s="5" t="n"/>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>Record executed physical purchases and sales of crude, feedstocks, and products completely and promptly — counterparty, product and quality, quantity, price and pricing basis, delivery terms, location, period, and title-transfer terms — linked to book and strategy, so the trade record is available to confirmation, risk, actualization, and settlement.</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>Covers deal entry and validation for physical commodity transactions: capturing full commercial terms including delivery basis and title-transfer terms, validating against execution evidence, linking to book, strategy, and contract, and correcting capture errors. Excludes negotiating or deciding the trade (strategy processes and the authorized execution role); excludes confirmation with the counterparty (CM-1-2-2-2); excludes movement actualization (CM-1-2-3-1) and settlement (CM-1-2-4-1-1, CM-1-2-4-1-2); excludes product exchange agreements, administered under Manage Product Exchange Agreements (CM-1-2-7-1-1).</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Capture full commercial terms of executed physical deals, including delivery and title-transfer terms | validate against execution evidence | link deals to book, strategy, and contract | correct capture errors</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>Trade negotiation and execution (strategy processes, authorized execution role) | confirmation (CM-1-2-2-2) | actualization and settlement (CM-1-2-3-1, CM-1-2-4-1) | product exchange agreement administration (CM-1-2-7-1-1)</t>
+        </is>
+      </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>Physical Deal Entry</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Batch 08 (2026-09-19). First of the eight deal-type capture variants; each shares the capture discipline and differs by instrument terms. Title-transfer, delivery-point, and quality terms retained per Hamid's review — they drive actualization, invoicing, tax, and settlement downstream. APQC: no meaningful candidate.</t>
+        </is>
+      </c>
+      <c r="U95" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V95" s="5" t="inlineStr">
+        <is>
+          <t>One accurate record per physical deal, immediately after execution.</t>
+        </is>
+      </c>
+      <c r="W95" s="5" t="inlineStr">
+        <is>
+          <t>SRC-CFTC-GLOSS-001 | SRC-EIA-GLOSS-001</t>
+        </is>
+      </c>
       <c r="X95" s="5" t="n"/>
-      <c r="Y95" s="5" t="n"/>
-      <c r="Z95" s="5" t="n"/>
-      <c r="AA95" s="5" t="n"/>
-      <c r="AB95" s="5" t="n"/>
-      <c r="AC95" s="5" t="n"/>
+      <c r="Y95" s="5" t="inlineStr">
+        <is>
+          <t>executed deal terms | execution evidence | book and strategy assignments</t>
+        </is>
+      </c>
+      <c r="Z95" s="5" t="inlineStr">
+        <is>
+          <t>validated physical deal records</t>
+        </is>
+      </c>
+      <c r="AA95" s="5" t="inlineStr">
+        <is>
+          <t>follows: Obtain Trade Approval | precedes: Confirmations Management | enables: Actualizations</t>
+        </is>
+      </c>
+      <c r="AB95" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC95" s="5" t="inlineStr">
+        <is>
+          <t>event-driven</t>
+        </is>
+      </c>
       <c r="AD95" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -12626,18 +12874,80 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U96" s="5" t="n"/>
-      <c r="V96" s="5" t="n"/>
-      <c r="W96" s="5" t="n"/>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>Record exchange-executed futures and listed-options trades with contract, delivery month, quantity, price, account, clearing-broker, and allocation details; validate captured execution data against available execution and broker messages; and resolve trade-capture exceptions so the trading record reflects the executed cleared position.</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>Covers capture of exchange-executed, cleared instruments: deal entry from execution records, allocation to books and strategies, validation against execution and broker messages, and resolution of capture exceptions. 'Exchange' here means executed on a futures exchange and cleared — not product exchange agreements, which are administered under Manage Product Exchange Agreements (CM-1-2-7-1-1) and Manage Refined Product Exchanges (CM-1-2-6-2-2). Excludes independent broker, clearing, and exchange reconciliation controls where those are performed by the middle office, risk, finance operations, or another designated control function; excludes margining and collateral, owned by Credit Risk Management (Perform Margining, CM-1-2-2-1-5); excludes broker settlement (Settle Broker, CM-1-2-4-1-16) and exchange-trade settlement (CM-1-2-4-1-3).</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Capture exchange-executed trades with contract and clearing detail | allocate to books and strategies | validate captured data against execution and broker messages | resolve trade-capture exceptions</t>
+        </is>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>Independent broker, clearing, and exchange reconciliation controls (designated control function) | product exchange agreements (CM-1-2-7-1-1, CM-1-2-6-2-2) | margining and collateral (CM-1-2-2-1-5) | broker and exchange settlement (CM-1-2-4-1-16, CM-1-2-4-1-3)</t>
+        </is>
+      </c>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>Exchange-Traded Deal Capture | Futures Trade Capture</t>
+        </is>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Batch 08 (2026-09-19). Reworded at Hamid's direction to separate capture validation from independent reconciliation controls: this process resolves its own execution and capture breaks; the independent broker/clearing reconciliation control is owned by a designated control function, whose identity is an open follow-up noted in the batch 08 PR. 'Exchange' disambiguated: exchange-executed cleared instruments, corroborated by the Settle Exchange Trades and Settle Broker siblings; barrel exchanges live in the products branches. APQC 19582 is foreign-exchange trading; false lexical match, comparative evidence only.</t>
+        </is>
+      </c>
+      <c r="U96" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V96" s="5" t="inlineStr">
+        <is>
+          <t>The trading record reflects the executed cleared position, exception by exception.</t>
+        </is>
+      </c>
+      <c r="W96" s="5" t="inlineStr">
+        <is>
+          <t>SRC-CFTC-GLOSS-001</t>
+        </is>
+      </c>
       <c r="X96" s="5" t="n"/>
-      <c r="Y96" s="5" t="n"/>
-      <c r="Z96" s="5" t="n"/>
-      <c r="AA96" s="5" t="n"/>
-      <c r="AB96" s="5" t="n"/>
-      <c r="AC96" s="5" t="n"/>
+      <c r="Y96" s="5" t="inlineStr">
+        <is>
+          <t>execution records and broker messages | account and book mappings</t>
+        </is>
+      </c>
+      <c r="Z96" s="5" t="inlineStr">
+        <is>
+          <t>captured, exception-resolved exchange trade records</t>
+        </is>
+      </c>
+      <c r="AA96" s="5" t="inlineStr">
+        <is>
+          <t>follows: Obtain Trade Approval | enables: Perform Margining | precedes: Settle Exchange Trades</t>
+        </is>
+      </c>
+      <c r="AB96" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC96" s="5" t="inlineStr">
+        <is>
+          <t>event-driven</t>
+        </is>
+      </c>
       <c r="AD96" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -12705,18 +13015,80 @@
           <t>no meaningful APQC candidate</t>
         </is>
       </c>
-      <c r="U97" s="5" t="n"/>
-      <c r="V97" s="5" t="n"/>
-      <c r="W97" s="5" t="n"/>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>Record executed storage and throughput deals — facility, capacity, injection and withdrawal rights, fees, and period — so capacity positions, obligations, and costs are represented in the trading system from execution onward.</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>Covers deal entry for storage capacity transactions: leased tankage and cavern capacity, throughput commitments, and capacity resale, with their rights, fee structures, and periods. The negotiation of storage and throughput agreements is owned by Negotiate Storage / Throughput Agreements (CM-1-2-7-1-3); this node captures the executed deal into the trading record. Excludes storage inventory administration (Manage Third Party Storage, CM-1-1-3-7-11); excludes storage settlement (Settle Terminal/Storage, CM-1-2-4-1-14).</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Capture storage and throughput deal terms | represent capacity rights, obligations, and fees | link deals to books and strategies | correct capture errors</t>
+        </is>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>Agreement negotiation (CM-1-2-7-1-3) | third-party storage inventory administration (CM-1-1-3-7-11) | storage settlement (CM-1-2-4-1-14)</t>
+        </is>
+      </c>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>Storage Capacity Deal Capture</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Batch 08 (2026-09-19). Negotiate-versus-capture split with CM-1-2-7-1-3 mirrors the established decide-versus-record pattern. APQC: no meaningful candidate.</t>
+        </is>
+      </c>
+      <c r="U97" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V97" s="5" t="inlineStr">
+        <is>
+          <t>Capacity deals exist in the book the moment they exist in the market.</t>
+        </is>
+      </c>
+      <c r="W97" s="5" t="inlineStr">
+        <is>
+          <t>SRC-CFTC-GLOSS-001</t>
+        </is>
+      </c>
       <c r="X97" s="5" t="n"/>
-      <c r="Y97" s="5" t="n"/>
-      <c r="Z97" s="5" t="n"/>
-      <c r="AA97" s="5" t="n"/>
-      <c r="AB97" s="5" t="n"/>
-      <c r="AC97" s="5" t="n"/>
+      <c r="Y97" s="5" t="inlineStr">
+        <is>
+          <t>executed storage deal terms | facility and capacity references</t>
+        </is>
+      </c>
+      <c r="Z97" s="5" t="inlineStr">
+        <is>
+          <t>captured storage deal records</t>
+        </is>
+      </c>
+      <c r="AA97" s="5" t="inlineStr">
+        <is>
+          <t>follows: Obtain Trade Approval | enables: Manage Third Party Storage | precedes: Settle Terminal/Storage</t>
+        </is>
+      </c>
+      <c r="AB97" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC97" s="5" t="inlineStr">
+        <is>
+          <t>event-driven</t>
+        </is>
+      </c>
       <c r="AD97" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -12784,18 +13156,80 @@
           <t>no meaningful APQC candidate</t>
         </is>
       </c>
-      <c r="U98" s="5" t="n"/>
-      <c r="V98" s="5" t="n"/>
-      <c r="W98" s="5" t="n"/>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>Record executed purchases, sales, and transfers of program-specific environmental instruments — such as RINs, RECs, and emissions allowances — with program, vintage, quantity, price, and compliance-period detail, so instrument positions are accurate from execution onward.</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>Covers deal entry for environmental and renewable instruments, treating each as program-specific per the batch 07 decision: capturing program, instrument type, vintage, and compliance-period attributes alongside commercial terms. Excludes forecasting the position (Forecast Renewables, CM-1-2-1-1-3); excludes instrument actualization (Perform RINs/REC Actualization, CM-1-2-3-1-7); excludes emissions settlement (Settle Emissions, CM-1-2-4-1-8); excludes regulatory filing (EHS &amp; Government Reporting, locked rule) and the allowance-position economics (Manage and Support Emission Trading, CM-1-1-7-3-3). Program applicability is jurisdiction-specific.</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Capture environmental and renewable deal terms with program, vintage, and period attributes | link deals to compliance positions, books, and strategies | validate against execution evidence | correct capture errors</t>
+        </is>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>Position forecasting (CM-1-2-1-1-3) | instrument actualization (CM-1-2-3-1-7) | settlement (CM-1-2-4-1-8) | regulatory filing (EHS &amp; Government Reporting) | allowance-position economics (CM-1-1-7-3-3)</t>
+        </is>
+      </c>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>Environmental Instrument Deal Capture</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Batch 08 (2026-09-19). Program-specific instrument treatment per the batch 07 Forecast Renewables decision; the in-scope instrument set remains the open follow-up recorded there. Jurisdiction-specific applicability per the EPA source limitations. APQC: no meaningful candidate.</t>
+        </is>
+      </c>
+      <c r="U98" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V98" s="5" t="inlineStr">
+        <is>
+          <t>Every credit bought, sold, or transferred is on the book with its program identity intact.</t>
+        </is>
+      </c>
+      <c r="W98" s="5" t="inlineStr">
+        <is>
+          <t>SRC-EPA-RFS-001 | SRC-EPA-EMTR-001</t>
+        </is>
+      </c>
       <c r="X98" s="5" t="n"/>
-      <c r="Y98" s="5" t="n"/>
-      <c r="Z98" s="5" t="n"/>
-      <c r="AA98" s="5" t="n"/>
-      <c r="AB98" s="5" t="n"/>
-      <c r="AC98" s="5" t="n"/>
+      <c r="Y98" s="5" t="inlineStr">
+        <is>
+          <t>executed instrument deal terms | program and vintage references | compliance-period calendars</t>
+        </is>
+      </c>
+      <c r="Z98" s="5" t="inlineStr">
+        <is>
+          <t>captured environmental instrument deal records</t>
+        </is>
+      </c>
+      <c r="AA98" s="5" t="inlineStr">
+        <is>
+          <t>follows: Obtain Trade Approval | informed-by: Forecast Renewables | precedes: Perform RINs/REC Actualization</t>
+        </is>
+      </c>
+      <c r="AB98" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC98" s="5" t="inlineStr">
+        <is>
+          <t>event-driven</t>
+        </is>
+      </c>
       <c r="AD98" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -12863,18 +13297,80 @@
           <t>no meaningful APQC candidate</t>
         </is>
       </c>
-      <c r="U99" s="5" t="n"/>
-      <c r="V99" s="5" t="n"/>
-      <c r="W99" s="5" t="n"/>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>Record executed over-the-counter derivative trades — swaps, options, and other bilateral instruments, with underlying index, fixed and floating terms, notional quantity, tenor, and counterparty — flagging reportable transactions, so financial positions and obligations are accurate from execution onward.</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>Covers deal entry for bilateral financial instruments: full instrument terms, index and pricing references, and the regulatory attributes that determine reportability under applicable trade-reporting regimes. Excludes trade reporting submission itself (Report Trades to SDR, CM-1-2-1-3-10); excludes confirmation (CM-1-2-2-2); excludes valuation and curves (Market Risk Management: Setup And Manage Curves, CM-1-2-2-3-3; Manage Commodity Valuations, CM-1-2-2-3-15); excludes OTC settlement (Settle Financial OTC Trades, CM-1-2-4-1-11).</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Capture OTC instrument terms and references | flag reportable transactions and their attributes | link deals to books, strategies, and master agreements | correct capture errors</t>
+        </is>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>Regulatory reporting submission (CM-1-2-1-3-10) | confirmation (CM-1-2-2-2) | valuation and curve management (CM-1-2-2-3) | OTC settlement (CM-1-2-4-1-11)</t>
+        </is>
+      </c>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>OTC Derivatives Capture | Swap Trade Capture</t>
+        </is>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Batch 08 (2026-09-19). Reportability flagging here, submission at CM-1-2-1-3-10 — under US CFTC rules the capture data drives creation-data reporting; other regimes apply their own rules. Swap terminology per the CFTC glossary. APQC: no meaningful candidate.</t>
+        </is>
+      </c>
+      <c r="U99" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V99" s="5" t="inlineStr">
+        <is>
+          <t>Bilateral derivatives are on the book with the attributes regulation and risk need.</t>
+        </is>
+      </c>
+      <c r="W99" s="5" t="inlineStr">
+        <is>
+          <t>SRC-CFTC-GLOSS-001 | SRC-CFTC-P45-001</t>
+        </is>
+      </c>
       <c r="X99" s="5" t="n"/>
-      <c r="Y99" s="5" t="n"/>
-      <c r="Z99" s="5" t="n"/>
-      <c r="AA99" s="5" t="n"/>
-      <c r="AB99" s="5" t="n"/>
-      <c r="AC99" s="5" t="n"/>
+      <c r="Y99" s="5" t="inlineStr">
+        <is>
+          <t>executed OTC terms | index and reference data | master agreement links</t>
+        </is>
+      </c>
+      <c r="Z99" s="5" t="inlineStr">
+        <is>
+          <t>captured OTC deal records with reporting attributes</t>
+        </is>
+      </c>
+      <c r="AA99" s="5" t="inlineStr">
+        <is>
+          <t>follows: Obtain Trade Approval | precedes: Report Trades to SDR | precedes: Confirmations Management</t>
+        </is>
+      </c>
+      <c r="AB99" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC99" s="5" t="inlineStr">
+        <is>
+          <t>event-driven</t>
+        </is>
+      </c>
       <c r="AD99" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -12942,18 +13438,80 @@
           <t>no meaningful APQC candidate</t>
         </is>
       </c>
-      <c r="U100" s="5" t="n"/>
-      <c r="V100" s="5" t="n"/>
-      <c r="W100" s="5" t="n"/>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>Record executed structured and non-standard transactions — multi-leg, embedded-optionality, tolling, prepay, and similar bespoke deals — decomposing them into capturable components so their positions, risks, and obligations are fully represented rather than approximated.</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>Covers the specialized capture of deals that do not fit standard templates: decomposing the transaction into legs and components the systems can represent, verifying the representation reproduces the deal's economics and risks, and coordinating with the designated valuation, risk, legal, accounting, and operations stakeholders as required to ensure the captured representation is complete, controllable, and suitable for downstream valuation, confirmation, accounting, and settlement. Structured deals route through escalated approval (Obtain Trade Approval, CM-1-2-1-3-2) before execution. Excludes structuring and negotiating the deal (strategy and origination); excludes independent valuation methodology, model validation, and valuation-control approval, owned by the designated valuation and control functions (Market Risk Management for valuation methodology, CM-1-2-2-3-15); excludes each component's downstream confirmation and settlement, which follow their instrument types (Confirmations Management, CM-1-2-2-2; Settlements, CM-1-2-4-1).</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Decompose structured deals into capturable components | verify the representation reproduces deal economics and risk | coordinate with designated valuation, risk, legal, accounting, and operations stakeholders | correct representation errors</t>
+        </is>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>Deal structuring and negotiation (strategy, origination) | independent valuation methodology, model validation, and valuation-control approval (designated valuation and control functions; CM-1-2-2-3-15) | component confirmation and settlement per instrument type (Confirmations Management, CM-1-2-2-2; Settlements, CM-1-2-4-1)</t>
+        </is>
+      </c>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>Structured Transaction Capture</t>
+        </is>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Batch 08 (2026-09-19). Coordination widened at Hamid's direction to the designated valuation, risk, legal, accounting, and operations stakeholders — independent validation and accounting treatment are not assumed identical to Market Risk ownership; which reviewers are mandatory is a follow-up noted in the batch 08 PR. The representation-fidelity duty is the distinguishing purpose: a structured deal captured as the wrong legs is a silent risk error. APQC: no meaningful candidate.</t>
+        </is>
+      </c>
+      <c r="U100" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V100" s="5" t="inlineStr">
+        <is>
+          <t>Bespoke deals are represented whole, not approximated.</t>
+        </is>
+      </c>
+      <c r="W100" s="5" t="inlineStr">
+        <is>
+          <t>SRC-CFTC-GLOSS-001</t>
+        </is>
+      </c>
       <c r="X100" s="5" t="n"/>
-      <c r="Y100" s="5" t="n"/>
-      <c r="Z100" s="5" t="n"/>
-      <c r="AA100" s="5" t="n"/>
-      <c r="AB100" s="5" t="n"/>
-      <c r="AC100" s="5" t="n"/>
+      <c r="Y100" s="5" t="inlineStr">
+        <is>
+          <t>executed structured deal terms | component and leg templates | stakeholder representation requirements</t>
+        </is>
+      </c>
+      <c r="Z100" s="5" t="inlineStr">
+        <is>
+          <t>decomposed, verified structured deal records</t>
+        </is>
+      </c>
+      <c r="AA100" s="5" t="inlineStr">
+        <is>
+          <t>follows: Obtain Trade Approval | requires: Manage Commodity Valuations | precedes: Confirmations Management</t>
+        </is>
+      </c>
+      <c r="AB100" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC100" s="5" t="inlineStr">
+        <is>
+          <t>event-driven</t>
+        </is>
+      </c>
       <c r="AD100" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -13021,18 +13579,80 @@
           <t>no meaningful APQC candidate</t>
         </is>
       </c>
-      <c r="U101" s="5" t="n"/>
-      <c r="V101" s="5" t="n"/>
-      <c r="W101" s="5" t="n"/>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>Record executed transportation capacity deals — pipeline capacity, vessel charters, railcar commitments, and trucking capacity, with route or path, capacity, period, and rates — so transport positions, obligations, and costs are represented from execution onward.</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>Covers deal entry for transportation capacity transactions across modes, including capacity acquired, released, or resold. The ongoing administration of carrier relationships and contracts is owned by Manage Carrier Contracts (CM-1-2-1-2-9) and Manage Product Transport Agreements (CM-1-2-7-1-2); nominations that use the captured capacity are owned by Plan &amp; Execute Nominations (CM-1-1-3-6-1); transport settlement follows the mode-specific settlement nodes (CM-1-2-4-1-12/-13/-4/-5); physical transport operation is owned by Midstream and carriers.</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Capture transportation capacity deal terms by mode | represent capacity rights, obligations, and rates | link deals to books and strategies | correct capture errors</t>
+        </is>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>Carrier contract administration (CM-1-2-1-2-9, CM-1-2-7-1-2) | nominations and capacity use (CM-1-1-3-6-1) | mode-specific settlement (CM-1-2-4-1) | physical transport operation (Midstream, carriers)</t>
+        </is>
+      </c>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>Transport Capacity Deal Capture</t>
+        </is>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Batch 08 (2026-09-19). Deal capture here; contract lifecycle at Contract Management; usage at nominations; settlement at the mode-specific settlement nodes — a durable taxonomy rule per Hamid's review. APQC: no meaningful candidate.</t>
+        </is>
+      </c>
+      <c r="U101" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V101" s="5" t="inlineStr">
+        <is>
+          <t>Transport capacity is on the book the moment it is committed.</t>
+        </is>
+      </c>
+      <c r="W101" s="5" t="inlineStr">
+        <is>
+          <t>SRC-CFTC-GLOSS-001 | SRC-DOE-RPPL-001</t>
+        </is>
+      </c>
       <c r="X101" s="5" t="n"/>
-      <c r="Y101" s="5" t="n"/>
-      <c r="Z101" s="5" t="n"/>
-      <c r="AA101" s="5" t="n"/>
-      <c r="AB101" s="5" t="n"/>
-      <c r="AC101" s="5" t="n"/>
+      <c r="Y101" s="5" t="inlineStr">
+        <is>
+          <t>executed transport deal terms | route, path, and mode references | rate structures</t>
+        </is>
+      </c>
+      <c r="Z101" s="5" t="inlineStr">
+        <is>
+          <t>captured transportation deal records</t>
+        </is>
+      </c>
+      <c r="AA101" s="5" t="inlineStr">
+        <is>
+          <t>follows: Obtain Trade Approval | enables: Plan &amp; Execute Nominations | precedes: Settle Pipelines</t>
+        </is>
+      </c>
+      <c r="AB101" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC101" s="5" t="inlineStr">
+        <is>
+          <t>event-driven</t>
+        </is>
+      </c>
       <c r="AD101" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -13100,18 +13720,80 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U102" s="5" t="n"/>
-      <c r="V102" s="5" t="n"/>
-      <c r="W102" s="5" t="n"/>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>Determine whether an executed swap or other transaction is reportable under an applicable trade-reporting regime and, where the organization is the reporting counterparty or has delegated reporting responsibility, submit required creation data to the designated registered swap data repository within applicable deadlines; correct errors and retain required reporting evidence.</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>Covers reportability determination, creation-data submission, corrections, resubmissions, acknowledgements, and evidence retention under applicable regimes. Under US CFTC Part 45, this includes creation-data reporting as defined by the applicable rule. Confirmation-event and continuation reporting may be handled by Report Confirmation To SDR (CM-1-2-2-2-4) where the reporting model and regulation require it. Excludes regulatory-policy ownership and monitoring, which belong to Regulatory &amp; Compliance (CM-1-2-4-3); excludes the legal determination of reporting responsibility where Legal/Compliance retains that authority; excludes regimes, jurisdictions, instruments, and reporting events not applicable to the organization.</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Determine reportability under applicable regimes | submit required creation data within deadlines where the organization holds reporting responsibility | correct, resubmit, and track acknowledgements | retain required reporting evidence</t>
+        </is>
+      </c>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>Regulatory-policy ownership and compliance monitoring (CM-1-2-4-3) | legal determination of reporting responsibility (Legal/Compliance) | confirmation-event and continuation reporting (CM-1-2-2-2-4) | non-applicable regimes, instruments, and events</t>
+        </is>
+      </c>
+      <c r="R102" t="inlineStr">
+        <is>
+          <t>Swap Data Reporting (Creation Data) | Trade Regulatory Reporting</t>
+        </is>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Batch 08 (2026-09-19). Scoped at Hamid's direction to applicable regimes and assigned reporting responsibility — CFTC Part 45 is US-specific evidence for the creation-data versus continuation-data distinction (17 CFR 45.3 versus 45.4), which is the boundary with CM-1-2-2-2-4, recorded so the Confirmations batch inherits it; it does not make every trade, entity, or jurisdiction reportable. Which entity is the reporting counterparty or delegated reporter per regime is a follow-up noted in the batch 08 PR. APQC 11175 is an unrelated profitability candidate.</t>
+        </is>
+      </c>
+      <c r="U102" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V102" s="5" t="inlineStr">
+        <is>
+          <t>Every reportable trade the organization must report reaches the repository on time, once, correctly.</t>
+        </is>
+      </c>
+      <c r="W102" s="5" t="inlineStr">
+        <is>
+          <t>SRC-CFTC-P45-001 | SRC-CFTC-GLOSS-001</t>
+        </is>
+      </c>
       <c r="X102" s="5" t="n"/>
-      <c r="Y102" s="5" t="n"/>
-      <c r="Z102" s="5" t="n"/>
-      <c r="AA102" s="5" t="n"/>
-      <c r="AB102" s="5" t="n"/>
-      <c r="AC102" s="5" t="n"/>
+      <c r="Y102" s="5" t="inlineStr">
+        <is>
+          <t>captured deals with reporting attributes | applicable reporting rules and deadlines | repository specifications</t>
+        </is>
+      </c>
+      <c r="Z102" s="5" t="inlineStr">
+        <is>
+          <t>submitted, evidenced creation-data reports under applicable regimes</t>
+        </is>
+      </c>
+      <c r="AA102" s="5" t="inlineStr">
+        <is>
+          <t>follows: Capture Financial (OTC) Trades | precedes: Report Confirmation To SDR | governed-by: Regulatory &amp; Compliance</t>
+        </is>
+      </c>
+      <c r="AB102" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC102" s="5" t="inlineStr">
+        <is>
+          <t>event-driven</t>
+        </is>
+      </c>
       <c r="AD102" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -13179,18 +13861,80 @@
           <t>no meaningful APQC candidate</t>
         </is>
       </c>
-      <c r="U103" s="5" t="n"/>
-      <c r="V103" s="5" t="n"/>
-      <c r="W103" s="5" t="n"/>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>Record executed power transmission deals — transmission service, capacity, and congestion-related rights, with path, quantity, period, and charges — so transmission positions and obligations are represented from execution onward.</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>Covers deal entry for power transmission transactions supporting the power side of the portfolio, consistent with the power nodes elsewhere in the branch (Receive Power Generation Forecast, CM-1-2-1-1-6; Settle Power, CM-1-2-4-1-15; Settle ISO/Power Pools, CM-1-2-4-1-7). Excludes physical transmission scheduling and grid/system operations, owned by the relevant system authorities; excludes power and ISO settlement (CM-1-2-4-1-15, CM-1-2-4-1-7).</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Capture transmission deal terms with path, period, and charges | represent transmission rights and obligations | link deals to books and strategies | correct capture errors</t>
+        </is>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>Transmission scheduling and grid/system operations (system authorities) | power and ISO settlement (CM-1-2-4-1-15, CM-1-2-4-1-7)</t>
+        </is>
+      </c>
+      <c r="R103" t="inlineStr">
+        <is>
+          <t>Power Transmission Deal Capture</t>
+        </is>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Batch 08 (2026-09-19). The dispatch/grid-operations exclusion follows the batch 07 wording on CM-1-2-1-1-6. APQC: no meaningful candidate.</t>
+        </is>
+      </c>
+      <c r="U103" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V103" s="5" t="inlineStr">
+        <is>
+          <t>Transmission rights are on the book with their path and period intact.</t>
+        </is>
+      </c>
+      <c r="W103" s="5" t="inlineStr">
+        <is>
+          <t>SRC-CFTC-GLOSS-001</t>
+        </is>
+      </c>
       <c r="X103" s="5" t="n"/>
-      <c r="Y103" s="5" t="n"/>
-      <c r="Z103" s="5" t="n"/>
-      <c r="AA103" s="5" t="n"/>
-      <c r="AB103" s="5" t="n"/>
-      <c r="AC103" s="5" t="n"/>
+      <c r="Y103" s="5" t="inlineStr">
+        <is>
+          <t>executed transmission deal terms | path and period references | charge structures</t>
+        </is>
+      </c>
+      <c r="Z103" s="5" t="inlineStr">
+        <is>
+          <t>captured transmission deal records</t>
+        </is>
+      </c>
+      <c r="AA103" s="5" t="inlineStr">
+        <is>
+          <t>follows: Obtain Trade Approval | informed-by: Receive Power Generation Forecast | precedes: Settle Power</t>
+        </is>
+      </c>
+      <c r="AB103" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC103" s="5" t="inlineStr">
+        <is>
+          <t>event-driven</t>
+        </is>
+      </c>
       <c r="AD103" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -45507,7 +46251,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -45556,7 +46300,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
@@ -46680,6 +47423,53 @@
         </is>
       </c>
       <c r="I30" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>SRC-CFTC-P45-001</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>U.S. Commodity Futures Trading Commission</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>17 CFR Part 45 - Swap Data Recordkeeping and Reporting Requirements (creation data 45.3, continuation data 45.4); supporting interpretation: CFTC Part 45 fact sheet and 2020 amendment materials</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Current regulation; accessed 2026-09-19</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>17 CFR Part 45; https://www.cftc.gov/LawRegulation/DoddFrankAct/Rulemakings/DF_17_Recordkeeping/index.htm</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Regulatory</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Applies to US CFTC-regulated swap-data reporting. Supports terminology and the creation-data/continuation-data distinction only; does not establish that every trade, product, legal entity, or jurisdiction is reportable to an SDR or determine internal ownership of reporting controls. Evidence only, not text to copy.</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Trade-level versus confirmation-level reporting boundary (CM-1-2-1-3-10 versus CM-1-2-2-2-4)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
         <is>
           <t>active</t>
         </is>

--- a/business_architecture/ontology/build/output/step3c-definition-authoring-workbook.xlsx
+++ b/business_architecture/ontology/build/output/step3c-definition-authoring-workbook.xlsx
@@ -11372,18 +11372,80 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U80" s="5" t="n"/>
-      <c r="V80" s="5" t="n"/>
-      <c r="W80" s="5" t="n"/>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>Administer trading counterparties and commercial agreements through their lifecycle — onboarding and maintaining counterparty records; establishing, maintaining, terminating, and novating master agreements, standing agreements, and relevant transaction frameworks; managing specialized agreement types; and monitoring contractual obligations — so trading occurs with authorized counterparties under current, governed terms.</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>Covers the controlled lifecycle administration of trading counterparties (create, maintain, terminate or novate) and trading agreements (create, maintain, terminate or novate), the specialized administration of lease, carrier, and storage contracts, the counterparty and agreement consequences of merger-and-acquisition events, and contract monitoring. Accommodates physical contracts, master agreements such as ISDA-type frameworks, transaction confirmations governed by a master agreement, capacity and lease arrangements, and spot transactions governed by standard terms or market rules rather than a bespoke contract record. Excludes legal drafting, legal review, and legal-risk management, owned by Legal &amp; Corporate Communications under its locked rule; excludes credit reviews, limits, and collateral, owned by Credit Risk Management (CM-1-2-2-1); excludes commercial negotiation of agreements where a negotiating owner exists (for example Negotiate Storage / Throughput Agreements, CM-1-2-7-1-3); excludes deal capture (Trade Capture, CM-1-2-1-3) and deal-level confirmation (CM-1-2-2-2).</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Onboard, maintain, and terminate or novate counterparties | establish, maintain, and terminate or novate agreements and master agreements | administer lease, carrier, and storage contract specializations | handle M&amp;A consequences for counterparties and agreements | monitor contractual obligations</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>Legal services and legal-risk management (Legal &amp; Corporate Communications) | credit reviews, limits, and collateral (CM-1-2-2-1) | agreement negotiation where separately owned (CM-1-2-7-1) | deal capture and confirmation (CM-1-2-1-3, CM-1-2-2-2)</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>Counterparty &amp; Contract Administration</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Batch 09 (2026-09-19). Q1 decision (Hamid, Option A): process — lifecycle stages applied to two entity kinds plus type variants and control activities, per the batch 08 variant test. This taxonomy locates the commercial lifecycle-administration process under Trading Management; actual execution may involve Trading, Credit Risk, Regulatory &amp; Compliance, Legal, Finance Operations, or Shared Services according to the enterprise operating model. The negotiate, administer, capture, use/actualize/settle pattern from batch 08 is a taxonomy heuristic, not a universal sequential lifecycle: some agreements are frameworks rather than tradable deals, some deals execute under existing agreements, and some contractual rights are used without a separately captured transaction. APQC 20682 is an unrelated IT candidate.</t>
+        </is>
+      </c>
+      <c r="U80" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V80" s="5" t="inlineStr">
+        <is>
+          <t>Trading occurs with authorized counterparties under current, governed terms.</t>
+        </is>
+      </c>
+      <c r="W80" s="5" t="inlineStr">
+        <is>
+          <t>SRC-CFTC-GLOSS-001 | SRC-ISDA-MA-001</t>
+        </is>
+      </c>
       <c r="X80" s="5" t="n"/>
-      <c r="Y80" s="5" t="n"/>
-      <c r="Z80" s="5" t="n"/>
-      <c r="AA80" s="5" t="n"/>
-      <c r="AB80" s="5" t="n"/>
-      <c r="AC80" s="5" t="n"/>
+      <c r="Y80" s="5" t="inlineStr">
+        <is>
+          <t>counterparty applications and due-diligence results | negotiated agreement terms | corporate event notices | contract obligations and calendars</t>
+        </is>
+      </c>
+      <c r="Z80" s="5" t="inlineStr">
+        <is>
+          <t>governed counterparty and agreement records through their lifecycle</t>
+        </is>
+      </c>
+      <c r="AA80" s="5" t="inlineStr">
+        <is>
+          <t>enables: Trade Capture | enables: Confirmations Management | governed-by: Credit Risk Management</t>
+        </is>
+      </c>
+      <c r="AB80" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC80" s="5" t="inlineStr">
+        <is>
+          <t>continuous</t>
+        </is>
+      </c>
       <c r="AD80" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -11451,18 +11513,80 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U81" s="5" t="n"/>
-      <c r="V81" s="5" t="n"/>
-      <c r="W81" s="5" t="n"/>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>Coordinate onboarding of a prospective trading counterparty by collecting required legal-entity, tax, settlement, and commercial documentation; initiating and recording required compliance, sanctions/KYC, legal, and credit clearances through their accountable owners; and creating the authorized counterparty and settlement records once required approvals are complete.</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>Covers counterparty onboarding coordination: documentation collection and completeness validation, initiation and tracking of required clearances through their owning processes, setup of the counterparty record with settlement instructions and hierarchy links, and activation for trading once approvals are complete. Credit reviews and limits are owned by Perform Counterparty Credit Reviews (CM-1-2-2-1-1) and Manage Credit Limits (CM-1-2-2-1-2); compliance policy by Regulatory &amp; Compliance (CM-1-2-4-3); legal review by Legal &amp; Corporate Communications. Excludes independent KYC/sanctions determination, beneficial-owner due diligence, and regulatory-risk acceptance, which sit with the appropriate Regulatory &amp; Compliance or Legal process when its detailed taxonomy is authored. Excludes commercial customer master data, owned by Manage Master Data under Order Management (CM-1-3-7-1) — trading counterparty records live here.</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Collect and validate completeness of counterparty documentation | initiate and record required clearances through their accountable owners | create the counterparty record and settlement details once approvals complete | activate the counterparty for trading</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>Independent KYC/sanctions determination, beneficial-owner due diligence, and regulatory-risk acceptance (Regulatory &amp; Compliance / Legal) | credit reviews and limit setting (CM-1-2-2-1-1, CM-1-2-2-1-2) | legal review (Legal &amp; Corporate Communications) | commercial customer master data (CM-1-3-7-1)</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>Counterparty Onboarding</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Batch 09 (2026-09-19). Reworded at Hamid's direction to distinguish process coordination from independent verification: this process validates completeness and reconciles data; Compliance, Legal, and Credit retain independent decision rights. Which function operationally performs onboarding (Trading, middle office, Legal Operations, Compliance, Shared Services, or an MDM team) is a follow-up noted in the batch 09 PR. Trading counterparty records here versus commercial customer master data at CM-1-3-7-1 is the record boundary. APQC 10147 is an unrelated budget candidate.</t>
+        </is>
+      </c>
+      <c r="U81" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V81" s="5" t="inlineStr">
+        <is>
+          <t>No trading with an unverified or incompletely cleared counterparty.</t>
+        </is>
+      </c>
+      <c r="W81" s="5" t="inlineStr">
+        <is>
+          <t>SRC-CFTC-GLOSS-001</t>
+        </is>
+      </c>
       <c r="X81" s="5" t="n"/>
-      <c r="Y81" s="5" t="n"/>
-      <c r="Z81" s="5" t="n"/>
-      <c r="AA81" s="5" t="n"/>
-      <c r="AB81" s="5" t="n"/>
-      <c r="AC81" s="5" t="n"/>
+      <c r="Y81" s="5" t="inlineStr">
+        <is>
+          <t>counterparty applications and legal documentation | clearance outcomes from accountable owners | settlement instructions</t>
+        </is>
+      </c>
+      <c r="Z81" s="5" t="inlineStr">
+        <is>
+          <t>activated counterparty records with recorded clearances</t>
+        </is>
+      </c>
+      <c r="AA81" s="5" t="inlineStr">
+        <is>
+          <t>precedes: Create New Contract | requires: Perform Counterparty Credit Reviews</t>
+        </is>
+      </c>
+      <c r="AB81" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC81" s="5" t="inlineStr">
+        <is>
+          <t>event-driven</t>
+        </is>
+      </c>
       <c r="AD81" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -11530,18 +11654,80 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U82" s="5" t="n"/>
-      <c r="V82" s="5" t="n"/>
-      <c r="W82" s="5" t="n"/>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>Maintain active counterparty records through their life — processing changes to legal identity, ownership, settlement details, and documentation, keeping records synchronized with credit and compliance status, and periodically reconfirming record accuracy.</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>Covers ongoing counterparty record maintenance: change processing, periodic reconfirmation, documentation refresh, and synchronization with credit and compliance outcomes owned by their processes. Excludes the credit and compliance judgments themselves (CM-1-2-2-1, CM-1-2-4-3); excludes termination and novation, owned by Terminate/Novate Counterparty (CM-1-2-1-2-3); excludes M&amp;A-driven changes, owned by Manage M&amp;A Activity (CM-1-2-1-2-4).</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Process counterparty record changes | refresh documentation periodically | synchronize records with credit and compliance status | reconfirm record accuracy on a defined cadence</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>Credit and compliance judgments (CM-1-2-2-1, CM-1-2-4-3) | termination and novation (CM-1-2-1-2-3) | M&amp;A-driven changes (CM-1-2-1-2-4)</t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>Counterparty Record Maintenance</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Batch 09 (2026-09-19). APQC 11743 is an unrelated routing candidate.</t>
+        </is>
+      </c>
+      <c r="U82" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V82" s="5" t="inlineStr">
+        <is>
+          <t>Counterparty records stay true to the counterparty.</t>
+        </is>
+      </c>
+      <c r="W82" s="5" t="inlineStr">
+        <is>
+          <t>SRC-CFTC-GLOSS-001</t>
+        </is>
+      </c>
       <c r="X82" s="5" t="n"/>
-      <c r="Y82" s="5" t="n"/>
-      <c r="Z82" s="5" t="n"/>
-      <c r="AA82" s="5" t="n"/>
-      <c r="AB82" s="5" t="n"/>
-      <c r="AC82" s="5" t="n"/>
+      <c r="Y82" s="5" t="inlineStr">
+        <is>
+          <t>change notices and documentation | credit and compliance status updates</t>
+        </is>
+      </c>
+      <c r="Z82" s="5" t="inlineStr">
+        <is>
+          <t>current, reconfirmed counterparty records</t>
+        </is>
+      </c>
+      <c r="AA82" s="5" t="inlineStr">
+        <is>
+          <t>follows: Create New Counterparty | enables: Trade Capture</t>
+        </is>
+      </c>
+      <c r="AB82" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC82" s="5" t="inlineStr">
+        <is>
+          <t>continuous</t>
+        </is>
+      </c>
       <c r="AD82" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -11609,18 +11795,80 @@
           <t>no meaningful APQC candidate</t>
         </is>
       </c>
-      <c r="U83" s="5" t="n"/>
-      <c r="V83" s="5" t="n"/>
-      <c r="W83" s="5" t="n"/>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>Coordinate the administrative counterparty offboarding or transfer — confirming that affected positions, agreements, collateral, payment instructions, and reporting responsibilities have been closed, settled, transferred, or queued for legally effective novation — and deactivate or transition counterparty records with preserved history.</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>Covers controlled exit and transfer coordination: verifying no unresolved positions, obligations, disputes, or collateral remain or are queued for legally effective novation; coordinating consents, effective dates, and counterparty communication; and executing the administrative record transfer or deactivation with audit history. The legally effective novation is the legal event, executed through documents owned by Legal &amp; Corporate Communications; this process performs the administrative transfer of records once that event is effective. Collateral release is owned by Manage Collateral (CM-1-2-2-1-3); settlement of remaining obligations by the Settlements cluster (CM-1-2-4-1).</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Verify positions, agreements, collateral, and reporting responsibilities are closed, settled, transferred, or queued for legally effective novation | coordinate consents, effective dates, and communication | execute the administrative transfer or deactivation | preserve record history</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>Legal execution of novation and termination documents (Legal &amp; Corporate Communications) | collateral release (CM-1-2-2-1-3) | settlement of remaining obligations (CM-1-2-4-1)</t>
+        </is>
+      </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>Counterparty Offboarding &amp; Novation Administration</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Batch 09 (2026-09-19). Reworded at Hamid's direction: 'legally effective novation' names the legal event (Legal owns its documents); 'administrative transfer' names the operational record change this process owns — the two are never conflated. Novation terminology per the CFTC glossary; master-agreement close-out mechanics per ISDA documentation as reference evidence for applicable OTC frameworks. APQC: no meaningful candidate.</t>
+        </is>
+      </c>
+      <c r="U83" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V83" s="5" t="inlineStr">
+        <is>
+          <t>Counterparty exits leave nothing open and nothing lost.</t>
+        </is>
+      </c>
+      <c r="W83" s="5" t="inlineStr">
+        <is>
+          <t>SRC-CFTC-GLOSS-001 | SRC-ISDA-MA-001</t>
+        </is>
+      </c>
       <c r="X83" s="5" t="n"/>
-      <c r="Y83" s="5" t="n"/>
-      <c r="Z83" s="5" t="n"/>
-      <c r="AA83" s="5" t="n"/>
-      <c r="AB83" s="5" t="n"/>
-      <c r="AC83" s="5" t="n"/>
+      <c r="Y83" s="5" t="inlineStr">
+        <is>
+          <t>open position and obligation reports | novation consents and effective dates | master agreement terms</t>
+        </is>
+      </c>
+      <c r="Z83" s="5" t="inlineStr">
+        <is>
+          <t>cleanly transferred or deactivated counterparty records with preserved history</t>
+        </is>
+      </c>
+      <c r="AA83" s="5" t="inlineStr">
+        <is>
+          <t>follows: Manage Existing Counterparty | requires: Manage Collateral</t>
+        </is>
+      </c>
+      <c r="AB83" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC83" s="5" t="inlineStr">
+        <is>
+          <t>event-driven</t>
+        </is>
+      </c>
       <c r="AD83" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -11688,18 +11936,80 @@
           <t>FALSE MATCH (human gate): LSC 'Manage M&amp;A Activity' is mergers-and-acquisitions activity; APQC 'Monitor and manage IT activity risk' (20729) is IT risk management. Name similarity came from the shared tokens 'manage'/'activity'. Validator agrees with APQC, but the LSC→APQC link is invalid.</t>
         </is>
       </c>
-      <c r="U84" s="5" t="n"/>
-      <c r="V84" s="5" t="n"/>
-      <c r="W84" s="5" t="n"/>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>Administer the counterparty, agreement, trade-record, and obligation consequences of merger, acquisition, divestiture, restructuring, or legal-entity change events affecting either a trading counterparty or the company's own trading entities — coordinating, recording, and operationalizing the resulting novations, assignments, renamings, and record transfers once required legal documentation and approvals are complete.</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>Covers event-driven M&amp;A consequence administration in both directions: identifying affected counterparties, agreements, and open positions when a corporate event occurs; planning and coordinating the resulting legal-entity renames and identifier changes, counterparty-master updates, assignments, consent requests, novations, trade and portfolio transfers, and changes to payment, settlement, collateral, tax, and reporting entities; and verifying continuity of obligations throughout. Excludes corporate-development strategy, target identification, due diligence, valuation, transaction negotiation, financing, regulatory merger approval, and legal execution of transaction or novation documents; credit reassessment of surviving entities is owned by Credit Risk Management (CM-1-2-2-1); updates to delegated authority follow Market Risk Management (CM-1-2-2-3-2).</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Identify counterparties, agreements, and positions affected by a corporate event | plan and coordinate renames, assignments, novations, and transfers | operationalize record changes once legal documentation and approvals are complete | verify continuity of obligations, collateral, and reporting</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>Corporate-development strategy, diligence, valuation, negotiation, financing, and regulatory merger approval (outside the taxonomy) | legal execution of transaction and novation documents (Legal &amp; Corporate Communications) | credit reassessment (CM-1-2-2-1) | delegated-authority updates (CM-1-2-2-3-2)</t>
+        </is>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>M&amp;A Counterparty &amp; Contract Transition</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Batch 09 (2026-09-19). Q2 decision (Hamid, Option A): both directions — counterparty-side and company-side corporate events — because both land as the same administrative novation, assignment, and transfer work; restructuring and legal-entity changes included at Hamid's direction. The process coordinates, records, and operationalizes; it never executes legal documents. The Step 3b human gate already confirmed the mergers-and-acquisitions reading (APQC 20729 rejected as a false token match); authored consistent with that rejection.</t>
+        </is>
+      </c>
+      <c r="U84" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V84" s="5" t="inlineStr">
+        <is>
+          <t>Corporate events never leave a trade, agreement, or obligation pointing at the wrong entity.</t>
+        </is>
+      </c>
+      <c r="W84" s="5" t="inlineStr">
+        <is>
+          <t>SRC-CFTC-GLOSS-001 | SRC-ISDA-MA-001</t>
+        </is>
+      </c>
       <c r="X84" s="5" t="n"/>
-      <c r="Y84" s="5" t="n"/>
-      <c r="Z84" s="5" t="n"/>
-      <c r="AA84" s="5" t="n"/>
-      <c r="AB84" s="5" t="n"/>
-      <c r="AC84" s="5" t="n"/>
+      <c r="Y84" s="5" t="inlineStr">
+        <is>
+          <t>corporate event notices | affected counterparty and agreement inventories | novation and assignment consents | completed legal documentation</t>
+        </is>
+      </c>
+      <c r="Z84" s="5" t="inlineStr">
+        <is>
+          <t>completed administrative transitions with valid records and continuous obligations</t>
+        </is>
+      </c>
+      <c r="AA84" s="5" t="inlineStr">
+        <is>
+          <t>triggers: Terminate/Novate Counterparty | triggers: Terminate/Novate Contract</t>
+        </is>
+      </c>
+      <c r="AB84" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC84" s="5" t="inlineStr">
+        <is>
+          <t>event-driven</t>
+        </is>
+      </c>
       <c r="AD84" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -11767,18 +12077,80 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U85" s="5" t="n"/>
-      <c r="V85" s="5" t="n"/>
-      <c r="W85" s="5" t="n"/>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>Establish new trading agreements in the contract record — capturing negotiated terms, verifying required approvals and legal review are complete, linking the agreement to its counterparty and settlement basis, and activating it — so transactions governed by the agreement can be captured, confirmed, actualized, and settled against controlled terms.</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>Covers agreement establishment: recording master agreements (such as ISDA-type frameworks), general terms and conditions, and standing commercial contracts; verifying legal review and required approvals occurred with their owners; linking agreements to counterparty records; and activating them for use. Negotiation and legal drafting are owned by the commercial negotiating owner and Legal &amp; Corporate Communications; deal-level transactions under an agreement are captured by Trade Capture (CM-1-2-1-3) and confirmed by Confirmations Management (CM-1-2-2-2); pre-trade authorization of individual transactions is owned by Obtain Trade Approval (CM-1-2-1-3-2), not by contract activation.</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Record negotiated agreement and master agreement terms | verify legal review and approvals are complete | link agreements to counterparties and settlement basis | activate agreements for use</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>Commercial negotiation (negotiating owner) | legal drafting and review (Legal &amp; Corporate Communications) | deal capture under the agreement (CM-1-2-1-3) | pre-trade authorization of transactions (CM-1-2-1-3-2) | deal confirmation (CM-1-2-2-2)</t>
+        </is>
+      </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>Contract Establishment</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Batch 09 (2026-09-19). Purpose reworded at Hamid's direction to avoid an absolute gate: agreements required under enterprise policy must be recorded and approved before dependent transactions are processed, but spot-market, exchange-traded, and standing-terms transactions may be governed by standard terms or market rules rather than a bespoke contract record. Master-agreement structure (agreement, schedule, confirmations, credit support) per ISDA documentation as reference evidence for applicable OTC frameworks. APQC 10147 is an unrelated budget candidate.</t>
+        </is>
+      </c>
+      <c r="U85" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V85" s="5" t="inlineStr">
+        <is>
+          <t>Ensure agreements required for trading are recorded, approved, current, and linked to the appropriate counterparty before dependent transactions are captured or processed.</t>
+        </is>
+      </c>
+      <c r="W85" s="5" t="inlineStr">
+        <is>
+          <t>SRC-ISDA-MA-001 | SRC-CFTC-GLOSS-001</t>
+        </is>
+      </c>
       <c r="X85" s="5" t="n"/>
-      <c r="Y85" s="5" t="n"/>
-      <c r="Z85" s="5" t="n"/>
-      <c r="AA85" s="5" t="n"/>
-      <c r="AB85" s="5" t="n"/>
-      <c r="AC85" s="5" t="n"/>
+      <c r="Y85" s="5" t="inlineStr">
+        <is>
+          <t>negotiated terms | legal review outcomes | counterparty records</t>
+        </is>
+      </c>
+      <c r="Z85" s="5" t="inlineStr">
+        <is>
+          <t>activated, governed agreement records</t>
+        </is>
+      </c>
+      <c r="AA85" s="5" t="inlineStr">
+        <is>
+          <t>follows: Create New Counterparty | enables: Trade Capture</t>
+        </is>
+      </c>
+      <c r="AB85" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC85" s="5" t="inlineStr">
+        <is>
+          <t>event-driven</t>
+        </is>
+      </c>
       <c r="AD85" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -11846,18 +12218,80 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U86" s="5" t="n"/>
-      <c r="V86" s="5" t="n"/>
-      <c r="W86" s="5" t="n"/>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>Maintain active agreements through their life — processing approved amendments, extensions, and renewals, keeping recorded terms synchronized with what the parties have agreed, and managing agreement documentation and versions — so the contract record always reflects the operative agreement.</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>Covers ongoing agreement administration: amendment and renewal processing with required approvals, version and document control, term synchronization with trading and settlement systems, and administration of agreement-linked references. This process administers approved commercial and legal changes; it does not negotiate terms, draft legal amendments, or determine legal enforceability — the record is updated after commercial and legal agreement and approval, never independently. Excludes renegotiation of commercial terms (negotiating owner, with Legal &amp; Corporate Communications for legal changes); excludes termination and novation (CM-1-2-1-2-7); excludes obligation monitoring (Monitor Contracts, CM-1-2-1-2-11).</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Process approved amendments, extensions, and renewals | control agreement versions and documents | synchronize recorded terms with trading and settlement systems | administer agreement-linked references</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>Commercial renegotiation (negotiating owner) | legal drafting and enforceability determination (Legal &amp; Corporate Communications) | termination and novation (CM-1-2-1-2-7) | obligation monitoring (CM-1-2-1-2-11)</t>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>Contract Administration</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Batch 09 (2026-09-19). The administers-approved-changes sentence added at Hamid's direction: record updates follow agreement and approval; this process never independently changes terms. APQC 11743 is an unrelated routing candidate.</t>
+        </is>
+      </c>
+      <c r="U86" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V86" s="5" t="inlineStr">
+        <is>
+          <t>The contract record always reflects the operative agreement.</t>
+        </is>
+      </c>
+      <c r="W86" s="5" t="inlineStr">
+        <is>
+          <t>SRC-ISDA-MA-001</t>
+        </is>
+      </c>
       <c r="X86" s="5" t="n"/>
-      <c r="Y86" s="5" t="n"/>
-      <c r="Z86" s="5" t="n"/>
-      <c r="AA86" s="5" t="n"/>
-      <c r="AB86" s="5" t="n"/>
-      <c r="AC86" s="5" t="n"/>
+      <c r="Y86" s="5" t="inlineStr">
+        <is>
+          <t>approved amendment and renewal requests | approval outcomes | agreed term changes</t>
+        </is>
+      </c>
+      <c r="Z86" s="5" t="inlineStr">
+        <is>
+          <t>current, version-controlled agreement records</t>
+        </is>
+      </c>
+      <c r="AA86" s="5" t="inlineStr">
+        <is>
+          <t>follows: Create New Contract | enables: Monitor Contracts</t>
+        </is>
+      </c>
+      <c r="AB86" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC86" s="5" t="inlineStr">
+        <is>
+          <t>continuous</t>
+        </is>
+      </c>
       <c r="AD86" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -11925,18 +12359,80 @@
           <t>no meaningful APQC candidate</t>
         </is>
       </c>
-      <c r="U87" s="5" t="n"/>
-      <c r="V87" s="5" t="n"/>
-      <c r="W87" s="5" t="n"/>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>End or transfer an agreement in a controlled way — confirming obligations under it are fulfilled, settled, or queued for legally effective novation, executing the administrative termination or transfer steps, and closing the agreement record with its history preserved.</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>Covers controlled agreement exit: verifying open deals, deliveries, and payments under the agreement are complete or queued for legally effective novation, coordinating effective dates and consents, applying master-agreement close-out mechanics where relevant, and archiving the record. Legal execution of termination and novation documents is owned by Legal &amp; Corporate Communications; close-out settlement amounts by the Settlements cluster (CM-1-2-4-1); disputes follow their dispute processes (CM-1-2-2-2-5, CM-1-2-4-1-17).</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Verify obligations are fulfilled, settled, or queued for legally effective novation | coordinate consents and effective dates | execute administrative termination or transfer | archive the agreement record with history</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>Legal document execution (Legal &amp; Corporate Communications) | close-out settlement (CM-1-2-4-1) | dispute resolution (CM-1-2-2-2-5, CM-1-2-4-1-17)</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>Contract Termination &amp; Novation Administration</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Batch 09 (2026-09-19). Same administrative-versus-legally-effective distinction as CM-1-2-1-2-3. Close-out mechanics per ISDA documentation as reference evidence for applicable OTC frameworks; novation per the CFTC glossary. APQC: no meaningful candidate.</t>
+        </is>
+      </c>
+      <c r="U87" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V87" s="5" t="inlineStr">
+        <is>
+          <t>Agreements end clean or transfer whole.</t>
+        </is>
+      </c>
+      <c r="W87" s="5" t="inlineStr">
+        <is>
+          <t>SRC-ISDA-MA-001 | SRC-CFTC-GLOSS-001</t>
+        </is>
+      </c>
       <c r="X87" s="5" t="n"/>
-      <c r="Y87" s="5" t="n"/>
-      <c r="Z87" s="5" t="n"/>
-      <c r="AA87" s="5" t="n"/>
-      <c r="AB87" s="5" t="n"/>
-      <c r="AC87" s="5" t="n"/>
+      <c r="Y87" s="5" t="inlineStr">
+        <is>
+          <t>open obligation reports | consents and effective dates | master agreement terms</t>
+        </is>
+      </c>
+      <c r="Z87" s="5" t="inlineStr">
+        <is>
+          <t>cleanly terminated or transferred agreement records</t>
+        </is>
+      </c>
+      <c r="AA87" s="5" t="inlineStr">
+        <is>
+          <t>follows: Manage Existing Contract | enables: Settlements</t>
+        </is>
+      </c>
+      <c r="AB87" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC87" s="5" t="inlineStr">
+        <is>
+          <t>event-driven</t>
+        </is>
+      </c>
       <c r="AD87" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -12004,18 +12500,80 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U88" s="5" t="n"/>
-      <c r="V88" s="5" t="n"/>
-      <c r="W88" s="5" t="n"/>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>Administer crude and condensate lease purchase contracts — first-purchase arrangements at the lease or wellhead — through their life: recorded terms, price and deduction bases, division-of-interest references, amendments, and renewals, so lease purchases actualize and settle against current, correct contract terms.</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>Covers the contract-administration side of lease purchasing: maintaining lease contract records with their pricing, gravity and quality adjustment, deduction, and interest-distribution references; processing amendments and renewals; and keeping terms synchronized with actualization and settlement. Included only where the downstream Supply &amp; Trading organization purchases crude or condensate at the lease/wellhead or administers associated first-purchaser arrangements; exploration and production leasehold management, land administration, and upstream royalty accounting remain outside scope. Lease volume actualization is owned by Perform Lease Actualization (CM-1-2-3-1-6); first-purchaser settlement by Settle First Purchaser/Leases (CM-1-2-4-1-6); royalty and interest payment execution by Manage Marketing Interests &amp; Royalty Payments (CM-1-2-4-2-3).</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Maintain lease purchase contract records and pricing bases | administer amendments and renewals | keep division-of-interest and deduction references current | synchronize terms with actualization and settlement</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>Exploration and production leasehold management, land administration, and upstream royalty accounting (outside scope) | lease volume actualization (CM-1-2-3-1-6) | first-purchaser settlement (CM-1-2-4-1-6) | royalty and interest payments (CM-1-2-4-2-3) | negotiation of lease purchase terms (commercial owner)</t>
+        </is>
+      </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>Lease Purchase Contract Administration</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Batch 09 (2026-09-19). 'Lease' read in the crude-marketing sense — first-purchase contracts at the lease or wellhead — corroborated by the Perform Lease Actualization and Settle First Purchaser/Leases siblings; not real-estate or equipment leasing. Scope caveat added at Hamid's direction; whether lease-purchase activity is genuinely in scope for the downstream organization or inherited from an integrated enterprise taxonomy is a follow-up noted in the batch 09 PR. APQC 11743 is an unrelated routing candidate.</t>
+        </is>
+      </c>
+      <c r="U88" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V88" s="5" t="inlineStr">
+        <is>
+          <t>Lease purchases settle against the terms actually in force.</t>
+        </is>
+      </c>
+      <c r="W88" s="5" t="inlineStr">
+        <is>
+          <t>SRC-EIA-GLOSS-001 | SRC-CFTC-GLOSS-001</t>
+        </is>
+      </c>
       <c r="X88" s="5" t="n"/>
-      <c r="Y88" s="5" t="n"/>
-      <c r="Z88" s="5" t="n"/>
-      <c r="AA88" s="5" t="n"/>
-      <c r="AB88" s="5" t="n"/>
-      <c r="AC88" s="5" t="n"/>
+      <c r="Y88" s="5" t="inlineStr">
+        <is>
+          <t>lease contract terms and pricing bases | division-of-interest data | amendment requests</t>
+        </is>
+      </c>
+      <c r="Z88" s="5" t="inlineStr">
+        <is>
+          <t>current lease purchase contract records</t>
+        </is>
+      </c>
+      <c r="AA88" s="5" t="inlineStr">
+        <is>
+          <t>enables: Perform Lease Actualization | enables: Settle First Purchaser/Leases</t>
+        </is>
+      </c>
+      <c r="AB88" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC88" s="5" t="inlineStr">
+        <is>
+          <t>continuous</t>
+        </is>
+      </c>
       <c r="AD88" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -12083,18 +12641,80 @@
           <t>strong APQC candidate but no validator agreed</t>
         </is>
       </c>
-      <c r="U89" s="5" t="n"/>
-      <c r="V89" s="5" t="n"/>
-      <c r="W89" s="5" t="n"/>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>Administer contracts with pipeline, marine, rail, and truck carriers through their life — recorded rates, capacity commitments, service terms, amendments, and renewals — so transportation deals, nominations, and freight settlement operate against current, correct carrier terms.</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>Covers the contract-administration side of carrier relationships across modes: maintaining carrier contract records, rate and accessorial references, and commitment terms; processing amendments and renewals; and keeping terms synchronized with capacity deals and settlement. Boundary rule with the products branch: carrier capacity, tariff, freight-rate, charter, pipeline, railcar, trucking, and network-access agreements that support supply and trading movements are administered here; customer-facing and commercial product-delivery agreements, including delivery terms linked to product sale and marketing arrangements, belong to Manage Product Transport Agreements (CM-1-2-7-1-2). Transportation capacity deals are captured by Capture Transportation Deals (CM-1-2-1-3-9); nominations by Plan &amp; Execute Nominations (CM-1-1-3-6-1); mode-specific settlement by the Settlements cluster; demurrage by Demurrage Management (CM-1-2-4-4).</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Maintain carrier contract records, rates, and commitments by mode | administer amendments and renewals | keep terms synchronized with deals and settlement | track carrier contract expiries and renewal windows</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>Customer-facing product-delivery agreements (CM-1-2-7-1-2) | transportation deal capture (CM-1-2-1-3-9) | nominations and capacity use (CM-1-1-3-6-1) | freight settlement and demurrage (CM-1-2-4-1, CM-1-2-4-4) | physical movement execution (Midstream, distribution operator, carrier)</t>
+        </is>
+      </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>Carrier Contract Administration</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Batch 09 (2026-09-19). The carrier-versus-product-transport rule was sharpened at Hamid's direction: supply/trading-movement carrier agreements here; customer-facing delivery agreements at CM-1-2-7-1-2 — a decision-log-worthy rule that prevents duplication by transport mode alone. Confirming the intended boundary with the products branch is a follow-up noted in the batch 09 PR. APQC 10291 'Manage contracts' scored 0.8 STRONG with no validator; supporting comparative evidence.</t>
+        </is>
+      </c>
+      <c r="U89" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V89" s="5" t="inlineStr">
+        <is>
+          <t>Freight moves and settles against the carrier terms actually in force.</t>
+        </is>
+      </c>
+      <c r="W89" s="5" t="inlineStr">
+        <is>
+          <t>SRC-CFTC-GLOSS-001 | SRC-DOE-RPPL-001</t>
+        </is>
+      </c>
       <c r="X89" s="5" t="n"/>
-      <c r="Y89" s="5" t="n"/>
-      <c r="Z89" s="5" t="n"/>
-      <c r="AA89" s="5" t="n"/>
-      <c r="AB89" s="5" t="n"/>
-      <c r="AC89" s="5" t="n"/>
+      <c r="Y89" s="5" t="inlineStr">
+        <is>
+          <t>carrier contract terms and rates | amendment requests | deal and settlement feedback</t>
+        </is>
+      </c>
+      <c r="Z89" s="5" t="inlineStr">
+        <is>
+          <t>current carrier contract records by mode</t>
+        </is>
+      </c>
+      <c r="AA89" s="5" t="inlineStr">
+        <is>
+          <t>enables: Capture Transportation Deals | enables: Plan &amp; Execute Nominations</t>
+        </is>
+      </c>
+      <c r="AB89" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC89" s="5" t="inlineStr">
+        <is>
+          <t>continuous</t>
+        </is>
+      </c>
       <c r="AD89" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -12157,18 +12777,80 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U90" s="5" t="n"/>
-      <c r="V90" s="5" t="n"/>
-      <c r="W90" s="5" t="n"/>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>Administer storage and throughput contracts through their life — recorded capacity, injection and withdrawal rights, fee structures, amendments, and renewals — so storage deals, inventory administration, and settlement operate against current, correct contract terms.</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>Covers the contract-administration position in the storage split: negotiation is owned by Negotiate Storage / Throughput Agreements (CM-1-2-7-1-3); where storage capacity is commercially traded, allocated, acquired, released, or represented as a distinct transaction it is captured by Capture Storage Deals (CM-1-2-1-3-5), and otherwise the contract record maintained here remains the governed source for contractual storage rights and charges; company stock in the facilities is administered by Manage Third Party Storage (CM-1-1-3-7-11); storage charges settle at Settle Terminal/Storage (CM-1-2-4-1-14). This node maintains the contract record itself — terms, rights, fees, versions, renewals — and keeps the others supplied with current terms.</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Maintain storage and throughput contract records, rights, and fees | administer amendments and renewals | keep terms synchronized with deals, inventory administration, and settlement | track expiries and renewal windows</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>Negotiation (CM-1-2-7-1-3) | capacity deal capture where a distinct transaction exists (CM-1-2-1-3-5) | third-party storage inventory administration (CM-1-1-3-7-11) | storage settlement (CM-1-2-4-1-14)</t>
+        </is>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>Storage Contract Administration</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Batch 09 (2026-09-19). The storage split (negotiate, administer, capture, use, settle) is stated on all participating nodes; the conditional-capture wording was added at Hamid's direction — not every storage contract produces a distinct captured deal, and where none exists the contract record here is the governed source of rights and charges. APQC 12944 is the third-party-bulk-storage candidate; comparative evidence only.</t>
+        </is>
+      </c>
+      <c r="U90" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V90" s="5" t="inlineStr">
+        <is>
+          <t>Storage rights and fees in the systems match the contract in force.</t>
+        </is>
+      </c>
+      <c r="W90" s="5" t="inlineStr">
+        <is>
+          <t>SRC-CFTC-GLOSS-001 | SRC-EI-HM32-001</t>
+        </is>
+      </c>
       <c r="X90" s="5" t="n"/>
-      <c r="Y90" s="5" t="n"/>
-      <c r="Z90" s="5" t="n"/>
-      <c r="AA90" s="5" t="n"/>
-      <c r="AB90" s="5" t="n"/>
-      <c r="AC90" s="5" t="n"/>
+      <c r="Y90" s="5" t="inlineStr">
+        <is>
+          <t>negotiated storage terms | amendment requests | deal and settlement feedback</t>
+        </is>
+      </c>
+      <c r="Z90" s="5" t="inlineStr">
+        <is>
+          <t>current storage contract records</t>
+        </is>
+      </c>
+      <c r="AA90" s="5" t="inlineStr">
+        <is>
+          <t>follows: Negotiate Storage / Throughput Agreements | enables: Capture Storage Deals | enables: Manage Third Party Storage</t>
+        </is>
+      </c>
+      <c r="AB90" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC90" s="5" t="inlineStr">
+        <is>
+          <t>continuous</t>
+        </is>
+      </c>
       <c r="AD90" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -12236,18 +12918,80 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U91" s="5" t="n"/>
-      <c r="V91" s="5" t="n"/>
-      <c r="W91" s="5" t="n"/>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>Monitor active agreements against their terms — tracking obligations, commitments, expiries, renewal windows, and utilization against contracted volumes and service levels — surfacing issues to the responsible owners before they become breaches or lapses.</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>Covers contract-obligation monitoring across the portfolio: obligation and commitment tracking, expiry and renewal-window alerting, utilization against contracted volumes, and escalation of at-risk items to the contract, commercial, or legal owner. Excludes trading compliance monitoring, owned by Regulatory &amp; Compliance (Monitor External Trading Compliance, CM-1-2-4-3-2; Monitor Internal Trading Compliance, CM-1-2-4-3-3); excludes dispute handling (CM-1-2-2-2-5, CM-1-2-4-1-17); excludes acting on the findings — amendments and renewals run through Manage Existing Contract (CM-1-2-1-2-6).</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Track obligations, commitments, and service levels against terms | alert on expiries and renewal windows | monitor utilization against contracted volumes | escalate at-risk items to responsible owners</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>Trading compliance monitoring (CM-1-2-4-3-2, CM-1-2-4-3-3) | dispute handling (CM-1-2-2-2-5, CM-1-2-4-1-17) | amendments and renewals (CM-1-2-1-2-6)</t>
+        </is>
+      </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>Contract Obligation Monitoring</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Batch 09 (2026-09-19). Monitoring surfaces; the lifecycle siblings act — the same detect-versus-decide split established in batch 04. APQC 10291 comparative evidence only.</t>
+        </is>
+      </c>
+      <c r="U91" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V91" s="5" t="inlineStr">
+        <is>
+          <t>No agreement lapses, breaches, or under-uses unnoticed.</t>
+        </is>
+      </c>
+      <c r="W91" s="5" t="inlineStr">
+        <is>
+          <t>SRC-CFTC-GLOSS-001</t>
+        </is>
+      </c>
       <c r="X91" s="5" t="n"/>
-      <c r="Y91" s="5" t="n"/>
-      <c r="Z91" s="5" t="n"/>
-      <c r="AA91" s="5" t="n"/>
-      <c r="AB91" s="5" t="n"/>
-      <c r="AC91" s="5" t="n"/>
+      <c r="Y91" s="5" t="inlineStr">
+        <is>
+          <t>contract terms and calendars | utilization and delivery data | commitment schedules</t>
+        </is>
+      </c>
+      <c r="Z91" s="5" t="inlineStr">
+        <is>
+          <t>monitored obligations with escalated at-risk items</t>
+        </is>
+      </c>
+      <c r="AA91" s="5" t="inlineStr">
+        <is>
+          <t>follows: Manage Existing Contract | triggers: Manage Existing Contract | enables: Trading Strategy Management</t>
+        </is>
+      </c>
+      <c r="AB91" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC91" s="5" t="inlineStr">
+        <is>
+          <t>continuous</t>
+        </is>
+      </c>
       <c r="AD91" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -46251,7 +46995,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -46300,6 +47044,7 @@
         </is>
       </c>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
@@ -47470,6 +48215,53 @@
         </is>
       </c>
       <c r="I31" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>SRC-ISDA-MA-001</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>International Swaps and Derivatives Association</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>ISDA Master Agreements and User Guides (master agreement, schedule, confirmations, credit support structure)</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Accessed 2026-09-19</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>https://www.isda.org/book-taxonomy/mas-and-user-guides/</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Industry standards body</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>ISDA OTC-derivatives master-agreement, confirmation, close-out, and novation terminology. Applies to relevant OTC derivative frameworks only; does not define physical commodity, transportation, storage, lease-purchase, or enterprise contract-management practices, nor internal ownership assignments. Evidence only, not text to copy.</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Contract establishment, termination/novation, and M&amp;A transition mechanics for applicable OTC frameworks</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
         <is>
           <t>active</t>
         </is>

--- a/business_architecture/ontology/build/output/step3c-definition-authoring-workbook.xlsx
+++ b/business_architecture/ontology/build/output/step3c-definition-authoring-workbook.xlsx
@@ -15593,18 +15593,80 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U114" s="5" t="n"/>
-      <c r="V114" s="5" t="n"/>
-      <c r="W114" s="5" t="n"/>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>Independently confirm and match executed trades with counterparties by generating, receiving, validating, documenting, modifying, reporting, and resolving discrepancies in trade confirmations, so the organization and its counterparty have evidenced agreement on the applicable trade terms.</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>Covers the per-trade confirmation lifecycle after capture: outgoing confirmation generation, incoming confirmation matching, documentation control, modification processing, continuation reporting where required, and dispute resolution. This process performs an independent control over the trade-capture record. The enterprise may operate that control through a middle-office, operations, shared-services, or other designated function; this taxonomy does not prescribe the organizational delivery model. Excludes deal capture and its corrections, owned by Trade Capture (CM-1-2-1-3); excludes master agreement establishment and administration, owned by Contract Management (CM-1-2-1-2); excludes settlement and settlement disputes (CM-1-2-4-1, CM-1-2-4-1-17); excludes risk measurement (Market Risk Management, CM-1-2-2-3).</t>
+        </is>
+      </c>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Generate and match trade confirmations | maintain confirmation documentation and evidence | process agreed trade modifications through re-confirmation | report confirmation and continuation events where required | resolve confirmation disputes</t>
+        </is>
+      </c>
+      <c r="Q114" t="inlineStr">
+        <is>
+          <t>Deal capture and capture corrections (CM-1-2-1-3) | master agreement administration (CM-1-2-1-2) | settlement and settlement disputes (CM-1-2-4-1) | risk measurement and limits (CM-1-2-2-3)</t>
+        </is>
+      </c>
+      <c r="R114" t="inlineStr">
+        <is>
+          <t>Trade Confirmation Management</t>
+        </is>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Batch 10 (2026-09-19). Concept type: process (Hamid confirmed) — a per-trade lifecycle (generate, document, modify, report, dispute), per the batch 08 variant test. Reworded at Hamid's direction to describe an organizationally neutral independent control rather than prescribing a middle-office delivery model — the approved L3 definition's 'middle office' names the control function, not a mandated organization. Confirmation structure per ISDA documentation for applicable OTC frameworks; physical and other deal types are confirmed per their governing agreements, standard terms, exchange rules, or platform matching. APQC 20682 is an unrelated IT candidate.</t>
+        </is>
+      </c>
+      <c r="U114" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V114" s="5" t="inlineStr">
+        <is>
+          <t>Establish timely, retained evidence that the organization and counterparty agree — or have a controlled, visible disagreement — on the applicable trade terms.</t>
+        </is>
+      </c>
+      <c r="W114" s="5" t="inlineStr">
+        <is>
+          <t>SRC-ISDA-MA-001 | SRC-CFTC-GLOSS-001</t>
+        </is>
+      </c>
       <c r="X114" s="5" t="n"/>
-      <c r="Y114" s="5" t="n"/>
-      <c r="Z114" s="5" t="n"/>
-      <c r="AA114" s="5" t="n"/>
-      <c r="AB114" s="5" t="n"/>
-      <c r="AC114" s="5" t="n"/>
+      <c r="Y114" s="5" t="inlineStr">
+        <is>
+          <t>captured deal records | counterparty confirmations and acknowledgements | governing agreement terms</t>
+        </is>
+      </c>
+      <c r="Z114" s="5" t="inlineStr">
+        <is>
+          <t>matched, evidenced trade confirmations</t>
+        </is>
+      </c>
+      <c r="AA114" s="5" t="inlineStr">
+        <is>
+          <t>follows: Trade Capture | precedes: Settlements | governed-by: Regulatory &amp; Compliance</t>
+        </is>
+      </c>
+      <c r="AB114" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC114" s="5" t="inlineStr">
+        <is>
+          <t>event-driven</t>
+        </is>
+      </c>
       <c r="AD114" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -15672,18 +15734,80 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U115" s="5" t="n"/>
-      <c r="V115" s="5" t="n"/>
-      <c r="W115" s="5" t="n"/>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>Produce and dispatch outgoing trade confirmations from captured deal records — using the templates and terms of the governing agreement — and match incoming counterparty confirmations or equivalent contractual acknowledgements against the captured deal record, using the applicable product, agreement, and confirmation standards, chasing unconfirmed trades within applicable timeliness requirements.</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>Covers confirmation generation and matching: assembling confirmations from captured terms per the governing master agreement or standard terms, dispatching through the agreed channel (including electronic confirmation platforms where used), matching incoming confirmations or equivalent acknowledgements against the capture record per the applicable standards, and escalating aging unconfirmed trades. Confirmation methods vary by product and agreement — bilateral confirmations, platform matching, exchange rules, and contractual notices are all accommodated. Mismatches route to Manage Confirm Disputes (CM-1-2-2-2-5); capture errors surfaced by matching route back to Trade Capture (CM-1-2-1-3) for correction. Excludes confirmation template and documentation control, owned by Manage Confirmation Documentation (CM-1-2-2-2-2).</t>
+        </is>
+      </c>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Assemble and dispatch confirmations from captured terms | match incoming confirmations or equivalent acknowledgements per applicable standards | chase and escalate unconfirmed trades within timeliness requirements | route mismatches and capture errors to their owners</t>
+        </is>
+      </c>
+      <c r="Q115" t="inlineStr">
+        <is>
+          <t>Template and documentation control (CM-1-2-2-2-2) | dispute resolution (CM-1-2-2-2-5) | capture correction (CM-1-2-1-3)</t>
+        </is>
+      </c>
+      <c r="R115" t="inlineStr">
+        <is>
+          <t>Confirmation Generation &amp; Matching</t>
+        </is>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>Batch 10 (2026-09-19). Reworded at Hamid's direction: matching runs against 'counterparty confirmations or equivalent contractual acknowledgements' per applicable product, agreement, and confirmation standards — not asserted as universal literal field-by-field automated comparison; timeliness requirements vary by regime, instrument, and counterparty classification. APQC 10136 is an unrelated sales-forecast candidate.</t>
+        </is>
+      </c>
+      <c r="U115" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V115" s="5" t="inlineStr">
+        <is>
+          <t>Every trade is confirmed or visibly chased, never silently unconfirmed.</t>
+        </is>
+      </c>
+      <c r="W115" s="5" t="inlineStr">
+        <is>
+          <t>SRC-ISDA-MA-001 | SRC-CFTC-GLOSS-001</t>
+        </is>
+      </c>
       <c r="X115" s="5" t="n"/>
-      <c r="Y115" s="5" t="n"/>
-      <c r="Z115" s="5" t="n"/>
-      <c r="AA115" s="5" t="n"/>
-      <c r="AB115" s="5" t="n"/>
-      <c r="AC115" s="5" t="n"/>
+      <c r="Y115" s="5" t="inlineStr">
+        <is>
+          <t>captured deal records | governing agreement templates | incoming counterparty confirmations and acknowledgements</t>
+        </is>
+      </c>
+      <c r="Z115" s="5" t="inlineStr">
+        <is>
+          <t>dispatched and matched confirmations with chase status</t>
+        </is>
+      </c>
+      <c r="AA115" s="5" t="inlineStr">
+        <is>
+          <t>follows: Trade Capture | precedes: Manage Confirm Disputes | uses-input: Manage Confirmation Documentation</t>
+        </is>
+      </c>
+      <c r="AB115" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC115" s="5" t="inlineStr">
+        <is>
+          <t>event-driven</t>
+        </is>
+      </c>
       <c r="AD115" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -15751,18 +15875,80 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U116" s="5" t="n"/>
-      <c r="V116" s="5" t="n"/>
-      <c r="W116" s="5" t="n"/>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>Maintain the confirmation documentation basis — approved templates and standard wording aligned to governing agreements, the archive of dispatched and matched confirmations, and the evidence trail that shows what was agreed and when — so confirmations are consistent, current, and provable.</t>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>Covers documentation control for the confirmation process: template and standard-wording maintenance aligned to master agreements and standard terms, version control, the confirmation archive, and retention of matching and dispatch evidence. Legal approval of template wording is owned by Legal &amp; Corporate Communications under its locked rule; the governing agreements themselves are administered by Contract Management (CM-1-2-1-2); regulatory record-retention policy is owned by Regulatory &amp; Compliance (CM-1-2-4-3).</t>
+        </is>
+      </c>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>Maintain approved confirmation templates and standard wording | control template versions against governing agreements | archive dispatched and matched confirmations | retain dispatch and matching evidence</t>
+        </is>
+      </c>
+      <c r="Q116" t="inlineStr">
+        <is>
+          <t>Legal approval of wording (Legal &amp; Corporate Communications) | governing agreement administration (CM-1-2-1-2) | retention policy setting (CM-1-2-4-3)</t>
+        </is>
+      </c>
+      <c r="R116" t="inlineStr">
+        <is>
+          <t>Confirmation Template &amp; Records Control</t>
+        </is>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>Batch 10 (2026-09-19). Template-versus-agreement split: templates implement what the governing agreements say; changing the agreement is Contract Management's lifecycle, reflected here afterward. APQC 11743 is an unrelated routing candidate.</t>
+        </is>
+      </c>
+      <c r="U116" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V116" s="5" t="inlineStr">
+        <is>
+          <t>Confirmations are consistent with the governing agreements and provable years later.</t>
+        </is>
+      </c>
+      <c r="W116" s="5" t="inlineStr">
+        <is>
+          <t>SRC-ISDA-MA-001</t>
+        </is>
+      </c>
       <c r="X116" s="5" t="n"/>
-      <c r="Y116" s="5" t="n"/>
-      <c r="Z116" s="5" t="n"/>
-      <c r="AA116" s="5" t="n"/>
-      <c r="AB116" s="5" t="n"/>
-      <c r="AC116" s="5" t="n"/>
+      <c r="Y116" s="5" t="inlineStr">
+        <is>
+          <t>governing agreement terms | legal-approved wording | dispatched and matched confirmations</t>
+        </is>
+      </c>
+      <c r="Z116" s="5" t="inlineStr">
+        <is>
+          <t>current templates and a complete confirmation archive</t>
+        </is>
+      </c>
+      <c r="AA116" s="5" t="inlineStr">
+        <is>
+          <t>enables: Generate Confirms | informed-by: Contract Management</t>
+        </is>
+      </c>
+      <c r="AB116" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC116" s="5" t="inlineStr">
+        <is>
+          <t>event-driven</t>
+        </is>
+      </c>
       <c r="AD116" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -15830,18 +16016,80 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U117" s="5" t="n"/>
-      <c r="V117" s="5" t="n"/>
-      <c r="W117" s="5" t="n"/>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>Coordinate the confirmation-side processing of agreed post-execution changes to a trade — including amendments, allocations, partial terminations, and early terminations — by validating counterparty agreement, initiating or validating the required controlled trade-record update, re-confirming revised terms, and triggering applicable lifecycle reporting.</t>
+        </is>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>Covers the confirmation-side lifecycle of trade changes: intake and validation of modification requests, verification that both parties agree the change, initiation or validation of the required controlled trade-record update, re-confirmation of modified terms, and triggering of continuation reporting through Report Confirmation To SDR (CM-1-2-2-2-4) where required. The authorized trade-record owner performs the controlled capture update; this process verifies that the record and confirmation reflect the mutually agreed change — it does not independently decide commercial amendments, execute legal novations, or correct internal capture errors that do not alter mutually agreed terms. Excludes the commercial decision to modify (trading and strategy processes); excludes novations and assignments, owned by Contract Management (CM-1-2-1-2-3, CM-1-2-1-2-7); excludes unilateral capture corrections (CM-1-2-1-3).</t>
+        </is>
+      </c>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Intake and validate agreed modification requests | verify counterparty agreement to the change | initiate or validate the controlled trade-record update | re-confirm revised terms and trigger applicable reporting</t>
+        </is>
+      </c>
+      <c r="Q117" t="inlineStr">
+        <is>
+          <t>Commercial modification decisions (trading, strategy) | novations and assignments (CM-1-2-1-2) | unilateral capture corrections (CM-1-2-1-3) | performing the capture update itself (authorized trade-record owner, CM-1-2-1-3)</t>
+        </is>
+      </c>
+      <c r="R117" t="inlineStr">
+        <is>
+          <t>Trade Amendment Processing</t>
+        </is>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>Batch 10 (2026-09-19). Reworded at Hamid's direction: this process coordinates and verifies; the authorized trade-record owner performs the controlled update. Modification versus novation: a modification changes agreed terms between the same parties and stays here; a change of party is a novation and belongs to Contract Management per batch 09. Aligned with the batch 08 capture-correction distinction. APQC 11040 is an unrelated trade-association candidate; false lexical match.</t>
+        </is>
+      </c>
+      <c r="U117" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V117" s="5" t="inlineStr">
+        <is>
+          <t>Modified trades are as provably agreed as new ones.</t>
+        </is>
+      </c>
+      <c r="W117" s="5" t="inlineStr">
+        <is>
+          <t>SRC-ISDA-MA-001 | SRC-CFTC-P45-001</t>
+        </is>
+      </c>
       <c r="X117" s="5" t="n"/>
-      <c r="Y117" s="5" t="n"/>
-      <c r="Z117" s="5" t="n"/>
-      <c r="AA117" s="5" t="n"/>
-      <c r="AB117" s="5" t="n"/>
-      <c r="AC117" s="5" t="n"/>
+      <c r="Y117" s="5" t="inlineStr">
+        <is>
+          <t>agreed modification requests | capture records | counterparty consents</t>
+        </is>
+      </c>
+      <c r="Z117" s="5" t="inlineStr">
+        <is>
+          <t>re-confirmed modified trades with triggered reporting</t>
+        </is>
+      </c>
+      <c r="AA117" s="5" t="inlineStr">
+        <is>
+          <t>follows: Generate Confirms | triggers: Report Confirmation To SDR | requires: Trade Capture</t>
+        </is>
+      </c>
+      <c r="AB117" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC117" s="5" t="inlineStr">
+        <is>
+          <t>event-driven</t>
+        </is>
+      </c>
       <c r="AD117" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -15909,18 +16157,80 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U118" s="5" t="n"/>
-      <c r="V118" s="5" t="n"/>
-      <c r="W118" s="5" t="n"/>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>Report confirmation and lifecycle events for reportable transactions under an applicable trade-reporting regime — submitting required continuation data for amendments, terminations, and other post-execution events to the designated registered swap data repository within applicable deadlines, where the organization holds reporting responsibility — correcting errors and retaining reporting evidence.</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>Covers continuation-side reporting under applicable regimes: determining which confirmation and lifecycle events require reporting, submitting continuation data within deadlines, corrections, resubmissions, acknowledgements, and evidence retention. A confirmation, modification, or lifecycle event triggers continuation-data reporting only where the applicable regime requires reporting, the event is reportable, and the organization has reporting responsibility or an assigned delegated-reporting obligation. Under US CFTC Part 45 this is continuation-data reporting (45.4); trade creation data is reported at capture by Report Trades to SDR (CM-1-2-1-3-10) — the boundary recorded in batch 08. Excludes regulatory-policy ownership and monitoring (Regulatory &amp; Compliance, CM-1-2-4-3); excludes the legal determination of reporting responsibility (Legal/Compliance); excludes regimes, instruments, and events not applicable to the organization.</t>
+        </is>
+      </c>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>Determine reportable confirmation and lifecycle events under applicable regimes | submit required continuation data within deadlines where responsible | correct, resubmit, and track acknowledgements | retain reporting evidence</t>
+        </is>
+      </c>
+      <c r="Q118" t="inlineStr">
+        <is>
+          <t>Creation-data reporting (CM-1-2-1-3-10) | regulatory-policy ownership and monitoring (CM-1-2-4-3) | legal determination of reporting responsibility (Legal/Compliance) | non-applicable regimes and events</t>
+        </is>
+      </c>
+      <c r="R118" t="inlineStr">
+        <is>
+          <t>Swap Data Reporting (Continuation Data)</t>
+        </is>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>Batch 10 (2026-09-19). Trigger made explicitly conditional at Hamid's direction: reporting occurs only where the regime requires it, the event is reportable, and the organization holds or is delegated reporting responsibility — not every confirmation event produces a reportable continuation event. Relations use 'informed-by' rather than 'follows' because the controlled relationship vocabulary has no conditional form; the conditionality is recorded here. CFTC Part 45 (45.3 versus 45.4) is US-specific evidence for the boundary with CM-1-2-1-3-10; it is not a universal model for physical confirmations, exchange-traded futures, or other jurisdictions. APQC 11175 is an unrelated profitability candidate.</t>
+        </is>
+      </c>
+      <c r="U118" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V118" s="5" t="inlineStr">
+        <is>
+          <t>Every reportable lifecycle event the organization must report reaches the repository on time, once, correctly.</t>
+        </is>
+      </c>
+      <c r="W118" s="5" t="inlineStr">
+        <is>
+          <t>SRC-CFTC-P45-001 | SRC-CFTC-GLOSS-001</t>
+        </is>
+      </c>
       <c r="X118" s="5" t="n"/>
-      <c r="Y118" s="5" t="n"/>
-      <c r="Z118" s="5" t="n"/>
-      <c r="AA118" s="5" t="n"/>
-      <c r="AB118" s="5" t="n"/>
-      <c r="AC118" s="5" t="n"/>
+      <c r="Y118" s="5" t="inlineStr">
+        <is>
+          <t>confirmation and lifecycle events | applicable reporting rules and deadlines | repository specifications</t>
+        </is>
+      </c>
+      <c r="Z118" s="5" t="inlineStr">
+        <is>
+          <t>submitted, evidenced continuation-data reports under applicable regimes</t>
+        </is>
+      </c>
+      <c r="AA118" s="5" t="inlineStr">
+        <is>
+          <t>informed-by: Report Trades to SDR | informed-by: Manage Trade Modifications | governed-by: Regulatory &amp; Compliance</t>
+        </is>
+      </c>
+      <c r="AB118" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC118" s="5" t="inlineStr">
+        <is>
+          <t>event-driven</t>
+        </is>
+      </c>
       <c r="AD118" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -15988,18 +16298,80 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U119" s="5" t="n"/>
-      <c r="V119" s="5" t="n"/>
-      <c r="W119" s="5" t="n"/>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>Resolve confirmation mismatches and disputes — logging discrepancies between the capture record and the counterparty's confirmation, investigating against execution evidence, agreeing the correct terms with the counterparty, and driving the resolution into the records and any required re-reporting.</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>Covers the confirmation dispute lifecycle: discrepancy logging and classification, investigation against capture and execution evidence, counterparty negotiation of the correct terms, escalation of aging or material disputes, and closure through corrected records, re-confirmation, and re-reporting where required. Excludes settlement disputes, owned by Manage Settlement Disputes (CM-1-2-4-1-17); excludes actualization disputes (Manage Actualization Disputes, CM-1-2-3-1-8); excludes demurrage claims (CM-1-2-4-4); excludes legal proceedings, owned by Legal &amp; Corporate Communications.</t>
+        </is>
+      </c>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>Log and classify confirmation discrepancies | investigate against capture and execution evidence | negotiate and agree correct terms with the counterparty | drive resolution into records, re-confirmation, and re-reporting</t>
+        </is>
+      </c>
+      <c r="Q119" t="inlineStr">
+        <is>
+          <t>Settlement disputes (CM-1-2-4-1-17) | actualization disputes (CM-1-2-3-1-8) | demurrage claims (CM-1-2-4-4) | legal proceedings (Legal &amp; Corporate Communications)</t>
+        </is>
+      </c>
+      <c r="R119" t="inlineStr">
+        <is>
+          <t>Confirmation Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>Batch 10 (2026-09-19). The dispute partition rule (Hamid, batch 10): confirmation disputes answer 'what did the parties agree the terms were' (here); actualization disputes answer 'what was physically delivered, received, measured, or performed' (CM-1-2-3-1-8); settlement disputes answer 'what is owed, invoiced, received, paid, netted, or applied' (CM-1-2-4-1-17); demurrage claims answer 'was delay or capacity usage compensable' (CM-1-2-4-4); legal proceedings belong to Legal &amp; Corporate Communications. The lifecycle-stage question is the placement test. APQC 11743 is an unrelated routing candidate.</t>
+        </is>
+      </c>
+      <c r="U119" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V119" s="5" t="inlineStr">
+        <is>
+          <t>No confirmation mismatch survives unexamined or unresolved.</t>
+        </is>
+      </c>
+      <c r="W119" s="5" t="inlineStr">
+        <is>
+          <t>SRC-ISDA-MA-001 | SRC-CFTC-GLOSS-001</t>
+        </is>
+      </c>
       <c r="X119" s="5" t="n"/>
-      <c r="Y119" s="5" t="n"/>
-      <c r="Z119" s="5" t="n"/>
-      <c r="AA119" s="5" t="n"/>
-      <c r="AB119" s="5" t="n"/>
-      <c r="AC119" s="5" t="n"/>
+      <c r="Y119" s="5" t="inlineStr">
+        <is>
+          <t>confirmation mismatches | capture and execution evidence | counterparty correspondence</t>
+        </is>
+      </c>
+      <c r="Z119" s="5" t="inlineStr">
+        <is>
+          <t>resolved disputes with corrected, re-confirmed records</t>
+        </is>
+      </c>
+      <c r="AA119" s="5" t="inlineStr">
+        <is>
+          <t>follows: Generate Confirms | triggers: Manage Trade Modifications | enables: Settlements</t>
+        </is>
+      </c>
+      <c r="AB119" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC119" s="5" t="inlineStr">
+        <is>
+          <t>event-driven</t>
+        </is>
+      </c>
       <c r="AD119" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -47044,7 +47416,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>

--- a/business_architecture/ontology/build/output/step3c-definition-authoring-workbook.xlsx
+++ b/business_architecture/ontology/build/output/step3c-definition-authoring-workbook.xlsx
@@ -14887,18 +14887,80 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U105" s="5" t="n"/>
-      <c r="V105" s="5" t="n"/>
-      <c r="W105" s="5" t="n"/>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>The capability to control counterparty credit risk in trading — assessing counterparty creditworthiness, setting and maintaining credit limits, administering credit support and margin, measuring exposure, analyzing portfolio credit risk, monitoring positions against limits, and reporting the credit risk picture — so credit losses are anticipated, bounded, and visible before they happen.</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>Covers the independent credit-risk control over trading counterparties: reviews, limits, credit-support and collateral administration, exposure calculation, margining, advanced analytics, continuous monitoring, and reporting. This is an independent control function; the enterprise may operate it through middle-office, risk, or another designated function — the taxonomy does not prescribe the delivery model. Excludes trading decisions and pre-trade checks, which apply these limits (Manage Pre-Trade Analysis, CM-1-2-1-3-1); excludes commercial customer credit in order-to-cash, owned by Manage Credit &amp; Risk (CM-1-3-7-4) — the boundary is the relationship and exposure type, not the organizational branch; excludes market risk, owned by Market Risk Management (CM-1-2-2-3); excludes inventory risk (Assess &amp; Manage Inventory Risk, CM-1-2-5-4-1); excludes credit-loss accounting — provisions, impairments, write-offs, and disclosures — owned by Finance under its locked rule; excludes legal enforcement, security documentation, and insolvency action, owned by Legal &amp; Corporate Communications.</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Assess counterparty creditworthiness | set and maintain credit limits | administer credit support, collateral, and margining | calculate and monitor credit exposure | analyze and report portfolio credit risk</t>
+        </is>
+      </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>Trading decisions and pre-trade checks (CM-1-2-1-3-1) | commercial customer credit (CM-1-3-7-4) | market risk (CM-1-2-2-3) | inventory risk (CM-1-2-5-4-1) | credit-loss accounting: provisions, write-offs, disclosures (Finance) | legal enforcement and security documentation (Legal &amp; Corporate Communications)</t>
+        </is>
+      </c>
+      <c r="R105" t="inlineStr">
+        <is>
+          <t>Counterparty Credit Risk Management</t>
+        </is>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Batch 11 (2026-09-19). Concept type: capability (Hamid confirmed) — heterogeneous recurring control processes jointly enabling one outcome; a counterparty can be reviewed, monitored, collateralized, margined, reported, and re-limited concurrently, so there is no single per-counterparty lifecycle. Binding credit-boundary rule (Hamid, batch 11): Trading Counterparty Credit Risk governs exposure arising from trading, commodity and capacity positions, settlement cycles, collateral, margin, master agreements, and counterparty default risk. Commercial Customer Credit governs exposure arising from customer orders, deliveries, invoices, receivables, payment terms, credit holds, and collections (Manage Credit &amp; Risk, CM-1-3-7-4). The same legal entity may be subject to both processes in different roles; shared legal identity does not merge the exposure, decision rights, limit structures, or control processes. Organizational delivery model not prescribed, per the batch 10 neutrality decision. APQC 20711 is an IT-risk candidate; comparative evidence only.</t>
+        </is>
+      </c>
+      <c r="U105" s="5" t="inlineStr">
+        <is>
+          <t>capability</t>
+        </is>
+      </c>
+      <c r="V105" s="5" t="inlineStr">
+        <is>
+          <t>Credit losses are anticipated, bounded, and visible before they happen.</t>
+        </is>
+      </c>
+      <c r="W105" s="5" t="inlineStr">
+        <is>
+          <t>SRC-CCRO-001 | SRC-CFTC-GLOSS-001 | SRC-ISDA-MA-001</t>
+        </is>
+      </c>
       <c r="X105" s="5" t="n"/>
-      <c r="Y105" s="5" t="n"/>
-      <c r="Z105" s="5" t="n"/>
-      <c r="AA105" s="5" t="n"/>
-      <c r="AB105" s="5" t="n"/>
-      <c r="AC105" s="5" t="n"/>
+      <c r="Y105" s="5" t="inlineStr">
+        <is>
+          <t>counterparty financials and ratings | positions and mark-to-market | credit-support and agreement terms | risk appetite</t>
+        </is>
+      </c>
+      <c r="Z105" s="5" t="inlineStr">
+        <is>
+          <t>bounded, monitored, reported counterparty credit risk</t>
+        </is>
+      </c>
+      <c r="AA105" s="5" t="inlineStr">
+        <is>
+          <t>governed-by: Regulatory &amp; Compliance | enables: Trade Capture | enables: Contract Management</t>
+        </is>
+      </c>
+      <c r="AB105" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC105" s="5" t="inlineStr">
+        <is>
+          <t>continuous</t>
+        </is>
+      </c>
       <c r="AD105" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -14966,18 +15028,80 @@
           <t>strong APQC candidate but no validator agreed</t>
         </is>
       </c>
-      <c r="U106" s="5" t="n"/>
-      <c r="V106" s="5" t="n"/>
-      <c r="W106" s="5" t="n"/>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>Assess a counterparty's creditworthiness — at onboarding, on a periodic cycle, and on trigger events — analyzing financial statements, ratings, ownership and support structures, payment behavior, and qualitative factors, and assigning or updating the internal credit assessment that limits and monitoring run on.</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>Covers the credit assessment process: initial reviews supporting onboarding (Create New Counterparty, CM-1-2-1-2-1, coordinates them), scheduled periodic reviews, and event-triggered reassessments on deterioration signals or corporate events. The output is the internal credit assessment consumed by Manage Credit Limits (CM-1-2-2-1-2). Excludes setting the limits themselves (CM-1-2-2-1-2); excludes continuous surveillance (Monitor &amp; Analyze Credit, CM-1-2-2-1-7); excludes commercial customer credit assessment (CM-1-3-7-4).</t>
+        </is>
+      </c>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Perform onboarding, periodic, and event-triggered credit reviews | analyze financials, ratings, ownership, and payment behavior | assign and update internal credit assessments | recommend limit and credit-support consequences</t>
+        </is>
+      </c>
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>Limit setting (CM-1-2-2-1-2) | continuous surveillance (CM-1-2-2-1-7) | customer credit assessment (CM-1-3-7-4)</t>
+        </is>
+      </c>
+      <c r="R106" t="inlineStr">
+        <is>
+          <t>Counterparty Credit Assessment</t>
+        </is>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Batch 11 (2026-09-19). Review versus surveillance split: this node reassesses on cycle and trigger; CM-1-2-2-1-7 watches continuously and triggers this node. APQC 19587 STRONG with no validator; supporting comparative evidence.</t>
+        </is>
+      </c>
+      <c r="U106" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V106" s="5" t="inlineStr">
+        <is>
+          <t>Every counterparty's creditworthiness is currently and defensibly assessed.</t>
+        </is>
+      </c>
+      <c r="W106" s="5" t="inlineStr">
+        <is>
+          <t>SRC-CCRO-001 | SRC-CFTC-GLOSS-001</t>
+        </is>
+      </c>
       <c r="X106" s="5" t="n"/>
-      <c r="Y106" s="5" t="n"/>
-      <c r="Z106" s="5" t="n"/>
-      <c r="AA106" s="5" t="n"/>
-      <c r="AB106" s="5" t="n"/>
-      <c r="AC106" s="5" t="n"/>
+      <c r="Y106" s="5" t="inlineStr">
+        <is>
+          <t>counterparty financials and ratings | ownership and support structures | payment and dispute history</t>
+        </is>
+      </c>
+      <c r="Z106" s="5" t="inlineStr">
+        <is>
+          <t>current internal credit assessments</t>
+        </is>
+      </c>
+      <c r="AA106" s="5" t="inlineStr">
+        <is>
+          <t>enables: Manage Credit Limits | enables: Create New Counterparty | informed-by: Monitor &amp; Analyze Credit</t>
+        </is>
+      </c>
+      <c r="AB106" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC106" s="5" t="inlineStr">
+        <is>
+          <t>periodic</t>
+        </is>
+      </c>
       <c r="AD106" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -15045,18 +15169,80 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U107" s="5" t="n"/>
-      <c r="V107" s="5" t="n"/>
-      <c r="W107" s="5" t="n"/>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>Establish, maintain, publish, and adjust credit limits for trading counterparties and counterparty groups — based on approved credit assessments, risk appetite, exposure methodology, and credit-support arrangements — administer documented temporary-excess and exception decisions under delegated authority, and reduce, suspend, or withdraw limits when deterioration or policy triggers require it.</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>Covers the limit lifecycle: establishing limits from assessments and appetite, structuring them by counterparty, group, tenor, and product where applicable, publishing them to the connected controls, administering and recording temporary-excess approvals made under the approved delegation of authority, and cutting limits on deterioration. Enforcement occurs through the connected controls — pre-trade checks (Manage Pre-Trade Analysis, CM-1-2-1-3-1), surveillance and escalation (CM-1-2-2-1-7), and applicable transaction controls — not through this process itself. Excludes the credit assessment (CM-1-2-2-1-1); excludes portfolio risk appetite, which is governance above this process; excludes customer credit limits in order-to-cash (CM-1-3-7-4).</t>
+        </is>
+      </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Establish and structure limits from assessments and appetite | maintain and publish limits by counterparty and group | administer and record temporary-excess approvals under the delegation of authority | reduce, suspend, or withdraw limits on deterioration or policy triggers</t>
+        </is>
+      </c>
+      <c r="Q107" t="inlineStr">
+        <is>
+          <t>Credit assessment (CM-1-2-2-1-1) | limit enforcement through connected controls (CM-1-2-1-3-1, CM-1-2-2-1-7) | portfolio risk appetite (risk governance) | customer credit limits (CM-1-3-7-4)</t>
+        </is>
+      </c>
+      <c r="R107" t="inlineStr">
+        <is>
+          <t>Credit Limit Administration</t>
+        </is>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Batch 11 (2026-09-19). Reworded at Hamid's direction: this process establishes, publishes, and administers limits and delegated exception decisions; enforcement happens through connected pre-trade, surveillance, and transaction controls. Temporary excesses are administered and recorded under the approved delegation of authority — which function holds that exception authority is a follow-up noted in the batch 11 PR. APQC 20929 is a corporate-card candidate; false lexical match.</t>
+        </is>
+      </c>
+      <c r="U107" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V107" s="5" t="inlineStr">
+        <is>
+          <t>Exposure capacity always matches assessed creditworthiness.</t>
+        </is>
+      </c>
+      <c r="W107" s="5" t="inlineStr">
+        <is>
+          <t>SRC-CCRO-001 | SRC-CFTC-GLOSS-001</t>
+        </is>
+      </c>
       <c r="X107" s="5" t="n"/>
-      <c r="Y107" s="5" t="n"/>
-      <c r="Z107" s="5" t="n"/>
-      <c r="AA107" s="5" t="n"/>
-      <c r="AB107" s="5" t="n"/>
-      <c r="AC107" s="5" t="n"/>
+      <c r="Y107" s="5" t="inlineStr">
+        <is>
+          <t>internal credit assessments | risk appetite | exposure and utilization data</t>
+        </is>
+      </c>
+      <c r="Z107" s="5" t="inlineStr">
+        <is>
+          <t>current, approved, and published credit limits and exception decisions</t>
+        </is>
+      </c>
+      <c r="AA107" s="5" t="inlineStr">
+        <is>
+          <t>follows: Perform Counterparty Credit Reviews | enables: Manage Pre-Trade Analysis | enables: Monitor &amp; Analyze Credit</t>
+        </is>
+      </c>
+      <c r="AB107" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC107" s="5" t="inlineStr">
+        <is>
+          <t>continuous</t>
+        </is>
+      </c>
       <c r="AD107" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -15124,18 +15310,80 @@
           <t>strong APQC candidate but no validator agreed</t>
         </is>
       </c>
-      <c r="U108" s="5" t="n"/>
-      <c r="V108" s="5" t="n"/>
-      <c r="W108" s="5" t="n"/>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>Administer contractual credit support both held and posted — cash collateral, securities, letters of credit, guarantees, and other eligible security, with their haircuts, thresholds, independent amounts, and substitutions — calling, receiving, returning, valuing, and reconciling credit support under the applicable arrangements, so credit exposure is secured to the extent the agreements require.</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>Covers administration of bilateral and other contractually agreed credit-support arrangements across held and posted positions: issuing and answering calls per credit-support annexes and credit terms, valuing collateral with applicable haircuts, managing eligibility, thresholds, independent amounts, and substitutions, reconciling balances with counterparties, and coordinating release at offboarding (Terminate/Novate Counterparty, CM-1-2-1-2-3). Includes letters of credit, guarantees, and eligible security where in scope. Excludes CCP, exchange, and broker margin workflows, which belong to Perform Margining (CM-1-2-2-1-5) — bilateral margin required under a credit-support arrangement remains within this process unless the detailed operating model intentionally separates it. Credit-support documentation is established through Contract Management (CM-1-2-1-2) with Legal &amp; Corporate Communications; the cash and securities movements themselves execute through the settlement and finance processes.</t>
+        </is>
+      </c>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Issue and answer credit-support calls per agreements | value collateral with applicable haircuts | manage eligibility, thresholds, independent amounts, and substitutions | reconcile credit-support positions and coordinate release</t>
+        </is>
+      </c>
+      <c r="Q108" t="inlineStr">
+        <is>
+          <t>CCP, exchange, and broker margin workflows (CM-1-2-2-1-5) | credit-support documentation (CM-1-2-1-2, Legal &amp; Corporate Communications) | cash and securities movement execution (settlement and finance processes)</t>
+        </is>
+      </c>
+      <c r="R108" t="inlineStr">
+        <is>
+          <t>Credit Support Administration | Collateral Administration</t>
+        </is>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Batch 11 (2026-09-19). Broadened at Hamid's direction from 'bilateral versus cleared' to credit support versus CCP/exchange/broker margin: contractual credit support of all forms — cash, securities, letters of credit, guarantees — is administered here, and bilateral margin under a credit-support arrangement stays here unless the operating model separates it. Which collateral forms are genuinely in scope, and whether bilateral IM/VM workflows sit with Credit Risk, Treasury, or a specialized team, are follow-ups noted in the batch 11 PR. Credit-support structure per ISDA documentation for applicable OTC frameworks. APQC 19586 scored 0.8 STRONG with no validator; supporting comparative evidence.</t>
+        </is>
+      </c>
+      <c r="U108" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V108" s="5" t="inlineStr">
+        <is>
+          <t>Exposure is secured exactly as the agreements require, both ways.</t>
+        </is>
+      </c>
+      <c r="W108" s="5" t="inlineStr">
+        <is>
+          <t>SRC-ISDA-MA-001 | SRC-CFTC-GLOSS-001 | SRC-CCRO-001</t>
+        </is>
+      </c>
       <c r="X108" s="5" t="n"/>
-      <c r="Y108" s="5" t="n"/>
-      <c r="Z108" s="5" t="n"/>
-      <c r="AA108" s="5" t="n"/>
-      <c r="AB108" s="5" t="n"/>
-      <c r="AC108" s="5" t="n"/>
+      <c r="Y108" s="5" t="inlineStr">
+        <is>
+          <t>credit-support terms | exposure calculations | collateral valuations | counterparty statements</t>
+        </is>
+      </c>
+      <c r="Z108" s="5" t="inlineStr">
+        <is>
+          <t>reconciled, agreement-compliant credit-support positions</t>
+        </is>
+      </c>
+      <c r="AA108" s="5" t="inlineStr">
+        <is>
+          <t>uses-input: Calculate Credit Exposure | enables: Terminate/Novate Counterparty | informed-by: Contract Management</t>
+        </is>
+      </c>
+      <c r="AB108" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC108" s="5" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
       <c r="AD108" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -15198,18 +15446,80 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U109" s="5" t="n"/>
-      <c r="V109" s="5" t="n"/>
-      <c r="W109" s="5" t="n"/>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>Calculate current and, where required by approved methodology, potential future credit exposure for each counterparty and group — aggregating trading positions, mark-to-market values, delivered-but-unpaid and other settlement-cycle exposures, and applicable netting, collateral, and credit-support effects — so limits, monitoring, and credit support run on a defensible exposure number.</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>Covers the exposure measurement process: assembling positions, mark-to-market, and settlement-cycle amounts by counterparty and group; applying enforceable netting and credit-support offsets per the governing agreements; computing potential future exposure where the approved methodology requires it; and publishing exposures to limits, monitoring, and credit support. Exposure measurement may incorporate wrong-way-risk adjustments, concentration considerations, and stressed assumptions where required by approved methodology; portfolio-level analysis remains in Perform Advanced Credit Risk Analytics (CM-1-2-2-1-6). Valuation inputs (curves, marks) are owned by Market Risk Management (CM-1-2-2-3-3, CM-1-2-2-3-15); netting enforceability is a legal determination (Legal &amp; Corporate Communications).</t>
+        </is>
+      </c>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Assemble positions and amounts by counterparty and group | apply enforceable netting and credit-support effects | compute current and methodology-required potential future exposure | publish exposures to limits, monitoring, and credit support</t>
+        </is>
+      </c>
+      <c r="Q109" t="inlineStr">
+        <is>
+          <t>Valuation and curve ownership (CM-1-2-2-3) | netting enforceability determination (Legal &amp; Corporate Communications) | portfolio-level analytics (CM-1-2-2-1-6) | limit decisions (CM-1-2-2-1-2)</t>
+        </is>
+      </c>
+      <c r="R109" t="inlineStr">
+        <is>
+          <t>Credit Exposure Measurement</t>
+        </is>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Batch 11 (2026-09-19). Methodology-qualified at Hamid's direction: potential future exposure, wrong-way-risk adjustments, and stressed assumptions apply where the approved methodology requires them — not silently in every number; the exposure-versus-analytics split with CM-1-2-2-1-6 is preserved. Consumes marks and curves owned by Market Risk; owns the aggregation and offsets. APQC 12893 is a WEAK review-link.</t>
+        </is>
+      </c>
+      <c r="U109" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V109" s="5" t="inlineStr">
+        <is>
+          <t>One defensible exposure number per counterparty, every day.</t>
+        </is>
+      </c>
+      <c r="W109" s="5" t="inlineStr">
+        <is>
+          <t>SRC-CFTC-GLOSS-001 | SRC-ISDA-MA-001 | SRC-CCRO-001</t>
+        </is>
+      </c>
       <c r="X109" s="5" t="n"/>
-      <c r="Y109" s="5" t="n"/>
-      <c r="Z109" s="5" t="n"/>
-      <c r="AA109" s="5" t="n"/>
-      <c r="AB109" s="5" t="n"/>
-      <c r="AC109" s="5" t="n"/>
+      <c r="Y109" s="5" t="inlineStr">
+        <is>
+          <t>positions and mark-to-market | settlement-cycle amounts | netting and credit-support terms</t>
+        </is>
+      </c>
+      <c r="Z109" s="5" t="inlineStr">
+        <is>
+          <t>published current and potential exposures by counterparty and group</t>
+        </is>
+      </c>
+      <c r="AA109" s="5" t="inlineStr">
+        <is>
+          <t>uses-input: Manage Commodity Valuations | enables: Manage Credit Limits | enables: Manage Collateral</t>
+        </is>
+      </c>
+      <c r="AB109" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC109" s="5" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
       <c r="AD109" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -15277,18 +15587,80 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U110" s="5" t="n"/>
-      <c r="V110" s="5" t="n"/>
-      <c r="W110" s="5" t="n"/>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>Administer margin obligations for cleared and other applicable margined positions — receiving, validating, forecasting, and issuing or responding to margin calls as applicable, reconciling margin balances against CCP, exchange, broker, and counterparty statements, and escalating failed or disputed calls — so margin obligations are met and margin held matches what positions require.</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>Covers the margining cycle: validating externally calculated margin requirements and calculating internal forecasts or independent checks where required, issuing or responding to calls within deadlines, reconciling margin balances against CCP, exchange, broker, and counterparty statements, escalating failures and disputes, and forecasting margin requirements for liquidity visibility. Cleared positions arrive from Capture Exchange Trades (CM-1-2-1-3-4); contractual credit support is administered at Manage Collateral (CM-1-2-2-1-3); the cash movements execute through settlement and finance processes (Settle Broker, CM-1-2-4-1-16).</t>
+        </is>
+      </c>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Validate externally calculated margin requirements and run internal forecasts or independent checks where required | issue or respond to margin calls within deadlines | reconcile margin balances against CCP, exchange, broker, and counterparty statements | escalate failures and disputes and forecast requirements</t>
+        </is>
+      </c>
+      <c r="Q110" t="inlineStr">
+        <is>
+          <t>Contractual credit-support administration (CM-1-2-2-1-3) | exchange trade capture (CM-1-2-1-3-4) | margin cash movement execution (CM-1-2-4-1-16, finance processes)</t>
+        </is>
+      </c>
+      <c r="R110" t="inlineStr">
+        <is>
+          <t>Margin Management</t>
+        </is>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Batch 11 (2026-09-19). Reworded at Hamid's direction: the CCP, clearing broker, or exchange typically computes formal margin requirements — this process validates, forecasts, and operates the calls rather than asserting in-house calculation authority for every cleared product. Margin versus credit support split per the -3 rule. APQC 10954 'Perform abandonment' is an unrelated false match.</t>
+        </is>
+      </c>
+      <c r="U110" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V110" s="5" t="inlineStr">
+        <is>
+          <t>Margin obligations are always met, and margin held always matches the positions.</t>
+        </is>
+      </c>
+      <c r="W110" s="5" t="inlineStr">
+        <is>
+          <t>SRC-CFTC-GLOSS-001</t>
+        </is>
+      </c>
       <c r="X110" s="5" t="n"/>
-      <c r="Y110" s="5" t="n"/>
-      <c r="Z110" s="5" t="n"/>
-      <c r="AA110" s="5" t="n"/>
-      <c r="AB110" s="5" t="n"/>
-      <c r="AC110" s="5" t="n"/>
+      <c r="Y110" s="5" t="inlineStr">
+        <is>
+          <t>cleared positions and prices | CCP, exchange, and broker margin statements | margin methodologies and deadlines</t>
+        </is>
+      </c>
+      <c r="Z110" s="5" t="inlineStr">
+        <is>
+          <t>validated, reconciled, escalation-managed margin positions</t>
+        </is>
+      </c>
+      <c r="AA110" s="5" t="inlineStr">
+        <is>
+          <t>follows: Capture Exchange Trades | uses-input: Calculate Credit Exposure | precedes: Settle Broker</t>
+        </is>
+      </c>
+      <c r="AB110" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC110" s="5" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
       <c r="AD110" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -15356,18 +15728,80 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U111" s="5" t="n"/>
-      <c r="V111" s="5" t="n"/>
-      <c r="W111" s="5" t="n"/>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>Analyze credit risk at portfolio level — concentrations, stress and scenario impacts, default-likelihood signals, and correlation effects such as wrong-way exposure — so appetite, limits, and mitigation decisions rest on more than single-counterparty views.</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>Covers portfolio credit analytics: concentration analysis by counterparty group, sector, geography, and product; credit stress testing and scenario impacts; default-likelihood and early-warning modeling; and wrong-way risk analysis where exposure and default likelihood move together. Findings feed limit structures (CM-1-2-2-1-2) and reporting (CM-1-2-2-1-8). Excludes decision-making on risk appetite and portfolio credit concentration limits where those are set by the designated risk-governance body — this node analyzes and recommends; excludes market risk scenarios, owned by Manage And Run Risk Scenarios (CM-1-2-2-3-11) and Conduct Advanced Risk Analytics (CM-1-2-2-3-12); excludes independent model validation (designated validation function).</t>
+        </is>
+      </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Analyze portfolio concentrations | run credit stress tests and scenarios | model default likelihood and early-warning signals | analyze wrong-way risk and recommend mitigation</t>
+        </is>
+      </c>
+      <c r="Q111" t="inlineStr">
+        <is>
+          <t>Risk-appetite and concentration-limit approval (designated risk-governance body) | market risk scenarios and analytics (CM-1-2-2-3-11, CM-1-2-2-3-12) | independent model validation (designated validation function) | limit decisions (CM-1-2-2-1-2)</t>
+        </is>
+      </c>
+      <c r="R111" t="inlineStr">
+        <is>
+          <t>Portfolio Credit Analytics</t>
+        </is>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Batch 11 (2026-09-19). Analyze-and-recommend only: appetite and concentration-limit approval sit with the designated risk-governance body, per Hamid's edit; independent validation not assumed owned here, per the batch 08 precedent. APQC 19568 is a process-control candidate; false lexical match.</t>
+        </is>
+      </c>
+      <c r="U111" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V111" s="5" t="inlineStr">
+        <is>
+          <t>The portfolio's credit weak points are found before a default finds them.</t>
+        </is>
+      </c>
+      <c r="W111" s="5" t="inlineStr">
+        <is>
+          <t>SRC-CCRO-001 | SRC-CFTC-GLOSS-001</t>
+        </is>
+      </c>
       <c r="X111" s="5" t="n"/>
-      <c r="Y111" s="5" t="n"/>
-      <c r="Z111" s="5" t="n"/>
-      <c r="AA111" s="5" t="n"/>
-      <c r="AB111" s="5" t="n"/>
-      <c r="AC111" s="5" t="n"/>
+      <c r="Y111" s="5" t="inlineStr">
+        <is>
+          <t>exposures and limits | counterparty groupings and sectors | stress scenarios | default and ratings data</t>
+        </is>
+      </c>
+      <c r="Z111" s="5" t="inlineStr">
+        <is>
+          <t>portfolio credit analyses with mitigation recommendations</t>
+        </is>
+      </c>
+      <c r="AA111" s="5" t="inlineStr">
+        <is>
+          <t>uses-input: Calculate Credit Exposure | enables: Manage Credit Limits | enables: Manage Credit Risk Reporting</t>
+        </is>
+      </c>
+      <c r="AB111" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC111" s="5" t="inlineStr">
+        <is>
+          <t>periodic</t>
+        </is>
+      </c>
       <c r="AD111" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -15435,18 +15869,80 @@
           <t>strong APQC candidate but no validator agreed</t>
         </is>
       </c>
-      <c r="U112" s="5" t="n"/>
-      <c r="V112" s="5" t="n"/>
-      <c r="W112" s="5" t="n"/>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>Continuously watch counterparty credit — exposures against limits, breach detection and aging, and early-warning signals from ratings, news, payment behavior, and market indicators — escalating breaches and deterioration per policy and triggering reassessment where warranted.</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>Covers continuous credit surveillance: daily exposure-versus-limit monitoring, breach identification, escalation, and tracking to resolution, and early-warning monitoring of deterioration signals that trigger event-driven reviews (CM-1-2-2-1-1) or limit actions (CM-1-2-2-1-2). Excludes the periodic reassessment itself (CM-1-2-2-1-1); excludes limit decisions (CM-1-2-2-1-2); excludes customer credit monitoring in order-to-cash (Monitor Credit Against Limit, CM-1-3-7-4-3).</t>
+        </is>
+      </c>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Monitor exposures against limits daily | detect, escalate, and track breaches | watch early-warning deterioration signals | trigger reviews and limit actions</t>
+        </is>
+      </c>
+      <c r="Q112" t="inlineStr">
+        <is>
+          <t>Periodic credit reassessment (CM-1-2-2-1-1) | limit decisions (CM-1-2-2-1-2) | customer credit monitoring (CM-1-3-7-4-3)</t>
+        </is>
+      </c>
+      <c r="R112" t="inlineStr">
+        <is>
+          <t>Credit Surveillance</t>
+        </is>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Batch 11 (2026-09-19). The detect-versus-decide split: surveillance here, decisions at -1 and -2 — the batch 04 pattern applied to credit. APQC 11215 STRONG with no validator; supporting comparative evidence.</t>
+        </is>
+      </c>
+      <c r="U112" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V112" s="5" t="inlineStr">
+        <is>
+          <t>No breach and no deterioration signal goes unseen or unescalated.</t>
+        </is>
+      </c>
+      <c r="W112" s="5" t="inlineStr">
+        <is>
+          <t>SRC-CCRO-001 | SRC-CFTC-GLOSS-001</t>
+        </is>
+      </c>
       <c r="X112" s="5" t="n"/>
-      <c r="Y112" s="5" t="n"/>
-      <c r="Z112" s="5" t="n"/>
-      <c r="AA112" s="5" t="n"/>
-      <c r="AB112" s="5" t="n"/>
-      <c r="AC112" s="5" t="n"/>
+      <c r="Y112" s="5" t="inlineStr">
+        <is>
+          <t>published exposures and limits | ratings, news, and payment signals | breach policy</t>
+        </is>
+      </c>
+      <c r="Z112" s="5" t="inlineStr">
+        <is>
+          <t>escalated breaches and deterioration alerts with tracking</t>
+        </is>
+      </c>
+      <c r="AA112" s="5" t="inlineStr">
+        <is>
+          <t>uses-input: Calculate Credit Exposure | triggers: Perform Counterparty Credit Reviews | triggers: Manage Credit Limits</t>
+        </is>
+      </c>
+      <c r="AB112" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC112" s="5" t="inlineStr">
+        <is>
+          <t>continuous</t>
+        </is>
+      </c>
       <c r="AD112" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -15514,18 +16010,80 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U113" s="5" t="n"/>
-      <c r="V113" s="5" t="n"/>
-      <c r="W113" s="5" t="n"/>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>Produce governed internal credit-risk reports — exposures, limit utilization, breaches, credit-support and margin positions, and concentrations, at agreed cadences and levels for management and committees — and provide controlled inputs to applicable external or regulatory reporting through their accountable owners, so the credit risk picture is current, consistent, and decision-ready.</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>Covers credit-risk report production and distribution: standard management and committee reporting, breach and exception reporting, credit-support and concentration views, and controlled inputs to external and regulatory reporting owned by their accountable processes. Excludes financial reporting and disclosures, owned by Finance under its locked rule; excludes regulatory filing ownership (Regulatory &amp; Compliance, CM-1-2-4-3); excludes defining enterprise KPIs (KPI workstream).</t>
+        </is>
+      </c>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Produce management and committee credit-risk reporting | report breaches and exceptions | report credit-support, margin, and concentration positions | provide controlled inputs to external reporting through accountable owners</t>
+        </is>
+      </c>
+      <c r="Q113" t="inlineStr">
+        <is>
+          <t>Financial reporting and disclosures (Finance) | regulatory filing ownership (CM-1-2-4-3) | enterprise KPI definition (KPI workstream)</t>
+        </is>
+      </c>
+      <c r="R113" t="inlineStr">
+        <is>
+          <t>Credit Risk Reporting</t>
+        </is>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Batch 11 (2026-09-19). Internal report production here; external and statutory reporting is supported through, never owned instead of, its accountable owners — Hamid's edit prevents reading report production as regulator submission. APQC 10522 is an HR-reporting candidate; false lexical match.</t>
+        </is>
+      </c>
+      <c r="U113" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V113" s="5" t="inlineStr">
+        <is>
+          <t>The credit risk picture reaches its decision-makers current, consistent, and on time.</t>
+        </is>
+      </c>
+      <c r="W113" s="5" t="inlineStr">
+        <is>
+          <t>SRC-CCRO-001</t>
+        </is>
+      </c>
       <c r="X113" s="5" t="n"/>
-      <c r="Y113" s="5" t="n"/>
-      <c r="Z113" s="5" t="n"/>
-      <c r="AA113" s="5" t="n"/>
-      <c r="AB113" s="5" t="n"/>
-      <c r="AC113" s="5" t="n"/>
+      <c r="Y113" s="5" t="inlineStr">
+        <is>
+          <t>exposures, limits, and breaches | credit-support and margin positions | concentration analyses</t>
+        </is>
+      </c>
+      <c r="Z113" s="5" t="inlineStr">
+        <is>
+          <t>distributed, governed credit-risk reports and controlled external-reporting inputs</t>
+        </is>
+      </c>
+      <c r="AA113" s="5" t="inlineStr">
+        <is>
+          <t>uses-input: Monitor &amp; Analyze Credit | uses-input: Perform Advanced Credit Risk Analytics | enables: Trading Strategy Management</t>
+        </is>
+      </c>
+      <c r="AB113" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC113" s="5" t="inlineStr">
+        <is>
+          <t>periodic</t>
+        </is>
+      </c>
       <c r="AD113" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -47367,7 +47925,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -47416,6 +47974,7 @@
         </is>
       </c>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
@@ -48633,6 +49192,53 @@
         </is>
       </c>
       <c r="I32" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>SRC-CCRO-001</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Committee of Chief Risk Officers</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Energy Credit Industry Standards - credit risk best-practices white paper series (incl. Credit Risk Best Practices)</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Series; accessed 2026-09-19</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>https://www.ccro.org/credit-industry-standards</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Industry-practice body</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Energy-trading credit-risk terminology and control-practice context, including counterparty review, limit, exposure, collateral, margin, monitoring, and reporting. Does not determine internal ownership, governance authorities, regulatory obligations, legal enforceability, credit methodology, model assumptions, limit amounts, or customer-credit practices. Evidence only, not text to copy.</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Credit review, limit, exposure, credit-support, and margining practice context for energy trading</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
         <is>
           <t>active</t>
         </is>

--- a/business_architecture/ontology/build/output/step3c-definition-authoring-workbook.xlsx
+++ b/business_architecture/ontology/build/output/step3c-definition-authoring-workbook.xlsx
@@ -16997,18 +16997,80 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U120" s="5" t="n"/>
-      <c r="V120" s="5" t="n"/>
-      <c r="W120" s="5" t="n"/>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>The capability to independently measure, control, monitor, analyze, and report market risk in the trading book by governing risk-book structures, delegated authority, market-data inputs, valuations, limits, control cycles, positions, profit and loss, scenarios, and risk reporting.</t>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>Covers the independent market-risk control over the trading book: control-framework structures (risk-book structure, delegation of authority, risk limits), market-data and valuation ownership (curves, volatilities and correlations, commodity valuations), the daily and monthly control cycles, risk measurement and monitoring, position and P&amp;L control, risk-policy compliance monitoring, scenarios, advanced analytics, and reporting. An independent control function per the approved L3 definition; the delivery model is not prescribed. Excludes enterprise-wide strategic commodity-price risk, corporate hedging policy, capital allocation, and non-trading operating exposure unless those exposures are expressly booked into the governed trading portfolio. Excludes trading decisions and strategy stewardship, which are governed by these controls (CM-1-2-1-4); excludes credit risk (CM-1-2-2-1); excludes regulatory trading compliance (CM-1-2-4-3); excludes accounting P&amp;L and its reconciliation ownership (Accounting, CM-1-2-4-2, with the economic-to-accounting reconciliation at CM-1-2-4-2-6); excludes independent model validation (designated validation function).</t>
+        </is>
+      </c>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>Maintain risk-book structure, delegation of authority, and risk limits | own curves, volatilities, and valuations | run daily and monthly control cycles | measure, monitor, and analyze market risk, positions, and P&amp;L | report the risk picture</t>
+        </is>
+      </c>
+      <c r="Q120" t="inlineStr">
+        <is>
+          <t>Enterprise-wide commodity-price risk, corporate hedging policy, and non-trading exposure not booked into the trading portfolio | trading decisions and strategy stewardship (CM-1-2-1-4) | credit risk (CM-1-2-2-1) | regulatory trading compliance (CM-1-2-4-3) | accounting P&amp;L (CM-1-2-4-2) | independent model validation (designated validation function)</t>
+        </is>
+      </c>
+      <c r="R120" t="inlineStr">
+        <is>
+          <t>Trading Market Risk Control</t>
+        </is>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>Batch 12 (2026-09-19). Concept type: capability (Hamid confirmed), per the batch 11 reasoning — concurrent heterogeneous control processes, no single lifecycle. Bound explicitly to the trading book at Hamid's direction: refinery-margin, procurement-price, inventory, and corporate hedging exposures are governed here only when expressly booked into the governed trading portfolio; whether a separate corporate hedging program exists is a follow-up noted in the batch 12 PR. Middle-office framing per the approved L3 definition names the control function, not a mandated organization (batch 10 neutrality). APQC 20711 is an IT-risk candidate; comparative evidence only.</t>
+        </is>
+      </c>
+      <c r="U120" s="5" t="inlineStr">
+        <is>
+          <t>capability</t>
+        </is>
+      </c>
+      <c r="V120" s="5" t="inlineStr">
+        <is>
+          <t>Losses from market moves in the trading book are measured, bounded, and visible before they compound.</t>
+        </is>
+      </c>
+      <c r="W120" s="5" t="inlineStr">
+        <is>
+          <t>SRC-CCRO-002A | SRC-CFTC-GLOSS-001</t>
+        </is>
+      </c>
       <c r="X120" s="5" t="n"/>
-      <c r="Y120" s="5" t="n"/>
-      <c r="Z120" s="5" t="n"/>
-      <c r="AA120" s="5" t="n"/>
-      <c r="AB120" s="5" t="n"/>
-      <c r="AC120" s="5" t="n"/>
+      <c r="Y120" s="5" t="inlineStr">
+        <is>
+          <t>captured positions | market prices and data | risk appetite and policy | governance decisions</t>
+        </is>
+      </c>
+      <c r="Z120" s="5" t="inlineStr">
+        <is>
+          <t>measured, bounded, visible trading-book market risk with governed control structures</t>
+        </is>
+      </c>
+      <c r="AA120" s="5" t="inlineStr">
+        <is>
+          <t>governed-by: Regulatory &amp; Compliance | enables: Trading Strategy Management | enables: Trade Capture</t>
+        </is>
+      </c>
+      <c r="AB120" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC120" s="5" t="inlineStr">
+        <is>
+          <t>continuous</t>
+        </is>
+      </c>
       <c r="AD120" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -17076,18 +17138,80 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U121" s="5" t="n"/>
-      <c r="V121" s="5" t="n"/>
-      <c r="W121" s="5" t="n"/>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>Establish and maintain the governed trading-book and portfolio hierarchy used for risk aggregation, valuation, position control, and P&amp;L reporting — defining risk-reporting book attributes, responsible owners, aggregation relationships, and effective-dated changes — and keep trading, risk, and reporting systems aligned to it.</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>Covers governance of the risk-reporting and control structure: defining risk books with their attributes, owners, and aggregation relationships; controlling openings, closures, and moves with approvals and effective dates; and keeping capture, risk, and reporting systems aligned to one structure. Trading Strategy Management (CM-1-2-1-4) defines and stewards business strategies; Trade Capture (CM-1-2-1-3) assigns individual deals into the approved structure; this process governs the risk-reporting and control hierarchy that strategies and deals map into. Excludes legal-entity, ledger, cost-center, profit-center, and chart-of-accounts structures, owned by Accounting (CM-1-2-4-2-8).</t>
+        </is>
+      </c>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>Define risk books, attributes, owners, and aggregation relationships | control structure changes with approvals and effective dates | keep capture, risk, and reporting aligned to one structure | maintain structure history</t>
+        </is>
+      </c>
+      <c r="Q121" t="inlineStr">
+        <is>
+          <t>Business strategy definition and stewardship (CM-1-2-1-4) | deal-to-book assignment at capture (CM-1-2-1-3) | legal-entity, ledger, and chart-of-accounts structures (CM-1-2-4-2-8)</t>
+        </is>
+      </c>
+      <c r="R121" t="inlineStr">
+        <is>
+          <t>Risk Book Structure Governance</t>
+        </is>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>Batch 12 (2026-09-19). Narrowed at Hamid's direction: strategy is business intent (Trading Strategy Management); the book is a controlled risk and P&amp;L aggregation construct governed here — the two never collide. APQC 16385 is a generic framework candidate.</t>
+        </is>
+      </c>
+      <c r="U121" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V121" s="5" t="inlineStr">
+        <is>
+          <t>One governed risk-reporting structure that every position and P&amp;L number rolls up through.</t>
+        </is>
+      </c>
+      <c r="W121" s="5" t="inlineStr">
+        <is>
+          <t>SRC-CCRO-002A</t>
+        </is>
+      </c>
       <c r="X121" s="5" t="n"/>
-      <c r="Y121" s="5" t="n"/>
-      <c r="Z121" s="5" t="n"/>
-      <c r="AA121" s="5" t="n"/>
-      <c r="AB121" s="5" t="n"/>
-      <c r="AC121" s="5" t="n"/>
+      <c r="Y121" s="5" t="inlineStr">
+        <is>
+          <t>structure change requests | ownership and aggregation assignments</t>
+        </is>
+      </c>
+      <c r="Z121" s="5" t="inlineStr">
+        <is>
+          <t>governed, versioned risk-book and portfolio hierarchy</t>
+        </is>
+      </c>
+      <c r="AA121" s="5" t="inlineStr">
+        <is>
+          <t>enables: Trade Capture | enables: Perform Position &amp; PNL Analysis</t>
+        </is>
+      </c>
+      <c r="AB121" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC121" s="5" t="inlineStr">
+        <is>
+          <t>periodic</t>
+        </is>
+      </c>
       <c r="AD121" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -17155,18 +17279,80 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U122" s="5" t="n"/>
-      <c r="V122" s="5" t="n"/>
-      <c r="W122" s="5" t="n"/>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>Establish and maintain the trading delegation of authority — who may trade what products, instruments, tenors, and sizes, and which approvals are required beyond each authority — keeping it current with roles, strategies, and governance decisions so every trade's authorization has a defined basis.</t>
+        </is>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>Covers the authority framework: defining and documenting delegated trading authorities by role, product, instrument, tenor, and size; maintaining them as people, strategies, and appetite change; and publishing them to the processes that apply them. The DOA is applied — never set — by Obtain Trade Approval (CM-1-2-1-3-2) and aligned to by Trading Strategy Management (CM-1-2-1-4), per the batch 07-08 decisions; authority levels derive from governance decisions owned by the designated risk-governance body. Excludes HR role administration; excludes system access provisioning (Process Excellence &amp; IT).</t>
+        </is>
+      </c>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>Define and document delegated authorities by role, product, instrument, tenor, and size | maintain authorities as roles, strategies, and appetite change | publish the DOA to the applying processes | keep authority history auditable</t>
+        </is>
+      </c>
+      <c r="Q122" t="inlineStr">
+        <is>
+          <t>Applying the DOA to individual trades (CM-1-2-1-3-2) | risk-appetite decisions (designated risk-governance body) | HR role administration | system access provisioning (Process Excellence &amp; IT)</t>
+        </is>
+      </c>
+      <c r="R122" t="inlineStr">
+        <is>
+          <t>Trading Delegation of Authority Management</t>
+        </is>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>Batch 12 (2026-09-19). Set here, applied at CM-1-2-1-3-2 — closing the set-versus-apply loop recorded in batches 07-09. Which body owns risk appetite and final limit-exception approval is a follow-up noted in the batch 12 PR. APQC 16385 is a generic framework candidate.</t>
+        </is>
+      </c>
+      <c r="U122" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V122" s="5" t="inlineStr">
+        <is>
+          <t>Every trade's authorization has a defined, current, auditable basis.</t>
+        </is>
+      </c>
+      <c r="W122" s="5" t="inlineStr">
+        <is>
+          <t>SRC-CCRO-002A</t>
+        </is>
+      </c>
       <c r="X122" s="5" t="n"/>
-      <c r="Y122" s="5" t="n"/>
-      <c r="Z122" s="5" t="n"/>
-      <c r="AA122" s="5" t="n"/>
-      <c r="AB122" s="5" t="n"/>
-      <c r="AC122" s="5" t="n"/>
+      <c r="Y122" s="5" t="inlineStr">
+        <is>
+          <t>governance and appetite decisions | role and strategy changes</t>
+        </is>
+      </c>
+      <c r="Z122" s="5" t="inlineStr">
+        <is>
+          <t>current, published, auditable delegation of authority</t>
+        </is>
+      </c>
+      <c r="AA122" s="5" t="inlineStr">
+        <is>
+          <t>enables: Obtain Trade Approval | enables: Trading Strategy Management | governed-by: Regulatory &amp; Compliance</t>
+        </is>
+      </c>
+      <c r="AB122" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC122" s="5" t="inlineStr">
+        <is>
+          <t>periodic</t>
+        </is>
+      </c>
       <c r="AD122" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -17234,18 +17420,80 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U123" s="5" t="n"/>
-      <c r="V123" s="5" t="n"/>
-      <c r="W123" s="5" t="n"/>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>Construct and maintain the forward price curves the organization values and measures risk with — sourcing market data, building and validating curves by commodity, location, and tenor per approved methodology, and publishing the official curve set on the control calendar.</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>Covers curve ownership: market-data sourcing and quality checks, curve construction per approved methodology including illiquid-tenor and basis treatment, validation and exception handling, and publication of the official daily curve set consumed by valuation, risk measurement, credit exposure (CM-1-2-2-1-4), and revenue projection (CM-1-2-1-1-5). Curve methodology approval and independent validation sit with the designated governance and validation functions — this process constructs and publishes, it does not approve its own methodology. Excludes market-data vendor selection and licensing, which sit with the applicable procurement and Process Excellence &amp; IT processes per the operating model; excludes volatilities and correlations (CM-1-2-2-3-14).</t>
+        </is>
+      </c>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>Source and quality-check market data | construct curves per approved methodology | validate curves and handle exceptions | publish the official curve set on the control calendar</t>
+        </is>
+      </c>
+      <c r="Q123" t="inlineStr">
+        <is>
+          <t>Curve methodology approval and independent validation (designated governance and validation functions) | market-data vendor selection and licensing (procurement, Process Excellence &amp; IT) | volatilities and correlations (CM-1-2-2-3-14) | trading views on prices (front office)</t>
+        </is>
+      </c>
+      <c r="R123" t="inlineStr">
+        <is>
+          <t>Forward Curve Management</t>
+        </is>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>Batch 12 (2026-09-19). The curves consumed by batches 07 and 11 are owned here; methodology-qualified per the batch 11 discipline. Market-data vendor and licensing ownership is a follow-up noted in the batch 12 PR. APQC 11743 is an unrelated routing candidate.</t>
+        </is>
+      </c>
+      <c r="U123" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V123" s="5" t="inlineStr">
+        <is>
+          <t>One official, defensible curve set that everything values against.</t>
+        </is>
+      </c>
+      <c r="W123" s="5" t="inlineStr">
+        <is>
+          <t>SRC-CCRO-002A | SRC-CFTC-GLOSS-001</t>
+        </is>
+      </c>
       <c r="X123" s="5" t="n"/>
-      <c r="Y123" s="5" t="n"/>
-      <c r="Z123" s="5" t="n"/>
-      <c r="AA123" s="5" t="n"/>
-      <c r="AB123" s="5" t="n"/>
-      <c r="AC123" s="5" t="n"/>
+      <c r="Y123" s="5" t="inlineStr">
+        <is>
+          <t>market prices and broker quotes | curve methodologies | control calendar</t>
+        </is>
+      </c>
+      <c r="Z123" s="5" t="inlineStr">
+        <is>
+          <t>published official curve set</t>
+        </is>
+      </c>
+      <c r="AA123" s="5" t="inlineStr">
+        <is>
+          <t>enables: Manage Commodity Valuations | enables: Calculate Credit Exposure | enables: Measure Risk</t>
+        </is>
+      </c>
+      <c r="AB123" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC123" s="5" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
       <c r="AD123" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -17313,18 +17561,80 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U124" s="5" t="n"/>
-      <c r="V124" s="5" t="n"/>
-      <c r="W124" s="5" t="n"/>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>Coordinate and evidence the daily trading-risk control cycle — performing or obtaining capture-completeness checks, freezing the official market-data set, running or obtaining valuation, position, P&amp;L, and risk-measure outputs, investigating material exceptions, and obtaining the designated control approvals for the daily controlled result.</t>
+        </is>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>Covers the end-of-day control cycle as coordinated orchestration: capture-completeness checks performed or obtained from their owners, the official market-data and curve freeze, valuation and risk runs, position and P&amp;L production, material-exception investigation, and the designated control approvals — which may sit with different functions (front-office attestation of completeness, risk sign-off of control results, operations validation of settlement status) per the operating model; no single universal sign-off authority is asserted. Orchestrates outputs owned by the sibling processes (curves at CM-1-2-2-3-3, valuations at CM-1-2-2-3-15, measures at CM-1-2-2-3-7, position and P&amp;L at CM-1-2-2-3-9) without owning their methodologies. Excludes the monthly cycle (CM-1-2-2-3-5); excludes accounting close (CM-1-2-4-2).</t>
+        </is>
+      </c>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>Perform or obtain capture-completeness checks | freeze the official market-data set | run or obtain valuation, position, P&amp;L, and risk outputs | investigate material exceptions and obtain designated control approvals</t>
+        </is>
+      </c>
+      <c r="Q124" t="inlineStr">
+        <is>
+          <t>Methodology and output ownership (sibling processes) | monthly cycle (CM-1-2-2-3-5) | accounting close (CM-1-2-4-2)</t>
+        </is>
+      </c>
+      <c r="R124" t="inlineStr">
+        <is>
+          <t>Daily Risk Control Cycle</t>
+        </is>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>Batch 12 (2026-09-19). Reworded at Hamid's direction: the cycle is coordinated and evidenced with designated control approvals rather than a single universal sign-off — different functions may attest different elements per the operating model. An orchestration process over sibling-owned outputs. APQC 19568 is a process-control candidate; false lexical match.</t>
+        </is>
+      </c>
+      <c r="U124" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V124" s="5" t="inlineStr">
+        <is>
+          <t>Every trading day closes once, evidenced, with its designated approvals obtained.</t>
+        </is>
+      </c>
+      <c r="W124" s="5" t="inlineStr">
+        <is>
+          <t>SRC-CCRO-002A</t>
+        </is>
+      </c>
       <c r="X124" s="5" t="n"/>
-      <c r="Y124" s="5" t="n"/>
-      <c r="Z124" s="5" t="n"/>
-      <c r="AA124" s="5" t="n"/>
-      <c r="AB124" s="5" t="n"/>
-      <c r="AC124" s="5" t="n"/>
+      <c r="Y124" s="5" t="inlineStr">
+        <is>
+          <t>captured trades | market data and curves | exception reports</t>
+        </is>
+      </c>
+      <c r="Z124" s="5" t="inlineStr">
+        <is>
+          <t>evidenced daily controlled result with designated approvals</t>
+        </is>
+      </c>
+      <c r="AA124" s="5" t="inlineStr">
+        <is>
+          <t>uses-input: Setup And Manage Curves | uses-input: Manage Commodity Valuations | precedes: Perform End-of-Month (EOM) Process</t>
+        </is>
+      </c>
+      <c r="AB124" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC124" s="5" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
       <c r="AD124" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -17392,18 +17702,80 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U125" s="5" t="n"/>
-      <c r="V125" s="5" t="n"/>
-      <c r="W125" s="5" t="n"/>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>Coordinate and evidence the month-end trading-risk control cycle — reconciling and reviewing the month's daily controlled results, producing month-end economic valuation, position, P&amp;L, and risk outputs, resolving or formally carrying forward approved exceptions — and provide the controlled economic inputs required by Accounting's reconciliation and close processes.</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>Covers the end-of-month control cycle: month-end valuation and risk runs, reconciliation and review of daily controlled results across the month, resolution or documented carry-forward of approved exceptions, provision of the controlled economic inputs to Reconcile Economic PNL To Accounting PNL (CM-1-2-4-2-6) and to reporting, and the designated month-end control approvals per the operating model. Excludes the accounting close and postings, owned by Accounting (CM-1-2-4-2); excludes reconciliation ownership itself — CM-1-2-4-2-6 owns the economic-to-accounting reconciliation and this process supplies the economic side, a boundary the Settlements &amp; Accounting batch inherits.</t>
+        </is>
+      </c>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>Run month-end valuations and risk measures | reconcile and review the month's daily controlled results | resolve or formally carry forward approved exceptions | provide controlled economic inputs to Accounting's reconciliation and close</t>
+        </is>
+      </c>
+      <c r="Q125" t="inlineStr">
+        <is>
+          <t>Accounting close and postings (CM-1-2-4-2) | economic-to-accounting reconciliation ownership (CM-1-2-4-2-6) | financial reporting (Finance)</t>
+        </is>
+      </c>
+      <c r="R125" t="inlineStr">
+        <is>
+          <t>Monthly Risk Control Cycle</t>
+        </is>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>Batch 12 (2026-09-19). Reworded at Hamid's direction: coordinated and evidenced with designated approvals, and framed as the economic-input provider to Accounting's reconciliation and close — supply, never ownership, of CM-1-2-4-2-6's economic side. APQC 19568 false lexical match.</t>
+        </is>
+      </c>
+      <c r="U125" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V125" s="5" t="inlineStr">
+        <is>
+          <t>The month closes once, reconciled, with risk and accounting telling one story.</t>
+        </is>
+      </c>
+      <c r="W125" s="5" t="inlineStr">
+        <is>
+          <t>SRC-CCRO-002A</t>
+        </is>
+      </c>
       <c r="X125" s="5" t="n"/>
-      <c r="Y125" s="5" t="n"/>
-      <c r="Z125" s="5" t="n"/>
-      <c r="AA125" s="5" t="n"/>
-      <c r="AB125" s="5" t="n"/>
-      <c r="AC125" s="5" t="n"/>
+      <c r="Y125" s="5" t="inlineStr">
+        <is>
+          <t>evidenced daily results | month-end market data | accounting calendar</t>
+        </is>
+      </c>
+      <c r="Z125" s="5" t="inlineStr">
+        <is>
+          <t>evidenced month-end economic result set with controlled inputs to Accounting</t>
+        </is>
+      </c>
+      <c r="AA125" s="5" t="inlineStr">
+        <is>
+          <t>follows: Perform End-of-day (EOD) Process | enables: Reconcile Economic PNL To Accounting PNL | enables: Manage Risk Reporting</t>
+        </is>
+      </c>
+      <c r="AB125" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC125" s="5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AD125" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -17471,18 +17843,80 @@
           <t>strong APQC candidate but no validator agreed</t>
         </is>
       </c>
-      <c r="U126" s="5" t="n"/>
-      <c r="V126" s="5" t="n"/>
-      <c r="W126" s="5" t="n"/>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>Establish, maintain, publish, and adjust market-risk limits — by book, strategy, commodity, tenor, and measure — derived from approved risk appetite; administer documented temporary-excess and exception decisions under delegated authority; and tighten or suspend limits when conditions or policy triggers require it.</t>
+        </is>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>Covers the market-risk limit lifecycle: establishing limits from appetite across the measures the approved framework uses (such as value-at-risk, position, stop-loss, and tenor limits), publishing them to the applying and monitoring processes, administering and recording temporary-excess approvals under the delegation of authority, and adjusting limits on regime change or deterioration. Enforcement occurs through connected controls — pre-trade checks, monitoring and escalation (CM-1-2-2-3-8), and policy-compliance monitoring (CM-1-2-2-3-10). Risk appetite itself is set by the designated risk-governance body. Excludes credit limits (CM-1-2-2-1-2).</t>
+        </is>
+      </c>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>Establish and structure market-risk limits from approved appetite | publish limits to applying and monitoring processes | administer and record temporary-excess decisions under delegated authority | tighten or suspend limits on triggers</t>
+        </is>
+      </c>
+      <c r="Q126" t="inlineStr">
+        <is>
+          <t>Risk-appetite setting (designated risk-governance body) | limit enforcement through connected controls (CM-1-2-2-3-8, CM-1-2-2-3-10, pre-trade checks) | credit limits (CM-1-2-2-1-2)</t>
+        </is>
+      </c>
+      <c r="R126" t="inlineStr">
+        <is>
+          <t>Market Risk Limit Administration</t>
+        </is>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>Batch 12 (2026-09-19). Mirrors the batch 11 credit-limits rule exactly: establish, publish, administer; enforcement through connected controls; appetite above. APQC 11211 STRONG with no validator; supporting comparative evidence.</t>
+        </is>
+      </c>
+      <c r="U126" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V126" s="5" t="inlineStr">
+        <is>
+          <t>Market exposure capacity always matches approved appetite.</t>
+        </is>
+      </c>
+      <c r="W126" s="5" t="inlineStr">
+        <is>
+          <t>SRC-CCRO-002A | SRC-CFTC-GLOSS-001</t>
+        </is>
+      </c>
       <c r="X126" s="5" t="n"/>
-      <c r="Y126" s="5" t="n"/>
-      <c r="Z126" s="5" t="n"/>
-      <c r="AA126" s="5" t="n"/>
-      <c r="AB126" s="5" t="n"/>
-      <c r="AC126" s="5" t="n"/>
+      <c r="Y126" s="5" t="inlineStr">
+        <is>
+          <t>approved risk appetite | risk measures and utilization | governance decisions</t>
+        </is>
+      </c>
+      <c r="Z126" s="5" t="inlineStr">
+        <is>
+          <t>current, approved, published market-risk limits and exception decisions</t>
+        </is>
+      </c>
+      <c r="AA126" s="5" t="inlineStr">
+        <is>
+          <t>enables: Monitor Risk | enables: Trading Strategy Management | informed-by: Measure Risk</t>
+        </is>
+      </c>
+      <c r="AB126" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC126" s="5" t="inlineStr">
+        <is>
+          <t>continuous</t>
+        </is>
+      </c>
       <c r="AD126" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -17550,18 +17984,80 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U127" s="5" t="n"/>
-      <c r="V127" s="5" t="n"/>
-      <c r="W127" s="5" t="n"/>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>Compute the organization's market-risk measures — value-at-risk, sensitivities, position and tenor exposures, and the other measures the approved framework requires — from validated positions, curves, and volatilities, publishing them on the control calendar so limits, monitoring, and reporting run on one measured picture.</t>
+        </is>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>Covers risk measurement: running the approved measures per methodology against validated inputs, quality-checking and explaining day-on-day moves, and publishing results to monitoring (CM-1-2-2-3-8), limits (CM-1-2-2-3-6), and reporting (CM-1-2-2-3-13). Which measures apply is set by the approved framework; measure methodologies and their independent validation sit with the designated governance and validation functions. Excludes scenario and stress analysis (CM-1-2-2-3-11); excludes credit exposure measurement (CM-1-2-2-1-4).</t>
+        </is>
+      </c>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>Run approved risk measures per methodology | quality-check and explain measure movements | publish measures on the control calendar | maintain measurement input traceability</t>
+        </is>
+      </c>
+      <c r="Q127" t="inlineStr">
+        <is>
+          <t>Measure methodology approval and independent validation (designated functions) | scenario and stress analysis (CM-1-2-2-3-11) | credit exposure (CM-1-2-2-1-4)</t>
+        </is>
+      </c>
+      <c r="R127" t="inlineStr">
+        <is>
+          <t>Market Risk Measurement</t>
+        </is>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>Batch 12 (2026-09-19). Methodology-qualified per the batch 11 discipline: the measures the approved framework requires, never an asserted universal metric set. APQC 16436 is a generic benchmarking candidate.</t>
+        </is>
+      </c>
+      <c r="U127" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V127" s="5" t="inlineStr">
+        <is>
+          <t>One measured, methodology-true risk picture per control cycle.</t>
+        </is>
+      </c>
+      <c r="W127" s="5" t="inlineStr">
+        <is>
+          <t>SRC-CCRO-002A | SRC-CFTC-GLOSS-001</t>
+        </is>
+      </c>
       <c r="X127" s="5" t="n"/>
-      <c r="Y127" s="5" t="n"/>
-      <c r="Z127" s="5" t="n"/>
-      <c r="AA127" s="5" t="n"/>
-      <c r="AB127" s="5" t="n"/>
-      <c r="AC127" s="5" t="n"/>
+      <c r="Y127" s="5" t="inlineStr">
+        <is>
+          <t>validated positions | official curves and volatilities | approved measure methodologies</t>
+        </is>
+      </c>
+      <c r="Z127" s="5" t="inlineStr">
+        <is>
+          <t>published market-risk measures</t>
+        </is>
+      </c>
+      <c r="AA127" s="5" t="inlineStr">
+        <is>
+          <t>uses-input: Setup And Manage Curves | uses-input: Manage Volatilities And Correlations | enables: Monitor Risk</t>
+        </is>
+      </c>
+      <c r="AB127" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC127" s="5" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
       <c r="AD127" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -17629,18 +18125,80 @@
           <t>strong APQC candidate but no validator agreed</t>
         </is>
       </c>
-      <c r="U128" s="5" t="n"/>
-      <c r="V128" s="5" t="n"/>
-      <c r="W128" s="5" t="n"/>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>Continuously watch market risk against limits — detecting breaches and near-breaches, escalating them per policy, tracking them to resolution, and watching concentration and regime signals — so no excursion goes unseen or unescalated.</t>
+        </is>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>Covers market-risk surveillance: measure-versus-limit monitoring, breach and near-breach detection, escalation and resolution tracking, and watching for concentrations and market-regime changes that warrant limit or appetite review. The detect-versus-decide split holds: this process surfaces; limit actions are taken at Manage Risk Limits (CM-1-2-2-3-6) and appetite questions go to the risk-governance body. Excludes credit surveillance (CM-1-2-2-1-7); excludes risk-policy compliance monitoring (CM-1-2-2-3-10).</t>
+        </is>
+      </c>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>Monitor measures against limits | detect and escalate breaches and near-breaches | track breaches to resolution | watch concentration and regime signals</t>
+        </is>
+      </c>
+      <c r="Q128" t="inlineStr">
+        <is>
+          <t>Limit decisions (CM-1-2-2-3-6) | appetite decisions (risk-governance body) | credit surveillance (CM-1-2-2-1-7) | policy-compliance monitoring (CM-1-2-2-3-10)</t>
+        </is>
+      </c>
+      <c r="R128" t="inlineStr">
+        <is>
+          <t>Market Risk Surveillance</t>
+        </is>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>Batch 12 (2026-09-19). The batch 04 detect-versus-decide pattern, as applied to credit in batch 11. APQC 20729 is an IT-risk candidate; false lexical match.</t>
+        </is>
+      </c>
+      <c r="U128" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V128" s="5" t="inlineStr">
+        <is>
+          <t>No limit excursion goes unseen or unescalated.</t>
+        </is>
+      </c>
+      <c r="W128" s="5" t="inlineStr">
+        <is>
+          <t>SRC-CCRO-002A</t>
+        </is>
+      </c>
       <c r="X128" s="5" t="n"/>
-      <c r="Y128" s="5" t="n"/>
-      <c r="Z128" s="5" t="n"/>
-      <c r="AA128" s="5" t="n"/>
-      <c r="AB128" s="5" t="n"/>
-      <c r="AC128" s="5" t="n"/>
+      <c r="Y128" s="5" t="inlineStr">
+        <is>
+          <t>published risk measures | current limits | escalation policy</t>
+        </is>
+      </c>
+      <c r="Z128" s="5" t="inlineStr">
+        <is>
+          <t>escalated, tracked limit excursions and regime alerts</t>
+        </is>
+      </c>
+      <c r="AA128" s="5" t="inlineStr">
+        <is>
+          <t>uses-input: Measure Risk | triggers: Manage Risk Limits | enables: Manage Risk Reporting</t>
+        </is>
+      </c>
+      <c r="AB128" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC128" s="5" t="inlineStr">
+        <is>
+          <t>continuous</t>
+        </is>
+      </c>
       <c r="AD128" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -17708,18 +18266,80 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U129" s="5" t="n"/>
-      <c r="V129" s="5" t="n"/>
-      <c r="W129" s="5" t="n"/>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>Produce and analyze the official, controlled position and realized and unrealized P&amp;L picture — explaining daily P&amp;L by its drivers (price, position, new deals, amendments, and other effects), investigating unexplained amounts, and delivering the validated P&amp;L that management, risk, and the accounting reconciliation consume.</t>
+        </is>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>Covers official position and P&amp;L production and attribution: daily P&amp;L explanation by driver, unexplained-P&amp;L investigation and thresholds, position validation against capture, and delivery of the controlled result to management, reporting, and Reconcile Economic PNL To Accounting PNL (CM-1-2-4-2-6). This is the official, controlled figure that batch 07's Forecast Revenue explicitly defers to — the forward-looking projection lives there (CM-1-2-1-1-5); the governed result lives here. Excludes accounting P&amp;L and postings, owned by Accounting (CM-1-2-4-2); excludes valuation methodology (CM-1-2-2-3-15).</t>
+        </is>
+      </c>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>Produce the official controlled position and P&amp;L | attribute P&amp;L to drivers and investigate unexplained amounts | validate positions against capture | deliver controlled results to management, reporting, and reconciliation</t>
+        </is>
+      </c>
+      <c r="Q129" t="inlineStr">
+        <is>
+          <t>Forward revenue projection (CM-1-2-1-1-5) | accounting P&amp;L and postings (CM-1-2-4-2) | valuation methodology (CM-1-2-2-3-15)</t>
+        </is>
+      </c>
+      <c r="R129" t="inlineStr">
+        <is>
+          <t>Position &amp; P&amp;L Control | P&amp;L Attribution</t>
+        </is>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>Batch 12 (2026-09-19). Closes the batch 07 deferral: projected economics at CM-1-2-1-1-5, official controlled results here, accounting results at CM-1-2-4-2, reconciled at CM-1-2-4-2-6. Business-facing label 'Perform Position &amp; P&amp;L Analysis' queued for the naming pass per Hamid — 'PNL' retained in the technical label, 'P&amp;L' used in prose. APQC 11783 is the competitive-analysis false match batch 02 already rejected.</t>
+        </is>
+      </c>
+      <c r="U129" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V129" s="5" t="inlineStr">
+        <is>
+          <t>One official P&amp;L per day, explained to its drivers.</t>
+        </is>
+      </c>
+      <c r="W129" s="5" t="inlineStr">
+        <is>
+          <t>SRC-CCRO-002A | SRC-CFTC-GLOSS-001</t>
+        </is>
+      </c>
       <c r="X129" s="5" t="n"/>
-      <c r="Y129" s="5" t="n"/>
-      <c r="Z129" s="5" t="n"/>
-      <c r="AA129" s="5" t="n"/>
-      <c r="AB129" s="5" t="n"/>
-      <c r="AC129" s="5" t="n"/>
+      <c r="Y129" s="5" t="inlineStr">
+        <is>
+          <t>validated positions and valuations | prior-day results | deal activity</t>
+        </is>
+      </c>
+      <c r="Z129" s="5" t="inlineStr">
+        <is>
+          <t>official, explained daily position and P&amp;L</t>
+        </is>
+      </c>
+      <c r="AA129" s="5" t="inlineStr">
+        <is>
+          <t>uses-input: Manage Commodity Valuations | enables: Reconcile Economic PNL To Accounting PNL | enables: Manage Risk Reporting</t>
+        </is>
+      </c>
+      <c r="AB129" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC129" s="5" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
       <c r="AD129" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -17787,15 +18407,87 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U130" s="5" t="n"/>
-      <c r="V130" s="5" t="n"/>
-      <c r="W130" s="5" t="n"/>
-      <c r="X130" s="5" t="n"/>
-      <c r="Y130" s="5" t="n"/>
-      <c r="Z130" s="5" t="n"/>
-      <c r="AA130" s="5" t="n"/>
-      <c r="AB130" s="5" t="n"/>
-      <c r="AC130" s="5" t="n"/>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>Monitor adherence to the organization's own market-risk policies and control framework — mandate and delegation-of-authority adherence, control-cycle completion, exception-procedure use, and policy-required documentation — surfacing violations and control gaps to the accountable owners.</t>
+        </is>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>Covers internal risk-policy compliance monitoring: checking that trading activity stays within mandates and the delegation of authority, that control cycles complete with their designated approvals, that exceptions follow their documented procedures, and that policy-required records exist; escalating violations and recurring gaps. The boundary with regulatory compliance is internal-versus-external rules: adherence to the organization's own risk framework is monitored here; compliance with external law, regulation, and market rules is owned by Regulatory &amp; Compliance (CM-1-2-4-3). Excludes policy authorship (risk governance) and disciplinary action (management, HR).</t>
+        </is>
+      </c>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>Monitor mandate and DOA adherence | verify control-cycle completion and designated approvals | check exception-procedure use and documentation | escalate violations and control gaps</t>
+        </is>
+      </c>
+      <c r="Q130" t="inlineStr">
+        <is>
+          <t>Regulatory compliance monitoring (CM-1-2-4-3) | policy authorship (risk governance) | disciplinary action (management, HR)</t>
+        </is>
+      </c>
+      <c r="R130" t="inlineStr">
+        <is>
+          <t>Risk Framework Compliance Monitoring</t>
+        </is>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>Batch 12 (2026-09-19). Fully drafted and conditionally approved by Hamid; held pending on the recorded cross-batch dependency because an approved row may carry no material open question. Internal-versus-external rules is the boundary with CM-1-2-4-3.</t>
+        </is>
+      </c>
+      <c r="U130" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V130" s="5" t="inlineStr">
+        <is>
+          <t>The risk framework is followed in fact, not just on paper.</t>
+        </is>
+      </c>
+      <c r="W130" s="5" t="inlineStr">
+        <is>
+          <t>SRC-CCRO-002A</t>
+        </is>
+      </c>
+      <c r="X130" s="5" t="inlineStr">
+        <is>
+          <t>Question: What is the precise boundary between Monitor Risk Policy Compliance and the future Monitor Internal Trade Controls (CM-1-2-4-3-4)?
+Context: This node monitors adherence to the internal market-risk framework (risk appetite, approved limits, book mandates, DOA, valuation and risk-control procedures, control-cycle evidence, exception approvals). Monitor Internal Trade Controls must be defined in the Regulatory &amp; Compliance batch as compliance-control monitoring for internally implemented controls that support external obligations (required deal approvals, audit evidence, reporting controls, market-conduct and surveillance controls).
+Options:
+A) The internal-versus-external-rules split holds as drafted, and CM-1-2-4-3-4 is defined with a reciprocal scope exclusion so neither node tests the other's framework.
+B) The future CM-1-2-4-3-4 definition overlaps market-risk policy testing, requiring a narrowing of one node's scope.
+Evidence: Batch 12 decision (Hamid, 2026-09-19): approve this row's content conditionally; the dependency must be resolved when the Regulatory &amp; Compliance cluster is authored, with a reciprocal exclusion recorded on whichever side needs it.
+Recommendation: Resolve in the Settlements &amp; Accounting / Regulatory &amp; Compliance batch; flip this row to approved once the reciprocal exclusion is confirmed. No content change expected under Option A.</t>
+        </is>
+      </c>
+      <c r="Y130" s="5" t="inlineStr">
+        <is>
+          <t>policies, mandates, and DOA | control-cycle records | exception logs</t>
+        </is>
+      </c>
+      <c r="Z130" s="5" t="inlineStr">
+        <is>
+          <t>escalated policy violations and control-gap findings</t>
+        </is>
+      </c>
+      <c r="AA130" s="5" t="inlineStr">
+        <is>
+          <t>uses-input: Establish &amp; Maintain Delegation Of Authority (DOA) | enables: Manage Risk Reporting | governed-by: Regulatory &amp; Compliance</t>
+        </is>
+      </c>
+      <c r="AB130" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC130" s="5" t="inlineStr">
+        <is>
+          <t>continuous</t>
+        </is>
+      </c>
       <c r="AD130" t="inlineStr">
         <is>
           <t>pending</t>
@@ -17866,18 +18558,80 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U131" s="5" t="n"/>
-      <c r="V131" s="5" t="n"/>
-      <c r="W131" s="5" t="n"/>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>Define, maintain, and run the market-risk scenario and stress set — historical and hypothetical market shocks, commodity and basis stresses, and event scenarios — quantifying their P&amp;L and risk impacts so the organization knows what adverse markets would do to the book before they happen.</t>
+        </is>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>Covers trading-book scenario and stress analysis: maintaining the approved scenario library, running scenarios on the control calendar and on demand, quantifying P&amp;L and measure impacts, and feeding results to limits, appetite discussions, and reporting. This is the trading and market-risk scenario home that batch 02's approved Perform Scenario Analysis (CM-1-1-4-7-8) explicitly points to — production-case scenario analysis stays there. Excludes credit stress testing (CM-1-2-2-1-6); excludes scenario methodology approval (risk governance).</t>
+        </is>
+      </c>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>Maintain the approved scenario and stress library | run scenarios on calendar and on demand | quantify P&amp;L and measure impacts | feed results to limits, appetite, and reporting</t>
+        </is>
+      </c>
+      <c r="Q131" t="inlineStr">
+        <is>
+          <t>Production-case scenario analysis (CM-1-1-4-7-8) | credit stress testing (CM-1-2-2-1-6) | scenario methodology approval (risk governance)</t>
+        </is>
+      </c>
+      <c r="R131" t="inlineStr">
+        <is>
+          <t>Market Risk Scenario &amp; Stress Testing</t>
+        </is>
+      </c>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>Batch 12 (2026-09-19). Closes the batch 02 pointer: trading and market-risk scenarios here; production scenarios at CM-1-1-4-7-8. APQC 11211 is a WEAK review-link.</t>
+        </is>
+      </c>
+      <c r="U131" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V131" s="5" t="inlineStr">
+        <is>
+          <t>Adverse markets are rehearsed before they are real.</t>
+        </is>
+      </c>
+      <c r="W131" s="5" t="inlineStr">
+        <is>
+          <t>SRC-CCRO-002A</t>
+        </is>
+      </c>
       <c r="X131" s="5" t="n"/>
-      <c r="Y131" s="5" t="n"/>
-      <c r="Z131" s="5" t="n"/>
-      <c r="AA131" s="5" t="n"/>
-      <c r="AB131" s="5" t="n"/>
-      <c r="AC131" s="5" t="n"/>
+      <c r="Y131" s="5" t="inlineStr">
+        <is>
+          <t>positions and valuations | scenario library | market histories</t>
+        </is>
+      </c>
+      <c r="Z131" s="5" t="inlineStr">
+        <is>
+          <t>quantified scenario and stress impacts</t>
+        </is>
+      </c>
+      <c r="AA131" s="5" t="inlineStr">
+        <is>
+          <t>uses-input: Measure Risk | enables: Manage Risk Limits | enables: Manage Risk Reporting</t>
+        </is>
+      </c>
+      <c r="AB131" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC131" s="5" t="inlineStr">
+        <is>
+          <t>periodic</t>
+        </is>
+      </c>
       <c r="AD131" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -17945,18 +18699,80 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U132" s="5" t="n"/>
-      <c r="V132" s="5" t="n"/>
-      <c r="W132" s="5" t="n"/>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>Analyze market risk beyond the standard measures — backtesting the measures against outcomes, analyzing model behavior and measure limitations, investigating risk concentrations and emerging exposures, and developing analytical improvements — recommending changes to methodologies, limits, and controls.</t>
+        </is>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>Covers advanced market-risk analysis: backtesting and performance analysis of the risk measures, deep-dives into concentrations, correlations, and emerging exposure patterns, analysis of measure and model limitations, and recommendations to the governance and control owners. Analyze-and-recommend only: methodology approval and independent model validation sit with the designated governance and validation functions (model-risk practice per the CCRO Model Risk publication as reference evidence). Excludes credit analytics (CM-1-2-2-1-6); excludes running the standard measures (CM-1-2-2-3-7).</t>
+        </is>
+      </c>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>Backtest risk measures against outcomes | analyze concentrations, correlations, and emerging exposures | analyze measure and model limitations | recommend methodology, limit, and control changes</t>
+        </is>
+      </c>
+      <c r="Q132" t="inlineStr">
+        <is>
+          <t>Methodology approval and independent model validation (designated functions) | credit analytics (CM-1-2-2-1-6) | standard measure production (CM-1-2-2-3-7)</t>
+        </is>
+      </c>
+      <c r="R132" t="inlineStr">
+        <is>
+          <t>Advanced Market Risk Analytics</t>
+        </is>
+      </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>Batch 12 (2026-09-19). Analyze-and-recommend per the batch 11 rule; model-risk boundaries per CCRO Model Risk practice as evidence. APQC 20728 is an IT-threat candidate; false lexical match.</t>
+        </is>
+      </c>
+      <c r="U132" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V132" s="5" t="inlineStr">
+        <is>
+          <t>The risk framework's blind spots are found by analysis, not by losses.</t>
+        </is>
+      </c>
+      <c r="W132" s="5" t="inlineStr">
+        <is>
+          <t>SRC-CCRO-002B | SRC-CCRO-002A</t>
+        </is>
+      </c>
       <c r="X132" s="5" t="n"/>
-      <c r="Y132" s="5" t="n"/>
-      <c r="Z132" s="5" t="n"/>
-      <c r="AA132" s="5" t="n"/>
-      <c r="AB132" s="5" t="n"/>
-      <c r="AC132" s="5" t="n"/>
+      <c r="Y132" s="5" t="inlineStr">
+        <is>
+          <t>measure histories and outcomes | positions and market data | model documentation</t>
+        </is>
+      </c>
+      <c r="Z132" s="5" t="inlineStr">
+        <is>
+          <t>analytical findings with methodology and control recommendations</t>
+        </is>
+      </c>
+      <c r="AA132" s="5" t="inlineStr">
+        <is>
+          <t>uses-input: Measure Risk | enables: Manage Risk Limits | enables: Manage Risk Reporting</t>
+        </is>
+      </c>
+      <c r="AB132" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC132" s="5" t="inlineStr">
+        <is>
+          <t>periodic</t>
+        </is>
+      </c>
       <c r="AD132" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -18024,18 +18840,80 @@
           <t>strong APQC candidate but no validator agreed</t>
         </is>
       </c>
-      <c r="U133" s="5" t="n"/>
-      <c r="V133" s="5" t="n"/>
-      <c r="W133" s="5" t="n"/>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>Produce governed internal market-risk reports — measures, limit utilization, breaches, scenario results, positions, and P&amp;L, at agreed cadences for management and committees — and provide controlled inputs to applicable external or regulatory reporting through their accountable owners.</t>
+        </is>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>Covers market-risk report production and distribution: daily and periodic management and committee reporting, breach and exception reporting, scenario and stress reporting, and controlled inputs to external reporting owned by its accountable processes. Excludes financial reporting and disclosures (Finance, locked rule); excludes regulatory filing ownership (CM-1-2-4-3); excludes credit-risk reporting (CM-1-2-2-1-8); excludes enterprise KPI definition (KPI workstream).</t>
+        </is>
+      </c>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>Produce management and committee risk reporting | report breaches, exceptions, and scenario results | distribute on the agreed calendar | provide controlled inputs to external reporting through accountable owners</t>
+        </is>
+      </c>
+      <c r="Q133" t="inlineStr">
+        <is>
+          <t>Financial reporting and disclosures (Finance) | regulatory filing ownership (CM-1-2-4-3) | credit-risk reporting (CM-1-2-2-1-8) | enterprise KPI definition (KPI workstream)</t>
+        </is>
+      </c>
+      <c r="R133" t="inlineStr">
+        <is>
+          <t>Market Risk Reporting</t>
+        </is>
+      </c>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>Batch 12 (2026-09-19). Mirrors the batch 11 reporting rule: internal production here; external reporting supported through, never owned instead of, accountable owners. APQC 10522 is an HR-reporting false match.</t>
+        </is>
+      </c>
+      <c r="U133" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V133" s="5" t="inlineStr">
+        <is>
+          <t>The risk picture reaches its decision-makers current, consistent, and on time.</t>
+        </is>
+      </c>
+      <c r="W133" s="5" t="inlineStr">
+        <is>
+          <t>SRC-CCRO-002A</t>
+        </is>
+      </c>
       <c r="X133" s="5" t="n"/>
-      <c r="Y133" s="5" t="n"/>
-      <c r="Z133" s="5" t="n"/>
-      <c r="AA133" s="5" t="n"/>
-      <c r="AB133" s="5" t="n"/>
-      <c r="AC133" s="5" t="n"/>
+      <c r="Y133" s="5" t="inlineStr">
+        <is>
+          <t>measures, limits, and breaches | scenario results | position and P&amp;L results</t>
+        </is>
+      </c>
+      <c r="Z133" s="5" t="inlineStr">
+        <is>
+          <t>distributed, governed market-risk reports and controlled external inputs</t>
+        </is>
+      </c>
+      <c r="AA133" s="5" t="inlineStr">
+        <is>
+          <t>uses-input: Monitor Risk | uses-input: Perform Position &amp; PNL Analysis | enables: Trading Strategy Management</t>
+        </is>
+      </c>
+      <c r="AB133" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC133" s="5" t="inlineStr">
+        <is>
+          <t>periodic</t>
+        </is>
+      </c>
       <c r="AD133" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -18103,18 +18981,80 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U134" s="5" t="n"/>
-      <c r="V134" s="5" t="n"/>
-      <c r="W134" s="5" t="n"/>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>Source, construct, validate, and publish the volatility and correlation parameters that option valuation and risk measurement depend on — by commodity, location, and tenor per approved methodology — so valuations and measures rest on governed market parameters, not ad hoc inputs.</t>
+        </is>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>Covers volatility and correlation ownership: sourcing implied and historical inputs, constructing surfaces and matrices per approved methodology, validating and handling exceptions, and publishing the official parameter set to valuation (CM-1-2-2-3-15) and risk measurement (CM-1-2-2-3-7). Methodology approval and independent validation sit with the designated governance and validation functions; curves are the sibling at CM-1-2-2-3-3.</t>
+        </is>
+      </c>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>Source implied and historical volatility and correlation inputs | construct surfaces and matrices per approved methodology | validate parameters and handle exceptions | publish the official parameter set</t>
+        </is>
+      </c>
+      <c r="Q134" t="inlineStr">
+        <is>
+          <t>Methodology approval and independent validation (designated functions) | curve construction (CM-1-2-2-3-3) | option trading decisions (front office)</t>
+        </is>
+      </c>
+      <c r="R134" t="inlineStr">
+        <is>
+          <t>Volatility Surface &amp; Correlation Management</t>
+        </is>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>Batch 12 (2026-09-19). The market-data sibling to curves; same ownership pattern. APQC 11743 is an unrelated routing candidate.</t>
+        </is>
+      </c>
+      <c r="U134" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V134" s="5" t="inlineStr">
+        <is>
+          <t>Governed parameters behind every option value and correlated measure.</t>
+        </is>
+      </c>
+      <c r="W134" s="5" t="inlineStr">
+        <is>
+          <t>SRC-CCRO-002A | SRC-CFTC-GLOSS-001</t>
+        </is>
+      </c>
       <c r="X134" s="5" t="n"/>
-      <c r="Y134" s="5" t="n"/>
-      <c r="Z134" s="5" t="n"/>
-      <c r="AA134" s="5" t="n"/>
-      <c r="AB134" s="5" t="n"/>
-      <c r="AC134" s="5" t="n"/>
+      <c r="Y134" s="5" t="inlineStr">
+        <is>
+          <t>implied and historical market data | parameter methodologies</t>
+        </is>
+      </c>
+      <c r="Z134" s="5" t="inlineStr">
+        <is>
+          <t>published official volatility and correlation set</t>
+        </is>
+      </c>
+      <c r="AA134" s="5" t="inlineStr">
+        <is>
+          <t>enables: Manage Commodity Valuations | enables: Measure Risk</t>
+        </is>
+      </c>
+      <c r="AB134" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC134" s="5" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
       <c r="AD134" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -18182,18 +19122,80 @@
           <t>strong APQC candidate but no validator agreed</t>
         </is>
       </c>
-      <c r="U135" s="5" t="n"/>
-      <c r="V135" s="5" t="n"/>
-      <c r="W135" s="5" t="n"/>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>Produce and control the official valuations of the trading book — marking positions to market or, where approved, to model per approved methodology from the official curves and parameters, applying approved valuation adjustments, investigating exceptions, and publishing the valuations that P&amp;L, risk, exposure, and reconciliation run on.</t>
+        </is>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>Covers valuation ownership: running mark-to-market and approved mark-to-model valuations from the official curves (CM-1-2-2-3-3) and parameters (CM-1-2-2-3-14), applying approved valuation adjustments, independent price verification against external sources where required, exception investigation, and publication to position and P&amp;L (CM-1-2-2-3-9), risk measurement (CM-1-2-2-3-7), and credit exposure (CM-1-2-2-1-4). Valuation adjustments may include approved liquidity, model, credit, funding, or other adjustments where applicable to the portfolio and approved methodology; this process executes the approved valuation-control procedures — it does not approve valuation policy, accounting classification, or model methodology, which sit with the designated governance, Accounting (Manage Accounting Treatments, CM-1-2-4-2-1), and validation functions. Structured-deal representation fidelity is the capture side's duty (CM-1-2-1-3-8) with valuation representation coordinated here.</t>
+        </is>
+      </c>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>Run mark-to-market and approved mark-to-model valuations | apply approved valuation adjustments per procedure | perform independent price verification where required | investigate exceptions and publish official valuations</t>
+        </is>
+      </c>
+      <c r="Q135" t="inlineStr">
+        <is>
+          <t>Valuation policy, methodology approval, and independent model validation (designated governance and validation functions) | accounting classification and valuation treatments (CM-1-2-4-2-1) | structured-deal capture representation (CM-1-2-1-3-8)</t>
+        </is>
+      </c>
+      <c r="R135" t="inlineStr">
+        <is>
+          <t>Trading Book Valuation | Mark-to-Market Management</t>
+        </is>
+      </c>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>Batch 12 (2026-09-19). Adjustment ownership clarified at Hamid's direction: this process executes approved valuation-control procedures — adjustment categories apply only where relevant to the portfolio and approved methodology, and policy, accounting classification, and model methodology are owned elsewhere; which adjustments are material for the portfolio is a follow-up noted in the batch 12 PR. The valuation node batches 08 and 11 point at. Model-risk boundaries per CCRO Model Risk practice as evidence. APQC 12953 STRONG with no validator; supporting comparative evidence.</t>
+        </is>
+      </c>
+      <c r="U135" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V135" s="5" t="inlineStr">
+        <is>
+          <t>One official value per position, methodologically defensible, every day.</t>
+        </is>
+      </c>
+      <c r="W135" s="5" t="inlineStr">
+        <is>
+          <t>SRC-CCRO-002A | SRC-CCRO-002B | SRC-CFTC-GLOSS-001</t>
+        </is>
+      </c>
       <c r="X135" s="5" t="n"/>
-      <c r="Y135" s="5" t="n"/>
-      <c r="Z135" s="5" t="n"/>
-      <c r="AA135" s="5" t="n"/>
-      <c r="AB135" s="5" t="n"/>
-      <c r="AC135" s="5" t="n"/>
+      <c r="Y135" s="5" t="inlineStr">
+        <is>
+          <t>validated positions | official curves and parameters | valuation methodologies and approved adjustments</t>
+        </is>
+      </c>
+      <c r="Z135" s="5" t="inlineStr">
+        <is>
+          <t>published official trading-book valuations</t>
+        </is>
+      </c>
+      <c r="AA135" s="5" t="inlineStr">
+        <is>
+          <t>uses-input: Setup And Manage Curves | uses-input: Manage Volatilities And Correlations | enables: Perform Position &amp; PNL Analysis</t>
+        </is>
+      </c>
+      <c r="AB135" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC135" s="5" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
       <c r="AD135" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -47925,7 +48927,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -49239,6 +50241,100 @@
         </is>
       </c>
       <c r="I33" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>SRC-CCRO-002A</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Committee of Chief Risk Officers</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Risk Management Standards for Energy Market Participants (Version 1.0, 2012)</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>v1.0, 2012; accessed 2026-09-19</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>CCRO, Risk Management Standards for Energy Market Participants v1.0; https://www.ccro.org/</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Industry-practice body (guidance, not regulatory or consensus standard authority)</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Market-risk framework, controls, measurement, scenario, and valuation terminology for energy market participants. Does not determine internal ownership, governance authorities, methodologies, measure sets, limit amounts, or regulatory obligations. Evidence only, not text to copy.</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Market-risk control framework, measurement, scenario, and reporting practice context</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>SRC-CCRO-002B</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Committee of Chief Risk Officers</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Model Risk in Energy (white paper, Edition 1.0)</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Edition 1.0; accessed 2026-09-19</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>https://www.ccro.org/model-risk-in-energy</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Industry-practice body (guidance, not regulatory or consensus standard authority)</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Model-risk boundaries, model governance, and validation terminology for energy trading. Does not determine internal ownership, validation mandates, or methodologies. Evidence only, not text to copy.</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Model governance and validation boundaries for valuation and risk analytics</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
         <is>
           <t>active</t>
         </is>

--- a/business_architecture/ontology/build/output/step3c-definition-authoring-workbook.xlsx
+++ b/business_architecture/ontology/build/output/step3c-definition-authoring-workbook.xlsx
@@ -19263,18 +19263,80 @@
           <t>no meaningful APQC candidate</t>
         </is>
       </c>
-      <c r="U136" s="5" t="n"/>
-      <c r="V136" s="5" t="n"/>
-      <c r="W136" s="5" t="n"/>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>Update trading deal, movement, and entitlement records with contractually applicable actual quantities, qualities, dates, statuses, and charge determinants from execution, custody-transfer, registry, and other agreed evidence, replacing planned or estimated values so settlement, economic P&amp;L, risk, and downstream reporting use controlled actuals.</t>
+        </is>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>Covers the per-movement actualization lifecycle across transport and instrument modes: matching execution evidence to the captured deal and scheduled movement, recording actual quantities, qualities, dates, and statuses on the contractual measurement basis, recording verified charge determinants, and closing the movement in the trading record. Actualizations may record or validate charge determinants — such as tariff basis, freight basis, throughput quantity, storage days, accessorial events, loss allowances, quality adjustments, and contractual rate references — and may calculate provisional amounts where the controlled trading-system design assigns that function; it does not own invoice generation, final settlement calculation, payment, accounting accrual or posting, or financial dispute resolution. Actualization updates the trading system's deal, movement, and entitlement records; it consumes measurement results and does not perform physical measurement, which is executed at custody transfer by operating personnel and independent inspectors under the applicable measurement standards (API MPMS). Excludes trade capture (CM-1-2-1-3); confirmation of agreed terms (CM-1-2-2-2); settlement and invoicing (CM-1-2-4-1); per-movement closure in distribution scheduling and inventory records and network book-to-physical stock reconciliation, owned by Discharge &amp; Reconcile Load (CM-1-1-3-6-4) and Perform Inventory Reconciliation (CM-1-1-3-7-5) under the locked SCM boundary; demurrage claims (CM-1-2-4-4).</t>
+        </is>
+      </c>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>Match execution and measurement evidence to deals and scheduled movements | record actual quantities, qualities, dates, and statuses on the contractual measurement basis | record verified charge determinants and, where the trading system is configured to do so, provisional or contractually derived charge amounts for downstream settlement validation | close movements in the trading record for settlement</t>
+        </is>
+      </c>
+      <c r="Q136" t="inlineStr">
+        <is>
+          <t>Physical measurement at custody transfer (operations and independent inspection per API MPMS) | trade capture (CM-1-2-1-3) | confirmation (CM-1-2-2-2) | invoice generation, final settlement calculation, payment, and accrual (CM-1-2-4-1, Accounting) | distribution movement closure and stock reconciliation (CM-1-1-3-6-4, CM-1-1-3-7-5) | demurrage claims (CM-1-2-4-4)</t>
+        </is>
+      </c>
+      <c r="R136" t="inlineStr">
+        <is>
+          <t>Deal Actualization | Movement Actualization</t>
+        </is>
+      </c>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>Batch 13 (2026-09-19). 'Actualization' is energy-trading (ETRM/CTRM) practice terminology: replacing planned or estimated deal and movement values with measured actuals. Concept-type: process per the batch 08 variant test — one per-movement lifecycle discipline applied across mode variants, like Trade Capture. 'Entitlement' covers commingled stock, exchanges, storage, and instrument arrangements where the commercial fact is not a uniquely identifiable physical parcel. Q2 decision (Hamid, batch 13): charge-determinant actualization, not universal cost actualization — Actualizations records the verified operational and contractual facts needed to determine charges (actual quantity, quality, duration, route, capacity use, tariff/fee basis, dates, loss/gain treatment, and other rate inputs); Settlements applies rates, calculates settlement amounts, invoices, pays or receives, accrues, nets, and resolves financial disputes. Trading-record versus stock-record boundary: the same custody-transfer documents feed this process (trading deal, movement, and entitlement records) and the SCM inventory processes (physical stock and scheduling records); each updates its own record. Measurement authority: API MPMS (tank gauging Ch. 3; marine cargo Ch. 17; lease-tank custody transfer Ch. 18). 'P&amp;L' prose convention per batch 12. APQC 19948 is an unrelated candidate.</t>
+        </is>
+      </c>
+      <c r="U136" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V136" s="5" t="inlineStr">
+        <is>
+          <t>Ensure the trading record reflects what was actually delivered, received, and measured, so settlement, accounting, and risk run on controlled actuals rather than estimates.</t>
+        </is>
+      </c>
+      <c r="W136" s="5" t="inlineStr">
+        <is>
+          <t>SRC-API-MPMS-001 | SRC-EI-HM32-001 | SRC-EIA-GLOSS-001</t>
+        </is>
+      </c>
       <c r="X136" s="5" t="n"/>
-      <c r="Y136" s="5" t="n"/>
-      <c r="Z136" s="5" t="n"/>
-      <c r="AA136" s="5" t="n"/>
-      <c r="AB136" s="5" t="n"/>
-      <c r="AC136" s="5" t="n"/>
+      <c r="Y136" s="5" t="inlineStr">
+        <is>
+          <t>Captured deal and scheduled movement records | meter tickets, bills of lading, and run tickets | inspection and outturn reports | carrier, terminal, and registry statements</t>
+        </is>
+      </c>
+      <c r="Z136" s="5" t="inlineStr">
+        <is>
+          <t>Actualized deal, movement, and entitlement records ready for settlement</t>
+        </is>
+      </c>
+      <c r="AA136" s="5" t="inlineStr">
+        <is>
+          <t>follows: Trade Capture | informed-by: Confirmations Management | precedes: Settlements</t>
+        </is>
+      </c>
+      <c r="AB136" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC136" s="5" t="inlineStr">
+        <is>
+          <t>event-driven</t>
+        </is>
+      </c>
       <c r="AD136" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -19342,18 +19404,75 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U137" s="5" t="n"/>
-      <c r="V137" s="5" t="n"/>
-      <c r="W137" s="5" t="n"/>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>Actualize pipeline movements of crude, feedstocks, and products — recording actual receipt and delivery volumes, qualities, and dates from pipeline meter tickets, carrier statements, and shipper reports, applying pipeline loss allowance, quality-bank, proration, or other carrier and tariff adjustments where applicable, and reconciling actuals against nominated and scheduled volumes — so pipeline transactions settle on verified actuals.</t>
+        </is>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>Covers matching pipeline carrier evidence to deals and scheduled movements, recording actual volumes on the tariff measurement basis, recording applicable carrier and tariff entitlement and quality-adjustment results, recording actual pipeline tariff and charge determinants and validating applicable transportation charges for settlement, and surfacing discrepancies between carrier-reported and scheduled volumes. Loss allowance, quality-bank, and proration mechanisms are tariff- and carrier-specific and apply only where the governing tariff provides them; a quality bank may adjust an entitlement or economic balance rather than a physical quality measurement. Excludes pipeline nomination and scheduling (the owning transportation and scheduling processes); pipeline settlement and invoicing (Settle Pipelines, CM-1-2-4-1-12); transportation deal capture (CM-1-2-1-3-9); actualization disputes (Manage Actualization Disputes, CM-1-2-3-1-8).</t>
+        </is>
+      </c>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>Match carrier tickets and statements to deals and movements | record actual volumes, qualities, and dates per tariff basis | record applicable carrier and tariff entitlement and quality-adjustment results where applicable | record actual pipeline tariff and charge determinants and validate applicable transportation charges for settlement</t>
+        </is>
+      </c>
+      <c r="Q137" t="inlineStr">
+        <is>
+          <t>Nomination and scheduling (owning transportation processes) | pipeline settlement (CM-1-2-4-1-12) | transportation deal capture (CM-1-2-1-3-9) | actualization disputes (CM-1-2-3-1-8)</t>
+        </is>
+      </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>Batch 13 (2026-09-19). Pipeline loss allowance (PLA), quality banks, and proration are tariff mechanisms recorded at actualization only where the governing tariff provides them; the tariff itself is administered by the carrier under the applicable regulatory regime. Q2 charge-determinant rule applied: this process records determinants and validates charges; Settle Pipelines owns settlement. APQC 20042 'Monitor pipeline' is a WEAK operational-monitoring candidate, not this accounting activity.</t>
+        </is>
+      </c>
+      <c r="U137" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V137" s="5" t="inlineStr">
+        <is>
+          <t>Make pipeline movement records reflect carrier-measured actuals under the governing tariff terms.</t>
+        </is>
+      </c>
+      <c r="W137" s="5" t="inlineStr">
+        <is>
+          <t>SRC-API-MPMS-001 | SRC-DOE-RPPL-001</t>
+        </is>
+      </c>
       <c r="X137" s="5" t="n"/>
-      <c r="Y137" s="5" t="n"/>
-      <c r="Z137" s="5" t="n"/>
-      <c r="AA137" s="5" t="n"/>
-      <c r="AB137" s="5" t="n"/>
-      <c r="AC137" s="5" t="n"/>
+      <c r="Y137" s="5" t="inlineStr">
+        <is>
+          <t>Pipeline meter tickets and carrier statements | shipper reports | scheduled movements and nominations | tariff terms</t>
+        </is>
+      </c>
+      <c r="Z137" s="5" t="inlineStr">
+        <is>
+          <t>Actualized pipeline movement records</t>
+        </is>
+      </c>
+      <c r="AA137" s="5" t="inlineStr">
+        <is>
+          <t>precedes: Settle Pipelines | follows: Capture Physical Trades</t>
+        </is>
+      </c>
+      <c r="AB137" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC137" s="5" t="inlineStr">
+        <is>
+          <t>event-driven</t>
+        </is>
+      </c>
       <c r="AD137" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -19421,18 +19540,75 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U138" s="5" t="n"/>
-      <c r="V138" s="5" t="n"/>
-      <c r="W138" s="5" t="n"/>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>Actualize truck movements of crude, feedstocks, and products — recording actual loaded and delivered volumes, qualities, and dates from bills of lading, terminal lifting records, and truck tickets, recorded on the contractually applicable measurement and temperature/volume basis — so truck transactions settle on verified actuals.</t>
+        </is>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>Covers matching truck shipment evidence — rack lifting records, bills of lading, delivery tickets — to deals and scheduled movements, recording actual volumes and qualities on the contractually applicable measurement basis, recording verified freight-charge determinants and validating charge inputs for settlement, and surfacing load-versus-delivery discrepancies. Crude gathered from lease tanks by truck actualizes under Perform Lease Actualization (CM-1-2-3-1-6) with its run-ticket and contract-terms context. Excludes truck dispatch and scheduling (the owning logistics processes); truck settlement (Settle Trucks, CM-1-2-4-1-4); actualization disputes (CM-1-2-3-1-8).</t>
+        </is>
+      </c>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>Match bills of lading and lifting records to deals and movements | record actual volumes, qualities, and dates on the contractually applicable measurement basis | record verified freight-charge determinants and validate charge inputs for settlement | surface load-versus-delivery discrepancies</t>
+        </is>
+      </c>
+      <c r="Q138" t="inlineStr">
+        <is>
+          <t>Lease-tank truck gathering (CM-1-2-3-1-6) | truck dispatch and scheduling (logistics processes) | truck settlement (CM-1-2-4-1-4) | actualization disputes (CM-1-2-3-1-8)</t>
+        </is>
+      </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>Batch 13 (2026-09-19). The governing unit-of-measure basis may be gross, net, observed, standard, mass, or another contractual basis; not every truck transaction involves a temperature correction. Boundary to CM-1-2-3-1-6: mode-based rows partition by evidence and contract context — lease run tickets and first-purchase terms belong to Lease Actualization even though a truck performs the movement. Q2 charge-determinant rule applied. APQC 10954 'Perform abandonment' is a false lexical match.</t>
+        </is>
+      </c>
+      <c r="U138" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V138" s="5" t="inlineStr">
+        <is>
+          <t>Make truck movement records reflect measured lifted and delivered actuals on the contractual basis.</t>
+        </is>
+      </c>
+      <c r="W138" s="5" t="inlineStr">
+        <is>
+          <t>SRC-API-MPMS-001 | SRC-EI-HM32-001</t>
+        </is>
+      </c>
       <c r="X138" s="5" t="n"/>
-      <c r="Y138" s="5" t="n"/>
-      <c r="Z138" s="5" t="n"/>
-      <c r="AA138" s="5" t="n"/>
-      <c r="AB138" s="5" t="n"/>
-      <c r="AC138" s="5" t="n"/>
+      <c r="Y138" s="5" t="inlineStr">
+        <is>
+          <t>Bills of lading and delivery tickets | terminal rack lifting records | scheduled movements | freight terms</t>
+        </is>
+      </c>
+      <c r="Z138" s="5" t="inlineStr">
+        <is>
+          <t>Actualized truck movement records</t>
+        </is>
+      </c>
+      <c r="AA138" s="5" t="inlineStr">
+        <is>
+          <t>precedes: Settle Trucks | follows: Capture Physical Trades</t>
+        </is>
+      </c>
+      <c r="AB138" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC138" s="5" t="inlineStr">
+        <is>
+          <t>event-driven</t>
+        </is>
+      </c>
       <c r="AD138" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -19500,18 +19676,75 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U139" s="5" t="n"/>
-      <c r="V139" s="5" t="n"/>
-      <c r="W139" s="5" t="n"/>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>Actualize railcar movements of crude, feedstocks, and products — recording actual loaded and received quantities, weights, qualities, and dates from railcar shipping documents, scale weights, and gauging records on the contractually applicable basis — so rail transactions settle on verified actuals.</t>
+        </is>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>Covers matching rail shipment evidence — bills of lading, railcar weight and volume determinations, inspection records — to deals and scheduled movements, recording actuals per railcar and shipment on the contractual basis, recording verified rail freight and accessorial charge determinants for settlement, and surfacing origin-versus-destination discrepancies. Quantities may be weight-, volume-, or mass-balance-based according to commodity, equipment, carrier practice, and contract. Excludes railcar fleet management and rail logistics scheduling (the owning logistics processes); rail settlement (Settle Rail, CM-1-2-4-1-13); actualization disputes (CM-1-2-3-1-8).</t>
+        </is>
+      </c>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>Match rail shipping documents to deals and movements | record actual quantities, weights, qualities, and dates per railcar on the contractual basis | record verified rail freight and accessorial charge determinants for settlement | surface origin-versus-destination discrepancies</t>
+        </is>
+      </c>
+      <c r="Q139" t="inlineStr">
+        <is>
+          <t>Railcar fleet management and rail scheduling (logistics processes) | rail settlement (CM-1-2-4-1-13) | actualization disputes (CM-1-2-3-1-8)</t>
+        </is>
+      </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>Batch 13 (2026-09-19). Rail quantities may be determined by scale weight, gauging, or mass balance according to commodity, equipment, carrier practice, and contract; the contractual measurement basis governs. Q2 charge-determinant rule applied. APQC 10954 is a false lexical match.</t>
+        </is>
+      </c>
+      <c r="U139" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V139" s="5" t="inlineStr">
+        <is>
+          <t>Make rail movement records reflect measured shipped and received actuals on the contractual basis.</t>
+        </is>
+      </c>
+      <c r="W139" s="5" t="inlineStr">
+        <is>
+          <t>SRC-API-MPMS-001</t>
+        </is>
+      </c>
       <c r="X139" s="5" t="n"/>
-      <c r="Y139" s="5" t="n"/>
-      <c r="Z139" s="5" t="n"/>
-      <c r="AA139" s="5" t="n"/>
-      <c r="AB139" s="5" t="n"/>
-      <c r="AC139" s="5" t="n"/>
+      <c r="Y139" s="5" t="inlineStr">
+        <is>
+          <t>Railcar bills of lading and shipping documents | scale weights and gauging records | scheduled movements | freight terms</t>
+        </is>
+      </c>
+      <c r="Z139" s="5" t="inlineStr">
+        <is>
+          <t>Actualized rail movement records</t>
+        </is>
+      </c>
+      <c r="AA139" s="5" t="inlineStr">
+        <is>
+          <t>precedes: Settle Rail | follows: Capture Physical Trades</t>
+        </is>
+      </c>
+      <c r="AB139" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC139" s="5" t="inlineStr">
+        <is>
+          <t>event-driven</t>
+        </is>
+      </c>
       <c r="AD139" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -19579,18 +19812,80 @@
           <t>no meaningful APQC candidate</t>
         </is>
       </c>
-      <c r="U140" s="5" t="n"/>
-      <c r="V140" s="5" t="n"/>
-      <c r="W140" s="5" t="n"/>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>Actualize marine movements by vessel and barge — recording actual loaded and outturn quantities, qualities, and dates from bills of lading, independent inspection reports, and ship and shore figures per marine measurement practice, and identifying apparent voyage gains, losses, and quantity differences according to the contractual measurement basis — so marine transactions settle on verified actuals.</t>
+        </is>
+      </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>Covers matching marine cargo evidence — bill of lading and outturn quantities, load- and discharge-port inspection reports, ship and shore measurements, timesheets and statements of fact for date actuals — to deals and scheduled voyages, following marine cargo measurement practice (API MPMS Ch. 17); recording actuals on the contractual bill-of-lading or outturn basis; identifying and recording apparent voyage gains, losses, and quantity differences according to the contractual measurement basis, agreed measurement hierarchy, and applicable claim process; and recording verified freight, laytime, and voyage-cost determinants for settlement. Relevant time, notice, and event facts may be made available to Demurrage Management (CM-1-2-4-4); that process determines potential demurrage under the applicable charter party, contract, or terminal terms. Excludes vessel chartering and voyage operations (the owning chartering and marine logistics processes); marine settlement (Settle Vessels &amp; Barge, CM-1-2-4-1-5); demurrage claim identification and management (CM-1-2-4-4); actualization disputes (CM-1-2-3-1-8).</t>
+        </is>
+      </c>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>Match bills of lading, outturn, and inspection reports to deals and voyages | record actuals on the contractual bill-of-lading or outturn basis | identify and record apparent voyage gains, losses, and quantity differences per the agreed measurement hierarchy | record verified freight, laytime, and voyage-cost determinants for settlement</t>
+        </is>
+      </c>
+      <c r="Q140" t="inlineStr">
+        <is>
+          <t>Chartering and voyage operations (marine logistics processes) | marine settlement (CM-1-2-4-1-5) | demurrage determination and claims (CM-1-2-4-4) | actualization disputes (CM-1-2-3-1-8)</t>
+        </is>
+      </c>
+      <c r="R140" t="inlineStr">
+        <is>
+          <t>Marine Actualization</t>
+        </is>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>Batch 13 (2026-09-19). Marine measurement per API MPMS Ch. 17; whether a cargo settles on bill-of-lading or outturn quantity is a contractual term captured with the deal — actualization applies the contractual basis, it does not choose it. Load/discharge differences are recorded as apparent gains or losses: they may reflect measurement, temperature, density, timing, sampling, or contractual-settlement effects rather than physical loss. Actualization supplies time, notice, and event facts but does not make the demurrage determination (CM-1-2-4-4). Receipt-side outturn confirmation for distribution movements is owned by Discharge &amp; Reconcile Load (CM-1-1-3-6-4); this row owns the trading-record actualization. Q2 charge-determinant rule applied. APQC: no meaningful candidate.</t>
+        </is>
+      </c>
+      <c r="U140" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V140" s="5" t="inlineStr">
+        <is>
+          <t>Make marine movement records reflect inspected load and outturn actuals and make apparent voyage differences visible.</t>
+        </is>
+      </c>
+      <c r="W140" s="5" t="inlineStr">
+        <is>
+          <t>SRC-API-MPMS-001 | SRC-EI-HM32-001</t>
+        </is>
+      </c>
       <c r="X140" s="5" t="n"/>
-      <c r="Y140" s="5" t="n"/>
-      <c r="Z140" s="5" t="n"/>
-      <c r="AA140" s="5" t="n"/>
-      <c r="AB140" s="5" t="n"/>
-      <c r="AC140" s="5" t="n"/>
+      <c r="Y140" s="5" t="inlineStr">
+        <is>
+          <t>Bills of lading and outturn reports | independent inspection reports | statements of fact and timesheets | voyage and freight terms</t>
+        </is>
+      </c>
+      <c r="Z140" s="5" t="inlineStr">
+        <is>
+          <t>Actualized marine movement records</t>
+        </is>
+      </c>
+      <c r="AA140" s="5" t="inlineStr">
+        <is>
+          <t>precedes: Settle Vessels &amp; Barge | follows: Capture Physical Trades | enables: Identify Potential Demurrage</t>
+        </is>
+      </c>
+      <c r="AB140" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC140" s="5" t="inlineStr">
+        <is>
+          <t>event-driven</t>
+        </is>
+      </c>
       <c r="AD140" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -19658,18 +19953,75 @@
           <t>no meaningful APQC candidate</t>
         </is>
       </c>
-      <c r="U141" s="5" t="n"/>
-      <c r="V141" s="5" t="n"/>
-      <c r="W141" s="5" t="n"/>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>Actualize terminal and storage transactions — recording transaction-level receipt, delivery, throughput, and contractually relevant storage-balance actuals for the associated deal or capacity arrangement from terminal operator statements, tank gauging records, and throughput reports, and recording verified throughput, storage, blending, and handling charge determinants and applicable contractual bases — so terminal and storage transactions settle on verified actuals.</t>
+        </is>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>Covers matching terminal operator evidence — receipt and delivery tickets, tank gauging and inventory statements, throughput reports — to deals, scheduled movements, and capacity arrangements; recording transaction-level receipt, delivery, throughput, and contractually relevant storage-balance actuals per movement and period; recognizing terminal gains and losses per the agreement's loss-allowance terms; and recording verified throughput, storage, blending, and handling charge determinants and applicable contractual bases. Storage-deal terms come from capture (Capture Storage Deals, CM-1-2-1-3-5). Excludes terminal operations and physical measurement (terminal operator); terminal and storage settlement (Settle Terminal/Storage, CM-1-2-4-1-14); network book-to-physical stock reconciliation, owned by Perform Inventory Reconciliation (CM-1-1-3-7-5); actualization disputes (CM-1-2-3-1-8).</t>
+        </is>
+      </c>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>Match terminal statements and tickets to deals and movements | record transaction-level receipt, delivery, throughput, and contractually relevant storage-balance actuals | recognize terminal gains and losses per agreement terms | record verified throughput, storage, blending, and handling charge determinants and applicable contractual bases</t>
+        </is>
+      </c>
+      <c r="Q141" t="inlineStr">
+        <is>
+          <t>Terminal operations and physical measurement (terminal operator) | terminal and storage settlement (CM-1-2-4-1-14) | network stock reconciliation (CM-1-1-3-7-5) | actualization disputes (CM-1-2-3-1-8)</t>
+        </is>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>Batch 13 (2026-09-19). Trading-record versus stock-record boundary applied: terminal statements actualize transaction-level actuals and charge determinants for the associated deal or capacity arrangement here, while periodic book-to-physical stock reconciliation across the network remains with CM-1-1-3-7-5 (EI HM 32 practice). Q2 charge-determinant rule applied. APQC 10954 is a false lexical match.</t>
+        </is>
+      </c>
+      <c r="U141" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V141" s="5" t="inlineStr">
+        <is>
+          <t>Make terminal and storage transaction records reflect operator-measured actuals and contractual charge determinants.</t>
+        </is>
+      </c>
+      <c r="W141" s="5" t="inlineStr">
+        <is>
+          <t>SRC-API-MPMS-001 | SRC-EI-HM32-001</t>
+        </is>
+      </c>
       <c r="X141" s="5" t="n"/>
-      <c r="Y141" s="5" t="n"/>
-      <c r="Z141" s="5" t="n"/>
-      <c r="AA141" s="5" t="n"/>
-      <c r="AB141" s="5" t="n"/>
-      <c r="AC141" s="5" t="n"/>
+      <c r="Y141" s="5" t="inlineStr">
+        <is>
+          <t>Terminal receipt and delivery tickets | tank gauging and inventory statements | throughput reports | terminal and storage agreement terms</t>
+        </is>
+      </c>
+      <c r="Z141" s="5" t="inlineStr">
+        <is>
+          <t>Actualized terminal and storage transaction records</t>
+        </is>
+      </c>
+      <c r="AA141" s="5" t="inlineStr">
+        <is>
+          <t>precedes: Settle Terminal/Storage | follows: Capture Storage Deals</t>
+        </is>
+      </c>
+      <c r="AB141" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC141" s="5" t="inlineStr">
+        <is>
+          <t>event-driven</t>
+        </is>
+      </c>
       <c r="AD141" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -19737,18 +20089,80 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U142" s="5" t="n"/>
-      <c r="V142" s="5" t="n"/>
-      <c r="W142" s="5" t="n"/>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>Actualize crude and condensate lease purchases — recording actual volumes, gravities, and qualities from run tickets and LACT meter records taken at lease-tank custody transfer, applying the contractual gravity, quality, and deduction adjustments and division-of-interest references — so first-purchase transactions settle on verified actuals.</t>
+        </is>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>Covers matching lease custody-transfer evidence — run tickets from manual gauging or LACT meter records — to lease purchase contracts; recording actual volumes and qualities per lease and run; applying gravity and quality adjustments, deductions, and division-of-interest references maintained under Manage Lease Contract (CM-1-2-1-2-8); and closing lease runs for settlement. Measurement procedures at the lease tank follow API MPMS Ch. 18 custody-transfer practice, performed by the gathering party. Included only where the downstream organization purchases at the lease/wellhead, per the batch 09 scope caveat. This process does not include upstream leasehold administration, land management, production allocation, royalty calculation policy, or exploration-and-production accounting. Excludes lease contract administration (CM-1-2-1-2-8); first-purchaser settlement (Settle First Purchaser/Leases, CM-1-2-4-1-6); royalty and interest payment execution (Manage Marketing Interests &amp; Royalty Payments, CM-1-2-4-2-3); actualization disputes (CM-1-2-3-1-8).</t>
+        </is>
+      </c>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>Match run tickets and LACT records to lease contracts | record actual volumes, gravities, and qualities per lease and run | apply contractual adjustments, deductions, and division-of-interest references | close lease runs for settlement</t>
+        </is>
+      </c>
+      <c r="Q142" t="inlineStr">
+        <is>
+          <t>Upstream leasehold administration, land management, production allocation, royalty calculation policy, and exploration-and-production accounting (outside scope) | lease contract administration (CM-1-2-1-2-8) | first-purchaser settlement (CM-1-2-4-1-6) | royalty and interest payments (CM-1-2-4-2-3) | physical gauging and metering (gathering party per API MPMS) | actualization disputes (CM-1-2-3-1-8)</t>
+        </is>
+      </c>
+      <c r="R142" t="inlineStr">
+        <is>
+          <t>First-Purchase Actualization</t>
+        </is>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>Batch 13 (2026-09-19). 'Lease' in the crude-marketing first-purchase sense per batch 09; the batch 09 follow-up on whether lease-purchase activity is genuinely downstream-owned still stands and is carried in the batch 13 PR. Run-ticket measurement per API MPMS Ch. 18.1 (manual gauging, lease tanks to truck); LACT (lease automatic custody transfer) metering where installed. APQC 10954 is a false lexical match.</t>
+        </is>
+      </c>
+      <c r="U142" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V142" s="5" t="inlineStr">
+        <is>
+          <t>Make lease purchase records reflect run-ticket and meter actuals under contractual terms.</t>
+        </is>
+      </c>
+      <c r="W142" s="5" t="inlineStr">
+        <is>
+          <t>SRC-API-MPMS-001</t>
+        </is>
+      </c>
       <c r="X142" s="5" t="n"/>
-      <c r="Y142" s="5" t="n"/>
-      <c r="Z142" s="5" t="n"/>
-      <c r="AA142" s="5" t="n"/>
-      <c r="AB142" s="5" t="n"/>
-      <c r="AC142" s="5" t="n"/>
+      <c r="Y142" s="5" t="inlineStr">
+        <is>
+          <t>Run tickets and LACT meter records | lease contract terms and division-of-interest references (CM-1-2-1-2-8) | scheduled lease runs</t>
+        </is>
+      </c>
+      <c r="Z142" s="5" t="inlineStr">
+        <is>
+          <t>Actualized lease purchase records</t>
+        </is>
+      </c>
+      <c r="AA142" s="5" t="inlineStr">
+        <is>
+          <t>follows: Manage Lease Contract | precedes: Settle First Purchaser/Leases</t>
+        </is>
+      </c>
+      <c r="AB142" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC142" s="5" t="inlineStr">
+        <is>
+          <t>event-driven</t>
+        </is>
+      </c>
       <c r="AD142" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -19816,18 +20230,80 @@
           <t>no meaningful APQC candidate</t>
         </is>
       </c>
-      <c r="U143" s="5" t="n"/>
-      <c r="V143" s="5" t="n"/>
-      <c r="W143" s="5" t="n"/>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>Update environmental-attribute and renewable-instrument trading records from authoritative registry lifecycle events — including issuance or generation, separation where applicable, transfer, acquisition, sale, retirement, and cancellation — and reconcile internal instrument positions to the applicable registry or regulatory system of record.</t>
+        </is>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>Covers transaction-level recording, controlled submission or instruction of registry events where authorized, receipt of registry confirmations, internal-to-registry position reconciliation, exception investigation, and evidence retention for RIN, REC, and other in-scope environmental instruments. For US RFS transactions, EMTS transaction reporting is subject to the applicable EPA rules and account-holder and delegation model (40 CFR 80.1452). For RECs, registry actions are subject to the applicable regional tracking system and program rules; program applicability is jurisdiction-specific. Excludes regulatory-policy interpretation, compliance-applicability and compliance-accountability decisions, periodic regulatory filing, attestation, audit response, renewable-volume-obligation demonstration, and broader EHS compliance reporting, owned by EHS &amp; Government Reporting under its locked rule; position forecasting (Forecast Renewables, CM-1-2-1-1-3); deal capture (Capture Environmental/Renewable Deals, CM-1-2-1-3-6); environmental instrument settlement (Settle Emissions, CM-1-2-4-1-8); actualization disputes (CM-1-2-3-1-8).</t>
+        </is>
+      </c>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>Record registry lifecycle events against deals and positions | submit or instruct registry events where the organization has assigned registry-account authority | reconcile internal instrument positions to EMTS and registry records | investigate exceptions and retain registry evidence</t>
+        </is>
+      </c>
+      <c r="Q143" t="inlineStr">
+        <is>
+          <t>Regulatory policy, compliance accountability, periodic filings, attestations, audit response, and RVO demonstrations (EHS &amp; Government Reporting, locked rule) | position forecasting (CM-1-2-1-1-3) | deal capture (CM-1-2-1-3-6) | settlement (CM-1-2-4-1-8) | actualization disputes (CM-1-2-3-1-8)</t>
+        </is>
+      </c>
+      <c r="R143" t="inlineStr">
+        <is>
+          <t>Environmental Instrument Actualization</t>
+        </is>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>Batch 13 (2026-09-19). Q3 decision (Hamid): approve operational registry-event processing where the function is authorized — this process records, submits, receives, reconciles, and evidences transaction-level registry lifecycle events where the organization has assigned registry-account authority and the event is part of the transaction lifecycle; EHS &amp; Government Reporting retains regulatory policy, compliance applicability, periodic compliance demonstrations, attestations, regulatory reporting, and final compliance accountability. Registry events are not necessarily submitted by this process — they may be initiated by a compliance team, producer, obligated party, registry administrator, or delegated service provider per the operating model (organizational neutrality, batch 10). EMTS is the RFS database of record for RIN transactions (40 CFR 80.1452); RECs are tracked in regional energy-attribute tracking systems whose specific operating rules are registry-specific — EPA material is context, not a universal registry-operating standard. Report Trades to SDR precedent (batch 08) applied. APQC: no meaningful candidate.</t>
+        </is>
+      </c>
+      <c r="U143" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V143" s="5" t="inlineStr">
+        <is>
+          <t>Keep instrument positions verified against the applicable regulatory and registry systems of record.</t>
+        </is>
+      </c>
+      <c r="W143" s="5" t="inlineStr">
+        <is>
+          <t>SRC-EPA-RFS-001 | SRC-EPA-EMTS-001 | SRC-EPA-REC-001</t>
+        </is>
+      </c>
       <c r="X143" s="5" t="n"/>
-      <c r="Y143" s="5" t="n"/>
-      <c r="Z143" s="5" t="n"/>
-      <c r="AA143" s="5" t="n"/>
-      <c r="AB143" s="5" t="n"/>
-      <c r="AC143" s="5" t="n"/>
+      <c r="Y143" s="5" t="inlineStr">
+        <is>
+          <t>Captured environmental and renewable deals (CM-1-2-1-3-6) | EMTS transaction records | registry statements and confirmations | blending and production data for RIN separation events</t>
+        </is>
+      </c>
+      <c r="Z143" s="5" t="inlineStr">
+        <is>
+          <t>Actualized instrument positions reconciled to EMTS and registries</t>
+        </is>
+      </c>
+      <c r="AA143" s="5" t="inlineStr">
+        <is>
+          <t>follows: Capture Environmental/Renewable Deals | informed-by: Forecast Renewables | precedes: Settle Emissions</t>
+        </is>
+      </c>
+      <c r="AB143" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC143" s="5" t="inlineStr">
+        <is>
+          <t>event-driven</t>
+        </is>
+      </c>
       <c r="AD143" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -19895,18 +20371,75 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U144" s="5" t="n"/>
-      <c r="V144" s="5" t="n"/>
-      <c r="W144" s="5" t="n"/>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>Manage disputes over what was physically delivered, received, measured, or performed — logging and classifying quantity, quality, and measurement discrepancies, investigating against custody-transfer evidence and independent inspection, coordinating investigation, evidence exchange, and agreement or adjudication of corrected actuals with the relevant external parties under the governing agreement and applicable measurement hierarchy, and closing disputes through corrected actualized records.</t>
+        </is>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>Covers the actualization dispute lifecycle across all modes: discrepancy logging and classification; investigation against tickets, inspection reports, and statements; coordination of investigation, evidence exchange, and agreement or adjudication of corrected actuals with counterparties, carriers, inspectors, and terminal operators under the governing agreement and applicable measurement hierarchy — some disputes resolve through independent surveyor findings, contract-defined measurement hierarchies, or contractual claims handling; escalation of aging or material disputes; and closure through corrected actualized records. Under the batch 10 dispute partition, this process answers 'what was physically delivered, received, measured, or performed'. An actualization dispute may inform, coexist with, or give rise to a settlement dispute; it is not universally a predecessor of one. Excludes confirmation disputes over agreed terms (Manage Confirm Disputes, CM-1-2-2-2-5); settlement disputes over amounts owed and paid (Manage Settlement Disputes, CM-1-2-4-1-17); demurrage claims (CM-1-2-4-4); financial recovery of carrier claims, which follows the relevant commercial agreements through settlement; legal proceedings, owned by Legal &amp; Corporate Communications.</t>
+        </is>
+      </c>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>Log and classify quantity, quality, and measurement discrepancies | investigate against custody-transfer and inspection evidence | coordinate evidence exchange and agreement or adjudication of corrected actuals under the governing agreement and measurement hierarchy | escalate and close disputes through corrected records</t>
+        </is>
+      </c>
+      <c r="Q144" t="inlineStr">
+        <is>
+          <t>Confirmation disputes (CM-1-2-2-2-5) | settlement disputes (CM-1-2-4-1-17) | demurrage claims (CM-1-2-4-4) | carrier claim recovery (commercial agreements via settlement) | legal proceedings (Legal &amp; Corporate Communications)</t>
+        </is>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>Batch 13 (2026-09-19). Dispute partition rule (Hamid, batch 10) applied verbatim: confirmation disputes answer 'what did the parties agree the terms were'; actualization disputes answer 'what was physically delivered, received, measured, or performed' (here); settlement disputes answer 'what is owed, invoiced, received, paid, netted, or applied'; demurrage claims answer 'was delay or capacity usage compensable'; legal proceedings belong to Legal &amp; Corporate Communications. The requested 'may-inform: Manage Settlement Disputes' relation has no controlled relationship_type; per the batch 10 conditional-relation precedent the rule is recorded here verbatim — an actualization dispute may inform, coexist with, or generate a settlement dispute — and the reciprocal 'informed-by: Manage Actualization Disputes' is queued for CM-1-2-4-1-17 in the Settlements batch. This process coordinates evidence and controlled correction; it does not claim unilateral power to settle every dispute — some require independent surveyor findings, contractual claims handling, or legal escalation. APQC 11743 is an unrelated routing candidate.</t>
+        </is>
+      </c>
+      <c r="U144" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V144" s="5" t="inlineStr">
+        <is>
+          <t>Resolve physical-delivery and measurement disagreements so the actualized record is correct and settlement proceeds on agreed actuals.</t>
+        </is>
+      </c>
+      <c r="W144" s="5" t="inlineStr">
+        <is>
+          <t>SRC-API-MPMS-001 | SRC-EI-HM32-001</t>
+        </is>
+      </c>
       <c r="X144" s="5" t="n"/>
-      <c r="Y144" s="5" t="n"/>
-      <c r="Z144" s="5" t="n"/>
-      <c r="AA144" s="5" t="n"/>
-      <c r="AB144" s="5" t="n"/>
-      <c r="AC144" s="5" t="n"/>
+      <c r="Y144" s="5" t="inlineStr">
+        <is>
+          <t>Actualization discrepancies from the mode processes | custody-transfer documents and inspection reports | counterparty, carrier, inspector, and operator communications</t>
+        </is>
+      </c>
+      <c r="Z144" s="5" t="inlineStr">
+        <is>
+          <t>Closed disputes with corrected actualized records</t>
+        </is>
+      </c>
+      <c r="AA144" s="5" t="inlineStr">
+        <is>
+          <t>follows: Actualizations | informed-by: Manage Confirm Disputes</t>
+        </is>
+      </c>
+      <c r="AB144" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC144" s="5" t="inlineStr">
+        <is>
+          <t>event-driven</t>
+        </is>
+      </c>
       <c r="AD144" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -48927,7 +49460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:I37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -50335,6 +50868,100 @@
         </is>
       </c>
       <c r="I35" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>SRC-EPA-EMTS-001</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>U.S. Environmental Protection Agency</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>EPA Moderated Transaction System (EMTS) requirements - RIN generation, separation, trade, and retirement transaction reporting</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Current regulation; accessed 2026-09-19</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>40 CFR 80.1452; https://www.ecfr.gov/current/title-40/chapter-I/subchapter-C/part-80/subpart-M/section-80.1452</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Regulatory</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>US RFS/EMTS transaction reporting and recordkeeping mechanics, including applicable party and account-holder obligations. Does not establish internal organizational ownership and does not apply to non-US programs, REC tracking systems, or all environmental instruments. Evidence only, not text to copy.</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>RIN transaction lifecycle (generation, separation, trade, retirement) and EMTS reporting mechanics for CM-1-2-3-1-7</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>SRC-EPA-REC-001</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>U.S. Environmental Protection Agency</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Renewable Energy Certificates (RECs) and Energy Attribute Tracking Systems (Green Power Markets)</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Accessed 2026-09-19</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>https://www.epa.gov/green-power-markets/renewable-energy-certificates-recs</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Regulatory (program guidance; voluntary-market and RPS-tracking context)</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>General REC and energy-attribute tracking-system terminology and context. Does not define requirements for a specific REC registry, renewable portfolio standard, voluntary-market claim, or enterprise operating responsibility. Evidence only, not text to copy.</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>REC and energy-attribute tracking-system context for CM-1-2-3-1-7</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
         <is>
           <t>active</t>
         </is>

--- a/business_architecture/ontology/build/output/step3c-definition-authoring-workbook.xlsx
+++ b/business_architecture/ontology/build/output/step3c-definition-authoring-workbook.xlsx
@@ -20507,18 +20507,80 @@
           <t>no meaningful APQC candidate</t>
         </is>
       </c>
-      <c r="U145" s="5" t="n"/>
-      <c r="V145" s="5" t="n"/>
-      <c r="W145" s="5" t="n"/>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>Determine and complete the financial settlement of trading transactions — calculating amounts owed and due from actualized quantities, contractual prices, and verified charge determinants; generating and validating invoices; netting where agreements provide; preparing, validating, and submitting authorized settlement instructions or payment requests to the designated Accounts Payable, Accounts Receivable, Treasury, banking, or shared-services process; tracking payment or receipt status; and retaining settlement evidence — so every transaction closes financially on verified actuals and contractual terms.</t>
+        </is>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>Covers the per-transaction settlement lifecycle across commodity, market-channel, and logistics-service variants: assembling actualized quantities and charge determinants, applying contractual and market prices and rates, calculating settlement amounts, generating outbound and validating inbound invoices and statements, netting under the governing agreements, preparing and submitting authorized settlement instructions and payment requests to the designated finance processes, tracking payment and receipt status, and retaining settlement evidence. Under the batch 10 partition, settlement answers 'what is owed, invoiced, received, paid, netted, or applied'. Consumes actualized records and charge determinants from Actualizations (CM-1-2-3-1) per the batch 13 charge-determinant rule. Where a contract bundles commodity value and logistics charges into one commercial settlement, the settlement process retains the contractual charge components and allocates them to the appropriate commodity and service settlement records where the accounting, tax, operational, or control model requires that distinction. Settlement does not independently approve payment release, initiate an unauthorized bank transfer, post accounting entries, apply cash, determine accounting treatment, or perform treasury cash management unless those authorities are expressly delegated in the enterprise operating model. Excludes actualization of quantities and determinants (CM-1-2-3-1); AR/AP booking, cash application, accruals, sub-ledger, general ledger, and tax, owned by Accounting (CM-1-2-4-2); payment release and bank execution (Treasury and banking processes per the enterprise operating model); financial write-offs and valuation (Finance, locked rule); demurrage claims (CM-1-2-4-4); credit exposure and limits (CM-1-2-2-1).</t>
+        </is>
+      </c>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>Calculate settlement amounts from actualized quantities, prices, and charge determinants | generate and validate invoices and settlement statements | net obligations under governing agreements | prepare, validate, and submit authorized settlement instructions and payment requests to the designated finance processes | track payment and receipt status and retain settlement evidence</t>
+        </is>
+      </c>
+      <c r="Q145" t="inlineStr">
+        <is>
+          <t>Actualization (CM-1-2-3-1) | AR/AP booking, cash application, accruals, and GL (CM-1-2-4-2) | payment release and bank execution (Treasury/banking processes) | write-offs and valuation (Finance, locked rule) | demurrage claims (CM-1-2-4-4) | credit exposure and limits (CM-1-2-2-1)</t>
+        </is>
+      </c>
+      <c r="R145" t="inlineStr">
+        <is>
+          <t>Trade Settlement | Commercial Settlement</t>
+        </is>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>Batch 14 (2026-09-20). Concept-type: process per the batch 08/13 variant test — one settlement lifecycle across commodity, channel, and logistics-service variants. Q2 decision (Hamid): commodity-value settlement (value of the commodity or instrument, with trade counterparties) and logistics-service settlement (freight, tariff, charter hire, throughput, storage, handling, with carriers and operators) are distinct; one physical delivery may legitimately produce both; bundled delivered-price contracts are allocated per the scope-note rule. Q3 decision (Hamid): Settlements determines contractual amounts, validates invoices and statements, manages netting, and prepares/submits authorized settlement instructions; Accounting owns booking, cash application, accruals, and GL; Treasury/banking executes payment release and bank movement; Finance owns write-offs and accounting policy (locked rule); the operating model locates these authorities (organizational neutrality, batch 10). Dispute partition (batch 10): settlement disputes answer 'what is owed, invoiced, received, paid, netted, or applied'. APQC 19948 is an unrelated candidate.</t>
+        </is>
+      </c>
+      <c r="U145" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V145" s="5" t="inlineStr">
+        <is>
+          <t>Close every trading transaction financially on verified actuals and contractual terms, with a controlled and evidenced trail from actual to authorized settlement instruction.</t>
+        </is>
+      </c>
+      <c r="W145" s="5" t="inlineStr">
+        <is>
+          <t>SRC-CFTC-GLOSS-001 | SRC-EIA-GLOSS-001</t>
+        </is>
+      </c>
       <c r="X145" s="5" t="n"/>
-      <c r="Y145" s="5" t="n"/>
-      <c r="Z145" s="5" t="n"/>
-      <c r="AA145" s="5" t="n"/>
-      <c r="AB145" s="5" t="n"/>
-      <c r="AC145" s="5" t="n"/>
+      <c r="Y145" s="5" t="inlineStr">
+        <is>
+          <t>Actualized deal, movement, and entitlement records (CM-1-2-3-1) | contractual prices, rates, and netting terms | counterparty, carrier, exchange, broker, ISO, and registry invoices and statements</t>
+        </is>
+      </c>
+      <c r="Z145" s="5" t="inlineStr">
+        <is>
+          <t>Settled transactions with validated invoices, netting, and authorized settlement instructions evidenced</t>
+        </is>
+      </c>
+      <c r="AA145" s="5" t="inlineStr">
+        <is>
+          <t>follows: Actualizations | informed-by: Confirmations Management | enables: Manage AR/AP &amp; Actuals</t>
+        </is>
+      </c>
+      <c r="AB145" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC145" s="5" t="inlineStr">
+        <is>
+          <t>event-driven</t>
+        </is>
+      </c>
       <c r="AD145" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -20581,18 +20643,75 @@
           <t>no meaningful APQC candidate</t>
         </is>
       </c>
-      <c r="U146" s="5" t="n"/>
-      <c r="V146" s="5" t="n"/>
-      <c r="W146" s="5" t="n"/>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>Settle physical crude oil and condensate purchases and sales — applying contractual pricing, including provisional pricing, deferred pricing, or subsequent price determination where the contract provides, and contractually defined quality adjustments to actualized volumes, issuing and validating invoices, netting where agreements allow, and submitting authorized payment and receipt instructions — so crude transactions complete financially on verified actuals.</t>
+        </is>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>Covers crude and condensate commodity-value settlement: assembling actualized volumes and qualities, applying contract price formulas, differentials, escalators, and contractually defined quality adjustments, managing provisional-to-final invoice cycles where the contract provides for provisional pricing, deferred pricing, or subsequent price determination, validating inbound invoices, netting, and preparing and submitting authorized payment and receipt instructions through the designated finance processes. Lease/first-purchase crude settles under Settle First Purchaser/Leases (CM-1-2-4-1-6). Transportation charges for the movements settle under the mode processes (CM-1-2-4-1-4/-5/-12/-13); bundled delivered-price contracts follow the L4 allocation rule. Excludes actualization (CM-1-2-3-1); exchange-cleared transactions (CM-1-2-4-1-3); settlement disputes (CM-1-2-4-1-17).</t>
+        </is>
+      </c>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>Apply contractual pricing and quality adjustments to actualized volumes | manage provisional and final invoice cycles where the contract provides | validate counterparty invoices and net where agreements provide | prepare and submit authorized payment or receipt instructions through the designated finance processes and track status</t>
+        </is>
+      </c>
+      <c r="Q146" t="inlineStr">
+        <is>
+          <t>First-purchase/lease settlement (CM-1-2-4-1-6) | transportation-charge settlement (mode processes) | actualization (CM-1-2-3-1) | exchange-cleared settlement (CM-1-2-4-1-3) | settlement disputes (CM-1-2-4-1-17)</t>
+        </is>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>Batch 14 (2026-09-20). Provisional/final invoicing applies only where the contract provides for provisional pricing, deferred pricing, or subsequent price determination. Quality adjustments follow the contractually defined specifications (gravity, sulfur, water and sediment, contaminants, volume-temperature basis, and other contract terms) — the contract governs, not a fixed list. Q2 commodity-value reading applied. APQC 12901 is an unrelated forecasting candidate.</t>
+        </is>
+      </c>
+      <c r="U146" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V146" s="5" t="inlineStr">
+        <is>
+          <t>Complete crude purchases and sales financially on actualized volumes and contractual pricing.</t>
+        </is>
+      </c>
+      <c r="W146" s="5" t="inlineStr">
+        <is>
+          <t>SRC-CFTC-GLOSS-001 | SRC-EIA-GLOSS-001</t>
+        </is>
+      </c>
       <c r="X146" s="5" t="n"/>
-      <c r="Y146" s="5" t="n"/>
-      <c r="Z146" s="5" t="n"/>
-      <c r="AA146" s="5" t="n"/>
-      <c r="AB146" s="5" t="n"/>
-      <c r="AC146" s="5" t="n"/>
+      <c r="Y146" s="5" t="inlineStr">
+        <is>
+          <t>Actualized crude movements (CM-1-2-3-1) | contract pricing terms | price indices and quotations | counterparty invoices</t>
+        </is>
+      </c>
+      <c r="Z146" s="5" t="inlineStr">
+        <is>
+          <t>Settled crude transactions with validated invoices and authorized payment instructions</t>
+        </is>
+      </c>
+      <c r="AA146" s="5" t="inlineStr">
+        <is>
+          <t>follows: Perform Pipeline Actualization | follows: Perform Vessel &amp; Barge Actualization | precedes: Manage AR/AP &amp; Actuals</t>
+        </is>
+      </c>
+      <c r="AB146" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC146" s="5" t="inlineStr">
+        <is>
+          <t>event-driven</t>
+        </is>
+      </c>
       <c r="AD146" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -20660,18 +20779,75 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U147" s="5" t="n"/>
-      <c r="V147" s="5" t="n"/>
-      <c r="W147" s="5" t="n"/>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>Settle physical refined product purchases and sales — applying contractual and index-based pricing to actualized volumes on the contractual measurement basis, generating and validating invoices, netting where agreements provide, and submitting authorized payment and receipt instructions — so product transactions complete financially on verified actuals.</t>
+        </is>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>Covers refined-product commodity-value settlement: assembling actualized volumes and qualities, applying contract and index pricing with differentials and adjustments, generating outbound and validating inbound invoices, netting, and preparing and submitting authorized payment and receipt instructions through the designated finance processes. The product-versus-intermediate boundary follows the commodity classification, product master, and commercial classification captured with the deal — not the physical location or whether a stream is used inside a refinery; intermediates settle under Settle Intermediates (CM-1-2-4-1-18). Product exchange agreements settle per their agreement terms with imbalance treatment administered under Manage Product Exchange Agreements (CM-1-2-7-1-1). Transportation and terminal charges settle under the mode processes; bundled delivered-price contracts follow the L4 allocation rule. Excludes actualization (CM-1-2-3-1); settlement disputes (CM-1-2-4-1-17).</t>
+        </is>
+      </c>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>Apply contractual and index pricing to actualized product volumes | generate and validate invoices | net where agreements provide | prepare and submit authorized payment or receipt instructions through the designated finance processes and track status</t>
+        </is>
+      </c>
+      <c r="Q147" t="inlineStr">
+        <is>
+          <t>Intermediates settlement (CM-1-2-4-1-18) | exchange-agreement administration (CM-1-2-7-1-1) | transportation and terminal charges (mode processes) | actualization (CM-1-2-3-1) | settlement disputes (CM-1-2-4-1-17)</t>
+        </is>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>Batch 14 (2026-09-20). Q2 commodity-value reading applied. Product-versus-intermediate partition rule (Hamid, batch 14): follows the commodity classification, product master, and commercial classification captured with the deal — not simply the physical location or refinery use; matters for blendstocks, refinery intermediates, bio-components, and imported feedstocks. APQC 12914 'Sell by-products' is a WEAK sales candidate, not settlement.</t>
+        </is>
+      </c>
+      <c r="U147" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V147" s="5" t="inlineStr">
+        <is>
+          <t>Complete refined product purchases and sales financially on actualized volumes and contractual pricing.</t>
+        </is>
+      </c>
+      <c r="W147" s="5" t="inlineStr">
+        <is>
+          <t>SRC-CFTC-GLOSS-001 | SRC-EIA-GLOSS-001</t>
+        </is>
+      </c>
       <c r="X147" s="5" t="n"/>
-      <c r="Y147" s="5" t="n"/>
-      <c r="Z147" s="5" t="n"/>
-      <c r="AA147" s="5" t="n"/>
-      <c r="AB147" s="5" t="n"/>
-      <c r="AC147" s="5" t="n"/>
+      <c r="Y147" s="5" t="inlineStr">
+        <is>
+          <t>Actualized product movements | contract and index pricing terms | counterparty invoices</t>
+        </is>
+      </c>
+      <c r="Z147" s="5" t="inlineStr">
+        <is>
+          <t>Settled product transactions</t>
+        </is>
+      </c>
+      <c r="AA147" s="5" t="inlineStr">
+        <is>
+          <t>follows: Actualizations | precedes: Manage AR/AP &amp; Actuals</t>
+        </is>
+      </c>
+      <c r="AB147" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC147" s="5" t="inlineStr">
+        <is>
+          <t>event-driven</t>
+        </is>
+      </c>
       <c r="AD147" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -20739,18 +20915,75 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U148" s="5" t="n"/>
-      <c r="V148" s="5" t="n"/>
-      <c r="W148" s="5" t="n"/>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>Settle exchange-traded and cleared transactions — validating and allocating daily settlement variation and final settlement amounts to trades and positions against exchange and clearinghouse values, settling expiries, exercises, and deliveries per contract specifications, and reconciling trade-level settlement outcomes — so cleared positions complete financially per exchange rules.</t>
+        </is>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>Covers trade-level settlement of exchange-traded and cleared instruments: validating daily settlement prices and variation amounts against clearinghouse determinations and allocating them to trades and positions, settling contract expiries, option exercises and assignments, and physically delivered exchange contracts per contract specifications, and reconciling settlement outcomes at the trade and position level. Daily settlement variation may operationally flow through the broker or clearing account: this process validates and allocates the exchange and clearing settlement values; Settle Broker (CM-1-2-4-1-16) reconciles the broker account and coordinates the associated cash movement. Margin requirement validation and calls are owned by Perform Margining (CM-1-2-2-1-5). Excludes exchange trade capture (CM-1-2-1-3-4); settlement disputes (CM-1-2-4-1-17).</t>
+        </is>
+      </c>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>Validate and allocate daily settlement variation against clearinghouse values | settle expiries, exercises, assignments, and deliveries per contract specifications | reconcile trade-level settlement outcomes</t>
+        </is>
+      </c>
+      <c r="Q148" t="inlineStr">
+        <is>
+          <t>Margining (CM-1-2-2-1-5) | broker account reconciliation and associated cash movement (CM-1-2-4-1-16) | exchange trade capture (CM-1-2-1-3-4) | settlement disputes (CM-1-2-4-1-17)</t>
+        </is>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>Batch 14 (2026-09-20). Q4 decision (Hamid): trade/position-level settlement under exchange and clearing rules here; the broker/clearing-member account relationship at CM-1-2-4-1-16; margin requirement control at CM-1-2-2-1-5. Daily settlement variation is often handled operationally through the broker/clearing account rather than as a standalone trade-level payment — the split is validate-and-allocate here, reconcile-and-coordinate-cash there. Settlement values are determined by the exchange/clearinghouse; this process validates and applies them, consistent with the batch 11 validate-not-recalculate pattern. APQC 19582 is an FX-execution candidate, not settlement.</t>
+        </is>
+      </c>
+      <c r="U148" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V148" s="5" t="inlineStr">
+        <is>
+          <t>Ensure cleared transactions settle exactly per exchange and clearinghouse determinations, with discrepancies surfaced.</t>
+        </is>
+      </c>
+      <c r="W148" s="5" t="inlineStr">
+        <is>
+          <t>SRC-CFTC-GLOSS-001</t>
+        </is>
+      </c>
       <c r="X148" s="5" t="n"/>
-      <c r="Y148" s="5" t="n"/>
-      <c r="Z148" s="5" t="n"/>
-      <c r="AA148" s="5" t="n"/>
-      <c r="AB148" s="5" t="n"/>
-      <c r="AC148" s="5" t="n"/>
+      <c r="Y148" s="5" t="inlineStr">
+        <is>
+          <t>Captured exchange trades (CM-1-2-1-3-4) | exchange and clearinghouse settlement values | contract specifications</t>
+        </is>
+      </c>
+      <c r="Z148" s="5" t="inlineStr">
+        <is>
+          <t>Settled exchange transactions reconciled to clearinghouse values</t>
+        </is>
+      </c>
+      <c r="AA148" s="5" t="inlineStr">
+        <is>
+          <t>follows: Capture Exchange Trades | informed-by: Perform Margining | precedes: Settle Broker</t>
+        </is>
+      </c>
+      <c r="AB148" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC148" s="5" t="inlineStr">
+        <is>
+          <t>event-driven</t>
+        </is>
+      </c>
       <c r="AD148" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -20818,18 +21051,75 @@
           <t>no meaningful APQC candidate</t>
         </is>
       </c>
-      <c r="U149" s="5" t="n"/>
-      <c r="V149" s="5" t="n"/>
-      <c r="W149" s="5" t="n"/>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>Settle truck transportation charges with carriers — validating freight invoices against actualized movements and verified freight-charge determinants, applying contracted rates and accessorials, resolving invoice variances, and submitting authorized payment instructions — so trucking services complete financially on verified movement actuals.</t>
+        </is>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>Covers logistics-service settlement for truck movements: validating carrier freight invoices against actualized truck movements and the freight-charge determinants recorded at actualization (CM-1-2-3-1-2), applying contracted rates, fuel surcharges, and accessorial charges, resolving rate and quantity variances with carriers, netting where agreements provide, and preparing and submitting authorized payment instructions through the designated finance processes. The commodity value of the moved product settles under the commodity processes; bundled delivered-price contracts follow the L4 allocation rule. Excludes truck actualization (CM-1-2-3-1-2); carrier contracting (the owning logistics and procurement processes); settlement disputes (CM-1-2-4-1-17).</t>
+        </is>
+      </c>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>Validate carrier freight invoices against actualized movements and determinants | apply contracted rates, surcharges, and accessorials | resolve carrier invoice variances | prepare and submit authorized payment or receipt instructions through the designated finance processes and track status</t>
+        </is>
+      </c>
+      <c r="Q149" t="inlineStr">
+        <is>
+          <t>Commodity-value settlement (commodity processes) | truck actualization (CM-1-2-3-1-2) | carrier contracting (logistics/procurement processes) | settlement disputes (CM-1-2-4-1-17)</t>
+        </is>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>Batch 14 (2026-09-20). Q2 logistics-service reading applied: this row settles the trucking service charge; the product value settles under the commodity rows; one delivery may produce both settlement streams. APQC: no meaningful candidate.</t>
+        </is>
+      </c>
+      <c r="U149" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V149" s="5" t="inlineStr">
+        <is>
+          <t>Pay carriers correctly for verified trucking services.</t>
+        </is>
+      </c>
+      <c r="W149" s="5" t="inlineStr">
+        <is>
+          <t>SRC-EIA-GLOSS-001</t>
+        </is>
+      </c>
       <c r="X149" s="5" t="n"/>
-      <c r="Y149" s="5" t="n"/>
-      <c r="Z149" s="5" t="n"/>
-      <c r="AA149" s="5" t="n"/>
-      <c r="AB149" s="5" t="n"/>
-      <c r="AC149" s="5" t="n"/>
+      <c r="Y149" s="5" t="inlineStr">
+        <is>
+          <t>Actualized truck movements and freight determinants (CM-1-2-3-1-2) | carrier invoices | contracted rates</t>
+        </is>
+      </c>
+      <c r="Z149" s="5" t="inlineStr">
+        <is>
+          <t>Settled truck freight charges</t>
+        </is>
+      </c>
+      <c r="AA149" s="5" t="inlineStr">
+        <is>
+          <t>follows: Perform Truck Actualization | precedes: Manage AR/AP &amp; Actuals</t>
+        </is>
+      </c>
+      <c r="AB149" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC149" s="5" t="inlineStr">
+        <is>
+          <t>event-driven</t>
+        </is>
+      </c>
       <c r="AD149" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -20892,18 +21182,75 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U150" s="5" t="n"/>
-      <c r="V150" s="5" t="n"/>
-      <c r="W150" s="5" t="n"/>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>Settle marine transportation charges — validating freight, charter hire, and voyage-related invoices against actualized voyages and verified freight, laytime, and voyage-cost determinants, applying charter party and freight-agreement terms, resolving variances, and submitting authorized payment instructions — so marine services complete financially on verified voyage actuals.</t>
+        </is>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>Covers logistics-service settlement for marine movements: validating owner and operator invoices for freight, charter hire, deadfreight, and other agreed voyage-service charges against actualized voyages and the determinants recorded at actualization (CM-1-2-3-1-4), applying charter party and contract-of-affreightment terms, resolving variances, and preparing and submitting authorized payment instructions through the designated finance processes. Freight and agreed voyage-service charges are settled here; demurrage, detention, despatch, and delay compensation follow the governing charter party, terminal agreement, or transport contract and are handled by Demurrage Management (CM-1-2-4-4) where that process is in scope, per the batch 10 partition. The cargo value settles under the commodity processes. Excludes marine actualization (CM-1-2-3-1-4); chartering and voyage operations (marine logistics processes); demurrage, detention, despatch, and delay compensation (CM-1-2-4-4); settlement disputes (CM-1-2-4-1-17).</t>
+        </is>
+      </c>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>Validate freight, charter hire, and voyage-charge invoices against actualized voyages | apply charter party and freight-agreement terms | resolve variances with owners and operators | prepare and submit authorized payment or receipt instructions through the designated finance processes and track status</t>
+        </is>
+      </c>
+      <c r="Q150" t="inlineStr">
+        <is>
+          <t>Cargo-value settlement (commodity processes) | marine actualization (CM-1-2-3-1-4) | demurrage, detention, despatch, and delay compensation (CM-1-2-4-4) | chartering (marine logistics processes) | settlement disputes (CM-1-2-4-1-17)</t>
+        </is>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>Batch 14 (2026-09-20). Q2 logistics-service reading applied. Agreed freight and voyage-service charges settle here; delay and capacity compensation (demurrage, detention, despatch) stays wholly with CM-1-2-4-4 — not all maritime claims are demurrage, and the governing agreement decides the claim type. APQC 12927 'Qualify vessels' is a vetting candidate, not settlement.</t>
+        </is>
+      </c>
+      <c r="U150" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V150" s="5" t="inlineStr">
+        <is>
+          <t>Pay marine service providers correctly for verified voyage services.</t>
+        </is>
+      </c>
+      <c r="W150" s="5" t="inlineStr">
+        <is>
+          <t>SRC-EIA-GLOSS-001</t>
+        </is>
+      </c>
       <c r="X150" s="5" t="n"/>
-      <c r="Y150" s="5" t="n"/>
-      <c r="Z150" s="5" t="n"/>
-      <c r="AA150" s="5" t="n"/>
-      <c r="AB150" s="5" t="n"/>
-      <c r="AC150" s="5" t="n"/>
+      <c r="Y150" s="5" t="inlineStr">
+        <is>
+          <t>Actualized voyages and voyage-cost determinants (CM-1-2-3-1-4) | owner and operator invoices | charter party and freight terms</t>
+        </is>
+      </c>
+      <c r="Z150" s="5" t="inlineStr">
+        <is>
+          <t>Settled marine transportation charges</t>
+        </is>
+      </c>
+      <c r="AA150" s="5" t="inlineStr">
+        <is>
+          <t>follows: Perform Vessel &amp; Barge Actualization | precedes: Manage AR/AP &amp; Actuals</t>
+        </is>
+      </c>
+      <c r="AB150" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC150" s="5" t="inlineStr">
+        <is>
+          <t>event-driven</t>
+        </is>
+      </c>
       <c r="AD150" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -20971,18 +21318,75 @@
           <t>no meaningful APQC candidate</t>
         </is>
       </c>
-      <c r="U151" s="5" t="n"/>
-      <c r="V151" s="5" t="n"/>
-      <c r="W151" s="5" t="n"/>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>Settle crude and condensate first-purchase transactions — calculating amounts due from actualized lease runs under contractual pricing, gravity and quality adjustments, and deductions, producing settlement statements consistent with the division-of-interest references, and submitting authorized payment instructions — so lease purchases complete financially on verified run actuals.</t>
+        </is>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>Included only where the downstream Supply &amp; Trading organization purchases crude or condensate at lease/wellhead or administers first-purchaser arrangements, per the batch 09 scope caveat. Covers first-purchaser settlement: assembling actualized lease runs (Perform Lease Actualization, CM-1-2-3-1-6), applying contract pricing, gravity and quality adjustments, and deductions maintained under Manage Lease Contract (CM-1-2-1-2-8), producing lease settlement statements consistent with division-of-interest references, and preparing and submitting authorized payment instructions through the designated finance processes. Royalty and interest payment execution to owners is owned by Manage Marketing Interests &amp; Royalty Payments (CM-1-2-4-2-3). This process does not absorb upstream land and lease administration, production allocation, royalty policy, exploration-and-production accounting, owner-payment entitlement calculation policy, or statutory first-purchaser compliance obligations not delegated to downstream. Excludes lease actualization (CM-1-2-3-1-6); lease contract administration (CM-1-2-1-2-8); settlement disputes (CM-1-2-4-1-17).</t>
+        </is>
+      </c>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>Calculate first-purchase amounts from actualized runs and contract terms | produce lease settlement statements consistent with division-of-interest references | prepare and submit authorized payment or receipt instructions through the designated finance processes and track status | synchronize with royalty-payment execution</t>
+        </is>
+      </c>
+      <c r="Q151" t="inlineStr">
+        <is>
+          <t>Royalty and interest payment execution (CM-1-2-4-2-3) | lease actualization (CM-1-2-3-1-6) | lease contract administration (CM-1-2-1-2-8) | upstream land/lease administration, production allocation, royalty policy, E&amp;P accounting, owner-payment entitlement policy, and non-delegated statutory first-purchaser compliance (outside scope) | settlement disputes (CM-1-2-4-1-17)</t>
+        </is>
+      </c>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>Batch 14 (2026-09-20). Conditional downstream scope: 'first purchaser' per the batch 09 crude-marketing reading; the standing batch 09 follow-up on whether lease-purchase activity is genuinely downstream-owned or a cross-segment/integrated-company exception applies here and is carried in the batch 14 PR. APQC: no meaningful candidate.</t>
+        </is>
+      </c>
+      <c r="U151" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V151" s="5" t="inlineStr">
+        <is>
+          <t>Complete lease purchases financially on verified runs and contractual terms, feeding correct interest-level payment execution.</t>
+        </is>
+      </c>
+      <c r="W151" s="5" t="inlineStr">
+        <is>
+          <t>SRC-API-MPMS-001</t>
+        </is>
+      </c>
       <c r="X151" s="5" t="n"/>
-      <c r="Y151" s="5" t="n"/>
-      <c r="Z151" s="5" t="n"/>
-      <c r="AA151" s="5" t="n"/>
-      <c r="AB151" s="5" t="n"/>
-      <c r="AC151" s="5" t="n"/>
+      <c r="Y151" s="5" t="inlineStr">
+        <is>
+          <t>Actualized lease runs (CM-1-2-3-1-6) | lease contract pricing and deduction terms (CM-1-2-1-2-8) | division-of-interest references</t>
+        </is>
+      </c>
+      <c r="Z151" s="5" t="inlineStr">
+        <is>
+          <t>Settled first-purchase transactions with statements for payment execution</t>
+        </is>
+      </c>
+      <c r="AA151" s="5" t="inlineStr">
+        <is>
+          <t>follows: Perform Lease Actualization | precedes: Manage Marketing Interests &amp; Royalty Payments</t>
+        </is>
+      </c>
+      <c r="AB151" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC151" s="5" t="inlineStr">
+        <is>
+          <t>event-driven</t>
+        </is>
+      </c>
       <c r="AD151" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -21050,18 +21454,75 @@
           <t>no meaningful APQC candidate</t>
         </is>
       </c>
-      <c r="U152" s="5" t="n"/>
-      <c r="V152" s="5" t="n"/>
-      <c r="W152" s="5" t="n"/>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>Settle transactions with independent system operators, regional transmission organizations, and power pools — validating ISO settlement statements across the day-ahead and real-time settlement cycles and their subsequent true-up versions, performing independent shadow-settlement checks, disputing discrepancies within ISO timelines, and submitting authorized payment and receipt instructions — so ISO-cleared activity completes financially per market rules.</t>
+        </is>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>Covers ISO/RTO and power-pool settlement: receiving and validating settlement statements for energy, capacity, ancillary services, transmission, and associated charge types under the market's two-settlement (day-ahead/real-time) design and multi-version true-up calendar; performing shadow settlement against internal scheduling and metering data; raising statement disputes within the ISO's dispute windows; and preparing and submitting authorized payment and receipt instructions through the designated finance processes. The applicable ISO/RTO settlement statement is the governing market settlement record under that market's tariff, subject to the organization's validation and dispute rights; the ISO tariff is authoritative for charge types, timing, dispute windows, and true-up treatment. Bilateral (non-ISO) power settles under Settle Power (CM-1-2-4-1-15). Excludes market participation strategy and bidding (trading processes); transmission deal capture (CM-1-2-1-3-11); settlement disputes outside ISO statement processes (CM-1-2-4-1-17).</t>
+        </is>
+      </c>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>Validate ISO settlement statements across versions and charge types | perform shadow settlement against internal data | raise statement disputes within ISO timelines | prepare and submit authorized payment or receipt instructions through the designated finance processes and track status</t>
+        </is>
+      </c>
+      <c r="Q152" t="inlineStr">
+        <is>
+          <t>Bilateral power settlement (CM-1-2-4-1-15) | bidding and market participation strategy (trading processes) | transmission deal capture (CM-1-2-1-3-11) | non-ISO settlement disputes (CM-1-2-4-1-17)</t>
+        </is>
+      </c>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>Batch 14 (2026-09-20). Q5: no actualization sibling — the applicable ISO/RTO settlement statement is the governing market settlement record under that market's tariff, subject to validation and dispute rights; shadow settlement is the internal verification and control step. ISO/RTO applicability is jurisdiction-specific (US market design per FERC; other jurisdictions differ), and each ISO's tariff and business-practice manuals govern its settlement calendar, billing determinants, and dispute procedures. APQC: no meaningful candidate.</t>
+        </is>
+      </c>
+      <c r="U152" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V152" s="5" t="inlineStr">
+        <is>
+          <t>Ensure ISO-cleared activity settles exactly per validated market statements, with discrepancies disputed in time.</t>
+        </is>
+      </c>
+      <c r="W152" s="5" t="inlineStr">
+        <is>
+          <t>SRC-FERC-RTO-001</t>
+        </is>
+      </c>
       <c r="X152" s="5" t="n"/>
-      <c r="Y152" s="5" t="n"/>
-      <c r="Z152" s="5" t="n"/>
-      <c r="AA152" s="5" t="n"/>
-      <c r="AB152" s="5" t="n"/>
-      <c r="AC152" s="5" t="n"/>
+      <c r="Y152" s="5" t="inlineStr">
+        <is>
+          <t>ISO settlement statements and true-ups | internal scheduling and metering data | market tariff and charge-type references</t>
+        </is>
+      </c>
+      <c r="Z152" s="5" t="inlineStr">
+        <is>
+          <t>Validated and settled ISO statements</t>
+        </is>
+      </c>
+      <c r="AA152" s="5" t="inlineStr">
+        <is>
+          <t>follows: Capture Transmission Deals | precedes: Manage AR/AP &amp; Actuals</t>
+        </is>
+      </c>
+      <c r="AB152" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC152" s="5" t="inlineStr">
+        <is>
+          <t>event-driven</t>
+        </is>
+      </c>
       <c r="AD152" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -21124,18 +21585,80 @@
           <t>no meaningful APQC candidate</t>
         </is>
       </c>
-      <c r="U153" s="5" t="n"/>
-      <c r="V153" s="5" t="n"/>
-      <c r="W153" s="5" t="n"/>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>Settle environmental and renewable instrument transactions — RINs, allowances, RECs, and similar program instruments — calculating amounts due from actualized registry transfers and contractual pricing, generating and validating invoices, and submitting authorized payment instructions against confirmed instrument delivery — so instrument trades complete financially on verified registry actuals.</t>
+        </is>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>Covers financial settlement of environmental-instrument transactions: assembling actualized registry lifecycle events (Perform RINs/REC Actualization, CM-1-2-3-1-7), applying contract pricing, generating and validating invoices, preparing and submitting authorized payment instructions through the designated finance processes against confirmed registry transfer or retirement where the contract links payment to delivery, and evidencing completion. Program applicability is jurisdiction-specific. Excludes instrument actualization and registry-event processing (CM-1-2-3-1-7); deal capture (CM-1-2-1-3-6); compliance filings and RVO demonstrations (EHS &amp; Government Reporting, locked rule); allowance-position economics (CM-1-1-7-3-3); settlement disputes (CM-1-2-4-1-17).</t>
+        </is>
+      </c>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>Calculate amounts due from actualized registry events and contract pricing | generate and validate instrument invoices | prepare and submit authorized payment or receipt instructions through the designated finance processes and track status | evidence completion against confirmed transfers</t>
+        </is>
+      </c>
+      <c r="Q153" t="inlineStr">
+        <is>
+          <t>Registry-event processing and reconciliation (CM-1-2-3-1-7) | deal capture (CM-1-2-1-3-6) | compliance filings (EHS &amp; Government Reporting) | allowance-position economics (CM-1-1-7-3-3) | settlement disputes (CM-1-2-4-1-17)</t>
+        </is>
+      </c>
+      <c r="R153" t="inlineStr">
+        <is>
+          <t>Settle Environmental Instruments</t>
+        </is>
+      </c>
+      <c r="T153" t="inlineStr">
+        <is>
+          <t>Batch 14 (2026-09-20). Row name reads 'Emissions' but the settled scope spans the environmental-instrument families handled by capture (CM-1-2-1-3-6) and actualization (CM-1-2-3-1-7): RINs, allowances, RECs, and similar program instruments; 'Settle Environmental Instruments' queued for the naming pass. Payment-versus-transfer linkage is contract-specific. APQC 19511 is a vehicle-testing candidate, unrelated.</t>
+        </is>
+      </c>
+      <c r="U153" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V153" s="5" t="inlineStr">
+        <is>
+          <t>Complete environmental-instrument trades financially against verified registry delivery.</t>
+        </is>
+      </c>
+      <c r="W153" s="5" t="inlineStr">
+        <is>
+          <t>SRC-EPA-RFS-001 | SRC-EPA-REC-001</t>
+        </is>
+      </c>
       <c r="X153" s="5" t="n"/>
-      <c r="Y153" s="5" t="n"/>
-      <c r="Z153" s="5" t="n"/>
-      <c r="AA153" s="5" t="n"/>
-      <c r="AB153" s="5" t="n"/>
-      <c r="AC153" s="5" t="n"/>
+      <c r="Y153" s="5" t="inlineStr">
+        <is>
+          <t>Actualized registry events (CM-1-2-3-1-7) | contract pricing | counterparty invoices</t>
+        </is>
+      </c>
+      <c r="Z153" s="5" t="inlineStr">
+        <is>
+          <t>Settled environmental-instrument transactions</t>
+        </is>
+      </c>
+      <c r="AA153" s="5" t="inlineStr">
+        <is>
+          <t>follows: Perform RINs/REC Actualization | precedes: Manage AR/AP &amp; Actuals</t>
+        </is>
+      </c>
+      <c r="AB153" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC153" s="5" t="inlineStr">
+        <is>
+          <t>event-driven</t>
+        </is>
+      </c>
       <c r="AD153" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -21198,18 +21721,75 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U154" s="5" t="n"/>
-      <c r="V154" s="5" t="n"/>
-      <c r="W154" s="5" t="n"/>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>Manage the controlled working and evidentiary document set used by trading settlement — generating, receiving, validating, distributing, and retaining settlement statements, payment instructions, supporting actualization evidence, and applicable invoices — so every settlement is executed and evidenced from controlled, complete documents.</t>
+        </is>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>Covers the settlement document working set across all settlement processes: outbound invoice and statement generation and distribution; inbound document receipt, registration, and completeness checking; association of supporting evidence (tickets, inspection reports, statements) with the settlement record; netting statement documentation; and retention and retrieval of the settlement working set per the applicable requirements. This process controls settlement documents for trading settlement purposes; it is not the legal system of record for every enterprise invoice and does not own enterprise records-retention policy. Excludes confirmation documentation (Manage Confirmation Documentation, CM-1-2-2-2-2); contract and legal documents (Contract Management, CM-1-2-1-2; Legal &amp; Corporate Communications); accounting records and financial-reporting documentation and workpapers (CM-1-2-4-2-7); enterprise records-retention policy (the accountable governance owner); the settlement calculations themselves (the owning settlement processes).</t>
+        </is>
+      </c>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>Generate and distribute outbound invoices and statements | receive, register, and completeness-check inbound documents | associate supporting evidence with settlement records | retain and retrieve the settlement working set per applicable requirements</t>
+        </is>
+      </c>
+      <c r="Q154" t="inlineStr">
+        <is>
+          <t>Confirmation documents (CM-1-2-2-2-2) | contract and legal documents (CM-1-2-1-2, Legal &amp; Corporate Communications) | accounting and financial-reporting records and workpapers (CM-1-2-4-2-7) | enterprise records-retention policy (governance owner) | settlement calculation (owning settlement processes)</t>
+        </is>
+      </c>
+      <c r="T154" t="inlineStr">
+        <is>
+          <t>Batch 14 (2026-09-20). Document-control process serving the settlement family, parallel to Manage Confirmation Documentation (batch 10); scope is the trading-settlement working and evidentiary set, not the enterprise document system of record. Record-retention requirements are jurisdiction- and instrument-specific. APQC 19601 is an HSSE-records candidate, not trading settlement.</t>
+        </is>
+      </c>
+      <c r="U154" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V154" s="5" t="inlineStr">
+        <is>
+          <t>Keep settlement execution running on complete, controlled, retrievable documents.</t>
+        </is>
+      </c>
+      <c r="W154" s="5" t="inlineStr">
+        <is>
+          <t>SRC-CFTC-GLOSS-001</t>
+        </is>
+      </c>
       <c r="X154" s="5" t="n"/>
-      <c r="Y154" s="5" t="n"/>
-      <c r="Z154" s="5" t="n"/>
-      <c r="AA154" s="5" t="n"/>
-      <c r="AB154" s="5" t="n"/>
-      <c r="AC154" s="5" t="n"/>
+      <c r="Y154" s="5" t="inlineStr">
+        <is>
+          <t>Settlement calculations and statements from the settlement processes | inbound counterparty and carrier documents | retention requirements</t>
+        </is>
+      </c>
+      <c r="Z154" s="5" t="inlineStr">
+        <is>
+          <t>Controlled, retained settlement documentation linked to settlement records</t>
+        </is>
+      </c>
+      <c r="AA154" s="5" t="inlineStr">
+        <is>
+          <t>assures: Settlements | informed-by: Manage Confirmation Documentation</t>
+        </is>
+      </c>
+      <c r="AB154" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC154" s="5" t="inlineStr">
+        <is>
+          <t>event-driven</t>
+        </is>
+      </c>
       <c r="AD154" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -21277,18 +21857,75 @@
           <t>no meaningful APQC candidate</t>
         </is>
       </c>
-      <c r="U155" s="5" t="n"/>
-      <c r="V155" s="5" t="n"/>
-      <c r="W155" s="5" t="n"/>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>Settle natural gas purchases, sales, transportation, and storage — applying index and contract pricing to scheduled and flowing-gas quantities, validating pipeline and counterparty invoices per the applicable business-practice standards, settling imbalances and cash-outs per tariff and contract, and submitting authorized payment and receipt instructions — so gas transactions complete financially on verified quantities.</t>
+        </is>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>Covers natural gas settlement: applying first-of-month and daily index and contract pricing to confirmed scheduled and allocated flowing-gas quantities, validating transporter and counterparty invoices following the applicable wholesale gas business-practice standards (NAESB WGQ invoicing standards in US interstate practice), settling transportation, fuel, and imbalance charges and cash-outs per tariff and contract, netting, and preparing and submitting authorized payment and receipt instructions through the designated finance processes. Pipeline allocation, flow, imbalance, and invoice statements provide the applicable quantity and charge basis under the relevant tariff, contract, and allocation methodology (no separate actualization sibling, per the batch 14 Q5 note); the specific pipeline's tariff and the bilateral contracts govern the transaction. Gas scheduling and nominations are owned by the gas scheduling processes. Excludes gas trading and capture (CM-1-2-1-3); settlement disputes (CM-1-2-4-1-17).</t>
+        </is>
+      </c>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>Apply index and contract pricing to allocated gas quantities | validate transporter and counterparty invoices per applicable standards | settle imbalances and cash-outs per tariff and contract | prepare and submit authorized payment or receipt instructions through the designated finance processes and track status</t>
+        </is>
+      </c>
+      <c r="Q155" t="inlineStr">
+        <is>
+          <t>Gas nominations and scheduling (gas scheduling processes) | gas deal capture (CM-1-2-1-3) | settlement disputes (CM-1-2-4-1-17)</t>
+        </is>
+      </c>
+      <c r="T155" t="inlineStr">
+        <is>
+          <t>Batch 14 (2026-09-20). Q5: pipeline allocation, flow, imbalance, and invoice statements provide the applicable quantity and charge basis under the relevant tariff, contract, and allocation methodology — pipeline tariffs and bilateral agreements govern the specific transaction and take precedence; NAESB WGQ standards are US industry-practice context, jurisdiction-specific elsewhere. APQC: no meaningful candidate.</t>
+        </is>
+      </c>
+      <c r="U155" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V155" s="5" t="inlineStr">
+        <is>
+          <t>Complete gas transactions financially on allocated quantities, applicable indices, and tariff terms.</t>
+        </is>
+      </c>
+      <c r="W155" s="5" t="inlineStr">
+        <is>
+          <t>SRC-NAESB-WGQ-001 | SRC-EIA-GLOSS-001</t>
+        </is>
+      </c>
       <c r="X155" s="5" t="n"/>
-      <c r="Y155" s="5" t="n"/>
-      <c r="Z155" s="5" t="n"/>
-      <c r="AA155" s="5" t="n"/>
-      <c r="AB155" s="5" t="n"/>
-      <c r="AC155" s="5" t="n"/>
+      <c r="Y155" s="5" t="inlineStr">
+        <is>
+          <t>Confirmed nominations and allocated flowing-gas statements | index prices and contract terms | transporter and counterparty invoices</t>
+        </is>
+      </c>
+      <c r="Z155" s="5" t="inlineStr">
+        <is>
+          <t>Settled gas transactions</t>
+        </is>
+      </c>
+      <c r="AA155" s="5" t="inlineStr">
+        <is>
+          <t>follows: Capture Physical Trades | precedes: Manage AR/AP &amp; Actuals</t>
+        </is>
+      </c>
+      <c r="AB155" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC155" s="5" t="inlineStr">
+        <is>
+          <t>event-driven</t>
+        </is>
+      </c>
       <c r="AD155" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -21351,18 +21988,75 @@
           <t>no meaningful APQC candidate</t>
         </is>
       </c>
-      <c r="U156" s="5" t="n"/>
-      <c r="V156" s="5" t="n"/>
-      <c r="W156" s="5" t="n"/>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>Settle bilateral financial over-the-counter derivatives — determining settlement amounts from contractual fixings and floating-price observations per the confirmed terms, exchanging and validating settlement calculations with counterparties, netting payments under the governing master agreements, and submitting authorized payment and receipt instructions — so financial trades complete per their documented terms.</t>
+        </is>
+      </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>Covers financial OTC settlement: observing fixings and floating prices per the confirmed trade terms, calculating and validating settlement amounts, agreeing amounts with counterparties, applying payment netting under the governing master agreements (ISDA or equivalent), preparing and submitting authorized payment and receipt instructions through the designated finance processes, and evidencing completion. Cleared OTC positions settle through the clearing channel (CM-1-2-4-1-3, CM-1-2-4-1-16). Collateral and credit-support administration is owned by Manage Collateral (CM-1-2-2-1-3); close-out netting on default is executed under the master agreement with Legal and Credit Risk. Excludes trade capture (CM-1-2-1-3-7); confirmation (CM-1-2-2-2); settlement disputes (CM-1-2-4-1-17).</t>
+        </is>
+      </c>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>Determine settlement amounts from fixings per confirmed terms | agree and validate amounts with counterparties | apply payment netting under master agreements | prepare and submit authorized payment or receipt instructions through the designated finance processes and track status</t>
+        </is>
+      </c>
+      <c r="Q156" t="inlineStr">
+        <is>
+          <t>Cleared settlement (CM-1-2-4-1-3, CM-1-2-4-1-16) | collateral administration (CM-1-2-2-1-3) | close-out netting on default (master agreement, Legal/Credit Risk) | capture and confirmation (CM-1-2-1-3-7, CM-1-2-2-2) | settlement disputes (CM-1-2-4-1-17)</t>
+        </is>
+      </c>
+      <c r="T156" t="inlineStr">
+        <is>
+          <t>Batch 14 (2026-09-20). Payment netting (routine settlement of offsetting amounts, applied only where legally enforceable and operationally configured) is distinguished from close-out netting (default remedy) per ISDA master agreement structure. APQC 17058 is an unrelated finance candidate.</t>
+        </is>
+      </c>
+      <c r="U156" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V156" s="5" t="inlineStr">
+        <is>
+          <t>Complete financial OTC trades exactly per documented terms and netting provisions.</t>
+        </is>
+      </c>
+      <c r="W156" s="5" t="inlineStr">
+        <is>
+          <t>SRC-ISDA-MA-001 | SRC-CFTC-GLOSS-001</t>
+        </is>
+      </c>
       <c r="X156" s="5" t="n"/>
-      <c r="Y156" s="5" t="n"/>
-      <c r="Z156" s="5" t="n"/>
-      <c r="AA156" s="5" t="n"/>
-      <c r="AB156" s="5" t="n"/>
-      <c r="AC156" s="5" t="n"/>
+      <c r="Y156" s="5" t="inlineStr">
+        <is>
+          <t>Confirmed financial trades (CM-1-2-2-2) | price fixings and observations | master agreement netting terms</t>
+        </is>
+      </c>
+      <c r="Z156" s="5" t="inlineStr">
+        <is>
+          <t>Settled financial OTC payments, netted per agreements</t>
+        </is>
+      </c>
+      <c r="AA156" s="5" t="inlineStr">
+        <is>
+          <t>follows: Capture Financial (OTC) Trades | informed-by: Confirmations Management | precedes: Manage AR/AP &amp; Actuals</t>
+        </is>
+      </c>
+      <c r="AB156" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC156" s="5" t="inlineStr">
+        <is>
+          <t>event-driven</t>
+        </is>
+      </c>
       <c r="AD156" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -21430,18 +22124,75 @@
           <t>no meaningful APQC candidate</t>
         </is>
       </c>
-      <c r="U157" s="5" t="n"/>
-      <c r="V157" s="5" t="n"/>
-      <c r="W157" s="5" t="n"/>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>Settle pipeline transportation charges with carriers — validating pipeline invoices for tariff transportation, fuel, loss allowance, and related charges against actualized pipeline movements and verified tariff determinants, resolving variances, and submitting authorized payment instructions — so pipeline services complete financially on verified movement actuals.</t>
+        </is>
+      </c>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>Covers logistics-service settlement for pipeline movements: validating carrier invoices for transportation, fuel and power, loss allowance, quality bank, and related tariff charges against actualized pipeline movements and the tariff and charge determinants recorded at actualization (CM-1-2-3-1-1), resolving rate and volume variances with carriers, and preparing and submitting authorized payment instructions through the designated finance processes. The governing tariff and transportation agreements determine the applicable charges. The commodity value of the moved product settles under the commodity processes; bundled delivered-price contracts follow the L4 allocation rule. Excludes pipeline actualization (CM-1-2-3-1-1); capacity contracting and nominations (transportation processes); settlement disputes (CM-1-2-4-1-17).</t>
+        </is>
+      </c>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>Validate pipeline tariff invoices against actualized movements and determinants | resolve rate and volume variances with carriers | prepare and submit authorized payment or receipt instructions through the designated finance processes and track status</t>
+        </is>
+      </c>
+      <c r="Q157" t="inlineStr">
+        <is>
+          <t>Commodity-value settlement (commodity processes) | pipeline actualization (CM-1-2-3-1-1) | capacity contracting and nominations (transportation processes) | settlement disputes (CM-1-2-4-1-17)</t>
+        </is>
+      </c>
+      <c r="T157" t="inlineStr">
+        <is>
+          <t>Batch 14 (2026-09-20). Q2 logistics-service reading applied; tariff mechanisms (PLA, quality bank, proration) are recorded at actualization and validated here per the batch 13 charge-determinant rule; the governing tariff takes precedence for the specific transaction. APQC: no meaningful candidate.</t>
+        </is>
+      </c>
+      <c r="U157" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V157" s="5" t="inlineStr">
+        <is>
+          <t>Pay pipeline carriers correctly for verified transportation services under tariff terms.</t>
+        </is>
+      </c>
+      <c r="W157" s="5" t="inlineStr">
+        <is>
+          <t>SRC-DOE-RPPL-001</t>
+        </is>
+      </c>
       <c r="X157" s="5" t="n"/>
-      <c r="Y157" s="5" t="n"/>
-      <c r="Z157" s="5" t="n"/>
-      <c r="AA157" s="5" t="n"/>
-      <c r="AB157" s="5" t="n"/>
-      <c r="AC157" s="5" t="n"/>
+      <c r="Y157" s="5" t="inlineStr">
+        <is>
+          <t>Actualized pipeline movements and tariff determinants (CM-1-2-3-1-1) | carrier invoices | tariff rate references</t>
+        </is>
+      </c>
+      <c r="Z157" s="5" t="inlineStr">
+        <is>
+          <t>Settled pipeline transportation charges</t>
+        </is>
+      </c>
+      <c r="AA157" s="5" t="inlineStr">
+        <is>
+          <t>follows: Perform Pipeline Actualization | precedes: Manage AR/AP &amp; Actuals</t>
+        </is>
+      </c>
+      <c r="AB157" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC157" s="5" t="inlineStr">
+        <is>
+          <t>event-driven</t>
+        </is>
+      </c>
       <c r="AD157" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -21504,18 +22255,75 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U158" s="5" t="n"/>
-      <c r="V158" s="5" t="n"/>
-      <c r="W158" s="5" t="n"/>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>Settle rail transportation charges with railroads and rail service providers — validating freight and accessorial invoices against actualized rail movements and verified charge determinants, applying contracted and tariff rates, resolving variances, and submitting authorized payment instructions — so rail services complete financially on verified movement actuals.</t>
+        </is>
+      </c>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>Covers logistics-service settlement for rail movements: validating railroad freight invoices and accessorial charges (car-hire and detention charges included where the rail agreement governs them) against actualized rail movements and determinants (CM-1-2-3-1-3), applying contracted and tariff rates, resolving variances, and preparing and submitting authorized payment instructions through the designated finance processes. Railcar lease and fleet costs follow their governing agreements through the owning fleet processes. The commodity value settles under the commodity processes; bundled delivered-price contracts follow the L4 allocation rule. Excludes rail actualization (CM-1-2-3-1-3); rail contracting and fleet management (logistics processes); marine/terminal demurrage claims (CM-1-2-4-4); settlement disputes (CM-1-2-4-1-17).</t>
+        </is>
+      </c>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>Validate rail freight and accessorial invoices against actualized movements | apply contracted and tariff rates | resolve variances with rail providers | prepare and submit authorized payment or receipt instructions through the designated finance processes and track status</t>
+        </is>
+      </c>
+      <c r="Q158" t="inlineStr">
+        <is>
+          <t>Commodity-value settlement (commodity processes) | rail actualization (CM-1-2-3-1-3) | rail contracting and fleet management (logistics processes) | settlement disputes (CM-1-2-4-1-17)</t>
+        </is>
+      </c>
+      <c r="T158" t="inlineStr">
+        <is>
+          <t>Batch 14 (2026-09-20). Q2 logistics-service reading applied. Rail car-hire/detention charges settle here when the rail agreement governs them; marine and terminal demurrage remains with CM-1-2-4-4 per the batch 10 partition. APQC 12931 'Schedule rail' is a scheduling candidate, not settlement.</t>
+        </is>
+      </c>
+      <c r="U158" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V158" s="5" t="inlineStr">
+        <is>
+          <t>Pay rail providers correctly for verified rail services.</t>
+        </is>
+      </c>
+      <c r="W158" s="5" t="inlineStr">
+        <is>
+          <t>SRC-EIA-GLOSS-001</t>
+        </is>
+      </c>
       <c r="X158" s="5" t="n"/>
-      <c r="Y158" s="5" t="n"/>
-      <c r="Z158" s="5" t="n"/>
-      <c r="AA158" s="5" t="n"/>
-      <c r="AB158" s="5" t="n"/>
-      <c r="AC158" s="5" t="n"/>
+      <c r="Y158" s="5" t="inlineStr">
+        <is>
+          <t>Actualized rail movements and determinants (CM-1-2-3-1-3) | railroad invoices | contracted and tariff rates</t>
+        </is>
+      </c>
+      <c r="Z158" s="5" t="inlineStr">
+        <is>
+          <t>Settled rail transportation charges</t>
+        </is>
+      </c>
+      <c r="AA158" s="5" t="inlineStr">
+        <is>
+          <t>follows: Perform Railcar Actualization | precedes: Manage AR/AP &amp; Actuals</t>
+        </is>
+      </c>
+      <c r="AB158" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC158" s="5" t="inlineStr">
+        <is>
+          <t>event-driven</t>
+        </is>
+      </c>
       <c r="AD158" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -21583,18 +22391,75 @@
           <t>no meaningful APQC candidate</t>
         </is>
       </c>
-      <c r="U159" s="5" t="n"/>
-      <c r="V159" s="5" t="n"/>
-      <c r="W159" s="5" t="n"/>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>Settle terminal and storage service charges — validating operator invoices for throughput, storage, blending, handling, and ancillary services against actualized terminal transactions and verified charge determinants and contractual bases, resolving variances, and submitting authorized payment instructions — so terminal and storage services complete financially on verified actuals.</t>
+        </is>
+      </c>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>Covers logistics-service settlement for terminal and storage arrangements: validating terminal and storage operator invoices against actualized transaction-level actuals and the charge determinants and contractual bases recorded at actualization (CM-1-2-3-1-5), applying agreement rates including minimum-throughput and capacity-reservation provisions, resolving variances, and preparing and submitting authorized payment instructions through the designated finance processes. Storage-deal commodity economics settle under the commodity and channel processes; the deal terms come from Capture Storage Deals (CM-1-2-1-3-5); bundled arrangements follow the L4 allocation rule. Excludes terminal actualization (CM-1-2-3-1-5); terminal contracting (commercial/logistics processes); network stock reconciliation (CM-1-1-3-7-5); settlement disputes (CM-1-2-4-1-17).</t>
+        </is>
+      </c>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>Validate terminal and storage invoices against actualized transactions and determinants | apply agreement rates including minimum-throughput and capacity provisions | resolve variances with operators | prepare and submit authorized payment or receipt instructions through the designated finance processes and track status</t>
+        </is>
+      </c>
+      <c r="Q159" t="inlineStr">
+        <is>
+          <t>Storage-deal commodity economics (commodity/channel processes) | terminal actualization (CM-1-2-3-1-5) | terminal contracting (commercial/logistics processes) | settlement disputes (CM-1-2-4-1-17)</t>
+        </is>
+      </c>
+      <c r="T159" t="inlineStr">
+        <is>
+          <t>Batch 14 (2026-09-20). Q2 logistics-service reading applied. Minimum-throughput and capacity-reservation charges settle per the agreement even when unused; determinants come from actualization per batch 13. APQC 19558 is a storage-constraints candidate, not settlement.</t>
+        </is>
+      </c>
+      <c r="U159" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V159" s="5" t="inlineStr">
+        <is>
+          <t>Pay terminal and storage operators correctly for verified services under agreement terms.</t>
+        </is>
+      </c>
+      <c r="W159" s="5" t="inlineStr">
+        <is>
+          <t>SRC-EI-HM32-001</t>
+        </is>
+      </c>
       <c r="X159" s="5" t="n"/>
-      <c r="Y159" s="5" t="n"/>
-      <c r="Z159" s="5" t="n"/>
-      <c r="AA159" s="5" t="n"/>
-      <c r="AB159" s="5" t="n"/>
-      <c r="AC159" s="5" t="n"/>
+      <c r="Y159" s="5" t="inlineStr">
+        <is>
+          <t>Actualized terminal transactions and determinants (CM-1-2-3-1-5) | operator invoices | terminal and storage agreement rates</t>
+        </is>
+      </c>
+      <c r="Z159" s="5" t="inlineStr">
+        <is>
+          <t>Settled terminal and storage charges</t>
+        </is>
+      </c>
+      <c r="AA159" s="5" t="inlineStr">
+        <is>
+          <t>follows: Perform Terminal/Storage Actualization | precedes: Manage AR/AP &amp; Actuals</t>
+        </is>
+      </c>
+      <c r="AB159" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC159" s="5" t="inlineStr">
+        <is>
+          <t>event-driven</t>
+        </is>
+      </c>
       <c r="AD159" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -21662,18 +22527,75 @@
           <t>no meaningful APQC candidate</t>
         </is>
       </c>
-      <c r="U160" s="5" t="n"/>
-      <c r="V160" s="5" t="n"/>
-      <c r="W160" s="5" t="n"/>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>Settle bilateral power transactions outside ISO markets — applying contract and index pricing to scheduled and delivered quantities, validating counterparty invoices and settlement data, netting where agreements provide, and submitting authorized payment and receipt instructions — so bilateral power transactions complete financially on verified quantities.</t>
+        </is>
+      </c>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>Covers bilateral (non-ISO-cleared) power settlement: applying contract and index pricing to confirmed scheduled and delivered quantities, validating counterparty invoices, netting, and preparing and submitting authorized payment and receipt instructions through the designated finance processes. Delivered quantities may be derived from meter data, scheduling coordinator records, bilateral schedules, ISO/RTO data, or other contractually agreed sources (batch 14 Q5 note). ISO/RTO-cleared activity settles under Settle ISO/Power Pools (CM-1-2-4-1-7); a bilateral transaction scheduled through an ISO may have both a bilateral settlement here and ISO charges there. Excludes power trading and capture (CM-1-2-1-3); transmission deal capture (CM-1-2-1-3-11); settlement disputes (CM-1-2-4-1-17).</t>
+        </is>
+      </c>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>Apply contract and index pricing to scheduled and delivered power quantities | validate counterparty invoices | net where agreements provide | prepare and submit authorized payment or receipt instructions through the designated finance processes and track status</t>
+        </is>
+      </c>
+      <c r="Q160" t="inlineStr">
+        <is>
+          <t>ISO-cleared settlement (CM-1-2-4-1-7) | power deal capture (CM-1-2-1-3) | transmission capture (CM-1-2-1-3-11) | settlement disputes (CM-1-2-4-1-17)</t>
+        </is>
+      </c>
+      <c r="T160" t="inlineStr">
+        <is>
+          <t>Batch 14 (2026-09-20). Boundary to -7: bilateral contract settlement here; ISO statement settlement there; one transaction may touch both. Delivered-quantity sources are contractually agreed and market-design-specific (meter data, scheduling coordinator records, bilateral schedules, ISO/RTO data, or other agreed sources). APQC: no meaningful candidate.</t>
+        </is>
+      </c>
+      <c r="U160" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V160" s="5" t="inlineStr">
+        <is>
+          <t>Complete bilateral power transactions financially on verified scheduled and delivered quantities.</t>
+        </is>
+      </c>
+      <c r="W160" s="5" t="inlineStr">
+        <is>
+          <t>SRC-FERC-RTO-001 | SRC-EIA-GLOSS-001</t>
+        </is>
+      </c>
       <c r="X160" s="5" t="n"/>
-      <c r="Y160" s="5" t="n"/>
-      <c r="Z160" s="5" t="n"/>
-      <c r="AA160" s="5" t="n"/>
-      <c r="AB160" s="5" t="n"/>
-      <c r="AC160" s="5" t="n"/>
+      <c r="Y160" s="5" t="inlineStr">
+        <is>
+          <t>Confirmed schedules and metering data | contract and index prices | counterparty invoices</t>
+        </is>
+      </c>
+      <c r="Z160" s="5" t="inlineStr">
+        <is>
+          <t>Settled bilateral power transactions</t>
+        </is>
+      </c>
+      <c r="AA160" s="5" t="inlineStr">
+        <is>
+          <t>follows: Capture Physical Trades | precedes: Manage AR/AP &amp; Actuals</t>
+        </is>
+      </c>
+      <c r="AB160" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC160" s="5" t="inlineStr">
+        <is>
+          <t>event-driven</t>
+        </is>
+      </c>
       <c r="AD160" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -21741,18 +22663,75 @@
           <t>no meaningful APQC candidate</t>
         </is>
       </c>
-      <c r="U161" s="5" t="n"/>
-      <c r="V161" s="5" t="n"/>
-      <c r="W161" s="5" t="n"/>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>Settle broker and clearing-member account activity — reconciling broker statements against internal trade, position, and margin records, validating commissions, fees, and charges, preparing, submitting, tracking, and reconciling authorized broker-facing payment or collateral-transfer instructions, including margin transfers, through the designated Treasury, banking, or payment-operations process, and resolving statement discrepancies — so broker accounts remain accurate, funded, and evidenced.</t>
+        </is>
+      </c>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>Covers the broker-facing account relationship for executing and clearing brokers: daily reconciliation of broker statements against internal trades, positions, and cash and margin balances; validation of commissions, exchange and clearing fees, and other charges against agreed schedules; preparation, submission, tracking, and reconciliation of authorized broker-facing payment and collateral-transfer instructions, including margin transfers, through the designated Treasury, banking, or payment-operations process, per the batch 11 binding and the batch 14 Q3 payment-authority rule; and resolution of statement discrepancies with brokers. Margin requirement validation and calls are owned by Perform Margining (CM-1-2-2-1-5); trade-level exchange settlement values by Settle Exchange Trades (CM-1-2-4-1-3). Excludes broker relationship management and selection (commercial processes); margining (CM-1-2-2-1-5); bank payment release and execution (Treasury/banking processes); settlement disputes escalated beyond broker statement resolution (CM-1-2-4-1-17).</t>
+        </is>
+      </c>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>Reconcile broker statements against internal trade, position, and margin records | validate commissions, fees, and charges | prepare, submit, track, and reconcile authorized broker-facing payment and margin-transfer instructions through the designated process | resolve statement discrepancies</t>
+        </is>
+      </c>
+      <c r="Q161" t="inlineStr">
+        <is>
+          <t>Margin requirement validation and calls (CM-1-2-2-1-5) | trade-level exchange settlement (CM-1-2-4-1-3) | bank payment release and execution (Treasury/banking processes) | broker selection and relationship management (commercial processes) | settlement disputes (CM-1-2-4-1-17)</t>
+        </is>
+      </c>
+      <c r="T161" t="inlineStr">
+        <is>
+          <t>Batch 14 (2026-09-20). Q4 decision (Hamid) applied: broker-facing account relationship here; trade-level cleared settlement at -3; margin requirement control at CM-1-2-2-1-5. The batch 11 binding is preserved as the operational broker-account side of margin cash movements — this process prepares, submits, tracks, and reconciles the authorized instructions; the designated Treasury, banking, or payment-operations process executes the bank movement. Whether this process submits payment instructions or only requests them is operating-model-specific (open question carried in the batch 14 PR). APQC: no meaningful candidate.</t>
+        </is>
+      </c>
+      <c r="U161" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V161" s="5" t="inlineStr">
+        <is>
+          <t>Keep broker accounts reconciled, correctly charged, and funded through authorized, tracked instructions with an evidenced trail.</t>
+        </is>
+      </c>
+      <c r="W161" s="5" t="inlineStr">
+        <is>
+          <t>SRC-CFTC-GLOSS-001</t>
+        </is>
+      </c>
       <c r="X161" s="5" t="n"/>
-      <c r="Y161" s="5" t="n"/>
-      <c r="Z161" s="5" t="n"/>
-      <c r="AA161" s="5" t="n"/>
-      <c r="AB161" s="5" t="n"/>
-      <c r="AC161" s="5" t="n"/>
+      <c r="Y161" s="5" t="inlineStr">
+        <is>
+          <t>Broker and clearing statements | internal trade, position, and margin records | commission and fee schedules | margin calls validated by CM-1-2-2-1-5</t>
+        </is>
+      </c>
+      <c r="Z161" s="5" t="inlineStr">
+        <is>
+          <t>Reconciled broker accounts with authorized broker-payment and margin-transfer instructions, status, and evidence</t>
+        </is>
+      </c>
+      <c r="AA161" s="5" t="inlineStr">
+        <is>
+          <t>follows: Settle Exchange Trades | informed-by: Perform Margining | precedes: Manage AR/AP &amp; Actuals</t>
+        </is>
+      </c>
+      <c r="AB161" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC161" s="5" t="inlineStr">
+        <is>
+          <t>event-driven</t>
+        </is>
+      </c>
       <c r="AD161" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -21820,18 +22799,75 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U162" s="5" t="n"/>
-      <c r="V162" s="5" t="n"/>
-      <c r="W162" s="5" t="n"/>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>Manage disputes over what is owed, invoiced, received, paid, netted, or applied — logging and classifying settlement discrepancies, investigating against actualized records, contractual terms, and settlement calculations, coordinating resolution with counterparties, carriers, brokers, and operators under the governing agreements, escalating aging or material disputes, and closing them through corrected settlements and evidenced adjustments.</t>
+        </is>
+      </c>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>Covers the settlement dispute lifecycle across all settlement processes: discrepancy logging and classification; investigation against actualized quantities and determinants, contractual prices and rates, and settlement calculations; coordination of resolution with the relevant external parties under the governing agreements; escalation of aging or material disputes; and closure through corrected settlements, credit notes, or evidenced adjustments. Under the batch 10 dispute partition, this process answers 'what is owed, invoiced, received, paid, netted, or applied'. Where a dispute concerns an invoice calculation but not the underlying actual or agreed terms, it remains a settlement dispute; a dispute whose root cause is a physical or measurement disagreement is redirected to Manage Actualization Disputes (CM-1-2-3-1-8). Excludes confirmation disputes (CM-1-2-2-2-5); actualization disputes (CM-1-2-3-1-8); demurrage claims (CM-1-2-4-4); ISO statement disputes within ISO processes (CM-1-2-4-1-7); financial write-offs (Finance, locked rule); legal proceedings (Legal &amp; Corporate Communications).</t>
+        </is>
+      </c>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>Log and classify settlement discrepancies | investigate against actuals, terms, and calculations | coordinate resolution under governing agreements | escalate and close through corrected settlements and evidenced adjustments</t>
+        </is>
+      </c>
+      <c r="Q162" t="inlineStr">
+        <is>
+          <t>Confirmation disputes (CM-1-2-2-2-5) | actualization disputes (CM-1-2-3-1-8) | demurrage claims (CM-1-2-4-4) | ISO statement disputes (CM-1-2-4-1-7) | write-offs (Finance, locked rule) | legal proceedings (Legal &amp; Corporate Communications)</t>
+        </is>
+      </c>
+      <c r="T162" t="inlineStr">
+        <is>
+          <t>Batch 14 (2026-09-20). Dispute partition rule (Hamid, batch 10) applied verbatim: confirmation disputes answer 'what did the parties agree the terms were'; actualization disputes answer 'what was physically delivered, received, measured, or performed'; settlement disputes answer 'what is owed, invoiced, received, paid, netted, or applied' (here); demurrage claims answer 'was delay or capacity usage compensable'; legal proceedings belong to Legal &amp; Corporate Communications. Invoice-calculation rule (Hamid, batch 14): a dispute about the invoice calculation, not the underlying actual or agreed terms, remains a settlement dispute. The requested 'may-be-informed-by' relations have no controlled relationship_type; per the batch 10/13 conditional-relation precedent, informed-by is used with the conditional rule recorded verbatim: a settlement dispute may be caused by an unresolved actualization dispute or a confirmation mismatch, may be purely financial (rate, tax, invoice, netting, fee, timing, or duplicate-charge issues), and may continue after the underlying physical or confirmation question is settled — no strict lifecycle sequencing is implied. APQC 11743 is an unrelated routing candidate.</t>
+        </is>
+      </c>
+      <c r="U162" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V162" s="5" t="inlineStr">
+        <is>
+          <t>Resolve financial-settlement disagreements so transactions close on correct, evidenced amounts.</t>
+        </is>
+      </c>
+      <c r="W162" s="5" t="inlineStr">
+        <is>
+          <t>SRC-CFTC-GLOSS-001</t>
+        </is>
+      </c>
       <c r="X162" s="5" t="n"/>
-      <c r="Y162" s="5" t="n"/>
-      <c r="Z162" s="5" t="n"/>
-      <c r="AA162" s="5" t="n"/>
-      <c r="AB162" s="5" t="n"/>
-      <c r="AC162" s="5" t="n"/>
+      <c r="Y162" s="5" t="inlineStr">
+        <is>
+          <t>Settlement discrepancies from the settlement processes | actualized records and determinants | contractual terms and calculations | counterparty communications</t>
+        </is>
+      </c>
+      <c r="Z162" s="5" t="inlineStr">
+        <is>
+          <t>Closed settlement disputes with corrected, evidenced settlements</t>
+        </is>
+      </c>
+      <c r="AA162" s="5" t="inlineStr">
+        <is>
+          <t>follows: Settlements | informed-by: Manage Actualization Disputes | informed-by: Manage Confirm Disputes</t>
+        </is>
+      </c>
+      <c r="AB162" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC162" s="5" t="inlineStr">
+        <is>
+          <t>event-driven</t>
+        </is>
+      </c>
       <c r="AD162" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -21899,18 +22935,75 @@
           <t>no meaningful APQC candidate</t>
         </is>
       </c>
-      <c r="U163" s="5" t="n"/>
-      <c r="V163" s="5" t="n"/>
-      <c r="W163" s="5" t="n"/>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>Settle purchases and sales of refinery intermediates and blend components — applying contractual and index-based pricing to actualized volumes and qualities, generating and validating invoices, netting where agreements provide, and submitting authorized payment and receipt instructions — so intermediate transactions complete financially on verified actuals.</t>
+        </is>
+      </c>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>Covers commodity-value settlement for intermediates and blend components (for example vacuum gasoil, naphtha, reformate, alkylate, blendstocks): applying contract and index pricing with quality adjustments to actualized volumes, generating and validating invoices, netting, and preparing and submitting authorized payment and receipt instructions through the designated finance processes. The product-versus-intermediate boundary follows the commodity classification, product master, and commercial classification captured with the deal — not the physical location or whether a stream is used inside a refinery; finished refined products settle under Settle Products (CM-1-2-4-1-2). Transportation and terminal charges settle under the mode processes. Excludes actualization (CM-1-2-3-1); settlement disputes (CM-1-2-4-1-17).</t>
+        </is>
+      </c>
+      <c r="P163" t="inlineStr">
+        <is>
+          <t>Apply contractual and index pricing with quality adjustments to actualized intermediate volumes | generate and validate invoices | net where agreements provide | prepare and submit authorized payment or receipt instructions through the designated finance processes and track status</t>
+        </is>
+      </c>
+      <c r="Q163" t="inlineStr">
+        <is>
+          <t>Finished-product settlement (CM-1-2-4-1-2) | transportation and terminal charges (mode processes) | actualization (CM-1-2-3-1) | settlement disputes (CM-1-2-4-1-17)</t>
+        </is>
+      </c>
+      <c r="T163" t="inlineStr">
+        <is>
+          <t>Batch 14 (2026-09-20). Product-versus-intermediate partition rule (Hamid, batch 14): follows the commodity classification, product master, and commercial classification captured with the deal — not simply the physical location or refinery use; matters for blendstocks, refinery intermediates, bio-components, and imported feedstocks. Consistent with the batch 04 finished-products-plus-intermediates material scope. APQC: no meaningful candidate.</t>
+        </is>
+      </c>
+      <c r="U163" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V163" s="5" t="inlineStr">
+        <is>
+          <t>Complete intermediate and blend-component transactions financially on verified actuals.</t>
+        </is>
+      </c>
+      <c r="W163" s="5" t="inlineStr">
+        <is>
+          <t>SRC-EIA-GLOSS-001</t>
+        </is>
+      </c>
       <c r="X163" s="5" t="n"/>
-      <c r="Y163" s="5" t="n"/>
-      <c r="Z163" s="5" t="n"/>
-      <c r="AA163" s="5" t="n"/>
-      <c r="AB163" s="5" t="n"/>
-      <c r="AC163" s="5" t="n"/>
+      <c r="Y163" s="5" t="inlineStr">
+        <is>
+          <t>Actualized intermediate movements | contract and index pricing | counterparty invoices</t>
+        </is>
+      </c>
+      <c r="Z163" s="5" t="inlineStr">
+        <is>
+          <t>Settled intermediate transactions</t>
+        </is>
+      </c>
+      <c r="AA163" s="5" t="inlineStr">
+        <is>
+          <t>follows: Actualizations | precedes: Manage AR/AP &amp; Actuals</t>
+        </is>
+      </c>
+      <c r="AB163" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC163" s="5" t="inlineStr">
+        <is>
+          <t>event-driven</t>
+        </is>
+      </c>
       <c r="AD163" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -21978,18 +23071,75 @@
           <t>no meaningful APQC candidate</t>
         </is>
       </c>
-      <c r="U164" s="5" t="n"/>
-      <c r="V164" s="5" t="n"/>
-      <c r="W164" s="5" t="n"/>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>Settle purchases and sales of other commodities traded by the organization — such as NGLs, petrochemicals, sulfur, petroleum coke, and other by-products or ancillary commodities — applying contractual pricing to actualized quantities, generating and validating invoices, and submitting authorized payment and receipt instructions on the same settlement discipline as the named commodity processes.</t>
+        </is>
+      </c>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>This is a controlled residual category, not a default dumping ground: a commodity belongs here only if no named sibling owns its commercial settlement and its settlement mechanics do not require a distinct regulated, market-channel, or logistics-service process. Covers commodity-value settlement for such commodities: applying contract and index pricing to actualized quantities, generating and validating invoices, netting where agreements provide, and preparing and submitting authorized payment and receipt instructions through the designated finance processes. If trading volume or control needs justify it, a dedicated row should be proposed through taxonomy governance rather than broadening this row. Transportation and terminal charges settle under the mode processes. Excludes crude (CM-1-2-4-1-1), products (CM-1-2-4-1-2), intermediates (CM-1-2-4-1-18), gas (CM-1-2-4-1-10), power (CM-1-2-4-1-7/-15), environmental instruments (CM-1-2-4-1-8); actualization (CM-1-2-3-1); settlement disputes (CM-1-2-4-1-17).</t>
+        </is>
+      </c>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t>Apply contractual pricing to actualized quantities of unlisted commodities | generate and validate invoices | net where agreements provide | prepare and submit authorized payment or receipt instructions through the designated finance processes and track status</t>
+        </is>
+      </c>
+      <c r="Q164" t="inlineStr">
+        <is>
+          <t>Commodities with named settlement rows (CM-1-2-4-1-1/-2/-7/-8/-10/-15/-18) | actualization (CM-1-2-3-1) | settlement disputes (CM-1-2-4-1-17)</t>
+        </is>
+      </c>
+      <c r="T164" t="inlineStr">
+        <is>
+          <t>Batch 14 (2026-09-20). Controlled residual category (Hamid, batch 14): membership requires that no named sibling owns the commodity's commercial settlement and that its mechanics need no distinct regulated, market-channel, or logistics-service process; growth routes through taxonomy governance, not scope creep. APQC: no meaningful candidate.</t>
+        </is>
+      </c>
+      <c r="U164" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V164" s="5" t="inlineStr">
+        <is>
+          <t>Give every traded commodity a settlement owner without diluting the named processes.</t>
+        </is>
+      </c>
+      <c r="W164" s="5" t="inlineStr">
+        <is>
+          <t>SRC-EIA-GLOSS-001</t>
+        </is>
+      </c>
       <c r="X164" s="5" t="n"/>
-      <c r="Y164" s="5" t="n"/>
-      <c r="Z164" s="5" t="n"/>
-      <c r="AA164" s="5" t="n"/>
-      <c r="AB164" s="5" t="n"/>
-      <c r="AC164" s="5" t="n"/>
+      <c r="Y164" s="5" t="inlineStr">
+        <is>
+          <t>Actualized movements of unlisted commodities | contract pricing | counterparty invoices</t>
+        </is>
+      </c>
+      <c r="Z164" s="5" t="inlineStr">
+        <is>
+          <t>Settled other-commodity transactions</t>
+        </is>
+      </c>
+      <c r="AA164" s="5" t="inlineStr">
+        <is>
+          <t>follows: Actualizations | precedes: Manage AR/AP &amp; Actuals</t>
+        </is>
+      </c>
+      <c r="AB164" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC164" s="5" t="inlineStr">
+        <is>
+          <t>event-driven</t>
+        </is>
+      </c>
       <c r="AD164" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -49460,7 +50610,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -50962,6 +52112,100 @@
         </is>
       </c>
       <c r="I37" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>SRC-FERC-RTO-001</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Federal Energy Regulatory Commission</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>RTOs and ISOs (regional transmission organizations and independent system operators; two-settlement market design context)</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Accessed 2026-09-19</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>https://www.ferc.gov/power-sales-and-markets/rtos-and-isos</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Regulatory</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>US RTO/ISO market-structure and market-settlement context, including day-ahead and real-time market design where applicable. Does not define a specific ISO/RTO's settlement calendar, billing determinants, charge types, resettlement/versioning, dispute procedures, or internal process ownership. Evidence only, not text to copy.</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>ISO/RTO two-settlement market design context for CM-1-2-4-1-7 and CM-1-2-4-1-15</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>SRC-NAESB-WGQ-001</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>North American Energy Standards Board</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Wholesale Gas Quadrant Business Practice Standards (nominations, flowing gas, invoicing)</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Version 4.0, 2023-09-29; accessed 2026-09-19 (version evidenced by NAESB public report naesb.org/pdf4/naesb_092923_wgq_version_40_report.pdf; standards text is member/purchase access - claims based on public materials)</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>https://www.naesb.org/wgq/imp.asp</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Industry standards body</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>US wholesale natural-gas nomination, allocation, flowing-gas, and invoicing practice context. Pipeline tariffs, interconnection agreements, imbalance rules, and bilateral contracts govern the specific transaction and take precedence. Does not establish enterprise settlement ownership or apply outside the relevant jurisdiction. Evidence only, not text to copy.</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>US wholesale gas business-practice context for CM-1-2-4-1-10</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
         <is>
           <t>active</t>
         </is>

--- a/business_architecture/ontology/build/output/step3c-definition-authoring-workbook.xlsx
+++ b/business_architecture/ontology/build/output/step3c-definition-authoring-workbook.xlsx
@@ -23207,18 +23207,80 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U165" s="5" t="n"/>
-      <c r="V165" s="5" t="n"/>
-      <c r="W165" s="5" t="n"/>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>The capability to record, value, reconcile, and report the financial effects of supply and trading activity by maintaining controlled sub-ledger and general-ledger records; booking authorized settlement outcomes, receivables, payables, actuals, accruals, taxes, and interest obligations; reconciling economic P&amp;L to accounting P&amp;L; and producing controlled financial evidence and reporting within the enterprise accounting-policy framework.</t>
+        </is>
+      </c>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>Covers the trading and supply accounting capability: transaction-level treatment assessment, sub-ledger and GL recording, AR/AP and actuals booking from authorized settlement outcomes (batch 14 Q3 chain), cash application, accruals, financial production and inventory accounting, royalty and interest disbursement execution, economic-to-accounting P&amp;L reconciliation using the controlled economic inputs delivered by Market Risk at end of month (batch 12), transaction and commodity tax execution, financial documentation and reporting, financial system and ledger-structure administration, and trading-specific accounting procedures. This capability supports Supply &amp; Trading and may be operated by Product Control, Trading Accounting, Finance Operations, Accounting, Shared Services, or another designated accounting function; the taxonomy placement does not prescribe the accountable legal, finance, or organizational owner. Operates within the enterprise accounting policy framework: financial write-off approval, valuation policy, material technical-accounting conclusions, and enterprise accounting policy are owned by Finance under the locked Finance rule; payment release and bank execution by Treasury and banking processes; settlement calculation and invoice validation by Settlements (CM-1-2-4-1); the refinery operational material balance by Perform Production Accounting (CM-1-1-7-1-3); network book-to-physical stock reconciliation by Perform Inventory Reconciliation (CM-1-1-3-7-5).</t>
+        </is>
+      </c>
+      <c r="P165" t="inlineStr">
+        <is>
+          <t>Book, value, and reconcile trading activity in sub-ledger and GL | apply cash, accrue, and post actuals from authorized settlement outcomes | reconcile economic P&amp;L to accounting P&amp;L | assess treatments, execute transaction taxes, and produce controlled financial documentation</t>
+        </is>
+      </c>
+      <c r="Q165" t="inlineStr">
+        <is>
+          <t>Enterprise accounting policy, valuation policy, material technical-accounting conclusions, and write-off approval (Finance, locked rule) | payment release and bank execution (Treasury/banking) | settlement calculation and invoicing (CM-1-2-4-1) | refinery material balance (CM-1-1-7-1-3) | network stock reconciliation (CM-1-1-3-7-5) | credit exposure and limits (CM-1-2-2-1)</t>
+        </is>
+      </c>
+      <c r="R165" t="inlineStr">
+        <is>
+          <t>Trading Accounting | Product Control</t>
+        </is>
+      </c>
+      <c r="T165" t="inlineStr">
+        <is>
+          <t>Batch 15 (2026-09-20). Concept-type: capability per the batch 11/12 test — heterogeneous concurrent record-and-control functions, not one per-transaction lifecycle. Organizational neutrality (Hamid, batch 15): responsible domain recorded as Finance-enabled Supply &amp; Trading — a trading-accounting capability serving Supply &amp; Trading, delivered through Product Control, Trading Accounting, Finance Operations, Accounting, Shared Services, or another designated function per the operating model; taxonomy branch placement under Commercial &amp; Marketing does not prescribe the accountable owner. Execute-within-policy pattern: accounting executes within the Finance-owned policy framework, parallel to the batch 11 limits and batch 12 valuation-control precedents. 'P&amp;L' in prose per the batch 12 convention. APQC 10774 is a WEAK financial-accounting candidate, comparative evidence only.</t>
+        </is>
+      </c>
+      <c r="U165" s="5" t="inlineStr">
+        <is>
+          <t>capability</t>
+        </is>
+      </c>
+      <c r="V165" s="5" t="inlineStr">
+        <is>
+          <t>Give supply and trading activity a complete, controlled, and reconciled financial record within enterprise policy.</t>
+        </is>
+      </c>
+      <c r="W165" s="5" t="inlineStr">
+        <is>
+          <t>SRC-FASB-ASC815-001 | SRC-APQC-PCF-001</t>
+        </is>
+      </c>
       <c r="X165" s="5" t="n"/>
-      <c r="Y165" s="5" t="n"/>
-      <c r="Z165" s="5" t="n"/>
-      <c r="AA165" s="5" t="n"/>
-      <c r="AB165" s="5" t="n"/>
-      <c r="AC165" s="5" t="n"/>
+      <c r="Y165" s="5" t="inlineStr">
+        <is>
+          <t>Authorized settlement outcomes (CM-1-2-4-1) | controlled economic P&amp;L inputs at EOM (CM-1-2-2-3-5) | operational production and inventory balances (CM-1-1-7-1-3, CM-1-1-3-7-5) | enterprise accounting policy (Finance)</t>
+        </is>
+      </c>
+      <c r="Z165" s="5" t="inlineStr">
+        <is>
+          <t>Complete, reconciled trading financial records, postings, and controlled financial reporting</t>
+        </is>
+      </c>
+      <c r="AA165" s="5" t="inlineStr">
+        <is>
+          <t>follows: Settlements | uses-input: Perform End-of-Month (EOM) Process | governed-by: Develop Accounting Policies &amp; Procedures</t>
+        </is>
+      </c>
+      <c r="AB165" s="5" t="inlineStr">
+        <is>
+          <t>Finance-enabled Supply &amp; Trading</t>
+        </is>
+      </c>
+      <c r="AC165" s="5" t="inlineStr">
+        <is>
+          <t>continuous</t>
+        </is>
+      </c>
       <c r="AD165" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -23286,18 +23348,75 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U166" s="5" t="n"/>
-      <c r="V166" s="5" t="n"/>
-      <c r="W166" s="5" t="n"/>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>Assess, document, and apply the accounting treatment of trading transactions under approved enterprise policy — derivative versus normal purchase/normal sale scope, own-use, lease, storage, and exchange treatments, and gross-versus-net presentation — obtaining Finance/controller approval or escalation for material, new, complex, or policy-sensitive conclusions, so transactions are recorded under the correct, evidenced treatment.</t>
+        </is>
+      </c>
+      <c r="O166" t="inlineStr">
+        <is>
+          <t>Covers transaction-level treatment assessment and documentation: assessing new deal types, structures, and amendments against the applicable accounting standards and enterprise policy (for US GAAP, ASC 815 derivative scope, the normal purchases and normal sales election, and hedge accounting requirements are the recurring assessments), documenting the treatment conclusion and its evidence, supporting hedge designation documentation, and maintaining the treatment reference used by posting and reconciliation processes. Material, new, complex, or policy-sensitive conclusions require Finance/controller approval or escalation; hedge designation approval follows the approved hedging policy through its accountable owners (Finance, Treasury, or Controller per the operating model), not this process. Treatment assessments apply enterprise accounting policy owned by Finance under the locked rule. Excludes enterprise accounting policy and material technical-accounting conclusions (Finance, locked rule); hedge designation approval (per approved hedging policy); valuation adjustment execution (Manage Commodity Valuations, CM-1-2-2-3-15, batch 12); trading-procedure documentation (CM-1-2-4-2-12); posting execution (the recording processes).</t>
+        </is>
+      </c>
+      <c r="P166" t="inlineStr">
+        <is>
+          <t>Assess deal types and structures against standards and approved policy | document treatment conclusions with evidence | escalate material, new, complex, or policy-sensitive conclusions to Finance | maintain the treatment reference and support hedge designation documentation</t>
+        </is>
+      </c>
+      <c r="Q166" t="inlineStr">
+        <is>
+          <t>Enterprise accounting policy and material technical-accounting conclusions (Finance, locked rule) | hedge designation approval (per approved hedging policy) | valuation adjustments (CM-1-2-2-3-15) | procedure documentation (CM-1-2-4-2-12) | posting execution (recording processes)</t>
+        </is>
+      </c>
+      <c r="T166" t="inlineStr">
+        <is>
+          <t>Batch 15 (2026-09-20). Assess-document-apply with escalation (Hamid, batch 15): treatment work is performed under approved policy with Finance/controller approval for material conclusions — delegated technical-accounting authority is operating-model-specific and not assumed. Batch 12 exclusion on CM-1-2-2-3-15 honored: valuation execution does not approve accounting classification; classification assessment lands here, policy and material conclusions with Finance. ASC 815 supports the accounting concepts, not the organization's approval design. Standards are jurisdiction-specific: ASC 815 under US GAAP; IFRS 9 and related standards elsewhere. APQC 10731 is a fixed-asset candidate, unrelated.</t>
+        </is>
+      </c>
+      <c r="U166" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V166" s="5" t="inlineStr">
+        <is>
+          <t>Ensure every transaction is recorded under a correct, documented, policy-compliant treatment with material conclusions properly approved.</t>
+        </is>
+      </c>
+      <c r="W166" s="5" t="inlineStr">
+        <is>
+          <t>SRC-FASB-ASC815-001</t>
+        </is>
+      </c>
       <c r="X166" s="5" t="n"/>
-      <c r="Y166" s="5" t="n"/>
-      <c r="Z166" s="5" t="n"/>
-      <c r="AA166" s="5" t="n"/>
-      <c r="AB166" s="5" t="n"/>
-      <c r="AC166" s="5" t="n"/>
+      <c r="Y166" s="5" t="inlineStr">
+        <is>
+          <t>New and amended deal types and structures (CM-1-2-1-3) | enterprise accounting policy (Finance) | accounting standards references</t>
+        </is>
+      </c>
+      <c r="Z166" s="5" t="inlineStr">
+        <is>
+          <t>Documented treatment assessments and the treatment reference, with material conclusions Finance-approved</t>
+        </is>
+      </c>
+      <c r="AA166" s="5" t="inlineStr">
+        <is>
+          <t>informed-by: Trade Capture | enables: Manage Trading Sub-Ledger | governed-by: Develop Accounting Policies &amp; Procedures</t>
+        </is>
+      </c>
+      <c r="AB166" s="5" t="inlineStr">
+        <is>
+          <t>Finance-enabled Supply &amp; Trading</t>
+        </is>
+      </c>
+      <c r="AC166" s="5" t="inlineStr">
+        <is>
+          <t>event-driven</t>
+        </is>
+      </c>
       <c r="AD166" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -23365,18 +23484,80 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U167" s="5" t="n"/>
-      <c r="V167" s="5" t="n"/>
-      <c r="W167" s="5" t="n"/>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>Maintain the financial accounting of production and inventory for supply and trading activity — recording and reconciling financial inventory balances and cost-of-sales effects under the enterprise-approved inventory valuation methodology, from verified operational balances — so the financial books carry a complete, correctly valued representation of physical activity.</t>
+        </is>
+      </c>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>Covers the financial-accounting side of production and inventory: recording and valuing production receipts, inventory movements, transfers, and exchange imbalances into the sub-ledger and GL; recording and reconciling financial inventory balances and cost-of-sales effects under the enterprise-approved inventory valuation methodology; and reconciling the financial inventory records to the operational balances. Operational quantities arrive as controlled inputs: the refinery daily material balance is owned by Perform Production Accounting (CM-1-1-7-1-3, batch 06) and network book-to-physical reconciliation by Perform Inventory Reconciliation (CM-1-1-3-7-5, batch 04) — this process values what those processes have verified; it does not re-perform the operational balance. Financial reconciliation to operational balances may identify differences for investigation but does not authorize operational stock adjustments, production remeasurement, or physical loss determination. Inventory valuation methodology, write-off approval, and valuation entries policy are owned by Finance under the locked rule. Excludes the operational balances (CM-1-1-7-1-3, CM-1-1-3-7-5); operational stock adjustments and loss determination (operational owners); valuation policy and write-offs (Finance); settlement (CM-1-2-4-1).</t>
+        </is>
+      </c>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>Record and value production receipts, inventory movements, and exchanges into the accounting records | record and reconcile financial inventory balances and cost-of-sales effects per the approved methodology | reconcile financial records to operational balances and refer differences for investigation | post correcting entries per approved corrections</t>
+        </is>
+      </c>
+      <c r="Q167" t="inlineStr">
+        <is>
+          <t>Refinery material balance (CM-1-1-7-1-3) | network stock reconciliation (CM-1-1-3-7-5) | operational stock adjustments, remeasurement, and loss determination (operational owners) | valuation methodology and write-offs (Finance, locked rule) | settlement (CM-1-2-4-1)</t>
+        </is>
+      </c>
+      <c r="R167" t="inlineStr">
+        <is>
+          <t>Manage Production &amp; Inventory Accounting</t>
+        </is>
+      </c>
+      <c r="T167" t="inlineStr">
+        <is>
+          <t>Batch 15 (2026-09-20). Q2 decision: financial production and inventory accounting here; operational material balance and stock reconciliation with their batch 04/06 owners — the same operational source feeds each process, but each owns a different record and decision, extending the batch 13 record-partition principle into the accounting layer. Record-not-compute (Hamid, batch 15): this process maintains the financial representation of verified balances; it does not compute inventory independently of operational systems. Preferred normalized label 'Manage Production &amp; Inventory Accounting' recorded as alt label and queued for the naming pass (row names mirror the locked taxonomy). APQC 10224 is a scheduling candidate, unrelated.</t>
+        </is>
+      </c>
+      <c r="U167" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V167" s="5" t="inlineStr">
+        <is>
+          <t>Keep the financial books correctly valued and complete against verified physical activity.</t>
+        </is>
+      </c>
+      <c r="W167" s="5" t="inlineStr">
+        <is>
+          <t>SRC-EI-HM31-001 | SRC-APQC-PCF-001</t>
+        </is>
+      </c>
       <c r="X167" s="5" t="n"/>
-      <c r="Y167" s="5" t="n"/>
-      <c r="Z167" s="5" t="n"/>
-      <c r="AA167" s="5" t="n"/>
-      <c r="AB167" s="5" t="n"/>
-      <c r="AC167" s="5" t="n"/>
+      <c r="Y167" s="5" t="inlineStr">
+        <is>
+          <t>Refinery accounted balances (CM-1-1-7-1-3) | reconciled stock positions (CM-1-1-3-7-5) | actualized movements (CM-1-2-3-1) | enterprise valuation methodology (Finance)</t>
+        </is>
+      </c>
+      <c r="Z167" s="5" t="inlineStr">
+        <is>
+          <t>Valued production and inventory accounting records reconciled to operational balances</t>
+        </is>
+      </c>
+      <c r="AA167" s="5" t="inlineStr">
+        <is>
+          <t>uses-input: Perform Production Accounting | uses-input: Perform Inventory Reconciliation | enables: Manage Trading Sub-Ledger</t>
+        </is>
+      </c>
+      <c r="AB167" s="5" t="inlineStr">
+        <is>
+          <t>Finance-enabled Supply &amp; Trading</t>
+        </is>
+      </c>
+      <c r="AC167" s="5" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
       <c r="AD167" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -23444,18 +23625,75 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U168" s="5" t="n"/>
-      <c r="V168" s="5" t="n"/>
-      <c r="W168" s="5" t="n"/>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>Execute royalty and interest disbursements arising from first-purchase and marketing arrangements — calculating owner-level distributions from settled lease transactions and division-of-interest references, managing suspense and unclaimed amounts per the applicable requirements, and submitting authorized disbursement instructions — so interest owners are paid correctly and on time.</t>
+        </is>
+      </c>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>Included only where the downstream organization purchases at lease/wellhead or administers first-purchaser arrangements, per the batch 09 caveat carried through lease contract administration (CM-1-2-1-2-8), lease actualization (CM-1-2-3-1-6), and first-purchaser settlement (CM-1-2-4-1-6). This process is not in scope for ordinary downstream product marketing unless the organization is the first purchaser or contractually responsible disburser for lease/wellhead production. Covers disbursement execution: computing owner-level distributions from settled first-purchase transactions and current division-of-interest references, applying contractual deductions, managing suspense accounts and unclaimed-property handling per the applicable jurisdiction's requirements, responding to owner inquiries on payments, and preparing and submitting authorized disbursement instructions through the designated finance processes (batch 14 Q3 rule). Owner-payment entitlement calculation policy, upstream royalty policy, division-order legal determinations, and E&amp;P accounting remain outside scope per batches 13-14. Excludes first-purchaser settlement calculation (CM-1-2-4-1-6); lease contract administration (CM-1-2-1-2-8); entitlement and royalty policy (outside scope); payment release and bank execution (Treasury/banking).</t>
+        </is>
+      </c>
+      <c r="P168" t="inlineStr">
+        <is>
+          <t>Compute owner-level distributions from settled transactions and division-of-interest references | manage suspense and unclaimed amounts per applicable requirements | respond to owner payment inquiries | prepare and submit authorized disbursement instructions and track status</t>
+        </is>
+      </c>
+      <c r="Q168" t="inlineStr">
+        <is>
+          <t>First-purchaser settlement (CM-1-2-4-1-6) | lease contract administration (CM-1-2-1-2-8) | entitlement policy, royalty policy, division-order legal determinations, and E&amp;P accounting (outside scope) | ordinary downstream product marketing (not applicable) | payment release and bank execution (Treasury/banking)</t>
+        </is>
+      </c>
+      <c r="T168" t="inlineStr">
+        <is>
+          <t>Batch 15 (2026-09-20). Execution-only row completing the lease chain (contract b09, actualization b13, settlement b14, disbursement here); conditional downstream scope and the standing batch 09 ownership follow-up apply. Suspense and unclaimed-property requirements are jurisdiction-specific. APQC 20008 is a marketing-plans candidate, a false lexical match on 'marketing'.</t>
+        </is>
+      </c>
+      <c r="U168" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V168" s="5" t="inlineStr">
+        <is>
+          <t>Pay interest owners correctly from settled first-purchase transactions with a controlled, evidenced trail.</t>
+        </is>
+      </c>
+      <c r="W168" s="5" t="inlineStr">
+        <is>
+          <t>SRC-EIA-GLOSS-001</t>
+        </is>
+      </c>
       <c r="X168" s="5" t="n"/>
-      <c r="Y168" s="5" t="n"/>
-      <c r="Z168" s="5" t="n"/>
-      <c r="AA168" s="5" t="n"/>
-      <c r="AB168" s="5" t="n"/>
-      <c r="AC168" s="5" t="n"/>
+      <c r="Y168" s="5" t="inlineStr">
+        <is>
+          <t>Settled first-purchase transactions and statements (CM-1-2-4-1-6) | division-of-interest references (CM-1-2-1-2-8) | jurisdictional suspense and unclaimed-property requirements</t>
+        </is>
+      </c>
+      <c r="Z168" s="5" t="inlineStr">
+        <is>
+          <t>Authorized, submitted, tracked, and evidenced royalty and interest disbursement instructions</t>
+        </is>
+      </c>
+      <c r="AA168" s="5" t="inlineStr">
+        <is>
+          <t>follows: Settle First Purchaser/Leases | uses-input: Manage Lease Contract</t>
+        </is>
+      </c>
+      <c r="AB168" s="5" t="inlineStr">
+        <is>
+          <t>Finance-enabled Supply &amp; Trading</t>
+        </is>
+      </c>
+      <c r="AC168" s="5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AD168" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -23523,18 +23761,75 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U169" s="5" t="n"/>
-      <c r="V169" s="5" t="n"/>
-      <c r="W169" s="5" t="n"/>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>Record trading receivables, payables, and actuals in the accounting records — recording authorized settlement outcomes and validated invoices in AR/AP, posting actualized transaction values, monitoring open items and aging, and keeping the payables and receivables position complete and current — so the financial position reflects settled and actualized activity.</t>
+        </is>
+      </c>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>Covers AR/AP and actuals recording for trading activity: recording authorized settlement outcomes and validated invoices in AR/AP (invoice validation itself remains with Settlements per the batch 14 Q3 chain), posting actualized values and settlement outcomes to the accounting records, monitoring open items, aging, and unmatched instructions, and coordinating overdue items with Settlements and Credit Risk through the accountable owners. Cash receipts are applied by Manage Cash Application (CM-1-2-4-2-9); accrual of un-invoiced activity by Manage Accruals (CM-1-2-4-2-10); payment release and bank execution by Treasury and banking processes; collection risk decisions and credit holds by Credit Risk (CM-1-2-2-1) under the batch 11 boundary. Excludes settlement calculation and invoice validation (CM-1-2-4-1); cash application (CM-1-2-4-2-9); accruals (CM-1-2-4-2-10); credit decisions (CM-1-2-2-1); payment execution (Treasury/banking).</t>
+        </is>
+      </c>
+      <c r="P169" t="inlineStr">
+        <is>
+          <t>Record authorized settlement outcomes and validated invoices in AR/AP | post actualized values and settlement outcomes | monitor open items, aging, and unmatched instructions | coordinate overdue items with the accountable owners</t>
+        </is>
+      </c>
+      <c r="Q169" t="inlineStr">
+        <is>
+          <t>Settlement calculation and invoice validation (CM-1-2-4-1) | cash application (CM-1-2-4-2-9) | accruals (CM-1-2-4-2-10) | credit decisions and holds (CM-1-2-2-1) | payment release (Treasury/banking)</t>
+        </is>
+      </c>
+      <c r="T169" t="inlineStr">
+        <is>
+          <t>Batch 15 (2026-09-20). Receiving end of the batch 14 Q3 chain: Settlements validates and submits, this process records. 'Actuals' means actualized transaction values posted to the financial records, consistent with batch 13 terminology. Whether AR/AP operations sit in the trading organization or a shared-services center is operating-model-specific (organizational neutrality, batch 10). APQC 11743 is an unrelated routing candidate.</t>
+        </is>
+      </c>
+      <c r="U169" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V169" s="5" t="inlineStr">
+        <is>
+          <t>Keep the trading payables and receivables position complete, current, and evidenced.</t>
+        </is>
+      </c>
+      <c r="W169" s="5" t="inlineStr">
+        <is>
+          <t>SRC-APQC-PCF-001</t>
+        </is>
+      </c>
       <c r="X169" s="5" t="n"/>
-      <c r="Y169" s="5" t="n"/>
-      <c r="Z169" s="5" t="n"/>
-      <c r="AA169" s="5" t="n"/>
-      <c r="AB169" s="5" t="n"/>
-      <c r="AC169" s="5" t="n"/>
+      <c r="Y169" s="5" t="inlineStr">
+        <is>
+          <t>Authorized settlement outcomes and validated invoices (CM-1-2-4-1) | actualized transaction values (CM-1-2-3-1)</t>
+        </is>
+      </c>
+      <c r="Z169" s="5" t="inlineStr">
+        <is>
+          <t>Booked, monitored AR/AP and actuals records</t>
+        </is>
+      </c>
+      <c r="AA169" s="5" t="inlineStr">
+        <is>
+          <t>follows: Settlements | enables: Manage Cash Application | enables: Manage Trading Sub-Ledger</t>
+        </is>
+      </c>
+      <c r="AB169" s="5" t="inlineStr">
+        <is>
+          <t>Finance-enabled Supply &amp; Trading</t>
+        </is>
+      </c>
+      <c r="AC169" s="5" t="inlineStr">
+        <is>
+          <t>event-driven</t>
+        </is>
+      </c>
       <c r="AD169" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -23602,18 +23897,75 @@
           <t>no meaningful APQC candidate</t>
         </is>
       </c>
-      <c r="U170" s="5" t="n"/>
-      <c r="V170" s="5" t="n"/>
-      <c r="W170" s="5" t="n"/>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>Maintain the trading sub-ledger as the complete transactional accounting record — ensuring every captured, actualized, and settled transaction posts correctly under its determined treatment, reconciling the sub-ledger to the general ledger, and enforcing period cut-off — so the general ledger can rely on a complete, reconciled trading record.</t>
+        </is>
+      </c>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t>Covers sub-ledger control, whether implemented in the CTRM/ETRM platform, an ERP sub-ledger, or an integrated accounting architecture: monitoring posting completeness from capture, actualization, settlement, and accounting sources; validating that postings follow the determined treatments (CM-1-2-4-2-1); reconciling sub-ledger balances to the general ledger and resolving breaks; enforcing period cut-off and controlled reopening; and evidencing the reconciliation. Ledger and account structures are administered by Manage Financial System/GL (CM-1-2-4-2-8, per the batch 12 binding); the postings themselves originate in the owning recording processes. Excludes GL and ledger-structure administration (CM-1-2-4-2-8); treatment assessment (CM-1-2-4-2-1); source postings (owning processes); financial reporting (CM-1-2-4-2-7).</t>
+        </is>
+      </c>
+      <c r="P170" t="inlineStr">
+        <is>
+          <t>Monitor posting completeness across sources | validate postings against determined treatments | reconcile sub-ledger to GL and resolve breaks | enforce period cut-off with evidence</t>
+        </is>
+      </c>
+      <c r="Q170" t="inlineStr">
+        <is>
+          <t>Ledger-structure administration (CM-1-2-4-2-8) | treatment assessment (CM-1-2-4-2-1) | source postings (owning processes) | financial reporting (CM-1-2-4-2-7)</t>
+        </is>
+      </c>
+      <c r="T170" t="inlineStr">
+        <is>
+          <t>Batch 15 (2026-09-20). The sub-ledger is the transactional accounting record beneath the GL; its physical implementation (CTRM/ETRM, ERP, or integrated architecture) is system-design-specific and not assumed — relevant to the future system-integration workstream. This row owns the completeness and reconciliation control, not the structures or the source postings. APQC 11743 is an unrelated routing candidate.</t>
+        </is>
+      </c>
+      <c r="U170" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V170" s="5" t="inlineStr">
+        <is>
+          <t>Guarantee the GL rests on a complete, reconciled, cut-off-controlled trading record.</t>
+        </is>
+      </c>
+      <c r="W170" s="5" t="inlineStr">
+        <is>
+          <t>SRC-APQC-PCF-001</t>
+        </is>
+      </c>
       <c r="X170" s="5" t="n"/>
-      <c r="Y170" s="5" t="n"/>
-      <c r="Z170" s="5" t="n"/>
-      <c r="AA170" s="5" t="n"/>
-      <c r="AB170" s="5" t="n"/>
-      <c r="AC170" s="5" t="n"/>
+      <c r="Y170" s="5" t="inlineStr">
+        <is>
+          <t>Postings from capture, actualization, settlement, and accounting processes | treatment reference (CM-1-2-4-2-1) | GL balances (CM-1-2-4-2-8)</t>
+        </is>
+      </c>
+      <c r="Z170" s="5" t="inlineStr">
+        <is>
+          <t>Reconciled sub-ledger with evidenced cut-off</t>
+        </is>
+      </c>
+      <c r="AA170" s="5" t="inlineStr">
+        <is>
+          <t>uses-input: Manage AR/AP &amp; Actuals | uses-input: Manage Accounting Treatments | enables: Reconcile Economic PNL To Accounting PNL</t>
+        </is>
+      </c>
+      <c r="AB170" s="5" t="inlineStr">
+        <is>
+          <t>Finance-enabled Supply &amp; Trading</t>
+        </is>
+      </c>
+      <c r="AC170" s="5" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
       <c r="AD170" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -23676,18 +24028,75 @@
           <t>no meaningful APQC candidate</t>
         </is>
       </c>
-      <c r="U171" s="5" t="n"/>
-      <c r="V171" s="5" t="n"/>
-      <c r="W171" s="5" t="n"/>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>Reconcile the economic profit and loss produced by the trading risk processes to the profit and loss recorded in the accounting books — identifying, quantifying, explaining, and evidencing expected and unexpected differences by cause — so management, risk, and financial views of trading results are provably consistent.</t>
+        </is>
+      </c>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>Covers the economic-to-accounting P&amp;L reconciliation at each close: taking the controlled economic P&amp;L inputs delivered by the end-of-month process (Perform End-of-Month (EOM) Process, CM-1-2-2-3-5, per the batch 12 binding) and the accounting P&amp;L from the reconciled sub-ledger and GL; identifying, quantifying, explaining, and evidencing expected and unexpected differences by cause — accounting treatment effects (hedge accounting, normal purchase/normal sale election, own-use), accrual and timing differences, valuation-basis differences, inventory valuation and cost-allocation timing, realized-versus-unrealized timing, valuation adjustments, tax and statutory adjustments, and scope differences; and escalating unexplained or out-of-tolerance differences. The reconciliation is a bridge: expected differences are explained and evidenced, not eliminated. Interim indicative reconciliations may run more frequently per local procedure. Excludes producing the economic P&amp;L (Market Risk Management, CM-1-2-2-3, batch 12); producing the accounting P&amp;L (the recording processes); valuation policy (Finance, locked rule).</t>
+        </is>
+      </c>
+      <c r="P171" t="inlineStr">
+        <is>
+          <t>Assemble economic and accounting P&amp;L on a consistent basis | quantify and explain expected and unexpected differences by cause | evidence the reconciliation bridge | escalate unexplained or out-of-tolerance differences</t>
+        </is>
+      </c>
+      <c r="Q171" t="inlineStr">
+        <is>
+          <t>Economic P&amp;L production (CM-1-2-2-3) | accounting P&amp;L production (recording processes) | valuation policy (Finance, locked rule)</t>
+        </is>
+      </c>
+      <c r="T171" t="inlineStr">
+        <is>
+          <t>Batch 15 (2026-09-20). Receiving end of the batch 12 EOM binding: Market Risk coordinates and evidences the month-end economic close and provides controlled economic inputs; this process owns the reconciliation to the books. Bridge-not-elimination (Hamid, batch 15): expected differences (NPNS/own-use treatment, hedge-accounting timing, accrual timing, valuation basis, inventory and cost-allocation timing, realized-versus-unrealized, tax and statutory adjustments) are systematic and are explained, not defects to remove. 'PNL' retained in the technical label; 'P&amp;L' in prose per the batch 12 convention, label queued for the naming pass. APQC 12940 'Reconcile inventories' is unrelated.</t>
+        </is>
+      </c>
+      <c r="U171" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V171" s="5" t="inlineStr">
+        <is>
+          <t>Prove management and financial views of trading results agree, with every difference explained.</t>
+        </is>
+      </c>
+      <c r="W171" s="5" t="inlineStr">
+        <is>
+          <t>SRC-FASB-ASC815-001 | SRC-CCRO-002A</t>
+        </is>
+      </c>
       <c r="X171" s="5" t="n"/>
-      <c r="Y171" s="5" t="n"/>
-      <c r="Z171" s="5" t="n"/>
-      <c r="AA171" s="5" t="n"/>
-      <c r="AB171" s="5" t="n"/>
-      <c r="AC171" s="5" t="n"/>
+      <c r="Y171" s="5" t="inlineStr">
+        <is>
+          <t>Controlled economic P&amp;L inputs (CM-1-2-2-3-5) | accounting P&amp;L from the reconciled sub-ledger (CM-1-2-4-2-5) | treatment reference (CM-1-2-4-2-1)</t>
+        </is>
+      </c>
+      <c r="Z171" s="5" t="inlineStr">
+        <is>
+          <t>Evidenced economic-to-accounting P&amp;L reconciliation bridge</t>
+        </is>
+      </c>
+      <c r="AA171" s="5" t="inlineStr">
+        <is>
+          <t>uses-input: Perform End-of-Month (EOM) Process | uses-input: Manage Trading Sub-Ledger | informed-by: Manage Accounting Treatments</t>
+        </is>
+      </c>
+      <c r="AB171" s="5" t="inlineStr">
+        <is>
+          <t>Finance-enabled Supply &amp; Trading</t>
+        </is>
+      </c>
+      <c r="AC171" s="5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AD171" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -23755,18 +24164,80 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U172" s="5" t="n"/>
-      <c r="V172" s="5" t="n"/>
-      <c r="W172" s="5" t="n"/>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>Prepare and control the financial documentation and internal financial reporting for supply and trading activity — management reporting on financial results, accounting workpapers and reconciliation evidence, and controlled inputs to external financial reporting through the accountable owners — so financial information about trading is complete, evidenced, and consistently produced.</t>
+        </is>
+      </c>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t>Covers financial information control for trading: producing internal financial and management reporting on trading results; maintaining accounting workpapers, reconciliation evidence, and close documentation (including the settlement-accounting records excluded from the batch 14 settlement-documents working set); and preparing controlled inputs to external financial reporting, statutory filings, and audit requests through the accountable Finance owners, per the batch 11 internal-reports-and-controlled-inputs precedent. Excludes external financial reporting ownership and statutory filings (Finance); risk reporting (Market Risk and Credit Risk reporting processes, batches 11-12); the settlement working document set (CM-1-2-4-1-9); enterprise records-retention policy (governance owner).</t>
+        </is>
+      </c>
+      <c r="P172" t="inlineStr">
+        <is>
+          <t>Produce internal financial and management reporting on trading results | maintain accounting workpapers and close documentation | prepare controlled inputs to external reporting and audits through accountable owners</t>
+        </is>
+      </c>
+      <c r="Q172" t="inlineStr">
+        <is>
+          <t>External financial reporting and statutory filings (Finance) | risk reporting (CM-1-2-2-1, CM-1-2-2-3) | settlement working documents (CM-1-2-4-1-9) | records-retention policy (governance owner)</t>
+        </is>
+      </c>
+      <c r="R172" t="inlineStr">
+        <is>
+          <t>Manage Financial Information Documentation and Reporting</t>
+        </is>
+      </c>
+      <c r="T172" t="inlineStr">
+        <is>
+          <t>Batch 15 (2026-09-20). Internal reports plus controlled inputs through accountable owners, per the batch 11 precedent; external reporting accountability stays with Finance. Normalized label 'Manage Financial Information Documentation and Reporting' recorded as alt label and queued for the naming pass — the 'Info.' abbreviation should not survive into the canonical glossary. APQC 20765 'Manage information' is a generic IT candidate.</t>
+        </is>
+      </c>
+      <c r="U172" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V172" s="5" t="inlineStr">
+        <is>
+          <t>Make trading financial information complete, evidenced, and reliably reportable.</t>
+        </is>
+      </c>
+      <c r="W172" s="5" t="inlineStr">
+        <is>
+          <t>SRC-APQC-PCF-001</t>
+        </is>
+      </c>
       <c r="X172" s="5" t="n"/>
-      <c r="Y172" s="5" t="n"/>
-      <c r="Z172" s="5" t="n"/>
-      <c r="AA172" s="5" t="n"/>
-      <c r="AB172" s="5" t="n"/>
-      <c r="AC172" s="5" t="n"/>
+      <c r="Y172" s="5" t="inlineStr">
+        <is>
+          <t>Reconciled sub-ledger and GL balances | P&amp;L reconciliation bridge (CM-1-2-4-2-6) | reporting calendars and audit requests</t>
+        </is>
+      </c>
+      <c r="Z172" s="5" t="inlineStr">
+        <is>
+          <t>Internal financial reporting and controlled external-reporting inputs with evidence</t>
+        </is>
+      </c>
+      <c r="AA172" s="5" t="inlineStr">
+        <is>
+          <t>uses-input: Reconcile Economic PNL To Accounting PNL | uses-input: Manage Trading Sub-Ledger | assures: Accounting</t>
+        </is>
+      </c>
+      <c r="AB172" s="5" t="inlineStr">
+        <is>
+          <t>Finance-enabled Supply &amp; Trading</t>
+        </is>
+      </c>
+      <c r="AC172" s="5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AD172" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -23829,18 +24300,75 @@
           <t>strong APQC candidate but no validator agreed</t>
         </is>
       </c>
-      <c r="U173" s="5" t="n"/>
-      <c r="V173" s="5" t="n"/>
-      <c r="W173" s="5" t="n"/>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>Administer the financial system structures used by trading accounting — chart-of-accounts mapping, ledger and book structures, posting rules and business interface configuration from trading systems to the general ledger, and accounting master data — so postings land correctly, completely, and controllably in the financial records.</t>
+        </is>
+      </c>
+      <c r="O173" t="inlineStr">
+        <is>
+          <t>Covers accounting-structure administration: maintaining ledger and book structures for trading accounting (the accounting counterpart of the batch 12 decision that risk book structures live with Market Risk and ledger structures here); chart-of-accounts mapping for trading transactions; posting rules and business-side interface configuration between trading, settlement, and financial systems; accounting master data within the accounting domain; and posting-interface error monitoring and business resolution. Changes follow the applicable change control. Enterprise master-data governance frameworks are excluded per the batch 05 precedent; ownership and operation of the enterprise GL platform itself follows the IT and Shared Services operating model. Excludes technical application development, integration-platform operation, identity and security administration, infrastructure, and release deployment, owned by Process Excellence &amp; IT or the relevant technology delivery function; enterprise GL platform ownership (IT/Shared Services per operating model); enterprise master-data governance (batch 05 exclusion); risk book structures (CM-1-2-2-3-1, batch 12); sub-ledger reconciliation control (CM-1-2-4-2-5).</t>
+        </is>
+      </c>
+      <c r="P173" t="inlineStr">
+        <is>
+          <t>Maintain ledger and book structures and chart-of-accounts mapping | configure posting rules and business-side interface settings | maintain accounting master data within the accounting domain | monitor posting-interface errors and drive business resolution</t>
+        </is>
+      </c>
+      <c r="Q173" t="inlineStr">
+        <is>
+          <t>Technical development, integration-platform operation, security administration, infrastructure, and release deployment (Process Excellence &amp; IT / technology delivery) | enterprise GL platform ownership (IT/Shared Services) | enterprise master-data governance (batch 05 exclusion) | risk book structures (CM-1-2-2-3-1) | sub-ledger reconciliation (CM-1-2-4-2-5)</t>
+        </is>
+      </c>
+      <c r="T173" t="inlineStr">
+        <is>
+          <t>Batch 15 (2026-09-20). Business administration versus technical ownership (Hamid, batch 15): this process owns accounting-specific configuration and business interface administration; technical development, platform operation, security, infrastructure, and deployment belong to the technology delivery function. Receiving end of the batch 12 book-structure partition: risk-reporting hierarchies at CM-1-2-2-3-1, ledger structures here. APQC 17058 scored STRONG at 3b but NO SOURCE — honored; comparative evidence only.</t>
+        </is>
+      </c>
+      <c r="U173" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V173" s="5" t="inlineStr">
+        <is>
+          <t>Keep the structural plumbing of trading accounting correct and controlled on the business side.</t>
+        </is>
+      </c>
+      <c r="W173" s="5" t="inlineStr">
+        <is>
+          <t>SRC-APQC-PCF-001</t>
+        </is>
+      </c>
       <c r="X173" s="5" t="n"/>
-      <c r="Y173" s="5" t="n"/>
-      <c r="Z173" s="5" t="n"/>
-      <c r="AA173" s="5" t="n"/>
-      <c r="AB173" s="5" t="n"/>
-      <c r="AC173" s="5" t="n"/>
+      <c r="Y173" s="5" t="inlineStr">
+        <is>
+          <t>Approved structure and mapping change requests | interface specifications from trading and settlement systems | accounting master data requirements</t>
+        </is>
+      </c>
+      <c r="Z173" s="5" t="inlineStr">
+        <is>
+          <t>Controlled ledger structures, mappings, and business interface configuration</t>
+        </is>
+      </c>
+      <c r="AA173" s="5" t="inlineStr">
+        <is>
+          <t>enables: Manage Trading Sub-Ledger | enables: Manage AR/AP &amp; Actuals | informed-by: Manage Trading Books &amp; Strategies Structure</t>
+        </is>
+      </c>
+      <c r="AB173" s="5" t="inlineStr">
+        <is>
+          <t>Finance-enabled Supply &amp; Trading</t>
+        </is>
+      </c>
+      <c r="AC173" s="5" t="inlineStr">
+        <is>
+          <t>continuous</t>
+        </is>
+      </c>
       <c r="AD173" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -23908,18 +24436,75 @@
           <t>strong APQC candidate but no validator agreed</t>
         </is>
       </c>
-      <c r="U174" s="5" t="n"/>
-      <c r="V174" s="5" t="n"/>
-      <c r="W174" s="5" t="n"/>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>Apply cash receipts to open trading receivables — matching bank-reported receipts against invoices, settlement statements, and netting arrangements, investigating and coordinating resolution of unapplied, unidentified, short, and over payments, and evidencing application — so the receivables position is accurate and cash is accounted for daily.</t>
+        </is>
+      </c>
+      <c r="O174" t="inlineStr">
+        <is>
+          <t>Covers cash application for trading receivables: matching bank-reported receipts against open items using invoice references, settlement statements, and netting agreements; applying receipts and posting application entries; investigating and coordinating resolution of unapplied, unidentified, short, and over payments with Settlements, AR, Credit, and counterparty contacts as applicable — Credit Risk makes any resulting credit decision under the batch 11 boundary, not this process; and evidencing daily application. Bank account operation, cash positioning, and funds movement are owned by Treasury and banking processes (batch 14 Q3 rule); whether cash application runs in the trading organization or a shared-services center is operating-model-specific. Excludes bank account operation and cash management (Treasury/banking); receivables booking (CM-1-2-4-2-4); settlement calculation (CM-1-2-4-1); credit decisions (CM-1-2-2-1).</t>
+        </is>
+      </c>
+      <c r="P174" t="inlineStr">
+        <is>
+          <t>Match bank-reported receipts to open items and netting arrangements | apply receipts and post application entries | investigate and coordinate resolution of unapplied, unidentified, short, and over payments | evidence daily application</t>
+        </is>
+      </c>
+      <c r="Q174" t="inlineStr">
+        <is>
+          <t>Bank operation and cash management (Treasury/banking) | receivables booking (CM-1-2-4-2-4) | settlement calculation (CM-1-2-4-1) | credit decisions (CM-1-2-2-1)</t>
+        </is>
+      </c>
+      <c r="T174" t="inlineStr">
+        <is>
+          <t>Batch 15 (2026-09-20). Application-not-custody: this process accounts for cash received; Treasury owns the cash itself. Short payments or delinquency may trigger credit involvement, but the credit decision belongs to Credit Risk (batch 11 boundary). APQC 10759 'Manage cash' scored STRONG at 3b but NO SOURCE — honored; that candidate is treasury cash management, a false match for application.</t>
+        </is>
+      </c>
+      <c r="U174" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V174" s="5" t="inlineStr">
+        <is>
+          <t>Account for every receipt against the right open item, daily and evidenced.</t>
+        </is>
+      </c>
+      <c r="W174" s="5" t="inlineStr">
+        <is>
+          <t>SRC-APQC-PCF-001</t>
+        </is>
+      </c>
       <c r="X174" s="5" t="n"/>
-      <c r="Y174" s="5" t="n"/>
-      <c r="Z174" s="5" t="n"/>
-      <c r="AA174" s="5" t="n"/>
-      <c r="AB174" s="5" t="n"/>
-      <c r="AC174" s="5" t="n"/>
+      <c r="Y174" s="5" t="inlineStr">
+        <is>
+          <t>Bank receipt reporting (Treasury/banking) | open receivables (CM-1-2-4-2-4) | netting agreements and settlement statements</t>
+        </is>
+      </c>
+      <c r="Z174" s="5" t="inlineStr">
+        <is>
+          <t>Applied cash with resolved exceptions and evidence</t>
+        </is>
+      </c>
+      <c r="AA174" s="5" t="inlineStr">
+        <is>
+          <t>follows: Manage AR/AP &amp; Actuals | uses-input: Settlements</t>
+        </is>
+      </c>
+      <c r="AB174" s="5" t="inlineStr">
+        <is>
+          <t>Finance-enabled Supply &amp; Trading</t>
+        </is>
+      </c>
+      <c r="AC174" s="5" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
       <c r="AD174" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -23987,18 +24572,75 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U175" s="5" t="n"/>
-      <c r="V175" s="5" t="n"/>
-      <c r="W175" s="5" t="n"/>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>Calculate, post, and true up accruals for trading activity — un-invoiced delivered or received volumes, expected fees and charges, and estimated prices pending final determination — per the enterprise accrual methodology, so each period's books are complete for activity not yet settled.</t>
+        </is>
+      </c>
+      <c r="O175" t="inlineStr">
+        <is>
+          <t>Covers the accrual cycle: identifying accruable activity from actualized movements and open settlement items, estimating accrual values per the enterprise methodology, posting accruals at cut-off, reversing or truing up against actual settlements, and analyzing accrual accuracy. Accruals may be based on actualized but uninvoiced activity, estimated unactualized activity where policy permits, expected service charges, or deferred pricing, depending on the approved close methodology (including provisional-price estimates pending final price determination per the batch 14 crude pricing pattern). Accrual methodology and materiality policy are owned by Finance under the locked rule; this process executes them. Excludes accrual methodology and policy (Finance, locked rule); settlement (CM-1-2-4-1); actualization (CM-1-2-3-1); AR/AP booking of settled items (CM-1-2-4-2-4).</t>
+        </is>
+      </c>
+      <c r="P175" t="inlineStr">
+        <is>
+          <t>Identify accruable activity per the approved close methodology | estimate accrual values per enterprise methodology | post at cut-off and true up against settlements | analyze accrual accuracy</t>
+        </is>
+      </c>
+      <c r="Q175" t="inlineStr">
+        <is>
+          <t>Accrual methodology and policy (Finance, locked rule) | settlement (CM-1-2-4-1) | actualization (CM-1-2-3-1) | booking of settled items (CM-1-2-4-2-4)</t>
+        </is>
+      </c>
+      <c r="T175" t="inlineStr">
+        <is>
+          <t>Batch 15 (2026-09-20). Execute-within-policy: methodology is Finance-owned, execution here. Accrual bases (Hamid, batch 15) span actualized-but-uninvoiced, policy-permitted estimated unactualized activity, expected service charges, and deferred pricing — not only delivered/received-not-invoiced. Accrual-to-actual analysis feeds estimation improvement. APQC 11743 is an unrelated routing candidate.</t>
+        </is>
+      </c>
+      <c r="U175" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V175" s="5" t="inlineStr">
+        <is>
+          <t>Make each period's books complete for real activity that has not yet settled.</t>
+        </is>
+      </c>
+      <c r="W175" s="5" t="inlineStr">
+        <is>
+          <t>SRC-APQC-PCF-001</t>
+        </is>
+      </c>
       <c r="X175" s="5" t="n"/>
-      <c r="Y175" s="5" t="n"/>
-      <c r="Z175" s="5" t="n"/>
-      <c r="AA175" s="5" t="n"/>
-      <c r="AB175" s="5" t="n"/>
-      <c r="AC175" s="5" t="n"/>
+      <c r="Y175" s="5" t="inlineStr">
+        <is>
+          <t>Actualized movements not yet settled (CM-1-2-3-1) | open settlement items (CM-1-2-4-1) | enterprise accrual methodology (Finance)</t>
+        </is>
+      </c>
+      <c r="Z175" s="5" t="inlineStr">
+        <is>
+          <t>Posted, evidenced, trued-up accruals</t>
+        </is>
+      </c>
+      <c r="AA175" s="5" t="inlineStr">
+        <is>
+          <t>uses-input: Actualizations | uses-input: Settlements | enables: Manage Trading Sub-Ledger</t>
+        </is>
+      </c>
+      <c r="AB175" s="5" t="inlineStr">
+        <is>
+          <t>Finance-enabled Supply &amp; Trading</t>
+        </is>
+      </c>
+      <c r="AC175" s="5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AD175" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -24066,18 +24708,75 @@
           <t>strong APQC candidate but no validator agreed</t>
         </is>
       </c>
-      <c r="U176" s="5" t="n"/>
-      <c r="V176" s="5" t="n"/>
-      <c r="W176" s="5" t="n"/>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>Execute transaction- and commodity-tax accounting for supply and trading activity by applying approved tax rules and tax-determination data to transactions, recording tax amounts, maintaining required transaction-level evidence, and preparing controlled tax-accounting and filing-support outputs for the accountable enterprise Tax function.</t>
+        </is>
+      </c>
+      <c r="O176" t="inlineStr">
+        <is>
+          <t>Covers transaction-tax execution for trading activity: applying approved tax rules and tax-determination data to purchases, sales, blends, and movements (in the United States, federal motor-fuels excise taxes under the IRS Publication 510 regime, plus state motor-fuel, sales and use, and similar taxes; other jurisdictions per their regimes); recording and accruing tax amounts; maintaining required transaction-level evidence; and preparing controlled tax-accounting and filing-support outputs for the accountable enterprise Tax function. This process consumes approved tax rules, jurisdiction and product tax classifications, licenses, exemption certificates, and tax-determination master data from their accountable owners; it may validate their presence and applicability to an individual transaction but does not establish tax policy, determine legal tax positions, own tax registrations or licenses, or file tax returns unless expressly delegated. Excludes tax policy, strategy, legal tax positions, registrations and licenses, corporate income tax, and tax-return filing (enterprise Tax function/Finance and accountable owners); settlement of tax-inclusive invoices (CM-1-2-4-1); customs and trade compliance where separately owned.</t>
+        </is>
+      </c>
+      <c r="P176" t="inlineStr">
+        <is>
+          <t>Apply approved tax rules and determination data to trading transactions | validate presence and applicability of licenses, exemptions, and classifications per transaction | record and accrue tax amounts with transaction-level evidence | prepare controlled tax-accounting and filing-support outputs for the Tax function</t>
+        </is>
+      </c>
+      <c r="Q176" t="inlineStr">
+        <is>
+          <t>Tax policy, strategy, legal positions, registrations, licenses, and return filing (enterprise Tax function/Finance and accountable owners) | corporate income tax (enterprise Tax function) | settlement of invoices (CM-1-2-4-1) | separately owned customs and trade compliance</t>
+        </is>
+      </c>
+      <c r="T176" t="inlineStr">
+        <is>
+          <t>Batch 15 (2026-09-20). Q3 decision (Hamid): transaction- and commodity-tax accounting execution under approved rules — tax-determination data, licenses, exemption certificates, and classifications are consumed from their accountable owners (Tax, Legal, EHS, or master-data governance per the operating model), validated for presence and applicability, never owned here; separation-of-duties in downstream fuels taxation. Motor-fuels excise is jurisdiction-specific; IRS Publication 510 covers the US federal regime as context, not tax advice; state and non-US regimes differ. APQC 10736 'Manage taxes' scored 1.0 at 3b but NO SOURCE — honored; that candidate is the corporate tax function, broader than this execution row.</t>
+        </is>
+      </c>
+      <c r="U176" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V176" s="5" t="inlineStr">
+        <is>
+          <t>Ensure every trading transaction carries correct, evidenced transaction-tax treatment under approved rules.</t>
+        </is>
+      </c>
+      <c r="W176" s="5" t="inlineStr">
+        <is>
+          <t>SRC-IRS-P510-001</t>
+        </is>
+      </c>
       <c r="X176" s="5" t="n"/>
-      <c r="Y176" s="5" t="n"/>
-      <c r="Z176" s="5" t="n"/>
-      <c r="AA176" s="5" t="n"/>
-      <c r="AB176" s="5" t="n"/>
-      <c r="AC176" s="5" t="n"/>
+      <c r="Y176" s="5" t="inlineStr">
+        <is>
+          <t>Captured and actualized transactions (CM-1-2-1-3, CM-1-2-3-1) | approved tax rules, classifications, licenses, and exemption data (accountable owners) | jurisdictional tax rates</t>
+        </is>
+      </c>
+      <c r="Z176" s="5" t="inlineStr">
+        <is>
+          <t>Recorded, accrued, evidenced transaction taxes with controlled filing-support outputs</t>
+        </is>
+      </c>
+      <c r="AA176" s="5" t="inlineStr">
+        <is>
+          <t>uses-input: Actualizations | enables: Manage Trading Sub-Ledger | informed-by: Develop Accounting Policies &amp; Procedures</t>
+        </is>
+      </c>
+      <c r="AB176" s="5" t="inlineStr">
+        <is>
+          <t>Finance-enabled Supply &amp; Trading</t>
+        </is>
+      </c>
+      <c r="AC176" s="5" t="inlineStr">
+        <is>
+          <t>periodic</t>
+        </is>
+      </c>
       <c r="AD176" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -24145,18 +24844,80 @@
           <t>strong APQC candidate but no validator agreed</t>
         </is>
       </c>
-      <c r="U177" s="5" t="n"/>
-      <c r="V177" s="5" t="n"/>
-      <c r="W177" s="5" t="n"/>
+      <c r="N177" t="inlineStr">
+        <is>
+          <t>Develop, maintain, version, and communicate trading-specific accounting procedures, close instructions, and implementation guidance that operationalize Finance-owned enterprise accounting policy for supply and trading activity.</t>
+        </is>
+      </c>
+      <c r="O177" t="inlineStr">
+        <is>
+          <t>Covers trading accounting procedure management: developing and maintaining desk-level procedures, close instructions, and implementation guidance that operationalize enterprise accounting policy for trading transaction types; assessing new products, structures, and standards changes for procedural impact and coordinating with Manage Accounting Treatments (CM-1-2-4-2-1) on treatment consequences; escalating policy gaps and interpretation questions to Finance; and maintaining procedure currency and version control. Boundary rule: Finance/Controller establishes enterprise accounting policy and decides material new policy questions (supported by technical accounting where applicable); Manage Accounting Treatments determines transaction-level treatment under approved policy; this process maintains the procedures, close instructions, and operational guidance; the accounting processes execute them. This process implements policy and never sets it, on the set-versus-apply pattern established in batches 07 and 11. Excludes enterprise accounting policy and material policy interpretation (Finance, locked rule); transaction-level treatment assessment (CM-1-2-4-2-1); enterprise records-retention and governance policy (governance owners).</t>
+        </is>
+      </c>
+      <c r="P177" t="inlineStr">
+        <is>
+          <t>Develop, maintain, version, and communicate trading accounting procedures and close instructions implementing enterprise policy | assess new products and standards changes for procedural impact | escalate policy gaps and questions to Finance | maintain procedure currency and version control</t>
+        </is>
+      </c>
+      <c r="Q177" t="inlineStr">
+        <is>
+          <t>Enterprise accounting policy and material policy interpretation (Finance, locked rule) | transaction-level treatment assessment (CM-1-2-4-2-1) | enterprise governance and retention policy (governance owners)</t>
+        </is>
+      </c>
+      <c r="R177" t="inlineStr">
+        <is>
+          <t>Maintain Trading Accounting Procedures and Guidance | Manage Trading Accounting Procedures</t>
+        </is>
+      </c>
+      <c r="T177" t="inlineStr">
+        <is>
+          <t>Batch 15 (2026-09-20). Q4 decision (Hamid): despite the row name, this process develops procedures within — never policy above — the Finance-owned framework; the set-versus-apply pattern (batches 07/11) governs. The displayed label overstates the mandate: preferred normalized label 'Maintain Trading Accounting Procedures and Guidance' (alternative 'Manage Trading Accounting Procedures') recorded as alt labels and queued for the naming pass with priority. APQC 16592 scored STRONG at 3b but NO SOURCE — honored; it is a retail omni-channel candidate.</t>
+        </is>
+      </c>
+      <c r="U177" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V177" s="5" t="inlineStr">
+        <is>
+          <t>Keep trading accounting execution consistent, current, and provably within enterprise policy.</t>
+        </is>
+      </c>
+      <c r="W177" s="5" t="inlineStr">
+        <is>
+          <t>SRC-FASB-ASC815-001 | SRC-APQC-PCF-001</t>
+        </is>
+      </c>
       <c r="X177" s="5" t="n"/>
-      <c r="Y177" s="5" t="n"/>
-      <c r="Z177" s="5" t="n"/>
-      <c r="AA177" s="5" t="n"/>
-      <c r="AB177" s="5" t="n"/>
-      <c r="AC177" s="5" t="n"/>
+      <c r="Y177" s="5" t="inlineStr">
+        <is>
+          <t>Enterprise accounting policy (Finance) | new products and structures (CM-1-2-1-3) | standards changes | treatment assessments (CM-1-2-4-2-1)</t>
+        </is>
+      </c>
+      <c r="Z177" s="5" t="inlineStr">
+        <is>
+          <t>Current, version-controlled trading accounting procedures and guidance</t>
+        </is>
+      </c>
+      <c r="AA177" s="5" t="inlineStr">
+        <is>
+          <t>governed-by: Accounting | enables: Manage Accounting Treatments | informed-by: Trade Capture</t>
+        </is>
+      </c>
+      <c r="AB177" s="5" t="inlineStr">
+        <is>
+          <t>Finance-enabled Supply &amp; Trading</t>
+        </is>
+      </c>
+      <c r="AC177" s="5" t="inlineStr">
+        <is>
+          <t>periodic</t>
+        </is>
+      </c>
       <c r="AD177" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -50610,7 +51371,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -52206,6 +52967,100 @@
         </is>
       </c>
       <c r="I39" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>SRC-FASB-ASC815-001</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Financial Accounting Standards Board</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>ASC Topic 815, Derivatives and Hedging (derivative recognition and fair value measurement; hedge accounting; normal purchases and normal sales scope exception)</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Current codification; public release evidence: ASU 2017-12 Targeted Improvements to Accounting for Hedging Activities; accessed 2026-09-20 (codification text is subscription access - claims based on public ASU releases and standard summaries)</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>FASB ASC 815; https://asc.fasb.org/</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Accounting standards authority</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>US GAAP derivative and hedge accounting concepts relevant to treatment assessment and economic-versus-accounting P&amp;L differences: derivative scope, hedge accounting, normal purchases and normal sales, treatment-assessment terminology. Not for internal process ownership, accounting conclusions on individual transactions, IFRS or non-US accounting, or tax treatment. Jurisdiction-specific - IFRS 9 and related standards govern elsewhere. Evidence only, not text to copy.</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Treatment assessment and P&amp;L-difference causes for CM-1-2-4-2-1, CM-1-2-4-2-6, CM-1-2-4-2-12</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>SRC-IRS-P510-001</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Internal Revenue Service</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Publication 510, Excise Taxes (federal motor-fuels excise taxes, fuel tax credits and refunds; Form 720 regime)</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Rev. December 2025; accessed 2026-09-20</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>https://www.irs.gov/publications/p510</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Regulatory</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>US federal motor-fuels excise tax mechanics and terminology context. Does not cover state motor-fuel or non-US regimes, does not determine internal tax-function ownership or process design, and is not tax advice. Evidence only, not text to copy.</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>US federal motor-fuels excise context for CM-1-2-4-2-11</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
         <is>
           <t>active</t>
         </is>

--- a/business_architecture/ontology/build/output/step3c-definition-authoring-workbook.xlsx
+++ b/business_architecture/ontology/build/output/step3c-definition-authoring-workbook.xlsx
@@ -18434,7 +18434,7 @@
       </c>
       <c r="T130" t="inlineStr">
         <is>
-          <t>Batch 12 (2026-09-19). Fully drafted and conditionally approved by Hamid; held pending on the recorded cross-batch dependency because an approved row may carry no material open question. Internal-versus-external rules is the boundary with CM-1-2-4-3.</t>
+          <t>Batch 12 (2026-09-19). Fully drafted and conditionally approved by Hamid; held pending on the recorded cross-batch dependency because an approved row may carry no material open question. Internal-versus-external rules is the boundary with CM-1-2-4-3. Batch 16 resolution (Hamid, 2026-09-20): the cross-batch boundary with Monitor Internal Trade Controls is resolved. Monitor Risk Policy Compliance monitors adherence to the internal market-risk framework, including risk appetite, approved limits, risk-book mandates, delegated trading authority, valuation and risk-control procedures, control-cycle evidence, and risk-exception approvals. Monitor Internal Trade Controls (CM-1-2-4-3-4) monitors the operation and evidence of internally implemented controls supporting external trading obligations. Neither process tests or owns the other's framework. Governance note (Hamid, batch 16): the market-risk framework is governed by the designated Risk Governance body, not Compliance — the former 'governed-by: Regulatory &amp; Compliance' relation is removed; no 'Risk Governance' taxonomy node exists and 'related-to' is not a controlled relationship_type, so the non-hierarchical relationship to Regulatory &amp; Compliance is carried here in prose per the conditional-relation precedent (batches 10/13/14). Row content otherwise unchanged from the batch 12 conditional approval.</t>
         </is>
       </c>
       <c r="U130" s="5" t="inlineStr">
@@ -18452,17 +18452,7 @@
           <t>SRC-CCRO-002A</t>
         </is>
       </c>
-      <c r="X130" s="5" t="inlineStr">
-        <is>
-          <t>Question: What is the precise boundary between Monitor Risk Policy Compliance and the future Monitor Internal Trade Controls (CM-1-2-4-3-4)?
-Context: This node monitors adherence to the internal market-risk framework (risk appetite, approved limits, book mandates, DOA, valuation and risk-control procedures, control-cycle evidence, exception approvals). Monitor Internal Trade Controls must be defined in the Regulatory &amp; Compliance batch as compliance-control monitoring for internally implemented controls that support external obligations (required deal approvals, audit evidence, reporting controls, market-conduct and surveillance controls).
-Options:
-A) The internal-versus-external-rules split holds as drafted, and CM-1-2-4-3-4 is defined with a reciprocal scope exclusion so neither node tests the other's framework.
-B) The future CM-1-2-4-3-4 definition overlaps market-risk policy testing, requiring a narrowing of one node's scope.
-Evidence: Batch 12 decision (Hamid, 2026-09-19): approve this row's content conditionally; the dependency must be resolved when the Regulatory &amp; Compliance cluster is authored, with a reciprocal exclusion recorded on whichever side needs it.
-Recommendation: Resolve in the Settlements &amp; Accounting / Regulatory &amp; Compliance batch; flip this row to approved once the reciprocal exclusion is confirmed. No content change expected under Option A.</t>
-        </is>
-      </c>
+      <c r="X130" s="5" t="n"/>
       <c r="Y130" s="5" t="inlineStr">
         <is>
           <t>policies, mandates, and DOA | control-cycle records | exception logs</t>
@@ -18475,7 +18465,7 @@
       </c>
       <c r="AA130" s="5" t="inlineStr">
         <is>
-          <t>uses-input: Establish &amp; Maintain Delegation Of Authority (DOA) | enables: Manage Risk Reporting | governed-by: Regulatory &amp; Compliance</t>
+          <t>uses-input: Establish &amp; Maintain Delegation Of Authority (DOA) | enables: Manage Risk Reporting</t>
         </is>
       </c>
       <c r="AB130" s="5" t="inlineStr">
@@ -18490,7 +18480,7 @@
       </c>
       <c r="AD130" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -24985,18 +24975,80 @@
           <t>strong APQC candidate but no validator agreed</t>
         </is>
       </c>
-      <c r="U178" s="5" t="n"/>
-      <c r="V178" s="5" t="n"/>
-      <c r="W178" s="5" t="n"/>
+      <c r="N178" t="inlineStr">
+        <is>
+          <t>The capability to keep supply and trading activity compliant with external law, regulation, and market rules and with the organization's own compliance framework — maintaining the trading compliance program's policies and procedures, monitoring external regulatory compliance, internal policy adherence, and the operation of compliance-supporting controls, assuring tax compliance, coordinating regulatory reporting obligations with their accountable owners, and managing compliance exceptions through to closure.</t>
+        </is>
+      </c>
+      <c r="O178" t="inlineStr">
+        <is>
+          <t>Covers the trading compliance capability: trading-specific compliance policies and procedures, external trading compliance monitoring including market-conduct surveillance, internal compliance-policy adherence monitoring, monitoring of internally implemented controls that support external obligations, tax compliance monitoring and assurance, RFS/RINs reporting coordination, and compliance exception management. The taxonomy places this capability in the Supply &amp; Trading branch because it governs trading activity. It is normally delivered with functional independence from trading decision-makers through an enterprise Compliance, Legal/Compliance, Risk/Compliance, or equivalent second-line function. Taxonomy placement does not establish operational reporting lines, approval authority, or organizational ownership. Boundary architecture: adherence to the internal market-risk framework is monitored by Monitor Risk Policy Compliance (CM-1-2-2-3-10) under the batch 12/16 reciprocal split; operational execution of regulatory reporting sits with its lifecycle owners (Report Trades to SDR, CM-1-2-1-3-10; Report Confirmation To SDR, CM-1-2-2-2-4; Perform RINs/REC Actualization, CM-1-2-3-1-7); environmental, health, safety, and government reporting filings, attestations, and submissions are owned by EHS &amp; Government Reporting under its locked rule; legal interpretation, enforcement response, and proceedings by Legal &amp; Corporate Communications; transaction-tax accounting execution by Manage Taxes (CM-1-2-4-2-11); enterprise tax policy and returns by the enterprise Tax function.</t>
+        </is>
+      </c>
+      <c r="P178" t="inlineStr">
+        <is>
+          <t>Maintain trading compliance policies and procedures | monitor external regulatory compliance and internal policy adherence | monitor compliance-supporting controls and assure tax compliance | coordinate reporting obligations with accountable owners and manage exceptions to closure</t>
+        </is>
+      </c>
+      <c r="Q178" t="inlineStr">
+        <is>
+          <t>Internal market-risk framework monitoring (CM-1-2-2-3-10) | operational regulatory reporting execution (CM-1-2-1-3-10, CM-1-2-2-2-4, CM-1-2-3-1-7) | EHS and government reporting filings and attestations (EHS &amp; Government Reporting, locked rule) | legal interpretation and proceedings (Legal &amp; Corporate Communications) | transaction-tax execution (CM-1-2-4-2-11) and enterprise tax policy/returns (Tax function)</t>
+        </is>
+      </c>
+      <c r="R178" t="inlineStr">
+        <is>
+          <t>Trading Compliance</t>
+        </is>
+      </c>
+      <c r="T178" t="inlineStr">
+        <is>
+          <t>Batch 16 (2026-09-20). Concept-type: capability per the batch 11/12/15 test. Monitor partition (Hamid, batch 16): external rules (CM-1-2-4-3-2); internal compliance policies (CM-1-2-4-3-3); compliance-supporting control operation (CM-1-2-4-3-4); internal market-risk framework (CM-1-2-2-3-10) — the batch 12 dependency is resolved under Option A with reciprocal exclusions on both sides. Q5 decision: taxonomy placement retained under Commercial &amp; Marketing with the mandatory independence and delivery-model statement in the scope note. APQC 16463 scored STRONG at 3b but NO SOURCE — honored; comparative evidence only.</t>
+        </is>
+      </c>
+      <c r="U178" s="5" t="inlineStr">
+        <is>
+          <t>capability</t>
+        </is>
+      </c>
+      <c r="V178" s="5" t="inlineStr">
+        <is>
+          <t>Keep trading activity provably compliant — with the law outside and the framework inside — and every compliance gap managed to closure.</t>
+        </is>
+      </c>
+      <c r="W178" s="5" t="inlineStr">
+        <is>
+          <t>SRC-CFTC-P180-001 | SRC-CFTC-GLOSS-001 | SRC-APQC-PCF-001</t>
+        </is>
+      </c>
       <c r="X178" s="5" t="n"/>
-      <c r="Y178" s="5" t="n"/>
-      <c r="Z178" s="5" t="n"/>
-      <c r="AA178" s="5" t="n"/>
-      <c r="AB178" s="5" t="n"/>
-      <c r="AC178" s="5" t="n"/>
+      <c r="Y178" s="5" t="inlineStr">
+        <is>
+          <t>Applicable law, regulation, and market rules | trading activity and control evidence from the lifecycle processes | enterprise compliance and legal frameworks</t>
+        </is>
+      </c>
+      <c r="Z178" s="5" t="inlineStr">
+        <is>
+          <t>A monitored, evidenced trading compliance posture with exceptions managed to closure</t>
+        </is>
+      </c>
+      <c r="AA178" s="5" t="inlineStr">
+        <is>
+          <t>assures: Trading Management | assures: Settlements | informed-by: Develop Compliance Policies &amp; Procedures</t>
+        </is>
+      </c>
+      <c r="AB178" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC178" s="5" t="inlineStr">
+        <is>
+          <t>continuous</t>
+        </is>
+      </c>
       <c r="AD178" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -25064,18 +25116,75 @@
           <t>strong APQC candidate but no validator agreed</t>
         </is>
       </c>
-      <c r="U179" s="5" t="n"/>
-      <c r="V179" s="5" t="n"/>
-      <c r="W179" s="5" t="n"/>
+      <c r="N179" t="inlineStr">
+        <is>
+          <t>Develop and maintain the trading compliance program's policies and procedures — market-conduct rules, information barriers, personal-account dealing, communications and conflicts requirements, regulatory-change management, and compliance monitoring and escalation procedures — within the enterprise compliance and legal governance framework, so trading activity operates under current, communicated compliance requirements.</t>
+        </is>
+      </c>
+      <c r="O179" t="inlineStr">
+        <is>
+          <t>Covers trading compliance program documentation: developing and maintaining trading-specific compliance policies and procedures; translating regulatory change into updated requirements through a managed regulatory-change process; defining monitoring, surveillance, escalation, and training requirements for the trading business; and communicating and version-controlling the program. It defines trading-program requirements within — never above — the enterprise framework: enterprise-wide compliance policy, legal interpretation, and regulatory legal positions are owned by the enterprise compliance function and Legal &amp; Corporate Communications; the risk-policy framework is owned by risk governance (batches 11-12); this process holds no independent policy-setting authority outside that delegation. Excludes enterprise compliance policy and legal interpretation (enterprise compliance, Legal &amp; Corporate Communications); risk policies and limits frameworks (risk governance, CM-1-2-2-1, CM-1-2-2-3); trading accounting procedures (CM-1-2-4-2-12); executing the monitoring the policies require (CM-1-2-4-3-2/-3/-4).</t>
+        </is>
+      </c>
+      <c r="P179" t="inlineStr">
+        <is>
+          <t>Develop and maintain trading compliance policies and procedures within the enterprise framework | manage regulatory change into program requirements | define monitoring, escalation, and training requirements | communicate and version-control the program</t>
+        </is>
+      </c>
+      <c r="Q179" t="inlineStr">
+        <is>
+          <t>Enterprise compliance policy and legal interpretation (enterprise compliance, Legal &amp; Corporate Communications) | risk-policy frameworks (CM-1-2-2-1, CM-1-2-2-3) | accounting procedures (CM-1-2-4-2-12) | monitoring execution (CM-1-2-4-3-2/-3/-4)</t>
+        </is>
+      </c>
+      <c r="T179" t="inlineStr">
+        <is>
+          <t>Batch 16 (2026-09-20). Trading-program-within-enterprise-framework, parallel to the batch 15 Q4 pattern: this row owns the trading compliance program's documentation under enterprise delegation; enterprise policy and legal interpretation stay above it. APQC 17469 scored STRONG at 3b but NO SOURCE — honored; comparative evidence only.</t>
+        </is>
+      </c>
+      <c r="U179" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V179" s="5" t="inlineStr">
+        <is>
+          <t>Keep the trading compliance program current, complete, and communicated.</t>
+        </is>
+      </c>
+      <c r="W179" s="5" t="inlineStr">
+        <is>
+          <t>SRC-CFTC-P180-001 | SRC-APQC-PCF-001</t>
+        </is>
+      </c>
       <c r="X179" s="5" t="n"/>
-      <c r="Y179" s="5" t="n"/>
-      <c r="Z179" s="5" t="n"/>
-      <c r="AA179" s="5" t="n"/>
-      <c r="AB179" s="5" t="n"/>
-      <c r="AC179" s="5" t="n"/>
+      <c r="Y179" s="5" t="inlineStr">
+        <is>
+          <t>Applicable law, regulation, and market-rule changes | enterprise compliance and legal frameworks | monitoring findings (CM-1-2-4-3-2/-3/-4) and exception patterns (CM-1-2-4-3-7)</t>
+        </is>
+      </c>
+      <c r="Z179" s="5" t="inlineStr">
+        <is>
+          <t>Current, version-controlled trading compliance policies and procedures</t>
+        </is>
+      </c>
+      <c r="AA179" s="5" t="inlineStr">
+        <is>
+          <t>enables: Monitor External Trading Compliance | enables: Monitor Internal Trading Compliance | governed-by: Regulatory &amp; Compliance</t>
+        </is>
+      </c>
+      <c r="AB179" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC179" s="5" t="inlineStr">
+        <is>
+          <t>periodic</t>
+        </is>
+      </c>
       <c r="AD179" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -25143,18 +25252,75 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U180" s="5" t="n"/>
-      <c r="V180" s="5" t="n"/>
-      <c r="W180" s="5" t="n"/>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>Monitor supply and trading activity for compliance with external law, regulation, and market rules — market-conduct and anti-manipulation surveillance, position-limit monitoring, exchange and market-rule adherence, licensing and registration status, and completion of regulatory reporting obligations by their owners — surfacing potential violations for assessment and escalation.</t>
+        </is>
+      </c>
+      <c r="O180" t="inlineStr">
+        <is>
+          <t>Covers external-compliance monitoring for trading: trade and communications surveillance for market conduct under the applicable anti-manipulation and anti-fraud regimes (in the United States, CEA section 6(c) as implemented by 17 CFR Part 180, and the FERC anti-manipulation rule for jurisdictional energy markets; other jurisdictions per their regimes); position-limit and accountability-level monitoring; exchange, clearinghouse, and market-rule adherence; licensing and registration status monitoring; and completion monitoring of regulatory reporting obligations executed by their lifecycle owners (SDR reporting at CM-1-2-1-3-10/CM-1-2-2-2-4, EMTS at CM-1-2-3-1-7) — this process checks that required reporting happened, it does not perform it. Potential violations are assessed and escalated per the compliance procedures; legal determination of liability, regulator interaction on enforcement, and proceedings are owned by Legal &amp; Corporate Communications. Excludes reporting execution (lifecycle owners); legal interpretation and enforcement response (Legal &amp; Corporate Communications); internal-policy monitoring (CM-1-2-4-3-3); control-operation monitoring (CM-1-2-4-3-4).</t>
+        </is>
+      </c>
+      <c r="P180" t="inlineStr">
+        <is>
+          <t>Conduct trade and communications surveillance for market conduct | monitor position limits, market rules, and licensing status | monitor completion of regulatory reporting obligations by their owners | assess and escalate potential violations per procedure</t>
+        </is>
+      </c>
+      <c r="Q180" t="inlineStr">
+        <is>
+          <t>Regulatory reporting execution (CM-1-2-1-3-10, CM-1-2-2-2-4, CM-1-2-3-1-7) | legal interpretation and enforcement response (Legal &amp; Corporate Communications) | internal-policy adherence (CM-1-2-4-3-3) | control-operation monitoring (CM-1-2-4-3-4)</t>
+        </is>
+      </c>
+      <c r="T180" t="inlineStr">
+        <is>
+          <t>Batch 16 (2026-09-20). Monitor-not-execute: reporting obligations are executed by their lifecycle owners (batch 08/10/13 decisions); this process monitors completion. Compliance surveillance detects and escalates; legal interpretation and enforcement response belong to Legal — the surveillance-versus-legal distinction (Hamid, batch 16). Applicable regimes are jurisdiction-specific; 17 CFR Part 180 (CFTC anti-manipulation/anti-fraud) and the FERC anti-manipulation rule (18 CFR 1c) anchor the US context; exchange and market rules are source-specific. Receives the Monitor Contracts exclusion (batch 09). APQC 10935 is a tax-compliance candidate, a false match.</t>
+        </is>
+      </c>
+      <c r="U180" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V180" s="5" t="inlineStr">
+        <is>
+          <t>Detect potential external-compliance violations early and route them to controlled assessment.</t>
+        </is>
+      </c>
+      <c r="W180" s="5" t="inlineStr">
+        <is>
+          <t>SRC-CFTC-P180-001 | SRC-CFTC-P45-001</t>
+        </is>
+      </c>
       <c r="X180" s="5" t="n"/>
-      <c r="Y180" s="5" t="n"/>
-      <c r="Z180" s="5" t="n"/>
-      <c r="AA180" s="5" t="n"/>
-      <c r="AB180" s="5" t="n"/>
-      <c r="AC180" s="5" t="n"/>
+      <c r="Y180" s="5" t="inlineStr">
+        <is>
+          <t>Trade, order, and communications data | position and limit data | regulatory reporting completion evidence | applicable regime requirements (CM-1-2-4-3-1)</t>
+        </is>
+      </c>
+      <c r="Z180" s="5" t="inlineStr">
+        <is>
+          <t>Surveillance results and escalated potential violations with evidence</t>
+        </is>
+      </c>
+      <c r="AA180" s="5" t="inlineStr">
+        <is>
+          <t>governed-by: Develop Compliance Policies &amp; Procedures | informed-by: Trade Capture | triggers: Manage Exceptions</t>
+        </is>
+      </c>
+      <c r="AB180" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC180" s="5" t="inlineStr">
+        <is>
+          <t>continuous</t>
+        </is>
+      </c>
       <c r="AD180" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -25222,18 +25388,75 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U181" s="5" t="n"/>
-      <c r="V181" s="5" t="n"/>
-      <c r="W181" s="5" t="n"/>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>Monitor adherence to the organization's internal trading compliance policies — conduct rules, information barriers, personal-account dealing, gifts and entertainment, communications requirements, and required compliance training — surfacing violations and adverse patterns for assessment and escalation.</t>
+        </is>
+      </c>
+      <c r="O181" t="inlineStr">
+        <is>
+          <t>Covers internal compliance-policy adherence monitoring: checking trading personnel's adherence to the compliance policies maintained under Develop Compliance Policies &amp; Procedures (CM-1-2-4-3-1) — conduct rules, information barriers and need-to-know restrictions, personal-account dealing requirements, gifts and entertainment rules, communications and recordkeeping requirements, training completion, and required declarations and attestations — and escalating violations and adverse patterns per the compliance procedures. The partition with its siblings: external law and market rules are monitored by CM-1-2-4-3-2; the operation of compliance-supporting controls by CM-1-2-4-3-4; the internal market-risk framework by Monitor Risk Policy Compliance (CM-1-2-2-3-10). Excludes external-compliance monitoring (CM-1-2-4-3-2); control-operation monitoring (CM-1-2-4-3-4); risk-framework monitoring (CM-1-2-2-3-10); risk-limit and credit-limit monitoring (CM-1-2-2-3, CM-1-2-2-1); disciplinary action (management, HR); policy authorship (CM-1-2-4-3-1).</t>
+        </is>
+      </c>
+      <c r="P181" t="inlineStr">
+        <is>
+          <t>Monitor adherence to conduct, information-barrier, personal-dealing, and communications policies | monitor required training completion and declarations | detect and escalate violations and adverse patterns | evidence the monitoring performed</t>
+        </is>
+      </c>
+      <c r="Q181" t="inlineStr">
+        <is>
+          <t>External-compliance monitoring (CM-1-2-4-3-2) | control-operation monitoring (CM-1-2-4-3-4) | risk-framework monitoring (CM-1-2-2-3-10) | risk and credit limit monitoring (CM-1-2-2-3, CM-1-2-2-1) | disciplinary action (management, HR) | policy authorship (CM-1-2-4-3-1)</t>
+        </is>
+      </c>
+      <c r="T181" t="inlineStr">
+        <is>
+          <t>Batch 16 (2026-09-20). People-adherence monitor: this row watches whether personnel follow internal compliance policies; CM-1-2-4-3-4 watches whether compliance-supporting controls operate. Receives the Monitor Contracts exclusion (batch 09). APQC 10935 is a tax-compliance candidate, a false match.</t>
+        </is>
+      </c>
+      <c r="U181" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V181" s="5" t="inlineStr">
+        <is>
+          <t>Keep internal compliance-policy adherence visible and violations escalated.</t>
+        </is>
+      </c>
+      <c r="W181" s="5" t="inlineStr">
+        <is>
+          <t>SRC-APQC-PCF-001</t>
+        </is>
+      </c>
       <c r="X181" s="5" t="n"/>
-      <c r="Y181" s="5" t="n"/>
-      <c r="Z181" s="5" t="n"/>
-      <c r="AA181" s="5" t="n"/>
-      <c r="AB181" s="5" t="n"/>
-      <c r="AC181" s="5" t="n"/>
+      <c r="Y181" s="5" t="inlineStr">
+        <is>
+          <t>Compliance policies and requirements (CM-1-2-4-3-1) | personnel activity, communications, and training data per policy | declarations and attestations</t>
+        </is>
+      </c>
+      <c r="Z181" s="5" t="inlineStr">
+        <is>
+          <t>Adherence monitoring results and escalated violations with evidence</t>
+        </is>
+      </c>
+      <c r="AA181" s="5" t="inlineStr">
+        <is>
+          <t>governed-by: Develop Compliance Policies &amp; Procedures | triggers: Manage Exceptions</t>
+        </is>
+      </c>
+      <c r="AB181" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC181" s="5" t="inlineStr">
+        <is>
+          <t>continuous</t>
+        </is>
+      </c>
       <c r="AD181" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -25301,18 +25524,75 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U182" s="5" t="n"/>
-      <c r="V182" s="5" t="n"/>
-      <c r="W182" s="5" t="n"/>
+      <c r="N182" t="inlineStr">
+        <is>
+          <t>Monitor the operation of internally implemented controls that support the organization's external trading obligations — verifying that required deal approvals are evidenced, regulatory reporting controls are complete and functioning, surveillance and recordkeeping controls operate as designed, and audit evidence exists — surfacing control failures and gaps to the accountable owners.</t>
+        </is>
+      </c>
+      <c r="O182" t="inlineStr">
+        <is>
+          <t>Covers compliance-control monitoring: testing and monitoring that internally implemented controls supporting external obligations operate and produce evidence — required pre-trade and deal approvals evidenced in the transaction record, regulatory reporting controls (SDR, EMTS, and registry reporting completeness and error handling by their owners), surveillance and communications-recordkeeping controls, and audit-evidence availability — and escalating control failures, design gaps, and recurring weaknesses to the accountable control owners. Reciprocal boundary per the batch 12/16 decision: this process does not test the internal market-risk framework — risk appetite, approved limits, book mandates, delegation of authority, valuation and risk-control procedures, control-cycle evidence, and risk-exception approvals are monitored by Monitor Risk Policy Compliance (CM-1-2-2-3-10); neither node tests or owns the other's framework, and each may consume information from the other where relevant. Excludes the market-risk framework (CM-1-2-2-3-10, reciprocal exclusion); performing the controls themselves (control owners); external-rule surveillance (CM-1-2-4-3-2); internal-policy adherence (CM-1-2-4-3-3); internal audit's independent assurance (internal audit function).</t>
+        </is>
+      </c>
+      <c r="P182" t="inlineStr">
+        <is>
+          <t>Verify required approvals are evidenced in transaction records | monitor regulatory reporting control completeness and error handling | test surveillance and recordkeeping control operation | escalate control failures and design gaps to accountable owners</t>
+        </is>
+      </c>
+      <c r="Q182" t="inlineStr">
+        <is>
+          <t>Internal market-risk framework monitoring (CM-1-2-2-3-10, reciprocal exclusion) | control execution (control owners) | external-rule surveillance (CM-1-2-4-3-2) | policy-adherence monitoring (CM-1-2-4-3-3) | independent internal audit (internal audit function)</t>
+        </is>
+      </c>
+      <c r="T182" t="inlineStr">
+        <is>
+          <t>Batch 16 (2026-09-20). Batch 12 dependency resolved (Hamid, Option A): this node monitors internally implemented controls supporting external obligations; Monitor Risk Policy Compliance (CM-1-2-2-3-10) monitors the internal market-risk framework; the reciprocal exclusion is recorded on both rows and neither tests the other's framework. Relationship note (Hamid, batch 16): no typed relation to Monitor Risk Policy Compliance is recorded — 'related-to' is not a controlled relationship_type and no defined data dependency exists; the non-hierarchical boundary lives in the scope notes per the conditional-relation precedent (batches 10/13/14). Control-operation monitor, distinct from the people-adherence monitor (CM-1-2-4-3-3). APQC 10735 'Manage internal controls' is a WEAK generic candidate.</t>
+        </is>
+      </c>
+      <c r="U182" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V182" s="5" t="inlineStr">
+        <is>
+          <t>Prove the controls the organization relies on for external obligations actually operate, with failures escalated.</t>
+        </is>
+      </c>
+      <c r="W182" s="5" t="inlineStr">
+        <is>
+          <t>SRC-CFTC-P45-001 | SRC-APQC-PCF-001</t>
+        </is>
+      </c>
       <c r="X182" s="5" t="n"/>
-      <c r="Y182" s="5" t="n"/>
-      <c r="Z182" s="5" t="n"/>
-      <c r="AA182" s="5" t="n"/>
-      <c r="AB182" s="5" t="n"/>
-      <c r="AC182" s="5" t="n"/>
+      <c r="Y182" s="5" t="inlineStr">
+        <is>
+          <t>Control designs and requirements (CM-1-2-4-3-1) | transaction, approval, and reporting evidence from the lifecycle processes | control-owner attestations</t>
+        </is>
+      </c>
+      <c r="Z182" s="5" t="inlineStr">
+        <is>
+          <t>Control-monitoring results with escalated failures and gaps</t>
+        </is>
+      </c>
+      <c r="AA182" s="5" t="inlineStr">
+        <is>
+          <t>governed-by: Develop Compliance Policies &amp; Procedures | triggers: Manage Exceptions</t>
+        </is>
+      </c>
+      <c r="AB182" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC182" s="5" t="inlineStr">
+        <is>
+          <t>continuous</t>
+        </is>
+      </c>
       <c r="AD182" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -25380,18 +25660,75 @@
           <t>strong APQC candidate but no validator agreed</t>
         </is>
       </c>
-      <c r="U183" s="5" t="n"/>
-      <c r="V183" s="5" t="n"/>
-      <c r="W183" s="5" t="n"/>
+      <c r="N183" t="inlineStr">
+        <is>
+          <t>Monitor and assure compliance with transaction- and commodity-tax obligations affecting supply and trading activity by reviewing evidence of registration, licensing, exemption-certificate, filing-calendar, and tax-determination-control compliance; coordinating relevant tax-authority notices and examinations with the enterprise Tax function; and escalating material gaps.</t>
+        </is>
+      </c>
+      <c r="O183" t="inlineStr">
+        <is>
+          <t>Covers tax compliance monitoring and assurance for trading activity: reviewing evidence that licenses and registrations are current, exemption certificates valid, filing calendars met by the accountable filers, and transaction-tax determination controls operating; coordinating responses to tax-authority notices, information requests, and examinations touching trading transactions with the enterprise Tax function and the affected process owners; and escalating material gaps. Consumes status and evidence from the accountable registration, licensing, tax, commercial, and master-data owners; it does not register, license, renew, file, or determine the legal tax position itself. Completes the batch 15 three-way split: transaction-tax accounting execution is owned by Manage Taxes (CM-1-2-4-2-11); tax policy, legal positions, registrations, and return filing by the enterprise Tax function and accountable owners; monitoring and assurance here. Excludes transaction-tax execution (CM-1-2-4-2-11); tax policy, legal positions, registration, licensing, renewal, and return filing (enterprise Tax function and accountable owners); customs and trade compliance where separately owned; income tax (enterprise Tax function).</t>
+        </is>
+      </c>
+      <c r="P183" t="inlineStr">
+        <is>
+          <t>Review evidence of license, registration, and exemption-certificate compliance | monitor filing-calendar adherence by accountable filers | monitor tax determination control operation | coordinate tax-authority notices and examinations with the Tax function and escalate material gaps</t>
+        </is>
+      </c>
+      <c r="Q183" t="inlineStr">
+        <is>
+          <t>Transaction-tax accounting execution (CM-1-2-4-2-11) | tax policy, registration, licensing, renewal, and return filing (enterprise Tax function, accountable owners) | customs and trade compliance (separately owned) | income tax (enterprise Tax function)</t>
+        </is>
+      </c>
+      <c r="T183" t="inlineStr">
+        <is>
+          <t>Batch 16 (2026-09-20). Q4 decision (Hamid): evidence-based monitoring and assurance, completing the batch 15 split (execute at CM-1-2-4-2-11; own policy, registrations, and filing at the Tax function and accountable owners; monitor here) — this process reviews evidence, it does not own the underlying data or renewal activity. Jurisdiction-specific regimes per batch 15; IRS Publication 510 anchors the US federal fuels context. APQC 17467 scored STRONG at 3b but NO SOURCE — honored; comparative evidence only.</t>
+        </is>
+      </c>
+      <c r="U183" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V183" s="5" t="inlineStr">
+        <is>
+          <t>Assure that trading tax obligations are actually being met by their owners, with material gaps escalated.</t>
+        </is>
+      </c>
+      <c r="W183" s="5" t="inlineStr">
+        <is>
+          <t>SRC-IRS-P510-001 | SRC-APQC-PCF-001</t>
+        </is>
+      </c>
       <c r="X183" s="5" t="n"/>
-      <c r="Y183" s="5" t="n"/>
-      <c r="Z183" s="5" t="n"/>
-      <c r="AA183" s="5" t="n"/>
-      <c r="AB183" s="5" t="n"/>
-      <c r="AC183" s="5" t="n"/>
+      <c r="Y183" s="5" t="inlineStr">
+        <is>
+          <t>Status and evidence from accountable registration, licensing, tax, commercial, and master-data owners | filing calendars and completion evidence | tax determination control evidence (CM-1-2-4-2-11) | tax-authority correspondence</t>
+        </is>
+      </c>
+      <c r="Z183" s="5" t="inlineStr">
+        <is>
+          <t>Tax compliance assurance results and coordinated authority responses</t>
+        </is>
+      </c>
+      <c r="AA183" s="5" t="inlineStr">
+        <is>
+          <t>assures: Manage Taxes | informed-by: Develop Compliance Policies &amp; Procedures | triggers: Manage Exceptions</t>
+        </is>
+      </c>
+      <c r="AB183" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC183" s="5" t="inlineStr">
+        <is>
+          <t>periodic</t>
+        </is>
+      </c>
       <c r="AD183" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -25459,18 +25796,75 @@
           <t>strong APQC candidate but no validator agreed</t>
         </is>
       </c>
-      <c r="U184" s="5" t="n"/>
-      <c r="V184" s="5" t="n"/>
-      <c r="W184" s="5" t="n"/>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>Coordinate the trading organization's Renewable Fuel Standard reporting obligations — assembling and quality-assuring RIN transaction, position, and renewable-volume-obligation data from the trading systems and registries, reconciling it to EMTS, and preparing controlled reporting inputs and supporting evidence for the accountable filer — so RFS reports attributable to trading activity are complete, accurate, and evidenced.</t>
+        </is>
+      </c>
+      <c r="O184" t="inlineStr">
+        <is>
+          <t>Covers the trading-side coordination of RFS reporting: assembling RIN generation, separation, trade, retirement, and position data from actualized registry records (Perform RINs/REC Actualization, CM-1-2-3-1-7) and trading systems; reconciling reportable data to EMTS; computing and quality-assuring renewable-volume-obligation inputs; preparing controlled reporting inputs, workpapers, and supporting evidence for the accountable filer; performing operational preparation, data-entry, workflow, or submission-support tasks only where a documented delegation assigns those tasks to the trading organization, while the accountable filer retains filing and attestation accountability; and tracking reporting-calendar completion. Boundary per the EHS &amp; Government Reporting locked rule and the batch 13 Q3 decision: periodic RFS compliance reports, attestations, audit responses, and RVO demonstrations are filed and attested by EHS &amp; Government Reporting (or the formally designated accountable filer per the operating model); per-transaction EMTS submissions are owned by CM-1-2-3-1-7; this process coordinates, assembles, reconciles, and evidences in support of the accountable filer. Program applicability is jurisdiction-specific; this row does not cover REC, LCFS, emissions-allowance, or other environmental-credit reporting programs. Excludes filing, attestation, and submission accountability (EHS &amp; Government Reporting, locked rule); per-transaction EMTS and registry submissions (CM-1-2-3-1-7); instrument settlement (CM-1-2-4-1-8); position forecasting (CM-1-2-1-1-3).</t>
+        </is>
+      </c>
+      <c r="P184" t="inlineStr">
+        <is>
+          <t>Assemble and quality-assure RIN transaction, position, and RVO data | reconcile reportable data to EMTS | prepare controlled reporting inputs and evidence for the accountable filer | perform documented delegated support tasks and track reporting-calendar completion</t>
+        </is>
+      </c>
+      <c r="Q184" t="inlineStr">
+        <is>
+          <t>Filing, attestation, and submission accountability (EHS &amp; Government Reporting, locked rule) | per-transaction EMTS submissions (CM-1-2-3-1-7) | instrument settlement (CM-1-2-4-1-8) | position forecasting (CM-1-2-1-1-3) | REC, LCFS, and other environmental-credit reporting programs (their accountable owners)</t>
+        </is>
+      </c>
+      <c r="T184" t="inlineStr">
+        <is>
+          <t>Batch 16 (2026-09-20). Q3 decision (Hamid, Option A with tightened accountability): controlled-inputs coordination on the batch 11 precedent — this process supports the accountable filer and never becomes the de facto owner of regulatory filing; operational tasks require a documented delegation with the accountable filer retaining filing and attestation accountability; the batch 13 Q3 split (per-transaction EMTS at CM-1-2-3-1-7, periodic compliance at EHS&amp;GR) is preserved exactly. EPA RFS/EMTS sources cover US RIN mechanics only — not internal ownership, delegation of account authority, EHS-versus-trading responsibilities, non-US programs, or other environmental-credit reporting. RFS mechanics per 40 CFR 80 subpart M (EMTS at 80.1452). APQC 10522 scored STRONG at 3b but NO SOURCE — honored; generic reporting candidate.</t>
+        </is>
+      </c>
+      <c r="U184" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V184" s="5" t="inlineStr">
+        <is>
+          <t>Ensure that RFS reporting attributable to trading activity is complete, reconciled, controlled, and evidenced for the accountable filer.</t>
+        </is>
+      </c>
+      <c r="W184" s="5" t="inlineStr">
+        <is>
+          <t>SRC-EPA-RFS-001 | SRC-EPA-EMTS-001</t>
+        </is>
+      </c>
       <c r="X184" s="5" t="n"/>
-      <c r="Y184" s="5" t="n"/>
-      <c r="Z184" s="5" t="n"/>
-      <c r="AA184" s="5" t="n"/>
-      <c r="AB184" s="5" t="n"/>
-      <c r="AC184" s="5" t="n"/>
+      <c r="Y184" s="5" t="inlineStr">
+        <is>
+          <t>Actualized registry events and positions (CM-1-2-3-1-7) | EMTS records | blending and production volumes | RFS reporting calendars and requirements</t>
+        </is>
+      </c>
+      <c r="Z184" s="5" t="inlineStr">
+        <is>
+          <t>Controlled, reconciled RFS reporting inputs and evidence for the accountable filer</t>
+        </is>
+      </c>
+      <c r="AA184" s="5" t="inlineStr">
+        <is>
+          <t>uses-input: Perform RINs/REC Actualization | enables: Monitor External Trading Compliance | governed-by: Develop Compliance Policies &amp; Procedures</t>
+        </is>
+      </c>
+      <c r="AB184" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC184" s="5" t="inlineStr">
+        <is>
+          <t>periodic</t>
+        </is>
+      </c>
       <c r="AD184" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -25538,18 +25932,75 @@
           <t>strong APQC candidate but no validator agreed</t>
         </is>
       </c>
-      <c r="U185" s="5" t="n"/>
-      <c r="V185" s="5" t="n"/>
-      <c r="W185" s="5" t="n"/>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>Manage compliance exceptions through their lifecycle — logging and classifying identified violations, control failures, and approved deviations, assessing severity and regulatory implications, coordinating waiver, remediation-plan, and closure approvals under the documented compliance delegation, tracking remediation to closure, and evidencing the record — so every compliance gap is visibly owned, decided, and closed.</t>
+        </is>
+      </c>
+      <c r="O185" t="inlineStr">
+        <is>
+          <t>Covers the compliance exception lifecycle across the cluster: intake from the monitoring processes (CM-1-2-4-3-2/-3/-4/-5) and self-reports; classification and severity assessment including regulatory-notification implications assessed with Legal; coordination of waiver, remediation-plan, and closure approvals under the documented compliance delegation — the authorized approver may be Compliance leadership, Legal, risk governance, management, or a committee per the delegation, and this process manages the workflow, evidence, and closure rather than approving every waiver itself; remediation planning, tracking, and closure; and pattern analysis feeding policy and control improvement (CM-1-2-4-3-1). Regulatory notification decisions and enforcement interaction are owned by Legal &amp; Corporate Communications; risk-limit and credit exceptions follow their own documented procedures (CM-1-2-2-3, CM-1-2-2-1, batches 11-12); disciplinary action is management and HR. Excludes regulatory notification decisions and legal proceedings (Legal &amp; Corporate Communications); risk and credit exception procedures (CM-1-2-2-1, CM-1-2-2-3); disciplinary action (management, HR); fixing the underlying controls (control owners, tracked here to closure).</t>
+        </is>
+      </c>
+      <c r="P185" t="inlineStr">
+        <is>
+          <t>Log and classify violations, control failures, and deviations | assess severity and regulatory implications with Legal | coordinate waiver, remediation-plan, and closure approvals under the documented delegation | track remediation to evidenced closure and analyze patterns</t>
+        </is>
+      </c>
+      <c r="Q185" t="inlineStr">
+        <is>
+          <t>Regulatory notification and proceedings (Legal &amp; Corporate Communications) | risk and credit exceptions (CM-1-2-2-1, CM-1-2-2-3) | disciplinary action (management, HR) | control remediation execution (control owners)</t>
+        </is>
+      </c>
+      <c r="T185" t="inlineStr">
+        <is>
+          <t>Batch 16 (2026-09-20). Coordinate-not-approve (Hamid, batch 16): this process manages the exception workflow, evidence, and closure; the authorized approver is whoever the documented compliance delegation designates. Compliance-exception lifecycle only: risk-limit exceptions (batch 12) and credit exceptions (batch 11) stay with their documented procedures; the exception partition mirrors the dispute partition discipline (batch 10). Pattern analysis closes the loop to CM-1-2-4-3-1. APQC 20807 scored STRONG at 3b but NO SOURCE — honored; it is an IT-architecture candidate.</t>
+        </is>
+      </c>
+      <c r="U185" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V185" s="5" t="inlineStr">
+        <is>
+          <t>Ensure no compliance gap dies in a log — every one is decided under the right authority, remediated, and evidenced.</t>
+        </is>
+      </c>
+      <c r="W185" s="5" t="inlineStr">
+        <is>
+          <t>SRC-APQC-PCF-001</t>
+        </is>
+      </c>
       <c r="X185" s="5" t="n"/>
-      <c r="Y185" s="5" t="n"/>
-      <c r="Z185" s="5" t="n"/>
-      <c r="AA185" s="5" t="n"/>
-      <c r="AB185" s="5" t="n"/>
-      <c r="AC185" s="5" t="n"/>
+      <c r="Y185" s="5" t="inlineStr">
+        <is>
+          <t>Escalations from the monitoring processes | self-reports | compliance procedures and delegations (CM-1-2-4-3-1)</t>
+        </is>
+      </c>
+      <c r="Z185" s="5" t="inlineStr">
+        <is>
+          <t>Decided, tracked, evidenced compliance exceptions closed through remediation</t>
+        </is>
+      </c>
+      <c r="AA185" s="5" t="inlineStr">
+        <is>
+          <t>follows: Monitor External Trading Compliance | follows: Monitor Internal Trade Controls | enables: Develop Compliance Policies &amp; Procedures</t>
+        </is>
+      </c>
+      <c r="AB185" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC185" s="5" t="inlineStr">
+        <is>
+          <t>event-driven</t>
+        </is>
+      </c>
       <c r="AD185" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -51371,7 +51822,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -53061,6 +53512,53 @@
         </is>
       </c>
       <c r="I41" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>SRC-CFTC-P180-001</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>U.S. Commodity Futures Trading Commission</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>17 CFR Part 180 - Prohibition Against Manipulation (rule 180.1 manipulative and deceptive devices; 180.2 price manipulation; CEA section 6(c) implementation)</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Current regulation; accessed 2026-09-20</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>17 CFR Part 180; https://www.ecfr.gov/current/title-17/chapter-I/part-180</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Regulatory</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>US market-conduct and anti-manipulation surveillance context for CFTC-jurisdictional markets. Does not cover FERC-jurisdictional conduct (18 CFR 1c), exchange-specific rules, or non-US regimes; does not prescribe internal surveillance design or organizational ownership; not a substitute for legal advice or interpretation. Evidence only, not text to copy.</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Market-conduct surveillance context for CM-1-2-4-3 and CM-1-2-4-3-2</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
         <is>
           <t>active</t>
         </is>

--- a/business_architecture/ontology/build/output/step3c-definition-authoring-workbook.xlsx
+++ b/business_architecture/ontology/build/output/step3c-definition-authoring-workbook.xlsx
@@ -26068,18 +26068,80 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U186" s="5" t="n"/>
-      <c r="V186" s="5" t="n"/>
-      <c r="W186" s="5" t="n"/>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t>Manage outbound and inbound claims for demurrage, despatch, detention, and other contractually defined delay or capacity-usage compensation by evaluating verified time, notice, and event evidence under the governing agreement; establishing entitlement or liability; creating, assessing, negotiating, documenting, invoicing, and tracking agreed claims; and escalating unresolved matters through the applicable commercial and legal processes.</t>
+        </is>
+      </c>
+      <c r="O186" t="inlineStr">
+        <is>
+          <t>Covers the two-directional claim lifecycle: identifying potential claims from actualized time, notice, and event facts (Perform Vessel &amp; Barge Actualization, CM-1-2-3-1-4, per the batch 13 handoff); creating, documenting, and pursuing outbound claims; receiving, assessing, and negotiating inbound claims; and preparing and submitting authorized receivable and payment requests through the designated finance processes per the batch 14 payment-authority rule. Under the batch 10 dispute partition, this cluster answers 'was delay or capacity usage compensable'. Includes marine demurrage and despatch under charter parties and contracts of affreightment, and detention or delay/capacity-usage claims only where the governing charter party, terminal agreement, or other commercial agreement treats them as a claim managed through this process; rail car-hire and detention charges settle with Settle Rail (CM-1-2-4-1-13) and truck detention-type accessorials with Settle Trucks (CM-1-2-4-1-4) where their transport agreements govern them, per the batch 14 carve-outs. Claims may be resolved by contractual determination, surveyor or terminal evidence, settlement agreement, credit note, set-off, arbitration, or legal process — not only bilateral negotiation; arbitration and litigation are conducted by Legal &amp; Corporate Communications. Laytime, demurrage, and related terms are calculated under the governing agreement; industry definitions (BIMCO Laytime Definitions for Charter Parties 2013) provide terminology, not contract terms. Excludes freight and voyage-charge settlement (CM-1-2-4-1-5); the underlying time-fact actualization (CM-1-2-3-1-4); confirmation, actualization, and settlement disputes (CM-1-2-2-2-5, CM-1-2-3-1-8, CM-1-2-4-1-17); legal proceedings and arbitration conduct (Legal &amp; Corporate Communications); AR/AP booking and cash application (CM-1-2-4-2-4, CM-1-2-4-2-9); chartering and voyage operations (marine logistics processes).</t>
+        </is>
+      </c>
+      <c r="P186" t="inlineStr">
+        <is>
+          <t>Determine potential claims from actualized time and event facts under governing terms | create, document, and pursue outbound claims | receive, assess, and negotiate inbound claims | prepare and submit authorized receivable and payment requests and track claims to evidenced closure</t>
+        </is>
+      </c>
+      <c r="Q186" t="inlineStr">
+        <is>
+          <t>Freight settlement (CM-1-2-4-1-5) | time-fact actualization (CM-1-2-3-1-4) | rail and truck detention-type charges under transport agreements (CM-1-2-4-1-13, CM-1-2-4-1-4) | other dispute quadrants (CM-1-2-2-2-5, CM-1-2-3-1-8, CM-1-2-4-1-17) | legal proceedings and arbitration (Legal &amp; Corporate Communications) | AR/AP booking and cash application (CM-1-2-4-2)</t>
+        </is>
+      </c>
+      <c r="R186" t="inlineStr">
+        <is>
+          <t>Demurrage &amp; Claims Management | Laytime Claims</t>
+        </is>
+      </c>
+      <c r="T186" t="inlineStr">
+        <is>
+          <t>Batch 17 (2026-09-20). Concept-type: process per the batch 08/13/14 variant test — one claim lifecycle in outbound and inbound directional variants. Dispute-partition placement principle (Hamid, batches 10/17, approved cross-branch): what did the parties agree — Manage Confirm Disputes (CM-1-2-2-2-5); what was delivered, received, measured, or performed — Manage Actualization Disputes (CM-1-2-3-1-8); what is owed, invoiced, received, paid, netted, or applied — Manage Settlement Disputes (CM-1-2-4-1-17); is delay, laytime, capacity usage, detention, demurrage, despatch, or similar compensation payable under the governing agreement — here; what legal remedy, enforcement, arbitration, or litigation applies — Legal &amp; Corporate Communications. A single incident can raise questions in more than one category; the processes exchange evidence and referrals rather than assuming a rigid sequence. Detention guardrail (Q2): demurrage relates to time beyond laytime, despatch to early completion, and detention may arise outside laytime mechanics or under distinct agreements — the contractual wording decides whether a delay charge is demurrage, detention, despatch, an accessorial, or a liquidated-damages claim, and only contract-governed claims route here. Terminology per BIMCO Laytime Definitions 2013 (laytime, demurrage, despatch, Notice of Readiness); the governing charter party controls over any standard definition. APQC 20682 is an unrelated IT candidate.</t>
+        </is>
+      </c>
+      <c r="U186" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V186" s="5" t="inlineStr">
+        <is>
+          <t>Recover and defend delay compensation correctly — no entitlement missed, no invalid claim paid, every claim evidenced.</t>
+        </is>
+      </c>
+      <c r="W186" s="5" t="inlineStr">
+        <is>
+          <t>SRC-BIMCO-LD-001 | SRC-EIA-GLOSS-001</t>
+        </is>
+      </c>
       <c r="X186" s="5" t="n"/>
-      <c r="Y186" s="5" t="n"/>
-      <c r="Z186" s="5" t="n"/>
-      <c r="AA186" s="5" t="n"/>
-      <c r="AB186" s="5" t="n"/>
-      <c r="AC186" s="5" t="n"/>
+      <c r="Y186" s="5" t="inlineStr">
+        <is>
+          <t>Actualized time, notice, and event facts (CM-1-2-3-1-4) | charter party, contract of affreightment, and terminal terms (CM-1-2-1-2-9) | counterparty claims and correspondence</t>
+        </is>
+      </c>
+      <c r="Z186" s="5" t="inlineStr">
+        <is>
+          <t>Resolved demurrage claims — pursued, defended, negotiated, invoiced, and evidenced</t>
+        </is>
+      </c>
+      <c r="AA186" s="5" t="inlineStr">
+        <is>
+          <t>uses-input: Perform Vessel &amp; Barge Actualization | uses-input: Manage Carrier Contracts | precedes: Manage AR/AP &amp; Actuals</t>
+        </is>
+      </c>
+      <c r="AB186" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC186" s="5" t="inlineStr">
+        <is>
+          <t>event-driven</t>
+        </is>
+      </c>
       <c r="AD186" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -26147,18 +26209,75 @@
           <t>strong APQC candidate but no validator agreed</t>
         </is>
       </c>
-      <c r="U187" s="5" t="n"/>
-      <c r="V187" s="5" t="n"/>
-      <c r="W187" s="5" t="n"/>
+      <c r="N187" t="inlineStr">
+        <is>
+          <t>Screen completed voyages and terminal operations for potential demurrage, despatch, and detention entitlements and exposures — comparing used against allowed laytime from actualized notices, statements of fact, and timesheets under the governing terms, computing preliminary claim values in both directions, and identifying the contractual deadlines and evidence needed to preserve or defend each claim — so every potential claim is identified before rights lapse.</t>
+        </is>
+      </c>
+      <c r="O187" t="inlineStr">
+        <is>
+          <t>Covers claim identification: screening completed movements using the actualized time, notice, and event facts (CM-1-2-3-1-4); performing preliminary laytime calculations under the governing charter party, contract, or terminal terms; identifying both outbound entitlements and inbound exposures; identifying relevant contractual notice, documentation, and time-limit requirements and flagging the deadlines and evidence needed to preserve or defend the claim; and routing identified potential claims to creation (outbound, CM-1-2-4-4-2) or anticipating inbound receipt (CM-1-2-4-4-3). Excludes the time-fact actualization itself (CM-1-2-3-1-4); claim creation and pursuit (CM-1-2-4-4-2, -5); inbound assessment (CM-1-2-4-4-4).</t>
+        </is>
+      </c>
+      <c r="P187" t="inlineStr">
+        <is>
+          <t>Screen completed movements against allowed laytime under governing terms | compute preliminary claim values in both directions | identify contractual notice, documentation, and time-limit requirements and flag deadlines and evidence needed | route identified potential claims</t>
+        </is>
+      </c>
+      <c r="Q187" t="inlineStr">
+        <is>
+          <t>Time-fact actualization (CM-1-2-3-1-4) | claim creation and negotiation (CM-1-2-4-4-2, -5) | inbound assessment (CM-1-2-4-4-4)</t>
+        </is>
+      </c>
+      <c r="T187" t="inlineStr">
+        <is>
+          <t>Batch 17 (2026-09-20). Receiving end of the batch 13 handoff: actualization supplies the facts, this process makes the potential-claim determination. Contract-first rule (Hamid, batch 17): notice, documentation, and time-limit requirements vary by agreement and are identified per contract, not assumed uniform. APQC 10188 'Identify potential customers' scored STRONG at 3b but NO SOURCE — honored; false lexical match.</t>
+        </is>
+      </c>
+      <c r="U187" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V187" s="5" t="inlineStr">
+        <is>
+          <t>Catch every compensable delay — in either direction — before claim rights expire.</t>
+        </is>
+      </c>
+      <c r="W187" s="5" t="inlineStr">
+        <is>
+          <t>SRC-BIMCO-LD-001</t>
+        </is>
+      </c>
       <c r="X187" s="5" t="n"/>
-      <c r="Y187" s="5" t="n"/>
-      <c r="Z187" s="5" t="n"/>
-      <c r="AA187" s="5" t="n"/>
-      <c r="AB187" s="5" t="n"/>
-      <c r="AC187" s="5" t="n"/>
+      <c r="Y187" s="5" t="inlineStr">
+        <is>
+          <t>Actualized voyage and terminal time facts (CM-1-2-3-1-4) | governing laytime terms (CM-1-2-1-2-9) | contractual notice and time-limit provisions</t>
+        </is>
+      </c>
+      <c r="Z187" s="5" t="inlineStr">
+        <is>
+          <t>Identified potential claims with preliminary calculations, deadlines, and evidence requirements flagged</t>
+        </is>
+      </c>
+      <c r="AA187" s="5" t="inlineStr">
+        <is>
+          <t>uses-input: Perform Vessel &amp; Barge Actualization | precedes: Create Claim</t>
+        </is>
+      </c>
+      <c r="AB187" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC187" s="5" t="inlineStr">
+        <is>
+          <t>event-driven</t>
+        </is>
+      </c>
       <c r="AD187" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -26226,18 +26345,80 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U188" s="5" t="n"/>
-      <c r="V188" s="5" t="n"/>
-      <c r="W188" s="5" t="n"/>
+      <c r="N188" t="inlineStr">
+        <is>
+          <t>Build outbound demurrage, despatch, and detention claims — performing the definitive laytime calculation under the governing terms, assembling the supporting evidence (notices of readiness, statements of fact, timesheets, port and terminal logs), verifying contractual notice, documentation, and time-limit requirements are met, obtaining the designated internal review, and issuing the claim to the responsible party — so outbound claims are complete, timely, and defensible.</t>
+        </is>
+      </c>
+      <c r="O188" t="inlineStr">
+        <is>
+          <t>Covers outbound claim preparation and issuance: definitive laytime and quantum calculation under the governing charter party, contract, or terminal terms including the exceptions and interruptions the terms allow; evidence assembly; verification of contractual notice, documentation, and time-limit requirements; the designated internal review per the documented delegation, including legal review or privileged advice where required by the governing agreement, claim value, dispute status, or escalation threshold; and formal claim issuance to the counterparty, charterer, terminal, or other responsible party. A missed contractual time limit or required document may prejudice, limit, or bar recovery under the governing agreement; the claim process identifies and escalates such conditions promptly. This process routes legal questions; it does not itself make legal conclusions about enforceability. Excludes identification (CM-1-2-4-4-1); negotiation of the issued claim (CM-1-2-4-4-5); claim invoicing (CM-1-2-4-4-7); inbound claims (CM-1-2-4-4-3/-4/-6/-8); legal opinions (Legal &amp; Corporate Communications).</t>
+        </is>
+      </c>
+      <c r="P188" t="inlineStr">
+        <is>
+          <t>Perform definitive laytime and quantum calculations under governing terms | assemble notices, statements of fact, and supporting evidence | verify contractual notice, documentation, and time-limit compliance and obtain designated review including legal review where required | issue claims to responsible parties</t>
+        </is>
+      </c>
+      <c r="Q188" t="inlineStr">
+        <is>
+          <t>Identification (CM-1-2-4-4-1) | negotiation (CM-1-2-4-4-5) | claim invoicing (CM-1-2-4-4-7) | inbound claims (CM-1-2-4-4-3/-4/-6/-8) | legal opinions (Legal &amp; Corporate Communications)</t>
+        </is>
+      </c>
+      <c r="R188" t="inlineStr">
+        <is>
+          <t>Create Outbound Delay Compensation Claim</t>
+        </is>
+      </c>
+      <c r="T188" t="inlineStr">
+        <is>
+          <t>Batch 17 (2026-09-20). Outbound leg of the two-directional lifecycle (Q3 reading); normalized label 'Create Outbound Delay Compensation Claim' queued for the naming pass. Legal-boundary rule (Hamid, batch 17): high-risk, high-value, or disputed claims route to legal review per threshold; time-limit consequences are contract-specific (may prejudice, limit, or bar recovery), never assumed. APQC 10147 is a budgeting candidate, a false match.</t>
+        </is>
+      </c>
+      <c r="U188" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V188" s="5" t="inlineStr">
+        <is>
+          <t>Issue outbound claims that are complete, timely, and hard to reject.</t>
+        </is>
+      </c>
+      <c r="W188" s="5" t="inlineStr">
+        <is>
+          <t>SRC-BIMCO-LD-001</t>
+        </is>
+      </c>
       <c r="X188" s="5" t="n"/>
-      <c r="Y188" s="5" t="n"/>
-      <c r="Z188" s="5" t="n"/>
-      <c r="AA188" s="5" t="n"/>
-      <c r="AB188" s="5" t="n"/>
-      <c r="AC188" s="5" t="n"/>
+      <c r="Y188" s="5" t="inlineStr">
+        <is>
+          <t>Identified potential claims (CM-1-2-4-4-1) | actualized time facts (CM-1-2-3-1-4) | governing terms and time limits (CM-1-2-1-2-9)</t>
+        </is>
+      </c>
+      <c r="Z188" s="5" t="inlineStr">
+        <is>
+          <t>Issued outbound claims with complete supporting evidence</t>
+        </is>
+      </c>
+      <c r="AA188" s="5" t="inlineStr">
+        <is>
+          <t>follows: Identify Potential Demurrage | precedes: Communicate and Negotiate Claim</t>
+        </is>
+      </c>
+      <c r="AB188" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC188" s="5" t="inlineStr">
+        <is>
+          <t>event-driven</t>
+        </is>
+      </c>
       <c r="AD188" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -26305,18 +26486,80 @@
           <t>strong APQC candidate but no validator agreed</t>
         </is>
       </c>
-      <c r="U189" s="5" t="n"/>
-      <c r="V189" s="5" t="n"/>
-      <c r="W189" s="5" t="n"/>
+      <c r="N189" t="inlineStr">
+        <is>
+          <t>Register inbound demurrage, despatch, and detention claims — logging received claims, acknowledging where the governing terms require, recording receipt-stage time-limit and documentation observations, and routing claims to assessment — so inbound claims enter a controlled process with their receipt-stage observations captured.</t>
+        </is>
+      </c>
+      <c r="O189" t="inlineStr">
+        <is>
+          <t>Covers inbound claim intake: registration and logging of claims received from owners, counterparties, terminals, and other claimants; acknowledgement where contractually required; receipt-stage time-limit and documentation observations recorded and made available for assessment, legal/commercial review, and the response position; and routing to Assess Claim (CM-1-2-4-4-4). Receipt-stage observations inform the response position; their legal effect is assessed downstream, not prejudged at intake. Excludes merit and quantum assessment (CM-1-2-4-4-4); negotiation (CM-1-2-4-4-6); invoice processing (CM-1-2-4-4-8); outbound claims (CM-1-2-4-4-1/-2/-5/-7).</t>
+        </is>
+      </c>
+      <c r="P189" t="inlineStr">
+        <is>
+          <t>Register and log received claims | acknowledge where required | record receipt-stage time-limit and documentation observations for assessment and review | route claims to assessment</t>
+        </is>
+      </c>
+      <c r="Q189" t="inlineStr">
+        <is>
+          <t>Merit and quantum assessment (CM-1-2-4-4-4) | negotiation (CM-1-2-4-4-6) | invoice processing (CM-1-2-4-4-8) | outbound claims (CM-1-2-4-4-1/-2/-5/-7)</t>
+        </is>
+      </c>
+      <c r="R189" t="inlineStr">
+        <is>
+          <t>Receive Inbound Delay Compensation Claim</t>
+        </is>
+      </c>
+      <c r="T189" t="inlineStr">
+        <is>
+          <t>Batch 17 (2026-09-20). Inbound leg intake (Q3 reading); normalized label 'Receive Inbound Delay Compensation Claim' queued. Receipt-stage observations are recorded without prejudging their legal effect (Hamid, batch 17) — assessment and legal/commercial review determine the response position. APQC 20096 'Receive warranty claim' scored STRONG at 3b but NO SOURCE — honored; warranty analogy, comparative only.</t>
+        </is>
+      </c>
+      <c r="U189" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V189" s="5" t="inlineStr">
+        <is>
+          <t>Give every inbound claim a controlled, recorded entry with receipt-stage observations captured at the door.</t>
+        </is>
+      </c>
+      <c r="W189" s="5" t="inlineStr">
+        <is>
+          <t>SRC-BIMCO-LD-001</t>
+        </is>
+      </c>
       <c r="X189" s="5" t="n"/>
-      <c r="Y189" s="5" t="n"/>
-      <c r="Z189" s="5" t="n"/>
-      <c r="AA189" s="5" t="n"/>
-      <c r="AB189" s="5" t="n"/>
-      <c r="AC189" s="5" t="n"/>
+      <c r="Y189" s="5" t="inlineStr">
+        <is>
+          <t>Inbound claims and supporting documents | governing terms and time limits (CM-1-2-1-2-9)</t>
+        </is>
+      </c>
+      <c r="Z189" s="5" t="inlineStr">
+        <is>
+          <t>Registered inbound claims routed to assessment with receipt-stage observations</t>
+        </is>
+      </c>
+      <c r="AA189" s="5" t="inlineStr">
+        <is>
+          <t>precedes: Assess Claim | uses-input: Manage Carrier Contracts</t>
+        </is>
+      </c>
+      <c r="AB189" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC189" s="5" t="inlineStr">
+        <is>
+          <t>event-driven</t>
+        </is>
+      </c>
       <c r="AD189" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -26384,18 +26627,80 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U190" s="5" t="n"/>
-      <c r="V190" s="5" t="n"/>
-      <c r="W190" s="5" t="n"/>
+      <c r="N190" t="inlineStr">
+        <is>
+          <t>Assess the merit and quantum of inbound claims — recalculating laytime independently from the organization's own actualized records under the governing terms, applying contractual exceptions, interruptions, allocation provisions, notices, and responsibility rules as the governing agreement provides, and determining an evidenced accept, counter, or reject position — so inbound claims are paid only to the extent actually owed.</t>
+        </is>
+      </c>
+      <c r="O190" t="inlineStr">
+        <is>
+          <t>Covers inbound claim assessment: independent laytime and quantum recalculation from the organization's own actualized time facts (CM-1-2-3-1-4) rather than the claimant's figures; application of contractual exceptions, interruptions, allocation provisions, notices, and responsibility rules as the governing agreement provides — specific causes such as weather or berth availability have whatever effect the contract gives them, no more; comparison against the claimed amount; and determination of an evidenced accept, counter, or reject position with the designated review per the documented delegation. Where the underlying physical or measurement facts are themselves disputed, the actualization dispute is handled by Manage Actualization Disputes (CM-1-2-3-1-8) per the batch 10 partition. Excludes intake (CM-1-2-4-4-3); negotiation of the position (CM-1-2-4-4-6); physical-fact disputes (CM-1-2-3-1-8); legal opinions (Legal &amp; Corporate Communications).</t>
+        </is>
+      </c>
+      <c r="P190" t="inlineStr">
+        <is>
+          <t>Recalculate laytime and quantum independently from own records | apply contractual exceptions, interruptions, allocation provisions, notices, and responsibility rules as the agreement provides | determine evidenced accept, counter, or reject positions with designated review</t>
+        </is>
+      </c>
+      <c r="Q190" t="inlineStr">
+        <is>
+          <t>Intake (CM-1-2-4-4-3) | negotiation (CM-1-2-4-4-6) | underlying physical-fact disputes (CM-1-2-3-1-8) | legal opinions (Legal &amp; Corporate Communications)</t>
+        </is>
+      </c>
+      <c r="R190" t="inlineStr">
+        <is>
+          <t>Assess Inbound Claim</t>
+        </is>
+      </c>
+      <c r="T190" t="inlineStr">
+        <is>
+          <t>Batch 17 (2026-09-20). Inbound assessment leg (Q3 reading); normalized label 'Assess Inbound Claim' queued. Independent-recalculation discipline mirrors the batch 11 validate-not-accept pattern. Contract-first rule: no cause is automatically exculpatory or compensable — the governing agreement decides. Dispute-partition routing: a disagreement about what physically happened goes to CM-1-2-3-1-8; a disagreement about compensability stays here. APQC 20105 is a claim-closure candidate, comparative only.</t>
+        </is>
+      </c>
+      <c r="U190" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V190" s="5" t="inlineStr">
+        <is>
+          <t>Pay only what is actually owed, on an evidenced recalculation, never on the claimant's arithmetic.</t>
+        </is>
+      </c>
+      <c r="W190" s="5" t="inlineStr">
+        <is>
+          <t>SRC-BIMCO-LD-001</t>
+        </is>
+      </c>
       <c r="X190" s="5" t="n"/>
-      <c r="Y190" s="5" t="n"/>
-      <c r="Z190" s="5" t="n"/>
-      <c r="AA190" s="5" t="n"/>
-      <c r="AB190" s="5" t="n"/>
-      <c r="AC190" s="5" t="n"/>
+      <c r="Y190" s="5" t="inlineStr">
+        <is>
+          <t>Registered inbound claims (CM-1-2-4-4-3) | own actualized time facts (CM-1-2-3-1-4) | governing terms, exceptions, and responsibility rules</t>
+        </is>
+      </c>
+      <c r="Z190" s="5" t="inlineStr">
+        <is>
+          <t>Evidenced accept, counter, or reject positions</t>
+        </is>
+      </c>
+      <c r="AA190" s="5" t="inlineStr">
+        <is>
+          <t>follows: Receive Demurrage Claim | precedes: Validate and Negotiate Claim | informed-by: Perform Vessel &amp; Barge Actualization</t>
+        </is>
+      </c>
+      <c r="AB190" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC190" s="5" t="inlineStr">
+        <is>
+          <t>event-driven</t>
+        </is>
+      </c>
       <c r="AD190" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -26463,18 +26768,80 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U191" s="5" t="n"/>
-      <c r="V191" s="5" t="n"/>
-      <c r="W191" s="5" t="n"/>
+      <c r="N191" t="inlineStr">
+        <is>
+          <t>Pursue issued outbound claims to resolution — presenting the claim and its evidence, responding to counterarguments and counter-calculations, negotiating commercial resolution within delegated claim-settlement authority, obtaining additional approval where a proposed compromise, waiver, credit, set-off, or write-down exceeds that authority, and agreeing resolution or escalating unresolved claims — so outbound entitlements convert to agreed, collectible amounts.</t>
+        </is>
+      </c>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>Covers outbound claim negotiation and resolution: claim presentation and follow-up; evidence exchange and response to counterpositions; negotiation of commercial resolution within the documented delegation of claim-settlement authority, with additional approval obtained where a proposed compromise, waiver, credit, set-off, or write-down exceeds delegated authority — a resolution creating a financial concession routes through Finance or the designated authority; agreement of the settled amount; and escalation of aging, material, or deadlocked claims per procedure. Resolution may also come by contractual determination, surveyor or terminal evidence, settlement agreement, credit note, set-off, arbitration, or legal process; arbitration and litigation are conducted by Legal &amp; Corporate Communications. Time-limit-preserving communications are maintained where negotiation extends near contractual limits. Excludes claim creation (CM-1-2-4-4-2); inbound negotiation (CM-1-2-4-4-6); claim invoicing (CM-1-2-4-4-7); write-off approval beyond delegated authority (Finance/designated authority); arbitration and litigation (Legal &amp; Corporate Communications).</t>
+        </is>
+      </c>
+      <c r="P191" t="inlineStr">
+        <is>
+          <t>Present claims and exchange evidence | respond to counterarguments and counter-calculations | negotiate commercial resolution within delegated authority and obtain additional approval for concessions beyond it | escalate aging, material, or deadlocked claims</t>
+        </is>
+      </c>
+      <c r="Q191" t="inlineStr">
+        <is>
+          <t>Claim creation (CM-1-2-4-4-2) | inbound negotiation (CM-1-2-4-4-6) | claim invoicing (CM-1-2-4-4-7) | write-offs and concessions beyond delegated authority (Finance/designated authority) | arbitration and litigation (Legal &amp; Corporate Communications)</t>
+        </is>
+      </c>
+      <c r="R191" t="inlineStr">
+        <is>
+          <t>Negotiate Outbound Claim</t>
+        </is>
+      </c>
+      <c r="T191" t="inlineStr">
+        <is>
+          <t>Batch 17 (2026-09-20). Outbound negotiation leg (Q3 reading); normalized label 'Negotiate Outbound Claim' queued. Authority limitation (Hamid, batch 17): claim resolution can create a financial concession — compromises, waivers, credits, set-offs, and write-downs beyond the documented delegation require the designated approval; this process never silently owns a Finance write-off or legal settlement authority. Resolution modes extend beyond bilateral negotiation. APQC 10046 'Communicate mission' is an unrelated candidate.</t>
+        </is>
+      </c>
+      <c r="U191" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V191" s="5" t="inlineStr">
+        <is>
+          <t>Convert issued claims into agreed, collectible amounts without surrendering entitled value or exceeding authority.</t>
+        </is>
+      </c>
+      <c r="W191" s="5" t="inlineStr">
+        <is>
+          <t>SRC-BIMCO-LD-001</t>
+        </is>
+      </c>
       <c r="X191" s="5" t="n"/>
-      <c r="Y191" s="5" t="n"/>
-      <c r="Z191" s="5" t="n"/>
-      <c r="AA191" s="5" t="n"/>
-      <c r="AB191" s="5" t="n"/>
-      <c r="AC191" s="5" t="n"/>
+      <c r="Y191" s="5" t="inlineStr">
+        <is>
+          <t>Issued claims and evidence (CM-1-2-4-4-2) | counterparty responses | delegated claim-settlement authority</t>
+        </is>
+      </c>
+      <c r="Z191" s="5" t="inlineStr">
+        <is>
+          <t>Agreed outbound claim resolutions or controlled escalations</t>
+        </is>
+      </c>
+      <c r="AA191" s="5" t="inlineStr">
+        <is>
+          <t>follows: Create Claim | precedes: Send Claim Invoice</t>
+        </is>
+      </c>
+      <c r="AB191" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC191" s="5" t="inlineStr">
+        <is>
+          <t>event-driven</t>
+        </is>
+      </c>
       <c r="AD191" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -26542,18 +26909,80 @@
           <t>strong APQC candidate but no validator agreed</t>
         </is>
       </c>
-      <c r="U192" s="5" t="n"/>
-      <c r="V192" s="5" t="n"/>
-      <c r="W192" s="5" t="n"/>
+      <c r="N192" t="inlineStr">
+        <is>
+          <t>Resolve inbound claims from the assessed position — communicating the assessed position with its evidence, negotiating, accepting, partially accepting, countering, or rejecting the claim within delegated authority, routing concessions, waivers, or formal settlement agreements through the required approval path, and agreeing resolution or escalating unresolved claims — so inbound exposure closes at the evidenced amount, not the claimed one.</t>
+        </is>
+      </c>
+      <c r="O192" t="inlineStr">
+        <is>
+          <t>Covers inbound claim negotiation and resolution: communicating the assessed position (CM-1-2-4-4-4) and its recalculation evidence to the claimant; negotiating, accepting, partially accepting, countering, or rejecting the claim within the documented delegation of claim-settlement authority; routing concessions, waivers, or formal settlement agreements through the required approval path — a resolution creating a financial concession routes through Finance or the designated authority; and escalating material, aging, or deadlocked claims per procedure. Resolution may also come by contractual determination, surveyor or terminal evidence, settlement agreement, credit note, set-off, arbitration, or legal process; arbitration and litigation are conducted by Legal &amp; Corporate Communications. Excludes the assessment itself (CM-1-2-4-4-4); outbound negotiation (CM-1-2-4-4-5); invoice processing (CM-1-2-4-4-8); concessions beyond delegated authority (Finance/designated authority); arbitration and litigation (Legal &amp; Corporate Communications).</t>
+        </is>
+      </c>
+      <c r="P192" t="inlineStr">
+        <is>
+          <t>Communicate assessed positions with evidence | negotiate, accept, partially accept, counter, or reject within delegated authority | route concessions, waivers, and settlement agreements through the required approval path | escalate material or deadlocked claims</t>
+        </is>
+      </c>
+      <c r="Q192" t="inlineStr">
+        <is>
+          <t>Assessment (CM-1-2-4-4-4) | outbound negotiation (CM-1-2-4-4-5) | invoice processing (CM-1-2-4-4-8) | concessions beyond delegated authority (Finance/designated authority) | arbitration and litigation (Legal &amp; Corporate Communications)</t>
+        </is>
+      </c>
+      <c r="R192" t="inlineStr">
+        <is>
+          <t>Validate and Negotiate Inbound Claim</t>
+        </is>
+      </c>
+      <c r="T192" t="inlineStr">
+        <is>
+          <t>Batch 17 (2026-09-20). Inbound negotiation leg (Q3 reading); normalized label 'Validate and Negotiate Inbound Claim' queued. Same authority limitation as the outbound leg: concessions beyond the documented delegation route to the designated approval. APQC 12671 'Validate warranty claim' scored STRONG at 3b but NO SOURCE — honored; warranty analogy, comparative only.</t>
+        </is>
+      </c>
+      <c r="U192" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V192" s="5" t="inlineStr">
+        <is>
+          <t>Close inbound exposure at the evidenced amount, under the right authority.</t>
+        </is>
+      </c>
+      <c r="W192" s="5" t="inlineStr">
+        <is>
+          <t>SRC-BIMCO-LD-001</t>
+        </is>
+      </c>
       <c r="X192" s="5" t="n"/>
-      <c r="Y192" s="5" t="n"/>
-      <c r="Z192" s="5" t="n"/>
-      <c r="AA192" s="5" t="n"/>
-      <c r="AB192" s="5" t="n"/>
-      <c r="AC192" s="5" t="n"/>
+      <c r="Y192" s="5" t="inlineStr">
+        <is>
+          <t>Assessed positions and evidence (CM-1-2-4-4-4) | claimant responses | delegated claim-settlement authority</t>
+        </is>
+      </c>
+      <c r="Z192" s="5" t="inlineStr">
+        <is>
+          <t>Agreed inbound claim resolutions or controlled escalations</t>
+        </is>
+      </c>
+      <c r="AA192" s="5" t="inlineStr">
+        <is>
+          <t>follows: Assess Claim | precedes: Receive Claim Invoice</t>
+        </is>
+      </c>
+      <c r="AB192" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC192" s="5" t="inlineStr">
+        <is>
+          <t>event-driven</t>
+        </is>
+      </c>
       <c r="AD192" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -26621,18 +27050,80 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U193" s="5" t="n"/>
-      <c r="V193" s="5" t="n"/>
-      <c r="W193" s="5" t="n"/>
+      <c r="N193" t="inlineStr">
+        <is>
+          <t>Invoice agreed outbound claims — issuing the claim invoice and settlement statement for the negotiated amount with its supporting calculation, submitting the receivable into the designated finance processes, tracking expected receipt, and obtaining confirmation from Accounting that the receivable is booked and cash applied — so agreed entitlements are collected and evidenced.</t>
+        </is>
+      </c>
+      <c r="O193" t="inlineStr">
+        <is>
+          <t>Covers outbound claim invoicing: generating the claim invoice and supporting settlement statement for the agreed amount; issuing to the paying party; submitting the receivable into the designated finance processes for booking (Manage AR/AP &amp; Actuals, CM-1-2-4-2-4) and receipt application (Manage Cash Application, CM-1-2-4-2-9) per the batch 14 payment-authority rule; tracking expected receipt and coordinating follow-up; obtaining confirmation from Accounting that the receivable has been booked and cash applied; and evidencing closure. A payment disagreement after agreement is a settlement dispute (CM-1-2-4-1-17) per the batch 10 partition. Excludes negotiation (CM-1-2-4-4-5); AR booking and cash application (CM-1-2-4-2-4, CM-1-2-4-2-9); post-agreement payment disputes (CM-1-2-4-1-17).</t>
+        </is>
+      </c>
+      <c r="P193" t="inlineStr">
+        <is>
+          <t>Generate claim invoices and settlement statements for agreed amounts | issue to paying parties and submit receivables to the designated finance processes | track expected receipt and coordinate follow-up | obtain booking and cash-application confirmation from Accounting and evidence closure</t>
+        </is>
+      </c>
+      <c r="Q193" t="inlineStr">
+        <is>
+          <t>Negotiation (CM-1-2-4-4-5) | AR booking and cash application (CM-1-2-4-2-4, CM-1-2-4-2-9) | post-agreement payment disputes (CM-1-2-4-1-17)</t>
+        </is>
+      </c>
+      <c r="R193" t="inlineStr">
+        <is>
+          <t>Invoice Agreed Outbound Claim</t>
+        </is>
+      </c>
+      <c r="T193" t="inlineStr">
+        <is>
+          <t>Batch 17 (2026-09-20). Outbound invoicing leg (Q3 reading); normalized label 'Invoice Agreed Outbound Claim' queued. Batch 14 Q3 rule applied: this process prepares and submits; Accounting books and applies — closure is confirmed by Accounting, not assumed here. Agreed-then-unpaid transitions to the settlement-dispute quadrant. APQC 20105 is a claim-closure candidate, comparative only.</t>
+        </is>
+      </c>
+      <c r="U193" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V193" s="5" t="inlineStr">
+        <is>
+          <t>Collect agreed claim amounts with a complete evidence trail.</t>
+        </is>
+      </c>
+      <c r="W193" s="5" t="inlineStr">
+        <is>
+          <t>SRC-BIMCO-LD-001</t>
+        </is>
+      </c>
       <c r="X193" s="5" t="n"/>
-      <c r="Y193" s="5" t="n"/>
-      <c r="Z193" s="5" t="n"/>
-      <c r="AA193" s="5" t="n"/>
-      <c r="AB193" s="5" t="n"/>
-      <c r="AC193" s="5" t="n"/>
+      <c r="Y193" s="5" t="inlineStr">
+        <is>
+          <t>Agreed resolutions (CM-1-2-4-4-5) | claim calculations and evidence | receivables process references</t>
+        </is>
+      </c>
+      <c r="Z193" s="5" t="inlineStr">
+        <is>
+          <t>Issued claim invoices with tracked receipt and Accounting-confirmed closure</t>
+        </is>
+      </c>
+      <c r="AA193" s="5" t="inlineStr">
+        <is>
+          <t>follows: Communicate and Negotiate Claim | precedes: Manage AR/AP &amp; Actuals</t>
+        </is>
+      </c>
+      <c r="AB193" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC193" s="5" t="inlineStr">
+        <is>
+          <t>event-driven</t>
+        </is>
+      </c>
       <c r="AD193" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -26700,18 +27191,80 @@
           <t>strong APQC candidate but no validator agreed</t>
         </is>
       </c>
-      <c r="U194" s="5" t="n"/>
-      <c r="V194" s="5" t="n"/>
-      <c r="W194" s="5" t="n"/>
+      <c r="N194" t="inlineStr">
+        <is>
+          <t>Process invoices for agreed inbound claims — validating the received invoice against the negotiated resolution and its evidence, preparing and submitting a payment request supported by the agreed resolution and required approvals to the designated Accounts Payable/Treasury process, and evidencing closure — so the organization pays exactly what was agreed, once, with a complete trail.</t>
+        </is>
+      </c>
+      <c r="O194" t="inlineStr">
+        <is>
+          <t>Covers inbound claim invoice processing: validating received claim invoices against the agreed resolution (CM-1-2-4-4-6) and its recalculation evidence; rejecting or querying invoices that do not match the agreement; preparing and submitting a payment request supported by the agreed resolution and required approvals to the designated Accounts Payable/Treasury process per the batch 14 payment-authority rule — the designated payment authority approves and releases payment, not this process; and evidencing closure. Duplicate or mismatched invoicing is surfaced back through negotiation or the settlement-dispute quadrant (CM-1-2-4-1-17). Excludes negotiation (CM-1-2-4-4-6); AP booking, payment approval, and payment execution (CM-1-2-4-2-4, Treasury/banking, designated payment authority); post-agreement disputes (CM-1-2-4-1-17).</t>
+        </is>
+      </c>
+      <c r="P194" t="inlineStr">
+        <is>
+          <t>Validate received invoices against agreed resolutions and evidence | reject or query mismatched invoices | prepare and submit payment requests with required approvals to the designated AP/Treasury process | evidence closure</t>
+        </is>
+      </c>
+      <c r="Q194" t="inlineStr">
+        <is>
+          <t>Negotiation (CM-1-2-4-4-6) | AP booking, payment approval, and payment execution (CM-1-2-4-2-4, Treasury/banking, designated authority) | post-agreement disputes (CM-1-2-4-1-17)</t>
+        </is>
+      </c>
+      <c r="R194" t="inlineStr">
+        <is>
+          <t>Process Invoice for Agreed Inbound Claim</t>
+        </is>
+      </c>
+      <c r="T194" t="inlineStr">
+        <is>
+          <t>Batch 17 (2026-09-20). Inbound invoicing leg (Q3 reading); normalized label 'Process Invoice for Agreed Inbound Claim' queued. Batch 14 Q3 rule applied: this process prepares the request; the designated payment authority approves and releases. Pay-what-was-agreed control: the invoice validates against the negotiated resolution, not the original claim. APQC 20096 scored STRONG at 3b but NO SOURCE — honored; warranty analogy, comparative only.</t>
+        </is>
+      </c>
+      <c r="U194" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V194" s="5" t="inlineStr">
+        <is>
+          <t>Pay agreed inbound claims exactly and once, with the trail to prove it.</t>
+        </is>
+      </c>
+      <c r="W194" s="5" t="inlineStr">
+        <is>
+          <t>SRC-BIMCO-LD-001</t>
+        </is>
+      </c>
       <c r="X194" s="5" t="n"/>
-      <c r="Y194" s="5" t="n"/>
-      <c r="Z194" s="5" t="n"/>
-      <c r="AA194" s="5" t="n"/>
-      <c r="AB194" s="5" t="n"/>
-      <c r="AC194" s="5" t="n"/>
+      <c r="Y194" s="5" t="inlineStr">
+        <is>
+          <t>Agreed resolutions (CM-1-2-4-4-6) | received claim invoices | payables process references</t>
+        </is>
+      </c>
+      <c r="Z194" s="5" t="inlineStr">
+        <is>
+          <t>Validated invoices with submitted, approved payment requests and closure evidence</t>
+        </is>
+      </c>
+      <c r="AA194" s="5" t="inlineStr">
+        <is>
+          <t>follows: Validate and Negotiate Claim | precedes: Manage AR/AP &amp; Actuals</t>
+        </is>
+      </c>
+      <c r="AB194" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC194" s="5" t="inlineStr">
+        <is>
+          <t>event-driven</t>
+        </is>
+      </c>
       <c r="AD194" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -51822,7 +52375,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I42"/>
+  <dimension ref="A1:I43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -53559,6 +54112,53 @@
         </is>
       </c>
       <c r="I42" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>SRC-BIMCO-LD-001</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>BIMCO (with the Baltic Exchange, Comite Maritime International, and FONASBA)</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Laytime Definitions for Charter Parties 2013 (laytime, demurrage, despatch, Notice of Readiness, and related terms)</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2013; accessed 2026-09-20</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>https://www.bimco.org/contractual-affairs/bimco-contracts/contracts/laytime-definitions-for-charter-parties-2013/</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Industry standards body</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Marine laytime and demurrage terminology and concepts. Definitions apply to a transaction only where incorporated into or otherwise applicable under the governing charter party, contract of affreightment, or agreement - the governing contract controls. Not a source for claim quantum, entitlement, legal enforceability, internal process ownership, or non-marine delay-compensation treatment. Evidence only, not text to copy.</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Laytime/demurrage terminology for the CM-1-2-4-4 cluster</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
         <is>
           <t>active</t>
         </is>

--- a/business_architecture/ontology/build/output/step3c-definition-authoring-workbook.xlsx
+++ b/business_architecture/ontology/build/output/step3c-definition-authoring-workbook.xlsx
@@ -27332,18 +27332,80 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U195" s="5" t="n"/>
-      <c r="V195" s="5" t="n"/>
-      <c r="W195" s="5" t="n"/>
+      <c r="N195" t="inlineStr">
+        <is>
+          <t>The capability to keep feedstock selection running on trustworthy quality and economic information — maintaining validated crude and feedstock quality data, reviewing the integrity of the evaluation models that consume it, and developing the quality-screened term and spot procurement slates that feed the feedstock recommendation and trading execution.</t>
+        </is>
+      </c>
+      <c r="O195" t="inlineStr">
+        <is>
+          <t>Covers the feedstock quality-information capability: crude and feedstock assay and quality-data stewardship (CM-1-2-5-1-1); integrity review of the LP and evaluation model representations that consume that data (CM-1-2-5-1-2); and development of the term (CM-1-2-5-1-3) and spot (CM-1-2-5-1-4) procurement slates, quality-screened against refinery capability. Under PTC-002 (Option 1, closed), the binding production slate and run rate are set by Refinery Planning (CM-1-1-4); this cluster's slates are procurement recommendations. Crude and feedstock evaluation — suitability and economic value of individual crudes — is owned by Evaluate Crude &amp; Feedstock (CM-1-1-4-7-2, batch 02). Excludes the binding production slate (CM-1-1-4, PTC-002); crude evaluation conclusions (CM-1-1-4-7-2); trade execution (CM-1-2-1-3); enterprise master-data governance (batch 05 exclusion); laboratory testing operations (Refining/laboratory functions).</t>
+        </is>
+      </c>
+      <c r="P195" t="inlineStr">
+        <is>
+          <t>Steward validated crude and feedstock quality data | review evaluation-model input integrity | develop quality-screened term and spot procurement slates | feed the feedstock recommendation and trading execution</t>
+        </is>
+      </c>
+      <c r="Q195" t="inlineStr">
+        <is>
+          <t>Binding production slate and run rate (CM-1-1-4, PTC-002) | crude evaluation (CM-1-1-4-7-2) | trade execution (CM-1-2-1-3) | enterprise master-data governance (batch 05 exclusion) | laboratory testing (Refining/laboratory)</t>
+        </is>
+      </c>
+      <c r="R195" t="inlineStr">
+        <is>
+          <t>Feedstock Quality &amp; Slate Development</t>
+        </is>
+      </c>
+      <c r="T195" t="inlineStr">
+        <is>
+          <t>Batch 18 (2026-09-20). Concept-type: capability per the batch 11/12/15 test — data stewardship, model review, and slate development are heterogeneous concurrent functions. PTC-002 honored: production slate decided by CM-1-1-4; procurement slates recommended here. The L4 label understates the slate-development content; naming-pass note recorded. APQC: no meaningful candidate.</t>
+        </is>
+      </c>
+      <c r="U195" s="5" t="inlineStr">
+        <is>
+          <t>capability</t>
+        </is>
+      </c>
+      <c r="V195" s="5" t="inlineStr">
+        <is>
+          <t>Make every feedstock decision run on validated quality data, sound models, and quality-screened procurement options.</t>
+        </is>
+      </c>
+      <c r="W195" s="5" t="inlineStr">
+        <is>
+          <t>SRC-DOE-SPRASSAY-001 | SRC-CMU-REFPLAN-001</t>
+        </is>
+      </c>
       <c r="X195" s="5" t="n"/>
-      <c r="Y195" s="5" t="n"/>
-      <c r="Z195" s="5" t="n"/>
-      <c r="AA195" s="5" t="n"/>
-      <c r="AB195" s="5" t="n"/>
-      <c r="AC195" s="5" t="n"/>
+      <c r="Y195" s="5" t="inlineStr">
+        <is>
+          <t>Crude assays and quality data | refinery capability and constraint data (CM-1-1-4) | market availability and pricing</t>
+        </is>
+      </c>
+      <c r="Z195" s="5" t="inlineStr">
+        <is>
+          <t>Validated quality data, model-integrity findings, and term/spot procurement slates</t>
+        </is>
+      </c>
+      <c r="AA195" s="5" t="inlineStr">
+        <is>
+          <t>enables: Plan Optimal Feedstock Slate And Run Rate | informed-by: Evaluate Crude &amp; Feedstock | enables: Coordinate Feedstock Trading</t>
+        </is>
+      </c>
+      <c r="AB195" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC195" s="5" t="inlineStr">
+        <is>
+          <t>continuous</t>
+        </is>
+      </c>
       <c r="AD195" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -27411,18 +27473,75 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U196" s="5" t="n"/>
-      <c r="V196" s="5" t="n"/>
-      <c r="W196" s="5" t="n"/>
+      <c r="N196" t="inlineStr">
+        <is>
+          <t>Steward the crude and feedstock quality data used in evaluation, planning, and trading — maintaining current, validated assays and quality records, tracking assay age and representativeness, incorporating new laboratory and cargo data under controlled update procedures, and distributing consistent quality data to the consuming models and processes.</t>
+        </is>
+      </c>
+      <c r="O196" t="inlineStr">
+        <is>
+          <t>Covers feedstock quality-data stewardship: maintaining the assay and quality-data library used by evaluation (CM-1-1-4-7-2), LP models, slate development, and trading; validating and versioning updates from laboratory analyses, inspection results, and cargo experience; tracking assay currency and representativeness against actual received quality; and controlled distribution so all consumers work from the same data. Laboratory testing itself is performed by Refining and laboratory functions; cargo inspection data arrives through actualization (CM-1-2-3-1); enterprise master-data governance frameworks are excluded per the batch 05 precedent. Excludes laboratory operations (Refining/laboratory); inspection execution (independent inspectors, CM-1-2-3-1 evidence); model structures (CM-1-2-5-1-2 reviews, model owners own); enterprise master-data governance (batch 05 exclusion).</t>
+        </is>
+      </c>
+      <c r="P196" t="inlineStr">
+        <is>
+          <t>Maintain validated, versioned assay and quality records | track assay currency and representativeness against received quality | incorporate laboratory, inspection, and cargo data under controlled updates | distribute consistent quality data to consumers</t>
+        </is>
+      </c>
+      <c r="Q196" t="inlineStr">
+        <is>
+          <t>Laboratory testing (Refining/laboratory) | inspection execution (CM-1-2-3-1 evidence chain) | model ownership (model owners) | enterprise master-data governance (batch 05 exclusion)</t>
+        </is>
+      </c>
+      <c r="T196" t="inlineStr">
+        <is>
+          <t>Batch 18 (2026-09-20). Assay stewardship in the SPR Crude Oil Assay Manual sense: standardized characterization data maintained current and validated for planning and evaluation use; implementation-level work should cite the actual contractual assay clauses, refinery lab standards, inspector procedures, and applicable API/ASTM methods for the specific attribute governed (Hamid, batch 18). The row name's lowercase 'feedstock' is a typographical artifact — corrected capitalization queued for the naming pass. APQC: no meaningful candidate.</t>
+        </is>
+      </c>
+      <c r="U196" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V196" s="5" t="inlineStr">
+        <is>
+          <t>One current, validated set of quality data behind every feedstock decision.</t>
+        </is>
+      </c>
+      <c r="W196" s="5" t="inlineStr">
+        <is>
+          <t>SRC-DOE-SPRASSAY-001 | SRC-API-MPMS-001</t>
+        </is>
+      </c>
       <c r="X196" s="5" t="n"/>
-      <c r="Y196" s="5" t="n"/>
-      <c r="Z196" s="5" t="n"/>
-      <c r="AA196" s="5" t="n"/>
-      <c r="AB196" s="5" t="n"/>
-      <c r="AC196" s="5" t="n"/>
+      <c r="Y196" s="5" t="inlineStr">
+        <is>
+          <t>Laboratory assays and analyses | inspection and cargo quality results (CM-1-2-3-1) | received-quality experience</t>
+        </is>
+      </c>
+      <c r="Z196" s="5" t="inlineStr">
+        <is>
+          <t>Current, validated, versioned feedstock quality data</t>
+        </is>
+      </c>
+      <c r="AA196" s="5" t="inlineStr">
+        <is>
+          <t>enables: Review LP Model Integrity | enables: Develop Term Slate | uses-input: Perform Vessel &amp; Barge Actualization</t>
+        </is>
+      </c>
+      <c r="AB196" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC196" s="5" t="inlineStr">
+        <is>
+          <t>continuous</t>
+        </is>
+      </c>
       <c r="AD196" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -27490,18 +27609,75 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U197" s="5" t="n"/>
-      <c r="V197" s="5" t="n"/>
-      <c r="W197" s="5" t="n"/>
+      <c r="N197" t="inlineStr">
+        <is>
+          <t>Review whether the feedstock data, yield representations, operating constraints, capacities, market assumptions, and other decision inputs used by feedstock-evaluation and planning models remain current, complete, internally consistent, and representative of the refinery and market conditions; document findings and escalate required corrections to accountable data and model owners.</t>
+        </is>
+      </c>
+      <c r="O197" t="inlineStr">
+        <is>
+          <t>Covers input-and-representation integrity review: periodic verification that the LP and evaluation models consuming feedstock data reflect current validated assays (CM-1-2-5-1-1), actual refinery configuration, constraints, and capacities, and current price and market assumptions; back-checking model predictions against actual outcomes where available; documenting findings; and escalating stale, inconsistent, or incomplete representations to the accountable data and model owners for correction. This process does not independently certify model validation, approve model methodology, alter model code, change LP constraints, or approve planning conclusions. Model methodology, structure, and ownership remain with their accountable owners: the refinery planning LP with Refinery Planning (CM-1-1-4) and its tooling; model-methodology approval and independent validation with the applicable model governance and validation functions (batch 12 rule). Excludes model validation certification and methodology approval (model governance/validation functions); model ownership and implementation (model owners, CM-1-1-4); evaluation conclusions (CM-1-1-4-7-2); data stewardship (CM-1-2-5-1-1).</t>
+        </is>
+      </c>
+      <c r="P197" t="inlineStr">
+        <is>
+          <t>Verify model inputs against validated quality data and current configuration | check price and assumption currency | back-check predictions against outcomes where available | document findings and escalate corrections to accountable data and model owners</t>
+        </is>
+      </c>
+      <c r="Q197" t="inlineStr">
+        <is>
+          <t>Model validation certification and methodology approval (model governance/validation) | model ownership, code, and constraints (model owners, CM-1-1-4) | evaluation conclusions (CM-1-1-4-7-2) | data stewardship (CM-1-2-5-1-1)</t>
+        </is>
+      </c>
+      <c r="T197" t="inlineStr">
+        <is>
+          <t>Batch 18 (2026-09-20). Q4 decision (Hamid): fitness-of-representation review distinguished from model ownership, methodology approval, and formal model validation — four responsibilities, four owners (data stewardship at CM-1-2-5-1-1; model architecture with Refinery Planning/designated owner; methodology approval and independent validation with model governance; representation review here). Review-and-escalate, never own (batch 11/12 patterns). LP modeling context per the refinery planning literature. APQC: no meaningful candidate.</t>
+        </is>
+      </c>
+      <c r="U197" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V197" s="5" t="inlineStr">
+        <is>
+          <t>Keep the models behind feedstock decisions honest about the refinery and the market as they are today.</t>
+        </is>
+      </c>
+      <c r="W197" s="5" t="inlineStr">
+        <is>
+          <t>SRC-CMU-REFPLAN-001 | SRC-EIA-LFMM-001</t>
+        </is>
+      </c>
       <c r="X197" s="5" t="n"/>
-      <c r="Y197" s="5" t="n"/>
-      <c r="Z197" s="5" t="n"/>
-      <c r="AA197" s="5" t="n"/>
-      <c r="AB197" s="5" t="n"/>
-      <c r="AC197" s="5" t="n"/>
+      <c r="Y197" s="5" t="inlineStr">
+        <is>
+          <t>Validated quality data (CM-1-2-5-1-1) | refinery configuration and constraint data | model input sets and predictions versus actuals</t>
+        </is>
+      </c>
+      <c r="Z197" s="5" t="inlineStr">
+        <is>
+          <t>Documented model-integrity findings escalated to accountable owners</t>
+        </is>
+      </c>
+      <c r="AA197" s="5" t="inlineStr">
+        <is>
+          <t>uses-input: Manage feedstock Data Quality | enables: Develop Term Slate | informed-by: Refinery Planning</t>
+        </is>
+      </c>
+      <c r="AB197" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC197" s="5" t="inlineStr">
+        <is>
+          <t>periodic</t>
+        </is>
+      </c>
       <c r="AD197" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -27569,18 +27745,75 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U198" s="5" t="n"/>
-      <c r="V198" s="5" t="n"/>
-      <c r="W198" s="5" t="n"/>
+      <c r="N198" t="inlineStr">
+        <is>
+          <t>Develop the recommended term feedstock procurement slate — the portfolio of crudes and feedstocks proposed for supply under agreements with multi-period or continuing commercial commitments, screened for refinery quality compatibility and evaluated for sustained economic attractiveness — so term procurement and the feedstock recommendation rest on a quality-assured base-load supply plan.</t>
+        </is>
+      </c>
+      <c r="O198" t="inlineStr">
+        <is>
+          <t>Covers term procurement-slate development: identifying candidate term supplies, screening them against refinery quality capability using validated data (CM-1-2-5-1-1) and current evaluations (CM-1-1-4-7-2), assessing sustained economic attractiveness and supply reliability, and recommending the term slate that anchors base-load feedstock supply. Term supply means feedstock sourced under an agreement with a multi-period or continuing commercial commitment; the term-versus-spot classification follows the organization's own commercial definitions, not a fixed contractual duration. The output is a procurement recommendation: under PTC-002 the binding production slate is Refinery Planning's (CM-1-1-4), and term-contract negotiation and execution belong to the contract and trading processes (CM-1-2-1-2, CM-1-2-1-3). Excludes the binding production slate (CM-1-1-4, PTC-002); crude evaluation (CM-1-1-4-7-2); contract negotiation and trade execution (CM-1-2-1-2, CM-1-2-1-3); spot procurement (CM-1-2-5-1-4).</t>
+        </is>
+      </c>
+      <c r="P198" t="inlineStr">
+        <is>
+          <t>Identify and screen candidate term supplies against refinery capability | assess sustained economics and supply reliability | recommend the term procurement slate | feed the feedstock recommendation and contract processes</t>
+        </is>
+      </c>
+      <c r="Q198" t="inlineStr">
+        <is>
+          <t>Binding production slate (CM-1-1-4, PTC-002) | crude evaluation (CM-1-1-4-7-2) | contract negotiation and execution (CM-1-2-1-2, CM-1-2-1-3) | spot slate (CM-1-2-5-1-4)</t>
+        </is>
+      </c>
+      <c r="T198" t="inlineStr">
+        <is>
+          <t>Batch 18 (2026-09-20). Q3 decision: 'term slate' read as the term procurement portfolio recommendation — base-load supply anchored by continuing commitments — not the production slate (PTC-002 forecloses that reading). Glossary rule (Hamid, batch 18): term supply is feedstock sourced under an agreement with a multi-period or continuing commercial commitment; spot supply is assessed or acquired for a discrete, near-term market opportunity or short-duration requirement; no fixed duration threshold is assumed — classifications vary by company, market, and contract. Quality screening justifies the Quality Management placement. APQC: no meaningful candidate.</t>
+        </is>
+      </c>
+      <c r="U198" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V198" s="5" t="inlineStr">
+        <is>
+          <t>Anchor base-load feedstock supply on quality-compatible, economically sustained term choices.</t>
+        </is>
+      </c>
+      <c r="W198" s="5" t="inlineStr">
+        <is>
+          <t>SRC-CMU-REFPLAN-001 | SRC-EIA-GLOSS-001</t>
+        </is>
+      </c>
       <c r="X198" s="5" t="n"/>
-      <c r="Y198" s="5" t="n"/>
-      <c r="Z198" s="5" t="n"/>
-      <c r="AA198" s="5" t="n"/>
-      <c r="AB198" s="5" t="n"/>
-      <c r="AC198" s="5" t="n"/>
+      <c r="Y198" s="5" t="inlineStr">
+        <is>
+          <t>Validated quality data (CM-1-2-5-1-1) | crude evaluations (CM-1-1-4-7-2) | feedstock demand (CM-1-2-5-2-2) | market availability and term pricing</t>
+        </is>
+      </c>
+      <c r="Z198" s="5" t="inlineStr">
+        <is>
+          <t>Recommended term procurement slate</t>
+        </is>
+      </c>
+      <c r="AA198" s="5" t="inlineStr">
+        <is>
+          <t>enables: Plan Optimal Feedstock Slate And Run Rate | informed-by: Evaluate Crude &amp; Feedstock | precedes: Create New Contract</t>
+        </is>
+      </c>
+      <c r="AB198" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC198" s="5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AD198" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -27648,18 +27881,75 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U199" s="5" t="n"/>
-      <c r="V199" s="5" t="n"/>
-      <c r="W199" s="5" t="n"/>
+      <c r="N199" t="inlineStr">
+        <is>
+          <t>Develop the recommended spot feedstock procurement slate — the quality-screened spot supply candidates that address residual demand, supply disruption, quality constraints, timing needs, or economic opportunities after considering committed term supply, ranked by current economic attractiveness and availability — so spot procurement decisions start from a vetted, refinery-compatible option set.</t>
+        </is>
+      </c>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t>Covers spot procurement-slate development: quantifying the requirement against current feedstock demand (CM-1-2-5-2-2) and committed term supply, screening available spot cargoes and grades for refinery quality compatibility, ranking candidates on current economics, logistics feasibility, and timing, and recommending the spot slate to the feedstock recommendation and trading processes. Spot supply means feedstock assessed or acquired for a discrete, near-term market opportunity or short-duration requirement — spot purchases may fill residual demand, replace disrupted term supply, resolve quality constraints, optimize economics, or create flexibility. The output is a procurement recommendation: the binding production slate is Refinery Planning's (CM-1-1-4, PTC-002); spot deal negotiation and execution belong to trading (CM-1-2-1-3). Excludes the binding production slate (CM-1-1-4, PTC-002); trade negotiation and execution (CM-1-2-1-3); term slate (CM-1-2-5-1-3); arrival and logistics planning (CM-1-2-5-3).</t>
+        </is>
+      </c>
+      <c r="P199" t="inlineStr">
+        <is>
+          <t>Quantify the spot requirement against demand and committed term supply | screen spot candidates for quality compatibility | rank candidates on economics, logistics feasibility, and timing | recommend the spot slate</t>
+        </is>
+      </c>
+      <c r="Q199" t="inlineStr">
+        <is>
+          <t>Binding production slate (CM-1-1-4, PTC-002) | trade execution (CM-1-2-1-3) | term slate (CM-1-2-5-1-3) | logistics planning (CM-1-2-5-3)</t>
+        </is>
+      </c>
+      <c r="T199" t="inlineStr">
+        <is>
+          <t>Batch 18 (2026-09-20). Q3 decision with Hamid's wording correction: spot is not only deficit-filling — it addresses residual demand, disruption replacement, quality constraints, timing needs, and economic opportunity. Glossary rule per CM-1-2-5-1-3 note: no fixed duration threshold. Faster cadence than the term slate reflects spot market rhythm. APQC: no meaningful candidate.</t>
+        </is>
+      </c>
+      <c r="U199" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V199" s="5" t="inlineStr">
+        <is>
+          <t>Give spot procurement a vetted, ranked, refinery-compatible option set at market speed.</t>
+        </is>
+      </c>
+      <c r="W199" s="5" t="inlineStr">
+        <is>
+          <t>SRC-CMU-REFPLAN-001 | SRC-EIA-GLOSS-001</t>
+        </is>
+      </c>
       <c r="X199" s="5" t="n"/>
-      <c r="Y199" s="5" t="n"/>
-      <c r="Z199" s="5" t="n"/>
-      <c r="AA199" s="5" t="n"/>
-      <c r="AB199" s="5" t="n"/>
-      <c r="AC199" s="5" t="n"/>
+      <c r="Y199" s="5" t="inlineStr">
+        <is>
+          <t>Feedstock demand and committed term supply (CM-1-2-5-2-2, CM-1-2-5-1-3) | validated quality data (CM-1-2-5-1-1) | spot availability and pricing</t>
+        </is>
+      </c>
+      <c r="Z199" s="5" t="inlineStr">
+        <is>
+          <t>Recommended spot procurement slate</t>
+        </is>
+      </c>
+      <c r="AA199" s="5" t="inlineStr">
+        <is>
+          <t>enables: Plan Optimal Feedstock Slate And Run Rate | enables: Coordinate Feedstock Trading | informed-by: Develop Term Slate</t>
+        </is>
+      </c>
+      <c r="AB199" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC199" s="5" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AD199" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -27727,18 +28017,80 @@
           <t>no meaningful APQC candidate</t>
         </is>
       </c>
-      <c r="U200" s="5" t="n"/>
-      <c r="V200" s="5" t="n"/>
-      <c r="W200" s="5" t="n"/>
+      <c r="N200" t="inlineStr">
+        <is>
+          <t>Translate the refinery production plan into feedstock supply action — developing the feedstock demand signal, recommending the economically attractive feedstock slate and run rate to Refinery Planning, and coordinating the resulting requirements with the trading processes — so feedstock supply is planned against a validated demand and an economically informed recommendation.</t>
+        </is>
+      </c>
+      <c r="O200" t="inlineStr">
+        <is>
+          <t>Covers the feedstock demand cycle: developing projected feedstock requirements by grade, quality, quantity, and timing from the production plan (CM-1-2-5-2-2); recommending the economically attractive feedstock slate and run rate to Refinery Planning under PTC-002 (CM-1-2-5-2-3); and coordinating the resulting purchase, sale, and exchange requirements with the trading processes (CM-1-2-5-2-1). Under PTC-002 (Option 1, closed): Refinery Planning decides the binding slate and run rate; this cluster develops demand, recommends, and coordinates — it decides none of the plan. Trading decides the deal (batch 05 decide-versus-advise pattern). Excludes the binding production plan, slate, and run rate (CM-1-1-4, PTC-002); trade negotiation and execution (CM-1-2-1-3); crude evaluation (CM-1-1-4-7-2); procurement slate development (CM-1-2-5-1-3/-4).</t>
+        </is>
+      </c>
+      <c r="P200" t="inlineStr">
+        <is>
+          <t>Develop the feedstock demand signal from the production plan | recommend the economically attractive slate and run rate to Refinery Planning | coordinate resulting requirements with trading | keep demand, recommendation, and coordination consistent</t>
+        </is>
+      </c>
+      <c r="Q200" t="inlineStr">
+        <is>
+          <t>Binding slate, run rate, and production plan (CM-1-1-4, PTC-002) | trade execution (CM-1-2-1-3) | crude evaluation (CM-1-1-4-7-2) | procurement slates (CM-1-2-5-1-3/-4)</t>
+        </is>
+      </c>
+      <c r="R200" t="inlineStr">
+        <is>
+          <t>Feedstock Demand Planning</t>
+        </is>
+      </c>
+      <c r="T200" t="inlineStr">
+        <is>
+          <t>Batch 18 (2026-09-20). Concept-type: process — one demand-to-coordination planning cycle (develop, recommend, coordinate), like the batch 03 Demand Forecasting precedent. PTC-002 honored at cluster level: this cluster advises and coordinates; Refinery Planning decides. APQC: no meaningful candidate.</t>
+        </is>
+      </c>
+      <c r="U200" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V200" s="5" t="inlineStr">
+        <is>
+          <t>Keep feedstock supply planned against a validated demand and an economically informed, advisory recommendation.</t>
+        </is>
+      </c>
+      <c r="W200" s="5" t="inlineStr">
+        <is>
+          <t>SRC-CMU-REFPLAN-001 | SRC-ORP-DPSC-001</t>
+        </is>
+      </c>
       <c r="X200" s="5" t="n"/>
-      <c r="Y200" s="5" t="n"/>
-      <c r="Z200" s="5" t="n"/>
-      <c r="AA200" s="5" t="n"/>
-      <c r="AB200" s="5" t="n"/>
-      <c r="AC200" s="5" t="n"/>
+      <c r="Y200" s="5" t="inlineStr">
+        <is>
+          <t>Refinery production plan (CM-1-1-4) | procurement slates (CM-1-2-5-1-3/-4) | market conditions</t>
+        </is>
+      </c>
+      <c r="Z200" s="5" t="inlineStr">
+        <is>
+          <t>Feedstock demand, slate/run-rate recommendation, and coordinated trading requirements</t>
+        </is>
+      </c>
+      <c r="AA200" s="5" t="inlineStr">
+        <is>
+          <t>informed-by: Refinery Planning | enables: Trading Management | uses-input: Crude/Feed Quality Management</t>
+        </is>
+      </c>
+      <c r="AB200" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC200" s="5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AD200" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -27806,18 +28158,75 @@
           <t>no meaningful APQC candidate</t>
         </is>
       </c>
-      <c r="U201" s="5" t="n"/>
-      <c r="V201" s="5" t="n"/>
-      <c r="W201" s="5" t="n"/>
+      <c r="N201" t="inlineStr">
+        <is>
+          <t>Coordinate feedstock supply requirements with the trading processes — translating demand, slate recommendations, and schedule imbalances into requested purchases, sales, or exchanges with their grade, quality, quantity, timing, and delivery requirements, evaluating proposed trades for plan and schedule fit, and incorporating agreed volumes back into the supply plan.</t>
+        </is>
+      </c>
+      <c r="O201" t="inlineStr">
+        <is>
+          <t>Covers the feedstock-side interface to trading, mirroring Coordinate Product Trading (CM-1-1-3-5-2, batch 05): specifying what the feedstock plan needs — grade, quality, quantity, timing, location, delivery basis; requesting trading action; evaluating proposed deals for refinery compatibility, schedule feasibility, and plan fit; and incorporating agreed volumes into the supply plan and downstream logistics planning (CM-1-2-5-3). Trading decides the deal; planning decides the plan (decide-versus-advise, batch 05); the binding plan is Refinery Planning's (PTC-002). Excludes trade negotiation and execution (CM-1-2-1-3); the binding production plan (CM-1-1-4); transportation arrangement (CM-1-2-5-3-1); exchange agreement administration (CM-1-2-7-1-1).</t>
+        </is>
+      </c>
+      <c r="P201" t="inlineStr">
+        <is>
+          <t>Specify feedstock requirements for trading action | request purchases, sales, or exchanges | evaluate proposed deals for plan, schedule, and refinery fit | incorporate agreed volumes into the supply plan</t>
+        </is>
+      </c>
+      <c r="Q201" t="inlineStr">
+        <is>
+          <t>Trade negotiation and execution (CM-1-2-1-3) | binding production plan (CM-1-1-4) | transportation arrangement (CM-1-2-5-3-1) | exchange agreement administration (CM-1-2-7-1-1)</t>
+        </is>
+      </c>
+      <c r="T201" t="inlineStr">
+        <is>
+          <t>Batch 18 (2026-09-20). Declared feedstock mirror of CM-1-1-3-5-2 (batch 05): this node specifies the need and consumes the result; Supply And Trading owns the trade. Decide-versus-advise pattern applied. APQC: no meaningful candidate.</t>
+        </is>
+      </c>
+      <c r="U201" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V201" s="5" t="inlineStr">
+        <is>
+          <t>Convert feedstock needs into trading requests and trading results into a workable supply plan.</t>
+        </is>
+      </c>
+      <c r="W201" s="5" t="inlineStr">
+        <is>
+          <t>SRC-ORP-DPSC-001</t>
+        </is>
+      </c>
       <c r="X201" s="5" t="n"/>
-      <c r="Y201" s="5" t="n"/>
-      <c r="Z201" s="5" t="n"/>
-      <c r="AA201" s="5" t="n"/>
-      <c r="AB201" s="5" t="n"/>
-      <c r="AC201" s="5" t="n"/>
+      <c r="Y201" s="5" t="inlineStr">
+        <is>
+          <t>Feedstock demand (CM-1-2-5-2-2) | slate recommendations (CM-1-2-5-1-3/-4, CM-1-2-5-2-3) | proposed trades from trading</t>
+        </is>
+      </c>
+      <c r="Z201" s="5" t="inlineStr">
+        <is>
+          <t>Coordinated trading requests and incorporated agreed volumes</t>
+        </is>
+      </c>
+      <c r="AA201" s="5" t="inlineStr">
+        <is>
+          <t>follows: Develop Feedstock Demand | enables: Trade Capture | precedes: Manage Feedstock Transportation</t>
+        </is>
+      </c>
+      <c r="AB201" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC201" s="5" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AD201" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -27885,18 +28294,75 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U202" s="5" t="n"/>
-      <c r="V202" s="5" t="n"/>
-      <c r="W202" s="5" t="n"/>
+      <c r="N202" t="inlineStr">
+        <is>
+          <t>Develop the projected feedstock requirement — quantity, grade, quality, and timing — from the refinery production plan and current inventory and supply positions, maintaining it as plans and positions change, so procurement, slate development, and trading coordination work from one validated demand signal.</t>
+        </is>
+      </c>
+      <c r="O202" t="inlineStr">
+        <is>
+          <t>Covers feedstock demand development: deriving requirements by grade family, quality envelope, quantity, and timing window from the binding production plan (CM-1-1-4) net of committed supply, in-transit volumes, and inventory positions (CM-1-2-5-4-2); maintaining the demand signal through plan revisions; and publishing it to slate development (CM-1-2-5-1-3/-4), the recommendation (CM-1-2-5-2-3), and trading coordination (CM-1-2-5-2-1). The demand derives from the plan; it does not set the plan (PTC-002). Excludes the production plan itself (CM-1-1-4); product demand forecasting (CM-1-2-6-2-3, batch 03 constraint honored); procurement and trading action (CM-1-2-5-2-1, CM-1-2-1-3).</t>
+        </is>
+      </c>
+      <c r="P202" t="inlineStr">
+        <is>
+          <t>Derive feedstock requirements from the production plan net of committed supply and inventory | maintain the demand signal through plan revisions | publish one validated demand to slate development, recommendation, and coordination</t>
+        </is>
+      </c>
+      <c r="Q202" t="inlineStr">
+        <is>
+          <t>Production plan (CM-1-1-4, PTC-002) | product demand forecasting (CM-1-2-6-2-3) | procurement and trading action (CM-1-2-5-2-1, CM-1-2-1-3)</t>
+        </is>
+      </c>
+      <c r="T202" t="inlineStr">
+        <is>
+          <t>Batch 18 (2026-09-20). Derived-not-decided: demand is computed from the binding plan and positions; the plan is Refinery Planning's. APQC: no meaningful candidate.</t>
+        </is>
+      </c>
+      <c r="U202" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V202" s="5" t="inlineStr">
+        <is>
+          <t>One validated feedstock demand signal behind every supply decision.</t>
+        </is>
+      </c>
+      <c r="W202" s="5" t="inlineStr">
+        <is>
+          <t>SRC-CMU-REFPLAN-001 | SRC-ORP-DPSC-001</t>
+        </is>
+      </c>
       <c r="X202" s="5" t="n"/>
-      <c r="Y202" s="5" t="n"/>
-      <c r="Z202" s="5" t="n"/>
-      <c r="AA202" s="5" t="n"/>
-      <c r="AB202" s="5" t="n"/>
-      <c r="AC202" s="5" t="n"/>
+      <c r="Y202" s="5" t="inlineStr">
+        <is>
+          <t>Binding production plan (CM-1-1-4) | committed supply and in-transit volumes | feedstock inventory positions (CM-1-2-5-4-2)</t>
+        </is>
+      </c>
+      <c r="Z202" s="5" t="inlineStr">
+        <is>
+          <t>Validated feedstock demand by grade, quality, quantity, and timing</t>
+        </is>
+      </c>
+      <c r="AA202" s="5" t="inlineStr">
+        <is>
+          <t>uses-input: Refinery Planning | uses-input: Manage Feedstock Inventory | precedes: Coordinate Feedstock Trading</t>
+        </is>
+      </c>
+      <c r="AB202" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC202" s="5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AD202" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -27964,23 +28430,80 @@
           <t>no meaningful APQC candidate</t>
         </is>
       </c>
+      <c r="N203" t="inlineStr">
+        <is>
+          <t>Recommend the economically attractive feedstock slate and run rate to Refinery Planning — combining the demand signal, procurement slates, market prices, and supply economics into a trading-side recommendation that feeds the binding plan without setting it — so the refinery plan is informed by the best current supply-market view.</t>
+        </is>
+      </c>
+      <c r="O203" t="inlineStr">
+        <is>
+          <t>Covers the trading-side slate and run-rate recommendation under PTC-002 (Option 1, closed 2026-09-18): assembling the economically attractive feedstock slate and run-rate case from the demand signal (CM-1-2-5-2-2), term and spot procurement slates (CM-1-2-5-1-3/-4), current market prices and differentials, and supply logistics; submitting the recommendation to Refinery Planning; and iterating as market conditions change. Refinery Planning (CM-1-1-4) decides the binding crude slate and run rate; this process advises and never sets, approves, or revises the plan. Crude evaluation is owned by Evaluate Crude &amp; Feedstock (CM-1-1-4-7-2, batch 02). Excludes the binding slate and run-rate decision (CM-1-1-4, PTC-002); crude evaluation (CM-1-1-4-7-2); procurement slate development (CM-1-2-5-1-3/-4); trade execution (CM-1-2-1-3).</t>
+        </is>
+      </c>
+      <c r="P203" t="inlineStr">
+        <is>
+          <t>Assemble the economically attractive slate and run-rate case from demand, slates, and market economics | submit the recommendation to Refinery Planning | iterate the recommendation as markets move</t>
+        </is>
+      </c>
+      <c r="Q203" t="inlineStr">
+        <is>
+          <t>Binding slate and run-rate decision (CM-1-1-4, PTC-002) | crude evaluation (CM-1-1-4-7-2) | procurement slate development (CM-1-2-5-1-3/-4) | trade execution (CM-1-2-1-3)</t>
+        </is>
+      </c>
+      <c r="R203" t="inlineStr">
+        <is>
+          <t>Recommend Feedstock Slate And Run Rate</t>
+        </is>
+      </c>
       <c r="T203" t="inlineStr">
         <is>
-          <t>Boundary decided by Hamid 2026-09-18, PTC-002 closed with no tree change. Refinery Planning (CM-1-1-4) decides the binding crude slate and run rate; this node advises. Whoever defines this row must scope it as the trading-side recommendation of an economically attractive feedstock slate and run rate feeding the refinery plan, and must not claim the slate or throughput decision. Row left pending: it sits in the Supply And Trading cluster and gets its definition in that batch, not this one.</t>
-        </is>
-      </c>
-      <c r="U203" s="5" t="n"/>
-      <c r="V203" s="5" t="n"/>
-      <c r="W203" s="5" t="n"/>
+          <t>Batch 18 (2026-09-20). PTC-002 implementation (Option 1, Hamid, closed 2026-09-18, quoted): 'Refinery Planning decides; Supply And Trading advises. CM-1-1-4 sets the binding crude slate and run rate. CM-1-2-5-2-3 is the trading-side recommendation of an economically attractive feedstock slate and run rate, feeding the plan without setting it.' The row label overstates the mandate ('Plan Optimal') and, per Hamid's batch 18 direction, the normalized label 'Recommend Feedstock Slate And Run Rate' is strongly queued for the naming pass to protect the PTC-002 decision from later misreading. Decide-versus-advise pattern (PTC-002 is its founding instance). APQC: no meaningful candidate.</t>
+        </is>
+      </c>
+      <c r="U203" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V203" s="5" t="inlineStr">
+        <is>
+          <t>Put the best current supply-market case in front of the planner who decides.</t>
+        </is>
+      </c>
+      <c r="W203" s="5" t="inlineStr">
+        <is>
+          <t>SRC-CMU-REFPLAN-001 | SRC-SNF-REFPS-001</t>
+        </is>
+      </c>
       <c r="X203" s="5" t="n"/>
-      <c r="Y203" s="5" t="n"/>
-      <c r="Z203" s="5" t="n"/>
-      <c r="AA203" s="5" t="n"/>
-      <c r="AB203" s="5" t="n"/>
-      <c r="AC203" s="5" t="n"/>
+      <c r="Y203" s="5" t="inlineStr">
+        <is>
+          <t>Feedstock demand (CM-1-2-5-2-2) | term and spot slates (CM-1-2-5-1-3/-4) | market prices, differentials, and logistics costs</t>
+        </is>
+      </c>
+      <c r="Z203" s="5" t="inlineStr">
+        <is>
+          <t>Trading-side slate and run-rate recommendation to Refinery Planning</t>
+        </is>
+      </c>
+      <c r="AA203" s="5" t="inlineStr">
+        <is>
+          <t>enables: Refinery Planning | uses-input: Develop Feedstock Demand | uses-input: Develop Spot Slate</t>
+        </is>
+      </c>
+      <c r="AB203" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC203" s="5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AD203" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -28048,18 +28571,80 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U204" s="5" t="n"/>
-      <c r="V204" s="5" t="n"/>
-      <c r="W204" s="5" t="n"/>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>Plan and manage the transportation of purchased crude and feedstocks to the refinery — coordinating movements across pipeline, marine, rail, and truck modes against the supply plan, scheduling deliveries into agreed refinery receipt windows, and planning arrivals with the refinery and terminal operations owners — so purchased feedstock arrives when, where, and how the refinery can receive it.</t>
+        </is>
+      </c>
+      <c r="O204" t="inlineStr">
+        <is>
+          <t>Covers feedstock transportation planning: coordinating and monitoring movements for purchased volumes under the applicable carrier and capacity arrangements (CM-1-2-5-3-1); scheduling deliveries into agreed refinery receipt windows (CM-1-2-5-3-2); and planning arrival timing and sequence with the refinery and terminal operations owners (CM-1-2-5-3-3). Operates against carrier contracts administered under Manage Carrier Contracts (CM-1-2-1-2-9) and transportation deals captured under CM-1-2-1-3-9; movement actuals are recorded by Actualizations (CM-1-2-3-1); transportation charges settle under the mode settlement processes (CM-1-2-4-1); delay-compensation claims follow Demurrage Management (CM-1-2-4-4); physical movement execution belongs to carriers and operators. Excludes carrier contracting (CM-1-2-1-2-9); transportation deal capture (CM-1-2-1-3-9); actualization (CM-1-2-3-1); freight settlement and demurrage (CM-1-2-4-1, CM-1-2-4-4); physical movement execution (carriers, operators); product distribution (CM-1-1-3, locked SCM boundary).</t>
+        </is>
+      </c>
+      <c r="P204" t="inlineStr">
+        <is>
+          <t>Coordinate feedstock movements across modes against the supply plan | schedule deliveries into agreed refinery receipt windows | plan arrivals with refinery and terminal operations owners | adjust movements as plans and conditions change</t>
+        </is>
+      </c>
+      <c r="Q204" t="inlineStr">
+        <is>
+          <t>Carrier contracting (CM-1-2-1-2-9) | transportation deal capture (CM-1-2-1-3-9) | actualization (CM-1-2-3-1) | freight settlement and demurrage (CM-1-2-4-1, CM-1-2-4-4) | physical execution (carriers, operators) | product distribution (CM-1-1-3)</t>
+        </is>
+      </c>
+      <c r="R204" t="inlineStr">
+        <is>
+          <t>Feedstock Logistics Planning</t>
+        </is>
+      </c>
+      <c r="T204" t="inlineStr">
+        <is>
+          <t>Batch 18 (2026-09-20). Concept-type: process — one per-movement transport-planning lifecycle (coordinate, schedule, plan arrival), the batch 13 variant test. Inbound-feedstock counterpart of the product-side distribution planning in CM-1-1-3 under the locked SCM boundary. APQC: no meaningful candidate.</t>
+        </is>
+      </c>
+      <c r="U204" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V204" s="5" t="inlineStr">
+        <is>
+          <t>Get purchased feedstock to the refinery gate at the right time, mode, and cost.</t>
+        </is>
+      </c>
+      <c r="W204" s="5" t="inlineStr">
+        <is>
+          <t>SRC-ORP-DPSC-001 | SRC-CMU-REFPLAN-001</t>
+        </is>
+      </c>
       <c r="X204" s="5" t="n"/>
-      <c r="Y204" s="5" t="n"/>
-      <c r="Z204" s="5" t="n"/>
-      <c r="AA204" s="5" t="n"/>
-      <c r="AB204" s="5" t="n"/>
-      <c r="AC204" s="5" t="n"/>
+      <c r="Y204" s="5" t="inlineStr">
+        <is>
+          <t>Agreed purchases and supply plan (CM-1-2-5-2-1) | carrier terms and capacity (CM-1-2-1-2-9) | refinery receipt constraints and tankage positions</t>
+        </is>
+      </c>
+      <c r="Z204" s="5" t="inlineStr">
+        <is>
+          <t>Planned, scheduled feedstock movements and arrival plans</t>
+        </is>
+      </c>
+      <c r="AA204" s="5" t="inlineStr">
+        <is>
+          <t>follows: Coordinate Feedstock Trading | uses-input: Manage Carrier Contracts | precedes: Actualizations</t>
+        </is>
+      </c>
+      <c r="AB204" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC204" s="5" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AD204" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -28127,18 +28712,75 @@
           <t>strong APQC candidate but no validator agreed</t>
         </is>
       </c>
-      <c r="U205" s="5" t="n"/>
-      <c r="V205" s="5" t="n"/>
-      <c r="W205" s="5" t="n"/>
+      <c r="N205" t="inlineStr">
+        <is>
+          <t>Coordinate and monitor the commercial and logistical arrangements required to move agreed feedstock volumes under available carrier contracts, capacity rights, nominations, fixtures, and transport agreements — selecting modes and routings, tracking movement status, and resolving in-transit issues with carriers and operators — so every purchased cargo has a managed path to the refinery.</t>
+        </is>
+      </c>
+      <c r="O205" t="inlineStr">
+        <is>
+          <t>Covers movement coordination and monitoring: mode and routing selection within the supply plan and carrier arrangements; requesting or coordinating nominations, fixtures, bookings, and carrier actions under contracts administered at CM-1-2-1-2-9 and deals captured at CM-1-2-1-3-9; movement status tracking; and in-transit issue resolution with carriers and operators, escalating schedule impacts to CM-1-2-5-3-2/-3. The process may request or coordinate nominations, fixtures, bookings, and carrier actions, but it does not execute charter-party negotiation, carrier contracting, physical transport, refinery discharge operations, or movement actualization. Excludes charter-party negotiation and chartering execution (marine logistics processes); carrier contracting (CM-1-2-1-2-9); delivery scheduling (CM-1-2-5-3-2); arrival planning (CM-1-2-5-3-3); actualization (CM-1-2-3-1).</t>
+        </is>
+      </c>
+      <c r="P205" t="inlineStr">
+        <is>
+          <t>Select modes and routings within the supply plan | request or coordinate nominations, fixtures, bookings, and carrier actions | track movement status | resolve in-transit issues and escalate schedule impacts</t>
+        </is>
+      </c>
+      <c r="Q205" t="inlineStr">
+        <is>
+          <t>Charter-party negotiation and chartering execution (marine logistics) | carrier contracting (CM-1-2-1-2-9) | delivery scheduling (CM-1-2-5-3-2) | arrival planning (CM-1-2-5-3-3) | actualization (CM-1-2-3-1)</t>
+        </is>
+      </c>
+      <c r="T205" t="inlineStr">
+        <is>
+          <t>Batch 18 (2026-09-20). Coordinate-not-execute (Hamid, batch 18): this process requests and coordinates under existing authority; charter negotiation, contracting, physical transport, discharge, and actualization stay with their owners — matching the Trade Capture, Contract Management, and nominations boundaries. Whether it holds authority to request nominations/fixtures directly or only coordinates already-authorized actions is an operating-model follow-up carried in the batch 18 PR. APQC: no meaningful candidate.</t>
+        </is>
+      </c>
+      <c r="U205" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V205" s="5" t="inlineStr">
+        <is>
+          <t>A managed, tracked path to the refinery for every purchased cargo.</t>
+        </is>
+      </c>
+      <c r="W205" s="5" t="inlineStr">
+        <is>
+          <t>SRC-ORP-DPSC-001</t>
+        </is>
+      </c>
       <c r="X205" s="5" t="n"/>
-      <c r="Y205" s="5" t="n"/>
-      <c r="Z205" s="5" t="n"/>
-      <c r="AA205" s="5" t="n"/>
-      <c r="AB205" s="5" t="n"/>
-      <c r="AC205" s="5" t="n"/>
+      <c r="Y205" s="5" t="inlineStr">
+        <is>
+          <t>Agreed purchases (CM-1-2-5-2-1) | carrier contracts and capacity (CM-1-2-1-2-9) | movement status from carriers</t>
+        </is>
+      </c>
+      <c r="Z205" s="5" t="inlineStr">
+        <is>
+          <t>Coordinated, tracked feedstock movements</t>
+        </is>
+      </c>
+      <c r="AA205" s="5" t="inlineStr">
+        <is>
+          <t>follows: Coordinate Feedstock Trading | precedes: Schedule Feedstock Delivery | uses-input: Manage Carrier Contracts</t>
+        </is>
+      </c>
+      <c r="AB205" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC205" s="5" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AD205" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -28206,18 +28848,75 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U206" s="5" t="n"/>
-      <c r="V206" s="5" t="n"/>
-      <c r="W206" s="5" t="n"/>
+      <c r="N206" t="inlineStr">
+        <is>
+          <t>Schedule feedstock deliveries into agreed refinery receipt windows by sequencing confirmed movements against available berth, pipeline-receipt, tankage, quality-segregation, and refinery-receipt constraints, coordinating and confirming proposed receipt windows with the relevant refinery and terminal scheduling and operations owners, and maintaining the delivery schedule as movements and refinery conditions change.</t>
+        </is>
+      </c>
+      <c r="O206" t="inlineStr">
+        <is>
+          <t>Covers delivery scheduling: sequencing coordinated movements (CM-1-2-5-3-1) into agreed refinery receipt windows against berth availability, pipeline receipt capacity, tank space, and quality-segregation needs; coordinating and confirming proposed receipt windows with the relevant refinery/terminal scheduling and operations owners, who retain authority over operational feasibility; and maintaining the schedule under movement delays and refinery changes. Refinery-side unit and tank operations scheduling belongs to Refining and the production-scheduling processes under the approved planning-scheduling-operations hierarchy (batch 06); this process schedules the deliveries, not the refinery. Excludes refinery unit and tank operations scheduling (Refining, CM-1-1-7-2, batch 06 hierarchy); receipt-window operational approval (refinery/terminal operations owners); movement coordination (CM-1-2-5-3-1); arrival planning (CM-1-2-5-3-3); discharge operations (terminal/refinery operators).</t>
+        </is>
+      </c>
+      <c r="P206" t="inlineStr">
+        <is>
+          <t>Sequence confirmed movements into agreed receipt windows against constraints | coordinate and confirm proposed receipt windows with refinery/terminal scheduling and operations owners | maintain the delivery schedule under changes</t>
+        </is>
+      </c>
+      <c r="Q206" t="inlineStr">
+        <is>
+          <t>Refinery operations scheduling (Refining, CM-1-1-7-2) | receipt-window operational approval (refinery/terminal operations owners) | movement coordination (CM-1-2-5-3-1) | arrival planning (CM-1-2-5-3-3) | discharge operations (operators)</t>
+        </is>
+      </c>
+      <c r="T206" t="inlineStr">
+        <is>
+          <t>Batch 18 (2026-09-20). Proposes-and-confirms, does not decide feasibility: refinery/terminal operations owners retain authority over operational receipt feasibility (Hamid, batch 18; batch 06 hierarchy). APQC: no meaningful candidate.</t>
+        </is>
+      </c>
+      <c r="U206" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V206" s="5" t="inlineStr">
+        <is>
+          <t>Deliveries land in windows the refinery has actually agreed it can receive.</t>
+        </is>
+      </c>
+      <c r="W206" s="5" t="inlineStr">
+        <is>
+          <t>SRC-CMU-REFPLAN-001</t>
+        </is>
+      </c>
       <c r="X206" s="5" t="n"/>
-      <c r="Y206" s="5" t="n"/>
-      <c r="Z206" s="5" t="n"/>
-      <c r="AA206" s="5" t="n"/>
-      <c r="AB206" s="5" t="n"/>
-      <c r="AC206" s="5" t="n"/>
+      <c r="Y206" s="5" t="inlineStr">
+        <is>
+          <t>Coordinated movements (CM-1-2-5-3-1) | berth, receipt, and tankage constraints | refinery schedule interfaces (CM-1-1-7-2)</t>
+        </is>
+      </c>
+      <c r="Z206" s="5" t="inlineStr">
+        <is>
+          <t>Confirmed, maintained feedstock delivery schedule</t>
+        </is>
+      </c>
+      <c r="AA206" s="5" t="inlineStr">
+        <is>
+          <t>follows: Manage Feedstock Transportation | precedes: Plan Feedstock Arrival | informed-by: Production Scheduling</t>
+        </is>
+      </c>
+      <c r="AB206" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC206" s="5" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AD206" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -28285,18 +28984,75 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U207" s="5" t="n"/>
-      <c r="V207" s="5" t="n"/>
-      <c r="W207" s="5" t="n"/>
+      <c r="N207" t="inlineStr">
+        <is>
+          <t>Plan individual feedstock arrivals — coordinating laycans, arrival timing, and berth and discharge sequencing with the terminal and refinery, recommending or coordinating proposed tank destinations with refinery/terminal operations subject to their operational authority, and adjusting the arrival plan as vessels, pipelines, and refinery conditions develop — so each arrival is prepared for timely, safe, and quality-compatible receipt, subject to operational conditions and the governing agreements.</t>
+        </is>
+      </c>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>Covers per-arrival planning: coordinating laycan and arrival timing with carriers; planning berth assignment and discharge sequence with terminal and refinery operations; recommending or coordinating proposed tank destinations with refinery/terminal operations, subject to their operational authority over safe discharge, line-up, and receipt feasibility; monitoring approach status and replanning under delay; and providing arrival facts context that downstream actualization and demurrage processes consume. Time, notice, and event facts are recorded at actualization (CM-1-2-3-1-4) and demurrage determination follows CM-1-2-4-4 (batch 17); physical berth and discharge operations belong to terminal and refinery operators. Excludes discharge operations and tank-destination operational decisions (terminal/refinery operators); time-fact actualization (CM-1-2-3-1-4); demurrage claims (CM-1-2-4-4); delivery scheduling (CM-1-2-5-3-2).</t>
+        </is>
+      </c>
+      <c r="P207" t="inlineStr">
+        <is>
+          <t>Coordinate laycans and arrival timing per cargo | plan berth and discharge sequence with operators | recommend or coordinate proposed tank destinations subject to operational authority | monitor approach, replan under delay, and provide arrival context downstream</t>
+        </is>
+      </c>
+      <c r="Q207" t="inlineStr">
+        <is>
+          <t>Discharge operations and tank-destination operational decisions (terminal/refinery operators) | time-fact actualization (CM-1-2-3-1-4) | demurrage claims (CM-1-2-4-4) | delivery scheduling (CM-1-2-5-3-2)</t>
+        </is>
+      </c>
+      <c r="T207" t="inlineStr">
+        <is>
+          <t>Batch 18 (2026-09-20). Prepares-not-guarantees (Hamid, batch 18): weather, congestion, force majeure, and operational constraints sit outside this process; it prepares each arrival for timely, safe, quality-compatible receipt subject to conditions and the governing agreements, and operators keep operational authority (batch 06 boundary). APQC: no meaningful candidate.</t>
+        </is>
+      </c>
+      <c r="U207" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V207" s="5" t="inlineStr">
+        <is>
+          <t>Every arrival prepared for receipt — timed, sequenced, and quality-compatible — under the operators' authority.</t>
+        </is>
+      </c>
+      <c r="W207" s="5" t="inlineStr">
+        <is>
+          <t>SRC-EI-HM32-001</t>
+        </is>
+      </c>
       <c r="X207" s="5" t="n"/>
-      <c r="Y207" s="5" t="n"/>
-      <c r="Z207" s="5" t="n"/>
-      <c r="AA207" s="5" t="n"/>
-      <c r="AB207" s="5" t="n"/>
-      <c r="AC207" s="5" t="n"/>
+      <c r="Y207" s="5" t="inlineStr">
+        <is>
+          <t>Delivery schedule (CM-1-2-5-3-2) | vessel/pipeline approach status | berth, tankage, and segregation constraints</t>
+        </is>
+      </c>
+      <c r="Z207" s="5" t="inlineStr">
+        <is>
+          <t>Per-cargo arrival plans maintained to discharge</t>
+        </is>
+      </c>
+      <c r="AA207" s="5" t="inlineStr">
+        <is>
+          <t>follows: Schedule Feedstock Delivery | enables: Perform Vessel &amp; Barge Actualization | informed-by: Manage Feedstock Inventory</t>
+        </is>
+      </c>
+      <c r="AB207" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC207" s="5" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
       <c r="AD207" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -28359,18 +29115,80 @@
           <t>no meaningful APQC candidate</t>
         </is>
       </c>
-      <c r="U208" s="5" t="n"/>
-      <c r="V208" s="5" t="n"/>
-      <c r="W208" s="5" t="n"/>
+      <c r="N208" t="inlineStr">
+        <is>
+          <t>The capability to keep the feedstock supply position sound — monitoring and controlling feedstock inventory positions against operating requirements, and assessing and managing the price, supply, and working-capital risk those positions carry — so the refinery is supplied without avoidable risk or trapped capital.</t>
+        </is>
+      </c>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>Covers the feedstock supply-position capability: feedstock inventory position monitoring and control (CM-1-2-5-4-2, the feedstock counterpart of the batch 04 finished-products row under its reciprocal constraint) and feedstock inventory risk assessment and management (CM-1-2-5-4-1, the receiving row of the batch 11 Credit Risk exclusion). Inventory policy — including crude and feedstock policy — is owned by the batch 04 policy rows (CM-1-1-3-7-1); reconciliation by CM-1-1-3-7-5; refinery tank operations by Refining. Excludes inventory policy design (CM-1-1-3-7-1); book-to-physical reconciliation (CM-1-1-3-7-5); tank operations (Refining); trading-book market risk measurement (CM-1-2-2-3, batch 12); counterparty credit risk (CM-1-2-2-1).</t>
+        </is>
+      </c>
+      <c r="P208" t="inlineStr">
+        <is>
+          <t>Monitor and control feedstock inventory positions | assess and manage feedstock inventory risk | keep supply-position information current for planning and trading</t>
+        </is>
+      </c>
+      <c r="Q208" t="inlineStr">
+        <is>
+          <t>Inventory policy (CM-1-1-3-7-1) | reconciliation (CM-1-1-3-7-5) | tank operations (Refining) | trading-book risk measurement (CM-1-2-2-3) | counterparty credit (CM-1-2-2-1)</t>
+        </is>
+      </c>
+      <c r="R208" t="inlineStr">
+        <is>
+          <t>Feedstock Supply Position Management</t>
+        </is>
+      </c>
+      <c r="T208" t="inlineStr">
+        <is>
+          <t>Batch 18 (2026-09-20). Concept-type: capability per the batch 11/12/15 test — two concurrent control functions, mirroring the batch 04 Inventory capability precedent. Receiving end of two bindings: the batch 04 reciprocal (finished products/intermediates there, feedstock here) and the batch 11 inventory-risk exclusion. APQC: no meaningful candidate.</t>
+        </is>
+      </c>
+      <c r="U208" s="5" t="inlineStr">
+        <is>
+          <t>capability</t>
+        </is>
+      </c>
+      <c r="V208" s="5" t="inlineStr">
+        <is>
+          <t>A supplied refinery, a controlled position, a bounded risk.</t>
+        </is>
+      </c>
+      <c r="W208" s="5" t="inlineStr">
+        <is>
+          <t>SRC-EI-HM32-001 | SRC-ORP-DPSC-001</t>
+        </is>
+      </c>
       <c r="X208" s="5" t="n"/>
-      <c r="Y208" s="5" t="n"/>
-      <c r="Z208" s="5" t="n"/>
-      <c r="AA208" s="5" t="n"/>
-      <c r="AB208" s="5" t="n"/>
-      <c r="AC208" s="5" t="n"/>
+      <c r="Y208" s="5" t="inlineStr">
+        <is>
+          <t>Feedstock positions, movements, and commitments | market prices | supply plan and demand (CM-1-2-5-2)</t>
+        </is>
+      </c>
+      <c r="Z208" s="5" t="inlineStr">
+        <is>
+          <t>Controlled feedstock positions with assessed, managed risk</t>
+        </is>
+      </c>
+      <c r="AA208" s="5" t="inlineStr">
+        <is>
+          <t>enables: Develop Feedstock Demand | informed-by: Crude/Feed Transportation Management | assures: Crude/Feed Demand Management</t>
+        </is>
+      </c>
+      <c r="AB208" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC208" s="5" t="inlineStr">
+        <is>
+          <t>continuous</t>
+        </is>
+      </c>
       <c r="AD208" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -28433,18 +29251,75 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U209" s="5" t="n"/>
-      <c r="V209" s="5" t="n"/>
-      <c r="W209" s="5" t="n"/>
+      <c r="N209" t="inlineStr">
+        <is>
+          <t>Assess the price, supply-availability, disruption, quality, concentration, and working-capital risk associated with feedstock inventory positions; recommend inventory, supply, operational, and hedging mitigations to accountable owners; and submit approved hedging requirements to the authorized trading process so risk is visible, understood, and managed within approved appetite.</t>
+        </is>
+      </c>
+      <c r="O209" t="inlineStr">
+        <is>
+          <t>Covers feedstock inventory risk: assessing price exposure from inventory valuation and forward prices; supply and disruption risk from delayed cargoes, outages, unavailable grades, or constrained logistics; quality and segregation risk from off-spec, incompatible, or constrained positioning; concentration risk from excessive exposure to one grade, source, geography, supplier, route, or facility; and working-capital risk from inventory value, dwell time, and cash tied up in stock; recommending inventory, supply, operational, and hedging mitigations to the accountable owners; and submitting approved hedging requirements or mitigation requests to the authorized trading process — Trading Strategy Management, Trade Approval, and Trade Capture govern strategy, authorization, and execution (batches 07-08). Receiving row of the batch 11 exclusion: inventory risk here, counterparty credit risk at CM-1-2-2-1. Boundary with Market Risk (batch 12): once a hedge or position is booked into the trading book, its measurement, limits, and P&amp;L belong to Market Risk Management (CM-1-2-2-3); non-trading inventory exposure is assessed here. Risk appetite, limit approval, and risk-measurement methodology remain with risk governance (batches 11-12). Excludes hedge strategy, authorization, and execution (CM-1-2-1-4, CM-1-2-1-3); trading-book measurement (CM-1-2-2-3, batch 12 rule); counterparty credit (CM-1-2-2-1); risk-appetite, limit, and methodology approval (risk governance); inventory policy (CM-1-1-3-7-1).</t>
+        </is>
+      </c>
+      <c r="P209" t="inlineStr">
+        <is>
+          <t>Assess price, supply, disruption, quality, concentration, and working-capital risk of feedstock positions | recommend inventory, supply, operational, and hedging mitigations to accountable owners | submit approved hedging requirements to the authorized trading process | keep inventory risk visible against requirements</t>
+        </is>
+      </c>
+      <c r="Q209" t="inlineStr">
+        <is>
+          <t>Hedge strategy, authorization, and execution (CM-1-2-1-4, CM-1-2-1-3) | trading-book risk measurement (CM-1-2-2-3) | counterparty credit (CM-1-2-2-1) | risk-appetite, limit, and methodology approval (risk governance) | inventory policy (CM-1-1-3-7-1)</t>
+        </is>
+      </c>
+      <c r="T209" t="inlineStr">
+        <is>
+          <t>Batch 18 (2026-09-20). Q5 decision (Hamid): receiving row of the batch 11 exclusion; request-not-initiate — this process submits approved hedging requirements to the authorized trading process; Trading Strategy Management, Trade Approval, and Trade Capture govern strategy, authorization, and execution (batch 07/08 chain); booked hedges are measured by Market Risk (batch 12 rule). Risk categories are illustrative, not a mandated metric set — measurement methodology is governance-controlled and company-specific. APQC: no meaningful candidate.</t>
+        </is>
+      </c>
+      <c r="U209" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V209" s="5" t="inlineStr">
+        <is>
+          <t>No feedstock inventory risk that nobody has measured, owned, and decided to carry.</t>
+        </is>
+      </c>
+      <c r="W209" s="5" t="inlineStr">
+        <is>
+          <t>SRC-ORP-DPSC-001 | SRC-CCRO-002A</t>
+        </is>
+      </c>
       <c r="X209" s="5" t="n"/>
-      <c r="Y209" s="5" t="n"/>
-      <c r="Z209" s="5" t="n"/>
-      <c r="AA209" s="5" t="n"/>
-      <c r="AB209" s="5" t="n"/>
-      <c r="AC209" s="5" t="n"/>
+      <c r="Y209" s="5" t="inlineStr">
+        <is>
+          <t>Feedstock positions (CM-1-2-5-4-2) | market prices and forward curves | refinery requirements (CM-1-2-5-2-2) | working-capital parameters</t>
+        </is>
+      </c>
+      <c r="Z209" s="5" t="inlineStr">
+        <is>
+          <t>Assessed inventory risk with recommended mitigations and submitted hedging requirements</t>
+        </is>
+      </c>
+      <c r="AA209" s="5" t="inlineStr">
+        <is>
+          <t>uses-input: Manage Feedstock Inventory | enables: Trading Management | informed-by: Market Risk Management</t>
+        </is>
+      </c>
+      <c r="AB209" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC209" s="5" t="inlineStr">
+        <is>
+          <t>continuous</t>
+        </is>
+      </c>
       <c r="AD209" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -28507,23 +29382,75 @@
           <t>strong APQC candidate but no validator agreed</t>
         </is>
       </c>
+      <c r="N210" t="inlineStr">
+        <is>
+          <t>Monitor and control actual and projected crude and feedstock inventory positions — identifying operating-limit, availability, quality, location, and balance exceptions against refinery requirements and the supply plan, coordinating timely response, and providing reliable current-position information to planning, trading, and logistics.</t>
+        </is>
+      </c>
+      <c r="O210" t="inlineStr">
+        <is>
+          <t>Covers feedstock position stewardship, the feedstock counterpart of Manage Inventory (CM-1-1-3-7-12) under the batch 04 reciprocal constraint: recurring review of physical and book feedstock positions, movements, in-transit volumes, and commitments; minimum, maximum, safety-stock, and operating-limit exceptions against refinery run requirements; short-term availability and quality-segregation risks; escalation and coordination of corrective actions through the accountable owners; and maintenance of the position view that demand development (CM-1-2-5-2-2), arrival planning (CM-1-2-5-3-3), and inventory risk (CM-1-2-5-4-1) consume. Excludes inventory policy design (CM-1-1-3-7-1); measurement methodology (CM-1-1-3-7-4); book-to-physical reconciliation (CM-1-1-3-7-5); finished-product and intermediates positions (CM-1-1-3-7-12, batch 04 reciprocal); tank operations (Refining); feedstock sourcing, purchase, exchange, and replenishment decision rights, which belong to the applicable supply-planning, Refinery Planning, and authorized trading processes.</t>
+        </is>
+      </c>
+      <c r="P210" t="inlineStr">
+        <is>
+          <t>Monitor physical, book, and in-transit feedstock positions against requirements | identify and escalate operating-limit, availability, and quality exceptions | coordinate corrective action through accountable owners | maintain the current-position view for planning, trading, and logistics</t>
+        </is>
+      </c>
+      <c r="Q210" t="inlineStr">
+        <is>
+          <t>Inventory policy (CM-1-1-3-7-1) | measurement methodology (CM-1-1-3-7-4) | reconciliation (CM-1-1-3-7-5) | finished-product/intermediates positions (CM-1-1-3-7-12) | tank operations (Refining) | sourcing, purchase, exchange, and replenishment decisions (supply-planning, Refinery Planning, and authorized trading processes)</t>
+        </is>
+      </c>
       <c r="T210" t="inlineStr">
         <is>
-          <t>Batch 04 (2026-09-19), binding constraint recorded per Hamid's Q3 decision, reciprocal to CM-1-1-3-7: the future definition of this node must be limited to crude-oil and refinery-feedstock inventory positions, availability, operating constraints, and supply/refinery coordination. It must not claim enterprise ownership of inventory policy, measurement standards, formal reconciliation, generic replenishment, or the management of finished-product and intermediate inventory positions — those sit in the Inventory cluster (CM-1-1-3-7). Row remains pending; it belongs to the Supply And Trading batch.</t>
-        </is>
-      </c>
-      <c r="U210" s="5" t="n"/>
-      <c r="V210" s="5" t="n"/>
-      <c r="W210" s="5" t="n"/>
+          <t>Batch 18 (2026-09-20). Receiving row of the batch 04 reciprocal: CM-1-1-3-7-12 holds finished products and intermediates so this row holds feedstock — the mirrored wording is deliberate. Identifies-and-escalates: feedstock sourcing, purchase, exchange, and replenishment decision rights belong to the applicable supply-planning, Refinery Planning, and authorized trading processes (Hamid, batch 18) — replenishment stays aligned to the binding Refinery Plan, never independent of it. EI HM 32 daily stock-control practice context. APQC: no meaningful candidate.</t>
+        </is>
+      </c>
+      <c r="U210" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V210" s="5" t="inlineStr">
+        <is>
+          <t>A current, reliable feedstock position with every exception owned and answered.</t>
+        </is>
+      </c>
+      <c r="W210" s="5" t="inlineStr">
+        <is>
+          <t>SRC-EI-HM32-001 | SRC-API-MPMS-001</t>
+        </is>
+      </c>
       <c r="X210" s="5" t="n"/>
-      <c r="Y210" s="5" t="n"/>
-      <c r="Z210" s="5" t="n"/>
-      <c r="AA210" s="5" t="n"/>
-      <c r="AB210" s="5" t="n"/>
-      <c r="AC210" s="5" t="n"/>
+      <c r="Y210" s="5" t="inlineStr">
+        <is>
+          <t>Tank gaugings and book positions | in-transit movements (CM-1-2-5-3) | refinery run requirements | commitments and receipts</t>
+        </is>
+      </c>
+      <c r="Z210" s="5" t="inlineStr">
+        <is>
+          <t>Controlled feedstock position view with escalated exceptions</t>
+        </is>
+      </c>
+      <c r="AA210" s="5" t="inlineStr">
+        <is>
+          <t>enables: Develop Feedstock Demand | enables: Assess &amp; Manage Inventory Risk | informed-by: Crude/Feed Transportation Management</t>
+        </is>
+      </c>
+      <c r="AB210" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC210" s="5" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
       <c r="AD210" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -52375,7 +53302,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:I44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -52424,7 +53351,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
@@ -54159,6 +55085,53 @@
         </is>
       </c>
       <c r="I43" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>SRC-DOE-SPRASSAY-001</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>U.S. Department of Energy, Strategic Petroleum Reserve</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Crude Oil Assay Manual (5th Edition) - standardized crude oil assay characterization and test-method framework</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>5th ed.; accessed 2026-09-20</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>https://www.spr.doe.gov/reports/docs/crudeoilassaymanual.pdf</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Government authority</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Crude assay content, characterization structure, and test-method context. SPR procedures do not establish the enterprise's assay-governance process, quality-data ownership, refinery-model approach, commercial assay convention, or contract-quality terms; implementation-level work cites contractual assay clauses, refinery lab standards, inspector procedures, and applicable API/ASTM methods. Evidence only, not text to copy.</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Crude assay characterization context for CM-1-2-5-1-1 and the Quality Management cluster</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
         <is>
           <t>active</t>
         </is>

--- a/business_architecture/ontology/build/output/step3c-definition-authoring-workbook.xlsx
+++ b/business_architecture/ontology/build/output/step3c-definition-authoring-workbook.xlsx
@@ -29518,18 +29518,80 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U211" s="5" t="n"/>
-      <c r="V211" s="5" t="n"/>
-      <c r="W211" s="5" t="n"/>
+      <c r="N211" t="inlineStr">
+        <is>
+          <t>Analyze the refined-product supply network's market participation — segmenting customers and markets on supply economics, evaluating market attractiveness for supply-network participation, and assessing cost-to-serve performance — and recommend where and whom the network should serve profitably, informing the network and participation decisions of the accountable commercial and planning owners.</t>
+        </is>
+      </c>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t>Covers the market-participation analysis cycle: supply-economics customer and market segmentation (CM-1-2-6-1-1), market attractiveness evaluation (CM-1-2-6-1-2), and cost-to-serve assessment (CM-1-2-6-1-3), combined into recommendations on network participation, service levels, and supply-envelope choices. Analyze-and-recommend (batch 11 pattern): supply, production, inventory, and allocation decisions are owned by Regional Optimization (CM-1-1-2, batch 03 rule); commercial and brand segmentation, pricing, and customer strategy by the Marketing processes (CM-1-3) where defined; network-investment decisions by their accountable owners. Excludes supply and allocation decisions (CM-1-1-2); commercial segmentation, pricing, and customer strategy (CM-1-3); network investment decisions (accountable owners); demand forecasting (CM-1-2-6-2-3, CM-1-1-1-1).</t>
+        </is>
+      </c>
+      <c r="P211" t="inlineStr">
+        <is>
+          <t>Segment customers and markets on supply economics | evaluate market attractiveness for supply-network participation | assess cost-to-serve performance | recommend network participation and service choices to accountable owners</t>
+        </is>
+      </c>
+      <c r="Q211" t="inlineStr">
+        <is>
+          <t>Supply and allocation decisions (CM-1-1-2) | commercial segmentation, pricing, and customer strategy (CM-1-3) | network investment decisions (accountable owners) | demand forecasting (CM-1-2-6-2-3, CM-1-1-1-1)</t>
+        </is>
+      </c>
+      <c r="R211" t="inlineStr">
+        <is>
+          <t>Supply Network Participation Analysis</t>
+        </is>
+      </c>
+      <c r="T211" t="inlineStr">
+        <is>
+          <t>Batch 19 (2026-09-20). Concept-type: process — one periodic analysis cycle (segment, evaluate, assess, recommend). Q5 decision: supply-economics analysis, distinct from Marketing's commercial segmentation; analyze-and-recommend with decisions at the accountable owners. Normalized label 'Supply Network Participation Analysis' queued — the current label sounds like network design/operations ownership (Hamid, batch 19). APQC candidates are WEAK generic matches.</t>
+        </is>
+      </c>
+      <c r="U211" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V211" s="5" t="inlineStr">
+        <is>
+          <t>Know which markets and customers the supply network serves profitably — and recommend accordingly.</t>
+        </is>
+      </c>
+      <c r="W211" s="5" t="inlineStr">
+        <is>
+          <t>SRC-LNL-T2S-001 | SRC-ORP-DPSC-001</t>
+        </is>
+      </c>
       <c r="X211" s="5" t="n"/>
-      <c r="Y211" s="5" t="n"/>
-      <c r="Z211" s="5" t="n"/>
-      <c r="AA211" s="5" t="n"/>
-      <c r="AB211" s="5" t="n"/>
-      <c r="AC211" s="5" t="n"/>
+      <c r="Y211" s="5" t="inlineStr">
+        <is>
+          <t>Sales, volume, and margin history | supply and logistics cost data | market and competitor intelligence</t>
+        </is>
+      </c>
+      <c r="Z211" s="5" t="inlineStr">
+        <is>
+          <t>Network participation and service recommendations with segmentation and cost-to-serve evidence</t>
+        </is>
+      </c>
+      <c r="AA211" s="5" t="inlineStr">
+        <is>
+          <t>enables: Regional Optimization | informed-by: Assess Cost-to-Serve Performance | enables: Refined Product Demand Management</t>
+        </is>
+      </c>
+      <c r="AB211" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC211" s="5" t="inlineStr">
+        <is>
+          <t>periodic</t>
+        </is>
+      </c>
       <c r="AD211" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -29597,18 +29659,75 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U212" s="5" t="n"/>
-      <c r="V212" s="5" t="n"/>
-      <c r="W212" s="5" t="n"/>
+      <c r="N212" t="inlineStr">
+        <is>
+          <t>Segment the customers and demand points served by the refined-product supply network on supply-economics dimensions — volume, product mix, location, delivery mode, service requirements, and margin contribution — so participation, service, and cost-to-serve analysis work from an economically meaningful segmentation.</t>
+        </is>
+      </c>
+      <c r="O212" t="inlineStr">
+        <is>
+          <t>Covers supply-economics segmentation: grouping customers and demand points by the dimensions that drive supply cost and value — volume and mix, location and logistics reach, delivery mode and service requirements, and contribution; maintaining the segmentation as the network and market change; and supplying it to attractiveness evaluation (CM-1-2-6-1-2) and cost-to-serve assessment (CM-1-2-6-1-3). Commercial, brand, and marketing segmentation for customer strategy, pricing, and offer design is owned by the Marketing processes (CM-1-3) where defined — the same customer may appear in both segmentations for different purposes. Excludes commercial and marketing segmentation (CM-1-3); customer strategy and pricing (CM-1-3); order and credit management (CM-1-3-7).</t>
+        </is>
+      </c>
+      <c r="P212" t="inlineStr">
+        <is>
+          <t>Group customers and demand points on supply-economics dimensions | maintain the segmentation as network and market change | supply the segmentation to attractiveness and cost-to-serve analysis</t>
+        </is>
+      </c>
+      <c r="Q212" t="inlineStr">
+        <is>
+          <t>Commercial and marketing segmentation (CM-1-3) | customer strategy and pricing (CM-1-3) | order and credit management (CM-1-3-7)</t>
+        </is>
+      </c>
+      <c r="T212" t="inlineStr">
+        <is>
+          <t>Batch 19 (2026-09-20). Four-lens rule (Hamid, batch 19, consistent with the Party-plus-Role customer-domain model): the same customer can legitimately exist in supply-economics segmentation (here), Marketing/commercial segmentation (CM-1-3), credit segmentation (credit and order processes), and the party/account hierarchy (customer domain/MDM) — no one segmentation is universal, and this row claims only the supply-economics lens; parallels the batch 11 relationship-based credit split. APQC 'Validate with customers' is a WEAK unrelated candidate.</t>
+        </is>
+      </c>
+      <c r="U212" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V212" s="5" t="inlineStr">
+        <is>
+          <t>An economically meaningful customer segmentation behind every network analysis.</t>
+        </is>
+      </c>
+      <c r="W212" s="5" t="inlineStr">
+        <is>
+          <t>SRC-LNL-T2S-001</t>
+        </is>
+      </c>
       <c r="X212" s="5" t="n"/>
-      <c r="Y212" s="5" t="n"/>
-      <c r="Z212" s="5" t="n"/>
-      <c r="AA212" s="5" t="n"/>
-      <c r="AB212" s="5" t="n"/>
-      <c r="AC212" s="5" t="n"/>
+      <c r="Y212" s="5" t="inlineStr">
+        <is>
+          <t>Customer volume, mix, location, and delivery data | logistics and service records | margin contribution</t>
+        </is>
+      </c>
+      <c r="Z212" s="5" t="inlineStr">
+        <is>
+          <t>Maintained supply-economics segmentation</t>
+        </is>
+      </c>
+      <c r="AA212" s="5" t="inlineStr">
+        <is>
+          <t>enables: Evaluate Market Attractiveness | enables: Assess Cost-to-Serve Performance</t>
+        </is>
+      </c>
+      <c r="AB212" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC212" s="5" t="inlineStr">
+        <is>
+          <t>periodic</t>
+        </is>
+      </c>
       <c r="AD212" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -29676,18 +29795,75 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U213" s="5" t="n"/>
-      <c r="V213" s="5" t="n"/>
-      <c r="W213" s="5" t="n"/>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>Evaluate market attractiveness for supply-network participation using accessible demand, realizable supply margin, logistics reach and cost, supply reliability, specification and regulatory constraints, and network fit — so participation recommendations rest on a consistent supply-network economic evaluation.</t>
+        </is>
+      </c>
+      <c r="O213" t="inlineStr">
+        <is>
+          <t>Covers market attractiveness evaluation centered on the supply-network question: assessing markets and segments on accessible demand, realizable supply margin from the network's supply points, logistics reach and cost, supply reliability, specification and regulatory constraints, and fit with the existing and planned network; ranking participation options; and feeding the evaluation into network recommendations (CM-1-2-6-1) and demand management (CM-1-2-6-2). This is not generic market-entry strategy: participation, supply, and allocation decisions stay with the accountable owners (CM-1-1-2, commercial leadership); market-entry strategy and marketing programs with CM-1-3. Excludes participation and allocation decisions (CM-1-1-2, accountable owners); marketing strategy and programs (CM-1-3); demand forecasting (CM-1-2-6-2-3).</t>
+        </is>
+      </c>
+      <c r="P213" t="inlineStr">
+        <is>
+          <t>Assess markets on accessible demand, realizable margin, logistics reach, reliability, and constraints | rank participation options consistently | feed evaluations into network recommendations and demand management</t>
+        </is>
+      </c>
+      <c r="Q213" t="inlineStr">
+        <is>
+          <t>Participation and allocation decisions (CM-1-1-2, accountable owners) | marketing strategy (CM-1-3) | demand forecasting (CM-1-2-6-2-3)</t>
+        </is>
+      </c>
+      <c r="T213" t="inlineStr">
+        <is>
+          <t>Batch 19 (2026-09-20). Supply-network-centered evaluation (Hamid, batch 19), not generic market-entry strategy — the question is what the network can serve profitably. Evaluate-and-rank, decide-elsewhere (batch 11 pattern); jurisdiction and specification requirements vary by market. APQC candidate is a WEAK generic match.</t>
+        </is>
+      </c>
+      <c r="U213" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V213" s="5" t="inlineStr">
+        <is>
+          <t>A consistent economic answer to 'is this market worth serving from our network?'</t>
+        </is>
+      </c>
+      <c r="W213" s="5" t="inlineStr">
+        <is>
+          <t>SRC-EIA-STEO-001 | SRC-LNL-T2S-001</t>
+        </is>
+      </c>
       <c r="X213" s="5" t="n"/>
-      <c r="Y213" s="5" t="n"/>
-      <c r="Z213" s="5" t="n"/>
-      <c r="AA213" s="5" t="n"/>
-      <c r="AB213" s="5" t="n"/>
-      <c r="AC213" s="5" t="n"/>
+      <c r="Y213" s="5" t="inlineStr">
+        <is>
+          <t>Segmentation (CM-1-2-6-1-1) | market demand and margin intelligence | logistics cost and access data</t>
+        </is>
+      </c>
+      <c r="Z213" s="5" t="inlineStr">
+        <is>
+          <t>Ranked market attractiveness evaluations for network participation</t>
+        </is>
+      </c>
+      <c r="AA213" s="5" t="inlineStr">
+        <is>
+          <t>uses-input: Segment Customers | enables: Network Management | informed-by: Assess Cost-to-Serve Performance</t>
+        </is>
+      </c>
+      <c r="AB213" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC213" s="5" t="inlineStr">
+        <is>
+          <t>periodic</t>
+        </is>
+      </c>
       <c r="AD213" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -29755,18 +29931,75 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U214" s="5" t="n"/>
-      <c r="V214" s="5" t="n"/>
-      <c r="W214" s="5" t="n"/>
+      <c r="N214" t="inlineStr">
+        <is>
+          <t>Assess the full cost of serving customers, segments, and markets from the refined-product supply network — supply, storage, handling, primary and secondary logistics, and service costs against realized margins — identifying where the network serves profitably, marginally, or at a loss, so participation and service recommendations rest on evidenced economics.</t>
+        </is>
+      </c>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>Covers cost-to-serve assessment: assembling supply, storage, throughput, handling, transportation, and service costs by segment, customer group, and market from the accountable cost owners' data; setting them against realized volumes and margins; identifying profitable, marginal, and loss-making service; and feeding results to segmentation, attractiveness evaluation, and network recommendations. Costs are reported at an agreed allocation and attribution basis; cost-to-serve analysis does not itself create accounting cost allocations or transfer-pricing rules — those remain with Accounting, Finance, and the applicable legal-entity policy. Uses governed cost and margin data from Accounting and the logistics processes; it does not produce cost accounting (CM-1-2-4-2), set prices (CM-1-3), or decide service changes (accountable owners). Excludes cost accounting production and allocation rules (CM-1-2-4-2, Finance); transfer pricing (Finance/legal-entity policy); pricing (CM-1-3); service and participation decisions (accountable owners); distribution cost-performance backcasting (CM-1-1-6, locked rule).</t>
+        </is>
+      </c>
+      <c r="P214" t="inlineStr">
+        <is>
+          <t>Assemble cost-to-serve by segment, customer group, and market from governed data at the agreed allocation basis | set costs against realized volumes and margins | identify profitable, marginal, and loss-making service | feed evidenced findings to network recommendations</t>
+        </is>
+      </c>
+      <c r="Q214" t="inlineStr">
+        <is>
+          <t>Cost accounting production and allocation rules (CM-1-2-4-2, Finance) | transfer pricing (Finance/legal-entity policy) | pricing (CM-1-3) | service and participation decisions (accountable owners) | distribution backcasting (CM-1-1-6, locked rule)</t>
+        </is>
+      </c>
+      <c r="T214" t="inlineStr">
+        <is>
+          <t>Batch 19 (2026-09-20). Assessment on governed data at an agreed allocation basis — consumes Accounting and logistics costs, never creates allocation or transfer-pricing rules (Hamid, batch 19); plan-variance backcasting remains with Distribution Backcasting under its locked rule (batch 03). APQC candidate is a WEAK production-performance match.</t>
+        </is>
+      </c>
+      <c r="U214" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V214" s="5" t="inlineStr">
+        <is>
+          <t>Know what serving each customer and market truly costs — and show it with evidence.</t>
+        </is>
+      </c>
+      <c r="W214" s="5" t="inlineStr">
+        <is>
+          <t>SRC-LNL-T2S-001 | SRC-ORP-DPSC-001</t>
+        </is>
+      </c>
       <c r="X214" s="5" t="n"/>
-      <c r="Y214" s="5" t="n"/>
-      <c r="Z214" s="5" t="n"/>
-      <c r="AA214" s="5" t="n"/>
-      <c r="AB214" s="5" t="n"/>
-      <c r="AC214" s="5" t="n"/>
+      <c r="Y214" s="5" t="inlineStr">
+        <is>
+          <t>Segmentation (CM-1-2-6-1-1) | governed cost data (CM-1-2-4-2, logistics processes) | realized volumes and margins</t>
+        </is>
+      </c>
+      <c r="Z214" s="5" t="inlineStr">
+        <is>
+          <t>Evidenced cost-to-serve assessments by segment and market</t>
+        </is>
+      </c>
+      <c r="AA214" s="5" t="inlineStr">
+        <is>
+          <t>uses-input: Segment Customers | enables: Network Management | uses-input: Accounting</t>
+        </is>
+      </c>
+      <c r="AB214" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC214" s="5" t="inlineStr">
+        <is>
+          <t>periodic</t>
+        </is>
+      </c>
       <c r="AD214" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -29834,18 +30067,80 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U215" s="5" t="n"/>
-      <c r="V215" s="5" t="n"/>
-      <c r="W215" s="5" t="n"/>
+      <c r="N215" t="inlineStr">
+        <is>
+          <t>Manage refined-product demand on the supply side — maintaining the operational demand picture the supply chain runs on, forecasting location-level product demand for supply operations, and managing product-exchange volumes as a balancing lever — so supply operations, replenishment, and trading coordination work from one current, operational demand view.</t>
+        </is>
+      </c>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t>Covers the operational demand cycle: managing the current demand picture against supply capability (CM-1-2-6-2-1), operational location-level demand forecasting for the supply-chain context (CM-1-2-6-2-3, under the batch 03 constraint), and operational management of product-exchange volumes as a supply and demand balancing lever (CM-1-2-6-2-2). The enterprise published demand forecast is owned by Demand Forecasting (CM-1-1-1-1) and consumed here as an input; trading's forward-view intake is Receive Demand Forecast (CM-1-2-1-1-2); the refinery-planning demand basis is Capture Product Demand Requirements (CM-1-1-4-7-1). Excludes the enterprise published forecast (CM-1-1-1-1, batch 03); trading forecast intake (CM-1-2-1-1-2); the refinery demand basis (CM-1-1-4-7-1); order capture and commitment (CM-1-3-7); supply and allocation decisions (CM-1-1-2).</t>
+        </is>
+      </c>
+      <c r="P215" t="inlineStr">
+        <is>
+          <t>Maintain the operational demand picture against supply capability | forecast location-level demand for supply operations | manage exchange volumes as a balancing lever | supply one operational demand view to supply operations and trading coordination</t>
+        </is>
+      </c>
+      <c r="Q215" t="inlineStr">
+        <is>
+          <t>Enterprise published forecast (CM-1-1-1-1) | trading forecast intake (CM-1-2-1-1-2) | refinery demand basis (CM-1-1-4-7-1) | order capture (CM-1-3-7) | supply and allocation decisions (CM-1-1-2)</t>
+        </is>
+      </c>
+      <c r="R215" t="inlineStr">
+        <is>
+          <t>Operational Product Demand Management</t>
+        </is>
+      </c>
+      <c r="T215" t="inlineStr">
+        <is>
+          <t>Batch 19 (2026-09-20). Concept-type: process — one operational demand cycle. Batch 03 three-way forecast partition implemented: enterprise published forecast (CM-1-1-1-1), trading intake (CM-1-2-1-1-2), operational SCM-context forecasting here. APQC candidate is an unrelated documentation match.</t>
+        </is>
+      </c>
+      <c r="U215" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V215" s="5" t="inlineStr">
+        <is>
+          <t>One current operational demand view behind supply operations, replenishment, and trading coordination.</t>
+        </is>
+      </c>
+      <c r="W215" s="5" t="inlineStr">
+        <is>
+          <t>SRC-EIA-STEO-001 | SRC-ORP-DPSC-001</t>
+        </is>
+      </c>
       <c r="X215" s="5" t="n"/>
-      <c r="Y215" s="5" t="n"/>
-      <c r="Z215" s="5" t="n"/>
-      <c r="AA215" s="5" t="n"/>
-      <c r="AB215" s="5" t="n"/>
-      <c r="AC215" s="5" t="n"/>
+      <c r="Y215" s="5" t="inlineStr">
+        <is>
+          <t>Published enterprise forecast (CM-1-1-1-1) | orders and lifting patterns | exchange positions and entitlements | supply capability</t>
+        </is>
+      </c>
+      <c r="Z215" s="5" t="inlineStr">
+        <is>
+          <t>Operational demand picture, location-level forecasts, and exchange-utilization plans</t>
+        </is>
+      </c>
+      <c r="AA215" s="5" t="inlineStr">
+        <is>
+          <t>uses-input: Demand Forecasting | enables: Supply Operations | enables: Coordinate Product Trading</t>
+        </is>
+      </c>
+      <c r="AB215" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC215" s="5" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AD215" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -29913,18 +30208,75 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U216" s="5" t="n"/>
-      <c r="V216" s="5" t="n"/>
-      <c r="W216" s="5" t="n"/>
+      <c r="N216" t="inlineStr">
+        <is>
+          <t>Manage the operational refined-product demand picture — consolidating current orders, lifting patterns, committed volumes, and forecast demand by product and location, comparing it against available supply, and surfacing imbalances for supply, replenishment, and trading action — so shortfalls and surpluses are visible and acted on before they become failures.</t>
+        </is>
+      </c>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>Covers operational demand management: consolidating the current demand view from orders, rack liftings, contract commitments, and the operational forecast (CM-1-2-6-2-3); comparing demand against available and planned supply by product and location; identifying imbalances, allocation pressure, and demand risks; and routing actions to the accountable owners — replenishment requirements to the batch 04 decision owner (CM-1-1-3-7-9), trading needs through Coordinate Product Trading (CM-1-1-3-5-2), exchange utilization to CM-1-2-6-2-2. It may recommend supply actions and contingency options, but allocation decisions remain with Regional Optimization (CM-1-1-2, batch 03 rule); order commitments with Order Management (CM-1-3-7). Excludes allocation decisions (CM-1-1-2); order capture and commitment (CM-1-3-7); replenishment decisions (CM-1-1-3-7-9); trade execution (CM-1-2-1-3).</t>
+        </is>
+      </c>
+      <c r="P216" t="inlineStr">
+        <is>
+          <t>Consolidate the current operational demand view by product and location | compare demand against available and planned supply | identify imbalances and recommend supply actions and contingency options | route actions to the accountable owners</t>
+        </is>
+      </c>
+      <c r="Q216" t="inlineStr">
+        <is>
+          <t>Allocation decisions (CM-1-1-2) | order capture and commitment (CM-1-3-7) | replenishment decisions (CM-1-1-3-7-9) | trade execution (CM-1-2-1-3)</t>
+        </is>
+      </c>
+      <c r="T216" t="inlineStr">
+        <is>
+          <t>Batch 19 (2026-09-20). Recommends-and-routes (Hamid, batch 19): the process actively recommends supply actions and contingencies while the batch 03/04 decision rights stay with their owners — allocation with Regional Optimization, replenishment with CM-1-1-3-7-9. APQC candidate is an unrelated image-management match.</t>
+        </is>
+      </c>
+      <c r="U216" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V216" s="5" t="inlineStr">
+        <is>
+          <t>No demand shortfall or surplus that nobody saw coming.</t>
+        </is>
+      </c>
+      <c r="W216" s="5" t="inlineStr">
+        <is>
+          <t>SRC-ORP-DPSC-001</t>
+        </is>
+      </c>
       <c r="X216" s="5" t="n"/>
-      <c r="Y216" s="5" t="n"/>
-      <c r="Z216" s="5" t="n"/>
-      <c r="AA216" s="5" t="n"/>
-      <c r="AB216" s="5" t="n"/>
-      <c r="AC216" s="5" t="n"/>
+      <c r="Y216" s="5" t="inlineStr">
+        <is>
+          <t>Orders and lifting data | operational forecast (CM-1-2-6-2-3) | supply availability | exchange positions (CM-1-2-6-2-2)</t>
+        </is>
+      </c>
+      <c r="Z216" s="5" t="inlineStr">
+        <is>
+          <t>Current demand-supply picture with recommended actions routed to owners</t>
+        </is>
+      </c>
+      <c r="AA216" s="5" t="inlineStr">
+        <is>
+          <t>uses-input: Forecast Refined Product Demand | enables: Manage Replenishment | enables: Coordinate Product Trading</t>
+        </is>
+      </c>
+      <c r="AB216" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC216" s="5" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AD216" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -29992,18 +30344,75 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U217" s="5" t="n"/>
-      <c r="V217" s="5" t="n"/>
-      <c r="W217" s="5" t="n"/>
+      <c r="N217" t="inlineStr">
+        <is>
+          <t>Coordinate operational utilization of product-exchange entitlements to support approved demand and supply requirements by monitoring available exchange positions, planning proposed lifting and delivery use by location and period, and communicating utilization requirements to the relevant agreement, trading, supply, and scheduling processes.</t>
+        </is>
+      </c>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t>Covers the operational use of product exchanges: monitoring available positions, entitlements, and imbalance status under existing exchange agreements for operational visibility; planning proposed lifting and delivery utilization by location and period against demand needs (CM-1-2-6-2-1) and supply plans; communicating utilization requirements to the agreement owner (CM-1-2-7-1-1), trading coordination, supply operations (CM-1-2-6-3), and the scheduling processes; and flagging utilization or imbalance concerns to the agreement owner. Operational visibility of imbalance status does not constitute contractual imbalance calculation, commercial decision, agreement administration, or settlement — exchange agreements, terms, and imbalance treatment are owned by Manage Product Exchange Agreements (CM-1-2-7-1-1, batch 08/14 bindings); 'exchange' here means product exchange arrangements, not futures exchanges (CM-1-2-1-3-4, batch 08). Excludes exchange agreement administration, contractual imbalance calculation, and imbalance treatment (CM-1-2-7-1-1); futures-exchange trading (CM-1-2-1-3-4); settlement (CM-1-2-4-1); movement scheduling (CM-1-1-3-6).</t>
+        </is>
+      </c>
+      <c r="P217" t="inlineStr">
+        <is>
+          <t>Monitor available exchange positions and entitlements for operational visibility | plan proposed lifting and delivery utilization by location and period | communicate utilization requirements to agreement, trading, supply, and scheduling processes | flag utilization and imbalance concerns to the agreement owner</t>
+        </is>
+      </c>
+      <c r="Q217" t="inlineStr">
+        <is>
+          <t>Exchange agreement administration and contractual imbalance calculation and treatment (CM-1-2-7-1-1) | futures-exchange trading (CM-1-2-1-3-4) | settlement (CM-1-2-4-1) | movement scheduling (CM-1-1-3-6)</t>
+        </is>
+      </c>
+      <c r="T217" t="inlineStr">
+        <is>
+          <t>Batch 19 (2026-09-20). Q4 decision with Hamid's caution applied: operational visibility and proposed utilization here; contractual imbalance calculation, commercial decisions, administration, and settlement at CM-1-2-7-1-1 (batch 08 'not product exchange agreements' and batch 14 imbalance-treatment bindings honored). Use-versus-administer split parallels the batch 11 set-versus-apply pattern. APQC candidate is an unrelated image-management match.</t>
+        </is>
+      </c>
+      <c r="U217" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V217" s="5" t="inlineStr">
+        <is>
+          <t>Exchange entitlements pulled at the right place and time — never wasted, never overdrawn.</t>
+        </is>
+      </c>
+      <c r="W217" s="5" t="inlineStr">
+        <is>
+          <t>SRC-ORP-DPSC-001</t>
+        </is>
+      </c>
       <c r="X217" s="5" t="n"/>
-      <c r="Y217" s="5" t="n"/>
-      <c r="Z217" s="5" t="n"/>
-      <c r="AA217" s="5" t="n"/>
-      <c r="AB217" s="5" t="n"/>
-      <c r="AC217" s="5" t="n"/>
+      <c r="Y217" s="5" t="inlineStr">
+        <is>
+          <t>Exchange positions and entitlements (CM-1-2-7-1-1) | demand needs (CM-1-2-6-2-1) | location supply plans</t>
+        </is>
+      </c>
+      <c r="Z217" s="5" t="inlineStr">
+        <is>
+          <t>Proposed exchange utilization plans communicated to the owning processes</t>
+        </is>
+      </c>
+      <c r="AA217" s="5" t="inlineStr">
+        <is>
+          <t>uses-input: Manage Refined Product Demand | enables: Supply Operations | informed-by: Manage Product Exchange Agreements</t>
+        </is>
+      </c>
+      <c r="AB217" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC217" s="5" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AD217" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -30071,18 +30480,80 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U218" s="5" t="n"/>
-      <c r="V218" s="5" t="n"/>
-      <c r="W218" s="5" t="n"/>
+      <c r="N218" t="inlineStr">
+        <is>
+          <t>Forecast refined-product demand operationally for the supply-chain context — projecting short-horizon demand by product, location, and period from lifting history, orders, seasonality, and local market signals, calibrated against the published enterprise forecast — so supply operations and replenishment run on location-level demand projections at operational granularity.</t>
+        </is>
+      </c>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>Covers operational demand forecasting under the batch 03 constraint: short-horizon, location-level projections by product and period for supply operations, replenishment support, and exchange utilization; built from rack lifting history, current orders, seasonality, weather and local market signals; calibrated against the published enterprise forecast (CM-1-1-1-1) and reconciled through governed exception and variance processes where material differences arise — operational forecasts can legitimately differ on local timing, geography, product granularity, and immediate operational signals, and this process consumes the enterprise forecast without producing, revising, republishing, or overriding it. The batch 03 three-way partition: enterprise published forecast at CM-1-1-1-1; trading intake at CM-1-2-1-1-2; operational SCM-context forecasting here. Excludes the enterprise published forecast (CM-1-1-1-1, batch 03); trading forecast intake and forward views (CM-1-2-1-1-2); the refinery-planning demand basis (CM-1-1-4-7-1); feedstock demand (CM-1-2-5-2-2, batch 18).</t>
+        </is>
+      </c>
+      <c r="P218" t="inlineStr">
+        <is>
+          <t>Project short-horizon demand by product, location, and period | build from lifting history, orders, and local signals | calibrate against the published enterprise forecast and reconcile material differences through governed variance processes | publish operational projections to supply operations and replenishment</t>
+        </is>
+      </c>
+      <c r="Q218" t="inlineStr">
+        <is>
+          <t>Enterprise published forecast (CM-1-1-1-1) | trading forecast intake (CM-1-2-1-1-2) | refinery demand basis (CM-1-1-4-7-1) | feedstock demand (CM-1-2-5-2-2)</t>
+        </is>
+      </c>
+      <c r="R218" t="inlineStr">
+        <is>
+          <t>Forecast Operational Refined Product Demand</t>
+        </is>
+      </c>
+      <c r="T218" t="inlineStr">
+        <is>
+          <t>Batch 19 (2026-09-20). Batch 03 constraint implemented: operational SCM-context forecasting consuming the published forecast as calibration input; legitimate local differences reconcile through governed exception/variance processes, not forced equality (Hamid, batch 19). Normalized label 'Forecast Operational Refined Product Demand' queued to make the boundary visible. The variance threshold that triggers escalation is an operating-model follow-up carried in the batch 19 PR. APQC 'Forecast IT service demand' is a false lexical match.</t>
+        </is>
+      </c>
+      <c r="U218" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V218" s="5" t="inlineStr">
+        <is>
+          <t>Location-level demand projections at the granularity supply operations actually runs on.</t>
+        </is>
+      </c>
+      <c r="W218" s="5" t="inlineStr">
+        <is>
+          <t>SRC-EIA-STEO-001 | SRC-ORP-DPSC-001</t>
+        </is>
+      </c>
       <c r="X218" s="5" t="n"/>
-      <c r="Y218" s="5" t="n"/>
-      <c r="Z218" s="5" t="n"/>
-      <c r="AA218" s="5" t="n"/>
-      <c r="AB218" s="5" t="n"/>
-      <c r="AC218" s="5" t="n"/>
+      <c r="Y218" s="5" t="inlineStr">
+        <is>
+          <t>Published enterprise forecast (CM-1-1-1-1) | rack lifting history and orders | seasonality and local market signals</t>
+        </is>
+      </c>
+      <c r="Z218" s="5" t="inlineStr">
+        <is>
+          <t>Operational location-level demand projections reconciled to the published forecast</t>
+        </is>
+      </c>
+      <c r="AA218" s="5" t="inlineStr">
+        <is>
+          <t>uses-input: Demand Forecasting | enables: Manage Refined Product Demand | enables: Manage Replenishment</t>
+        </is>
+      </c>
+      <c r="AB218" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC218" s="5" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AD218" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -30150,18 +30621,80 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U219" s="5" t="n"/>
-      <c r="V219" s="5" t="n"/>
-      <c r="W219" s="5" t="n"/>
+      <c r="N219" t="inlineStr">
+        <is>
+          <t>Fulfill approved refined-product replenishment and supply requirements from Supply &amp; Trading sources by coordinating product availability at purchased-supply, exchange, transfer, and third-party source points; confirming feasible supply and transport arrangements; and handing approved movements to the processes that schedule, actualize, and settle them.</t>
+        </is>
+      </c>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t>Covers the S&amp;T-sourced supply-fulfillment cycle under the Q2 (Option A) reading: coordinating commercial supply status and availability at source points where Supply And Trading supplies the network — purchased volumes, exchange locations, transfers, third-party terminals (CM-1-2-6-3-1); fulfilling network replenishment requirements from traded sources, consuming the replenishment decisions owned by Manage Inventory Replenishment (CM-1-1-3-7-9, batch 04) (CM-1-2-6-3-2); and coordinating transportation arrangements for S&amp;T-sourced primary movements (CM-1-2-6-3-3). Supply Operations may identify feasible commercial sources and communicate fulfillment constraints, but it does not decide network replenishment quantity or timing, allocate constrained product, execute trades, administer primary movements, or direct physical operations. The complementarity rule: Physical Distribution Scheduling (CM-1-1-3-6, batch 05) owns primary-movement nominations and shipper-side administration; Secondary Distribution Management (CM-1-1-3-8) owns terminal-to-customer delivery; this cluster supplies the network from commercial sources and provides its movements to the owning scheduling, actualization, and settlement processes. Excludes replenishment decisions (CM-1-1-3-7-9, batch 04); allocation decisions (CM-1-1-2); primary movement scheduling and administration (CM-1-1-3-6, batch 05); secondary distribution (CM-1-1-3-8); trade execution (CM-1-2-1-3); exchange agreement administration (CM-1-2-7-1-1); physical terminal and transport operations (operators, carriers, Midstream).</t>
+        </is>
+      </c>
+      <c r="P219" t="inlineStr">
+        <is>
+          <t>Coordinate commercial supply status at S&amp;T-supplied source points | fulfill approved replenishment requirements from traded, exchanged, and transferred product | confirm feasible supply and transport arrangements | hand approved movements to the owning scheduling, actualization, and settlement processes</t>
+        </is>
+      </c>
+      <c r="Q219" t="inlineStr">
+        <is>
+          <t>Replenishment decisions (CM-1-1-3-7-9) | allocation decisions (CM-1-1-2) | primary movement scheduling (CM-1-1-3-6) | secondary distribution (CM-1-1-3-8) | trade execution (CM-1-2-1-3) | exchange administration (CM-1-2-7-1-1) | physical operations (operators, carriers, Midstream)</t>
+        </is>
+      </c>
+      <c r="R219" t="inlineStr">
+        <is>
+          <t>S&amp;T Product Supply Fulfillment</t>
+        </is>
+      </c>
+      <c r="T219" t="inlineStr">
+        <is>
+          <t>Batch 19 (2026-09-20). Q2 decision (Hamid, Option A with fulfillment language): commercial-source fulfillment and supply coordination — never a parallel scheduling or dispatch organization; 'operate' wording removed because it can imply terminal-operations or dispatch ownership. The product-side mirror of the batch 18 feedstock logistics cluster, complementing the batch 04 replenishment decision and batch 05 distribution scheduling ownerships. Concept-type: process — one fulfillment cycle. APQC candidate is an unrelated internal-operations match.</t>
+        </is>
+      </c>
+      <c r="U219" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V219" s="5" t="inlineStr">
+        <is>
+          <t>The network reliably supplied from commercial sources, with every decision right left where earlier batches put it.</t>
+        </is>
+      </c>
+      <c r="W219" s="5" t="inlineStr">
+        <is>
+          <t>SRC-ORP-DPSC-001 | SRC-LNL-T2S-001</t>
+        </is>
+      </c>
       <c r="X219" s="5" t="n"/>
-      <c r="Y219" s="5" t="n"/>
-      <c r="Z219" s="5" t="n"/>
-      <c r="AA219" s="5" t="n"/>
-      <c r="AB219" s="5" t="n"/>
-      <c r="AC219" s="5" t="n"/>
+      <c r="Y219" s="5" t="inlineStr">
+        <is>
+          <t>Replenishment requirements (CM-1-1-3-7-9) | operational demand and exchange plans (CM-1-2-6-2) | agreed purchases and transfers (CM-1-2-1-3)</t>
+        </is>
+      </c>
+      <c r="Z219" s="5" t="inlineStr">
+        <is>
+          <t>Fulfilled supply requirements handed to the owning scheduling and actualization processes</t>
+        </is>
+      </c>
+      <c r="AA219" s="5" t="inlineStr">
+        <is>
+          <t>uses-input: Refined Product Demand Management | uses-input: Manage Inventory Replenishment | precedes: Physical Distribution Scheduling</t>
+        </is>
+      </c>
+      <c r="AB219" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC219" s="5" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AD219" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -30229,18 +30762,80 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U220" s="5" t="n"/>
-      <c r="V220" s="5" t="n"/>
-      <c r="W220" s="5" t="n"/>
+      <c r="N220" t="inlineStr">
+        <is>
+          <t>Coordinate commercial supply status at the source points where Supply And Trading supplies primary distribution — monitoring availability, loading capability, and product quality at purchased-supply, exchange, transfer, and third-party terminal locations, resolving supply issues with operators and counterparties, and keeping source-point status current for replenishment fulfillment and scheduling.</t>
+        </is>
+      </c>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>Covers S&amp;T-side source-point coordination: monitoring product availability, allocation, loading capability, and quality status at locations where the network is supplied from purchases, exchanges, transfers, and third-party terminals; resolving availability, quality, and loading issues with terminal operators, exchange partners, and suppliers; and maintaining current source-point status for replenishment fulfillment (CM-1-2-6-3-2), demand management (CM-1-2-6-2-1), and the scheduling processes. Physical terminal operations belong to the operators; own-refinery rack and terminal operations to Refining and Midstream; movement scheduling to CM-1-1-3-6. Excludes physical terminal operations (operators, Midstream); own-production scheduling and administration (CM-1-1-3-5/-6); terminal contracting (commercial processes); terminal/storage settlement (CM-1-2-4-1-14).</t>
+        </is>
+      </c>
+      <c r="P220" t="inlineStr">
+        <is>
+          <t>Monitor availability, loading capability, and quality at S&amp;T-supplied source points | resolve supply issues with operators and counterparties | keep source-point status current for replenishment fulfillment and scheduling</t>
+        </is>
+      </c>
+      <c r="Q220" t="inlineStr">
+        <is>
+          <t>Physical terminal operations (operators, Midstream) | own-production scheduling (CM-1-1-3-5/-6) | terminal contracting (commercial processes) | terminal settlement (CM-1-2-4-1-14)</t>
+        </is>
+      </c>
+      <c r="R220" t="inlineStr">
+        <is>
+          <t>Coordinate S&amp;T Source-Point Supply Operations</t>
+        </is>
+      </c>
+      <c r="T220" t="inlineStr">
+        <is>
+          <t>Batch 19 (2026-09-20). Coordinates-commercial-status, never operates (owner-versus-executor pattern, batch 05): operators run the terminals; this process coordinates the S&amp;T supply interest at them. Normalized label 'Coordinate S&amp;T Source-Point Supply Operations' queued to prevent mistaken inference of physical operations (Hamid, batch 19). APQC 'Manage treasury operations' is a false lexical match on 'operations'.</t>
+        </is>
+      </c>
+      <c r="U220" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V220" s="5" t="inlineStr">
+        <is>
+          <t>Every S&amp;T-supplied source point ready to load the right product when the network needs it.</t>
+        </is>
+      </c>
+      <c r="W220" s="5" t="inlineStr">
+        <is>
+          <t>SRC-EI-HM32-001 | SRC-ORP-DPSC-001</t>
+        </is>
+      </c>
       <c r="X220" s="5" t="n"/>
-      <c r="Y220" s="5" t="n"/>
-      <c r="Z220" s="5" t="n"/>
-      <c r="AA220" s="5" t="n"/>
-      <c r="AB220" s="5" t="n"/>
-      <c r="AC220" s="5" t="n"/>
+      <c r="Y220" s="5" t="inlineStr">
+        <is>
+          <t>Source-point status from operators and partners | agreed purchases, transfers, and exchange entitlements (CM-1-2-1-3, CM-1-2-7-1-1) | replenishment and demand needs</t>
+        </is>
+      </c>
+      <c r="Z220" s="5" t="inlineStr">
+        <is>
+          <t>Current, coordinated source-point supply status</t>
+        </is>
+      </c>
+      <c r="AA220" s="5" t="inlineStr">
+        <is>
+          <t>enables: Manage Replenishment | uses-input: Manage Refined Product Exchanges | uses-input: Coordinate Product Trading</t>
+        </is>
+      </c>
+      <c r="AB220" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC220" s="5" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
       <c r="AD220" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -30308,18 +30903,80 @@
           <t>strong APQC candidate but no validator agreed</t>
         </is>
       </c>
-      <c r="U221" s="5" t="n"/>
-      <c r="V221" s="5" t="n"/>
-      <c r="W221" s="5" t="n"/>
+      <c r="N221" t="inlineStr">
+        <is>
+          <t>Fulfill network replenishment requirements from Supply And Trading sources — receiving the replenishment quantities and timing decided by the network replenishment owner, sourcing them from purchased, exchanged, and transferred product where own production does not cover them, and confirming fulfillment plans, constraints, and exceptions back — so replenishment decisions are met without S&amp;T re-deciding them.</t>
+        </is>
+      </c>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>Covers replenishment fulfillment from commercial sources: receiving replenishment requirements decided by Manage Inventory Replenishment (CM-1-1-3-7-9, batch 04 — that process owns when and how much to resupply each stock point); determining the feasible S&amp;T source — purchased product, exchange liftings (CM-1-2-6-2-2), or transfers — where own production and the regional plan do not cover the requirement; initiating the sourcing through the coordination and trading processes; and confirming fulfillment plans, timing, constraints, and exceptions back to the requirement owner — under supply constraint, fulfillment may differ from the request, and the confirmation returns what is feasible for the owner's decision. This process fulfills, and never makes, the replenishment decision. Excludes the replenishment decision (CM-1-1-3-7-9, batch 04); allocation decisions (CM-1-1-2); trade execution (CM-1-2-1-3); movement scheduling (CM-1-1-3-6); feedstock replenishment (CM-1-2-5, batch 18).</t>
+        </is>
+      </c>
+      <c r="P221" t="inlineStr">
+        <is>
+          <t>Receive replenishment requirements from the deciding owner | determine the feasible S&amp;T source where own production does not cover | initiate sourcing through coordination and trading processes | confirm fulfillment plans, constraints, and exceptions back to the requirement owner</t>
+        </is>
+      </c>
+      <c r="Q221" t="inlineStr">
+        <is>
+          <t>Replenishment decisions (CM-1-1-3-7-9, batch 04) | allocation decisions (CM-1-1-2) | trade execution (CM-1-2-1-3) | movement scheduling (CM-1-1-3-6) | feedstock replenishment (CM-1-2-5)</t>
+        </is>
+      </c>
+      <c r="R221" t="inlineStr">
+        <is>
+          <t>Fulfill Replenishment From Trading Sources</t>
+        </is>
+      </c>
+      <c r="T221" t="inlineStr">
+        <is>
+          <t>Batch 19 (2026-09-20). Q2 decision at its sharpest point: the batch 04 decision right ('Manage Inventory Replenishment owns the replenishment decision') is preserved verbatim — this row is the S&amp;T fulfillment counterpart, decide-versus-fulfill mirroring decide-versus-advise. Normalized label 'Fulfill Replenishment From Trading Sources' queued with priority (Hamid, batch 19: highest naming collision in the batch; names mirror the locked taxonomy, so carried as alt label until the naming pass). APQC 'Manage collaborative replenishment planning' scored STRONG at 3b but NO SOURCE — honored.</t>
+        </is>
+      </c>
+      <c r="U221" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V221" s="5" t="inlineStr">
+        <is>
+          <t>Fulfill approved replenishment requirements from feasible commercial sources while returning confirmed timing, constraints, and exceptions to the replenishment decision owner.</t>
+        </is>
+      </c>
+      <c r="W221" s="5" t="inlineStr">
+        <is>
+          <t>SRC-ORP-DPSC-001</t>
+        </is>
+      </c>
       <c r="X221" s="5" t="n"/>
-      <c r="Y221" s="5" t="n"/>
-      <c r="Z221" s="5" t="n"/>
-      <c r="AA221" s="5" t="n"/>
-      <c r="AB221" s="5" t="n"/>
-      <c r="AC221" s="5" t="n"/>
+      <c r="Y221" s="5" t="inlineStr">
+        <is>
+          <t>Replenishment requirements (CM-1-1-3-7-9) | source-point status (CM-1-2-6-3-1) | exchange entitlements (CM-1-2-6-2-2) | available purchases and transfers</t>
+        </is>
+      </c>
+      <c r="Z221" s="5" t="inlineStr">
+        <is>
+          <t>Confirmed fulfillment plans with constraints and exceptions returned to the decision owner</t>
+        </is>
+      </c>
+      <c r="AA221" s="5" t="inlineStr">
+        <is>
+          <t>uses-input: Manage Inventory Replenishment | uses-input: Manage Primary Distribution Operations | enables: Coordinate Product Trading</t>
+        </is>
+      </c>
+      <c r="AB221" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC221" s="5" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
       <c r="AD221" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -30387,18 +31044,80 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U222" s="5" t="n"/>
-      <c r="V222" s="5" t="n"/>
-      <c r="W222" s="5" t="n"/>
+      <c r="N222" t="inlineStr">
+        <is>
+          <t>Coordinate transportation arrangements for Supply And Trading-sourced primary product movements — pipeline, marine, rail, and truck arrangements under available carrier contracts, capacity, and transport agreements for volumes S&amp;T supplies into the network — providing confirmed movement requirements to the processes that own scheduling and actualization.</t>
+        </is>
+      </c>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t>Covers transportation coordination for S&amp;T-sourced product movements, the product-side counterpart of the batch 18 feedstock transportation cluster: coordinating and monitoring the commercial and logistical arrangements to move S&amp;T-sourced volumes — purchases, exchange liftings, transfers — under carrier contracts (CM-1-2-1-2-9), capacity rights, and transportation deals (CM-1-2-1-3-9); requesting or coordinating nominations, bookings, and carrier actions under the batch 18 coordinate-not-execute rule; tracking status and resolving in-transit issues; and providing the confirmed source, transport, capacity, timing, and commercial-movement requirements to Physical Distribution Scheduling (CM-1-1-3-6), which owns primary movement nomination and shipper-side administration, and to Actualizations (CM-1-2-3-1), which owns commercial movement actuals. Excludes primary movement nomination, scheduling, and shipper-side administration (CM-1-1-3-6, batch 05); carrier contracting (CM-1-2-1-2-9); transportation deal capture (CM-1-2-1-3-9); charter-party negotiation and physical transport (marine logistics, carriers); actualization and freight settlement (CM-1-2-3-1, CM-1-2-4-1); secondary distribution (CM-1-1-3-8).</t>
+        </is>
+      </c>
+      <c r="P222" t="inlineStr">
+        <is>
+          <t>Coordinate transport arrangements for S&amp;T-sourced product movements under existing contracts and capacity | request or coordinate nominations, bookings, and carrier actions | track status and resolve in-transit issues | provide confirmed movement requirements to Physical Distribution Scheduling and Actualizations</t>
+        </is>
+      </c>
+      <c r="Q222" t="inlineStr">
+        <is>
+          <t>Primary movement nomination and administration (CM-1-1-3-6) | carrier contracting (CM-1-2-1-2-9) | transportation deal capture (CM-1-2-1-3-9) | charter negotiation and physical transport (marine logistics, carriers) | actualization and settlement (CM-1-2-3-1, CM-1-2-4-1) | secondary distribution (CM-1-1-3-8)</t>
+        </is>
+      </c>
+      <c r="R222" t="inlineStr">
+        <is>
+          <t>Coordinate S&amp;T-Sourced Primary Transportation</t>
+        </is>
+      </c>
+      <c r="T222" t="inlineStr">
+        <is>
+          <t>Batch 19 (2026-09-20). Deterministic handoff (Hamid, batch 19): confirmed movement requirements go to Physical Distribution Scheduling, which owns primary movement nomination and shipper-side administration (batch 05), and to Actualizations for commercial movement actuals — the handoff is unconditional, making the batch 05 boundary enforceable. Coordinate-not-execute per batch 18. Normalized label 'Coordinate S&amp;T-Sourced Primary Transportation' queued. APQC 'Manage bulk transportation' is a WEAK generic match.</t>
+        </is>
+      </c>
+      <c r="U222" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V222" s="5" t="inlineStr">
+        <is>
+          <t>S&amp;T-sourced product moved on managed arrangements, handed unconditionally to the processes that schedule and account for it.</t>
+        </is>
+      </c>
+      <c r="W222" s="5" t="inlineStr">
+        <is>
+          <t>SRC-ORP-DPSC-001 | SRC-DOE-RPPL-001</t>
+        </is>
+      </c>
       <c r="X222" s="5" t="n"/>
-      <c r="Y222" s="5" t="n"/>
-      <c r="Z222" s="5" t="n"/>
-      <c r="AA222" s="5" t="n"/>
-      <c r="AB222" s="5" t="n"/>
-      <c r="AC222" s="5" t="n"/>
+      <c r="Y222" s="5" t="inlineStr">
+        <is>
+          <t>Fulfillment plans (CM-1-2-6-3-2) | carrier contracts and capacity (CM-1-2-1-2-9) | movement status from carriers</t>
+        </is>
+      </c>
+      <c r="Z222" s="5" t="inlineStr">
+        <is>
+          <t>Coordinated transport arrangements with confirmed requirements provided to scheduling and actualization</t>
+        </is>
+      </c>
+      <c r="AA222" s="5" t="inlineStr">
+        <is>
+          <t>follows: Manage Replenishment | uses-input: Manage Carrier Contracts | precedes: Physical Distribution Scheduling</t>
+        </is>
+      </c>
+      <c r="AB222" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC222" s="5" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AD222" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>

--- a/business_architecture/ontology/build/output/step3c-definition-authoring-workbook.xlsx
+++ b/business_architecture/ontology/build/output/step3c-definition-authoring-workbook.xlsx
@@ -31180,18 +31180,80 @@
           <t>no meaningful APQC candidate</t>
         </is>
       </c>
-      <c r="U223" s="5" t="n"/>
-      <c r="V223" s="5" t="n"/>
-      <c r="W223" s="5" t="n"/>
+      <c r="N223" t="inlineStr">
+        <is>
+          <t>Negotiate, maintain commercial requirements for, and coordinate lifecycle changes to product-side agreements that enable product exchanges, customer delivery commitments, and storage/throughput access, so dependent supply, distribution, and settlement processes operate against current commercially agreed terms.</t>
+        </is>
+      </c>
+      <c r="O223" t="inlineStr">
+        <is>
+          <t>Covers the commercial-agreement lifecycle for three product-side agreement families: product exchange agreements including their terms, entitlement rules, and contractual imbalance treatment (CM-1-2-7-1-1); customer-facing product transport and delivery agreements (CM-1-2-7-1-2, under the batch 09 boundary rule); and negotiation of storage and throughput agreements (CM-1-2-7-1-3, under the batch 09 storage split). The handoff model: commercial negotiation and commercial-requirement ownership sit in this cluster; legal drafting, legal review, and execution authority with Legal &amp; Corporate Communications under its locked rule; the controlled contract record, document lifecycle, and renewal/termination/novation administration with Contract Management (CM-1-2-1-2) where the agreement is within its trading-contract scope; deal capture with Trade Capture (CM-1-2-1-3); operational use with Supply Operations, Distribution, and the relevant operating domains; settlement with Settlements (CM-1-2-4-1). Excludes trading contract administration and the controlled contract record (CM-1-2-1-2); legal services and execution authority (Legal &amp; Corporate Communications, locked rule); deal capture (CM-1-2-1-3); settlement (CM-1-2-4-1); operational exchange utilization (CM-1-2-6-2-2, batch 19).</t>
+        </is>
+      </c>
+      <c r="P223" t="inlineStr">
+        <is>
+          <t>Negotiate product exchange agreements with entitlement and imbalance terms | negotiate and maintain commercial requirements for customer-facing delivery agreements | negotiate storage and throughput agreements | coordinate lifecycle changes and keep dependent processes supplied with current terms</t>
+        </is>
+      </c>
+      <c r="Q223" t="inlineStr">
+        <is>
+          <t>Contract record and lifecycle administration (CM-1-2-1-2) | legal services and execution authority (Legal &amp; Corporate Communications, locked rule) | deal capture (CM-1-2-1-3) | settlement (CM-1-2-4-1) | operational exchange utilization (CM-1-2-6-2-2)</t>
+        </is>
+      </c>
+      <c r="R223" t="inlineStr">
+        <is>
+          <t>Product Commercial Agreements</t>
+        </is>
+      </c>
+      <c r="T223" t="inlineStr">
+        <is>
+          <t>Batch 20 (2026-09-20). Concept-type: process — one agreement-lifecycle discipline across three agreement families (batch 09 pattern). Handoff model (Hamid, batch 20): negotiation and commercial requirements here; record administration with Contract Management where in trading scope — the two never both 'administer' the same lifecycle. Receiving end of the batch 09 exclusions and the batch 08/14/19 exchange bindings. APQC 'Establish lifting agreements' scored NONE; comparative only.</t>
+        </is>
+      </c>
+      <c r="U223" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V223" s="5" t="inlineStr">
+        <is>
+          <t>Every exchange, delivery, and storage arrangement running on current, correct, commercially negotiated terms.</t>
+        </is>
+      </c>
+      <c r="W223" s="5" t="inlineStr">
+        <is>
+          <t>SRC-EIA-GLOSS-001 | SRC-APQC-PCF-001</t>
+        </is>
+      </c>
       <c r="X223" s="5" t="n"/>
-      <c r="Y223" s="5" t="n"/>
-      <c r="Z223" s="5" t="n"/>
-      <c r="AA223" s="5" t="n"/>
-      <c r="AB223" s="5" t="n"/>
-      <c r="AC223" s="5" t="n"/>
+      <c r="Y223" s="5" t="inlineStr">
+        <is>
+          <t>Commercial requirements from demand, supply, and network processes | counterparty proposals | legal review (Legal &amp; Corporate Communications)</t>
+        </is>
+      </c>
+      <c r="Z223" s="5" t="inlineStr">
+        <is>
+          <t>Negotiated product-side commercial agreements with maintained commercial requirements</t>
+        </is>
+      </c>
+      <c r="AA223" s="5" t="inlineStr">
+        <is>
+          <t>enables: Manage Refined Product Exchanges | enables: Supply Operations | informed-by: Contract Management</t>
+        </is>
+      </c>
+      <c r="AB223" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC223" s="5" t="inlineStr">
+        <is>
+          <t>event-driven</t>
+        </is>
+      </c>
       <c r="AD223" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -31259,18 +31321,75 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U224" s="5" t="n"/>
-      <c r="V224" s="5" t="n"/>
-      <c r="W224" s="5" t="n"/>
+      <c r="N224" t="inlineStr">
+        <is>
+          <t>Negotiate and administer product exchange agreements — the terms under which product is exchanged with other suppliers across locations and time — owning the entitlement rules, differentials, and contractual imbalance calculation and treatment, and recommending or making delegated commercial decisions on imbalance resolution, so exchange supply operates against governed agreements with controlled balances.</t>
+        </is>
+      </c>
+      <c r="O224" t="inlineStr">
+        <is>
+          <t>Covers the exchange-agreement lifecycle: negotiating exchange agreements with counterparty suppliers — locations, products, volumes, differentials and location/quality adjustments, entitlement rules, imbalance provisions, and termination terms; administering agreements through amendments and renewals; performing the contractual imbalance calculation and treatment the agreements provide (batch 14 binding); recommending or making delegated commercial decisions on imbalance resolution, make-up, cash-out, or other contractual remedies under the governing agreement — authority thresholds, Finance impact, and Legal review apply per the documented delegation; and supplying entitlement and position data to the operational utilization process. The batch 19 split: operational visibility and proposed utilization at Manage Refined Product Exchanges (CM-1-2-6-2-2); contractual calculation and commercial decisions here. 'Exchange' means product exchange arrangements, not futures exchanges (CM-1-2-1-3-4, batch 08). Exchange settlement executes per the agreements at Settlements (CM-1-2-4-1-2, batch 14). Excludes operational utilization planning (CM-1-2-6-2-2); futures-exchange trading (CM-1-2-1-3-4); settlement execution (CM-1-2-4-1); legal drafting and execution authority (Legal &amp; Corporate Communications); movement scheduling (CM-1-1-3-6).</t>
+        </is>
+      </c>
+      <c r="P224" t="inlineStr">
+        <is>
+          <t>Negotiate exchange agreements with entitlement, differential, and imbalance terms | administer amendments and renewals | perform contractual imbalance calculation and treatment and recommend or make delegated decisions on remedies | supply entitlement and position data to operational utilization</t>
+        </is>
+      </c>
+      <c r="Q224" t="inlineStr">
+        <is>
+          <t>Operational utilization (CM-1-2-6-2-2) | futures-exchange trading (CM-1-2-1-3-4) | settlement execution (CM-1-2-4-1) | legal drafting and execution (Legal &amp; Corporate Communications) | movement scheduling (CM-1-1-3-6)</t>
+        </is>
+      </c>
+      <c r="T224" t="inlineStr">
+        <is>
+          <t>Batch 20 (2026-09-20). Receiving row of six bindings (batches 08/09/14/18/19): 'not product exchange agreements' (futures split, b08); imbalance treatment administered here (b14); contractual imbalance calculation, commercial decision, agreement administration, and settlement conditions here versus operational visibility at CM-1-2-6-2-2 (b19). Delegated-authority rule (Hamid, batch 20): imbalance remedies are recommended or decided within the documented delegation and the governing agreement, respecting authority thresholds, Finance impact, and Legal review. The entitlement, not a parcel, is the governed object (b13 entitlement concept). APQC 'Manage product images' is a false lexical match.</t>
+        </is>
+      </c>
+      <c r="U224" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V224" s="5" t="inlineStr">
+        <is>
+          <t>Exchange supply governed by sound agreements, with every balance calculated, decided under the right authority, and controlled under contract.</t>
+        </is>
+      </c>
+      <c r="W224" s="5" t="inlineStr">
+        <is>
+          <t>SRC-EIA-GLOSS-001 | SRC-APQC-PCF-001</t>
+        </is>
+      </c>
       <c r="X224" s="5" t="n"/>
-      <c r="Y224" s="5" t="n"/>
-      <c r="Z224" s="5" t="n"/>
-      <c r="AA224" s="5" t="n"/>
-      <c r="AB224" s="5" t="n"/>
-      <c r="AC224" s="5" t="n"/>
+      <c r="Y224" s="5" t="inlineStr">
+        <is>
+          <t>Exchange requirements from demand and supply processes (CM-1-2-6-2-2, CM-1-2-6-3) | counterparty proposals | lifted and delivered volumes (CM-1-2-3-1)</t>
+        </is>
+      </c>
+      <c r="Z224" s="5" t="inlineStr">
+        <is>
+          <t>Governed exchange agreements with calculated balances, delegated decisions, and current entitlement data</t>
+        </is>
+      </c>
+      <c r="AA224" s="5" t="inlineStr">
+        <is>
+          <t>enables: Manage Refined Product Exchanges | informed-by: Actualizations | precedes: Settle Products</t>
+        </is>
+      </c>
+      <c r="AB224" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC224" s="5" t="inlineStr">
+        <is>
+          <t>event-driven</t>
+        </is>
+      </c>
       <c r="AD224" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -31338,18 +31457,75 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U225" s="5" t="n"/>
-      <c r="V225" s="5" t="n"/>
-      <c r="W225" s="5" t="n"/>
+      <c r="N225" t="inlineStr">
+        <is>
+          <t>Negotiate and administer customer-facing product transport and delivery agreements — the delivery terms linked to product sale and marketing arrangements, including delivered pricing bases, delivery service commitments, and receiving requirements — so product deliveries to customers operate against current, correct commercial delivery terms.</t>
+        </is>
+      </c>
+      <c r="O225" t="inlineStr">
+        <is>
+          <t>Covers the customer-facing side of the batch 09 boundary rule: negotiating and administering the transport and delivery agreements connected to product sale and marketing arrangements — delivered-price and freight bases, delivery windows and service commitments, receiving-facility requirements, and delivery-related liability terms — through amendments and renewals, keeping order management, secondary distribution, and settlement supplied with current terms. The classification test is the agreement's commercial purpose, not the physical transport mode: a truck contract can be a carrier agreement when it procures capacity or rates for supply movements (Manage Carrier Contracts, CM-1-2-1-2-9), or a customer-facing delivery agreement when it forms part of a product-sale commitment (here) — the batch 09 rule applied to every mode. Excludes carrier contracts for supply and trading movements (CM-1-2-1-2-9, batch 09 rule); customer order capture and fulfillment (CM-1-3-7); secondary delivery scheduling (CM-1-1-3-8); legal drafting and execution (Legal &amp; Corporate Communications); transportation deal capture (CM-1-2-1-3-9).</t>
+        </is>
+      </c>
+      <c r="P225" t="inlineStr">
+        <is>
+          <t>Negotiate customer-facing delivery and transport terms linked to product sales | administer amendments and renewals | maintain delivered-price, service, and receiving terms | keep order, distribution, and settlement processes supplied with current terms</t>
+        </is>
+      </c>
+      <c r="Q225" t="inlineStr">
+        <is>
+          <t>Carrier contracts for supply/trading movements (CM-1-2-1-2-9) | order capture and fulfillment (CM-1-3-7) | secondary delivery scheduling (CM-1-1-3-8) | legal drafting and execution (Legal &amp; Corporate Communications) | transportation deal capture (CM-1-2-1-3-9)</t>
+        </is>
+      </c>
+      <c r="T225" t="inlineStr">
+        <is>
+          <t>Batch 20 (2026-09-20). Receiving row of the batch 09 boundary rule with Hamid's classification test recorded verbatim: the agreement's commercial purpose decides — capacity/rates for supply movements versus part of a product-sale commitment — never the transport mode alone. APQC 'Manage product images' is a false lexical match.</t>
+        </is>
+      </c>
+      <c r="U225" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V225" s="5" t="inlineStr">
+        <is>
+          <t>Every customer delivery running on negotiated, current delivery terms.</t>
+        </is>
+      </c>
+      <c r="W225" s="5" t="inlineStr">
+        <is>
+          <t>SRC-EIA-GLOSS-001 | SRC-APQC-PCF-001</t>
+        </is>
+      </c>
       <c r="X225" s="5" t="n"/>
-      <c r="Y225" s="5" t="n"/>
-      <c r="Z225" s="5" t="n"/>
-      <c r="AA225" s="5" t="n"/>
-      <c r="AB225" s="5" t="n"/>
-      <c r="AC225" s="5" t="n"/>
+      <c r="Y225" s="5" t="inlineStr">
+        <is>
+          <t>Product sale and marketing arrangements (CM-1-3) | delivery capability and cost data | counterparty and customer proposals</t>
+        </is>
+      </c>
+      <c r="Z225" s="5" t="inlineStr">
+        <is>
+          <t>Administered customer-facing transport and delivery agreements</t>
+        </is>
+      </c>
+      <c r="AA225" s="5" t="inlineStr">
+        <is>
+          <t>informed-by: Manage Carrier Contracts | enables: Secondary Distribution Management | enables: Settlements</t>
+        </is>
+      </c>
+      <c r="AB225" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC225" s="5" t="inlineStr">
+        <is>
+          <t>event-driven</t>
+        </is>
+      </c>
       <c r="AD225" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -31417,18 +31593,75 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U226" s="5" t="n"/>
-      <c r="V226" s="5" t="n"/>
-      <c r="W226" s="5" t="n"/>
+      <c r="N226" t="inlineStr">
+        <is>
+          <t>Negotiate storage and throughput agreements — leased tankage, cavern capacity, terminal throughput, and handling arrangements — establishing capacity, fee structures, service levels, and quality-protection terms, obtaining required commercial approvals, coordinating execution through Legal and authorized signatories, and handing executed agreements to the contract record and deal capture, so storage and throughput capacity is secured on sound commercial terms.</t>
+        </is>
+      </c>
+      <c r="O226" t="inlineStr">
+        <is>
+          <t>Covers the negotiation position in the batch 09 storage split: identifying storage and throughput needs with the supply and trading processes; negotiating capacity, term, fee structures (throughput, storage, blending, handling, minimums), service levels, and quality-protection provisions; obtaining required commercial approvals and coordinating execution of the agreement through Legal and authorized signatories — execution authority remains with Legal &amp; Corporate Communications and the authorized signatories, not this process. On execution the agreement hands off per the split: the contract record is maintained by Manage Storage Contract (CM-1-2-1-2-10); commercially distinct capacity transactions are captured by Capture Storage Deals (CM-1-2-1-3-5) — per the batch 09 caveat, not every storage agreement results in a separately captured deal, only where capacity is commercially distinct, traded, allocated, acquired, released, or modeled as a transaction; company stock in third-party facilities is administered by Manage Third Party Storage (CM-1-1-3-7-11); charges settle at Settle Terminal/Storage (CM-1-2-4-1-14). Excludes contract record administration (CM-1-2-1-2-10); capacity deal capture (CM-1-2-1-3-5); third-party storage inventory administration (CM-1-1-3-7-11); storage settlement (CM-1-2-4-1-14); legal drafting and execution authority (Legal &amp; Corporate Communications).</t>
+        </is>
+      </c>
+      <c r="P226" t="inlineStr">
+        <is>
+          <t>Identify storage and throughput needs with supply and trading processes | negotiate capacity, fees, service levels, and quality-protection terms | obtain commercial approvals and coordinate execution through Legal and authorized signatories | hand executed agreements to the contract record and deal capture</t>
+        </is>
+      </c>
+      <c r="Q226" t="inlineStr">
+        <is>
+          <t>Contract record administration (CM-1-2-1-2-10) | capacity deal capture (CM-1-2-1-3-5) | third-party storage administration (CM-1-1-3-7-11) | storage settlement (CM-1-2-4-1-14) | legal drafting and execution authority (Legal &amp; Corporate Communications)</t>
+        </is>
+      </c>
+      <c r="T226" t="inlineStr">
+        <is>
+          <t>Batch 20 (2026-09-20). Receiving row of the batch 09 three-way storage split, applied verbatim, with Hamid's execution correction: this process obtains commercial approvals and coordinates execution; Legal and authorized signatories execute. The batch 09 capture caveat retained: a captured storage deal exists only where capacity is commercially distinct. APQC 'Negotiate service-level agreements' is a WEAK IT candidate.</t>
+        </is>
+      </c>
+      <c r="U226" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V226" s="5" t="inlineStr">
+        <is>
+          <t>Storage and throughput capacity secured when needed, on terms that protect product and economics.</t>
+        </is>
+      </c>
+      <c r="W226" s="5" t="inlineStr">
+        <is>
+          <t>SRC-EI-HM32-001 | SRC-APQC-PCF-001</t>
+        </is>
+      </c>
       <c r="X226" s="5" t="n"/>
-      <c r="Y226" s="5" t="n"/>
-      <c r="Z226" s="5" t="n"/>
-      <c r="AA226" s="5" t="n"/>
-      <c r="AB226" s="5" t="n"/>
-      <c r="AC226" s="5" t="n"/>
+      <c r="Y226" s="5" t="inlineStr">
+        <is>
+          <t>Capacity needs from supply, trading, and network processes | market capacity availability and rates | quality-protection requirements</t>
+        </is>
+      </c>
+      <c r="Z226" s="5" t="inlineStr">
+        <is>
+          <t>Executed storage and throughput agreements handed to record and capture</t>
+        </is>
+      </c>
+      <c r="AA226" s="5" t="inlineStr">
+        <is>
+          <t>precedes: Manage Storage Contract | precedes: Capture Storage Deals | informed-by: Supply Operations</t>
+        </is>
+      </c>
+      <c r="AB226" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC226" s="5" t="inlineStr">
+        <is>
+          <t>event-driven</t>
+        </is>
+      </c>
       <c r="AD226" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -31496,18 +31729,80 @@
           <t>no meaningful APQC candidate</t>
         </is>
       </c>
-      <c r="U227" s="5" t="n"/>
-      <c r="V227" s="5" t="n"/>
-      <c r="W227" s="5" t="n"/>
+      <c r="N227" t="inlineStr">
+        <is>
+          <t>The capability to operate and maintain company-managed marketing and distribution terminals, loading facilities, and associated distribution fleet assets where the business unit is the designated operating entity, including site safety execution, fleet capability management, and site-asset integrity and availability.</t>
+        </is>
+      </c>
+      <c r="O227" t="inlineStr">
+        <is>
+          <t>Covers the management of company-managed marketing and distribution terminal and fleet operations under the Q2 reading: site safety management (CM-1-2-7-2-1), fleet management (CM-1-2-7-2-2), and site asset management (CM-1-2-7-2-3), applied where the Marketing/Distribution business is the designated operating entity. Asset ownership alone does not determine scope: this capability applies only where the Marketing/Distribution business is operationally accountable for the site or fleet — Refining-operated, Midstream-operated, third-party-operated, and centrally operated assets remain with their designated operating domains or providers, and where the company owns but does not operate a facility, its interest is held through agreements (CM-1-2-7-1-3), source-point coordination (CM-1-2-6-3-1), storage administration (CM-1-1-3-7-11), and settlement (CM-1-2-4-1-14). The capability is located in the Supply &amp; Trading taxonomy because it supports marketing/distribution supply operations; its operational delivery may sit in a dedicated terminal operations, distribution operations, fleet, Midstream, engineering, or shared-services organization, depending on asset ownership and operating accountability. Scheduling remains with its owners (CM-1-1-3-6, CM-1-1-3-8, batch 05); EHS policy, regulatory reporting, and filings with EHS &amp; Government Reporting under its locked rule. Excludes Refining-, Midstream-, centrally-, and third-party-operated assets (their designated operators, locked rules); movement and delivery scheduling (CM-1-1-3-6, CM-1-1-3-8); EHS policy and regulatory reporting (EHS &amp; Government Reporting, locked rule); storage/terminal commercial agreements (CM-1-2-7-1-3).</t>
+        </is>
+      </c>
+      <c r="P227" t="inlineStr">
+        <is>
+          <t>Operate site safety programs within the enterprise EHS framework at company-managed sites | manage own and contracted fleet capability and compliance | manage site-asset integrity coordination and availability | keep company-managed operations safe, compliant, and available</t>
+        </is>
+      </c>
+      <c r="Q227" t="inlineStr">
+        <is>
+          <t>Refining-, Midstream-, centrally-, and third-party-operated assets (designated operators, locked rules) | movement and delivery scheduling (CM-1-1-3-6, CM-1-1-3-8) | EHS policy and regulatory reporting (EHS &amp; Government Reporting, locked rule) | storage/terminal agreements (CM-1-2-7-1-3)</t>
+        </is>
+      </c>
+      <c r="R227" t="inlineStr">
+        <is>
+          <t>Company-Managed Terminal &amp; Fleet Operations</t>
+        </is>
+      </c>
+      <c r="T227" t="inlineStr">
+        <is>
+          <t>Batch 20 (2026-09-20). Q2 decision (Hamid, narrowed): this capability applies where the company is the designated operator — never categorically 'the terminal operator', since the same legal entity may own a facility operated by a third party, Midstream, Refining, a joint venture, or a terminal services company. Every prior operator exclusion is preserved: for facilities operated elsewhere, the operator remains external to this cluster. Concept-type: capability per the batch 11 test. Which terminals, tanks, racks, and fleet assets are actually company-managed by Marketing/Distribution is an asset-inventory follow-up carried in the batch 20 PR. APQC 'Analyze internal operations' scored NONE; comparative only.</t>
+        </is>
+      </c>
+      <c r="U227" s="5" t="inlineStr">
+        <is>
+          <t>capability</t>
+        </is>
+      </c>
+      <c r="V227" s="5" t="inlineStr">
+        <is>
+          <t>Company-managed terminals and fleet that are safe, compliant, and reliably available.</t>
+        </is>
+      </c>
+      <c r="W227" s="5" t="inlineStr">
+        <is>
+          <t>SRC-OSHA-PSM-001 | SRC-EI-HM32-001</t>
+        </is>
+      </c>
       <c r="X227" s="5" t="n"/>
-      <c r="Y227" s="5" t="n"/>
-      <c r="Z227" s="5" t="n"/>
-      <c r="AA227" s="5" t="n"/>
-      <c r="AB227" s="5" t="n"/>
-      <c r="AC227" s="5" t="n"/>
+      <c r="Y227" s="5" t="inlineStr">
+        <is>
+          <t>Enterprise EHS framework and policies | fleet and asset condition data | supply and distribution requirements</t>
+        </is>
+      </c>
+      <c r="Z227" s="5" t="inlineStr">
+        <is>
+          <t>Safely and compliantly operated company-managed terminals and fleet</t>
+        </is>
+      </c>
+      <c r="AA227" s="5" t="inlineStr">
+        <is>
+          <t>enables: Secondary Distribution Management | enables: Supply Operations | governed-by: Develop Compliance Policies &amp; Procedures</t>
+        </is>
+      </c>
+      <c r="AB227" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC227" s="5" t="inlineStr">
+        <is>
+          <t>continuous</t>
+        </is>
+      </c>
       <c r="AD227" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -31575,18 +31870,75 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U228" s="5" t="n"/>
-      <c r="V228" s="5" t="n"/>
-      <c r="W228" s="5" t="n"/>
+      <c r="N228" t="inlineStr">
+        <is>
+          <t>Operate the safety programs at company-managed terminal and fleet operations — hazardous-materials handling safety, staff safety training and procedures, and contractor safety qualification and control — executing the enterprise EHS framework at site level, so people and operations at company-managed facilities are protected and compliant.</t>
+        </is>
+      </c>
+      <c r="O228" t="inlineStr">
+        <is>
+          <t>Covers line-management safety execution at company-managed sites: hazardous-materials handling and storage safety procedures for the products handled; staff safety training, competence, and procedure compliance; contractor safety qualification, induction, and work control; site safety inspections and observations; participating in site incident response, fact gathering, initial notification, and corrective-action execution, and providing required incident information to EHS for governed investigation, reportability assessment, and regulatory reporting. Where an operation is subject to applicable process-safety regulations or standards — such as OSHA PSM in the United States where regulated substances meet threshold conditions — the site executes applicable operating controls within the enterprise EHS/process-safety framework. Executes-within-framework: EHS &amp; Government Reporting owns safety policy, the EHS management framework, investigation governance, reportability assessment, regulatory reporting, and filings under its locked rule; this process operates the programs at site level and feeds it. Excludes EHS policy, framework, investigation governance, reportability assessment, and regulatory reporting (EHS &amp; Government Reporting, locked rule); separately established emergency-response ownership; third-party site safety (their operators); fleet transport-safety compliance administration (CM-1-2-7-2-2).</t>
+        </is>
+      </c>
+      <c r="P228" t="inlineStr">
+        <is>
+          <t>Operate hazardous-materials handling safety procedures | run staff safety training and procedure compliance | qualify, induct, and control contractors | participate in incident response and provide required incident information to EHS</t>
+        </is>
+      </c>
+      <c r="Q228" t="inlineStr">
+        <is>
+          <t>EHS policy, investigation governance, reportability assessment, and regulatory reporting (EHS &amp; Government Reporting, locked rule) | separately established emergency-response ownership | third-party site safety (their operators) | fleet transport-safety administration (CM-1-2-7-2-2)</t>
+        </is>
+      </c>
+      <c r="T228" t="inlineStr">
+        <is>
+          <t>Batch 20 (2026-09-20). Q3 decision with Hamid's incident split: the site executes response, gathers facts, notifies, and executes corrective actions; EHS governs investigation method, assesses reportability, and reports — execution versus accountability. Process-safety phrasing conditioned: applicable regimes (such as OSHA PSM where regulated substances meet threshold conditions) are executed within the enterprise EHS/process-safety framework; jurisdiction-specific. Executes-within-policy (batch 07/11/15 pattern). APQC 'Manage materials master lists' is a false lexical match.</t>
+        </is>
+      </c>
+      <c r="U228" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V228" s="5" t="inlineStr">
+        <is>
+          <t>Nobody hurt, nothing released, everything evidenced — at every company-managed site.</t>
+        </is>
+      </c>
+      <c r="W228" s="5" t="inlineStr">
+        <is>
+          <t>SRC-OSHA-PSM-001 | SRC-EI-HM32-001</t>
+        </is>
+      </c>
       <c r="X228" s="5" t="n"/>
-      <c r="Y228" s="5" t="n"/>
-      <c r="Z228" s="5" t="n"/>
-      <c r="AA228" s="5" t="n"/>
-      <c r="AB228" s="5" t="n"/>
-      <c r="AC228" s="5" t="n"/>
+      <c r="Y228" s="5" t="inlineStr">
+        <is>
+          <t>Enterprise EHS framework and policies | site hazard and product data | contractor and staff records</t>
+        </is>
+      </c>
+      <c r="Z228" s="5" t="inlineStr">
+        <is>
+          <t>Operated site safety programs with incident information and evidence into the EHS framework</t>
+        </is>
+      </c>
+      <c r="AA228" s="5" t="inlineStr">
+        <is>
+          <t>governed-by: Terminal Operations Management | enables: Manage Site Assets (Tank, Rack, Etc.) | informed-by: Manage Fleet (Own/Third Party)</t>
+        </is>
+      </c>
+      <c r="AB228" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC228" s="5" t="inlineStr">
+        <is>
+          <t>continuous</t>
+        </is>
+      </c>
       <c r="AD228" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -31649,18 +32001,75 @@
           <t>strong APQC candidate but no validator agreed</t>
         </is>
       </c>
-      <c r="U229" s="5" t="n"/>
-      <c r="V229" s="5" t="n"/>
-      <c r="W229" s="5" t="n"/>
+      <c r="N229" t="inlineStr">
+        <is>
+          <t>Manage the capacity, readiness, safety, compliance, maintenance, and performance of company-operated and contracted road-delivery fleet resources so Secondary Distribution Management can assign safe, qualified, and available vehicles and carriers to approved delivery schedules.</t>
+        </is>
+      </c>
+      <c r="O229" t="inlineStr">
+        <is>
+          <t>Covers fleet management for product distribution: fleet-capacity planning; vehicle standards, inspections, and maintenance-program governance; driver qualification and safety compliance; carrier qualification and carrier-performance management; transport-safety and hazardous-materials compliance programs (in the United States, the FMCSA motor-carrier safety regime under 49 CFR Parts 300-399 and the applicable PHMSA Hazardous Materials Regulations for cargo tanks; state and jurisdictional requirements additional); and fleet readiness. Where the company operates its own fleet, it provides the vehicles and drivers that execute scheduled deliveries; where third parties operate the fleet, it manages contractual qualification and performance. Route, load, and delivery-window scheduling and dispatch decisioning remain with Secondary Distribution Management (CM-1-1-3-8, batch 05). Excludes route, load, and delivery-window scheduling and dispatch decisioning (CM-1-1-3-8); customer order capture (CM-1-3-7); carrier contract negotiation where that belongs to Contract Management (CM-1-2-1-2-9); customer delivery terms (CM-1-2-7-1-2); marine, rail, and pipeline capacity (their owning processes); fleet financing and capital decisions (Finance, accountable owners); settlement (CM-1-2-4-1).</t>
+        </is>
+      </c>
+      <c r="P229" t="inlineStr">
+        <is>
+          <t>Plan fleet capacity across own and contracted resources | govern vehicle standards, inspections, and maintenance programs | administer driver qualification and transport-safety compliance | qualify and manage carriers and provide execution-ready fleet resources to scheduling</t>
+        </is>
+      </c>
+      <c r="Q229" t="inlineStr">
+        <is>
+          <t>Route, load, and dispatch scheduling (CM-1-1-3-8) | order capture (CM-1-3-7) | carrier contract negotiation (CM-1-2-1-2-9) | customer delivery terms (CM-1-2-7-1-2) | marine, rail, and pipeline capacity (owning processes) | fleet financing and capital decisions (Finance, accountable owners)</t>
+        </is>
+      </c>
+      <c r="T229" t="inlineStr">
+        <is>
+          <t>Batch 20 (2026-09-20). Hamid's consistency correction applied: where the company operates its own fleet, this function's vehicles and drivers execute the scheduled deliveries — execution is not categorically excluded; what stays excluded is the scheduling and dispatch decision (CM-1-1-3-8, batch 05 split). US transport-safety context spans two regimes: FMCSA motor-carrier safety regulations and PHMSA hazardous-materials/cargo-tank rules — different agencies; state, hours-of-service, CDL, drug/alcohol, inspection, and insurance requirements apply additionally; jurisdiction-specific elsewhere. Dispatch execution ownership after scheduling is an operating-model follow-up carried in the batch 20 PR. APQC 'Manage third party bulk storage' scored STRONG at 3b but NO SOURCE — honored; storage candidate, not fleet.</t>
+        </is>
+      </c>
+      <c r="U229" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V229" s="5" t="inlineStr">
+        <is>
+          <t>A safe, compliant, available fleet behind every scheduled delivery — driving it where the company operates it.</t>
+        </is>
+      </c>
+      <c r="W229" s="5" t="inlineStr">
+        <is>
+          <t>SRC-FMCSA-001 | SRC-EI-HM32-001</t>
+        </is>
+      </c>
       <c r="X229" s="5" t="n"/>
-      <c r="Y229" s="5" t="n"/>
-      <c r="Z229" s="5" t="n"/>
-      <c r="AA229" s="5" t="n"/>
-      <c r="AB229" s="5" t="n"/>
-      <c r="AC229" s="5" t="n"/>
+      <c r="Y229" s="5" t="inlineStr">
+        <is>
+          <t>Delivery demand and schedules (CM-1-1-3-8) | vehicle condition and compliance data | driver and carrier records | applicable transport regulations</t>
+        </is>
+      </c>
+      <c r="Z229" s="5" t="inlineStr">
+        <is>
+          <t>Execution-ready, compliant fleet capacity assigned through scheduling</t>
+        </is>
+      </c>
+      <c r="AA229" s="5" t="inlineStr">
+        <is>
+          <t>enables: Secondary Distribution Management | governed-by: Terminal Operations Management | informed-by: Manage Safety (Materials, Staff, Contractor)</t>
+        </is>
+      </c>
+      <c r="AB229" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC229" s="5" t="inlineStr">
+        <is>
+          <t>continuous</t>
+        </is>
+      </c>
       <c r="AD229" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -31723,18 +32132,75 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U230" s="5" t="n"/>
-      <c r="V230" s="5" t="n"/>
-      <c r="W230" s="5" t="n"/>
+      <c r="N230" t="inlineStr">
+        <is>
+          <t>Manage the operational availability, condition, integrity coordination, and business-use allocation of company-managed marketing and distribution terminal assets — including tanks, racks, meters, additive systems, vapor-recovery equipment, and supporting infrastructure — within enterprise engineering, maintenance, and EHS standards.</t>
+        </is>
+      </c>
+      <c r="O230" t="inlineStr">
+        <is>
+          <t>Covers site asset management at company-managed terminals: asset registers and condition monitoring; coordinating inspection, maintenance, and integrity requirements with the accountable engineering and maintenance providers (in-service aboveground storage tank inspection follows API 653 practice where applicable; measurement equipment per the applicable API MPMS chapters); maintenance planning with operations; maintaining business-use configuration and availability information for racks, bays, tanks, and associated assets and coordinating operational allocation with the designated terminal and scheduling owners; and asset performance and availability management. The process coordinates inspection, maintenance, and integrity requirements with accountable engineering and maintenance providers; it does not itself establish engineering standards, approve technical integrity methodology, perform regulated inspection certification, own capital-project decisions, or define measurement methodology. Excludes engineering standards and integrity methodology (enterprise engineering function); regulated inspection certification (certified inspectors/providers); capital investment decisions and projects (enterprise capital process, accountable owners); Refining- and Midstream-operated assets (locked rules); measurement methodology (CM-1-1-3-7-4); site safety programs (CM-1-2-7-2-1).</t>
+        </is>
+      </c>
+      <c r="P230" t="inlineStr">
+        <is>
+          <t>Maintain asset registers and condition monitoring | coordinate inspection, maintenance, and integrity requirements with accountable engineering and maintenance providers | plan maintenance with operations | maintain business-use configuration and availability information and coordinate allocation with designated owners</t>
+        </is>
+      </c>
+      <c r="Q230" t="inlineStr">
+        <is>
+          <t>Engineering standards and integrity methodology (enterprise engineering) | regulated inspection certification (certified providers) | capital decisions and projects (enterprise capital process) | Refining/Midstream assets (locked rules) | measurement methodology (CM-1-1-3-7-4) | site safety programs (CM-1-2-7-2-1)</t>
+        </is>
+      </c>
+      <c r="T230" t="inlineStr">
+        <is>
+          <t>Batch 20 (2026-09-20). Coordinates-integrity-and-availability (Hamid, batch 20): the process coordinates with accountable engineering and maintenance providers and maintains business-use configuration; standards, certification, methodology, and capital stay with their owners. API 653 anchors in-service aboveground storage tank inspection practice for API 650/12C-constructed tanks; applicability is tank- and jurisdiction-specific and the enterprise's engineering standards govern. Whether this row owns business-use allocation or only maintains availability data for a scheduling owner is an operating-model follow-up carried in the batch 20 PR. APQC 'Manage rack allocations' is a WEAK partial match, comparative only.</t>
+        </is>
+      </c>
+      <c r="U230" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V230" s="5" t="inlineStr">
+        <is>
+          <t>Every tank, rack, and meter at company-managed sites fit for service when operations needs it.</t>
+        </is>
+      </c>
+      <c r="W230" s="5" t="inlineStr">
+        <is>
+          <t>SRC-API-653-001 | SRC-API-MPMS-001</t>
+        </is>
+      </c>
       <c r="X230" s="5" t="n"/>
-      <c r="Y230" s="5" t="n"/>
-      <c r="Z230" s="5" t="n"/>
-      <c r="AA230" s="5" t="n"/>
-      <c r="AB230" s="5" t="n"/>
-      <c r="AC230" s="5" t="n"/>
+      <c r="Y230" s="5" t="inlineStr">
+        <is>
+          <t>Asset condition and inspection data | engineering and maintenance provider programs | operations requirements | product allocation needs</t>
+        </is>
+      </c>
+      <c r="Z230" s="5" t="inlineStr">
+        <is>
+          <t>Available, integrity-coordinated site assets with maintained business-use configuration</t>
+        </is>
+      </c>
+      <c r="AA230" s="5" t="inlineStr">
+        <is>
+          <t>governed-by: Terminal Operations Management | informed-by: Manage Safety (Materials, Staff, Contractor) | enables: Supply Operations</t>
+        </is>
+      </c>
+      <c r="AB230" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC230" s="5" t="inlineStr">
+        <is>
+          <t>continuous</t>
+        </is>
+      </c>
       <c r="AD230" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -54021,7 +54487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I44"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -54070,6 +54536,7 @@
         </is>
       </c>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
@@ -55851,6 +56318,100 @@
         </is>
       </c>
       <c r="I44" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>SRC-FMCSA-001</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>U.S. Department of Transportation (FMCSA; with applicable PHMSA regulations)</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>U.S. DOT motor-carrier safety and hazardous-materials transportation regulatory context: FMCSA Federal Motor Carrier Safety Regulations (49 CFR Parts 300-399) and applicable PHMSA Hazardous Materials Regulations (cargo tanks)</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Current regulations; accessed 2026-09-20</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>49 CFR Parts 300-399 (FMCSA); 49 CFR Parts 100-180 (PHMSA HMR); https://www.fmcsa.dot.gov/regulations</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Regulatory</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>US motor-carrier and hazardous-materials transport-safety compliance context for fleet management. FMCSA and PHMSA are distinct agencies and legal regimes; state, hours-of-service, CDL, drug/alcohol, inspection, and insurance requirements apply additionally; does not determine internal fleet ownership or process design; non-US regimes differ. Evidence only, not text to copy.</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Fleet transport-safety and cargo-tank compliance context for CM-1-2-7-2-2</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>SRC-API-653-001</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>American Petroleum Institute</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>API Standard 653 - Tank Inspection, Repair, Alteration, and Reconstruction (in-service aboveground storage tanks)</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>5th edition, 2014, with addenda; accessed 2026-09-20</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>API 653; https://www.api.org/products-and-services/individual-certification-programs/certifications/api653</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Industry standards body</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>In-service aboveground storage tank inspection and integrity practice context. Applicability is tank-specific (API 650/12C-constructed tanks) and jurisdiction-dependent; the enterprise's engineering standards and governing regulations control; not for underground tanks, pipeline integrity, metering methodology, capital decision rights, or asset-management ownership; standard text is purchase access - claims based on public API materials. Evidence only, not text to copy.</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Tank integrity practice context for CM-1-2-7-2-3</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
         <is>
           <t>active</t>
         </is>

--- a/business_architecture/ontology/build/output/step3c-definition-authoring-workbook.xlsx
+++ b/business_architecture/ontology/build/output/step3c-definition-authoring-workbook.xlsx
@@ -32268,18 +32268,75 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U231" s="5" t="n"/>
-      <c r="V231" s="5" t="n"/>
-      <c r="W231" s="5" t="n"/>
+      <c r="N231" t="inlineStr">
+        <is>
+          <t>Analyze the downstream product markets the company serves or could serve — market size, demand and supply balances, channel structure, margin pools, and regulatory and structural change — through a recurring, governed analysis cycle, so marketing strategy and planning decisions rest on a current, evidenced view of the market.</t>
+        </is>
+      </c>
+      <c r="O231" t="inlineStr">
+        <is>
+          <t>Covers the recurring market-analysis lifecycle for downstream fuels and products markets: sourcing market data (CM-1-3-1-1-1), defining each cycle's objectives and scope (CM-1-3-1-1-2), analyzing market size, demand and supply, channel structure, pricing environments, and margin pools (CM-1-3-1-1-3), and documenting governed findings (CM-1-3-1-1-4). Analyze-and-inform: strategy decisions belong to the strategy and planning branches (CM-1-3-2/3/5); the enterprise demand forecast to Demand Forecasting (CM-1-1-1-1, batch 03); supply-network economics to CM-1-2-6-1 (batch 19 four-lens rule); enterprise KPI definition to the KPI workstream. Excludes strategy decisions (CM-1-3-2/3); demand forecast production (CM-1-1-1-1); supply-economics analysis (CM-1-2-6-1); KPI definition (KPI workstream); competitor-specific analysis (CM-1-3-1-5).</t>
+        </is>
+      </c>
+      <c r="P231" t="inlineStr">
+        <is>
+          <t>Run the recurring market-analysis cycle | analyze market size, demand-supply, channels, and margin pools | maintain a current evidenced market view | feed strategy, planning, and Insight and Metrics</t>
+        </is>
+      </c>
+      <c r="Q231" t="inlineStr">
+        <is>
+          <t>Strategy decisions (CM-1-3-2/3) | demand forecast production (CM-1-1-1-1) | supply-economics analysis (CM-1-2-6-1) | KPI definition (KPI workstream) | competitor analysis (CM-1-3-1-5)</t>
+        </is>
+      </c>
+      <c r="T231" t="inlineStr">
+        <is>
+          <t>Batch 21 (2026-09-20). Concept-type: process — one four-step analysis lifecycle (the batch 08 variant pattern; this cluster is the template's first instance), confirmed in review. Lifecycle order normalized per review: Define Objectives &amp; Scope precedes Source &amp; Collect Information precedes Analyze Data precedes Document Findings. Market data for US fuels marketing is anchored by EIA's Petroleum Marketing Monthly and STEO within their US-only, survey-category limitations; vendor data under its licensing terms (batch 12 follow-up). Batch 21 durable rule (review): "Marketing Analysis produces governed evidence, insight, hypotheses, and recommendations. It does not itself set strategy, approve investments, establish prices, allocate product, publish the enterprise forecast, define enterprise KPIs, make commercial offers, or execute campaigns." APQC candidate is a WEAK generic intelligence match.</t>
+        </is>
+      </c>
+      <c r="U231" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V231" s="5" t="inlineStr">
+        <is>
+          <t>A current, evidenced market view under every marketing decision.</t>
+        </is>
+      </c>
+      <c r="W231" s="5" t="inlineStr">
+        <is>
+          <t>SRC-EIA-PMM-001 | SRC-EIA-STEO-001</t>
+        </is>
+      </c>
       <c r="X231" s="5" t="n"/>
-      <c r="Y231" s="5" t="n"/>
-      <c r="Z231" s="5" t="n"/>
-      <c r="AA231" s="5" t="n"/>
-      <c r="AB231" s="5" t="n"/>
-      <c r="AC231" s="5" t="n"/>
+      <c r="Y231" s="5" t="inlineStr">
+        <is>
+          <t>Government and industry market data (EIA PMM/STEO) | licensed vendor data | internal sales and channel data</t>
+        </is>
+      </c>
+      <c r="Z231" s="5" t="inlineStr">
+        <is>
+          <t>Governed market-analysis findings</t>
+        </is>
+      </c>
+      <c r="AA231" s="5" t="inlineStr">
+        <is>
+          <t>enables: Insight and Metrics | enables: Brand Strategy | informed-by: Demand Forecasting</t>
+        </is>
+      </c>
+      <c r="AB231" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC231" s="5" t="inlineStr">
+        <is>
+          <t>periodic</t>
+        </is>
+      </c>
       <c r="AD231" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -32347,18 +32404,75 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U232" s="5" t="n"/>
-      <c r="V232" s="5" t="n"/>
-      <c r="W232" s="5" t="n"/>
+      <c r="N232" t="inlineStr">
+        <is>
+          <t>Source and collect the market data the market-analysis cycle needs — government statistics, licensed market data, industry publications, and internal sales and channel data — qualifying sources, respecting licensing terms, and organizing collected data for analysis.</t>
+        </is>
+      </c>
+      <c r="O232" t="inlineStr">
+        <is>
+          <t>Covers market-data sourcing: identifying and qualifying sources for market size, demand, supply, price, and channel data; collecting under the applicable licensing and use terms; recording provenance and currency; and organizing data for the analysis step (CM-1-3-1-1-3). Data-vendor selection and licensing ownership follow the batch 12 follow-up owner; enterprise data governance frameworks apply where established. Excludes the analysis itself (CM-1-3-1-1-3); vendor licensing ownership (accountable owner per batch 12 follow-up); enterprise data governance (its owner).</t>
+        </is>
+      </c>
+      <c r="P232" t="inlineStr">
+        <is>
+          <t>Identify and qualify market data sources | collect under licensing and use terms | record provenance and currency | organize data for analysis</t>
+        </is>
+      </c>
+      <c r="Q232" t="inlineStr">
+        <is>
+          <t>Analysis (CM-1-3-1-1-3) | vendor licensing ownership (batch 12 follow-up owner) | enterprise data governance (its owner)</t>
+        </is>
+      </c>
+      <c r="T232" t="inlineStr">
+        <is>
+          <t>Batch 21 (2026-09-20). Sourcing step of the shared analysis lifecycle, market instance. Licensed data used within its terms — the licensing owner question stands (batch 12). APQC candidate is a WEAK account-data match.</t>
+        </is>
+      </c>
+      <c r="U232" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V232" s="5" t="inlineStr">
+        <is>
+          <t>The right market data, legitimately sourced, ready to analyze.</t>
+        </is>
+      </c>
+      <c r="W232" s="5" t="inlineStr">
+        <is>
+          <t>SRC-EIA-PMM-001</t>
+        </is>
+      </c>
       <c r="X232" s="5" t="n"/>
-      <c r="Y232" s="5" t="n"/>
-      <c r="Z232" s="5" t="n"/>
-      <c r="AA232" s="5" t="n"/>
-      <c r="AB232" s="5" t="n"/>
-      <c r="AC232" s="5" t="n"/>
+      <c r="Y232" s="5" t="inlineStr">
+        <is>
+          <t>Government statistics (EIA) | licensed vendor data | internal sales and channel records</t>
+        </is>
+      </c>
+      <c r="Z232" s="5" t="inlineStr">
+        <is>
+          <t>Qualified, organized market data with provenance</t>
+        </is>
+      </c>
+      <c r="AA232" s="5" t="inlineStr">
+        <is>
+          <t>follows: Define Analysis Objectives &amp; Scope | precedes: Analyze Data | governed-by: Market Analysis</t>
+        </is>
+      </c>
+      <c r="AB232" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC232" s="5" t="inlineStr">
+        <is>
+          <t>periodic</t>
+        </is>
+      </c>
       <c r="AD232" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -32421,18 +32535,75 @@
           <t>strong APQC candidate but no validator agreed</t>
         </is>
       </c>
-      <c r="U233" s="5" t="n"/>
-      <c r="V233" s="5" t="n"/>
-      <c r="W233" s="5" t="n"/>
+      <c r="N233" t="inlineStr">
+        <is>
+          <t>Define each market-analysis cycle's objectives, questions, scope, and method with the consuming stakeholders — which markets, products, channels, and periods, answering which decisions — so analysis effort lands on the questions strategy and planning actually need answered.</t>
+        </is>
+      </c>
+      <c r="O233" t="inlineStr">
+        <is>
+          <t>Covers analysis framing: agreeing the cycle's decision-supporting questions with the strategy, planning, and commercial consumers; setting market, product, channel, geography, and period scope; selecting methods and required data; and setting the cycle's deliverable and timing. The consumers own their decisions; this step owns the framing. Excludes the decisions the analysis supports (consumers); the analysis itself (CM-1-3-1-1-3); data collection (CM-1-3-1-1-1).</t>
+        </is>
+      </c>
+      <c r="P233" t="inlineStr">
+        <is>
+          <t>Agree decision-supporting questions with consumers | set market, product, channel, and period scope | select methods and required data | set deliverables and timing</t>
+        </is>
+      </c>
+      <c r="Q233" t="inlineStr">
+        <is>
+          <t>The supported decisions (consumers) | analysis execution (CM-1-3-1-1-3) | data collection (CM-1-3-1-1-1)</t>
+        </is>
+      </c>
+      <c r="T233" t="inlineStr">
+        <is>
+          <t>Batch 21 (2026-09-20). Framing step of the shared lifecycle, market instance — the lifecycle's first step per the normalized order. APQC 'Define objectives' scored STRONG at 3b but NO SOURCE — honored; generic-step match, comparative only.</t>
+        </is>
+      </c>
+      <c r="U233" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V233" s="5" t="inlineStr">
+        <is>
+          <t>Analysis aimed at real decisions, not analysis for its own sake.</t>
+        </is>
+      </c>
+      <c r="W233" s="5" t="inlineStr">
+        <is>
+          <t>SRC-APQC-PCF-001</t>
+        </is>
+      </c>
       <c r="X233" s="5" t="n"/>
-      <c r="Y233" s="5" t="n"/>
-      <c r="Z233" s="5" t="n"/>
-      <c r="AA233" s="5" t="n"/>
-      <c r="AB233" s="5" t="n"/>
-      <c r="AC233" s="5" t="n"/>
+      <c r="Y233" s="5" t="inlineStr">
+        <is>
+          <t>Consumer decision needs (CM-1-3-2/3/5) | prior findings | available data inventory</t>
+        </is>
+      </c>
+      <c r="Z233" s="5" t="inlineStr">
+        <is>
+          <t>Agreed analysis objectives, scope, and method per cycle</t>
+        </is>
+      </c>
+      <c r="AA233" s="5" t="inlineStr">
+        <is>
+          <t>precedes: Source &amp; Collect Information | precedes: Analyze Data | precedes: Document Findings | governed-by: Market Analysis</t>
+        </is>
+      </c>
+      <c r="AB233" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC233" s="5" t="inlineStr">
+        <is>
+          <t>periodic</t>
+        </is>
+      </c>
       <c r="AD233" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -32500,18 +32671,75 @@
           <t>strong APQC candidate but no validator agreed</t>
         </is>
       </c>
-      <c r="U234" s="5" t="n"/>
-      <c r="V234" s="5" t="n"/>
-      <c r="W234" s="5" t="n"/>
+      <c r="N234" t="inlineStr">
+        <is>
+          <t>Analyze the collected market data against the defined objectives — market sizing, demand and supply balance, channel and margin structure, trend and scenario analysis — producing evidenced analytical results with their assumptions and confidence stated.</t>
+        </is>
+      </c>
+      <c r="O234" t="inlineStr">
+        <is>
+          <t>Covers market-analysis execution: applying the defined methods to the qualified data; sizing markets and segments; analyzing demand-supply balances, channel structures, pricing environments, and margin pools; testing trends and scenarios; and stating assumptions, limitations, and confidence with the results. Results are analytical inputs to decisions, not decisions; forecast production stays with CM-1-1-1-1. Excludes decision-making (consumers); demand forecast production (CM-1-1-1-1); documentation and distribution (CM-1-3-1-1-4).</t>
+        </is>
+      </c>
+      <c r="P234" t="inlineStr">
+        <is>
+          <t>Apply defined methods to qualified data | size markets and analyze demand-supply, channels, and margins | test trends and scenarios | state assumptions, limitations, and confidence</t>
+        </is>
+      </c>
+      <c r="Q234" t="inlineStr">
+        <is>
+          <t>Decisions (consumers) | forecast production (CM-1-1-1-1) | documentation (CM-1-3-1-1-4)</t>
+        </is>
+      </c>
+      <c r="T234" t="inlineStr">
+        <is>
+          <t>Batch 21 (2026-09-20). Analysis step of the shared lifecycle, market instance. APQC 'Analyze data' scored STRONG at 3b but NO SOURCE — honored; generic-step match.</t>
+        </is>
+      </c>
+      <c r="U234" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V234" s="5" t="inlineStr">
+        <is>
+          <t>Evidenced answers to the framed questions, with honesty about confidence.</t>
+        </is>
+      </c>
+      <c r="W234" s="5" t="inlineStr">
+        <is>
+          <t>SRC-EIA-PMM-001 | SRC-APQC-PCF-001</t>
+        </is>
+      </c>
       <c r="X234" s="5" t="n"/>
-      <c r="Y234" s="5" t="n"/>
-      <c r="Z234" s="5" t="n"/>
-      <c r="AA234" s="5" t="n"/>
-      <c r="AB234" s="5" t="n"/>
-      <c r="AC234" s="5" t="n"/>
+      <c r="Y234" s="5" t="inlineStr">
+        <is>
+          <t>Qualified data (CM-1-3-1-1-1) | objectives and methods (CM-1-3-1-1-2)</t>
+        </is>
+      </c>
+      <c r="Z234" s="5" t="inlineStr">
+        <is>
+          <t>Evidenced market-analysis results</t>
+        </is>
+      </c>
+      <c r="AA234" s="5" t="inlineStr">
+        <is>
+          <t>follows: Source &amp; Collect Information | precedes: Document Findings</t>
+        </is>
+      </c>
+      <c r="AB234" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC234" s="5" t="inlineStr">
+        <is>
+          <t>periodic</t>
+        </is>
+      </c>
       <c r="AD234" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -32579,18 +32807,75 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U235" s="5" t="n"/>
-      <c r="V235" s="5" t="n"/>
-      <c r="W235" s="5" t="n"/>
+      <c r="N235" t="inlineStr">
+        <is>
+          <t>Document and distribute the market-analysis findings — governed findings records with their evidence, assumptions, and confidence — to the consuming strategy, planning, and insight processes, maintaining the findings library so analysis is reusable and auditable.</t>
+        </is>
+      </c>
+      <c r="O235" t="inlineStr">
+        <is>
+          <t>Covers findings documentation: producing the governed findings record with evidence, assumptions, limitations, and confidence; distributing to the agreed consumers and Insight and Metrics (CM-1-3-1-6); and maintaining the findings library with versioning and currency. Findings records preserve the evidence lineage, source-use restrictions, assumptions, analytical method, confidence/uncertainty, and applicable commercial, privacy, and competition-sensitivity classification. Excludes the analysis itself (CM-1-3-1-1-3); the consumers' decisions; enterprise records-retention policy (governance owner).</t>
+        </is>
+      </c>
+      <c r="P235" t="inlineStr">
+        <is>
+          <t>Produce governed findings records with evidence and confidence | distribute to agreed consumers and Insight and Metrics | maintain the versioned findings library</t>
+        </is>
+      </c>
+      <c r="Q235" t="inlineStr">
+        <is>
+          <t>Analysis (CM-1-3-1-1-3) | consumer decisions | records-retention policy (governance owner)</t>
+        </is>
+      </c>
+      <c r="T235" t="inlineStr">
+        <is>
+          <t>Batch 21 (2026-09-20). Documentation step of the shared lifecycle, market instance; the shared evidence-lineage statement (review) applies. APQC 'Document trade' is a false lexical match.</t>
+        </is>
+      </c>
+      <c r="U235" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V235" s="5" t="inlineStr">
+        <is>
+          <t>Findings that outlive the meeting — governed, evidenced, findable.</t>
+        </is>
+      </c>
+      <c r="W235" s="5" t="inlineStr">
+        <is>
+          <t>SRC-APQC-PCF-001</t>
+        </is>
+      </c>
       <c r="X235" s="5" t="n"/>
-      <c r="Y235" s="5" t="n"/>
-      <c r="Z235" s="5" t="n"/>
-      <c r="AA235" s="5" t="n"/>
-      <c r="AB235" s="5" t="n"/>
-      <c r="AC235" s="5" t="n"/>
+      <c r="Y235" s="5" t="inlineStr">
+        <is>
+          <t>Analysis results (CM-1-3-1-1-3) | distribution agreements with consumers</t>
+        </is>
+      </c>
+      <c r="Z235" s="5" t="inlineStr">
+        <is>
+          <t>Governed, distributed market findings</t>
+        </is>
+      </c>
+      <c r="AA235" s="5" t="inlineStr">
+        <is>
+          <t>follows: Analyze Data | enables: Insight and Metrics</t>
+        </is>
+      </c>
+      <c r="AB235" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC235" s="5" t="inlineStr">
+        <is>
+          <t>periodic</t>
+        </is>
+      </c>
       <c r="AD235" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -32658,18 +32943,75 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U236" s="5" t="n"/>
-      <c r="V236" s="5" t="n"/>
-      <c r="W236" s="5" t="n"/>
+      <c r="N236" t="inlineStr">
+        <is>
+          <t>Analyze the company's own position and performance in its downstream markets — market share, portfolio and asset position, capability strengths and gaps, and performance against the market, using approved internal data, external benchmarks, and stated comparability assumptions — through a recurring, governed analysis cycle, so strategy is built on an honest view of where the company stands.</t>
+        </is>
+      </c>
+      <c r="O236" t="inlineStr">
+        <is>
+          <t>Covers the recurring company-analysis lifecycle: sourcing internal performance, share, portfolio, and capability data alongside market benchmarks (CM-1-3-1-2-1); framing each cycle's questions (CM-1-3-1-2-2); analyzing share, position, capability, and relative performance (CM-1-3-1-2-3); and documenting governed findings (CM-1-3-1-2-4). Uses governed financial and operational data from its accountable owners (Accounting, batch 15; operations processes); it analyzes position, it does not produce financial results or decide strategy. Share and comparative-performance conclusions state their category definitions, data coverage, channel coverage, geographic scope, and comparability assumptions. Excludes strategy decisions (CM-1-3-2/3); financial reporting production (CM-1-2-4-2, Finance); cost-to-serve analysis (CM-1-2-6-1-3, batch 19); competitor analysis (CM-1-3-1-5); KPI definition (KPI workstream).</t>
+        </is>
+      </c>
+      <c r="P236" t="inlineStr">
+        <is>
+          <t>Run the recurring company-analysis cycle | analyze share, portfolio, capability, and relative performance | maintain an honest evidenced self-view | feed strategy and Insight and Metrics</t>
+        </is>
+      </c>
+      <c r="Q236" t="inlineStr">
+        <is>
+          <t>Strategy decisions (CM-1-3-2/3) | financial reporting (CM-1-2-4-2, Finance) | cost-to-serve (CM-1-2-6-1-3) | competitor analysis (CM-1-3-1-5) | KPI definition (KPI workstream)</t>
+        </is>
+      </c>
+      <c r="T236" t="inlineStr">
+        <is>
+          <t>Batch 21 (2026-09-20). Q2 partition: the company's own position and performance — the self-analysis lens; competitor conduct sits at CM-1-3-1-5 and market structure at CM-1-3-1-1. Data-quality qualifier added in review: approved internal data, external benchmarks, and stated comparability assumptions. Shared lifecycle, second instance; normalized order applies. Batch 21 durable rule (review): "Marketing Analysis produces governed evidence, insight, hypotheses, and recommendations. It does not itself set strategy, approve investments, establish prices, allocate product, publish the enterprise forecast, define enterprise KPIs, make commercial offers, or execute campaigns." APQC candidate is a WEAK pricing match.</t>
+        </is>
+      </c>
+      <c r="U236" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V236" s="5" t="inlineStr">
+        <is>
+          <t>Strategy built on where the company actually stands, not where it hopes it stands.</t>
+        </is>
+      </c>
+      <c r="W236" s="5" t="inlineStr">
+        <is>
+          <t>SRC-EIA-PMM-001 | SRC-APQC-PCF-001</t>
+        </is>
+      </c>
       <c r="X236" s="5" t="n"/>
-      <c r="Y236" s="5" t="n"/>
-      <c r="Z236" s="5" t="n"/>
-      <c r="AA236" s="5" t="n"/>
-      <c r="AB236" s="5" t="n"/>
-      <c r="AC236" s="5" t="n"/>
+      <c r="Y236" s="5" t="inlineStr">
+        <is>
+          <t>Governed financial and operational data (CM-1-2-4-2, operations) | share and benchmark data | capability assessments</t>
+        </is>
+      </c>
+      <c r="Z236" s="5" t="inlineStr">
+        <is>
+          <t>Governed company-position findings</t>
+        </is>
+      </c>
+      <c r="AA236" s="5" t="inlineStr">
+        <is>
+          <t>enables: Insight and Metrics | enables: Brand Strategy | uses-input: Accounting</t>
+        </is>
+      </c>
+      <c r="AB236" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC236" s="5" t="inlineStr">
+        <is>
+          <t>periodic</t>
+        </is>
+      </c>
       <c r="AD236" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -32737,18 +33079,75 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U237" s="5" t="n"/>
-      <c r="V237" s="5" t="n"/>
-      <c r="W237" s="5" t="n"/>
+      <c r="N237" t="inlineStr">
+        <is>
+          <t>Source and collect the data the company-analysis cycle needs — governed internal financial, volume, share, and capability data, and the external benchmarks to compare against — respecting the data owners' controls and organizing the data for analysis.</t>
+        </is>
+      </c>
+      <c r="O237" t="inlineStr">
+        <is>
+          <t>Covers company-analysis sourcing: internal performance, volume, margin, portfolio, and capability data from their accountable owners; external share and benchmark data under licensing terms; provenance and currency recording; organization for analysis (CM-1-3-1-2-3). Excludes producing the internal data (its owners); the analysis (CM-1-3-1-2-3); vendor licensing ownership (batch 12 follow-up owner).</t>
+        </is>
+      </c>
+      <c r="P237" t="inlineStr">
+        <is>
+          <t>Collect governed internal performance and capability data | collect external benchmarks under licensing terms | record provenance and organize for analysis</t>
+        </is>
+      </c>
+      <c r="Q237" t="inlineStr">
+        <is>
+          <t>Internal data production (accountable owners) | analysis (CM-1-3-1-2-3) | licensing ownership (batch 12 follow-up owner)</t>
+        </is>
+      </c>
+      <c r="T237" t="inlineStr">
+        <is>
+          <t>Batch 21 (2026-09-20). Shared lifecycle step, company instance — consumes governed data, never produces it. APQC candidate is a WEAK account-data match.</t>
+        </is>
+      </c>
+      <c r="U237" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V237" s="5" t="inlineStr">
+        <is>
+          <t>The company's own numbers and fair benchmarks, ready to analyze.</t>
+        </is>
+      </c>
+      <c r="W237" s="5" t="inlineStr">
+        <is>
+          <t>SRC-APQC-PCF-001</t>
+        </is>
+      </c>
       <c r="X237" s="5" t="n"/>
-      <c r="Y237" s="5" t="n"/>
-      <c r="Z237" s="5" t="n"/>
-      <c r="AA237" s="5" t="n"/>
-      <c r="AB237" s="5" t="n"/>
-      <c r="AC237" s="5" t="n"/>
+      <c r="Y237" s="5" t="inlineStr">
+        <is>
+          <t>Governed internal data (CM-1-2-4-2, operations) | licensed benchmarks</t>
+        </is>
+      </c>
+      <c r="Z237" s="5" t="inlineStr">
+        <is>
+          <t>Qualified, organized company and benchmark data</t>
+        </is>
+      </c>
+      <c r="AA237" s="5" t="inlineStr">
+        <is>
+          <t>follows: Define Analysis Objectives &amp; Scope | precedes: Analyze Data | governed-by: Company Analysis</t>
+        </is>
+      </c>
+      <c r="AB237" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC237" s="5" t="inlineStr">
+        <is>
+          <t>periodic</t>
+        </is>
+      </c>
       <c r="AD237" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -32811,18 +33210,75 @@
           <t>strong APQC candidate but no validator agreed</t>
         </is>
       </c>
-      <c r="U238" s="5" t="n"/>
-      <c r="V238" s="5" t="n"/>
-      <c r="W238" s="5" t="n"/>
+      <c r="N238" t="inlineStr">
+        <is>
+          <t>Define each company-analysis cycle's objectives, questions, scope, and method with the consuming stakeholders — which businesses, markets, capabilities, and periods, answering which strategic questions — so self-analysis lands where strategy needs it.</t>
+        </is>
+      </c>
+      <c r="O238" t="inlineStr">
+        <is>
+          <t>Covers framing for company analysis: agreeing decision-supporting questions with strategy and planning consumers; setting business, market, capability, and period scope; selecting methods and benchmarks; setting deliverables and timing. Excludes the supported decisions (consumers); analysis execution (CM-1-3-1-2-3); data collection (CM-1-3-1-2-1).</t>
+        </is>
+      </c>
+      <c r="P238" t="inlineStr">
+        <is>
+          <t>Agree strategic questions with consumers | set business, market, capability, and period scope | select methods and benchmarks | set deliverables and timing</t>
+        </is>
+      </c>
+      <c r="Q238" t="inlineStr">
+        <is>
+          <t>Supported decisions (consumers) | analysis (CM-1-3-1-2-3) | collection (CM-1-3-1-2-1)</t>
+        </is>
+      </c>
+      <c r="T238" t="inlineStr">
+        <is>
+          <t>Batch 21 (2026-09-20). Shared lifecycle step, company instance — first step per the normalized order. APQC 'Define objectives' STRONG/NO SOURCE — honored.</t>
+        </is>
+      </c>
+      <c r="U238" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V238" s="5" t="inlineStr">
+        <is>
+          <t>Self-analysis aimed at strategy's real questions.</t>
+        </is>
+      </c>
+      <c r="W238" s="5" t="inlineStr">
+        <is>
+          <t>SRC-APQC-PCF-001</t>
+        </is>
+      </c>
       <c r="X238" s="5" t="n"/>
-      <c r="Y238" s="5" t="n"/>
-      <c r="Z238" s="5" t="n"/>
-      <c r="AA238" s="5" t="n"/>
-      <c r="AB238" s="5" t="n"/>
-      <c r="AC238" s="5" t="n"/>
+      <c r="Y238" s="5" t="inlineStr">
+        <is>
+          <t>Consumer decision needs | prior findings | data inventory</t>
+        </is>
+      </c>
+      <c r="Z238" s="5" t="inlineStr">
+        <is>
+          <t>Agreed objectives, scope, and method per cycle</t>
+        </is>
+      </c>
+      <c r="AA238" s="5" t="inlineStr">
+        <is>
+          <t>precedes: Source &amp; Collect Information | precedes: Analyze Data | precedes: Document Findings | governed-by: Company Analysis</t>
+        </is>
+      </c>
+      <c r="AB238" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC238" s="5" t="inlineStr">
+        <is>
+          <t>periodic</t>
+        </is>
+      </c>
       <c r="AD238" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -32890,18 +33346,75 @@
           <t>strong APQC candidate but no validator agreed</t>
         </is>
       </c>
-      <c r="U239" s="5" t="n"/>
-      <c r="V239" s="5" t="n"/>
-      <c r="W239" s="5" t="n"/>
+      <c r="N239" t="inlineStr">
+        <is>
+          <t>Analyze the company's position against the defined objectives — share and share-trend analysis, portfolio and asset-position assessment, capability strengths and gaps, and performance versus market and benchmarks — producing evidenced results with assumptions and confidence stated.</t>
+        </is>
+      </c>
+      <c r="O239" t="inlineStr">
+        <is>
+          <t>Covers company-analysis execution: share and trend computation; portfolio and asset-position assessment; capability strength/gap analysis against market requirements; relative-performance analysis against benchmarks; assumptions, limitations, and confidence stated, including category definitions, data coverage, and comparability assumptions behind share and performance conclusions. Excludes decisions (consumers); financial result production (CM-1-2-4-2, Finance); documentation (CM-1-3-1-2-4).</t>
+        </is>
+      </c>
+      <c r="P239" t="inlineStr">
+        <is>
+          <t>Compute share and trends | assess portfolio and asset position | analyze capability strengths and gaps | benchmark relative performance with stated confidence</t>
+        </is>
+      </c>
+      <c r="Q239" t="inlineStr">
+        <is>
+          <t>Decisions (consumers) | financial production (CM-1-2-4-2) | documentation (CM-1-3-1-2-4)</t>
+        </is>
+      </c>
+      <c r="T239" t="inlineStr">
+        <is>
+          <t>Batch 21 (2026-09-20). Shared lifecycle step, company instance; comparability assumptions stated with results (review qualifier). APQC 'Analyze data' STRONG/NO SOURCE — honored.</t>
+        </is>
+      </c>
+      <c r="U239" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V239" s="5" t="inlineStr">
+        <is>
+          <t>An honest, evidenced answer to how the company is really positioned.</t>
+        </is>
+      </c>
+      <c r="W239" s="5" t="inlineStr">
+        <is>
+          <t>SRC-APQC-PCF-001</t>
+        </is>
+      </c>
       <c r="X239" s="5" t="n"/>
-      <c r="Y239" s="5" t="n"/>
-      <c r="Z239" s="5" t="n"/>
-      <c r="AA239" s="5" t="n"/>
-      <c r="AB239" s="5" t="n"/>
-      <c r="AC239" s="5" t="n"/>
+      <c r="Y239" s="5" t="inlineStr">
+        <is>
+          <t>Qualified data (CM-1-3-1-2-1) | objectives (CM-1-3-1-2-2)</t>
+        </is>
+      </c>
+      <c r="Z239" s="5" t="inlineStr">
+        <is>
+          <t>Evidenced company-position results</t>
+        </is>
+      </c>
+      <c r="AA239" s="5" t="inlineStr">
+        <is>
+          <t>follows: Source &amp; Collect Information | precedes: Document Findings</t>
+        </is>
+      </c>
+      <c r="AB239" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC239" s="5" t="inlineStr">
+        <is>
+          <t>periodic</t>
+        </is>
+      </c>
       <c r="AD239" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -32969,18 +33482,75 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U240" s="5" t="n"/>
-      <c r="V240" s="5" t="n"/>
-      <c r="W240" s="5" t="n"/>
+      <c r="N240" t="inlineStr">
+        <is>
+          <t>Document and distribute the company-analysis findings — governed records with evidence, assumptions, and confidence — to strategy, planning, and Insight and Metrics, maintaining the findings library.</t>
+        </is>
+      </c>
+      <c r="O240" t="inlineStr">
+        <is>
+          <t>Covers findings documentation for company analysis: governed records with evidence and confidence; distribution to agreed consumers and CM-1-3-1-6; versioned library maintenance. Sensitive internal assessments distribute per their classification. Findings records preserve the evidence lineage, source-use restrictions, assumptions, analytical method, confidence/uncertainty, and applicable commercial, privacy, and competition-sensitivity classification. Excludes the analysis (CM-1-3-1-2-3); consumer decisions; records-retention policy (governance owner).</t>
+        </is>
+      </c>
+      <c r="P240" t="inlineStr">
+        <is>
+          <t>Produce governed findings records | distribute per classification to agreed consumers | maintain the versioned library</t>
+        </is>
+      </c>
+      <c r="Q240" t="inlineStr">
+        <is>
+          <t>Analysis (CM-1-3-1-2-3) | decisions (consumers) | retention policy (governance owner)</t>
+        </is>
+      </c>
+      <c r="T240" t="inlineStr">
+        <is>
+          <t>Batch 21 (2026-09-20). Shared lifecycle step, company instance; internal-assessment classification respected; shared evidence-lineage statement applies. APQC 'Document trade' is a false match.</t>
+        </is>
+      </c>
+      <c r="U240" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V240" s="5" t="inlineStr">
+        <is>
+          <t>Self-knowledge that is governed, findable, and appropriately protected.</t>
+        </is>
+      </c>
+      <c r="W240" s="5" t="inlineStr">
+        <is>
+          <t>SRC-APQC-PCF-001</t>
+        </is>
+      </c>
       <c r="X240" s="5" t="n"/>
-      <c r="Y240" s="5" t="n"/>
-      <c r="Z240" s="5" t="n"/>
-      <c r="AA240" s="5" t="n"/>
-      <c r="AB240" s="5" t="n"/>
-      <c r="AC240" s="5" t="n"/>
+      <c r="Y240" s="5" t="inlineStr">
+        <is>
+          <t>Analysis results (CM-1-3-1-2-3) | classification rules</t>
+        </is>
+      </c>
+      <c r="Z240" s="5" t="inlineStr">
+        <is>
+          <t>Governed, distributed company findings</t>
+        </is>
+      </c>
+      <c r="AA240" s="5" t="inlineStr">
+        <is>
+          <t>follows: Analyze Data | enables: Insight and Metrics</t>
+        </is>
+      </c>
+      <c r="AB240" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC240" s="5" t="inlineStr">
+        <is>
+          <t>periodic</t>
+        </is>
+      </c>
       <c r="AD240" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -33048,18 +33618,75 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U241" s="5" t="n"/>
-      <c r="V241" s="5" t="n"/>
-      <c r="W241" s="5" t="n"/>
+      <c r="N241" t="inlineStr">
+        <is>
+          <t>Analyze end-consumer behavior in the company's downstream markets — needs, preferences, buying patterns, journey and experience drivers, and segment dynamics — through a recurring, governed analysis cycle operating within the applicable privacy frameworks, so consumer-facing strategy rests on evidenced consumer understanding.</t>
+        </is>
+      </c>
+      <c r="O241" t="inlineStr">
+        <is>
+          <t>Covers the recurring consumer-analysis lifecycle: sourcing consumer research, transaction, loyalty, and market data within privacy and consent constraints (CM-1-3-1-3-1); framing cycles (CM-1-3-1-3-2); analyzing needs, behavior, journeys, and segment dynamics (CM-1-3-1-3-3); documenting governed findings (CM-1-3-1-3-4). 'Consumer' means the end consumer (retail/B2C); direct customers and branded marketers are analyzed at CM-1-3-1-4. Personal, customer, loyalty, transaction, and behavioral data may be sourced and analyzed only for approved purposes, under the applicable lawful basis, notice/consent status where required, retention rules, access controls, data-minimization requirements, and privacy/security classifications established by the accountable Data Governance, Privacy, Legal, and Security owners. Analysis operates within these controls; it does not own privacy policy, consent and notice management, data-subject rights, data security, retention/deletion execution, or marketing-execution use of personal data. Excludes customer and marketer analysis (CM-1-3-1-4); consumer strategy decisions (CM-1-3-2-3, CM-1-3-2-5); privacy framework ownership (accountable governance owners); loyalty program operation (CM-1-3-6-6).</t>
+        </is>
+      </c>
+      <c r="P241" t="inlineStr">
+        <is>
+          <t>Run the recurring consumer-analysis cycle within privacy frameworks | analyze needs, behavior, journeys, and segments | maintain evidenced consumer understanding | feed consumer strategy and Insight and Metrics</t>
+        </is>
+      </c>
+      <c r="Q241" t="inlineStr">
+        <is>
+          <t>Customer/marketer analysis (CM-1-3-1-4) | strategy decisions (CM-1-3-2-3/-5) | privacy framework ownership and consent, rights, security, and retention operations (governance owners) | loyalty operation (CM-1-3-6-6)</t>
+        </is>
+      </c>
+      <c r="T241" t="inlineStr">
+        <is>
+          <t>Batch 21 (2026-09-20). Q2 partition: end consumers here; direct customers and branded marketers at CM-1-3-1-4 — the B2C/B2B lens split. Q3 review enhancement: the shared personal-data governance statement (verbatim in scope note) replaces the general privacy wording — analysis within approved controls is distinguished from ownership of privacy policy, consent, rights, security, and retention. Shared lifecycle, third instance; normalized order applies. Batch 21 durable rule (review): "Marketing Analysis produces governed evidence, insight, hypotheses, and recommendations. It does not itself set strategy, approve investments, establish prices, allocate product, publish the enterprise forecast, define enterprise KPIs, make commercial offers, or execute campaigns." APQC candidate is a WEAK pricing match.</t>
+        </is>
+      </c>
+      <c r="U241" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V241" s="5" t="inlineStr">
+        <is>
+          <t>Consumer-facing decisions built on evidenced, lawfully obtained consumer understanding.</t>
+        </is>
+      </c>
+      <c r="W241" s="5" t="inlineStr">
+        <is>
+          <t>SRC-EIA-PMM-001 | SRC-APQC-PCF-001</t>
+        </is>
+      </c>
       <c r="X241" s="5" t="n"/>
-      <c r="Y241" s="5" t="n"/>
-      <c r="Z241" s="5" t="n"/>
-      <c r="AA241" s="5" t="n"/>
-      <c r="AB241" s="5" t="n"/>
-      <c r="AC241" s="5" t="n"/>
+      <c r="Y241" s="5" t="inlineStr">
+        <is>
+          <t>Consumer research and panels | transaction and loyalty data within consent | market and demographic data</t>
+        </is>
+      </c>
+      <c r="Z241" s="5" t="inlineStr">
+        <is>
+          <t>Governed consumer-analysis findings</t>
+        </is>
+      </c>
+      <c r="AA241" s="5" t="inlineStr">
+        <is>
+          <t>enables: Consumer Value Proposition | enables: Insight and Metrics | informed-by: Market Analysis</t>
+        </is>
+      </c>
+      <c r="AB241" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC241" s="5" t="inlineStr">
+        <is>
+          <t>periodic</t>
+        </is>
+      </c>
       <c r="AD241" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -33127,18 +33754,75 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U242" s="5" t="n"/>
-      <c r="V242" s="5" t="n"/>
-      <c r="W242" s="5" t="n"/>
+      <c r="N242" t="inlineStr">
+        <is>
+          <t>Source and collect the consumer data the analysis cycle needs — research studies, panels, transaction and loyalty data, and demographic and market data — within consent, privacy, and licensing constraints, and organize it for analysis.</t>
+        </is>
+      </c>
+      <c r="O242" t="inlineStr">
+        <is>
+          <t>Covers consumer-data sourcing: research commissioning inputs, panel and study data, transaction and loyalty data used within its consent basis, demographic and market data; provenance, consent-basis, and currency recording; organization for analysis (CM-1-3-1-3-3). Sourcing operates under the shared personal-data governance statement recorded at CM-1-3-1-3: approved purposes, lawful basis, notice/consent status, retention, access, and minimization controls set by the accountable Data Governance, Privacy, Legal, and Security owners. Excludes privacy framework ownership (governance owners); the analysis (CM-1-3-1-3-3); loyalty program data operations (CM-1-3-6-6).</t>
+        </is>
+      </c>
+      <c r="P242" t="inlineStr">
+        <is>
+          <t>Collect research, panel, transaction, and demographic data within consent and licensing | record provenance and consent basis | organize for analysis</t>
+        </is>
+      </c>
+      <c r="Q242" t="inlineStr">
+        <is>
+          <t>Privacy framework ownership (governance owners) | analysis (CM-1-3-1-3-3) | loyalty data operations (CM-1-3-6-6)</t>
+        </is>
+      </c>
+      <c r="T242" t="inlineStr">
+        <is>
+          <t>Batch 21 (2026-09-20). Shared lifecycle step, consumer instance — consent basis recorded with the data; the cluster's shared personal-data governance statement governs sourcing. APQC candidate is a WEAK account-data match.</t>
+        </is>
+      </c>
+      <c r="U242" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V242" s="5" t="inlineStr">
+        <is>
+          <t>Consumer data that is useful and lawful, ready to analyze.</t>
+        </is>
+      </c>
+      <c r="W242" s="5" t="inlineStr">
+        <is>
+          <t>SRC-APQC-PCF-001</t>
+        </is>
+      </c>
       <c r="X242" s="5" t="n"/>
-      <c r="Y242" s="5" t="n"/>
-      <c r="Z242" s="5" t="n"/>
-      <c r="AA242" s="5" t="n"/>
-      <c r="AB242" s="5" t="n"/>
-      <c r="AC242" s="5" t="n"/>
+      <c r="Y242" s="5" t="inlineStr">
+        <is>
+          <t>Research and panel data | consented transaction/loyalty data | demographic data</t>
+        </is>
+      </c>
+      <c r="Z242" s="5" t="inlineStr">
+        <is>
+          <t>Qualified consumer data with provenance and consent basis</t>
+        </is>
+      </c>
+      <c r="AA242" s="5" t="inlineStr">
+        <is>
+          <t>follows: Define Analysis Objectives &amp; Scope | precedes: Analyze Data | governed-by: Consumer Analysis</t>
+        </is>
+      </c>
+      <c r="AB242" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC242" s="5" t="inlineStr">
+        <is>
+          <t>periodic</t>
+        </is>
+      </c>
       <c r="AD242" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -33201,18 +33885,75 @@
           <t>strong APQC candidate but no validator agreed</t>
         </is>
       </c>
-      <c r="U243" s="5" t="n"/>
-      <c r="V243" s="5" t="n"/>
-      <c r="W243" s="5" t="n"/>
+      <c r="N243" t="inlineStr">
+        <is>
+          <t>Define each consumer-analysis cycle's objectives, questions, scope, and method with the consuming stakeholders — which segments, behaviors, journeys, and markets, answering which proposition and experience questions — so consumer research answers real decisions.</t>
+        </is>
+      </c>
+      <c r="O243" t="inlineStr">
+        <is>
+          <t>Covers framing for consumer analysis: agreeing decision-supporting questions with proposition, experience, and planning consumers; setting segment, behavior, journey, geography, and period scope; selecting methods including research design needs; setting deliverables and timing. Excludes the supported decisions (consumers); analysis execution (CM-1-3-1-3-3); research fieldwork procurement (per the operating model).</t>
+        </is>
+      </c>
+      <c r="P243" t="inlineStr">
+        <is>
+          <t>Agree proposition and experience questions with consumers | set segment, behavior, and journey scope | select methods and research designs | set deliverables and timing</t>
+        </is>
+      </c>
+      <c r="Q243" t="inlineStr">
+        <is>
+          <t>Supported decisions (consumers) | analysis (CM-1-3-1-3-3) | fieldwork procurement (operating model)</t>
+        </is>
+      </c>
+      <c r="T243" t="inlineStr">
+        <is>
+          <t>Batch 21 (2026-09-20). Shared lifecycle step, consumer instance — first step per the normalized order. APQC 'Define objectives' STRONG/NO SOURCE — honored.</t>
+        </is>
+      </c>
+      <c r="U243" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V243" s="5" t="inlineStr">
+        <is>
+          <t>Research designed for decisions, not curiosity.</t>
+        </is>
+      </c>
+      <c r="W243" s="5" t="inlineStr">
+        <is>
+          <t>SRC-APQC-PCF-001</t>
+        </is>
+      </c>
       <c r="X243" s="5" t="n"/>
-      <c r="Y243" s="5" t="n"/>
-      <c r="Z243" s="5" t="n"/>
-      <c r="AA243" s="5" t="n"/>
-      <c r="AB243" s="5" t="n"/>
-      <c r="AC243" s="5" t="n"/>
+      <c r="Y243" s="5" t="inlineStr">
+        <is>
+          <t>Consumer strategy questions (CM-1-3-2-3/-5) | prior findings</t>
+        </is>
+      </c>
+      <c r="Z243" s="5" t="inlineStr">
+        <is>
+          <t>Agreed objectives, scope, and research design per cycle</t>
+        </is>
+      </c>
+      <c r="AA243" s="5" t="inlineStr">
+        <is>
+          <t>precedes: Source &amp; Collect Information | precedes: Analyze Data | precedes: Document Findings | governed-by: Consumer Analysis</t>
+        </is>
+      </c>
+      <c r="AB243" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC243" s="5" t="inlineStr">
+        <is>
+          <t>periodic</t>
+        </is>
+      </c>
       <c r="AD243" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -33280,18 +34021,75 @@
           <t>strong APQC candidate but no validator agreed</t>
         </is>
       </c>
-      <c r="U244" s="5" t="n"/>
-      <c r="V244" s="5" t="n"/>
-      <c r="W244" s="5" t="n"/>
+      <c r="N244" t="inlineStr">
+        <is>
+          <t>Analyze consumer data against the defined objectives — segmentation and segment dynamics, needs and preference analysis, behavior and journey analysis, and experience drivers — producing evidenced results with assumptions and confidence stated, within the privacy constraints the data carries.</t>
+        </is>
+      </c>
+      <c r="O244" t="inlineStr">
+        <is>
+          <t>Covers consumer-analysis execution: segment identification and dynamics; needs, preference, and price-response analysis; behavior, journey, and experience-driver analysis; assumptions, limitations, and confidence stated; analysis respecting the consent basis and privacy constraints recorded with the data. Consumer segmentation here is the marketing lens of the four-lens rule (batch 19). Excludes decisions (consumers); segmentation for supply economics (CM-1-2-6-1-1), credit, or party hierarchy (their lenses); documentation (CM-1-3-1-3-4).</t>
+        </is>
+      </c>
+      <c r="P244" t="inlineStr">
+        <is>
+          <t>Identify segments and dynamics | analyze needs, preferences, and price response | analyze behavior, journeys, and experience drivers | state assumptions and confidence within privacy constraints</t>
+        </is>
+      </c>
+      <c r="Q244" t="inlineStr">
+        <is>
+          <t>Decisions (consumers) | other segmentation lenses (CM-1-2-6-1-1, credit, party hierarchy) | documentation (CM-1-3-1-3-4)</t>
+        </is>
+      </c>
+      <c r="T244" t="inlineStr">
+        <is>
+          <t>Batch 21 (2026-09-20). Shared lifecycle step, consumer instance; the marketing-segmentation lens of the batch 19 four-lens rule. APQC 'Analyze data' STRONG/NO SOURCE — honored.</t>
+        </is>
+      </c>
+      <c r="U244" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V244" s="5" t="inlineStr">
+        <is>
+          <t>Evidenced consumer understanding at decision depth.</t>
+        </is>
+      </c>
+      <c r="W244" s="5" t="inlineStr">
+        <is>
+          <t>SRC-APQC-PCF-001</t>
+        </is>
+      </c>
       <c r="X244" s="5" t="n"/>
-      <c r="Y244" s="5" t="n"/>
-      <c r="Z244" s="5" t="n"/>
-      <c r="AA244" s="5" t="n"/>
-      <c r="AB244" s="5" t="n"/>
-      <c r="AC244" s="5" t="n"/>
+      <c r="Y244" s="5" t="inlineStr">
+        <is>
+          <t>Qualified consumer data (CM-1-3-1-3-1) | objectives (CM-1-3-1-3-2)</t>
+        </is>
+      </c>
+      <c r="Z244" s="5" t="inlineStr">
+        <is>
+          <t>Evidenced consumer-analysis results</t>
+        </is>
+      </c>
+      <c r="AA244" s="5" t="inlineStr">
+        <is>
+          <t>follows: Source &amp; Collect Information | precedes: Document Findings</t>
+        </is>
+      </c>
+      <c r="AB244" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC244" s="5" t="inlineStr">
+        <is>
+          <t>periodic</t>
+        </is>
+      </c>
       <c r="AD244" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -33359,18 +34157,75 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U245" s="5" t="n"/>
-      <c r="V245" s="5" t="n"/>
-      <c r="W245" s="5" t="n"/>
+      <c r="N245" t="inlineStr">
+        <is>
+          <t>Document and distribute consumer-analysis findings — governed records with evidence, assumptions, and confidence, respecting the privacy classification of underlying data — to proposition, experience, and planning consumers and Insight and Metrics, maintaining the findings library.</t>
+        </is>
+      </c>
+      <c r="O245" t="inlineStr">
+        <is>
+          <t>Covers findings documentation for consumer analysis: governed records with evidence and confidence, published at aggregation levels consistent with privacy constraints; distribution to agreed consumers and CM-1-3-1-6; versioned library maintenance. Consumer findings should normally be published at an aggregate, de-identified, or otherwise privacy-consistent level unless a specific approved use case authorizes controlled individual-level access. Findings records preserve the evidence lineage, source-use restrictions, assumptions, analytical method, confidence/uncertainty, and applicable commercial, privacy, and competition-sensitivity classification. Excludes the analysis (CM-1-3-1-3-3); consumer decisions; privacy framework ownership (governance owners).</t>
+        </is>
+      </c>
+      <c r="P245" t="inlineStr">
+        <is>
+          <t>Produce governed findings at privacy-consistent aggregation | distribute to agreed consumers | maintain the versioned library</t>
+        </is>
+      </c>
+      <c r="Q245" t="inlineStr">
+        <is>
+          <t>Analysis (CM-1-3-1-3-3) | decisions (consumers) | privacy frameworks (governance owners)</t>
+        </is>
+      </c>
+      <c r="T245" t="inlineStr">
+        <is>
+          <t>Batch 21 (2026-09-20). Shared lifecycle step, consumer instance; review default: aggregate/de-identified publication unless a specific approved use case authorizes controlled individual-level access; shared evidence-lineage statement applies. APQC 'Document trade' is a false match.</t>
+        </is>
+      </c>
+      <c r="U245" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V245" s="5" t="inlineStr">
+        <is>
+          <t>Consumer insight that travels — without the personal data traveling with it.</t>
+        </is>
+      </c>
+      <c r="W245" s="5" t="inlineStr">
+        <is>
+          <t>SRC-APQC-PCF-001</t>
+        </is>
+      </c>
       <c r="X245" s="5" t="n"/>
-      <c r="Y245" s="5" t="n"/>
-      <c r="Z245" s="5" t="n"/>
-      <c r="AA245" s="5" t="n"/>
-      <c r="AB245" s="5" t="n"/>
-      <c r="AC245" s="5" t="n"/>
+      <c r="Y245" s="5" t="inlineStr">
+        <is>
+          <t>Analysis results (CM-1-3-1-3-3) | privacy classifications</t>
+        </is>
+      </c>
+      <c r="Z245" s="5" t="inlineStr">
+        <is>
+          <t>Governed, privacy-consistent consumer findings</t>
+        </is>
+      </c>
+      <c r="AA245" s="5" t="inlineStr">
+        <is>
+          <t>follows: Analyze Data | enables: Insight and Metrics</t>
+        </is>
+      </c>
+      <c r="AB245" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC245" s="5" t="inlineStr">
+        <is>
+          <t>periodic</t>
+        </is>
+      </c>
       <c r="AD245" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -33438,18 +34293,75 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U246" s="5" t="n"/>
-      <c r="V246" s="5" t="n"/>
-      <c r="W246" s="5" t="n"/>
+      <c r="N246" t="inlineStr">
+        <is>
+          <t>Analyze the company's direct customers and branded marketers — commercial and industrial customers, resellers, and the branded wholesalers, jobbers, and distributors who market under or alongside the brand — their needs, economics, performance, and relationship health, through a recurring, governed analysis cycle, so B2B and channel strategy rests on evidenced counterparty understanding.</t>
+        </is>
+      </c>
+      <c r="O246" t="inlineStr">
+        <is>
+          <t>Covers the recurring customer-and-marketer analysis lifecycle: sourcing customer and marketer performance, volume, and relationship data (CM-1-3-1-4-1); framing cycles (CM-1-3-1-4-2); analyzing needs, channel economics, performance, and relationship health (CM-1-3-1-4-3); documenting governed findings (CM-1-3-1-4-4). 'Marketer' is read in the downstream fuels sense: branded wholesalers, jobbers, and distributors reselling under or alongside the brand. This is the marketing analysis lens of the batch 19 four-lens rule: the same entities appear in supply-economics segmentation (CM-1-2-6-1-1), credit assessment, and the party hierarchy through their own lenses. Personal, customer, loyalty, transaction, and behavioral data may be sourced and analyzed only for approved purposes, under the applicable lawful basis, notice/consent status where required, retention rules, access controls, data-minimization requirements, and privacy/security classifications established by the accountable Data Governance, Privacy, Legal, and Security owners. Assess relationship health and retention risk as an analytical signal; do not own account interventions, retention offers, sales actions, or account-management execution. Excludes end-consumer analysis (CM-1-3-1-3); credit assessment (batch 11 boundary); supply-economics segmentation (CM-1-2-6-1-1); channel strategy decisions (CM-1-3-2-4, CM-1-3-3-3); account management execution (CM-1-3-6).</t>
+        </is>
+      </c>
+      <c r="P246" t="inlineStr">
+        <is>
+          <t>Run the recurring customer-and-marketer analysis cycle | analyze needs, channel economics, performance, and relationship health as analytical signals | maintain evidenced counterparty understanding | feed channel strategy and Insight and Metrics</t>
+        </is>
+      </c>
+      <c r="Q246" t="inlineStr">
+        <is>
+          <t>Consumer analysis (CM-1-3-1-3) | credit assessment (batch 11 boundary) | supply-economics segmentation (CM-1-2-6-1-1) | channel strategy decisions (CM-1-3-2-4, CM-1-3-3-3) | account management execution (CM-1-3-6)</t>
+        </is>
+      </c>
+      <c r="T246" t="inlineStr">
+        <is>
+          <t>Batch 21 (2026-09-20). Q2 decision: 'marketer' in the downstream fuels sense — branded wholesalers, jobbers, distributors — alongside direct commercial customers; the B2B lens paired with the consumer (B2C) lens at CM-1-3-1-3. Glossary candidate (review): "Branded Marketer: a wholesaler, jobber, distributor, dealer, or other channel intermediary that markets or resells petroleum products under, alongside, or in association with a branded product, supply, or commercial arrangement" — defined so it is not confused with the corporate marketing function. Four-lens rule (batch 19) applied: analysis lens here, credit and supply-economics and hierarchy lenses elsewhere. Shared personal-data governance statement and account-management boundary added per review. Shared lifecycle, fourth instance. Batch 21 durable rule (review): "Marketing Analysis produces governed evidence, insight, hypotheses, and recommendations. It does not itself set strategy, approve investments, establish prices, allocate product, publish the enterprise forecast, define enterprise KPIs, make commercial offers, or execute campaigns." APQC candidate is a WEAK generic intelligence match.</t>
+        </is>
+      </c>
+      <c r="U246" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V246" s="5" t="inlineStr">
+        <is>
+          <t>B2B and channel decisions built on evidenced understanding of the customers and marketers who move the volume.</t>
+        </is>
+      </c>
+      <c r="W246" s="5" t="inlineStr">
+        <is>
+          <t>SRC-EIA-PMM-001 | SRC-APQC-PCF-001</t>
+        </is>
+      </c>
       <c r="X246" s="5" t="n"/>
-      <c r="Y246" s="5" t="n"/>
-      <c r="Z246" s="5" t="n"/>
-      <c r="AA246" s="5" t="n"/>
-      <c r="AB246" s="5" t="n"/>
-      <c r="AC246" s="5" t="n"/>
+      <c r="Y246" s="5" t="inlineStr">
+        <is>
+          <t>Customer and marketer volume, margin, and relationship data | channel economics | market context (CM-1-3-1-1)</t>
+        </is>
+      </c>
+      <c r="Z246" s="5" t="inlineStr">
+        <is>
+          <t>Governed customer-and-marketer findings</t>
+        </is>
+      </c>
+      <c r="AA246" s="5" t="inlineStr">
+        <is>
+          <t>enables: Customer And Marketer Value Proposition | enables: Insight and Metrics | informed-by: Market Analysis</t>
+        </is>
+      </c>
+      <c r="AB246" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC246" s="5" t="inlineStr">
+        <is>
+          <t>periodic</t>
+        </is>
+      </c>
       <c r="AD246" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -33517,18 +34429,75 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U247" s="5" t="n"/>
-      <c r="V247" s="5" t="n"/>
-      <c r="W247" s="5" t="n"/>
+      <c r="N247" t="inlineStr">
+        <is>
+          <t>Source and collect customer and marketer data for the analysis cycle — volumes, margins, service and relationship records, marketer network data, and external context — under the applicable data controls, organized for analysis.</t>
+        </is>
+      </c>
+      <c r="O247" t="inlineStr">
+        <is>
+          <t>Covers customer-and-marketer data sourcing: internal volume, margin, service, and relationship data from their accountable owners; marketer network and performance data; external market context; provenance and currency recording; organization for analysis (CM-1-3-1-4-3). Commercially sensitive counterparty data handled per its classification; personal and behavioral data under the shared governance statement recorded at CM-1-3-1-4. Excludes internal data production (accountable owners); the analysis (CM-1-3-1-4-3); credit data ownership (batch 11 boundary).</t>
+        </is>
+      </c>
+      <c r="P247" t="inlineStr">
+        <is>
+          <t>Collect volume, margin, service, and relationship data | collect marketer network data and external context | record provenance and organize for analysis</t>
+        </is>
+      </c>
+      <c r="Q247" t="inlineStr">
+        <is>
+          <t>Internal data production (owners) | analysis (CM-1-3-1-4-3) | credit data (batch 11 boundary)</t>
+        </is>
+      </c>
+      <c r="T247" t="inlineStr">
+        <is>
+          <t>Batch 21 (2026-09-20). Shared lifecycle step, customer/marketer instance. APQC candidate is a WEAK account-data match.</t>
+        </is>
+      </c>
+      <c r="U247" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V247" s="5" t="inlineStr">
+        <is>
+          <t>The counterparty facts, complete and controlled, ready to analyze.</t>
+        </is>
+      </c>
+      <c r="W247" s="5" t="inlineStr">
+        <is>
+          <t>SRC-APQC-PCF-001</t>
+        </is>
+      </c>
       <c r="X247" s="5" t="n"/>
-      <c r="Y247" s="5" t="n"/>
-      <c r="Z247" s="5" t="n"/>
-      <c r="AA247" s="5" t="n"/>
-      <c r="AB247" s="5" t="n"/>
-      <c r="AC247" s="5" t="n"/>
+      <c r="Y247" s="5" t="inlineStr">
+        <is>
+          <t>Internal volume/margin/service data | marketer network data | market context</t>
+        </is>
+      </c>
+      <c r="Z247" s="5" t="inlineStr">
+        <is>
+          <t>Qualified customer-and-marketer data</t>
+        </is>
+      </c>
+      <c r="AA247" s="5" t="inlineStr">
+        <is>
+          <t>follows: Define Analysis Objectives &amp; Scope | precedes: Analyze Data | governed-by: Customer And Marketer Analysis</t>
+        </is>
+      </c>
+      <c r="AB247" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC247" s="5" t="inlineStr">
+        <is>
+          <t>periodic</t>
+        </is>
+      </c>
       <c r="AD247" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -33591,18 +34560,75 @@
           <t>strong APQC candidate but no validator agreed</t>
         </is>
       </c>
-      <c r="U248" s="5" t="n"/>
-      <c r="V248" s="5" t="n"/>
-      <c r="W248" s="5" t="n"/>
+      <c r="N248" t="inlineStr">
+        <is>
+          <t>Define each customer-and-marketer analysis cycle's objectives, questions, scope, and method with the consuming stakeholders — which segments, channels, marketers, and periods, answering which proposition and channel questions.</t>
+        </is>
+      </c>
+      <c r="O248" t="inlineStr">
+        <is>
+          <t>Covers framing: agreeing decision-supporting questions with proposition, channel-strategy, and sales-planning consumers; setting customer-segment, channel, marketer, geography, and period scope; selecting methods; setting deliverables and timing. Excludes the supported decisions (consumers); analysis execution (CM-1-3-1-4-3); data collection (CM-1-3-1-4-1).</t>
+        </is>
+      </c>
+      <c r="P248" t="inlineStr">
+        <is>
+          <t>Agree proposition and channel questions with consumers | set segment, channel, and marketer scope | select methods | set deliverables and timing</t>
+        </is>
+      </c>
+      <c r="Q248" t="inlineStr">
+        <is>
+          <t>Supported decisions (consumers) | analysis (CM-1-3-1-4-3) | collection (CM-1-3-1-4-1)</t>
+        </is>
+      </c>
+      <c r="T248" t="inlineStr">
+        <is>
+          <t>Batch 21 (2026-09-20). Shared lifecycle step, customer/marketer instance — first step per the normalized order. APQC 'Define objectives' STRONG/NO SOURCE — honored.</t>
+        </is>
+      </c>
+      <c r="U248" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V248" s="5" t="inlineStr">
+        <is>
+          <t>Counterparty analysis aimed at channel and proposition decisions.</t>
+        </is>
+      </c>
+      <c r="W248" s="5" t="inlineStr">
+        <is>
+          <t>SRC-APQC-PCF-001</t>
+        </is>
+      </c>
       <c r="X248" s="5" t="n"/>
-      <c r="Y248" s="5" t="n"/>
-      <c r="Z248" s="5" t="n"/>
-      <c r="AA248" s="5" t="n"/>
-      <c r="AB248" s="5" t="n"/>
-      <c r="AC248" s="5" t="n"/>
+      <c r="Y248" s="5" t="inlineStr">
+        <is>
+          <t>Consumer decision needs (CM-1-3-2-2/-4) | prior findings</t>
+        </is>
+      </c>
+      <c r="Z248" s="5" t="inlineStr">
+        <is>
+          <t>Agreed objectives, scope, and method per cycle</t>
+        </is>
+      </c>
+      <c r="AA248" s="5" t="inlineStr">
+        <is>
+          <t>precedes: Source &amp; Collect Information | precedes: Analyze Data | precedes: Document Findings | governed-by: Customer And Marketer Analysis</t>
+        </is>
+      </c>
+      <c r="AB248" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC248" s="5" t="inlineStr">
+        <is>
+          <t>periodic</t>
+        </is>
+      </c>
       <c r="AD248" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -33670,18 +34696,75 @@
           <t>strong APQC candidate but no validator agreed</t>
         </is>
       </c>
-      <c r="U249" s="5" t="n"/>
-      <c r="V249" s="5" t="n"/>
-      <c r="W249" s="5" t="n"/>
+      <c r="N249" t="inlineStr">
+        <is>
+          <t>Analyze customer and marketer data against the defined objectives — needs and segment analysis, channel and counterparty economics, performance and share-of-wallet, and relationship health — producing evidenced results with assumptions and confidence stated.</t>
+        </is>
+      </c>
+      <c r="O249" t="inlineStr">
+        <is>
+          <t>Covers analysis execution: customer and marketer segment analysis on the marketing lens; channel and counterparty economics; volume, margin, and share-of-wallet performance; relationship health and retention risk; assumptions and confidence stated. Assess relationship health and retention risk as an analytical signal; do not own account interventions, retention offers, sales actions, or account-management execution. Cost-to-serve economics come from CM-1-2-6-1-3 (batch 19) as governed input; credit risk stays with the credit process (batch 11 boundary). Excludes decisions (consumers); cost-to-serve production (CM-1-2-6-1-3); credit assessment (batch 11 boundary); account interventions and sales actions (CM-1-3-6); documentation (CM-1-3-1-4-4).</t>
+        </is>
+      </c>
+      <c r="P249" t="inlineStr">
+        <is>
+          <t>Analyze segments, needs, and counterparty economics | analyze performance and share-of-wallet | assess relationship health and retention risk as an analytical signal | state assumptions and confidence</t>
+        </is>
+      </c>
+      <c r="Q249" t="inlineStr">
+        <is>
+          <t>Decisions (consumers) | cost-to-serve production (CM-1-2-6-1-3) | credit assessment (batch 11 boundary) | account interventions and sales actions (CM-1-3-6) | documentation (CM-1-3-1-4-4)</t>
+        </is>
+      </c>
+      <c r="T249" t="inlineStr">
+        <is>
+          <t>Batch 21 (2026-09-20). Shared lifecycle step, customer/marketer instance; consumes batch 19 cost-to-serve as governed input; relationship health is an analytical signal, never account-management execution (review boundary protecting the future CM-1-3-6 branch). APQC 'Analyze data' STRONG/NO SOURCE — honored.</t>
+        </is>
+      </c>
+      <c r="U249" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V249" s="5" t="inlineStr">
+        <is>
+          <t>Know each customer and marketer relationship as well as the numbers allow.</t>
+        </is>
+      </c>
+      <c r="W249" s="5" t="inlineStr">
+        <is>
+          <t>SRC-APQC-PCF-001</t>
+        </is>
+      </c>
       <c r="X249" s="5" t="n"/>
-      <c r="Y249" s="5" t="n"/>
-      <c r="Z249" s="5" t="n"/>
-      <c r="AA249" s="5" t="n"/>
-      <c r="AB249" s="5" t="n"/>
-      <c r="AC249" s="5" t="n"/>
+      <c r="Y249" s="5" t="inlineStr">
+        <is>
+          <t>Qualified data (CM-1-3-1-4-1) | cost-to-serve assessments (CM-1-2-6-1-3) | objectives (CM-1-3-1-4-2)</t>
+        </is>
+      </c>
+      <c r="Z249" s="5" t="inlineStr">
+        <is>
+          <t>Evidenced customer-and-marketer results</t>
+        </is>
+      </c>
+      <c r="AA249" s="5" t="inlineStr">
+        <is>
+          <t>follows: Source &amp; Collect Information | precedes: Document Findings | uses-input: Assess Cost-to-Serve Performance</t>
+        </is>
+      </c>
+      <c r="AB249" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC249" s="5" t="inlineStr">
+        <is>
+          <t>periodic</t>
+        </is>
+      </c>
       <c r="AD249" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -33749,18 +34832,75 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U250" s="5" t="n"/>
-      <c r="V250" s="5" t="n"/>
-      <c r="W250" s="5" t="n"/>
+      <c r="N250" t="inlineStr">
+        <is>
+          <t>Document and distribute customer-and-marketer findings — governed records with evidence, assumptions, and confidence, handled per commercial-sensitivity classification — to proposition, channel, and sales consumers and Insight and Metrics, maintaining the findings library.</t>
+        </is>
+      </c>
+      <c r="O250" t="inlineStr">
+        <is>
+          <t>Covers findings documentation: governed records with evidence and confidence; commercially sensitive counterparty findings distributed per classification; distribution to agreed consumers and CM-1-3-1-6; versioned library maintenance. Findings records preserve the evidence lineage, source-use restrictions, assumptions, analytical method, confidence/uncertainty, and applicable commercial, privacy, and competition-sensitivity classification. Excludes the analysis (CM-1-3-1-4-3); consumer decisions; records-retention policy (governance owner).</t>
+        </is>
+      </c>
+      <c r="P250" t="inlineStr">
+        <is>
+          <t>Produce governed findings records | distribute per commercial-sensitivity classification | maintain the versioned library</t>
+        </is>
+      </c>
+      <c r="Q250" t="inlineStr">
+        <is>
+          <t>Analysis (CM-1-3-1-4-3) | decisions (consumers) | retention policy (governance owner)</t>
+        </is>
+      </c>
+      <c r="T250" t="inlineStr">
+        <is>
+          <t>Batch 21 (2026-09-20). Shared lifecycle step, customer/marketer instance; counterparty confidentiality respected; shared evidence-lineage statement applies. APQC 'Document trade' is a false match.</t>
+        </is>
+      </c>
+      <c r="U250" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V250" s="5" t="inlineStr">
+        <is>
+          <t>Counterparty insight shared with the right people and no one else.</t>
+        </is>
+      </c>
+      <c r="W250" s="5" t="inlineStr">
+        <is>
+          <t>SRC-APQC-PCF-001</t>
+        </is>
+      </c>
       <c r="X250" s="5" t="n"/>
-      <c r="Y250" s="5" t="n"/>
-      <c r="Z250" s="5" t="n"/>
-      <c r="AA250" s="5" t="n"/>
-      <c r="AB250" s="5" t="n"/>
-      <c r="AC250" s="5" t="n"/>
+      <c r="Y250" s="5" t="inlineStr">
+        <is>
+          <t>Analysis results (CM-1-3-1-4-3) | classification rules</t>
+        </is>
+      </c>
+      <c r="Z250" s="5" t="inlineStr">
+        <is>
+          <t>Governed, classification-controlled findings</t>
+        </is>
+      </c>
+      <c r="AA250" s="5" t="inlineStr">
+        <is>
+          <t>follows: Analyze Data | enables: Insight and Metrics</t>
+        </is>
+      </c>
+      <c r="AB250" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC250" s="5" t="inlineStr">
+        <is>
+          <t>periodic</t>
+        </is>
+      </c>
       <c r="AD250" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -33828,18 +34968,75 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U251" s="5" t="n"/>
-      <c r="V251" s="5" t="n"/>
-      <c r="W251" s="5" t="n"/>
+      <c r="N251" t="inlineStr">
+        <is>
+          <t>Analyze competitors in the company's downstream markets — their positions, conduct, capabilities, network moves, and likely responses — through a recurring, governed analysis cycle using legitimately obtained information, so strategy anticipates the competition it will actually face.</t>
+        </is>
+      </c>
+      <c r="O251" t="inlineStr">
+        <is>
+          <t>Covers the recurring competitor-analysis lifecycle: sourcing legitimately obtainable competitor information (CM-1-3-1-5-1); framing cycles (CM-1-3-1-5-2); analyzing competitor positions, conduct, economics, and likely responses (CM-1-3-1-5-3); documenting governed findings (CM-1-3-1-5-4). Competitive intelligence is gathered only from legitimate sources and methods, within competition-law boundaries owned by Legal &amp; Corporate Communications and the compliance framework (batch 16). The process must not solicit, receive, retain, or use competitively sensitive information obtained through improper channels, including non-public competitor pricing, future commercial plans, capacity intentions, customer terms, or strategic information where acquisition or use would breach law, confidentiality obligations, or competition-policy controls. It may not determine competition-law legality independently; concerns are referred to Legal &amp; Corporate Communications and the compliance framework. Excludes market-structure analysis (CM-1-3-1-1); competition-law compliance ownership (Legal, compliance per batch 16); strategy decisions (CM-1-3-2/3); pricing decisions (CM-1-3-3-2, CM-1-3-6-3).</t>
+        </is>
+      </c>
+      <c r="P251" t="inlineStr">
+        <is>
+          <t>Run the recurring competitor-analysis cycle on legitimate sources | analyze competitor positions, conduct, and likely responses | maintain evidenced competitive understanding | feed strategy and Insight and Metrics</t>
+        </is>
+      </c>
+      <c r="Q251" t="inlineStr">
+        <is>
+          <t>Market-structure analysis (CM-1-3-1-1) | competition-law compliance ownership (Legal, CM-1-2-4-3 framework) | strategy decisions (CM-1-3-2/3) | pricing decisions (CM-1-3-3-2, CM-1-3-6-3) | improper-channel information (prohibited; referred to Legal/Compliance)</t>
+        </is>
+      </c>
+      <c r="T251" t="inlineStr">
+        <is>
+          <t>Batch 21 (2026-09-20). Q2 partition: competitor conduct and position here; market structure at CM-1-3-1-1. Review rule added verbatim: no solicitation, receipt, retention, or use of competitively sensitive information from improper channels; competition-law legality is never determined independently — concerns go to Legal/Compliance. Follow-up (review): if this branch is operationalized, register a legal/competition-policy source or the approved enterprise competition-law policy — the current CFTC/EIA source set carries no antitrust authority. Shared lifecycle, fifth instance. Batch 21 durable rule (review): "Marketing Analysis produces governed evidence, insight, hypotheses, and recommendations. It does not itself set strategy, approve investments, establish prices, allocate product, publish the enterprise forecast, define enterprise KPIs, make commercial offers, or execute campaigns." APQC candidate is a WEAK pricing match.</t>
+        </is>
+      </c>
+      <c r="U251" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V251" s="5" t="inlineStr">
+        <is>
+          <t>Never surprised by a competitor move the evidence already signaled.</t>
+        </is>
+      </c>
+      <c r="W251" s="5" t="inlineStr">
+        <is>
+          <t>SRC-EIA-PMM-001 | SRC-APQC-PCF-001</t>
+        </is>
+      </c>
       <c r="X251" s="5" t="n"/>
-      <c r="Y251" s="5" t="n"/>
-      <c r="Z251" s="5" t="n"/>
-      <c r="AA251" s="5" t="n"/>
-      <c r="AB251" s="5" t="n"/>
-      <c r="AC251" s="5" t="n"/>
+      <c r="Y251" s="5" t="inlineStr">
+        <is>
+          <t>Public and licensed competitor information | market observations | network and pricing observations from legitimate sources</t>
+        </is>
+      </c>
+      <c r="Z251" s="5" t="inlineStr">
+        <is>
+          <t>Governed competitor-analysis findings</t>
+        </is>
+      </c>
+      <c r="AA251" s="5" t="inlineStr">
+        <is>
+          <t>enables: Brand Strategy | enables: Insight and Metrics | informed-by: Market Analysis</t>
+        </is>
+      </c>
+      <c r="AB251" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC251" s="5" t="inlineStr">
+        <is>
+          <t>periodic</t>
+        </is>
+      </c>
       <c r="AD251" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -33907,18 +35104,75 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U252" s="5" t="n"/>
-      <c r="V252" s="5" t="n"/>
-      <c r="W252" s="5" t="n"/>
+      <c r="N252" t="inlineStr">
+        <is>
+          <t>Source and collect competitor information from legitimate sources — public filings and disclosures, licensed market data, observable market conduct, and published network and pricing information — recording provenance, and never through anti-competitive exchange or illegitimate means.</t>
+        </is>
+      </c>
+      <c r="O252" t="inlineStr">
+        <is>
+          <t>Covers competitor-information sourcing: public and licensed sources, observable conduct, and published data; provenance recording for every item; source-legitimacy screening under the compliance framework. The process must not solicit, receive, retain, or use competitively sensitive information obtained through improper channels, including non-public competitor pricing, future commercial plans, capacity intentions, customer terms, or strategic information where acquisition or use would breach law, confidentiality obligations, or competition-policy controls. It may not determine competition-law legality independently; concerns are referred to Legal &amp; Corporate Communications and the compliance framework. Information offered through improper channels is refused and reported per procedure. Competition-law boundaries are owned by Legal and the compliance framework (batch 16). Excludes the analysis (CM-1-3-1-5-3); competition-law ownership (Legal, compliance); any illegitimate or anti-competitive acquisition (prohibited, reported per procedure).</t>
+        </is>
+      </c>
+      <c r="P252" t="inlineStr">
+        <is>
+          <t>Collect from public, licensed, and observable legitimate sources | record provenance for every item | screen source legitimacy and refuse and report improper offers</t>
+        </is>
+      </c>
+      <c r="Q252" t="inlineStr">
+        <is>
+          <t>Analysis (CM-1-3-1-5-3) | competition-law ownership (Legal, compliance) | illegitimate acquisition (prohibited)</t>
+        </is>
+      </c>
+      <c r="T252" t="inlineStr">
+        <is>
+          <t>Batch 21 (2026-09-20). Shared lifecycle step, competitor instance, with the legitimacy screen: provenance recorded, improper offers refused and reported, legality questions referred to Legal/Compliance (batch 16 compliance architecture; review prohibition applied verbatim). APQC candidate is a WEAK account-data match.</t>
+        </is>
+      </c>
+      <c r="U252" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V252" s="5" t="inlineStr">
+        <is>
+          <t>Competitive information the company can defend having.</t>
+        </is>
+      </c>
+      <c r="W252" s="5" t="inlineStr">
+        <is>
+          <t>SRC-APQC-PCF-001</t>
+        </is>
+      </c>
       <c r="X252" s="5" t="n"/>
-      <c r="Y252" s="5" t="n"/>
-      <c r="Z252" s="5" t="n"/>
-      <c r="AA252" s="5" t="n"/>
-      <c r="AB252" s="5" t="n"/>
-      <c r="AC252" s="5" t="n"/>
+      <c r="Y252" s="5" t="inlineStr">
+        <is>
+          <t>Public filings and disclosures | licensed data | legitimate market observations</t>
+        </is>
+      </c>
+      <c r="Z252" s="5" t="inlineStr">
+        <is>
+          <t>Provenance-recorded, legitimacy-screened competitor information</t>
+        </is>
+      </c>
+      <c r="AA252" s="5" t="inlineStr">
+        <is>
+          <t>follows: Define Analysis Objectives &amp; Scope | precedes: Analyze Data | governed-by: Competitor Analysis</t>
+        </is>
+      </c>
+      <c r="AB252" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC252" s="5" t="inlineStr">
+        <is>
+          <t>periodic</t>
+        </is>
+      </c>
       <c r="AD252" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -33981,18 +35235,75 @@
           <t>strong APQC candidate but no validator agreed</t>
         </is>
       </c>
-      <c r="U253" s="5" t="n"/>
-      <c r="V253" s="5" t="n"/>
-      <c r="W253" s="5" t="n"/>
+      <c r="N253" t="inlineStr">
+        <is>
+          <t>Define each competitor-analysis cycle's objectives, questions, scope, and method with the consuming stakeholders — which competitors, markets, and dimensions, answering which strategic and response questions.</t>
+        </is>
+      </c>
+      <c r="O253" t="inlineStr">
+        <is>
+          <t>Covers framing: agreeing decision-supporting questions with strategy, planning, and pricing consumers; setting competitor, market, and dimension scope; selecting methods within the legitimate-sources rule; setting deliverables and timing. Excludes the supported decisions (consumers); analysis execution (CM-1-3-1-5-3); collection (CM-1-3-1-5-1).</t>
+        </is>
+      </c>
+      <c r="P253" t="inlineStr">
+        <is>
+          <t>Agree strategic and response questions with consumers | set competitor, market, and dimension scope | select methods within the legitimate-sources rule | set deliverables and timing</t>
+        </is>
+      </c>
+      <c r="Q253" t="inlineStr">
+        <is>
+          <t>Supported decisions (consumers) | analysis (CM-1-3-1-5-3) | collection (CM-1-3-1-5-1)</t>
+        </is>
+      </c>
+      <c r="T253" t="inlineStr">
+        <is>
+          <t>Batch 21 (2026-09-20). Shared lifecycle step, competitor instance — first step per the normalized order. APQC 'Define objectives' STRONG/NO SOURCE — honored.</t>
+        </is>
+      </c>
+      <c r="U253" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V253" s="5" t="inlineStr">
+        <is>
+          <t>Competitive questions worth answering, scoped to what can legitimately be known.</t>
+        </is>
+      </c>
+      <c r="W253" s="5" t="inlineStr">
+        <is>
+          <t>SRC-APQC-PCF-001</t>
+        </is>
+      </c>
       <c r="X253" s="5" t="n"/>
-      <c r="Y253" s="5" t="n"/>
-      <c r="Z253" s="5" t="n"/>
-      <c r="AA253" s="5" t="n"/>
-      <c r="AB253" s="5" t="n"/>
-      <c r="AC253" s="5" t="n"/>
+      <c r="Y253" s="5" t="inlineStr">
+        <is>
+          <t>Strategy and pricing questions | prior findings</t>
+        </is>
+      </c>
+      <c r="Z253" s="5" t="inlineStr">
+        <is>
+          <t>Agreed objectives, scope, and method per cycle</t>
+        </is>
+      </c>
+      <c r="AA253" s="5" t="inlineStr">
+        <is>
+          <t>precedes: Source &amp; Collect Information | precedes: Analyze Data | precedes: Document Findings | governed-by: Competitor Analysis</t>
+        </is>
+      </c>
+      <c r="AB253" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC253" s="5" t="inlineStr">
+        <is>
+          <t>periodic</t>
+        </is>
+      </c>
       <c r="AD253" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -34060,18 +35371,75 @@
           <t>strong APQC candidate but no validator agreed</t>
         </is>
       </c>
-      <c r="U254" s="5" t="n"/>
-      <c r="V254" s="5" t="n"/>
-      <c r="W254" s="5" t="n"/>
+      <c r="N254" t="inlineStr">
+        <is>
+          <t>Analyze competitor information against the defined objectives — position and share assessment, conduct and strategy inference, capability and economics estimation, and likely-response analysis — producing evidenced results that state what is known, inferred, and assumed.</t>
+        </is>
+      </c>
+      <c r="O254" t="inlineStr">
+        <is>
+          <t>Covers competitor-analysis execution: position and share assessment from legitimate data; conduct pattern and strategy inference; capability and economics estimation with stated uncertainty; likely-response and scenario analysis; explicit separation of known facts, inferences, and assumptions. Excludes decisions (consumers); market-structure analysis (CM-1-3-1-1); documentation (CM-1-3-1-5-4).</t>
+        </is>
+      </c>
+      <c r="P254" t="inlineStr">
+        <is>
+          <t>Assess positions and shares from legitimate data | infer conduct and strategy patterns | estimate capabilities and economics with stated uncertainty | analyze likely responses, separating fact from inference</t>
+        </is>
+      </c>
+      <c r="Q254" t="inlineStr">
+        <is>
+          <t>Decisions (consumers) | market-structure analysis (CM-1-3-1-1) | documentation (CM-1-3-1-5-4)</t>
+        </is>
+      </c>
+      <c r="T254" t="inlineStr">
+        <is>
+          <t>Batch 21 (2026-09-20). Shared lifecycle step, competitor instance; fact/inference/assumption separation is the quality rule. APQC 'Analyze data' STRONG/NO SOURCE — honored.</t>
+        </is>
+      </c>
+      <c r="U254" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V254" s="5" t="inlineStr">
+        <is>
+          <t>Competitive judgment that knows what it knows and admits what it guesses.</t>
+        </is>
+      </c>
+      <c r="W254" s="5" t="inlineStr">
+        <is>
+          <t>SRC-APQC-PCF-001</t>
+        </is>
+      </c>
       <c r="X254" s="5" t="n"/>
-      <c r="Y254" s="5" t="n"/>
-      <c r="Z254" s="5" t="n"/>
-      <c r="AA254" s="5" t="n"/>
-      <c r="AB254" s="5" t="n"/>
-      <c r="AC254" s="5" t="n"/>
+      <c r="Y254" s="5" t="inlineStr">
+        <is>
+          <t>Screened competitor information (CM-1-3-1-5-1) | objectives (CM-1-3-1-5-2) | market context (CM-1-3-1-1)</t>
+        </is>
+      </c>
+      <c r="Z254" s="5" t="inlineStr">
+        <is>
+          <t>Evidenced competitor results with stated confidence</t>
+        </is>
+      </c>
+      <c r="AA254" s="5" t="inlineStr">
+        <is>
+          <t>follows: Source &amp; Collect Information | precedes: Document Findings</t>
+        </is>
+      </c>
+      <c r="AB254" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC254" s="5" t="inlineStr">
+        <is>
+          <t>periodic</t>
+        </is>
+      </c>
       <c r="AD254" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -34139,18 +35507,75 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U255" s="5" t="n"/>
-      <c r="V255" s="5" t="n"/>
-      <c r="W255" s="5" t="n"/>
+      <c r="N255" t="inlineStr">
+        <is>
+          <t>Document and distribute competitor-analysis findings — governed records separating fact, inference, and assumption, handled per sensitivity classification — to strategy, planning, and pricing consumers and Insight and Metrics, maintaining the findings library.</t>
+        </is>
+      </c>
+      <c r="O255" t="inlineStr">
+        <is>
+          <t>Covers findings documentation: governed records with the fact/inference/assumption separation preserved; sensitivity-classified distribution to agreed consumers and CM-1-3-1-6; versioned library maintenance. Findings records preserve the evidence lineage, source-use restrictions, assumptions, analytical method, confidence/uncertainty, and applicable commercial, privacy, and competition-sensitivity classification. Excludes the analysis (CM-1-3-1-5-3); consumer decisions; records-retention policy (governance owner).</t>
+        </is>
+      </c>
+      <c r="P255" t="inlineStr">
+        <is>
+          <t>Produce governed findings preserving fact/inference separation | distribute per sensitivity classification | maintain the versioned library</t>
+        </is>
+      </c>
+      <c r="Q255" t="inlineStr">
+        <is>
+          <t>Analysis (CM-1-3-1-5-3) | decisions (consumers) | retention policy (governance owner)</t>
+        </is>
+      </c>
+      <c r="T255" t="inlineStr">
+        <is>
+          <t>Batch 21 (2026-09-20). Shared lifecycle step, competitor instance; shared evidence-lineage statement applies, including competition-sensitivity classification. APQC 'Document trade' is a false match.</t>
+        </is>
+      </c>
+      <c r="U255" s="5" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="V255" s="5" t="inlineStr">
+        <is>
+          <t>Competitive intelligence that stays honest as it travels.</t>
+        </is>
+      </c>
+      <c r="W255" s="5" t="inlineStr">
+        <is>
+          <t>SRC-APQC-PCF-001</t>
+        </is>
+      </c>
       <c r="X255" s="5" t="n"/>
-      <c r="Y255" s="5" t="n"/>
-      <c r="Z255" s="5" t="n"/>
-      <c r="AA255" s="5" t="n"/>
-      <c r="AB255" s="5" t="n"/>
-      <c r="AC255" s="5" t="n"/>
+      <c r="Y255" s="5" t="inlineStr">
+        <is>
+          <t>Analysis results (CM-1-3-1-5-3) | classification rules</t>
+        </is>
+      </c>
+      <c r="Z255" s="5" t="inlineStr">
+        <is>
+          <t>Governed, classified competitor findings</t>
+        </is>
+      </c>
+      <c r="AA255" s="5" t="inlineStr">
+        <is>
+          <t>follows: Analyze Data | enables: Insight and Metrics</t>
+        </is>
+      </c>
+      <c r="AB255" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC255" s="5" t="inlineStr">
+        <is>
+          <t>periodic</t>
+        </is>
+      </c>
       <c r="AD255" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -34218,18 +35643,80 @@
           <t>weak APQC candidate; manual review needed</t>
         </is>
       </c>
-      <c r="U256" s="5" t="n"/>
-      <c r="V256" s="5" t="n"/>
-      <c r="W256" s="5" t="n"/>
+      <c r="N256" t="inlineStr">
+        <is>
+          <t>The capability to synthesize governed market, company, consumer, customer/marketer, and competitor findings into decision-ready marketing insight; maintain shared marketing-analysis metrics, definitions, baselines, and evidence lineage; and monitor insight adoption and analytical effectiveness.</t>
+        </is>
+      </c>
+      <c r="O256" t="inlineStr">
+        <is>
+          <t>Covers cross-analysis synthesis and metrics stewardship as a standing capability: integrating governed findings from the five analysis processes (CM-1-3-1-1 through -5) into decision-ready insight and implications for strategy, planning, and execution consumers; packaging insight; maintaining the shared marketing-analysis metrics, definitions, baselines, and evidence lineage to analysis findings; and monitoring insight adoption, evidence reuse, and analytical effectiveness. Marketing-analysis metrics describe market conditions, customer/consumer insight, competitive position, segmentation, reach, channel economics, and analytical evidence quality. They may inform candidate KPIs but do not become enterprise KPIs unless separately classified, governed, approved, and published through the KPI Store. Excludes enterprise KPI definition and KPI Store governance (KPI workstream); marketing execution performance analysis (CM-1-3-5-5); financial performance reporting (CM-1-2-4-2, Finance); operational performance metrics owned by supply, distribution, or product domains; the subject analyses themselves (CM-1-3-1-1 through -5); strategy decisions (CM-1-3-2/3).</t>
+        </is>
+      </c>
+      <c r="P256" t="inlineStr">
+        <is>
+          <t>Synthesize the five analyses into decision-ready insight | maintain shared marketing-analysis metrics, definitions, baselines, and evidence lineage | monitor insight adoption, evidence reuse, and analytical effectiveness | serve one evidence base to strategy, planning, and execution</t>
+        </is>
+      </c>
+      <c r="Q256" t="inlineStr">
+        <is>
+          <t>Enterprise KPI definition and KPI Store governance (KPI workstream) | marketing execution performance analysis (CM-1-3-5-5) | financial performance reporting (CM-1-2-4-2) | operational metrics of supply, distribution, and product domains | the subject analyses (CM-1-3-1-1/-2/-3/-4/-5) | strategy decisions (CM-1-3-2/3)</t>
+        </is>
+      </c>
+      <c r="R256" t="inlineStr">
+        <is>
+          <t>Marketing Insight and Metrics Stewardship</t>
+        </is>
+      </c>
+      <c r="T256" t="inlineStr">
+        <is>
+          <t>Batch 21 (2026-09-20). Q1/Q4 review decision (Hamid): capability, not process — it combines three concurrent, differently cadenced functions (cross-subject synthesis and insight packaging; metrics, definitions, baselines, and evidence-lineage stewardship; insight-adoption and analytical-effectiveness monitoring) that form no single repeating lifecycle — the batch 04/07/11/12/15 capability test. Horizon: continuous. Preferred label 'Marketing Insight and Metrics Stewardship' recorded as alt label and queued for the naming pass (row name mirrors the locked taxonomy). KPI routing (review, verbatim in scope note): marketing-analysis metrics are evidence-layer measures that may inform candidate KPIs but become enterprise KPIs only through separate KPI Store classification, governance, approval, and publication (b11/12 exclusions carried forward). APQC 'Establish baseline metrics' is a WEAK partial match.</t>
+        </is>
+      </c>
+      <c r="U256" s="5" t="inlineStr">
+        <is>
+          <t>capability</t>
+        </is>
+      </c>
+      <c r="V256" s="5" t="inlineStr">
+        <is>
+          <t>One integrated, measurable evidence base under every marketing decision.</t>
+        </is>
+      </c>
+      <c r="W256" s="5" t="inlineStr">
+        <is>
+          <t>SRC-APQC-PCF-001 | SRC-EIA-PMM-001</t>
+        </is>
+      </c>
       <c r="X256" s="5" t="n"/>
-      <c r="Y256" s="5" t="n"/>
-      <c r="Z256" s="5" t="n"/>
-      <c r="AA256" s="5" t="n"/>
-      <c r="AB256" s="5" t="n"/>
-      <c r="AC256" s="5" t="n"/>
+      <c r="Y256" s="5" t="inlineStr">
+        <is>
+          <t>Governed findings from the five analyses | consumer decision calendars | metric definitions in use</t>
+        </is>
+      </c>
+      <c r="Z256" s="5" t="inlineStr">
+        <is>
+          <t>Decision-ready integrated insight and stewarded marketing-analysis metrics</t>
+        </is>
+      </c>
+      <c r="AA256" s="5" t="inlineStr">
+        <is>
+          <t>uses-input: Market Analysis | uses-input: Competitor Analysis | enables: Brand Strategy</t>
+        </is>
+      </c>
+      <c r="AB256" s="5" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="AC256" s="5" t="inlineStr">
+        <is>
+          <t>continuous</t>
+        </is>
+      </c>
       <c r="AD256" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -54487,7 +55974,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I46"/>
+  <dimension ref="A1:I47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -56412,6 +57899,53 @@
         </is>
       </c>
       <c r="I46" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>SRC-EIA-PMM-001</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>U.S. Energy Information Administration</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Petroleum Marketing Monthly (refiner, reseller, and retailer price and volume statistics by product and marketing category; EIA-782A/B survey basis)</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Monthly series; accessed 2026-09-20</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>https://www.eia.gov/petroleum/marketing/monthly/</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Government statistical authority</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>US refined-product marketing price, volume, and channel statistics for market, customer, and competitor analysis context at aggregate levels. US-only coverage; survey categories are EIA's, not the enterprise's segmentation; not evidence about individual competitors, customer behavior, consumer preferences, internal marketing design, or non-US markets; does not determine internal analysis design or ownership. Evidence only, not text to copy.</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>US marketing-statistics context for the CM-1-3-1 Marketing Analysis branch</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
         <is>
           <t>active</t>
         </is>
